--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7DF3C6-3A77-406F-9F51-A5A62CFED6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4173F6A4-F398-48E6-B3C5-3501E916ED34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -328,7 +328,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="51">
   <si>
     <t>id</t>
   </si>
@@ -385,12 +385,6 @@
   </si>
   <si>
     <t>List&lt;List&lt;int&gt;{,}&gt;{;}</t>
-  </si>
-  <si>
-    <t>rotateState</t>
-  </si>
-  <si>
-    <t>rotateStateFlag</t>
   </si>
   <si>
     <t>needExtraBet</t>
@@ -462,23 +456,39 @@
     <t>1,10010007</t>
   </si>
   <si>
-    <t>触发免费选择</t>
-  </si>
-  <si>
-    <t>1,10010009</t>
-  </si>
-  <si>
-    <t>4个触发黄金列车</t>
-  </si>
-  <si>
-    <t>5个触发黄金列车</t>
-  </si>
-  <si>
     <t>gameType</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Map&lt;int{,}int&gt;{;}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>rotateState</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,10010001</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,10010011</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发免费选择</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>4个触发免费选择触发黄金列车</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>5个触发免费选择触发黄金列车</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>spinType</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
@@ -4500,12 +4510,12 @@
     <col min="4" max="4" width="13.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="2" customWidth="1"/>
     <col min="6" max="6" width="8.5" style="4" customWidth="1"/>
-    <col min="7" max="7" width="10.125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="9.625" style="4" customWidth="1"/>
     <col min="8" max="8" width="10.625" style="2" customWidth="1"/>
     <col min="9" max="9" width="9" style="5" customWidth="1"/>
     <col min="10" max="10" width="16.125" style="6" customWidth="1"/>
-    <col min="11" max="11" width="26.375" style="6" customWidth="1"/>
-    <col min="12" max="12" width="120" style="4" customWidth="1"/>
+    <col min="11" max="11" width="14.875" style="6" customWidth="1"/>
+    <col min="12" max="12" width="47" style="4" customWidth="1"/>
     <col min="13" max="13" width="17.625" style="4" customWidth="1"/>
     <col min="14" max="14" width="24.75" style="4" customWidth="1"/>
     <col min="15" max="16" width="9" style="4"/>
@@ -4594,7 +4604,7 @@
         <v>16</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>18</v>
@@ -4614,43 +4624,43 @@
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>14</v>
@@ -4689,13 +4699,13 @@
         <v>1</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O5" s="2">
         <v>0</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:16" s="2" customFormat="1">
@@ -4730,13 +4740,13 @@
         <v>1</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O6" s="2">
         <v>0</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="2" customFormat="1">
@@ -4771,13 +4781,13 @@
         <v>1</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O7" s="2">
         <v>0</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:16" s="2" customFormat="1">
@@ -4812,13 +4822,13 @@
         <v>1</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O8" s="2">
         <v>0</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="2" customFormat="1">
@@ -4853,13 +4863,13 @@
         <v>1</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O9" s="2">
         <v>0</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="2" customFormat="1">
@@ -4894,13 +4904,13 @@
         <v>1</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O10" s="2">
         <v>0</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="2" customFormat="1">
@@ -4935,13 +4945,13 @@
         <v>1</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O11" s="2">
         <v>0</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="2" customFormat="1">
@@ -4976,13 +4986,13 @@
         <v>1</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O12" s="2">
         <v>0</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:16" s="2" customFormat="1">
@@ -5017,13 +5027,13 @@
         <v>1</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O13" s="2">
         <v>0</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="2" customFormat="1">
@@ -5058,13 +5068,13 @@
         <v>1</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O14" s="2">
         <v>0</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="2" customFormat="1">
@@ -5099,13 +5109,13 @@
         <v>1</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O15" s="2">
         <v>0</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:16" s="2" customFormat="1">
@@ -5140,13 +5150,13 @@
         <v>1</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O16" s="2">
         <v>0</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:16" s="2" customFormat="1">
@@ -5181,13 +5191,13 @@
         <v>1</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O17" s="2">
         <v>0</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:16" s="2" customFormat="1">
@@ -5222,13 +5232,13 @@
         <v>1</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O18" s="2">
         <v>0</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:16" s="2" customFormat="1">
@@ -5263,13 +5273,13 @@
         <v>1</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O19" s="2">
         <v>0</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:16" s="2" customFormat="1">
@@ -5304,13 +5314,13 @@
         <v>1</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O20" s="2">
         <v>0</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:16" s="2" customFormat="1">
@@ -5345,13 +5355,13 @@
         <v>1</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O21" s="2">
         <v>0</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:16" s="2" customFormat="1">
@@ -5386,13 +5396,13 @@
         <v>1</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O22" s="2">
         <v>0</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:16" s="2" customFormat="1">
@@ -5427,13 +5437,13 @@
         <v>1</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O23" s="2">
         <v>0</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:16" s="2" customFormat="1">
@@ -5468,13 +5478,13 @@
         <v>1</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O24" s="2">
         <v>0</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:16" s="2" customFormat="1">
@@ -5509,13 +5519,13 @@
         <v>1</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O25" s="2">
         <v>0</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:16" s="2" customFormat="1">
@@ -5550,13 +5560,13 @@
         <v>1</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O26" s="2">
         <v>0</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:16" s="2" customFormat="1">
@@ -5591,13 +5601,13 @@
         <v>1</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O27" s="2">
         <v>0</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:16" s="2" customFormat="1">
@@ -5632,13 +5642,13 @@
         <v>1</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O28" s="2">
         <v>0</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:16" s="2" customFormat="1">
@@ -5673,13 +5683,13 @@
         <v>1</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O29" s="2">
         <v>0</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:16" s="2" customFormat="1">
@@ -5714,13 +5724,13 @@
         <v>1</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O30" s="2">
         <v>0</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:16" s="2" customFormat="1">
@@ -5755,13 +5765,13 @@
         <v>1</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O31" s="2">
         <v>0</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:16" s="2" customFormat="1">
@@ -5796,13 +5806,13 @@
         <v>1</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O32" s="2">
         <v>0</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:16" s="2" customFormat="1">
@@ -5837,13 +5847,13 @@
         <v>1</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O33" s="2">
         <v>0</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:16" s="2" customFormat="1">
@@ -5878,13 +5888,13 @@
         <v>1</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O34" s="2">
         <v>0</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:16" s="2" customFormat="1">
@@ -5919,13 +5929,13 @@
         <v>1</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O35" s="2">
         <v>0</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:16" s="2" customFormat="1">
@@ -5960,13 +5970,13 @@
         <v>1</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O36" s="2">
         <v>0</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:16" s="2" customFormat="1">
@@ -6001,13 +6011,13 @@
         <v>1</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O37" s="2">
         <v>0</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:16" s="2" customFormat="1">
@@ -6042,13 +6052,13 @@
         <v>1</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O38" s="2">
         <v>0</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:16" s="2" customFormat="1">
@@ -6083,13 +6093,13 @@
         <v>2</v>
       </c>
       <c r="K39" s="9" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O39" s="2">
         <v>0</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:16" s="2" customFormat="1">
@@ -6124,13 +6134,13 @@
         <v>2</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O40" s="2">
         <v>0</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -6165,7 +6175,7 @@
         <v>2</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -6174,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -6209,7 +6219,7 @@
         <v>2</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
@@ -6218,7 +6228,7 @@
         <v>0</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -6253,7 +6263,7 @@
         <v>2</v>
       </c>
       <c r="K43" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
@@ -6262,7 +6272,7 @@
         <v>0</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -6297,7 +6307,7 @@
         <v>2</v>
       </c>
       <c r="K44" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
@@ -6306,7 +6316,7 @@
         <v>0</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -6341,7 +6351,7 @@
         <v>2</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
@@ -6350,7 +6360,7 @@
         <v>0</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -6385,7 +6395,7 @@
         <v>2</v>
       </c>
       <c r="K46" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
@@ -6394,7 +6404,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -6429,7 +6439,7 @@
         <v>2</v>
       </c>
       <c r="K47" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -6438,7 +6448,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -6473,7 +6483,7 @@
         <v>2</v>
       </c>
       <c r="K48" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
@@ -6482,7 +6492,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -6517,7 +6527,7 @@
         <v>2</v>
       </c>
       <c r="K49" s="9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
@@ -6526,7 +6536,7 @@
         <v>0</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -6561,7 +6571,7 @@
         <v>2</v>
       </c>
       <c r="K50" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
@@ -6570,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -6605,7 +6615,7 @@
         <v>2</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
@@ -6614,7 +6624,7 @@
         <v>0</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -6649,7 +6659,7 @@
         <v>2</v>
       </c>
       <c r="K52" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
@@ -6658,7 +6668,7 @@
         <v>0</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -6693,7 +6703,7 @@
         <v>2</v>
       </c>
       <c r="K53" s="9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -6702,7 +6712,7 @@
         <v>0</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -6737,7 +6747,7 @@
         <v>2</v>
       </c>
       <c r="K54" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6746,7 +6756,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -6781,7 +6791,7 @@
         <v>2</v>
       </c>
       <c r="K55" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -6790,7 +6800,7 @@
         <v>0</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -6825,7 +6835,7 @@
         <v>2</v>
       </c>
       <c r="K56" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -6834,7 +6844,7 @@
         <v>0</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -6869,7 +6879,7 @@
         <v>2</v>
       </c>
       <c r="K57" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -6878,7 +6888,7 @@
         <v>0</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -6913,7 +6923,7 @@
         <v>2</v>
       </c>
       <c r="K58" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -6922,7 +6932,7 @@
         <v>0</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -6957,7 +6967,7 @@
         <v>2</v>
       </c>
       <c r="K59" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -6966,7 +6976,7 @@
         <v>0</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -7001,7 +7011,7 @@
         <v>2</v>
       </c>
       <c r="K60" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7010,7 +7020,7 @@
         <v>0</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -7045,7 +7055,7 @@
         <v>2</v>
       </c>
       <c r="K61" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -7054,7 +7064,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -7089,7 +7099,7 @@
         <v>2</v>
       </c>
       <c r="K62" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -7098,7 +7108,7 @@
         <v>0</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -7133,7 +7143,7 @@
         <v>2</v>
       </c>
       <c r="K63" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -7142,7 +7152,7 @@
         <v>0</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -7177,7 +7187,7 @@
         <v>2</v>
       </c>
       <c r="K64" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
@@ -7186,7 +7196,7 @@
         <v>0</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -7221,7 +7231,7 @@
         <v>2</v>
       </c>
       <c r="K65" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -7230,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -7265,7 +7275,7 @@
         <v>2</v>
       </c>
       <c r="K66" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -7274,7 +7284,7 @@
         <v>0</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -7309,7 +7319,7 @@
         <v>2</v>
       </c>
       <c r="K67" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -7318,7 +7328,7 @@
         <v>0</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -7353,7 +7363,7 @@
         <v>2</v>
       </c>
       <c r="K68" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -7362,7 +7372,7 @@
         <v>0</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -7397,7 +7407,7 @@
         <v>2</v>
       </c>
       <c r="K69" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -7406,7 +7416,7 @@
         <v>0</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -7441,7 +7451,7 @@
         <v>2</v>
       </c>
       <c r="K70" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -7450,7 +7460,7 @@
         <v>0</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -7485,7 +7495,7 @@
         <v>2</v>
       </c>
       <c r="K71" s="9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
@@ -7494,7 +7504,7 @@
         <v>0</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -7529,7 +7539,7 @@
         <v>2</v>
       </c>
       <c r="K72" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -7538,7 +7548,7 @@
         <v>0</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -7573,7 +7583,7 @@
         <v>2</v>
       </c>
       <c r="K73" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -7582,7 +7592,7 @@
         <v>0</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -7618,7 +7628,7 @@
       <formula>MOD($B49,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F53:J54 L53:P73 F55:H70 I55:J73 F71:F73">
+  <conditionalFormatting sqref="F53:J54 F55:H70 I55:J73 F71:F73 L53:P73">
     <cfRule type="expression" dxfId="0" priority="3">
       <formula>MOD($B53,2)=1</formula>
     </cfRule>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4173F6A4-F398-48E6-B3C5-3501E916ED34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E5F5DB-AF16-44DF-A5C1-10F0E6A6A46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -328,7 +328,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="50">
   <si>
     <t>id</t>
   </si>
@@ -423,37 +423,19 @@
     <t>-</t>
   </si>
   <si>
-    <t>1,10010001</t>
-  </si>
-  <si>
     <t>拉火车绿火车MINI</t>
-  </si>
-  <si>
-    <t>1,10010002</t>
   </si>
   <si>
     <t>拉火车蓝火车MINOR</t>
   </si>
   <si>
-    <t>1,10010003</t>
-  </si>
-  <si>
     <t>拉火车紫火车MAJOR</t>
-  </si>
-  <si>
-    <t>1,10010004</t>
   </si>
   <si>
     <t>拉火车红火车GRAND</t>
   </si>
   <si>
-    <t>1,10010006</t>
-  </si>
-  <si>
     <t>黄金列车普通转触发</t>
-  </si>
-  <si>
-    <t>1,10010007</t>
   </si>
   <si>
     <t>gameType</t>
@@ -465,14 +447,6 @@
   </si>
   <si>
     <t>rotateState</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,10010001</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,10010011</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
@@ -490,6 +464,28 @@
   <si>
     <t>spinType</t>
     <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,10010001;2,10010001;3,10010001;4,10010001;5,10010001;6,10010001;7,10010001;</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,10010002;2,10010002;3,10010002;4,10010002;5,10010002;6,10010002;7,10010002;</t>
+  </si>
+  <si>
+    <t>1,10010003;2,10010003;3,10010003;4,10010003;5,10010003;6,10010003;7,10010003;</t>
+  </si>
+  <si>
+    <t>1,10010004;2,10010004;3,10010004;4,10010004;5,10010004;6,10010004;7,10010004;</t>
+  </si>
+  <si>
+    <t>1,10010006;2,10010006;3,10010006;4,10010006;5,10010006;6,10010006;7,10010006;</t>
+  </si>
+  <si>
+    <t>1,10010007;2,10010007;3,10010007;4,10010007;5,10010007;6,10010007;7,10010007;</t>
+  </si>
+  <si>
+    <t>1,10010011;2,10010011;3,10010011;4,10010011;5,10010011;6,10010011;7,10010011;</t>
   </si>
 </sst>
 </file>
@@ -4604,7 +4600,7 @@
         <v>16</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>18</v>
@@ -4624,13 +4620,13 @@
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>19</v>
@@ -6093,13 +6089,13 @@
         <v>2</v>
       </c>
       <c r="K39" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="O39" s="2">
         <v>0</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:16" s="2" customFormat="1">
@@ -6134,13 +6130,13 @@
         <v>2</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="O40" s="2">
         <v>0</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -6175,7 +6171,7 @@
         <v>2</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -6184,7 +6180,7 @@
         <v>0</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -6219,7 +6215,7 @@
         <v>2</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
@@ -6228,7 +6224,7 @@
         <v>0</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -6263,7 +6259,7 @@
         <v>2</v>
       </c>
       <c r="K43" s="9" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
@@ -6272,7 +6268,7 @@
         <v>0</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -6307,7 +6303,7 @@
         <v>2</v>
       </c>
       <c r="K44" s="9" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
@@ -6316,7 +6312,7 @@
         <v>0</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -6351,7 +6347,7 @@
         <v>2</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
@@ -6360,7 +6356,7 @@
         <v>0</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -6395,7 +6391,7 @@
         <v>2</v>
       </c>
       <c r="K46" s="9" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
@@ -6404,7 +6400,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -6439,7 +6435,7 @@
         <v>2</v>
       </c>
       <c r="K47" s="9" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -6448,7 +6444,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -6483,7 +6479,7 @@
         <v>2</v>
       </c>
       <c r="K48" s="9" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
@@ -6492,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -6527,7 +6523,7 @@
         <v>2</v>
       </c>
       <c r="K49" s="9" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
@@ -6536,7 +6532,7 @@
         <v>0</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -6571,7 +6567,7 @@
         <v>2</v>
       </c>
       <c r="K50" s="9" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
@@ -6580,7 +6576,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -6615,7 +6611,7 @@
         <v>2</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
@@ -6624,7 +6620,7 @@
         <v>0</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -6659,7 +6655,7 @@
         <v>2</v>
       </c>
       <c r="K52" s="9" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
@@ -6668,7 +6664,7 @@
         <v>0</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -6703,7 +6699,7 @@
         <v>2</v>
       </c>
       <c r="K53" s="9" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -6712,7 +6708,7 @@
         <v>0</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -6747,7 +6743,7 @@
         <v>2</v>
       </c>
       <c r="K54" s="9" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6756,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -6791,7 +6787,7 @@
         <v>2</v>
       </c>
       <c r="K55" s="9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -6800,7 +6796,7 @@
         <v>0</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -6835,7 +6831,7 @@
         <v>2</v>
       </c>
       <c r="K56" s="9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -6844,7 +6840,7 @@
         <v>0</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -6879,7 +6875,7 @@
         <v>2</v>
       </c>
       <c r="K57" s="9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -6888,7 +6884,7 @@
         <v>0</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -6923,7 +6919,7 @@
         <v>2</v>
       </c>
       <c r="K58" s="9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -6932,7 +6928,7 @@
         <v>0</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -6967,7 +6963,7 @@
         <v>2</v>
       </c>
       <c r="K59" s="9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -6976,7 +6972,7 @@
         <v>0</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -7011,7 +7007,7 @@
         <v>2</v>
       </c>
       <c r="K60" s="9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7020,7 +7016,7 @@
         <v>0</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -7055,7 +7051,7 @@
         <v>2</v>
       </c>
       <c r="K61" s="9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -7064,7 +7060,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -7099,7 +7095,7 @@
         <v>2</v>
       </c>
       <c r="K62" s="9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -7108,7 +7104,7 @@
         <v>0</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -7143,7 +7139,7 @@
         <v>2</v>
       </c>
       <c r="K63" s="9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -7152,7 +7148,7 @@
         <v>0</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -7187,7 +7183,7 @@
         <v>2</v>
       </c>
       <c r="K64" s="9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
@@ -7196,7 +7192,7 @@
         <v>0</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -7231,7 +7227,7 @@
         <v>2</v>
       </c>
       <c r="K65" s="9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -7240,7 +7236,7 @@
         <v>0</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -7275,7 +7271,7 @@
         <v>2</v>
       </c>
       <c r="K66" s="9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -7284,7 +7280,7 @@
         <v>0</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -7319,7 +7315,7 @@
         <v>2</v>
       </c>
       <c r="K67" s="9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -7328,7 +7324,7 @@
         <v>0</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -7363,7 +7359,7 @@
         <v>2</v>
       </c>
       <c r="K68" s="9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -7372,7 +7368,7 @@
         <v>0</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -7407,7 +7403,7 @@
         <v>2</v>
       </c>
       <c r="K69" s="9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -7416,7 +7412,7 @@
         <v>0</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -7451,7 +7447,7 @@
         <v>2</v>
       </c>
       <c r="K70" s="9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -7460,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -7495,7 +7491,7 @@
         <v>2</v>
       </c>
       <c r="K71" s="9" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
@@ -7504,7 +7500,7 @@
         <v>0</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -7539,7 +7535,7 @@
         <v>2</v>
       </c>
       <c r="K72" s="9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -7548,7 +7544,7 @@
         <v>0</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -7583,7 +7579,7 @@
         <v>2</v>
       </c>
       <c r="K73" s="9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -7592,7 +7588,7 @@
         <v>0</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -7628,7 +7624,7 @@
       <formula>MOD($B49,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F53:J54 F55:H70 I55:J73 F71:F73 L53:P73">
+  <conditionalFormatting sqref="F53:J54 L53:P73 F55:H70 I55:J73 F71:F73">
     <cfRule type="expression" dxfId="0" priority="3">
       <formula>MOD($B53,2)=1</formula>
     </cfRule>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E5F5DB-AF16-44DF-A5C1-10F0E6A6A46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8646AC53-BCB1-4533-B5CB-39C860526BBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -417,9 +417,6 @@
     <t>lineIdReward</t>
   </si>
   <si>
-    <t>13,1,2;13,2,4;13,3,6;13,4,8;15,1,5;15,2,10;15,3,15;15,4,201</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -486,6 +483,10 @@
   </si>
   <si>
     <t>1,10010011;2,10010011;3,10010011;4,10010011;5,10010011;6,10010011;7,10010011;</t>
+  </si>
+  <si>
+    <t>13,1,2;13,2,4;13,3,6;13,4,8;15,1,5;15,2,10;15,3,15;15,4,20</t>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4600,7 +4601,7 @@
         <v>16</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>18</v>
@@ -4620,13 +4621,13 @@
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>19</v>
@@ -4695,13 +4696,13 @@
         <v>1</v>
       </c>
       <c r="L5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O5" s="2">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:16" s="2" customFormat="1">
@@ -4736,13 +4737,13 @@
         <v>1</v>
       </c>
       <c r="L6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O6" s="2">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O6" s="2">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="2" customFormat="1">
@@ -4777,13 +4778,13 @@
         <v>1</v>
       </c>
       <c r="L7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O7" s="2">
-        <v>0</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:16" s="2" customFormat="1">
@@ -4818,13 +4819,13 @@
         <v>1</v>
       </c>
       <c r="L8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O8" s="2">
-        <v>0</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="2" customFormat="1">
@@ -4859,13 +4860,13 @@
         <v>1</v>
       </c>
       <c r="L9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O9" s="2">
-        <v>0</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="2" customFormat="1">
@@ -4900,13 +4901,13 @@
         <v>1</v>
       </c>
       <c r="L10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O10" s="2">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O10" s="2">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="2" customFormat="1">
@@ -4941,13 +4942,13 @@
         <v>1</v>
       </c>
       <c r="L11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O11" s="2">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O11" s="2">
-        <v>0</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="2" customFormat="1">
@@ -4982,13 +4983,13 @@
         <v>1</v>
       </c>
       <c r="L12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O12" s="2">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O12" s="2">
-        <v>0</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:16" s="2" customFormat="1">
@@ -5023,13 +5024,13 @@
         <v>1</v>
       </c>
       <c r="L13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O13" s="2">
+        <v>0</v>
+      </c>
+      <c r="P13" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O13" s="2">
-        <v>0</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="2" customFormat="1">
@@ -5064,13 +5065,13 @@
         <v>1</v>
       </c>
       <c r="L14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O14" s="2">
+        <v>0</v>
+      </c>
+      <c r="P14" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O14" s="2">
-        <v>0</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="2" customFormat="1">
@@ -5105,13 +5106,13 @@
         <v>1</v>
       </c>
       <c r="L15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O15" s="2">
+        <v>0</v>
+      </c>
+      <c r="P15" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O15" s="2">
-        <v>0</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:16" s="2" customFormat="1">
@@ -5146,13 +5147,13 @@
         <v>1</v>
       </c>
       <c r="L16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O16" s="2">
+        <v>0</v>
+      </c>
+      <c r="P16" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O16" s="2">
-        <v>0</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:16" s="2" customFormat="1">
@@ -5187,13 +5188,13 @@
         <v>1</v>
       </c>
       <c r="L17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O17" s="2">
+        <v>0</v>
+      </c>
+      <c r="P17" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O17" s="2">
-        <v>0</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:16" s="2" customFormat="1">
@@ -5228,13 +5229,13 @@
         <v>1</v>
       </c>
       <c r="L18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O18" s="2">
+        <v>0</v>
+      </c>
+      <c r="P18" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O18" s="2">
-        <v>0</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:16" s="2" customFormat="1">
@@ -5269,13 +5270,13 @@
         <v>1</v>
       </c>
       <c r="L19" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O19" s="2">
+        <v>0</v>
+      </c>
+      <c r="P19" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O19" s="2">
-        <v>0</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:16" s="2" customFormat="1">
@@ -5310,13 +5311,13 @@
         <v>1</v>
       </c>
       <c r="L20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O20" s="2">
+        <v>0</v>
+      </c>
+      <c r="P20" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O20" s="2">
-        <v>0</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:16" s="2" customFormat="1">
@@ -5351,13 +5352,13 @@
         <v>1</v>
       </c>
       <c r="L21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O21" s="2">
+        <v>0</v>
+      </c>
+      <c r="P21" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O21" s="2">
-        <v>0</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:16" s="2" customFormat="1">
@@ -5392,13 +5393,13 @@
         <v>1</v>
       </c>
       <c r="L22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O22" s="2">
+        <v>0</v>
+      </c>
+      <c r="P22" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O22" s="2">
-        <v>0</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:16" s="2" customFormat="1">
@@ -5433,13 +5434,13 @@
         <v>1</v>
       </c>
       <c r="L23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O23" s="2">
+        <v>0</v>
+      </c>
+      <c r="P23" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O23" s="2">
-        <v>0</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:16" s="2" customFormat="1">
@@ -5474,13 +5475,13 @@
         <v>1</v>
       </c>
       <c r="L24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O24" s="2">
+        <v>0</v>
+      </c>
+      <c r="P24" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O24" s="2">
-        <v>0</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:16" s="2" customFormat="1">
@@ -5515,13 +5516,13 @@
         <v>1</v>
       </c>
       <c r="L25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O25" s="2">
+        <v>0</v>
+      </c>
+      <c r="P25" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O25" s="2">
-        <v>0</v>
-      </c>
-      <c r="P25" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:16" s="2" customFormat="1">
@@ -5556,13 +5557,13 @@
         <v>1</v>
       </c>
       <c r="L26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O26" s="2">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O26" s="2">
-        <v>0</v>
-      </c>
-      <c r="P26" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:16" s="2" customFormat="1">
@@ -5597,13 +5598,13 @@
         <v>1</v>
       </c>
       <c r="L27" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O27" s="2">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O27" s="2">
-        <v>0</v>
-      </c>
-      <c r="P27" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:16" s="2" customFormat="1">
@@ -5638,13 +5639,13 @@
         <v>1</v>
       </c>
       <c r="L28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O28" s="2">
+        <v>0</v>
+      </c>
+      <c r="P28" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O28" s="2">
-        <v>0</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:16" s="2" customFormat="1">
@@ -5679,13 +5680,13 @@
         <v>1</v>
       </c>
       <c r="L29" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O29" s="2">
+        <v>0</v>
+      </c>
+      <c r="P29" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O29" s="2">
-        <v>0</v>
-      </c>
-      <c r="P29" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:16" s="2" customFormat="1">
@@ -5720,13 +5721,13 @@
         <v>1</v>
       </c>
       <c r="L30" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O30" s="2">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O30" s="2">
-        <v>0</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:16" s="2" customFormat="1">
@@ -5761,13 +5762,13 @@
         <v>1</v>
       </c>
       <c r="L31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O31" s="2">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O31" s="2">
-        <v>0</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:16" s="2" customFormat="1">
@@ -5802,13 +5803,13 @@
         <v>1</v>
       </c>
       <c r="L32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O32" s="2">
+        <v>0</v>
+      </c>
+      <c r="P32" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O32" s="2">
-        <v>0</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:16" s="2" customFormat="1">
@@ -5843,13 +5844,13 @@
         <v>1</v>
       </c>
       <c r="L33" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O33" s="2">
+        <v>0</v>
+      </c>
+      <c r="P33" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O33" s="2">
-        <v>0</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:16" s="2" customFormat="1">
@@ -5884,13 +5885,13 @@
         <v>1</v>
       </c>
       <c r="L34" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O34" s="2">
+        <v>0</v>
+      </c>
+      <c r="P34" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O34" s="2">
-        <v>0</v>
-      </c>
-      <c r="P34" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:16" s="2" customFormat="1">
@@ -5925,13 +5926,13 @@
         <v>1</v>
       </c>
       <c r="L35" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O35" s="2">
+        <v>0</v>
+      </c>
+      <c r="P35" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O35" s="2">
-        <v>0</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:16" s="2" customFormat="1">
@@ -5966,13 +5967,13 @@
         <v>1</v>
       </c>
       <c r="L36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O36" s="2">
+        <v>0</v>
+      </c>
+      <c r="P36" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O36" s="2">
-        <v>0</v>
-      </c>
-      <c r="P36" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:16" s="2" customFormat="1">
@@ -6007,13 +6008,13 @@
         <v>1</v>
       </c>
       <c r="L37" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O37" s="2">
+        <v>0</v>
+      </c>
+      <c r="P37" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O37" s="2">
-        <v>0</v>
-      </c>
-      <c r="P37" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:16" s="2" customFormat="1">
@@ -6048,13 +6049,13 @@
         <v>1</v>
       </c>
       <c r="L38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O38" s="2">
+        <v>0</v>
+      </c>
+      <c r="P38" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="O38" s="2">
-        <v>0</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:16" s="2" customFormat="1">
@@ -6089,13 +6090,13 @@
         <v>2</v>
       </c>
       <c r="K39" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O39" s="2">
         <v>0</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:16" s="2" customFormat="1">
@@ -6130,13 +6131,13 @@
         <v>2</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O40" s="2">
         <v>0</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -6171,7 +6172,7 @@
         <v>2</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -6180,7 +6181,7 @@
         <v>0</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -6215,7 +6216,7 @@
         <v>2</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
@@ -6224,7 +6225,7 @@
         <v>0</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -6259,7 +6260,7 @@
         <v>2</v>
       </c>
       <c r="K43" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
@@ -6268,7 +6269,7 @@
         <v>0</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -6303,7 +6304,7 @@
         <v>2</v>
       </c>
       <c r="K44" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
@@ -6312,7 +6313,7 @@
         <v>0</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -6347,7 +6348,7 @@
         <v>2</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
@@ -6356,7 +6357,7 @@
         <v>0</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -6391,7 +6392,7 @@
         <v>2</v>
       </c>
       <c r="K46" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
@@ -6400,7 +6401,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -6435,7 +6436,7 @@
         <v>2</v>
       </c>
       <c r="K47" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -6444,7 +6445,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -6479,7 +6480,7 @@
         <v>2</v>
       </c>
       <c r="K48" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
@@ -6488,7 +6489,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -6523,7 +6524,7 @@
         <v>2</v>
       </c>
       <c r="K49" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
@@ -6532,7 +6533,7 @@
         <v>0</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -6567,7 +6568,7 @@
         <v>2</v>
       </c>
       <c r="K50" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
@@ -6576,7 +6577,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -6611,7 +6612,7 @@
         <v>2</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
@@ -6620,7 +6621,7 @@
         <v>0</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -6655,7 +6656,7 @@
         <v>2</v>
       </c>
       <c r="K52" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
@@ -6664,7 +6665,7 @@
         <v>0</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -6699,7 +6700,7 @@
         <v>2</v>
       </c>
       <c r="K53" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -6708,7 +6709,7 @@
         <v>0</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -6743,7 +6744,7 @@
         <v>2</v>
       </c>
       <c r="K54" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6752,7 +6753,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -6787,7 +6788,7 @@
         <v>2</v>
       </c>
       <c r="K55" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -6796,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -6831,7 +6832,7 @@
         <v>2</v>
       </c>
       <c r="K56" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -6840,7 +6841,7 @@
         <v>0</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -6875,7 +6876,7 @@
         <v>2</v>
       </c>
       <c r="K57" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -6884,7 +6885,7 @@
         <v>0</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -6919,7 +6920,7 @@
         <v>2</v>
       </c>
       <c r="K58" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -6928,7 +6929,7 @@
         <v>0</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -6963,7 +6964,7 @@
         <v>2</v>
       </c>
       <c r="K59" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -6972,7 +6973,7 @@
         <v>0</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -7007,7 +7008,7 @@
         <v>2</v>
       </c>
       <c r="K60" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7016,7 +7017,7 @@
         <v>0</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -7051,7 +7052,7 @@
         <v>2</v>
       </c>
       <c r="K61" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -7060,7 +7061,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -7095,7 +7096,7 @@
         <v>2</v>
       </c>
       <c r="K62" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -7104,7 +7105,7 @@
         <v>0</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -7139,7 +7140,7 @@
         <v>2</v>
       </c>
       <c r="K63" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -7148,7 +7149,7 @@
         <v>0</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -7183,7 +7184,7 @@
         <v>2</v>
       </c>
       <c r="K64" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
@@ -7192,7 +7193,7 @@
         <v>0</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -7227,7 +7228,7 @@
         <v>2</v>
       </c>
       <c r="K65" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -7236,7 +7237,7 @@
         <v>0</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -7271,7 +7272,7 @@
         <v>2</v>
       </c>
       <c r="K66" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -7280,7 +7281,7 @@
         <v>0</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -7315,7 +7316,7 @@
         <v>2</v>
       </c>
       <c r="K67" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -7324,7 +7325,7 @@
         <v>0</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -7359,7 +7360,7 @@
         <v>2</v>
       </c>
       <c r="K68" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -7368,7 +7369,7 @@
         <v>0</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -7403,7 +7404,7 @@
         <v>2</v>
       </c>
       <c r="K69" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -7412,7 +7413,7 @@
         <v>0</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -7447,7 +7448,7 @@
         <v>2</v>
       </c>
       <c r="K70" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -7456,7 +7457,7 @@
         <v>0</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -7491,7 +7492,7 @@
         <v>2</v>
       </c>
       <c r="K71" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
@@ -7500,7 +7501,7 @@
         <v>0</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -7535,7 +7536,7 @@
         <v>2</v>
       </c>
       <c r="K72" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -7544,7 +7545,7 @@
         <v>0</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -7579,7 +7580,7 @@
         <v>2</v>
       </c>
       <c r="K73" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -7588,7 +7589,7 @@
         <v>0</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8646AC53-BCB1-4533-B5CB-39C860526BBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6B1EEF-A34F-47D2-AC2C-A79C6BCB09F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$P$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$P$58</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -328,7 +328,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="50">
   <si>
     <t>id</t>
   </si>
@@ -730,14 +730,7 @@
     <cellStyle name="超链接 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
     <cellStyle name="好_Sheet1" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.7993408001953185"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -4498,7 +4491,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:P73"/>
+  <dimension ref="A1:P58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -6773,13 +6766,13 @@
         <v>0</v>
       </c>
       <c r="F55" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G55" s="2">
         <v>2</v>
       </c>
       <c r="H55" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I55" s="5">
         <v>0</v>
@@ -6802,13 +6795,13 @@
     </row>
     <row r="56" spans="1:16">
       <c r="A56" s="2">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B56" s="2">
         <v>100100</v>
       </c>
       <c r="C56" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D56" s="2">
         <v>1</v>
@@ -6817,10 +6810,10 @@
         <v>0</v>
       </c>
       <c r="F56" s="2">
-        <v>18</v>
-      </c>
-      <c r="G56" s="2">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G56" s="4">
+        <v>4</v>
       </c>
       <c r="H56" s="2">
         <v>3</v>
@@ -6832,7 +6825,7 @@
         <v>2</v>
       </c>
       <c r="K56" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -6841,18 +6834,18 @@
         <v>0</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:16">
       <c r="A57" s="2">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="B57" s="2">
         <v>100100</v>
       </c>
       <c r="C57" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D57" s="2">
         <v>1</v>
@@ -6861,10 +6854,10 @@
         <v>0</v>
       </c>
       <c r="F57" s="2">
-        <v>18</v>
-      </c>
-      <c r="G57" s="2">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G57" s="4">
+        <v>4</v>
       </c>
       <c r="H57" s="2">
         <v>4</v>
@@ -6876,7 +6869,7 @@
         <v>2</v>
       </c>
       <c r="K57" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -6885,18 +6878,18 @@
         <v>0</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58" spans="1:16">
       <c r="A58" s="2">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B58" s="2">
         <v>100100</v>
       </c>
       <c r="C58" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D58" s="2">
         <v>1</v>
@@ -6905,10 +6898,10 @@
         <v>0</v>
       </c>
       <c r="F58" s="2">
-        <v>18</v>
-      </c>
-      <c r="G58" s="2">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G58" s="4">
+        <v>4</v>
       </c>
       <c r="H58" s="2">
         <v>5</v>
@@ -6920,7 +6913,7 @@
         <v>2</v>
       </c>
       <c r="K58" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -6929,688 +6922,23 @@
         <v>0</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16">
-      <c r="A59" s="2">
-        <v>55</v>
-      </c>
-      <c r="B59" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C59" s="2">
-        <v>4</v>
-      </c>
-      <c r="D59" s="2">
-        <v>1</v>
-      </c>
-      <c r="E59" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F59" s="2">
-        <v>18</v>
-      </c>
-      <c r="G59" s="2">
-        <v>2</v>
-      </c>
-      <c r="H59" s="2">
-        <v>6</v>
-      </c>
-      <c r="I59" s="5">
-        <v>0</v>
-      </c>
-      <c r="J59" s="2">
-        <v>2</v>
-      </c>
-      <c r="K59" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2">
-        <v>0</v>
-      </c>
-      <c r="P59" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16">
-      <c r="A60" s="2">
-        <v>56</v>
-      </c>
-      <c r="B60" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C60" s="2">
-        <v>4</v>
-      </c>
-      <c r="D60" s="2">
-        <v>1</v>
-      </c>
-      <c r="E60" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F60" s="2">
-        <v>18</v>
-      </c>
-      <c r="G60" s="2">
-        <v>2</v>
-      </c>
-      <c r="H60" s="2">
-        <v>7</v>
-      </c>
-      <c r="I60" s="5">
-        <v>0</v>
-      </c>
-      <c r="J60" s="2">
-        <v>2</v>
-      </c>
-      <c r="K60" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="L60" s="2"/>
-      <c r="M60" s="2"/>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2">
-        <v>0</v>
-      </c>
-      <c r="P60" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16">
-      <c r="A61" s="2">
-        <v>57</v>
-      </c>
-      <c r="B61" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C61" s="2">
-        <v>4</v>
-      </c>
-      <c r="D61" s="2">
-        <v>1</v>
-      </c>
-      <c r="E61" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F61" s="2">
-        <v>18</v>
-      </c>
-      <c r="G61" s="2">
-        <v>2</v>
-      </c>
-      <c r="H61" s="2">
-        <v>8</v>
-      </c>
-      <c r="I61" s="5">
-        <v>0</v>
-      </c>
-      <c r="J61" s="2">
-        <v>2</v>
-      </c>
-      <c r="K61" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="L61" s="2"/>
-      <c r="M61" s="2"/>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2">
-        <v>0</v>
-      </c>
-      <c r="P61" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16">
-      <c r="A62" s="2">
-        <v>58</v>
-      </c>
-      <c r="B62" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C62" s="2">
-        <v>4</v>
-      </c>
-      <c r="D62" s="2">
-        <v>1</v>
-      </c>
-      <c r="E62" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F62" s="2">
-        <v>18</v>
-      </c>
-      <c r="G62" s="2">
-        <v>2</v>
-      </c>
-      <c r="H62" s="2">
-        <v>9</v>
-      </c>
-      <c r="I62" s="5">
-        <v>0</v>
-      </c>
-      <c r="J62" s="2">
-        <v>2</v>
-      </c>
-      <c r="K62" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="L62" s="2"/>
-      <c r="M62" s="2"/>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2">
-        <v>0</v>
-      </c>
-      <c r="P62" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16">
-      <c r="A63" s="2">
-        <v>59</v>
-      </c>
-      <c r="B63" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C63" s="2">
-        <v>4</v>
-      </c>
-      <c r="D63" s="2">
-        <v>1</v>
-      </c>
-      <c r="E63" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F63" s="2">
-        <v>18</v>
-      </c>
-      <c r="G63" s="2">
-        <v>2</v>
-      </c>
-      <c r="H63" s="2">
-        <v>10</v>
-      </c>
-      <c r="I63" s="5">
-        <v>0</v>
-      </c>
-      <c r="J63" s="2">
-        <v>2</v>
-      </c>
-      <c r="K63" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="L63" s="2"/>
-      <c r="M63" s="2"/>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2">
-        <v>0</v>
-      </c>
-      <c r="P63" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16">
-      <c r="A64" s="2">
-        <v>60</v>
-      </c>
-      <c r="B64" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C64" s="2">
-        <v>4</v>
-      </c>
-      <c r="D64" s="2">
-        <v>1</v>
-      </c>
-      <c r="E64" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F64" s="2">
-        <v>18</v>
-      </c>
-      <c r="G64" s="2">
-        <v>2</v>
-      </c>
-      <c r="H64" s="2">
-        <v>11</v>
-      </c>
-      <c r="I64" s="5">
-        <v>0</v>
-      </c>
-      <c r="J64" s="2">
-        <v>2</v>
-      </c>
-      <c r="K64" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="L64" s="2"/>
-      <c r="M64" s="2"/>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2">
-        <v>0</v>
-      </c>
-      <c r="P64" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16">
-      <c r="A65" s="2">
-        <v>61</v>
-      </c>
-      <c r="B65" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C65" s="2">
-        <v>4</v>
-      </c>
-      <c r="D65" s="2">
-        <v>1</v>
-      </c>
-      <c r="E65" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F65" s="2">
-        <v>18</v>
-      </c>
-      <c r="G65" s="2">
-        <v>2</v>
-      </c>
-      <c r="H65" s="2">
-        <v>12</v>
-      </c>
-      <c r="I65" s="5">
-        <v>0</v>
-      </c>
-      <c r="J65" s="2">
-        <v>2</v>
-      </c>
-      <c r="K65" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="L65" s="2"/>
-      <c r="M65" s="2"/>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2">
-        <v>0</v>
-      </c>
-      <c r="P65" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16">
-      <c r="A66" s="2">
-        <v>62</v>
-      </c>
-      <c r="B66" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C66" s="2">
-        <v>4</v>
-      </c>
-      <c r="D66" s="2">
-        <v>1</v>
-      </c>
-      <c r="E66" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F66" s="2">
-        <v>18</v>
-      </c>
-      <c r="G66" s="2">
-        <v>2</v>
-      </c>
-      <c r="H66" s="2">
-        <v>13</v>
-      </c>
-      <c r="I66" s="5">
-        <v>0</v>
-      </c>
-      <c r="J66" s="2">
-        <v>2</v>
-      </c>
-      <c r="K66" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="L66" s="2"/>
-      <c r="M66" s="2"/>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2">
-        <v>0</v>
-      </c>
-      <c r="P66" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16">
-      <c r="A67" s="2">
-        <v>63</v>
-      </c>
-      <c r="B67" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C67" s="2">
-        <v>4</v>
-      </c>
-      <c r="D67" s="2">
-        <v>1</v>
-      </c>
-      <c r="E67" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F67" s="2">
-        <v>18</v>
-      </c>
-      <c r="G67" s="2">
-        <v>2</v>
-      </c>
-      <c r="H67" s="2">
-        <v>14</v>
-      </c>
-      <c r="I67" s="5">
-        <v>0</v>
-      </c>
-      <c r="J67" s="2">
-        <v>2</v>
-      </c>
-      <c r="K67" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="L67" s="2"/>
-      <c r="M67" s="2"/>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2">
-        <v>0</v>
-      </c>
-      <c r="P67" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16">
-      <c r="A68" s="2">
-        <v>64</v>
-      </c>
-      <c r="B68" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C68" s="2">
-        <v>4</v>
-      </c>
-      <c r="D68" s="2">
-        <v>1</v>
-      </c>
-      <c r="E68" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F68" s="2">
-        <v>18</v>
-      </c>
-      <c r="G68" s="2">
-        <v>2</v>
-      </c>
-      <c r="H68" s="2">
-        <v>15</v>
-      </c>
-      <c r="I68" s="5">
-        <v>0</v>
-      </c>
-      <c r="J68" s="2">
-        <v>2</v>
-      </c>
-      <c r="K68" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="L68" s="2"/>
-      <c r="M68" s="2"/>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2">
-        <v>0</v>
-      </c>
-      <c r="P68" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16">
-      <c r="A69" s="2">
-        <v>65</v>
-      </c>
-      <c r="B69" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C69" s="2">
-        <v>4</v>
-      </c>
-      <c r="D69" s="2">
-        <v>1</v>
-      </c>
-      <c r="E69" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F69" s="2">
-        <v>18</v>
-      </c>
-      <c r="G69" s="2">
-        <v>2</v>
-      </c>
-      <c r="H69" s="2">
-        <v>16</v>
-      </c>
-      <c r="I69" s="5">
-        <v>0</v>
-      </c>
-      <c r="J69" s="2">
-        <v>2</v>
-      </c>
-      <c r="K69" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="L69" s="2"/>
-      <c r="M69" s="2"/>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2">
-        <v>0</v>
-      </c>
-      <c r="P69" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16">
-      <c r="A70" s="2">
-        <v>66</v>
-      </c>
-      <c r="B70" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C70" s="2">
-        <v>4</v>
-      </c>
-      <c r="D70" s="2">
-        <v>1</v>
-      </c>
-      <c r="E70" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F70" s="2">
-        <v>18</v>
-      </c>
-      <c r="G70" s="2">
-        <v>2</v>
-      </c>
-      <c r="H70" s="2">
-        <v>17</v>
-      </c>
-      <c r="I70" s="5">
-        <v>0</v>
-      </c>
-      <c r="J70" s="2">
-        <v>2</v>
-      </c>
-      <c r="K70" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="L70" s="2"/>
-      <c r="M70" s="2"/>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2">
-        <v>0</v>
-      </c>
-      <c r="P70" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16">
-      <c r="A71" s="2">
-        <v>67</v>
-      </c>
-      <c r="B71" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C71" s="2">
-        <v>1</v>
-      </c>
-      <c r="D71" s="2">
-        <v>1</v>
-      </c>
-      <c r="E71" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F71" s="2">
-        <v>17</v>
-      </c>
-      <c r="G71" s="4">
-        <v>4</v>
-      </c>
-      <c r="H71" s="2">
-        <v>3</v>
-      </c>
-      <c r="I71" s="5">
-        <v>0</v>
-      </c>
-      <c r="J71" s="2">
-        <v>2</v>
-      </c>
-      <c r="K71" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="L71" s="2"/>
-      <c r="M71" s="2"/>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2">
-        <v>0</v>
-      </c>
-      <c r="P71" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16">
-      <c r="A72" s="2">
-        <v>68</v>
-      </c>
-      <c r="B72" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C72" s="2">
-        <v>1</v>
-      </c>
-      <c r="D72" s="2">
-        <v>1</v>
-      </c>
-      <c r="E72" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F72" s="2">
-        <v>17</v>
-      </c>
-      <c r="G72" s="4">
-        <v>4</v>
-      </c>
-      <c r="H72" s="2">
-        <v>4</v>
-      </c>
-      <c r="I72" s="5">
-        <v>0</v>
-      </c>
-      <c r="J72" s="2">
-        <v>2</v>
-      </c>
-      <c r="K72" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2">
-        <v>0</v>
-      </c>
-      <c r="P72" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16">
-      <c r="A73" s="2">
-        <v>69</v>
-      </c>
-      <c r="B73" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C73" s="2">
-        <v>1</v>
-      </c>
-      <c r="D73" s="2">
-        <v>1</v>
-      </c>
-      <c r="E73" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F73" s="2">
-        <v>17</v>
-      </c>
-      <c r="G73" s="4">
-        <v>4</v>
-      </c>
-      <c r="H73" s="2">
-        <v>5</v>
-      </c>
-      <c r="I73" s="5">
-        <v>0</v>
-      </c>
-      <c r="J73" s="2">
-        <v>2</v>
-      </c>
-      <c r="K73" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="L73" s="2"/>
-      <c r="M73" s="2"/>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2">
-        <v>0</v>
-      </c>
-      <c r="P73" s="2" t="s">
         <v>40</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:P73" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="B1:P58" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="16" type="noConversion"/>
-  <conditionalFormatting sqref="B41:B73 D43:E73">
-    <cfRule type="expression" dxfId="6" priority="4">
-      <formula>MOD($B41,2)=1</formula>
+  <conditionalFormatting sqref="B41:B58 D43:E58 C5:C58 B59:P1048576 L53:P58 F55:H55 I55:J58">
+    <cfRule type="expression" dxfId="5" priority="4">
+      <formula>MOD($B5,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:P4">
-    <cfRule type="expression" dxfId="5" priority="270">
+    <cfRule type="expression" dxfId="4" priority="270">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C5:C73">
-    <cfRule type="expression" dxfId="4" priority="1">
-      <formula>MOD($B5,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D41:J42 L41:P42 G71:H71 D72:H73 B74:P1048576">
+  <conditionalFormatting sqref="D41:J42 L41:P42 G56:H56 D57:H58">
     <cfRule type="expression" dxfId="3" priority="269">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
@@ -7625,7 +6953,7 @@
       <formula>MOD($B49,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F53:J54 L53:P73 F55:H70 I55:J73 F71:F73">
+  <conditionalFormatting sqref="F53:J54 F56:F58">
     <cfRule type="expression" dxfId="0" priority="3">
       <formula>MOD($B53,2)=1</formula>
     </cfRule>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6B1EEF-A34F-47D2-AC2C-A79C6BCB09F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC2394F-0738-48FD-9072-5D2C74128067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -384,7 +384,19 @@
     <t>bool</t>
   </si>
   <si>
+    <t>Map&lt;int{,}int&gt;{;}</t>
+  </si>
+  <si>
     <t>List&lt;List&lt;int&gt;{,}&gt;{;}</t>
+  </si>
+  <si>
+    <t>gameType</t>
+  </si>
+  <si>
+    <t>rotateState</t>
+  </si>
+  <si>
+    <t>spinType</t>
   </si>
   <si>
     <t>needExtraBet</t>
@@ -402,9 +414,6 @@
     <t>bet</t>
   </si>
   <si>
-    <t>rewardType</t>
-  </si>
-  <si>
     <t>featureTriggerId</t>
   </si>
   <si>
@@ -420,80 +429,63 @@
     <t>-</t>
   </si>
   <si>
+    <t>1,10010001;2,10010001;3,10010001;4,10010001;5,10010001;6,10010001;7,10010001;</t>
+  </si>
+  <si>
     <t>拉火车绿火车MINI</t>
+  </si>
+  <si>
+    <t>1,10010002;2,10010002;3,10010002;4,10010002;5,10010002;6,10010002;7,10010002;</t>
   </si>
   <si>
     <t>拉火车蓝火车MINOR</t>
   </si>
   <si>
+    <t>1,10010003;2,10010003;3,10010003;4,10010003;5,10010003;6,10010003;7,10010003;</t>
+  </si>
+  <si>
     <t>拉火车紫火车MAJOR</t>
+  </si>
+  <si>
+    <t>1,10010004;2,10010004;3,10010004;4,10010004;5,10010004;6,10010004;7,10010004;</t>
   </si>
   <si>
     <t>拉火车红火车GRAND</t>
   </si>
   <si>
+    <t>1,10010006;2,10010012;3,10010013;4,10010014;5,10010015;6,10010016;7,10010017;</t>
+  </si>
+  <si>
     <t>黄金列车普通转触发</t>
   </si>
   <si>
-    <t>gameType</t>
+    <t>1,10010007;2,10010018;3,10010019;4,10010020;5,10010021;6,10010022;7,10010023;</t>
+  </si>
+  <si>
+    <t>触发免费选择</t>
+  </si>
+  <si>
+    <t>1,10010011;2,10010030;3,10010031;4,10010032;5,10010033;6,10010034;7,10010035;</t>
+  </si>
+  <si>
+    <t>4个触发免费选择触发黄金列车</t>
+  </si>
+  <si>
+    <t>5个触发免费选择触发黄金列车</t>
+  </si>
+  <si>
+    <t>rewardType</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
-    <t>Map&lt;int{,}int&gt;{;}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>rotateState</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>触发免费选择</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>4个触发免费选择触发黄金列车</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>5个触发免费选择触发黄金列车</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>spinType</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,10010001;2,10010001;3,10010001;4,10010001;5,10010001;6,10010001;7,10010001;</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,10010002;2,10010002;3,10010002;4,10010002;5,10010002;6,10010002;7,10010002;</t>
-  </si>
-  <si>
-    <t>1,10010003;2,10010003;3,10010003;4,10010003;5,10010003;6,10010003;7,10010003;</t>
-  </si>
-  <si>
-    <t>1,10010004;2,10010004;3,10010004;4,10010004;5,10010004;6,10010004;7,10010004;</t>
-  </si>
-  <si>
-    <t>1,10010006;2,10010006;3,10010006;4,10010006;5,10010006;6,10010006;7,10010006;</t>
-  </si>
-  <si>
-    <t>1,10010007;2,10010007;3,10010007;4,10010007;5,10010007;6,10010007;7,10010007;</t>
-  </si>
-  <si>
-    <t>1,10010011;2,10010011;3,10010011;4,10010011;5,10010011;6,10010011;7,10010011;</t>
-  </si>
-  <si>
-    <t>13,1,2;13,2,4;13,3,6;13,4,8;15,1,5;15,2,10;15,3,15;15,4,20</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <t>13,1,2;13,2,4;13,3,6;13,4,8;14,1,5;14,2,10;14,3,15;14,4,20</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -545,14 +537,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <family val="3"/>
@@ -586,6 +570,13 @@
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
@@ -598,17 +589,18 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -633,13 +625,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -670,23 +662,23 @@
   </borders>
   <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -730,7 +722,21 @@
     <cellStyle name="超链接 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
     <cellStyle name="好_Sheet1" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="8" tint="0.7993408001953185"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="8" tint="0.7993408001953185"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -786,13 +792,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
@@ -868,7 +867,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1314450"/>
+          <a:off x="685800" y="895350"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -920,7 +919,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1314450"/>
+          <a:off x="685800" y="895350"/>
           <a:ext cx="9361170" cy="9524365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -972,7 +971,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1314450"/>
+          <a:off x="685800" y="895350"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1024,7 +1023,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1314450"/>
+          <a:off x="685800" y="895350"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1076,7 +1075,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1314450"/>
+          <a:off x="685800" y="895350"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1128,7 +1127,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1314450"/>
+          <a:off x="685800" y="895350"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1180,7 +1179,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1314450"/>
+          <a:off x="685800" y="895350"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1232,7 +1231,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1314450"/>
+          <a:off x="685800" y="895350"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1284,7 +1283,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1314450"/>
+          <a:off x="685800" y="895350"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1336,7 +1335,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1314450"/>
+          <a:off x="685800" y="895350"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1388,7 +1387,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1314450"/>
+          <a:off x="685800" y="895350"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1440,7 +1439,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1314450"/>
+          <a:off x="685800" y="895350"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1492,7 +1491,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1314450"/>
+          <a:off x="685800" y="895350"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1544,7 +1543,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1314450"/>
+          <a:off x="685800" y="895350"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1596,7 +1595,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1314450"/>
+          <a:off x="685800" y="895350"/>
           <a:ext cx="9361170" cy="9524365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1648,7 +1647,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1314450"/>
+          <a:off x="685800" y="895350"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1700,7 +1699,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1314450"/>
+          <a:off x="685800" y="895350"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1752,7 +1751,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1314450"/>
+          <a:off x="685800" y="895350"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1804,7 +1803,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1314450"/>
+          <a:off x="685800" y="895350"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1856,7 +1855,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1314450"/>
+          <a:off x="685800" y="895350"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1908,7 +1907,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1960,7 +1959,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2012,7 +2011,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2064,7 +2063,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2116,7 +2115,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2168,7 +2167,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2220,7 +2219,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9361170" cy="9524365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2272,7 +2271,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2324,7 +2323,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2376,7 +2375,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2428,7 +2427,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2480,7 +2479,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2532,7 +2531,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2584,7 +2583,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2636,7 +2635,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2688,7 +2687,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2740,7 +2739,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2792,7 +2791,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2844,7 +2843,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9361170" cy="9524365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2896,7 +2895,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2948,7 +2947,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3000,7 +2999,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3052,7 +3051,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3104,7 +3103,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3156,7 +3155,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3208,7 +3207,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3260,7 +3259,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3312,7 +3311,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3364,7 +3363,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9361170" cy="10240010"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3416,7 +3415,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3468,7 +3467,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9361170" cy="9972040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3520,7 +3519,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3572,7 +3571,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3624,7 +3623,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3676,7 +3675,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9361170" cy="10240010"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3728,7 +3727,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3780,7 +3779,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3832,7 +3831,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3884,7 +3883,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9361170" cy="9781540"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3936,7 +3935,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3988,7 +3987,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9361170" cy="9524365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4040,7 +4039,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4092,7 +4091,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4144,7 +4143,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4196,7 +4195,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8648700"/>
+          <a:off x="685800" y="8229600"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4492,7 +4491,7 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:P58"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
     <col min="2" max="2" width="11" style="2" customWidth="1"/>
@@ -4512,7 +4511,7 @@
     <col min="17" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" ht="37.5" customHeight="1">
+    <row r="1" spans="1:16" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4562,7 +4561,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="2" customFormat="1">
+    <row r="2" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
@@ -4594,70 +4593,70 @@
         <v>16</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="2" customFormat="1">
+    <row r="3" spans="1:16" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="2" customFormat="1"/>
-    <row r="5" spans="1:16" s="2" customFormat="1">
+    <row r="4" spans="1:16" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -4695,10 +4694,10 @@
         <v>0</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:16" s="2" customFormat="1">
+    <row r="6" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -4736,10 +4735,10 @@
         <v>0</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:16" s="2" customFormat="1">
+    <row r="7" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>3</v>
       </c>
@@ -4777,10 +4776,10 @@
         <v>0</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:16" s="2" customFormat="1">
+    <row r="8" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>4</v>
       </c>
@@ -4818,10 +4817,10 @@
         <v>0</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:16" s="2" customFormat="1">
+    <row r="9" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>5</v>
       </c>
@@ -4859,10 +4858,10 @@
         <v>0</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:16" s="2" customFormat="1">
+    <row r="10" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>6</v>
       </c>
@@ -4900,10 +4899,10 @@
         <v>0</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:16" s="2" customFormat="1">
+    <row r="11" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>7</v>
       </c>
@@ -4941,10 +4940,10 @@
         <v>0</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:16" s="2" customFormat="1">
+    <row r="12" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>8</v>
       </c>
@@ -4982,10 +4981,10 @@
         <v>0</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:16" s="2" customFormat="1">
+    <row r="13" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>9</v>
       </c>
@@ -5023,10 +5022,10 @@
         <v>0</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:16" s="2" customFormat="1">
+    <row r="14" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>10</v>
       </c>
@@ -5064,10 +5063,10 @@
         <v>0</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:16" s="2" customFormat="1">
+    <row r="15" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>11</v>
       </c>
@@ -5105,10 +5104,10 @@
         <v>0</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:16" s="2" customFormat="1">
+    <row r="16" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>12</v>
       </c>
@@ -5146,10 +5145,10 @@
         <v>0</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:16" s="2" customFormat="1">
+    <row r="17" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>13</v>
       </c>
@@ -5187,10 +5186,10 @@
         <v>0</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:16" s="2" customFormat="1">
+    <row r="18" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>14</v>
       </c>
@@ -5228,10 +5227,10 @@
         <v>0</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:16" s="2" customFormat="1">
+    <row r="19" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>15</v>
       </c>
@@ -5269,10 +5268,10 @@
         <v>0</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:16" s="2" customFormat="1">
+    <row r="20" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>16</v>
       </c>
@@ -5310,10 +5309,10 @@
         <v>0</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:16" s="2" customFormat="1">
+    <row r="21" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>17</v>
       </c>
@@ -5351,10 +5350,10 @@
         <v>0</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:16" s="2" customFormat="1">
+    <row r="22" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>18</v>
       </c>
@@ -5392,10 +5391,10 @@
         <v>0</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:16" s="2" customFormat="1">
+    <row r="23" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>19</v>
       </c>
@@ -5433,10 +5432,10 @@
         <v>0</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:16" s="2" customFormat="1">
+    <row r="24" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>20</v>
       </c>
@@ -5474,10 +5473,10 @@
         <v>0</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:16" s="2" customFormat="1">
+    <row r="25" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>21</v>
       </c>
@@ -5515,10 +5514,10 @@
         <v>0</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:16" s="2" customFormat="1">
+    <row r="26" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>22</v>
       </c>
@@ -5556,10 +5555,10 @@
         <v>0</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:16" s="2" customFormat="1">
+    <row r="27" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>23</v>
       </c>
@@ -5597,10 +5596,10 @@
         <v>0</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:16" s="2" customFormat="1">
+    <row r="28" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>24</v>
       </c>
@@ -5638,10 +5637,10 @@
         <v>0</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:16" s="2" customFormat="1">
+    <row r="29" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>25</v>
       </c>
@@ -5679,10 +5678,10 @@
         <v>0</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:16" s="2" customFormat="1">
+    <row r="30" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>26</v>
       </c>
@@ -5720,10 +5719,10 @@
         <v>0</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:16" s="2" customFormat="1">
+    <row r="31" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>27</v>
       </c>
@@ -5761,10 +5760,10 @@
         <v>0</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:16" s="2" customFormat="1">
+    <row r="32" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>28</v>
       </c>
@@ -5802,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:16" s="2" customFormat="1">
+    <row r="33" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>29</v>
       </c>
@@ -5843,10 +5842,10 @@
         <v>0</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:16" s="2" customFormat="1">
+    <row r="34" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>30</v>
       </c>
@@ -5884,10 +5883,10 @@
         <v>0</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:16" s="2" customFormat="1">
+    <row r="35" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>31</v>
       </c>
@@ -5925,10 +5924,10 @@
         <v>0</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:16" s="2" customFormat="1">
+    <row r="36" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>32</v>
       </c>
@@ -5966,10 +5965,10 @@
         <v>0</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:16" s="2" customFormat="1">
+    <row r="37" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>33</v>
       </c>
@@ -6007,10 +6006,10 @@
         <v>0</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:16" s="2" customFormat="1">
+    <row r="38" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>34</v>
       </c>
@@ -6048,10 +6047,10 @@
         <v>0</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:16" s="2" customFormat="1">
+    <row r="39" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>35</v>
       </c>
@@ -6083,16 +6082,16 @@
         <v>2</v>
       </c>
       <c r="K39" s="9" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="O39" s="2">
         <v>0</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="40" spans="1:16" s="2" customFormat="1">
+    <row r="40" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>36</v>
       </c>
@@ -6124,16 +6123,16 @@
         <v>2</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="O40" s="2">
         <v>0</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>37</v>
       </c>
@@ -6165,7 +6164,7 @@
         <v>2</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -6174,10 +6173,10 @@
         <v>0</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>38</v>
       </c>
@@ -6209,7 +6208,7 @@
         <v>2</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
@@ -6218,10 +6217,10 @@
         <v>0</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>39</v>
       </c>
@@ -6253,7 +6252,7 @@
         <v>2</v>
       </c>
       <c r="K43" s="9" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
@@ -6262,10 +6261,10 @@
         <v>0</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>40</v>
       </c>
@@ -6297,7 +6296,7 @@
         <v>2</v>
       </c>
       <c r="K44" s="9" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
@@ -6306,10 +6305,10 @@
         <v>0</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>41</v>
       </c>
@@ -6341,7 +6340,7 @@
         <v>2</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
@@ -6350,10 +6349,10 @@
         <v>0</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>42</v>
       </c>
@@ -6385,7 +6384,7 @@
         <v>2</v>
       </c>
       <c r="K46" s="9" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
@@ -6394,10 +6393,10 @@
         <v>0</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>43</v>
       </c>
@@ -6429,7 +6428,7 @@
         <v>2</v>
       </c>
       <c r="K47" s="9" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -6438,10 +6437,10 @@
         <v>0</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>44</v>
       </c>
@@ -6473,7 +6472,7 @@
         <v>2</v>
       </c>
       <c r="K48" s="9" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
@@ -6482,10 +6481,10 @@
         <v>0</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:16">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>45</v>
       </c>
@@ -6517,7 +6516,7 @@
         <v>2</v>
       </c>
       <c r="K49" s="9" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
@@ -6526,10 +6525,10 @@
         <v>0</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="50" spans="1:16">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>46</v>
       </c>
@@ -6561,7 +6560,7 @@
         <v>2</v>
       </c>
       <c r="K50" s="9" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
@@ -6570,10 +6569,10 @@
         <v>0</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>47</v>
       </c>
@@ -6605,7 +6604,7 @@
         <v>2</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
@@ -6614,10 +6613,10 @@
         <v>0</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="52" spans="1:16">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>48</v>
       </c>
@@ -6649,7 +6648,7 @@
         <v>2</v>
       </c>
       <c r="K52" s="9" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
@@ -6658,10 +6657,10 @@
         <v>0</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:16">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>49</v>
       </c>
@@ -6693,7 +6692,7 @@
         <v>2</v>
       </c>
       <c r="K53" s="9" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -6702,10 +6701,10 @@
         <v>0</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="54" spans="1:16">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>50</v>
       </c>
@@ -6737,7 +6736,7 @@
         <v>2</v>
       </c>
       <c r="K54" s="9" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6746,10 +6745,10 @@
         <v>0</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="55" spans="1:16">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>51</v>
       </c>
@@ -6781,7 +6780,7 @@
         <v>2</v>
       </c>
       <c r="K55" s="9" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -6790,10 +6789,10 @@
         <v>0</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="56" spans="1:16">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>67</v>
       </c>
@@ -6812,7 +6811,7 @@
       <c r="F56" s="2">
         <v>17</v>
       </c>
-      <c r="G56" s="4">
+      <c r="G56" s="2">
         <v>4</v>
       </c>
       <c r="H56" s="2">
@@ -6825,7 +6824,7 @@
         <v>2</v>
       </c>
       <c r="K56" s="9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -6834,10 +6833,10 @@
         <v>0</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="57" spans="1:16">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>68</v>
       </c>
@@ -6856,7 +6855,7 @@
       <c r="F57" s="2">
         <v>17</v>
       </c>
-      <c r="G57" s="4">
+      <c r="G57" s="2">
         <v>4</v>
       </c>
       <c r="H57" s="2">
@@ -6869,7 +6868,7 @@
         <v>2</v>
       </c>
       <c r="K57" s="9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -6878,10 +6877,10 @@
         <v>0</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="58" spans="1:16">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>69</v>
       </c>
@@ -6900,7 +6899,7 @@
       <c r="F58" s="2">
         <v>17</v>
       </c>
-      <c r="G58" s="4">
+      <c r="G58" s="2">
         <v>4</v>
       </c>
       <c r="H58" s="2">
@@ -6913,7 +6912,7 @@
         <v>2</v>
       </c>
       <c r="K58" s="9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -6922,39 +6921,49 @@
         <v>0</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B1:P58" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="16" type="noConversion"/>
-  <conditionalFormatting sqref="B41:B58 D43:E58 C5:C58 B59:P1048576 L53:P58 F55:H55 I55:J58">
-    <cfRule type="expression" dxfId="5" priority="4">
+  <conditionalFormatting sqref="B41:B58 D43:E58">
+    <cfRule type="expression" dxfId="7" priority="5">
+      <formula>MOD($B41,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:P4">
+    <cfRule type="expression" dxfId="6" priority="271">
+      <formula>MOD($B1,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5:C58">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>MOD($B5,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:P4">
+  <conditionalFormatting sqref="D41:J42 L41:P42 D57:F58 B59:P1048576">
     <cfRule type="expression" dxfId="4" priority="270">
-      <formula>MOD($B1,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D41:J42 L41:P42 G56:H56 D57:H58">
-    <cfRule type="expression" dxfId="3" priority="269">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F45:J46 L45:P46">
-    <cfRule type="expression" dxfId="2" priority="7">
+    <cfRule type="expression" dxfId="3" priority="8">
       <formula>MOD($B45,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F49:J50 L49:P50">
-    <cfRule type="expression" dxfId="1" priority="5">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>MOD($B49,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F53:J54 F56:F58">
-    <cfRule type="expression" dxfId="0" priority="3">
+  <conditionalFormatting sqref="F53:J58">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>MOD($B53,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L53:P58">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>MOD($B53,2)=1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC2394F-0738-48FD-9072-5D2C74128067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
@@ -19,24 +13,36 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$P$58</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
     <author>vidisJW</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="B1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">admin:
@@ -46,21 +52,19 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>游戏ID，标识码</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">pgos:
@@ -70,7 +74,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>1.普通
@@ -80,14 +83,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -97,21 +99,19 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>该游戏的元素ID</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="G1" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>vidisJW:</t>
@@ -120,7 +120,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -131,14 +130,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -148,21 +146,19 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>奖项数量</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -172,21 +168,19 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>中奖数量对应的倍数</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -196,7 +190,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>中奖后倍数的基数，线注或总赌注
@@ -208,14 +201,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -225,7 +217,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>该行元素的数量触发小游戏的ID，根据小游戏配置填写
@@ -233,14 +224,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="10"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -250,21 +240,19 @@
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>该数量如果其他元素组成时，根据其他元素的数量，倍率增加多少倍，格式为[{元素ID，数量，倍率}]，即该元素ID多少个后，对结果加成多少倍</t>
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -275,7 +263,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>[{1,[{线注,100}]}]
@@ -283,14 +270,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -300,7 +286,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Mr.M:
@@ -309,14 +294,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+    <comment ref="O1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>大于0表示该中奖线触发对应jp奖池</t>
@@ -414,6 +398,9 @@
     <t>bet</t>
   </si>
   <si>
+    <t>rewardType</t>
+  </si>
+  <si>
     <t>featureTriggerId</t>
   </si>
   <si>
@@ -424,6 +411,9 @@
   </si>
   <si>
     <t>lineIdReward</t>
+  </si>
+  <si>
+    <t>13,1,2;13,2,4;13,3,6;13,4,8;14,1,5;14,2,10;14,3,15;14,4,20</t>
   </si>
   <si>
     <t>-</t>
@@ -473,19 +463,18 @@
   <si>
     <t>5个触发免费选择触发黄金列车</t>
   </si>
-  <si>
-    <t>rewardType</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>13,1,2;13,2,4;13,3,6;13,4,8;14,1,5;14,2,10;14,3,15;14,4,20</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -497,41 +486,179 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -539,7 +666,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -547,7 +673,6 @@
       <sz val="12"/>
       <color theme="10"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -556,7 +681,6 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -564,53 +688,33 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -620,6 +724,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -635,8 +763,158 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -659,17 +937,129 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="8">
+  <cellStyleXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -678,104 +1068,233 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="8">
-    <cellStyle name="差_Sheet1" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+  <cellStyles count="56">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 10 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="常规 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="常规 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="超链接 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="超链接 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="好_Sheet1" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="差_Sheet1" xfId="49"/>
+    <cellStyle name="常规 10 2" xfId="50"/>
+    <cellStyle name="常规 2" xfId="51"/>
+    <cellStyle name="常规 3" xfId="52"/>
+    <cellStyle name="超链接 2" xfId="53"/>
+    <cellStyle name="超链接 3" xfId="54"/>
+    <cellStyle name="好_Sheet1" xfId="55"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.7993408001953185"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.7993408001953185"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.7993408001953185"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.7993408001953185"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.7993408001953185"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.7993408001953185"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.7993408001953185"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.7993408001953185"/>
+          <bgColor theme="8" tint="0.799340800195319"/>
         </patternFill>
       </fill>
     </dxf>
@@ -785,15 +1304,12 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -802,15 +1318,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361385" cy="9781935"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -854,15 +1364,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9428167" cy="9611543"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="14" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -906,15 +1410,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361385" cy="9524761"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="26" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -958,15 +1456,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9371440" cy="9381886"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="50" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="50" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1010,15 +1502,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9370910" cy="9508885"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="74" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="74" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1062,15 +1548,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9370910" cy="9239011"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="98" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="98" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1114,15 +1594,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="9789160"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="290" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022010000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="290" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1166,15 +1640,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="9789160"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="434" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000B2010000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="434" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1218,15 +1686,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9428167" cy="9611543"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="446" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000BE010000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="446" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1270,15 +1732,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="9789160"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="506" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000FA010000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="506" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1322,15 +1778,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9428167" cy="9611543"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="518" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006020000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="518" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1374,15 +1824,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="9789160"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="578" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042020000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="578" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1426,15 +1870,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9428167" cy="9611543"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="590" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E020000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="590" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1478,15 +1916,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="9789160"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="650" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008A020000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="650" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1530,15 +1962,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9428167" cy="9611543"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="662" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000096020000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="662" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1582,15 +2008,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="9524365"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="674" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A2020000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="674" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1634,15 +2054,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9371440" cy="9381886"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="698" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000BA020000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="698" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1686,15 +2100,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9370910" cy="9508885"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="722" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D2020000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="722" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1738,15 +2146,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9370910" cy="9239011"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="746" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000EA020000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="746" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1790,15 +2192,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="9789160"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1082" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A040000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1082" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1842,15 +2238,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9428167" cy="9611543"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1094" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046040000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1094" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1894,15 +2284,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="9789160"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1154" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000082040000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1154" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1946,15 +2330,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9428167" cy="9611543"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1166" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008E040000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1166" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1998,15 +2376,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="9789160"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1226" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CA040000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1226" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2050,15 +2422,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9428167" cy="9611543"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1238" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D6040000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1238" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2102,15 +2468,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="9789160"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1298" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012050000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1298" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2154,15 +2514,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9428167" cy="9611543"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1310" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001E050000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1310" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2206,15 +2560,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="9524365"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1322" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002A050000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1322" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2258,15 +2606,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9371440" cy="9381886"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1346" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042050000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1346" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2310,15 +2652,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9370910" cy="9508885"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1370" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A050000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1370" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2362,15 +2698,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9370910" cy="9239011"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1394" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072050000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1394" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2414,15 +2744,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="9789160"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1730" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000C2060000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1730" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2466,15 +2790,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9428167" cy="9611543"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1742" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CE060000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1742" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2518,15 +2836,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="9789160"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1802" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A070000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1802" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2570,15 +2882,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9428167" cy="9611543"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1814" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016070000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1814" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2622,15 +2928,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="9789160"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1874" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052070000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1874" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2674,15 +2974,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9428167" cy="9611543"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1886" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E070000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1886" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2726,15 +3020,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="9789160"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1946" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009A070000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1946" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2778,15 +3066,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9428167" cy="9611543"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1958" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A6070000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1958" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2830,15 +3112,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="9524365"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1970" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000B2070000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1970" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2882,15 +3158,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9371440" cy="9381886"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1994" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CA070000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1994" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2934,15 +3204,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9370910" cy="9508885"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2018" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000E2070000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2018" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2986,15 +3250,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9370910" cy="9239011"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2042" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000FA070000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2042" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3038,15 +3296,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="9789160"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2450" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000092090000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2450" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3090,15 +3342,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9428167" cy="9611543"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2462" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009E090000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2462" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3142,15 +3388,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="9789160"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2522" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000DA090000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2522" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3194,15 +3434,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9428167" cy="9611543"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2534" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000E6090000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2534" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3246,15 +3480,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="9789160"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2594" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000220A0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2594" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3298,15 +3526,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9428167" cy="9611543"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2606" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E0A0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2606" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3350,15 +3572,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="10240010"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2666" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A0A0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2666" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3402,15 +3618,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9428167" cy="9611543"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2678" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000760A0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2678" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3454,15 +3664,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="9972040"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2690" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000820A0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2690" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3506,15 +3710,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9371440" cy="9381886"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2714" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009A0A0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2714" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3558,15 +3756,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9370910" cy="9508885"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2738" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000B20A0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2738" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3610,15 +3802,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9370910" cy="9239011"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2762" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CA0A0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2762" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3662,15 +3848,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="10240010"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3098" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A0C0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3098" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3714,15 +3894,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="9789160"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3146" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A0C0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3146" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3766,15 +3940,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9428167" cy="9611543"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3158" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000560C0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3158" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3818,15 +3986,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9428167" cy="9611543"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3230" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009E0C0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3230" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3870,15 +4032,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361385" cy="9781935"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3302" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000E60C0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3302" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3922,15 +4078,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9428167" cy="9611543"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3314" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000F20C0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3314" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3974,15 +4124,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361385" cy="9524761"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3326" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000FE0C0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3326" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4026,15 +4170,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9371440" cy="9381886"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3350" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000160D0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3350" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4078,15 +4216,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9370910" cy="9508885"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3374" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E0D0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3374" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4130,15 +4262,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9370910" cy="9239011"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3398" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000460D0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3398" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4182,15 +4308,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9361170" cy="9789160"/>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3590" name="CustomShape 1" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000060E0000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3590" name="CustomShape 1" hidden="1"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4481,17 +4601,16 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:P58"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
     <col min="2" max="2" width="11" style="2" customWidth="1"/>
@@ -4511,7 +4630,7 @@
     <col min="17" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" s="1" customFormat="1" ht="37.5" customHeight="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4561,7 +4680,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" s="2" customFormat="1" spans="1:15">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
@@ -4608,7 +4727,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" s="2" customFormat="1" hidden="1" spans="1:15">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -4637,26 +4756,26 @@
         <v>27</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" s="2" customFormat="1" hidden="1"/>
+    <row r="5" s="2" customFormat="1" spans="1:16">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -4688,16 +4807,16 @@
         <v>1</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O5" s="2">
         <v>0</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" s="2" customFormat="1" spans="1:16">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -4729,16 +4848,16 @@
         <v>1</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O6" s="2">
         <v>0</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" s="2" customFormat="1" spans="1:16">
       <c r="A7" s="2">
         <v>3</v>
       </c>
@@ -4770,16 +4889,16 @@
         <v>1</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O7" s="2">
         <v>0</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" s="2" customFormat="1" spans="1:16">
       <c r="A8" s="2">
         <v>4</v>
       </c>
@@ -4811,16 +4930,16 @@
         <v>1</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O8" s="2">
         <v>0</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" s="2" customFormat="1" spans="1:16">
       <c r="A9" s="2">
         <v>5</v>
       </c>
@@ -4852,16 +4971,16 @@
         <v>1</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O9" s="2">
         <v>0</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" s="2" customFormat="1" spans="1:16">
       <c r="A10" s="2">
         <v>6</v>
       </c>
@@ -4893,16 +5012,16 @@
         <v>1</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O10" s="2">
         <v>0</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" s="2" customFormat="1" spans="1:16">
       <c r="A11" s="2">
         <v>7</v>
       </c>
@@ -4934,16 +5053,16 @@
         <v>1</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O11" s="2">
         <v>0</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" s="2" customFormat="1" spans="1:16">
       <c r="A12" s="2">
         <v>8</v>
       </c>
@@ -4975,16 +5094,16 @@
         <v>1</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O12" s="2">
         <v>0</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" s="2" customFormat="1" spans="1:16">
       <c r="A13" s="2">
         <v>9</v>
       </c>
@@ -5016,16 +5135,16 @@
         <v>1</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O13" s="2">
         <v>0</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" s="2" customFormat="1" spans="1:16">
       <c r="A14" s="2">
         <v>10</v>
       </c>
@@ -5051,22 +5170,22 @@
         <v>3</v>
       </c>
       <c r="I14" s="2">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="J14" s="2">
         <v>1</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O14" s="2">
         <v>0</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" s="2" customFormat="1" spans="1:16">
       <c r="A15" s="2">
         <v>11</v>
       </c>
@@ -5098,16 +5217,16 @@
         <v>1</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O15" s="2">
         <v>0</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" s="2" customFormat="1" spans="1:16">
       <c r="A16" s="2">
         <v>12</v>
       </c>
@@ -5139,16 +5258,16 @@
         <v>1</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O16" s="2">
         <v>0</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" s="2" customFormat="1" spans="1:16">
       <c r="A17" s="2">
         <v>13</v>
       </c>
@@ -5180,16 +5299,16 @@
         <v>1</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O17" s="2">
         <v>0</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" s="2" customFormat="1" spans="1:16">
       <c r="A18" s="2">
         <v>14</v>
       </c>
@@ -5221,16 +5340,16 @@
         <v>1</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O18" s="2">
         <v>0</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" s="2" customFormat="1" spans="1:16">
       <c r="A19" s="2">
         <v>15</v>
       </c>
@@ -5262,16 +5381,16 @@
         <v>1</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O19" s="2">
         <v>0</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" s="2" customFormat="1" spans="1:16">
       <c r="A20" s="2">
         <v>16</v>
       </c>
@@ -5303,16 +5422,16 @@
         <v>1</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O20" s="2">
         <v>0</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" s="2" customFormat="1" spans="1:16">
       <c r="A21" s="2">
         <v>17</v>
       </c>
@@ -5344,16 +5463,16 @@
         <v>1</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O21" s="2">
         <v>0</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" s="2" customFormat="1" spans="1:16">
       <c r="A22" s="2">
         <v>18</v>
       </c>
@@ -5385,16 +5504,16 @@
         <v>1</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O22" s="2">
         <v>0</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" s="2" customFormat="1" spans="1:16">
       <c r="A23" s="2">
         <v>19</v>
       </c>
@@ -5426,16 +5545,16 @@
         <v>1</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O23" s="2">
         <v>0</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" s="2" customFormat="1" spans="1:16">
       <c r="A24" s="2">
         <v>20</v>
       </c>
@@ -5467,16 +5586,16 @@
         <v>1</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O24" s="2">
         <v>0</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" s="2" customFormat="1" spans="1:16">
       <c r="A25" s="2">
         <v>21</v>
       </c>
@@ -5508,16 +5627,16 @@
         <v>1</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O25" s="2">
         <v>0</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" s="2" customFormat="1" spans="1:16">
       <c r="A26" s="2">
         <v>22</v>
       </c>
@@ -5549,16 +5668,16 @@
         <v>1</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O26" s="2">
         <v>0</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" s="2" customFormat="1" spans="1:16">
       <c r="A27" s="2">
         <v>23</v>
       </c>
@@ -5590,16 +5709,16 @@
         <v>1</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O27" s="2">
         <v>0</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" s="2" customFormat="1" spans="1:16">
       <c r="A28" s="2">
         <v>24</v>
       </c>
@@ -5631,16 +5750,16 @@
         <v>1</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O28" s="2">
         <v>0</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" s="2" customFormat="1" spans="1:16">
       <c r="A29" s="2">
         <v>25</v>
       </c>
@@ -5672,16 +5791,16 @@
         <v>1</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O29" s="2">
         <v>0</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" s="2" customFormat="1" spans="1:16">
       <c r="A30" s="2">
         <v>26</v>
       </c>
@@ -5713,16 +5832,16 @@
         <v>1</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O30" s="2">
         <v>0</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" s="2" customFormat="1" spans="1:16">
       <c r="A31" s="2">
         <v>27</v>
       </c>
@@ -5754,16 +5873,16 @@
         <v>1</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O31" s="2">
         <v>0</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" s="2" customFormat="1" spans="1:16">
       <c r="A32" s="2">
         <v>28</v>
       </c>
@@ -5795,16 +5914,16 @@
         <v>1</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O32" s="2">
         <v>0</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" s="2" customFormat="1" spans="1:16">
       <c r="A33" s="2">
         <v>29</v>
       </c>
@@ -5836,16 +5955,16 @@
         <v>1</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O33" s="2">
         <v>0</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" s="2" customFormat="1" spans="1:16">
       <c r="A34" s="2">
         <v>30</v>
       </c>
@@ -5877,16 +5996,16 @@
         <v>1</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O34" s="2">
         <v>0</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" s="2" customFormat="1" spans="1:16">
       <c r="A35" s="2">
         <v>31</v>
       </c>
@@ -5918,16 +6037,16 @@
         <v>1</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O35" s="2">
         <v>0</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" s="2" customFormat="1" spans="1:16">
       <c r="A36" s="2">
         <v>32</v>
       </c>
@@ -5959,16 +6078,16 @@
         <v>1</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O36" s="2">
         <v>0</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" s="2" customFormat="1" spans="1:16">
       <c r="A37" s="2">
         <v>33</v>
       </c>
@@ -6000,16 +6119,16 @@
         <v>1</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O37" s="2">
         <v>0</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" s="2" customFormat="1" spans="1:16">
       <c r="A38" s="2">
         <v>34</v>
       </c>
@@ -6041,16 +6160,16 @@
         <v>1</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O38" s="2">
         <v>0</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" s="2" customFormat="1" spans="1:16">
       <c r="A39" s="2">
         <v>35</v>
       </c>
@@ -6082,16 +6201,16 @@
         <v>2</v>
       </c>
       <c r="K39" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O39" s="2">
         <v>0</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" s="2" customFormat="1" spans="1:16">
       <c r="A40" s="2">
         <v>36</v>
       </c>
@@ -6123,16 +6242,16 @@
         <v>2</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O40" s="2">
         <v>0</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16">
       <c r="A41" s="2">
         <v>37</v>
       </c>
@@ -6164,7 +6283,7 @@
         <v>2</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -6173,10 +6292,10 @@
         <v>0</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16">
       <c r="A42" s="2">
         <v>38</v>
       </c>
@@ -6208,7 +6327,7 @@
         <v>2</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
@@ -6217,10 +6336,10 @@
         <v>0</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16">
       <c r="A43" s="2">
         <v>39</v>
       </c>
@@ -6252,7 +6371,7 @@
         <v>2</v>
       </c>
       <c r="K43" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
@@ -6261,10 +6380,10 @@
         <v>0</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16">
       <c r="A44" s="2">
         <v>40</v>
       </c>
@@ -6296,7 +6415,7 @@
         <v>2</v>
       </c>
       <c r="K44" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
@@ -6305,10 +6424,10 @@
         <v>0</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16">
       <c r="A45" s="2">
         <v>41</v>
       </c>
@@ -6340,7 +6459,7 @@
         <v>2</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
@@ -6349,10 +6468,10 @@
         <v>0</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16">
       <c r="A46" s="2">
         <v>42</v>
       </c>
@@ -6384,7 +6503,7 @@
         <v>2</v>
       </c>
       <c r="K46" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
@@ -6393,10 +6512,10 @@
         <v>0</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16">
       <c r="A47" s="2">
         <v>43</v>
       </c>
@@ -6428,7 +6547,7 @@
         <v>2</v>
       </c>
       <c r="K47" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -6437,10 +6556,10 @@
         <v>0</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16">
       <c r="A48" s="2">
         <v>44</v>
       </c>
@@ -6472,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="K48" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
@@ -6481,10 +6600,10 @@
         <v>0</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:16">
       <c r="A49" s="2">
         <v>45</v>
       </c>
@@ -6516,7 +6635,7 @@
         <v>2</v>
       </c>
       <c r="K49" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
@@ -6525,10 +6644,10 @@
         <v>0</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:16">
       <c r="A50" s="2">
         <v>46</v>
       </c>
@@ -6560,7 +6679,7 @@
         <v>2</v>
       </c>
       <c r="K50" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
@@ -6569,10 +6688,10 @@
         <v>0</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:16">
       <c r="A51" s="2">
         <v>47</v>
       </c>
@@ -6604,7 +6723,7 @@
         <v>2</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
@@ -6613,10 +6732,10 @@
         <v>0</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:16">
       <c r="A52" s="2">
         <v>48</v>
       </c>
@@ -6648,7 +6767,7 @@
         <v>2</v>
       </c>
       <c r="K52" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
@@ -6657,10 +6776,10 @@
         <v>0</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:16">
       <c r="A53" s="2">
         <v>49</v>
       </c>
@@ -6692,7 +6811,7 @@
         <v>2</v>
       </c>
       <c r="K53" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -6701,10 +6820,10 @@
         <v>0</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:16">
       <c r="A54" s="2">
         <v>50</v>
       </c>
@@ -6736,7 +6855,7 @@
         <v>2</v>
       </c>
       <c r="K54" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6745,10 +6864,10 @@
         <v>0</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:16">
       <c r="A55" s="2">
         <v>51</v>
       </c>
@@ -6780,7 +6899,7 @@
         <v>2</v>
       </c>
       <c r="K55" s="9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -6789,10 +6908,10 @@
         <v>0</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:16">
       <c r="A56" s="2">
         <v>67</v>
       </c>
@@ -6824,7 +6943,7 @@
         <v>2</v>
       </c>
       <c r="K56" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -6833,10 +6952,10 @@
         <v>0</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:16">
       <c r="A57" s="2">
         <v>68</v>
       </c>
@@ -6868,7 +6987,7 @@
         <v>2</v>
       </c>
       <c r="K57" s="9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -6877,10 +6996,10 @@
         <v>0</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:16">
       <c r="A58" s="2">
         <v>69</v>
       </c>
@@ -6912,7 +7031,7 @@
         <v>2</v>
       </c>
       <c r="K58" s="9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -6921,63 +7040,65 @@
         <v>0</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:P58" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:P58" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
+  <conditionalFormatting sqref="C5:C58">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>MOD($B5,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G56:G58">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD($B56,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:P4">
+    <cfRule type="expression" dxfId="0" priority="271">
+      <formula>MOD($B1,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B41:B58 D43:E58">
-    <cfRule type="expression" dxfId="7" priority="5">
+    <cfRule type="expression" dxfId="0" priority="5">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:P4">
-    <cfRule type="expression" dxfId="6" priority="271">
-      <formula>MOD($B1,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C5:C58">
-    <cfRule type="expression" dxfId="5" priority="2">
-      <formula>MOD($B5,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D41:J42 L41:P42 D57:F58 B59:P1048576">
-    <cfRule type="expression" dxfId="4" priority="270">
+  <conditionalFormatting sqref="D41:J42 L41:P42 H56:H58 D57:F58 B59:P1048576">
+    <cfRule type="expression" dxfId="0" priority="270">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F45:J46 L45:P46">
-    <cfRule type="expression" dxfId="3" priority="8">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>MOD($B45,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F49:J50 L49:P50">
-    <cfRule type="expression" dxfId="2" priority="6">
+    <cfRule type="expression" dxfId="0" priority="6">
       <formula>MOD($B49,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F53:J58">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>MOD($B53,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L53:P58">
+  <conditionalFormatting sqref="F53:J55 L53:P58 I56:J58 F56:F58">
     <cfRule type="expression" dxfId="0" priority="4">
       <formula>MOD($B53,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1">
       <formula1>"普通,免费,重转,全部"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1">
       <formula1>"线注,线注乘倍率,总赌注"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <headerFooter/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$P$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,6 +34,7 @@
   <authors>
     <author/>
     <author>vidisJW</author>
+    <author>Administrator</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
@@ -83,7 +84,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -101,11 +102,13 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>该游戏的元素ID</t>
+          <t xml:space="preserve">该游戏的元素ID：图案1_图案2……
+分号后续的图案也要视为目标图案
+</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1">
+    <comment ref="E1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -123,10 +126,33 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-连线：赔付线
-指定：指定的奖励
-滚轴：滚轴的奖励
-全局分散：针对需要全局计算的元素</t>
+1：连线_X连：根据赔付线从左至右，出现相同图案，同时还要在baseline表中判断图案位置是否与中奖线一致，连续X列都符合表示为X连，一条线触发一次
+2：指定图案_条件图案ID：条件图案出现，不需要考虑位置，一个指定图案触发一次
+3：满线图案_X连：从左至右，出现相同图案，连续X列表示X连，一个图案计算触发一次
+4：全局分散图案_数量：针对需要全局计算的元素，只考虑数量，此模式相同图案仅触发数量最多的一次
+5：满线图案_数量：从左至右，前一列出现相同图案，只统计数量，相同图案仅触发数量最多的一次</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">Mr.M:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>奖项数量</t>
         </r>
       </text>
     </comment>
@@ -148,7 +174,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>奖项数量</t>
+          <t>中奖数量对应的倍数</t>
         </r>
       </text>
     </comment>
@@ -170,61 +196,12 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>中奖数量对应的倍数</t>
+          <t>该行元素的数量触发小游戏的ID，根据小游戏配置填写
+小游戏id;</t>
         </r>
       </text>
     </comment>
     <comment ref="J1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Mr.M:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>中奖后倍数的基数，线注或总赌注
-线注，线注*赔付倍数
-线注乘倍率，线注*赔付倍数*基本表里的倍率
-总赌注，总赌注*赔付倍数
-1: 单线押分
-2: 总押分</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Mr.M:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>该行元素的数量触发小游戏的ID，根据小游戏配置填写
-滚轴模式,小游戏id;</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -246,7 +223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -255,22 +232,12 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">Mr.M:
-线注倍数，奖励基数，奖励倍数
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>[{1,[{线注,100}]}]
-非同种元素，累加累乘需要服务器实现</t>
+          <t>大于0表示该中奖线触发对应jp奖池
+jackpot不进结果库，触发时根据奖池配置及时计算</t>
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0">
+    <comment ref="J5" authorId="2">
       <text>
         <r>
           <rPr>
@@ -279,8 +246,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">Mr.M:
-</t>
+          <t>Administrator:</t>
         </r>
         <r>
           <rPr>
@@ -288,13 +254,13 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>Mr.M:
-所在线ID，奖励基数，奖励倍数
-[{1,[{总押分,100}]}]</t>
+          <t xml:space="preserve">
+13是wild×2
+14是wild×5</t>
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0">
+    <comment ref="D49" authorId="2">
       <text>
         <r>
           <rPr>
@@ -303,7 +269,16 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>大于0表示该中奖线触发对应jp奖池</t>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+普通麻将:黄金麻将</t>
         </r>
       </text>
     </comment>
@@ -312,7 +287,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="44">
   <si>
     <t>id</t>
   </si>
@@ -323,37 +298,22 @@
     <t>旋转状态</t>
   </si>
   <si>
-    <t>旋转状态标识</t>
+    <t>元素ID_相同元素_相同元素</t>
   </si>
   <si>
-    <t>是否额外投注</t>
+    <t>中奖条件</t>
   </si>
   <si>
-    <t>元素ID</t>
-  </si>
-  <si>
-    <t>线类型</t>
-  </si>
-  <si>
-    <t>数量</t>
+    <t>条件参数</t>
   </si>
   <si>
     <t>倍率</t>
   </si>
   <si>
-    <t>中奖基数</t>
-  </si>
-  <si>
     <t>触发小游戏ID</t>
   </si>
   <si>
-    <t>元素倍率加成</t>
-  </si>
-  <si>
-    <t>单线押分倍数加成</t>
-  </si>
-  <si>
-    <t>线ID加成</t>
+    <t>额外出现元素导致倍率加成</t>
   </si>
   <si>
     <t>jackpotID</t>
@@ -365,10 +325,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>Map&lt;int{,}int&gt;{;}</t>
+    <t>List&lt;int&gt;{_}</t>
   </si>
   <si>
     <t>List&lt;List&lt;int&gt;{,}&gt;{;}</t>
@@ -378,12 +335,6 @@
   </si>
   <si>
     <t>rotateState</t>
-  </si>
-  <si>
-    <t>spinType</t>
-  </si>
-  <si>
-    <t>needExtraBet</t>
   </si>
   <si>
     <t>elementId</t>
@@ -398,19 +349,13 @@
     <t>bet</t>
   </si>
   <si>
-    <t>rewardType</t>
-  </si>
-  <si>
     <t>featureTriggerId</t>
   </si>
   <si>
     <t>betTimes</t>
   </si>
   <si>
-    <t>scoreBetTimes</t>
-  </si>
-  <si>
-    <t>lineIdReward</t>
+    <t>最大连线</t>
   </si>
   <si>
     <t>13,1,2;13,2,4;13,3,6;13,4,8;14,1,5;14,2,10;14,3,15;14,4,20</t>
@@ -419,49 +364,61 @@
     <t>-</t>
   </si>
   <si>
-    <t>1,10010001;2,10010001;3,10010001;4,10010001;5,10010001;6,10010001;7,10010001;</t>
+    <t>同时出现 目标和条件元素</t>
   </si>
   <si>
     <t>拉火车绿火车MINI</t>
   </si>
   <si>
-    <t>1,10010002;2,10010002;3,10010002;4,10010002;5,10010002;6,10010002;7,10010002;</t>
-  </si>
-  <si>
     <t>拉火车蓝火车MINOR</t>
-  </si>
-  <si>
-    <t>1,10010003;2,10010003;3,10010003;4,10010003;5,10010003;6,10010003;7,10010003;</t>
   </si>
   <si>
     <t>拉火车紫火车MAJOR</t>
   </si>
   <si>
-    <t>1,10010004;2,10010004;3,10010004;4,10010004;5,10010004;6,10010004;7,10010004;</t>
-  </si>
-  <si>
     <t>拉火车红火车GRAND</t>
   </si>
   <si>
-    <t>1,10010006;2,10010012;3,10010013;4,10010014;5,10010015;6,10010016;7,10010017;</t>
+    <t>保险箱奖励</t>
   </si>
   <si>
     <t>黄金列车普通转触发</t>
   </si>
   <si>
-    <t>1,10010007;2,10010018;3,10010019;4,10010020;5,10010021;6,10010022;7,10010023;</t>
-  </si>
-  <si>
-    <t>触发免费选择</t>
-  </si>
-  <si>
-    <t>1,10010011;2,10010030;3,10010031;4,10010032;5,10010033;6,10010034;7,10010035;</t>
+    <t>触发免费选择 【拉火车&amp;免费旋转8次】</t>
   </si>
   <si>
     <t>4个触发免费选择触发黄金列车</t>
   </si>
   <si>
     <t>5个触发免费选择触发黄金列车</t>
+  </si>
+  <si>
+    <t>指定触发隐藏免费游戏，仅用于结果库生成</t>
+  </si>
+  <si>
+    <t>1_11</t>
+  </si>
+  <si>
+    <t>2_12</t>
+  </si>
+  <si>
+    <t>3_13</t>
+  </si>
+  <si>
+    <t>4_14</t>
+  </si>
+  <si>
+    <t>5_15</t>
+  </si>
+  <si>
+    <t>6_16</t>
+  </si>
+  <si>
+    <t>7_17</t>
+  </si>
+  <si>
+    <t>8_18</t>
   </si>
 </sst>
 </file>
@@ -474,7 +431,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -508,6 +465,19 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -692,7 +662,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -703,18 +683,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -723,7 +693,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.35"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -914,7 +920,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -934,6 +940,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1053,73 +1074,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1128,108 +1131,216 @@
     <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="56">
@@ -1290,11 +1401,28 @@
     <cellStyle name="超链接 3" xfId="54"/>
     <cellStyle name="好_Sheet1" xfId="55"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="8" tint="0.799340800195319"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1325,7 +1453,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="0"/>
+          <a:off x="876300" y="0"/>
           <a:ext cx="9361170" cy="9781540"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1371,7 +1499,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1417,7 +1545,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9361170" cy="9524365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1463,7 +1591,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1509,7 +1637,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1555,7 +1683,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1601,7 +1729,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1647,7 +1775,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1693,7 +1821,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1739,7 +1867,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1785,7 +1913,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1831,7 +1959,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1877,7 +2005,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1923,7 +2051,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1969,7 +2097,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2015,7 +2143,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9361170" cy="9524365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2061,7 +2189,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2107,7 +2235,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2153,7 +2281,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2199,7 +2327,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2245,7 +2373,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2291,7 +2419,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2337,7 +2465,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2383,7 +2511,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2429,7 +2557,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2475,7 +2603,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2521,7 +2649,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2567,7 +2695,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9524365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2613,7 +2741,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2659,7 +2787,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2705,7 +2833,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2751,7 +2879,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2797,7 +2925,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2843,7 +2971,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2889,7 +3017,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2935,7 +3063,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2981,7 +3109,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3027,7 +3155,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3073,7 +3201,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3119,7 +3247,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9524365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3165,7 +3293,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3211,7 +3339,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3257,7 +3385,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3303,7 +3431,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3349,7 +3477,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3395,7 +3523,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3441,7 +3569,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3487,7 +3615,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3533,7 +3661,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3579,7 +3707,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="10240010"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3625,7 +3753,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3671,7 +3799,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9972040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3717,7 +3845,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3763,7 +3891,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3809,7 +3937,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3855,7 +3983,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="10240010"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3901,7 +4029,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3947,7 +4075,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3993,7 +4121,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4039,7 +4167,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9781540"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4085,7 +4213,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4131,7 +4259,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9524365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4177,7 +4305,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4223,7 +4351,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4269,7 +4397,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4315,7 +4443,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4609,2490 +4737,2887 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:P58"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <dimension ref="A1:L85"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="9" style="3"/>
+    <col min="1" max="1" width="11.5" style="7"/>
     <col min="2" max="2" width="11" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="8.5" style="4" customWidth="1"/>
-    <col min="7" max="7" width="9.625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9" style="5" customWidth="1"/>
-    <col min="10" max="10" width="16.125" style="6" customWidth="1"/>
-    <col min="11" max="11" width="14.875" style="6" customWidth="1"/>
-    <col min="12" max="12" width="47" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.625" style="4" customWidth="1"/>
-    <col min="14" max="14" width="24.75" style="4" customWidth="1"/>
-    <col min="15" max="16" width="9" style="4"/>
-    <col min="17" max="16384" width="9" style="3"/>
+    <col min="3" max="3" width="10" style="8" customWidth="1"/>
+    <col min="4" max="4" width="14.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.25" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="12.2166666666667" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.85833333333333" style="9" customWidth="1"/>
+    <col min="9" max="9" width="19.1333333333333" style="9" customWidth="1"/>
+    <col min="10" max="10" width="29.75" style="2" customWidth="1"/>
+    <col min="11" max="11" width="10.375" style="2"/>
+    <col min="12" max="12" width="14.5583333333333" style="10" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="37.5" customHeight="1" spans="1:16">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="E1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="K1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+    </row>
+    <row r="2" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" s="2" customFormat="1" spans="1:15">
-      <c r="A2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="K2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" hidden="1" spans="1:15">
+        <v>11</v>
+      </c>
+      <c r="L2" s="10"/>
+    </row>
+    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="K3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" hidden="1"/>
-    <row r="5" s="2" customFormat="1" spans="1:16">
+        <v>9</v>
+      </c>
+      <c r="L3" s="10"/>
+    </row>
+    <row r="4" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C4" s="8"/>
+      <c r="L4" s="10"/>
+    </row>
+    <row r="5" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A5" s="2">
-        <v>1</v>
+        <f>(B5)*10000+D5+G5*100+E5*100000</f>
+        <v>1001100211</v>
       </c>
       <c r="B5" s="2">
         <v>100100</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="8">
         <v>4</v>
       </c>
       <c r="D5" s="2">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>11</v>
+      <c r="F5" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="G5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="2">
         <v>2</v>
       </c>
-      <c r="I5" s="2">
-        <v>2</v>
-      </c>
-      <c r="J5" s="2">
-        <v>1</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O5" s="2">
+      <c r="J5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="2">
         <v>0</v>
       </c>
-      <c r="P5" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:16">
+      <c r="L5" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A6" s="2">
-        <v>2</v>
+        <f t="shared" ref="A6:A42" si="0">(B6)*10000+D6+G6*100+E6*100000</f>
+        <v>1001100301</v>
       </c>
       <c r="B6" s="2">
         <v>100100</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="8">
         <v>4</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="E6" s="2" t="b">
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="2">
+        <v>3</v>
+      </c>
+      <c r="H6" s="2">
+        <v>5</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="2">
         <v>0</v>
       </c>
-      <c r="F6" s="2">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2">
-        <v>3</v>
-      </c>
-      <c r="I6" s="2">
-        <v>5</v>
-      </c>
-      <c r="J6" s="2">
-        <v>1</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O6" s="2">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:16">
+      <c r="L6" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A7" s="2">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>1001100302</v>
       </c>
       <c r="B7" s="2">
         <v>100100</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="8">
         <v>4</v>
       </c>
       <c r="D7" s="2">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" s="2" t="b">
+      <c r="F7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="2">
+        <v>3</v>
+      </c>
+      <c r="H7" s="2">
+        <v>5</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="2">
         <v>0</v>
       </c>
-      <c r="F7" s="2">
-        <v>2</v>
-      </c>
-      <c r="G7" s="2">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2">
-        <v>5</v>
-      </c>
-      <c r="J7" s="2">
-        <v>1</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O7" s="2">
-        <v>0</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:16">
+      <c r="L7" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A8" s="2">
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>1001100303</v>
       </c>
       <c r="B8" s="2">
         <v>100100</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="8">
         <v>4</v>
       </c>
       <c r="D8" s="2">
+        <v>3</v>
+      </c>
+      <c r="E8" s="2">
         <v>1</v>
       </c>
-      <c r="E8" s="2" t="b">
+      <c r="F8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="2">
+        <v>3</v>
+      </c>
+      <c r="H8" s="2">
+        <v>5</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="2">
         <v>0</v>
       </c>
-      <c r="F8" s="2">
-        <v>3</v>
-      </c>
-      <c r="G8" s="2">
-        <v>1</v>
-      </c>
-      <c r="H8" s="2">
-        <v>3</v>
-      </c>
-      <c r="I8" s="2">
-        <v>5</v>
-      </c>
-      <c r="J8" s="2">
-        <v>1</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O8" s="2">
-        <v>0</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" spans="1:16">
+      <c r="L8" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A9" s="2">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1001100304</v>
       </c>
       <c r="B9" s="2">
         <v>100100</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="8">
         <v>4</v>
       </c>
       <c r="D9" s="2">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2">
         <v>1</v>
       </c>
-      <c r="E9" s="2" t="b">
+      <c r="F9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="2">
+        <v>3</v>
+      </c>
+      <c r="H9" s="2">
+        <v>5</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="2">
         <v>0</v>
       </c>
-      <c r="F9" s="2">
-        <v>4</v>
-      </c>
-      <c r="G9" s="2">
-        <v>1</v>
-      </c>
-      <c r="H9" s="2">
-        <v>3</v>
-      </c>
-      <c r="I9" s="2">
-        <v>5</v>
-      </c>
-      <c r="J9" s="2">
-        <v>1</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O9" s="2">
-        <v>0</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" spans="1:16">
+      <c r="L9" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A10" s="2">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>1001100305</v>
       </c>
       <c r="B10" s="2">
         <v>100100</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="8">
         <v>4</v>
       </c>
       <c r="D10" s="2">
+        <v>5</v>
+      </c>
+      <c r="E10" s="2">
         <v>1</v>
       </c>
-      <c r="E10" s="2" t="b">
+      <c r="F10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="2">
+        <v>3</v>
+      </c>
+      <c r="H10" s="2">
+        <v>5</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="2">
         <v>0</v>
       </c>
-      <c r="F10" s="2">
-        <v>5</v>
-      </c>
-      <c r="G10" s="2">
-        <v>1</v>
-      </c>
-      <c r="H10" s="2">
-        <v>3</v>
-      </c>
-      <c r="I10" s="2">
-        <v>5</v>
-      </c>
-      <c r="J10" s="2">
-        <v>1</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O10" s="2">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="1:16">
+      <c r="L10" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A11" s="2">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>1001100306</v>
       </c>
       <c r="B11" s="2">
         <v>100100</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="8">
         <v>4</v>
       </c>
       <c r="D11" s="2">
+        <v>6</v>
+      </c>
+      <c r="E11" s="2">
         <v>1</v>
       </c>
-      <c r="E11" s="2" t="b">
+      <c r="F11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="2">
+        <v>3</v>
+      </c>
+      <c r="H11" s="2">
+        <v>5</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" s="2">
         <v>0</v>
       </c>
-      <c r="F11" s="2">
-        <v>6</v>
-      </c>
-      <c r="G11" s="2">
-        <v>1</v>
-      </c>
-      <c r="H11" s="2">
-        <v>3</v>
-      </c>
-      <c r="I11" s="2">
-        <v>5</v>
-      </c>
-      <c r="J11" s="2">
-        <v>1</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O11" s="2">
-        <v>0</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="1:16">
+      <c r="L11" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A12" s="2">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>1001100307</v>
       </c>
       <c r="B12" s="2">
         <v>100100</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="8">
         <v>4</v>
       </c>
       <c r="D12" s="2">
+        <v>7</v>
+      </c>
+      <c r="E12" s="2">
         <v>1</v>
       </c>
-      <c r="E12" s="2" t="b">
+      <c r="F12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="2">
+        <v>3</v>
+      </c>
+      <c r="H12" s="2">
+        <v>10</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K12" s="2">
         <v>0</v>
       </c>
-      <c r="F12" s="2">
-        <v>7</v>
-      </c>
-      <c r="G12" s="2">
-        <v>1</v>
-      </c>
-      <c r="H12" s="2">
-        <v>3</v>
-      </c>
-      <c r="I12" s="2">
-        <v>10</v>
-      </c>
-      <c r="J12" s="2">
-        <v>1</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O12" s="2">
-        <v>0</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" spans="1:16">
+      <c r="L12" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A13" s="2">
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>1001100308</v>
       </c>
       <c r="B13" s="2">
         <v>100100</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="8">
         <v>4</v>
       </c>
       <c r="D13" s="2">
+        <v>8</v>
+      </c>
+      <c r="E13" s="2">
         <v>1</v>
       </c>
-      <c r="E13" s="2" t="b">
+      <c r="F13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="2">
+        <v>3</v>
+      </c>
+      <c r="H13" s="2">
+        <v>10</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13" s="2">
         <v>0</v>
       </c>
-      <c r="F13" s="2">
-        <v>8</v>
-      </c>
-      <c r="G13" s="2">
-        <v>1</v>
-      </c>
-      <c r="H13" s="2">
-        <v>3</v>
-      </c>
-      <c r="I13" s="2">
-        <v>10</v>
-      </c>
-      <c r="J13" s="2">
-        <v>1</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O13" s="2">
-        <v>0</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="1:16">
+      <c r="L13" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A14" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>1001100309</v>
       </c>
       <c r="B14" s="2">
         <v>100100</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="8">
         <v>4</v>
       </c>
       <c r="D14" s="2">
+        <v>9</v>
+      </c>
+      <c r="E14" s="2">
         <v>1</v>
       </c>
-      <c r="E14" s="2" t="b">
+      <c r="F14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="2">
+        <v>3</v>
+      </c>
+      <c r="H14" s="2">
+        <v>15</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14" s="2">
         <v>0</v>
       </c>
-      <c r="F14" s="2">
-        <v>9</v>
-      </c>
-      <c r="G14" s="2">
-        <v>1</v>
-      </c>
-      <c r="H14" s="2">
-        <v>3</v>
-      </c>
-      <c r="I14" s="2">
-        <v>15</v>
-      </c>
-      <c r="J14" s="2">
-        <v>1</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O14" s="2">
-        <v>0</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:16">
+      <c r="L14" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A15" s="2">
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>1001100310</v>
       </c>
       <c r="B15" s="2">
         <v>100100</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="8">
         <v>4</v>
       </c>
       <c r="D15" s="2">
+        <v>10</v>
+      </c>
+      <c r="E15" s="2">
         <v>1</v>
       </c>
-      <c r="E15" s="2" t="b">
+      <c r="F15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="2">
+        <v>3</v>
+      </c>
+      <c r="H15" s="2">
+        <v>15</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K15" s="2">
         <v>0</v>
       </c>
-      <c r="F15" s="2">
-        <v>10</v>
-      </c>
-      <c r="G15" s="2">
-        <v>1</v>
-      </c>
-      <c r="H15" s="2">
-        <v>3</v>
-      </c>
-      <c r="I15" s="2">
-        <v>15</v>
-      </c>
-      <c r="J15" s="2">
-        <v>1</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O15" s="2">
-        <v>0</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:16">
+      <c r="L15" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A16" s="2">
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>1001100311</v>
       </c>
       <c r="B16" s="2">
         <v>100100</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="8">
         <v>4</v>
       </c>
       <c r="D16" s="2">
+        <v>11</v>
+      </c>
+      <c r="E16" s="2">
         <v>1</v>
       </c>
-      <c r="E16" s="2" t="b">
+      <c r="F16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="2">
+        <v>3</v>
+      </c>
+      <c r="H16" s="2">
+        <v>20</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K16" s="2">
         <v>0</v>
       </c>
-      <c r="F16" s="2">
-        <v>11</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1</v>
-      </c>
-      <c r="H16" s="2">
-        <v>3</v>
-      </c>
-      <c r="I16" s="2">
-        <v>20</v>
-      </c>
-      <c r="J16" s="2">
-        <v>1</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O16" s="2">
-        <v>0</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="1:16">
+      <c r="L16" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A17" s="2">
-        <v>13</v>
+        <f t="shared" si="0"/>
+        <v>1001100401</v>
       </c>
       <c r="B17" s="2">
         <v>100100</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="8">
         <v>4</v>
       </c>
       <c r="D17" s="2">
         <v>1</v>
       </c>
-      <c r="E17" s="2" t="b">
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="2">
+        <v>4</v>
+      </c>
+      <c r="H17" s="2">
+        <v>15</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" s="2">
         <v>0</v>
       </c>
-      <c r="F17" s="2">
-        <v>1</v>
-      </c>
-      <c r="G17" s="2">
-        <v>1</v>
-      </c>
-      <c r="H17" s="2">
-        <v>4</v>
-      </c>
-      <c r="I17" s="2">
-        <v>15</v>
-      </c>
-      <c r="J17" s="2">
-        <v>1</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O17" s="2">
-        <v>0</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="1:16">
+      <c r="L17" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A18" s="2">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>1001100402</v>
       </c>
       <c r="B18" s="2">
         <v>100100</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="8">
         <v>4</v>
       </c>
       <c r="D18" s="2">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2">
         <v>1</v>
       </c>
-      <c r="E18" s="2" t="b">
+      <c r="F18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="2">
+        <v>4</v>
+      </c>
+      <c r="H18" s="2">
+        <v>15</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K18" s="2">
         <v>0</v>
       </c>
-      <c r="F18" s="2">
-        <v>2</v>
-      </c>
-      <c r="G18" s="2">
-        <v>1</v>
-      </c>
-      <c r="H18" s="2">
-        <v>4</v>
-      </c>
-      <c r="I18" s="2">
-        <v>15</v>
-      </c>
-      <c r="J18" s="2">
-        <v>1</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O18" s="2">
-        <v>0</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="1:16">
+      <c r="L18" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A19" s="2">
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>1001100403</v>
       </c>
       <c r="B19" s="2">
         <v>100100</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="8">
         <v>4</v>
       </c>
       <c r="D19" s="2">
+        <v>3</v>
+      </c>
+      <c r="E19" s="2">
         <v>1</v>
       </c>
-      <c r="E19" s="2" t="b">
+      <c r="F19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="2">
+        <v>4</v>
+      </c>
+      <c r="H19" s="2">
+        <v>15</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K19" s="2">
         <v>0</v>
       </c>
-      <c r="F19" s="2">
-        <v>3</v>
-      </c>
-      <c r="G19" s="2">
-        <v>1</v>
-      </c>
-      <c r="H19" s="2">
-        <v>4</v>
-      </c>
-      <c r="I19" s="2">
-        <v>15</v>
-      </c>
-      <c r="J19" s="2">
-        <v>1</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O19" s="2">
-        <v>0</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="1:16">
+      <c r="L19" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A20" s="2">
-        <v>16</v>
+        <f t="shared" si="0"/>
+        <v>1001100404</v>
       </c>
       <c r="B20" s="2">
         <v>100100</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="8">
         <v>4</v>
       </c>
       <c r="D20" s="2">
+        <v>4</v>
+      </c>
+      <c r="E20" s="2">
         <v>1</v>
       </c>
-      <c r="E20" s="2" t="b">
+      <c r="F20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="2">
+        <v>4</v>
+      </c>
+      <c r="H20" s="2">
+        <v>15</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K20" s="2">
         <v>0</v>
       </c>
-      <c r="F20" s="2">
-        <v>4</v>
-      </c>
-      <c r="G20" s="2">
-        <v>1</v>
-      </c>
-      <c r="H20" s="2">
-        <v>4</v>
-      </c>
-      <c r="I20" s="2">
-        <v>15</v>
-      </c>
-      <c r="J20" s="2">
-        <v>1</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O20" s="2">
-        <v>0</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="1:16">
+      <c r="L20" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A21" s="2">
-        <v>17</v>
+        <f t="shared" si="0"/>
+        <v>1001100405</v>
       </c>
       <c r="B21" s="2">
         <v>100100</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="8">
         <v>4</v>
       </c>
       <c r="D21" s="2">
+        <v>5</v>
+      </c>
+      <c r="E21" s="2">
         <v>1</v>
       </c>
-      <c r="E21" s="2" t="b">
+      <c r="F21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="2">
+        <v>4</v>
+      </c>
+      <c r="H21" s="2">
+        <v>15</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K21" s="2">
         <v>0</v>
       </c>
-      <c r="F21" s="2">
-        <v>5</v>
-      </c>
-      <c r="G21" s="2">
-        <v>1</v>
-      </c>
-      <c r="H21" s="2">
-        <v>4</v>
-      </c>
-      <c r="I21" s="2">
-        <v>15</v>
-      </c>
-      <c r="J21" s="2">
-        <v>1</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O21" s="2">
-        <v>0</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" spans="1:16">
+      <c r="L21" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A22" s="2">
-        <v>18</v>
+        <f t="shared" si="0"/>
+        <v>1001100406</v>
       </c>
       <c r="B22" s="2">
         <v>100100</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="8">
         <v>4</v>
       </c>
       <c r="D22" s="2">
+        <v>6</v>
+      </c>
+      <c r="E22" s="2">
         <v>1</v>
       </c>
-      <c r="E22" s="2" t="b">
+      <c r="F22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="2">
+        <v>4</v>
+      </c>
+      <c r="H22" s="2">
+        <v>15</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" s="2">
         <v>0</v>
       </c>
-      <c r="F22" s="2">
-        <v>6</v>
-      </c>
-      <c r="G22" s="2">
-        <v>1</v>
-      </c>
-      <c r="H22" s="2">
-        <v>4</v>
-      </c>
-      <c r="I22" s="2">
-        <v>15</v>
-      </c>
-      <c r="J22" s="2">
-        <v>1</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O22" s="2">
-        <v>0</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" spans="1:16">
+      <c r="L22" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A23" s="2">
-        <v>19</v>
+        <f t="shared" si="0"/>
+        <v>1001100407</v>
       </c>
       <c r="B23" s="2">
         <v>100100</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="8">
         <v>4</v>
       </c>
       <c r="D23" s="2">
+        <v>7</v>
+      </c>
+      <c r="E23" s="2">
         <v>1</v>
       </c>
-      <c r="E23" s="2" t="b">
+      <c r="F23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="2">
+        <v>4</v>
+      </c>
+      <c r="H23" s="2">
+        <v>25</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K23" s="2">
         <v>0</v>
       </c>
-      <c r="F23" s="2">
-        <v>7</v>
-      </c>
-      <c r="G23" s="2">
-        <v>1</v>
-      </c>
-      <c r="H23" s="2">
-        <v>4</v>
-      </c>
-      <c r="I23" s="2">
-        <v>25</v>
-      </c>
-      <c r="J23" s="2">
-        <v>1</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O23" s="2">
-        <v>0</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" spans="1:16">
+      <c r="L23" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A24" s="2">
-        <v>20</v>
+        <f t="shared" si="0"/>
+        <v>1001100408</v>
       </c>
       <c r="B24" s="2">
         <v>100100</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="8">
         <v>4</v>
       </c>
       <c r="D24" s="2">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2">
         <v>1</v>
       </c>
-      <c r="E24" s="2" t="b">
+      <c r="F24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="2">
+        <v>4</v>
+      </c>
+      <c r="H24" s="2">
+        <v>25</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K24" s="2">
         <v>0</v>
       </c>
-      <c r="F24" s="2">
-        <v>8</v>
-      </c>
-      <c r="G24" s="2">
-        <v>1</v>
-      </c>
-      <c r="H24" s="2">
-        <v>4</v>
-      </c>
-      <c r="I24" s="2">
-        <v>25</v>
-      </c>
-      <c r="J24" s="2">
-        <v>1</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O24" s="2">
-        <v>0</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" spans="1:16">
+      <c r="L24" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A25" s="2">
-        <v>21</v>
+        <f t="shared" si="0"/>
+        <v>1001100409</v>
       </c>
       <c r="B25" s="2">
         <v>100100</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="8">
         <v>4</v>
       </c>
       <c r="D25" s="2">
+        <v>9</v>
+      </c>
+      <c r="E25" s="2">
         <v>1</v>
       </c>
-      <c r="E25" s="2" t="b">
+      <c r="F25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="2">
+        <v>4</v>
+      </c>
+      <c r="H25" s="2">
+        <v>30</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K25" s="2">
         <v>0</v>
       </c>
-      <c r="F25" s="2">
-        <v>9</v>
-      </c>
-      <c r="G25" s="2">
-        <v>1</v>
-      </c>
-      <c r="H25" s="2">
-        <v>4</v>
-      </c>
-      <c r="I25" s="2">
-        <v>30</v>
-      </c>
-      <c r="J25" s="2">
-        <v>1</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O25" s="2">
-        <v>0</v>
-      </c>
-      <c r="P25" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" spans="1:16">
+      <c r="L25" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A26" s="2">
-        <v>22</v>
+        <f t="shared" si="0"/>
+        <v>1001100410</v>
       </c>
       <c r="B26" s="2">
         <v>100100</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="8">
         <v>4</v>
       </c>
       <c r="D26" s="2">
+        <v>10</v>
+      </c>
+      <c r="E26" s="2">
         <v>1</v>
       </c>
-      <c r="E26" s="2" t="b">
+      <c r="F26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="2">
+        <v>4</v>
+      </c>
+      <c r="H26" s="2">
+        <v>30</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K26" s="2">
         <v>0</v>
       </c>
-      <c r="F26" s="2">
-        <v>10</v>
-      </c>
-      <c r="G26" s="2">
-        <v>1</v>
-      </c>
-      <c r="H26" s="2">
-        <v>4</v>
-      </c>
-      <c r="I26" s="2">
-        <v>30</v>
-      </c>
-      <c r="J26" s="2">
-        <v>1</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O26" s="2">
-        <v>0</v>
-      </c>
-      <c r="P26" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:16">
+      <c r="L26" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A27" s="2">
-        <v>23</v>
+        <f t="shared" si="0"/>
+        <v>1001100411</v>
       </c>
       <c r="B27" s="2">
         <v>100100</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="8">
         <v>4</v>
       </c>
       <c r="D27" s="2">
+        <v>11</v>
+      </c>
+      <c r="E27" s="2">
         <v>1</v>
       </c>
-      <c r="E27" s="2" t="b">
+      <c r="F27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="2">
+        <v>4</v>
+      </c>
+      <c r="H27" s="2">
+        <v>50</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K27" s="2">
         <v>0</v>
       </c>
-      <c r="F27" s="2">
-        <v>11</v>
-      </c>
-      <c r="G27" s="2">
-        <v>1</v>
-      </c>
-      <c r="H27" s="2">
-        <v>4</v>
-      </c>
-      <c r="I27" s="2">
-        <v>50</v>
-      </c>
-      <c r="J27" s="2">
-        <v>1</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O27" s="2">
-        <v>0</v>
-      </c>
-      <c r="P27" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" spans="1:16">
+      <c r="L27" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A28" s="2">
-        <v>24</v>
+        <f t="shared" si="0"/>
+        <v>1001100501</v>
       </c>
       <c r="B28" s="2">
         <v>100100</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="8">
         <v>4</v>
       </c>
       <c r="D28" s="2">
         <v>1</v>
       </c>
-      <c r="E28" s="2" t="b">
+      <c r="E28" s="2">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="2">
+        <v>5</v>
+      </c>
+      <c r="H28" s="2">
+        <v>50</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K28" s="2">
         <v>0</v>
       </c>
-      <c r="F28" s="2">
-        <v>1</v>
-      </c>
-      <c r="G28" s="2">
-        <v>1</v>
-      </c>
-      <c r="H28" s="2">
-        <v>5</v>
-      </c>
-      <c r="I28" s="2">
-        <v>50</v>
-      </c>
-      <c r="J28" s="2">
-        <v>1</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O28" s="2">
-        <v>0</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="1:16">
+      <c r="L28" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A29" s="2">
-        <v>25</v>
+        <f t="shared" si="0"/>
+        <v>1001100502</v>
       </c>
       <c r="B29" s="2">
         <v>100100</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="8">
         <v>4</v>
       </c>
       <c r="D29" s="2">
+        <v>2</v>
+      </c>
+      <c r="E29" s="2">
         <v>1</v>
       </c>
-      <c r="E29" s="2" t="b">
+      <c r="F29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="2">
+        <v>5</v>
+      </c>
+      <c r="H29" s="2">
+        <v>50</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K29" s="2">
         <v>0</v>
       </c>
-      <c r="F29" s="2">
-        <v>2</v>
-      </c>
-      <c r="G29" s="2">
-        <v>1</v>
-      </c>
-      <c r="H29" s="2">
-        <v>5</v>
-      </c>
-      <c r="I29" s="2">
-        <v>50</v>
-      </c>
-      <c r="J29" s="2">
-        <v>1</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O29" s="2">
-        <v>0</v>
-      </c>
-      <c r="P29" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="1:16">
+      <c r="L29" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A30" s="2">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>1001100503</v>
       </c>
       <c r="B30" s="2">
         <v>100100</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="8">
         <v>4</v>
       </c>
       <c r="D30" s="2">
+        <v>3</v>
+      </c>
+      <c r="E30" s="2">
         <v>1</v>
       </c>
-      <c r="E30" s="2" t="b">
+      <c r="F30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30" s="2">
+        <v>5</v>
+      </c>
+      <c r="H30" s="2">
+        <v>50</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K30" s="2">
         <v>0</v>
       </c>
-      <c r="F30" s="2">
-        <v>3</v>
-      </c>
-      <c r="G30" s="2">
-        <v>1</v>
-      </c>
-      <c r="H30" s="2">
-        <v>5</v>
-      </c>
-      <c r="I30" s="2">
-        <v>50</v>
-      </c>
-      <c r="J30" s="2">
-        <v>1</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O30" s="2">
-        <v>0</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" spans="1:16">
+      <c r="L30" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A31" s="2">
-        <v>27</v>
+        <f t="shared" si="0"/>
+        <v>1001100504</v>
       </c>
       <c r="B31" s="2">
         <v>100100</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="8">
         <v>4</v>
       </c>
       <c r="D31" s="2">
+        <v>4</v>
+      </c>
+      <c r="E31" s="2">
         <v>1</v>
       </c>
-      <c r="E31" s="2" t="b">
+      <c r="F31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G31" s="2">
+        <v>5</v>
+      </c>
+      <c r="H31" s="2">
+        <v>50</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K31" s="2">
         <v>0</v>
       </c>
-      <c r="F31" s="2">
-        <v>4</v>
-      </c>
-      <c r="G31" s="2">
-        <v>1</v>
-      </c>
-      <c r="H31" s="2">
-        <v>5</v>
-      </c>
-      <c r="I31" s="2">
-        <v>50</v>
-      </c>
-      <c r="J31" s="2">
-        <v>1</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O31" s="2">
-        <v>0</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="1:16">
+      <c r="L31" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A32" s="2">
-        <v>28</v>
+        <f t="shared" si="0"/>
+        <v>1001100505</v>
       </c>
       <c r="B32" s="2">
         <v>100100</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="8">
         <v>4</v>
       </c>
       <c r="D32" s="2">
+        <v>5</v>
+      </c>
+      <c r="E32" s="2">
         <v>1</v>
       </c>
-      <c r="E32" s="2" t="b">
+      <c r="F32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G32" s="2">
+        <v>5</v>
+      </c>
+      <c r="H32" s="2">
+        <v>50</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K32" s="2">
         <v>0</v>
       </c>
-      <c r="F32" s="2">
-        <v>5</v>
-      </c>
-      <c r="G32" s="2">
-        <v>1</v>
-      </c>
-      <c r="H32" s="2">
-        <v>5</v>
-      </c>
-      <c r="I32" s="2">
-        <v>50</v>
-      </c>
-      <c r="J32" s="2">
-        <v>1</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O32" s="2">
-        <v>0</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" spans="1:16">
+      <c r="L32" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A33" s="2">
-        <v>29</v>
+        <f t="shared" si="0"/>
+        <v>1001100506</v>
       </c>
       <c r="B33" s="2">
         <v>100100</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="8">
         <v>4</v>
       </c>
       <c r="D33" s="2">
+        <v>6</v>
+      </c>
+      <c r="E33" s="2">
         <v>1</v>
       </c>
-      <c r="E33" s="2" t="b">
+      <c r="F33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33" s="2">
+        <v>5</v>
+      </c>
+      <c r="H33" s="2">
+        <v>50</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K33" s="2">
         <v>0</v>
       </c>
-      <c r="F33" s="2">
-        <v>6</v>
-      </c>
-      <c r="G33" s="2">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2">
-        <v>5</v>
-      </c>
-      <c r="I33" s="2">
-        <v>50</v>
-      </c>
-      <c r="J33" s="2">
-        <v>1</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O33" s="2">
-        <v>0</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" spans="1:16">
+      <c r="L33" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A34" s="2">
-        <v>30</v>
+        <f t="shared" si="0"/>
+        <v>1001100507</v>
       </c>
       <c r="B34" s="2">
         <v>100100</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="8">
         <v>4</v>
       </c>
       <c r="D34" s="2">
+        <v>7</v>
+      </c>
+      <c r="E34" s="2">
         <v>1</v>
       </c>
-      <c r="E34" s="2" t="b">
+      <c r="F34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="2">
+        <v>5</v>
+      </c>
+      <c r="H34" s="2">
+        <v>100</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K34" s="2">
         <v>0</v>
       </c>
-      <c r="F34" s="2">
-        <v>7</v>
-      </c>
-      <c r="G34" s="2">
-        <v>1</v>
-      </c>
-      <c r="H34" s="2">
-        <v>5</v>
-      </c>
-      <c r="I34" s="2">
-        <v>100</v>
-      </c>
-      <c r="J34" s="2">
-        <v>1</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O34" s="2">
-        <v>0</v>
-      </c>
-      <c r="P34" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" spans="1:16">
+      <c r="L34" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A35" s="2">
-        <v>31</v>
+        <f t="shared" si="0"/>
+        <v>1001100508</v>
       </c>
       <c r="B35" s="2">
         <v>100100</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="8">
         <v>4</v>
       </c>
       <c r="D35" s="2">
+        <v>8</v>
+      </c>
+      <c r="E35" s="2">
         <v>1</v>
       </c>
-      <c r="E35" s="2" t="b">
+      <c r="F35" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" s="2">
+        <v>5</v>
+      </c>
+      <c r="H35" s="2">
+        <v>100</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" s="2">
         <v>0</v>
       </c>
-      <c r="F35" s="2">
-        <v>8</v>
-      </c>
-      <c r="G35" s="2">
-        <v>1</v>
-      </c>
-      <c r="H35" s="2">
-        <v>5</v>
-      </c>
-      <c r="I35" s="2">
-        <v>100</v>
-      </c>
-      <c r="J35" s="2">
-        <v>1</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O35" s="2">
-        <v>0</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" spans="1:16">
+      <c r="L35" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A36" s="2">
-        <v>32</v>
+        <f t="shared" si="0"/>
+        <v>1001100509</v>
       </c>
       <c r="B36" s="2">
         <v>100100</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="8">
         <v>4</v>
       </c>
       <c r="D36" s="2">
+        <v>9</v>
+      </c>
+      <c r="E36" s="2">
         <v>1</v>
       </c>
-      <c r="E36" s="2" t="b">
+      <c r="F36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="2">
+        <v>5</v>
+      </c>
+      <c r="H36" s="2">
+        <v>200</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="2">
         <v>0</v>
       </c>
-      <c r="F36" s="2">
-        <v>9</v>
-      </c>
-      <c r="G36" s="2">
-        <v>1</v>
-      </c>
-      <c r="H36" s="2">
-        <v>5</v>
-      </c>
-      <c r="I36" s="2">
-        <v>200</v>
-      </c>
-      <c r="J36" s="2">
-        <v>1</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O36" s="2">
-        <v>0</v>
-      </c>
-      <c r="P36" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" spans="1:16">
+      <c r="L36" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A37" s="2">
-        <v>33</v>
+        <f t="shared" si="0"/>
+        <v>1001100510</v>
       </c>
       <c r="B37" s="2">
         <v>100100</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="8">
         <v>4</v>
       </c>
       <c r="D37" s="2">
+        <v>10</v>
+      </c>
+      <c r="E37" s="2">
         <v>1</v>
       </c>
-      <c r="E37" s="2" t="b">
+      <c r="F37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G37" s="2">
+        <v>5</v>
+      </c>
+      <c r="H37" s="2">
+        <v>200</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K37" s="2">
         <v>0</v>
       </c>
-      <c r="F37" s="2">
-        <v>10</v>
-      </c>
-      <c r="G37" s="2">
-        <v>1</v>
-      </c>
-      <c r="H37" s="2">
-        <v>5</v>
-      </c>
-      <c r="I37" s="2">
-        <v>200</v>
-      </c>
-      <c r="J37" s="2">
-        <v>1</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O37" s="2">
-        <v>0</v>
-      </c>
-      <c r="P37" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38" s="2" customFormat="1" spans="1:16">
+      <c r="L37" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A38" s="2">
-        <v>34</v>
+        <f t="shared" si="0"/>
+        <v>1001100511</v>
       </c>
       <c r="B38" s="2">
         <v>100100</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="8">
         <v>4</v>
       </c>
       <c r="D38" s="2">
+        <v>11</v>
+      </c>
+      <c r="E38" s="2">
         <v>1</v>
       </c>
-      <c r="E38" s="2" t="b">
+      <c r="F38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38" s="2">
+        <v>5</v>
+      </c>
+      <c r="H38" s="2">
+        <v>300</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K38" s="2">
         <v>0</v>
       </c>
-      <c r="F38" s="2">
+      <c r="L38" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A39" s="2">
+        <f t="shared" si="0"/>
+        <v>1001201619</v>
+      </c>
+      <c r="B39" s="14">
+        <v>100100</v>
+      </c>
+      <c r="C39" s="8">
+        <v>4</v>
+      </c>
+      <c r="D39" s="14">
+        <v>19</v>
+      </c>
+      <c r="E39" s="14">
+        <v>2</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G39" s="14">
+        <v>16</v>
+      </c>
+      <c r="H39" s="14">
+        <v>0</v>
+      </c>
+      <c r="I39" s="26">
+        <v>30010001</v>
+      </c>
+      <c r="J39" s="14"/>
+      <c r="K39" s="27">
+        <v>4001001</v>
+      </c>
+      <c r="L39" s="28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A40" s="2">
+        <f t="shared" si="0"/>
+        <v>1001201620</v>
+      </c>
+      <c r="B40" s="14">
+        <v>100100</v>
+      </c>
+      <c r="C40" s="8">
+        <v>4</v>
+      </c>
+      <c r="D40" s="14">
+        <v>20</v>
+      </c>
+      <c r="E40" s="14">
+        <v>2</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G40" s="14">
+        <v>16</v>
+      </c>
+      <c r="H40" s="14">
+        <v>0</v>
+      </c>
+      <c r="I40" s="26">
+        <v>30010002</v>
+      </c>
+      <c r="J40" s="14"/>
+      <c r="K40" s="27">
+        <v>4001002</v>
+      </c>
+      <c r="L40" s="28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A41" s="2">
+        <f t="shared" si="0"/>
+        <v>1001201621</v>
+      </c>
+      <c r="B41" s="14">
+        <v>100100</v>
+      </c>
+      <c r="C41" s="8">
+        <v>4</v>
+      </c>
+      <c r="D41" s="14">
+        <v>21</v>
+      </c>
+      <c r="E41" s="14">
+        <v>2</v>
+      </c>
+      <c r="F41" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G41" s="14">
+        <v>16</v>
+      </c>
+      <c r="H41" s="15">
+        <v>0</v>
+      </c>
+      <c r="I41" s="26">
+        <v>30010003</v>
+      </c>
+      <c r="J41" s="14"/>
+      <c r="K41" s="27">
+        <v>4001003</v>
+      </c>
+      <c r="L41" s="28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A42" s="2">
+        <f t="shared" si="0"/>
+        <v>1001201622</v>
+      </c>
+      <c r="B42" s="14">
+        <v>100100</v>
+      </c>
+      <c r="C42" s="8">
+        <v>4</v>
+      </c>
+      <c r="D42" s="14">
+        <v>22</v>
+      </c>
+      <c r="E42" s="14">
+        <v>2</v>
+      </c>
+      <c r="F42" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42" s="14">
+        <v>16</v>
+      </c>
+      <c r="H42" s="15">
+        <v>0</v>
+      </c>
+      <c r="I42" s="26">
+        <v>30010004</v>
+      </c>
+      <c r="J42" s="14"/>
+      <c r="K42" s="27">
+        <v>4001004</v>
+      </c>
+      <c r="L42" s="28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="1:12">
+      <c r="A43" s="2">
+        <f t="shared" ref="A43:A48" si="1">(B43)*10000+D43+G43*100+E43*100000</f>
+        <v>1001201628</v>
+      </c>
+      <c r="B43" s="16">
+        <v>100100</v>
+      </c>
+      <c r="C43" s="8">
+        <v>4</v>
+      </c>
+      <c r="D43" s="16">
+        <v>28</v>
+      </c>
+      <c r="E43" s="16">
+        <v>2</v>
+      </c>
+      <c r="F43" s="16"/>
+      <c r="G43" s="16">
+        <v>16</v>
+      </c>
+      <c r="H43" s="17">
+        <v>0</v>
+      </c>
+      <c r="I43" s="29">
+        <v>30010005</v>
+      </c>
+      <c r="J43" s="16"/>
+      <c r="K43" s="16">
+        <v>0</v>
+      </c>
+      <c r="L43" s="30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="1:12">
+      <c r="A44" s="2">
+        <f t="shared" si="1"/>
+        <v>1001201528</v>
+      </c>
+      <c r="B44" s="18">
+        <v>100100</v>
+      </c>
+      <c r="C44" s="8">
+        <v>4</v>
+      </c>
+      <c r="D44" s="18">
+        <v>28</v>
+      </c>
+      <c r="E44" s="18">
+        <v>2</v>
+      </c>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18">
+        <v>15</v>
+      </c>
+      <c r="H44" s="19">
+        <v>0</v>
+      </c>
+      <c r="I44" s="31">
+        <v>30010006</v>
+      </c>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18">
+        <v>0</v>
+      </c>
+      <c r="L44" s="32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="1:12">
+      <c r="A45" s="2">
+        <f t="shared" si="1"/>
+        <v>1001400317</v>
+      </c>
+      <c r="B45" s="20">
+        <v>100100</v>
+      </c>
+      <c r="C45" s="8">
+        <v>1</v>
+      </c>
+      <c r="D45" s="20">
+        <v>17</v>
+      </c>
+      <c r="E45" s="20">
+        <v>4</v>
+      </c>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20">
+        <v>3</v>
+      </c>
+      <c r="H45" s="21">
+        <v>0</v>
+      </c>
+      <c r="I45" s="33"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="20">
+        <v>0</v>
+      </c>
+      <c r="L45" s="34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="1:12">
+      <c r="A46" s="2">
+        <f t="shared" si="1"/>
+        <v>1001400417</v>
+      </c>
+      <c r="B46" s="22">
+        <v>100100</v>
+      </c>
+      <c r="C46" s="8">
+        <v>1</v>
+      </c>
+      <c r="D46" s="22">
+        <v>17</v>
+      </c>
+      <c r="E46" s="22">
+        <v>4</v>
+      </c>
+      <c r="F46" s="22"/>
+      <c r="G46" s="22">
+        <v>4</v>
+      </c>
+      <c r="H46" s="23">
+        <v>0</v>
+      </c>
+      <c r="I46" s="35"/>
+      <c r="J46" s="22"/>
+      <c r="K46" s="22">
+        <v>0</v>
+      </c>
+      <c r="L46" s="36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="1:12">
+      <c r="A47" s="2">
+        <f t="shared" si="1"/>
+        <v>1001400517</v>
+      </c>
+      <c r="B47" s="22">
+        <v>100100</v>
+      </c>
+      <c r="C47" s="8">
+        <v>1</v>
+      </c>
+      <c r="D47" s="22">
+        <v>17</v>
+      </c>
+      <c r="E47" s="22">
+        <v>4</v>
+      </c>
+      <c r="F47" s="22"/>
+      <c r="G47" s="22">
+        <v>5</v>
+      </c>
+      <c r="H47" s="23">
+        <v>0</v>
+      </c>
+      <c r="I47" s="35"/>
+      <c r="J47" s="22"/>
+      <c r="K47" s="22">
+        <v>0</v>
+      </c>
+      <c r="L47" s="36" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A48" s="2">
+        <f t="shared" si="1"/>
+        <v>1001400130</v>
+      </c>
+      <c r="B48" s="22">
+        <v>100100</v>
+      </c>
+      <c r="C48" s="8">
+        <v>1</v>
+      </c>
+      <c r="D48" s="22">
+        <v>30</v>
+      </c>
+      <c r="E48" s="22">
+        <v>4</v>
+      </c>
+      <c r="F48" s="22"/>
+      <c r="G48" s="22">
+        <v>1</v>
+      </c>
+      <c r="H48" s="23">
+        <v>0</v>
+      </c>
+      <c r="I48" s="35">
+        <v>30010007</v>
+      </c>
+      <c r="J48" s="22"/>
+      <c r="K48" s="22">
+        <v>0</v>
+      </c>
+      <c r="L48" s="36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A49" s="2">
+        <v>1007300301</v>
+      </c>
+      <c r="B49" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C49" s="8">
+        <v>4</v>
+      </c>
+      <c r="D49" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E49" s="14">
+        <v>3</v>
+      </c>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14">
+        <v>3</v>
+      </c>
+      <c r="H49" s="15">
+        <v>2</v>
+      </c>
+      <c r="I49" s="15"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="14"/>
+      <c r="L49" s="10"/>
+    </row>
+    <row r="50" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A50" s="2">
+        <v>1007300302</v>
+      </c>
+      <c r="B50" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C50" s="8">
+        <v>4</v>
+      </c>
+      <c r="D50" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E50" s="14">
+        <v>3</v>
+      </c>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14">
+        <v>3</v>
+      </c>
+      <c r="H50" s="15">
+        <v>2</v>
+      </c>
+      <c r="I50" s="15"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="14"/>
+      <c r="L50" s="10"/>
+    </row>
+    <row r="51" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A51" s="2">
+        <v>1007300303</v>
+      </c>
+      <c r="B51" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C51" s="8">
+        <v>4</v>
+      </c>
+      <c r="D51" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="E51" s="14">
+        <v>3</v>
+      </c>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14">
+        <v>3</v>
+      </c>
+      <c r="H51" s="15">
+        <v>4</v>
+      </c>
+      <c r="I51" s="15"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="14"/>
+      <c r="L51" s="10"/>
+    </row>
+    <row r="52" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A52" s="2">
+        <v>1007300304</v>
+      </c>
+      <c r="B52" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C52" s="8">
+        <v>4</v>
+      </c>
+      <c r="D52" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E52" s="14">
+        <v>3</v>
+      </c>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14">
+        <v>3</v>
+      </c>
+      <c r="H52" s="15">
+        <v>4</v>
+      </c>
+      <c r="I52" s="15"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="14"/>
+      <c r="L52" s="10"/>
+    </row>
+    <row r="53" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A53" s="2">
+        <v>1007300305</v>
+      </c>
+      <c r="B53" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C53" s="8">
+        <v>4</v>
+      </c>
+      <c r="D53" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E53" s="14">
+        <v>3</v>
+      </c>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14">
+        <v>3</v>
+      </c>
+      <c r="H53" s="15">
+        <v>6</v>
+      </c>
+      <c r="I53" s="15"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="14"/>
+      <c r="L53" s="10"/>
+    </row>
+    <row r="54" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A54" s="2">
+        <v>1007300306</v>
+      </c>
+      <c r="B54" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C54" s="8">
+        <v>4</v>
+      </c>
+      <c r="D54" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E54" s="14">
+        <v>3</v>
+      </c>
+      <c r="F54" s="14"/>
+      <c r="G54" s="14">
+        <v>3</v>
+      </c>
+      <c r="H54" s="15">
+        <v>8</v>
+      </c>
+      <c r="I54" s="15"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="14"/>
+      <c r="L54" s="10"/>
+    </row>
+    <row r="55" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A55" s="2">
+        <v>1007300307</v>
+      </c>
+      <c r="B55" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C55" s="8">
+        <v>4</v>
+      </c>
+      <c r="D55" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E55" s="14">
+        <v>3</v>
+      </c>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14">
+        <v>3</v>
+      </c>
+      <c r="H55" s="15">
+        <v>10</v>
+      </c>
+      <c r="I55" s="15"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="14"/>
+      <c r="L55" s="10"/>
+    </row>
+    <row r="56" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A56" s="2">
+        <v>1007300308</v>
+      </c>
+      <c r="B56" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C56" s="8">
+        <v>4</v>
+      </c>
+      <c r="D56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E56" s="14">
+        <v>3</v>
+      </c>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14">
+        <v>3</v>
+      </c>
+      <c r="H56" s="15">
+        <v>15</v>
+      </c>
+      <c r="I56" s="15"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="14"/>
+      <c r="L56" s="10"/>
+    </row>
+    <row r="57" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A57" s="2">
+        <v>1007300401</v>
+      </c>
+      <c r="B57" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C57" s="8">
+        <v>4</v>
+      </c>
+      <c r="D57" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E57" s="14">
+        <v>3</v>
+      </c>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14">
+        <v>4</v>
+      </c>
+      <c r="H57" s="15">
+        <v>5</v>
+      </c>
+      <c r="I57" s="15"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="14"/>
+      <c r="L57" s="10"/>
+    </row>
+    <row r="58" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A58" s="2">
+        <v>1007300402</v>
+      </c>
+      <c r="B58" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C58" s="8">
+        <v>4</v>
+      </c>
+      <c r="D58" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E58" s="14">
+        <v>3</v>
+      </c>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14">
+        <v>4</v>
+      </c>
+      <c r="H58" s="15">
+        <v>5</v>
+      </c>
+      <c r="I58" s="15"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="14"/>
+      <c r="L58" s="10"/>
+    </row>
+    <row r="59" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A59" s="2">
+        <v>1007300403</v>
+      </c>
+      <c r="B59" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C59" s="8">
+        <v>4</v>
+      </c>
+      <c r="D59" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="E59" s="14">
+        <v>3</v>
+      </c>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14">
+        <v>4</v>
+      </c>
+      <c r="H59" s="15">
+        <v>10</v>
+      </c>
+      <c r="I59" s="15"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="14"/>
+      <c r="L59" s="10"/>
+    </row>
+    <row r="60" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A60" s="2">
+        <v>1007300404</v>
+      </c>
+      <c r="B60" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C60" s="8">
+        <v>4</v>
+      </c>
+      <c r="D60" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E60" s="14">
+        <v>3</v>
+      </c>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14">
+        <v>4</v>
+      </c>
+      <c r="H60" s="15">
+        <v>10</v>
+      </c>
+      <c r="I60" s="15"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="14"/>
+      <c r="L60" s="10"/>
+    </row>
+    <row r="61" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A61" s="2">
+        <v>1007300405</v>
+      </c>
+      <c r="B61" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C61" s="8">
+        <v>4</v>
+      </c>
+      <c r="D61" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E61" s="14">
+        <v>3</v>
+      </c>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14">
+        <v>4</v>
+      </c>
+      <c r="H61" s="15">
+        <v>15</v>
+      </c>
+      <c r="I61" s="15"/>
+      <c r="J61" s="14"/>
+      <c r="K61" s="14"/>
+      <c r="L61" s="10"/>
+    </row>
+    <row r="62" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A62" s="2">
+        <v>1007300406</v>
+      </c>
+      <c r="B62" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C62" s="8">
+        <v>4</v>
+      </c>
+      <c r="D62" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E62" s="14">
+        <v>3</v>
+      </c>
+      <c r="F62" s="14"/>
+      <c r="G62" s="14">
+        <v>4</v>
+      </c>
+      <c r="H62" s="15">
+        <v>20</v>
+      </c>
+      <c r="I62" s="15"/>
+      <c r="J62" s="14"/>
+      <c r="K62" s="14"/>
+      <c r="L62" s="10"/>
+    </row>
+    <row r="63" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A63" s="2">
+        <v>1007300407</v>
+      </c>
+      <c r="B63" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C63" s="8">
+        <v>4</v>
+      </c>
+      <c r="D63" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E63" s="14">
+        <v>3</v>
+      </c>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14">
+        <v>4</v>
+      </c>
+      <c r="H63" s="15">
+        <v>40</v>
+      </c>
+      <c r="I63" s="15"/>
+      <c r="J63" s="14"/>
+      <c r="K63" s="14"/>
+      <c r="L63" s="10"/>
+    </row>
+    <row r="64" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A64" s="2">
+        <v>1007300408</v>
+      </c>
+      <c r="B64" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C64" s="8">
+        <v>4</v>
+      </c>
+      <c r="D64" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E64" s="14">
+        <v>3</v>
+      </c>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14">
+        <v>4</v>
+      </c>
+      <c r="H64" s="15">
+        <v>60</v>
+      </c>
+      <c r="I64" s="15"/>
+      <c r="J64" s="14"/>
+      <c r="K64" s="14"/>
+      <c r="L64" s="10"/>
+    </row>
+    <row r="65" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A65" s="2">
+        <v>1007300501</v>
+      </c>
+      <c r="B65" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C65" s="8">
+        <v>4</v>
+      </c>
+      <c r="D65" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E65" s="14">
+        <v>3</v>
+      </c>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14">
+        <v>5</v>
+      </c>
+      <c r="H65" s="15">
+        <v>10</v>
+      </c>
+      <c r="I65" s="15"/>
+      <c r="J65" s="14"/>
+      <c r="K65" s="14"/>
+      <c r="L65" s="10"/>
+    </row>
+    <row r="66" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A66" s="2">
+        <v>1007300502</v>
+      </c>
+      <c r="B66" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C66" s="8">
+        <v>4</v>
+      </c>
+      <c r="D66" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E66" s="14">
+        <v>3</v>
+      </c>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14">
+        <v>5</v>
+      </c>
+      <c r="H66" s="15">
+        <v>10</v>
+      </c>
+      <c r="I66" s="15"/>
+      <c r="J66" s="14"/>
+      <c r="K66" s="14"/>
+      <c r="L66" s="10"/>
+    </row>
+    <row r="67" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A67" s="2">
+        <v>1007300503</v>
+      </c>
+      <c r="B67" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C67" s="8">
+        <v>4</v>
+      </c>
+      <c r="D67" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="E67" s="14">
+        <v>3</v>
+      </c>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14">
+        <v>5</v>
+      </c>
+      <c r="H67" s="15">
+        <v>20</v>
+      </c>
+      <c r="I67" s="15"/>
+      <c r="J67" s="14"/>
+      <c r="K67" s="14"/>
+      <c r="L67" s="10"/>
+    </row>
+    <row r="68" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A68" s="2">
+        <v>1007300504</v>
+      </c>
+      <c r="B68" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C68" s="8">
+        <v>4</v>
+      </c>
+      <c r="D68" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E68" s="14">
+        <v>3</v>
+      </c>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14">
+        <v>5</v>
+      </c>
+      <c r="H68" s="15">
+        <v>20</v>
+      </c>
+      <c r="I68" s="15"/>
+      <c r="J68" s="14"/>
+      <c r="K68" s="14"/>
+      <c r="L68" s="10"/>
+    </row>
+    <row r="69" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A69" s="2">
+        <v>1007300505</v>
+      </c>
+      <c r="B69" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C69" s="8">
+        <v>4</v>
+      </c>
+      <c r="D69" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E69" s="14">
+        <v>3</v>
+      </c>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14">
+        <v>5</v>
+      </c>
+      <c r="H69" s="15">
+        <v>30</v>
+      </c>
+      <c r="I69" s="15"/>
+      <c r="J69" s="14"/>
+      <c r="K69" s="14"/>
+      <c r="L69" s="10"/>
+    </row>
+    <row r="70" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A70" s="2">
+        <v>1007300506</v>
+      </c>
+      <c r="B70" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C70" s="8">
+        <v>4</v>
+      </c>
+      <c r="D70" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E70" s="14">
+        <v>3</v>
+      </c>
+      <c r="F70" s="14"/>
+      <c r="G70" s="14">
+        <v>5</v>
+      </c>
+      <c r="H70" s="15">
+        <v>40</v>
+      </c>
+      <c r="I70" s="15"/>
+      <c r="J70" s="14"/>
+      <c r="K70" s="14"/>
+      <c r="L70" s="10"/>
+    </row>
+    <row r="71" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A71" s="2">
+        <v>1007300507</v>
+      </c>
+      <c r="B71" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C71" s="8">
+        <v>4</v>
+      </c>
+      <c r="D71" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E71" s="14">
+        <v>3</v>
+      </c>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14">
+        <v>5</v>
+      </c>
+      <c r="H71" s="15">
+        <v>80</v>
+      </c>
+      <c r="I71" s="15"/>
+      <c r="J71" s="14"/>
+      <c r="K71" s="14"/>
+      <c r="L71" s="10"/>
+    </row>
+    <row r="72" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A72" s="2">
+        <v>1007300508</v>
+      </c>
+      <c r="B72" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C72" s="8">
+        <v>4</v>
+      </c>
+      <c r="D72" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E72" s="14">
+        <v>3</v>
+      </c>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14">
+        <v>5</v>
+      </c>
+      <c r="H72" s="15">
+        <v>120</v>
+      </c>
+      <c r="I72" s="15"/>
+      <c r="J72" s="14"/>
+      <c r="K72" s="14"/>
+      <c r="L72" s="10"/>
+    </row>
+    <row r="73" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A73" s="2">
+        <f t="shared" ref="A73:A85" si="2">(B73)*10000+D73+G73*100+E73*100000</f>
+        <v>1007400310</v>
+      </c>
+      <c r="B73" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C73" s="8">
+        <v>4</v>
+      </c>
+      <c r="D73" s="14">
+        <v>10</v>
+      </c>
+      <c r="E73" s="14">
+        <v>4</v>
+      </c>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14">
+        <v>3</v>
+      </c>
+      <c r="H73" s="15">
+        <v>0</v>
+      </c>
+      <c r="I73" s="15">
+        <v>30070001</v>
+      </c>
+      <c r="J73" s="14"/>
+      <c r="K73" s="14"/>
+      <c r="L73" s="10"/>
+    </row>
+    <row r="74" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A74" s="2">
+        <f t="shared" si="2"/>
+        <v>1007400410</v>
+      </c>
+      <c r="B74" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C74" s="8">
+        <v>4</v>
+      </c>
+      <c r="D74" s="14">
+        <v>10</v>
+      </c>
+      <c r="E74" s="14">
+        <v>4</v>
+      </c>
+      <c r="F74" s="14"/>
+      <c r="G74" s="14">
+        <v>4</v>
+      </c>
+      <c r="H74" s="15">
+        <v>0</v>
+      </c>
+      <c r="I74" s="15">
+        <v>30070002</v>
+      </c>
+      <c r="J74" s="14"/>
+      <c r="K74" s="14"/>
+      <c r="L74" s="10"/>
+    </row>
+    <row r="75" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A75" s="2">
+        <f t="shared" si="2"/>
+        <v>1014500502</v>
+      </c>
+      <c r="B75" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C75" s="8">
+        <v>4</v>
+      </c>
+      <c r="D75" s="37">
+        <v>2</v>
+      </c>
+      <c r="E75" s="37">
+        <v>5</v>
+      </c>
+      <c r="F75" s="37"/>
+      <c r="G75" s="37">
+        <v>5</v>
+      </c>
+      <c r="H75" s="38">
+        <v>1</v>
+      </c>
+      <c r="I75" s="38"/>
+      <c r="J75" s="37"/>
+      <c r="K75" s="37"/>
+      <c r="L75" s="10"/>
+    </row>
+    <row r="76" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A76" s="2">
+        <f t="shared" si="2"/>
+        <v>1014500503</v>
+      </c>
+      <c r="B76" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C76" s="8">
+        <v>4</v>
+      </c>
+      <c r="D76" s="37">
+        <v>3</v>
+      </c>
+      <c r="E76" s="37">
+        <v>5</v>
+      </c>
+      <c r="F76" s="37"/>
+      <c r="G76" s="37">
+        <v>5</v>
+      </c>
+      <c r="H76" s="38">
+        <v>1</v>
+      </c>
+      <c r="I76" s="38"/>
+      <c r="J76" s="37"/>
+      <c r="K76" s="37"/>
+      <c r="L76" s="10"/>
+    </row>
+    <row r="77" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A77" s="2">
+        <f t="shared" si="2"/>
+        <v>1014500504</v>
+      </c>
+      <c r="B77" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C77" s="8">
+        <v>4</v>
+      </c>
+      <c r="D77" s="37">
+        <v>4</v>
+      </c>
+      <c r="E77" s="37">
+        <v>5</v>
+      </c>
+      <c r="F77" s="37"/>
+      <c r="G77" s="37">
+        <v>5</v>
+      </c>
+      <c r="H77" s="38">
+        <v>1</v>
+      </c>
+      <c r="I77" s="38"/>
+      <c r="J77" s="37"/>
+      <c r="K77" s="37"/>
+      <c r="L77" s="10"/>
+    </row>
+    <row r="78" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A78" s="2">
+        <f t="shared" si="2"/>
+        <v>1014500505</v>
+      </c>
+      <c r="B78" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C78" s="8">
+        <v>4</v>
+      </c>
+      <c r="D78" s="37">
+        <v>5</v>
+      </c>
+      <c r="E78" s="37">
+        <v>5</v>
+      </c>
+      <c r="F78" s="37"/>
+      <c r="G78" s="37">
+        <v>5</v>
+      </c>
+      <c r="H78" s="38">
+        <v>2</v>
+      </c>
+      <c r="I78" s="38"/>
+      <c r="J78" s="37"/>
+      <c r="K78" s="37"/>
+      <c r="L78" s="10"/>
+    </row>
+    <row r="79" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A79" s="2">
+        <f t="shared" si="2"/>
+        <v>1014500506</v>
+      </c>
+      <c r="B79" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C79" s="8">
+        <v>4</v>
+      </c>
+      <c r="D79" s="37">
+        <v>6</v>
+      </c>
+      <c r="E79" s="37">
+        <v>5</v>
+      </c>
+      <c r="F79" s="37"/>
+      <c r="G79" s="37">
+        <v>5</v>
+      </c>
+      <c r="H79" s="38">
+        <v>2</v>
+      </c>
+      <c r="I79" s="38"/>
+      <c r="J79" s="37"/>
+      <c r="K79" s="37"/>
+      <c r="L79" s="10"/>
+    </row>
+    <row r="80" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A80" s="2">
+        <f t="shared" si="2"/>
+        <v>1014500507</v>
+      </c>
+      <c r="B80" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C80" s="8">
+        <v>4</v>
+      </c>
+      <c r="D80" s="37">
+        <v>7</v>
+      </c>
+      <c r="E80" s="37">
+        <v>5</v>
+      </c>
+      <c r="F80" s="37"/>
+      <c r="G80" s="37">
+        <v>5</v>
+      </c>
+      <c r="H80" s="38">
+        <v>2</v>
+      </c>
+      <c r="I80" s="38"/>
+      <c r="J80" s="37"/>
+      <c r="K80" s="37"/>
+      <c r="L80" s="10"/>
+    </row>
+    <row r="81" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A81" s="2">
+        <f t="shared" si="2"/>
+        <v>1014500508</v>
+      </c>
+      <c r="B81" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C81" s="8">
+        <v>4</v>
+      </c>
+      <c r="D81" s="37">
+        <v>8</v>
+      </c>
+      <c r="E81" s="37">
+        <v>5</v>
+      </c>
+      <c r="F81" s="37"/>
+      <c r="G81" s="37">
+        <v>5</v>
+      </c>
+      <c r="H81" s="38">
+        <v>3</v>
+      </c>
+      <c r="I81" s="38"/>
+      <c r="J81" s="37"/>
+      <c r="K81" s="37"/>
+      <c r="L81" s="10"/>
+    </row>
+    <row r="82" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A82" s="2">
+        <f t="shared" si="2"/>
+        <v>1014500509</v>
+      </c>
+      <c r="B82" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C82" s="8">
+        <v>4</v>
+      </c>
+      <c r="D82" s="37">
+        <v>9</v>
+      </c>
+      <c r="E82" s="37">
+        <v>5</v>
+      </c>
+      <c r="F82" s="37"/>
+      <c r="G82" s="37">
+        <v>5</v>
+      </c>
+      <c r="H82" s="38">
+        <v>3</v>
+      </c>
+      <c r="I82" s="38"/>
+      <c r="J82" s="37"/>
+      <c r="K82" s="37"/>
+      <c r="L82" s="10"/>
+    </row>
+    <row r="83" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A83" s="2">
+        <f t="shared" si="2"/>
+        <v>1014500510</v>
+      </c>
+      <c r="B83" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C83" s="8">
+        <v>4</v>
+      </c>
+      <c r="D83" s="37">
+        <v>10</v>
+      </c>
+      <c r="E83" s="37">
+        <v>5</v>
+      </c>
+      <c r="F83" s="37"/>
+      <c r="G83" s="37">
+        <v>5</v>
+      </c>
+      <c r="H83" s="38">
+        <v>4</v>
+      </c>
+      <c r="I83" s="38"/>
+      <c r="J83" s="37"/>
+      <c r="K83" s="37"/>
+      <c r="L83" s="10"/>
+    </row>
+    <row r="84" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A84" s="2">
+        <f t="shared" si="2"/>
+        <v>1014500511</v>
+      </c>
+      <c r="B84" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C84" s="8">
+        <v>4</v>
+      </c>
+      <c r="D84" s="37">
         <v>11</v>
       </c>
-      <c r="G38" s="2">
-        <v>1</v>
-      </c>
-      <c r="H38" s="2">
+      <c r="E84" s="37">
         <v>5</v>
       </c>
-      <c r="I38" s="2">
-        <v>300</v>
-      </c>
-      <c r="J38" s="2">
-        <v>1</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O38" s="2">
+      <c r="F84" s="37"/>
+      <c r="G84" s="37">
+        <v>5</v>
+      </c>
+      <c r="H84" s="38">
+        <v>5</v>
+      </c>
+      <c r="I84" s="38"/>
+      <c r="J84" s="37"/>
+      <c r="K84" s="37"/>
+      <c r="L84" s="10"/>
+    </row>
+    <row r="85" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A85" s="2">
+        <f t="shared" si="2"/>
+        <v>1014400513</v>
+      </c>
+      <c r="B85" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C85" s="8">
+        <v>4</v>
+      </c>
+      <c r="D85" s="37">
+        <v>13</v>
+      </c>
+      <c r="E85" s="37">
+        <v>4</v>
+      </c>
+      <c r="F85" s="37"/>
+      <c r="G85" s="37">
+        <v>5</v>
+      </c>
+      <c r="H85" s="38">
         <v>0</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="39" s="2" customFormat="1" spans="1:16">
-      <c r="A39" s="2">
-        <v>35</v>
-      </c>
-      <c r="B39" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C39" s="2">
-        <v>4</v>
-      </c>
-      <c r="D39" s="2">
-        <v>1</v>
-      </c>
-      <c r="E39" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F39" s="2">
-        <v>19</v>
-      </c>
-      <c r="G39" s="2">
-        <v>2</v>
-      </c>
-      <c r="H39" s="2">
-        <v>2</v>
-      </c>
-      <c r="I39" s="2">
-        <v>0</v>
-      </c>
-      <c r="J39" s="2">
-        <v>2</v>
-      </c>
-      <c r="K39" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="O39" s="2">
-        <v>0</v>
-      </c>
-      <c r="P39" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" s="2" customFormat="1" spans="1:16">
-      <c r="A40" s="2">
-        <v>36</v>
-      </c>
-      <c r="B40" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C40" s="2">
-        <v>4</v>
-      </c>
-      <c r="D40" s="2">
-        <v>1</v>
-      </c>
-      <c r="E40" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F40" s="2">
-        <v>20</v>
-      </c>
-      <c r="G40" s="2">
-        <v>2</v>
-      </c>
-      <c r="H40" s="2">
-        <v>2</v>
-      </c>
-      <c r="I40" s="2">
-        <v>0</v>
-      </c>
-      <c r="J40" s="2">
-        <v>2</v>
-      </c>
-      <c r="K40" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="O40" s="2">
-        <v>0</v>
-      </c>
-      <c r="P40" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16">
-      <c r="A41" s="2">
-        <v>37</v>
-      </c>
-      <c r="B41" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C41" s="2">
-        <v>4</v>
-      </c>
-      <c r="D41" s="2">
-        <v>1</v>
-      </c>
-      <c r="E41" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F41" s="2">
-        <v>21</v>
-      </c>
-      <c r="G41" s="2">
-        <v>2</v>
-      </c>
-      <c r="H41" s="2">
-        <v>2</v>
-      </c>
-      <c r="I41" s="5">
-        <v>0</v>
-      </c>
-      <c r="J41" s="2">
-        <v>2</v>
-      </c>
-      <c r="K41" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2">
-        <v>0</v>
-      </c>
-      <c r="P41" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16">
-      <c r="A42" s="2">
-        <v>38</v>
-      </c>
-      <c r="B42" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C42" s="2">
-        <v>4</v>
-      </c>
-      <c r="D42" s="2">
-        <v>1</v>
-      </c>
-      <c r="E42" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F42" s="2">
-        <v>22</v>
-      </c>
-      <c r="G42" s="2">
-        <v>2</v>
-      </c>
-      <c r="H42" s="2">
-        <v>2</v>
-      </c>
-      <c r="I42" s="5">
-        <v>0</v>
-      </c>
-      <c r="J42" s="2">
-        <v>2</v>
-      </c>
-      <c r="K42" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2">
-        <v>0</v>
-      </c>
-      <c r="P42" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16">
-      <c r="A43" s="2">
-        <v>39</v>
-      </c>
-      <c r="B43" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C43" s="2">
-        <v>4</v>
-      </c>
-      <c r="D43" s="2">
-        <v>1</v>
-      </c>
-      <c r="E43" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F43" s="2">
-        <v>19</v>
-      </c>
-      <c r="G43" s="2">
-        <v>2</v>
-      </c>
-      <c r="H43" s="2">
-        <v>3</v>
-      </c>
-      <c r="I43" s="2">
-        <v>0</v>
-      </c>
-      <c r="J43" s="2">
-        <v>2</v>
-      </c>
-      <c r="K43" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L43" s="2"/>
-      <c r="M43" s="2"/>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2">
-        <v>0</v>
-      </c>
-      <c r="P43" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16">
-      <c r="A44" s="2">
-        <v>40</v>
-      </c>
-      <c r="B44" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C44" s="2">
-        <v>4</v>
-      </c>
-      <c r="D44" s="2">
-        <v>1</v>
-      </c>
-      <c r="E44" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F44" s="2">
-        <v>20</v>
-      </c>
-      <c r="G44" s="2">
-        <v>2</v>
-      </c>
-      <c r="H44" s="2">
-        <v>3</v>
-      </c>
-      <c r="I44" s="2">
-        <v>0</v>
-      </c>
-      <c r="J44" s="2">
-        <v>2</v>
-      </c>
-      <c r="K44" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2">
-        <v>0</v>
-      </c>
-      <c r="P44" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16">
-      <c r="A45" s="2">
-        <v>41</v>
-      </c>
-      <c r="B45" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C45" s="2">
-        <v>4</v>
-      </c>
-      <c r="D45" s="2">
-        <v>1</v>
-      </c>
-      <c r="E45" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F45" s="2">
-        <v>21</v>
-      </c>
-      <c r="G45" s="2">
-        <v>2</v>
-      </c>
-      <c r="H45" s="2">
-        <v>3</v>
-      </c>
-      <c r="I45" s="5">
-        <v>0</v>
-      </c>
-      <c r="J45" s="2">
-        <v>2</v>
-      </c>
-      <c r="K45" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2">
-        <v>0</v>
-      </c>
-      <c r="P45" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16">
-      <c r="A46" s="2">
-        <v>42</v>
-      </c>
-      <c r="B46" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C46" s="2">
-        <v>4</v>
-      </c>
-      <c r="D46" s="2">
-        <v>1</v>
-      </c>
-      <c r="E46" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F46" s="2">
-        <v>22</v>
-      </c>
-      <c r="G46" s="2">
-        <v>2</v>
-      </c>
-      <c r="H46" s="2">
-        <v>3</v>
-      </c>
-      <c r="I46" s="5">
-        <v>0</v>
-      </c>
-      <c r="J46" s="2">
-        <v>2</v>
-      </c>
-      <c r="K46" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2">
-        <v>0</v>
-      </c>
-      <c r="P46" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16">
-      <c r="A47" s="2">
-        <v>43</v>
-      </c>
-      <c r="B47" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C47" s="2">
-        <v>4</v>
-      </c>
-      <c r="D47" s="2">
-        <v>1</v>
-      </c>
-      <c r="E47" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F47" s="2">
-        <v>19</v>
-      </c>
-      <c r="G47" s="2">
-        <v>2</v>
-      </c>
-      <c r="H47" s="2">
-        <v>4</v>
-      </c>
-      <c r="I47" s="2">
-        <v>0</v>
-      </c>
-      <c r="J47" s="2">
-        <v>2</v>
-      </c>
-      <c r="K47" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L47" s="2"/>
-      <c r="M47" s="2"/>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2">
-        <v>0</v>
-      </c>
-      <c r="P47" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16">
-      <c r="A48" s="2">
-        <v>44</v>
-      </c>
-      <c r="B48" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C48" s="2">
-        <v>4</v>
-      </c>
-      <c r="D48" s="2">
-        <v>1</v>
-      </c>
-      <c r="E48" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F48" s="2">
-        <v>20</v>
-      </c>
-      <c r="G48" s="2">
-        <v>2</v>
-      </c>
-      <c r="H48" s="2">
-        <v>4</v>
-      </c>
-      <c r="I48" s="2">
-        <v>0</v>
-      </c>
-      <c r="J48" s="2">
-        <v>2</v>
-      </c>
-      <c r="K48" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2">
-        <v>0</v>
-      </c>
-      <c r="P48" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16">
-      <c r="A49" s="2">
-        <v>45</v>
-      </c>
-      <c r="B49" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C49" s="2">
-        <v>4</v>
-      </c>
-      <c r="D49" s="2">
-        <v>1</v>
-      </c>
-      <c r="E49" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F49" s="2">
-        <v>21</v>
-      </c>
-      <c r="G49" s="2">
-        <v>2</v>
-      </c>
-      <c r="H49" s="2">
-        <v>4</v>
-      </c>
-      <c r="I49" s="5">
-        <v>0</v>
-      </c>
-      <c r="J49" s="2">
-        <v>2</v>
-      </c>
-      <c r="K49" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2">
-        <v>0</v>
-      </c>
-      <c r="P49" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16">
-      <c r="A50" s="2">
-        <v>46</v>
-      </c>
-      <c r="B50" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C50" s="2">
-        <v>4</v>
-      </c>
-      <c r="D50" s="2">
-        <v>1</v>
-      </c>
-      <c r="E50" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F50" s="2">
-        <v>22</v>
-      </c>
-      <c r="G50" s="2">
-        <v>2</v>
-      </c>
-      <c r="H50" s="2">
-        <v>4</v>
-      </c>
-      <c r="I50" s="5">
-        <v>0</v>
-      </c>
-      <c r="J50" s="2">
-        <v>2</v>
-      </c>
-      <c r="K50" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2">
-        <v>0</v>
-      </c>
-      <c r="P50" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16">
-      <c r="A51" s="2">
-        <v>47</v>
-      </c>
-      <c r="B51" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C51" s="2">
-        <v>4</v>
-      </c>
-      <c r="D51" s="2">
-        <v>1</v>
-      </c>
-      <c r="E51" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F51" s="2">
-        <v>19</v>
-      </c>
-      <c r="G51" s="2">
-        <v>2</v>
-      </c>
-      <c r="H51" s="2">
-        <v>5</v>
-      </c>
-      <c r="I51" s="2">
-        <v>0</v>
-      </c>
-      <c r="J51" s="2">
-        <v>2</v>
-      </c>
-      <c r="K51" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L51" s="2"/>
-      <c r="M51" s="2"/>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2">
-        <v>0</v>
-      </c>
-      <c r="P51" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16">
-      <c r="A52" s="2">
-        <v>48</v>
-      </c>
-      <c r="B52" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C52" s="2">
-        <v>4</v>
-      </c>
-      <c r="D52" s="2">
-        <v>1</v>
-      </c>
-      <c r="E52" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F52" s="2">
-        <v>20</v>
-      </c>
-      <c r="G52" s="2">
-        <v>2</v>
-      </c>
-      <c r="H52" s="2">
-        <v>5</v>
-      </c>
-      <c r="I52" s="2">
-        <v>0</v>
-      </c>
-      <c r="J52" s="2">
-        <v>2</v>
-      </c>
-      <c r="K52" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2">
-        <v>0</v>
-      </c>
-      <c r="P52" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16">
-      <c r="A53" s="2">
-        <v>49</v>
-      </c>
-      <c r="B53" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C53" s="2">
-        <v>4</v>
-      </c>
-      <c r="D53" s="2">
-        <v>1</v>
-      </c>
-      <c r="E53" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F53" s="2">
-        <v>21</v>
-      </c>
-      <c r="G53" s="2">
-        <v>2</v>
-      </c>
-      <c r="H53" s="2">
-        <v>5</v>
-      </c>
-      <c r="I53" s="5">
-        <v>0</v>
-      </c>
-      <c r="J53" s="2">
-        <v>2</v>
-      </c>
-      <c r="K53" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2">
-        <v>0</v>
-      </c>
-      <c r="P53" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16">
-      <c r="A54" s="2">
-        <v>50</v>
-      </c>
-      <c r="B54" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C54" s="2">
-        <v>4</v>
-      </c>
-      <c r="D54" s="2">
-        <v>1</v>
-      </c>
-      <c r="E54" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F54" s="2">
-        <v>22</v>
-      </c>
-      <c r="G54" s="2">
-        <v>2</v>
-      </c>
-      <c r="H54" s="2">
-        <v>5</v>
-      </c>
-      <c r="I54" s="5">
-        <v>0</v>
-      </c>
-      <c r="J54" s="2">
-        <v>2</v>
-      </c>
-      <c r="K54" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2">
-        <v>0</v>
-      </c>
-      <c r="P54" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16">
-      <c r="A55" s="2">
-        <v>51</v>
-      </c>
-      <c r="B55" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C55" s="2">
-        <v>4</v>
-      </c>
-      <c r="D55" s="2">
-        <v>1</v>
-      </c>
-      <c r="E55" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F55" s="2">
-        <v>15</v>
-      </c>
-      <c r="G55" s="2">
-        <v>2</v>
-      </c>
-      <c r="H55" s="2">
-        <v>1</v>
-      </c>
-      <c r="I55" s="5">
-        <v>0</v>
-      </c>
-      <c r="J55" s="2">
-        <v>2</v>
-      </c>
-      <c r="K55" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="L55" s="2"/>
-      <c r="M55" s="2"/>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2">
-        <v>0</v>
-      </c>
-      <c r="P55" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16">
-      <c r="A56" s="2">
-        <v>67</v>
-      </c>
-      <c r="B56" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C56" s="2">
-        <v>1</v>
-      </c>
-      <c r="D56" s="2">
-        <v>1</v>
-      </c>
-      <c r="E56" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F56" s="2">
-        <v>17</v>
-      </c>
-      <c r="G56" s="2">
-        <v>4</v>
-      </c>
-      <c r="H56" s="2">
-        <v>3</v>
-      </c>
-      <c r="I56" s="5">
-        <v>0</v>
-      </c>
-      <c r="J56" s="2">
-        <v>2</v>
-      </c>
-      <c r="K56" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="L56" s="2"/>
-      <c r="M56" s="2"/>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2">
-        <v>0</v>
-      </c>
-      <c r="P56" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16">
-      <c r="A57" s="2">
-        <v>68</v>
-      </c>
-      <c r="B57" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C57" s="2">
-        <v>1</v>
-      </c>
-      <c r="D57" s="2">
-        <v>1</v>
-      </c>
-      <c r="E57" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F57" s="2">
-        <v>17</v>
-      </c>
-      <c r="G57" s="2">
-        <v>4</v>
-      </c>
-      <c r="H57" s="2">
-        <v>4</v>
-      </c>
-      <c r="I57" s="5">
-        <v>0</v>
-      </c>
-      <c r="J57" s="2">
-        <v>2</v>
-      </c>
-      <c r="K57" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="L57" s="2"/>
-      <c r="M57" s="2"/>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2">
-        <v>0</v>
-      </c>
-      <c r="P57" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16">
-      <c r="A58" s="2">
-        <v>69</v>
-      </c>
-      <c r="B58" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C58" s="2">
-        <v>1</v>
-      </c>
-      <c r="D58" s="2">
-        <v>1</v>
-      </c>
-      <c r="E58" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F58" s="2">
-        <v>17</v>
-      </c>
-      <c r="G58" s="2">
-        <v>4</v>
-      </c>
-      <c r="H58" s="2">
-        <v>5</v>
-      </c>
-      <c r="I58" s="5">
-        <v>0</v>
-      </c>
-      <c r="J58" s="2">
-        <v>2</v>
-      </c>
-      <c r="K58" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="L58" s="2"/>
-      <c r="M58" s="2"/>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2">
-        <v>0</v>
-      </c>
-      <c r="P58" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="I85" s="38"/>
+      <c r="J85" s="37"/>
+      <c r="K85" s="39">
+        <v>4014001</v>
+      </c>
+      <c r="L85" s="10"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:P58" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L85" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="C5:C58">
+  <conditionalFormatting sqref="B43">
+    <cfRule type="expression" dxfId="0" priority="18">
+      <formula>MOD($B43,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C43">
+    <cfRule type="expression" dxfId="0" priority="16">
+      <formula>MOD($B43,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A48">
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48">
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>MOD($B48,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C48">
     <cfRule type="expression" dxfId="0" priority="2">
+      <formula>MOD($B48,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E48:F48">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD($B48,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E73:F73">
+    <cfRule type="expression" dxfId="0" priority="44">
+      <formula>MOD($B73,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E74:F74">
+    <cfRule type="expression" dxfId="0" priority="9">
+      <formula>MOD($B74,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C85:L85">
+    <cfRule type="expression" dxfId="0" priority="45">
+      <formula>MOD($B85,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D65:D72">
+    <cfRule type="expression" dxfId="0" priority="7">
+      <formula>MOD($B65,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K39:K42">
+    <cfRule type="duplicateValues" dxfId="2" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A47 A49:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="319"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:L4">
+    <cfRule type="expression" dxfId="0" priority="318">
+      <formula>MOD($B1,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5:C42 C44:C47">
+    <cfRule type="expression" dxfId="0" priority="49">
       <formula>MOD($B5,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G56:G58">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>MOD($B56,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:P4">
-    <cfRule type="expression" dxfId="0" priority="271">
-      <formula>MOD($B1,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B41:B58 D43:E58">
-    <cfRule type="expression" dxfId="0" priority="5">
+  <conditionalFormatting sqref="D41:H42 J41:J42 L41:L42 G45:G47 D46:D47 B49:L64 E65:F72 B86:L1048576">
+    <cfRule type="expression" dxfId="0" priority="317">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D41:J42 L41:P42 H56:H58 D57:F58 B59:P1048576">
-    <cfRule type="expression" dxfId="0" priority="270">
+  <conditionalFormatting sqref="B41:B42 B44:B47">
+    <cfRule type="expression" dxfId="0" priority="52">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F45:J46 L45:P46">
-    <cfRule type="expression" dxfId="0" priority="8">
+  <conditionalFormatting sqref="D43:H43 J43:L43">
+    <cfRule type="expression" dxfId="0" priority="17">
+      <formula>MOD($B43,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D44:H44 J44:L47 H45:H47 D45:D47">
+    <cfRule type="expression" dxfId="0" priority="51">
+      <formula>MOD($B44,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E45:F47">
+    <cfRule type="expression" dxfId="0" priority="48">
       <formula>MOD($B45,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F49:J50 L49:P50">
-    <cfRule type="expression" dxfId="0" priority="6">
-      <formula>MOD($B49,2)=1</formula>
+  <conditionalFormatting sqref="G48 D48">
+    <cfRule type="expression" dxfId="0" priority="5">
+      <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F53:J55 L53:P58 I56:J58 F56:F58">
-    <cfRule type="expression" dxfId="0" priority="4">
-      <formula>MOD($B53,2)=1</formula>
+  <conditionalFormatting sqref="J48:L48 H48 D48">
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <conditionalFormatting sqref="B65:C72 G65:L72">
+    <cfRule type="expression" dxfId="0" priority="47">
+      <formula>MOD($B65,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B73:D73 G73:L73">
+    <cfRule type="expression" dxfId="0" priority="43">
+      <formula>MOD($B73,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B74:D74 G74:L74">
+    <cfRule type="expression" dxfId="0" priority="8">
+      <formula>MOD($B74,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B75:L84 B85">
+    <cfRule type="expression" dxfId="0" priority="46">
+      <formula>MOD($B75,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1">
       <formula1>"普通,免费,重转,全部"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1">
-      <formula1>"线注,线注乘倍率,总赌注"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$P$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,6 +34,7 @@
   <authors>
     <author/>
     <author>vidisJW</author>
+    <author>Administrator</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
@@ -83,7 +84,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -101,11 +102,13 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>该游戏的元素ID</t>
+          <t xml:space="preserve">该游戏的元素ID：图案1_图案2……
+分号后续的图案也要视为目标图案
+</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1">
+    <comment ref="E1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -123,10 +126,33 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-连线：赔付线
-指定：指定的奖励
-滚轴：滚轴的奖励
-全局分散：针对需要全局计算的元素</t>
+1：连线_X连：根据赔付线从左至右，出现相同图案，同时还要在baseline表中判断图案位置是否与中奖线一致，连续X列都符合表示为X连，一条线触发一次
+2：指定图案_条件图案ID：条件图案出现，不需要考虑位置，一个指定图案触发一次
+3：满线图案_X连：从左至右，出现相同图案，连续X列表示X连，一个图案计算触发一次
+4：全局分散图案_数量：针对需要全局计算的元素，只考虑数量，此模式相同图案仅触发数量最多的一次
+5：满线图案_数量：从左至右，前一列出现相同图案，只统计数量，相同图案仅触发数量最多的一次</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">Mr.M:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>奖项数量</t>
         </r>
       </text>
     </comment>
@@ -148,7 +174,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>奖项数量</t>
+          <t>中奖数量对应的倍数</t>
         </r>
       </text>
     </comment>
@@ -170,61 +196,12 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>中奖数量对应的倍数</t>
+          <t>该行元素的数量触发小游戏的ID，根据小游戏配置填写
+小游戏id;</t>
         </r>
       </text>
     </comment>
     <comment ref="J1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Mr.M:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>中奖后倍数的基数，线注或总赌注
-线注，线注*赔付倍数
-线注乘倍率，线注*赔付倍数*基本表里的倍率
-总赌注，总赌注*赔付倍数
-1: 单线押分
-2: 总押分</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Mr.M:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>该行元素的数量触发小游戏的ID，根据小游戏配置填写
-滚轴模式,小游戏id;</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -246,7 +223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -255,22 +232,12 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">Mr.M:
-线注倍数，奖励基数，奖励倍数
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>[{1,[{线注,100}]}]
-非同种元素，累加累乘需要服务器实现</t>
+          <t>大于0表示该中奖线触发对应jp奖池
+jackpot不进结果库，触发时根据奖池配置及时计算</t>
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0">
+    <comment ref="J5" authorId="2">
       <text>
         <r>
           <rPr>
@@ -279,8 +246,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">Mr.M:
-</t>
+          <t>Administrator:</t>
         </r>
         <r>
           <rPr>
@@ -288,13 +254,13 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>Mr.M:
-所在线ID，奖励基数，奖励倍数
-[{1,[{总押分,100}]}]</t>
+          <t xml:space="preserve">
+13是wild×2
+14是wild×5</t>
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0">
+    <comment ref="D49" authorId="2">
       <text>
         <r>
           <rPr>
@@ -303,7 +269,16 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>大于0表示该中奖线触发对应jp奖池</t>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+普通麻将:黄金麻将</t>
         </r>
       </text>
     </comment>
@@ -312,7 +287,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="44">
   <si>
     <t>id</t>
   </si>
@@ -323,37 +298,22 @@
     <t>旋转状态</t>
   </si>
   <si>
-    <t>旋转状态标识</t>
+    <t>元素ID_相同元素_相同元素</t>
   </si>
   <si>
-    <t>是否额外投注</t>
+    <t>中奖条件</t>
   </si>
   <si>
-    <t>元素ID</t>
-  </si>
-  <si>
-    <t>线类型</t>
-  </si>
-  <si>
-    <t>数量</t>
+    <t>条件参数</t>
   </si>
   <si>
     <t>倍率</t>
   </si>
   <si>
-    <t>中奖基数</t>
-  </si>
-  <si>
     <t>触发小游戏ID</t>
   </si>
   <si>
-    <t>元素倍率加成</t>
-  </si>
-  <si>
-    <t>单线押分倍数加成</t>
-  </si>
-  <si>
-    <t>线ID加成</t>
+    <t>额外出现元素导致倍率加成</t>
   </si>
   <si>
     <t>jackpotID</t>
@@ -365,10 +325,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>Map&lt;int{,}int&gt;{;}</t>
+    <t>List&lt;int&gt;{_}</t>
   </si>
   <si>
     <t>List&lt;List&lt;int&gt;{,}&gt;{;}</t>
@@ -378,12 +335,6 @@
   </si>
   <si>
     <t>rotateState</t>
-  </si>
-  <si>
-    <t>spinType</t>
-  </si>
-  <si>
-    <t>needExtraBet</t>
   </si>
   <si>
     <t>elementId</t>
@@ -398,19 +349,13 @@
     <t>bet</t>
   </si>
   <si>
-    <t>rewardType</t>
-  </si>
-  <si>
     <t>featureTriggerId</t>
   </si>
   <si>
     <t>betTimes</t>
   </si>
   <si>
-    <t>scoreBetTimes</t>
-  </si>
-  <si>
-    <t>lineIdReward</t>
+    <t>最大连线</t>
   </si>
   <si>
     <t>13,1,2;13,2,4;13,3,6;13,4,8;14,1,5;14,2,10;14,3,15;14,4,20</t>
@@ -419,49 +364,61 @@
     <t>-</t>
   </si>
   <si>
-    <t>1,10010001;2,10010001;3,10010001;4,10010001;5,10010001;6,10010001;7,10010001;</t>
+    <t>同时出现 目标和条件元素</t>
   </si>
   <si>
     <t>拉火车绿火车MINI</t>
   </si>
   <si>
-    <t>1,10010002;2,10010002;3,10010002;4,10010002;5,10010002;6,10010002;7,10010002;</t>
-  </si>
-  <si>
     <t>拉火车蓝火车MINOR</t>
-  </si>
-  <si>
-    <t>1,10010003;2,10010003;3,10010003;4,10010003;5,10010003;6,10010003;7,10010003;</t>
   </si>
   <si>
     <t>拉火车紫火车MAJOR</t>
   </si>
   <si>
-    <t>1,10010004;2,10010004;3,10010004;4,10010004;5,10010004;6,10010004;7,10010004;</t>
-  </si>
-  <si>
     <t>拉火车红火车GRAND</t>
   </si>
   <si>
-    <t>1,10010006;2,10010012;3,10010013;4,10010014;5,10010015;6,10010016;7,10010017;</t>
+    <t>保险箱奖励</t>
   </si>
   <si>
     <t>黄金列车普通转触发</t>
   </si>
   <si>
-    <t>1,10010007;2,10010018;3,10010019;4,10010020;5,10010021;6,10010022;7,10010023;</t>
-  </si>
-  <si>
-    <t>触发免费选择</t>
-  </si>
-  <si>
-    <t>1,10010011;2,10010030;3,10010031;4,10010032;5,10010033;6,10010034;7,10010035;</t>
+    <t>触发免费选择 【拉火车&amp;免费旋转8次】</t>
   </si>
   <si>
     <t>4个触发免费选择触发黄金列车</t>
   </si>
   <si>
     <t>5个触发免费选择触发黄金列车</t>
+  </si>
+  <si>
+    <t>指定触发隐藏免费游戏，仅用于结果库生成</t>
+  </si>
+  <si>
+    <t>1_11</t>
+  </si>
+  <si>
+    <t>2_12</t>
+  </si>
+  <si>
+    <t>3_13</t>
+  </si>
+  <si>
+    <t>4_14</t>
+  </si>
+  <si>
+    <t>5_15</t>
+  </si>
+  <si>
+    <t>6_16</t>
+  </si>
+  <si>
+    <t>7_17</t>
+  </si>
+  <si>
+    <t>8_18</t>
   </si>
 </sst>
 </file>
@@ -474,7 +431,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -508,6 +465,19 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -698,12 +668,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -713,8 +677,14 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -723,7 +693,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.35"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -914,7 +920,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -934,6 +940,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1053,73 +1074,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1128,108 +1131,216 @@
     <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="56">
@@ -1290,11 +1401,28 @@
     <cellStyle name="超链接 3" xfId="54"/>
     <cellStyle name="好_Sheet1" xfId="55"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="8" tint="0.799340800195319"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1325,7 +1453,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="0"/>
+          <a:off x="876300" y="0"/>
           <a:ext cx="9361170" cy="9781540"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1371,7 +1499,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1417,7 +1545,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9361170" cy="9524365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1463,7 +1591,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1509,7 +1637,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1555,7 +1683,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1601,7 +1729,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1647,7 +1775,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1693,7 +1821,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1739,7 +1867,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1785,7 +1913,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1831,7 +1959,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1877,7 +2005,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1923,7 +2051,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1969,7 +2097,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2015,7 +2143,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9361170" cy="9524365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2061,7 +2189,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2107,7 +2235,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2153,7 +2281,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2199,7 +2327,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2245,7 +2373,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
+          <a:off x="876300" y="1206500"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2291,7 +2419,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2337,7 +2465,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2383,7 +2511,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2429,7 +2557,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2475,7 +2603,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2521,7 +2649,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2567,7 +2695,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9524365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2613,7 +2741,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2659,7 +2787,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2705,7 +2833,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2751,7 +2879,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2797,7 +2925,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2843,7 +2971,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2889,7 +3017,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2935,7 +3063,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2981,7 +3109,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3027,7 +3155,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3073,7 +3201,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3119,7 +3247,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9524365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3165,7 +3293,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3211,7 +3339,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3257,7 +3385,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3303,7 +3431,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3349,7 +3477,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3395,7 +3523,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3441,7 +3569,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3487,7 +3615,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3533,7 +3661,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3579,7 +3707,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="10240010"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3625,7 +3753,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3671,7 +3799,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9972040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3717,7 +3845,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3763,7 +3891,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3809,7 +3937,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3855,7 +3983,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="10240010"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3901,7 +4029,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3947,7 +4075,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3993,7 +4121,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4039,7 +4167,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9781540"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4085,7 +4213,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9427845" cy="9611360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4131,7 +4259,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9524365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4177,7 +4305,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9371330" cy="9381490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4223,7 +4351,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9370695" cy="9508490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4269,7 +4397,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9370695" cy="9238615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4315,7 +4443,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8229600"/>
+          <a:off x="876300" y="9652000"/>
           <a:ext cx="9361170" cy="9789160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4609,2490 +4737,2887 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:P58"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <dimension ref="A1:L85"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="9" style="3"/>
+    <col min="1" max="1" width="11.5" style="7"/>
     <col min="2" max="2" width="11" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="8.5" style="4" customWidth="1"/>
-    <col min="7" max="7" width="9.625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9" style="5" customWidth="1"/>
-    <col min="10" max="10" width="16.125" style="6" customWidth="1"/>
-    <col min="11" max="11" width="14.875" style="6" customWidth="1"/>
-    <col min="12" max="12" width="47" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.625" style="4" customWidth="1"/>
-    <col min="14" max="14" width="24.75" style="4" customWidth="1"/>
-    <col min="15" max="16" width="9" style="4"/>
-    <col min="17" max="16384" width="9" style="3"/>
+    <col min="3" max="3" width="10" style="8" customWidth="1"/>
+    <col min="4" max="4" width="14.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.25" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="12.2166666666667" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.85833333333333" style="9" customWidth="1"/>
+    <col min="9" max="9" width="19.1333333333333" style="9" customWidth="1"/>
+    <col min="10" max="10" width="29.75" style="2" customWidth="1"/>
+    <col min="11" max="11" width="10.375" style="2"/>
+    <col min="12" max="12" width="14.5583333333333" style="10" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="37.5" customHeight="1" spans="1:16">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="E1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="K1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+    </row>
+    <row r="2" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" s="2" customFormat="1" spans="1:15">
-      <c r="A2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="K2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" hidden="1" spans="1:15">
+        <v>11</v>
+      </c>
+      <c r="L2" s="10"/>
+    </row>
+    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="K3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" hidden="1"/>
-    <row r="5" s="2" customFormat="1" spans="1:16">
+        <v>9</v>
+      </c>
+      <c r="L3" s="10"/>
+    </row>
+    <row r="4" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C4" s="8"/>
+      <c r="L4" s="10"/>
+    </row>
+    <row r="5" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A5" s="2">
-        <v>1</v>
+        <f>(B5)*10000+D5+G5*100+E5*100000</f>
+        <v>1001100211</v>
       </c>
       <c r="B5" s="2">
         <v>100100</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="8">
         <v>4</v>
       </c>
       <c r="D5" s="2">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>11</v>
+      <c r="F5" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="G5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="2">
         <v>2</v>
       </c>
-      <c r="I5" s="2">
-        <v>2</v>
-      </c>
-      <c r="J5" s="2">
-        <v>1</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O5" s="2">
+      <c r="J5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="2">
         <v>0</v>
       </c>
-      <c r="P5" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:16">
+      <c r="L5" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A6" s="2">
-        <v>2</v>
+        <f t="shared" ref="A6:A42" si="0">(B6)*10000+D6+G6*100+E6*100000</f>
+        <v>1001100301</v>
       </c>
       <c r="B6" s="2">
         <v>100100</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="8">
         <v>4</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="E6" s="2" t="b">
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="2">
+        <v>3</v>
+      </c>
+      <c r="H6" s="2">
+        <v>5</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="2">
         <v>0</v>
       </c>
-      <c r="F6" s="2">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2">
-        <v>3</v>
-      </c>
-      <c r="I6" s="2">
-        <v>5</v>
-      </c>
-      <c r="J6" s="2">
-        <v>1</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O6" s="2">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:16">
+      <c r="L6" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A7" s="2">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>1001100302</v>
       </c>
       <c r="B7" s="2">
         <v>100100</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="8">
         <v>4</v>
       </c>
       <c r="D7" s="2">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" s="2" t="b">
+      <c r="F7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="2">
+        <v>3</v>
+      </c>
+      <c r="H7" s="2">
+        <v>5</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="2">
         <v>0</v>
       </c>
-      <c r="F7" s="2">
-        <v>2</v>
-      </c>
-      <c r="G7" s="2">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2">
-        <v>5</v>
-      </c>
-      <c r="J7" s="2">
-        <v>1</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O7" s="2">
-        <v>0</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:16">
+      <c r="L7" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A8" s="2">
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>1001100303</v>
       </c>
       <c r="B8" s="2">
         <v>100100</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="8">
         <v>4</v>
       </c>
       <c r="D8" s="2">
+        <v>3</v>
+      </c>
+      <c r="E8" s="2">
         <v>1</v>
       </c>
-      <c r="E8" s="2" t="b">
+      <c r="F8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="2">
+        <v>3</v>
+      </c>
+      <c r="H8" s="2">
+        <v>5</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="2">
         <v>0</v>
       </c>
-      <c r="F8" s="2">
-        <v>3</v>
-      </c>
-      <c r="G8" s="2">
-        <v>1</v>
-      </c>
-      <c r="H8" s="2">
-        <v>3</v>
-      </c>
-      <c r="I8" s="2">
-        <v>5</v>
-      </c>
-      <c r="J8" s="2">
-        <v>1</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O8" s="2">
-        <v>0</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" spans="1:16">
+      <c r="L8" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A9" s="2">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>1001100304</v>
       </c>
       <c r="B9" s="2">
         <v>100100</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="8">
         <v>4</v>
       </c>
       <c r="D9" s="2">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2">
         <v>1</v>
       </c>
-      <c r="E9" s="2" t="b">
+      <c r="F9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="2">
+        <v>3</v>
+      </c>
+      <c r="H9" s="2">
+        <v>5</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="2">
         <v>0</v>
       </c>
-      <c r="F9" s="2">
-        <v>4</v>
-      </c>
-      <c r="G9" s="2">
-        <v>1</v>
-      </c>
-      <c r="H9" s="2">
-        <v>3</v>
-      </c>
-      <c r="I9" s="2">
-        <v>5</v>
-      </c>
-      <c r="J9" s="2">
-        <v>1</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O9" s="2">
-        <v>0</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" spans="1:16">
+      <c r="L9" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A10" s="2">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>1001100305</v>
       </c>
       <c r="B10" s="2">
         <v>100100</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="8">
         <v>4</v>
       </c>
       <c r="D10" s="2">
+        <v>5</v>
+      </c>
+      <c r="E10" s="2">
         <v>1</v>
       </c>
-      <c r="E10" s="2" t="b">
+      <c r="F10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="2">
+        <v>3</v>
+      </c>
+      <c r="H10" s="2">
+        <v>5</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="2">
         <v>0</v>
       </c>
-      <c r="F10" s="2">
-        <v>5</v>
-      </c>
-      <c r="G10" s="2">
-        <v>1</v>
-      </c>
-      <c r="H10" s="2">
-        <v>3</v>
-      </c>
-      <c r="I10" s="2">
-        <v>5</v>
-      </c>
-      <c r="J10" s="2">
-        <v>1</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O10" s="2">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="1:16">
+      <c r="L10" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A11" s="2">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>1001100306</v>
       </c>
       <c r="B11" s="2">
         <v>100100</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="8">
         <v>4</v>
       </c>
       <c r="D11" s="2">
+        <v>6</v>
+      </c>
+      <c r="E11" s="2">
         <v>1</v>
       </c>
-      <c r="E11" s="2" t="b">
+      <c r="F11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="2">
+        <v>3</v>
+      </c>
+      <c r="H11" s="2">
+        <v>5</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" s="2">
         <v>0</v>
       </c>
-      <c r="F11" s="2">
-        <v>6</v>
-      </c>
-      <c r="G11" s="2">
-        <v>1</v>
-      </c>
-      <c r="H11" s="2">
-        <v>3</v>
-      </c>
-      <c r="I11" s="2">
-        <v>5</v>
-      </c>
-      <c r="J11" s="2">
-        <v>1</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O11" s="2">
-        <v>0</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="1:16">
+      <c r="L11" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A12" s="2">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>1001100307</v>
       </c>
       <c r="B12" s="2">
         <v>100100</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="8">
         <v>4</v>
       </c>
       <c r="D12" s="2">
+        <v>7</v>
+      </c>
+      <c r="E12" s="2">
         <v>1</v>
       </c>
-      <c r="E12" s="2" t="b">
+      <c r="F12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="2">
+        <v>3</v>
+      </c>
+      <c r="H12" s="2">
+        <v>10</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K12" s="2">
         <v>0</v>
       </c>
-      <c r="F12" s="2">
-        <v>7</v>
-      </c>
-      <c r="G12" s="2">
-        <v>1</v>
-      </c>
-      <c r="H12" s="2">
-        <v>3</v>
-      </c>
-      <c r="I12" s="2">
-        <v>10</v>
-      </c>
-      <c r="J12" s="2">
-        <v>1</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O12" s="2">
-        <v>0</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" spans="1:16">
+      <c r="L12" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A13" s="2">
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>1001100308</v>
       </c>
       <c r="B13" s="2">
         <v>100100</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="8">
         <v>4</v>
       </c>
       <c r="D13" s="2">
+        <v>8</v>
+      </c>
+      <c r="E13" s="2">
         <v>1</v>
       </c>
-      <c r="E13" s="2" t="b">
+      <c r="F13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="2">
+        <v>3</v>
+      </c>
+      <c r="H13" s="2">
+        <v>10</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13" s="2">
         <v>0</v>
       </c>
-      <c r="F13" s="2">
-        <v>8</v>
-      </c>
-      <c r="G13" s="2">
-        <v>1</v>
-      </c>
-      <c r="H13" s="2">
-        <v>3</v>
-      </c>
-      <c r="I13" s="2">
-        <v>10</v>
-      </c>
-      <c r="J13" s="2">
-        <v>1</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O13" s="2">
-        <v>0</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="1:16">
+      <c r="L13" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A14" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>1001100309</v>
       </c>
       <c r="B14" s="2">
         <v>100100</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="8">
         <v>4</v>
       </c>
       <c r="D14" s="2">
+        <v>9</v>
+      </c>
+      <c r="E14" s="2">
         <v>1</v>
       </c>
-      <c r="E14" s="2" t="b">
+      <c r="F14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="2">
+        <v>3</v>
+      </c>
+      <c r="H14" s="2">
+        <v>15</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14" s="2">
         <v>0</v>
       </c>
-      <c r="F14" s="2">
-        <v>9</v>
-      </c>
-      <c r="G14" s="2">
-        <v>1</v>
-      </c>
-      <c r="H14" s="2">
-        <v>3</v>
-      </c>
-      <c r="I14" s="2">
-        <v>15</v>
-      </c>
-      <c r="J14" s="2">
-        <v>1</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O14" s="2">
-        <v>0</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:16">
+      <c r="L14" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A15" s="2">
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>1001100310</v>
       </c>
       <c r="B15" s="2">
         <v>100100</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="8">
         <v>4</v>
       </c>
       <c r="D15" s="2">
+        <v>10</v>
+      </c>
+      <c r="E15" s="2">
         <v>1</v>
       </c>
-      <c r="E15" s="2" t="b">
+      <c r="F15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="2">
+        <v>3</v>
+      </c>
+      <c r="H15" s="2">
+        <v>15</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K15" s="2">
         <v>0</v>
       </c>
-      <c r="F15" s="2">
-        <v>10</v>
-      </c>
-      <c r="G15" s="2">
-        <v>1</v>
-      </c>
-      <c r="H15" s="2">
-        <v>3</v>
-      </c>
-      <c r="I15" s="2">
-        <v>15</v>
-      </c>
-      <c r="J15" s="2">
-        <v>1</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O15" s="2">
-        <v>0</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:16">
+      <c r="L15" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A16" s="2">
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>1001100311</v>
       </c>
       <c r="B16" s="2">
         <v>100100</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="8">
         <v>4</v>
       </c>
       <c r="D16" s="2">
+        <v>11</v>
+      </c>
+      <c r="E16" s="2">
         <v>1</v>
       </c>
-      <c r="E16" s="2" t="b">
+      <c r="F16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="2">
+        <v>3</v>
+      </c>
+      <c r="H16" s="2">
+        <v>20</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K16" s="2">
         <v>0</v>
       </c>
-      <c r="F16" s="2">
-        <v>11</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1</v>
-      </c>
-      <c r="H16" s="2">
-        <v>3</v>
-      </c>
-      <c r="I16" s="2">
-        <v>20</v>
-      </c>
-      <c r="J16" s="2">
-        <v>1</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O16" s="2">
-        <v>0</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="1:16">
+      <c r="L16" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A17" s="2">
-        <v>13</v>
+        <f t="shared" si="0"/>
+        <v>1001100401</v>
       </c>
       <c r="B17" s="2">
         <v>100100</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="8">
         <v>4</v>
       </c>
       <c r="D17" s="2">
         <v>1</v>
       </c>
-      <c r="E17" s="2" t="b">
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="2">
+        <v>4</v>
+      </c>
+      <c r="H17" s="2">
+        <v>15</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" s="2">
         <v>0</v>
       </c>
-      <c r="F17" s="2">
-        <v>1</v>
-      </c>
-      <c r="G17" s="2">
-        <v>1</v>
-      </c>
-      <c r="H17" s="2">
-        <v>4</v>
-      </c>
-      <c r="I17" s="2">
-        <v>15</v>
-      </c>
-      <c r="J17" s="2">
-        <v>1</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O17" s="2">
-        <v>0</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="1:16">
+      <c r="L17" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A18" s="2">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>1001100402</v>
       </c>
       <c r="B18" s="2">
         <v>100100</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="8">
         <v>4</v>
       </c>
       <c r="D18" s="2">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2">
         <v>1</v>
       </c>
-      <c r="E18" s="2" t="b">
+      <c r="F18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="2">
+        <v>4</v>
+      </c>
+      <c r="H18" s="2">
+        <v>15</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K18" s="2">
         <v>0</v>
       </c>
-      <c r="F18" s="2">
-        <v>2</v>
-      </c>
-      <c r="G18" s="2">
-        <v>1</v>
-      </c>
-      <c r="H18" s="2">
-        <v>4</v>
-      </c>
-      <c r="I18" s="2">
-        <v>15</v>
-      </c>
-      <c r="J18" s="2">
-        <v>1</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O18" s="2">
-        <v>0</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="1:16">
+      <c r="L18" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A19" s="2">
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>1001100403</v>
       </c>
       <c r="B19" s="2">
         <v>100100</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="8">
         <v>4</v>
       </c>
       <c r="D19" s="2">
+        <v>3</v>
+      </c>
+      <c r="E19" s="2">
         <v>1</v>
       </c>
-      <c r="E19" s="2" t="b">
+      <c r="F19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="2">
+        <v>4</v>
+      </c>
+      <c r="H19" s="2">
+        <v>15</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K19" s="2">
         <v>0</v>
       </c>
-      <c r="F19" s="2">
-        <v>3</v>
-      </c>
-      <c r="G19" s="2">
-        <v>1</v>
-      </c>
-      <c r="H19" s="2">
-        <v>4</v>
-      </c>
-      <c r="I19" s="2">
-        <v>15</v>
-      </c>
-      <c r="J19" s="2">
-        <v>1</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O19" s="2">
-        <v>0</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="1:16">
+      <c r="L19" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A20" s="2">
-        <v>16</v>
+        <f t="shared" si="0"/>
+        <v>1001100404</v>
       </c>
       <c r="B20" s="2">
         <v>100100</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="8">
         <v>4</v>
       </c>
       <c r="D20" s="2">
+        <v>4</v>
+      </c>
+      <c r="E20" s="2">
         <v>1</v>
       </c>
-      <c r="E20" s="2" t="b">
+      <c r="F20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="2">
+        <v>4</v>
+      </c>
+      <c r="H20" s="2">
+        <v>15</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K20" s="2">
         <v>0</v>
       </c>
-      <c r="F20" s="2">
-        <v>4</v>
-      </c>
-      <c r="G20" s="2">
-        <v>1</v>
-      </c>
-      <c r="H20" s="2">
-        <v>4</v>
-      </c>
-      <c r="I20" s="2">
-        <v>15</v>
-      </c>
-      <c r="J20" s="2">
-        <v>1</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O20" s="2">
-        <v>0</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="1:16">
+      <c r="L20" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A21" s="2">
-        <v>17</v>
+        <f t="shared" si="0"/>
+        <v>1001100405</v>
       </c>
       <c r="B21" s="2">
         <v>100100</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="8">
         <v>4</v>
       </c>
       <c r="D21" s="2">
+        <v>5</v>
+      </c>
+      <c r="E21" s="2">
         <v>1</v>
       </c>
-      <c r="E21" s="2" t="b">
+      <c r="F21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="2">
+        <v>4</v>
+      </c>
+      <c r="H21" s="2">
+        <v>15</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K21" s="2">
         <v>0</v>
       </c>
-      <c r="F21" s="2">
-        <v>5</v>
-      </c>
-      <c r="G21" s="2">
-        <v>1</v>
-      </c>
-      <c r="H21" s="2">
-        <v>4</v>
-      </c>
-      <c r="I21" s="2">
-        <v>15</v>
-      </c>
-      <c r="J21" s="2">
-        <v>1</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O21" s="2">
-        <v>0</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" spans="1:16">
+      <c r="L21" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A22" s="2">
-        <v>18</v>
+        <f t="shared" si="0"/>
+        <v>1001100406</v>
       </c>
       <c r="B22" s="2">
         <v>100100</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="8">
         <v>4</v>
       </c>
       <c r="D22" s="2">
+        <v>6</v>
+      </c>
+      <c r="E22" s="2">
         <v>1</v>
       </c>
-      <c r="E22" s="2" t="b">
+      <c r="F22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="2">
+        <v>4</v>
+      </c>
+      <c r="H22" s="2">
+        <v>15</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" s="2">
         <v>0</v>
       </c>
-      <c r="F22" s="2">
-        <v>6</v>
-      </c>
-      <c r="G22" s="2">
-        <v>1</v>
-      </c>
-      <c r="H22" s="2">
-        <v>4</v>
-      </c>
-      <c r="I22" s="2">
-        <v>15</v>
-      </c>
-      <c r="J22" s="2">
-        <v>1</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O22" s="2">
-        <v>0</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" spans="1:16">
+      <c r="L22" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A23" s="2">
-        <v>19</v>
+        <f t="shared" si="0"/>
+        <v>1001100407</v>
       </c>
       <c r="B23" s="2">
         <v>100100</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="8">
         <v>4</v>
       </c>
       <c r="D23" s="2">
+        <v>7</v>
+      </c>
+      <c r="E23" s="2">
         <v>1</v>
       </c>
-      <c r="E23" s="2" t="b">
+      <c r="F23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="2">
+        <v>4</v>
+      </c>
+      <c r="H23" s="2">
+        <v>25</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K23" s="2">
         <v>0</v>
       </c>
-      <c r="F23" s="2">
-        <v>7</v>
-      </c>
-      <c r="G23" s="2">
-        <v>1</v>
-      </c>
-      <c r="H23" s="2">
-        <v>4</v>
-      </c>
-      <c r="I23" s="2">
-        <v>25</v>
-      </c>
-      <c r="J23" s="2">
-        <v>1</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O23" s="2">
-        <v>0</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" spans="1:16">
+      <c r="L23" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A24" s="2">
-        <v>20</v>
+        <f t="shared" si="0"/>
+        <v>1001100408</v>
       </c>
       <c r="B24" s="2">
         <v>100100</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="8">
         <v>4</v>
       </c>
       <c r="D24" s="2">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2">
         <v>1</v>
       </c>
-      <c r="E24" s="2" t="b">
+      <c r="F24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="2">
+        <v>4</v>
+      </c>
+      <c r="H24" s="2">
+        <v>25</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K24" s="2">
         <v>0</v>
       </c>
-      <c r="F24" s="2">
-        <v>8</v>
-      </c>
-      <c r="G24" s="2">
-        <v>1</v>
-      </c>
-      <c r="H24" s="2">
-        <v>4</v>
-      </c>
-      <c r="I24" s="2">
-        <v>25</v>
-      </c>
-      <c r="J24" s="2">
-        <v>1</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O24" s="2">
-        <v>0</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" spans="1:16">
+      <c r="L24" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A25" s="2">
-        <v>21</v>
+        <f t="shared" si="0"/>
+        <v>1001100409</v>
       </c>
       <c r="B25" s="2">
         <v>100100</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="8">
         <v>4</v>
       </c>
       <c r="D25" s="2">
+        <v>9</v>
+      </c>
+      <c r="E25" s="2">
         <v>1</v>
       </c>
-      <c r="E25" s="2" t="b">
+      <c r="F25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="2">
+        <v>4</v>
+      </c>
+      <c r="H25" s="2">
+        <v>30</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K25" s="2">
         <v>0</v>
       </c>
-      <c r="F25" s="2">
-        <v>9</v>
-      </c>
-      <c r="G25" s="2">
-        <v>1</v>
-      </c>
-      <c r="H25" s="2">
-        <v>4</v>
-      </c>
-      <c r="I25" s="2">
-        <v>30</v>
-      </c>
-      <c r="J25" s="2">
-        <v>1</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O25" s="2">
-        <v>0</v>
-      </c>
-      <c r="P25" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" spans="1:16">
+      <c r="L25" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A26" s="2">
-        <v>22</v>
+        <f t="shared" si="0"/>
+        <v>1001100410</v>
       </c>
       <c r="B26" s="2">
         <v>100100</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="8">
         <v>4</v>
       </c>
       <c r="D26" s="2">
+        <v>10</v>
+      </c>
+      <c r="E26" s="2">
         <v>1</v>
       </c>
-      <c r="E26" s="2" t="b">
+      <c r="F26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="2">
+        <v>4</v>
+      </c>
+      <c r="H26" s="2">
+        <v>30</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K26" s="2">
         <v>0</v>
       </c>
-      <c r="F26" s="2">
-        <v>10</v>
-      </c>
-      <c r="G26" s="2">
-        <v>1</v>
-      </c>
-      <c r="H26" s="2">
-        <v>4</v>
-      </c>
-      <c r="I26" s="2">
-        <v>30</v>
-      </c>
-      <c r="J26" s="2">
-        <v>1</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O26" s="2">
-        <v>0</v>
-      </c>
-      <c r="P26" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:16">
+      <c r="L26" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A27" s="2">
-        <v>23</v>
+        <f t="shared" si="0"/>
+        <v>1001100411</v>
       </c>
       <c r="B27" s="2">
         <v>100100</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="8">
         <v>4</v>
       </c>
       <c r="D27" s="2">
+        <v>11</v>
+      </c>
+      <c r="E27" s="2">
         <v>1</v>
       </c>
-      <c r="E27" s="2" t="b">
+      <c r="F27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="2">
+        <v>4</v>
+      </c>
+      <c r="H27" s="2">
+        <v>50</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K27" s="2">
         <v>0</v>
       </c>
-      <c r="F27" s="2">
-        <v>11</v>
-      </c>
-      <c r="G27" s="2">
-        <v>1</v>
-      </c>
-      <c r="H27" s="2">
-        <v>4</v>
-      </c>
-      <c r="I27" s="2">
-        <v>50</v>
-      </c>
-      <c r="J27" s="2">
-        <v>1</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O27" s="2">
-        <v>0</v>
-      </c>
-      <c r="P27" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" spans="1:16">
+      <c r="L27" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A28" s="2">
-        <v>24</v>
+        <f t="shared" si="0"/>
+        <v>1001100501</v>
       </c>
       <c r="B28" s="2">
         <v>100100</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="8">
         <v>4</v>
       </c>
       <c r="D28" s="2">
         <v>1</v>
       </c>
-      <c r="E28" s="2" t="b">
+      <c r="E28" s="2">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="2">
+        <v>5</v>
+      </c>
+      <c r="H28" s="2">
+        <v>50</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K28" s="2">
         <v>0</v>
       </c>
-      <c r="F28" s="2">
-        <v>1</v>
-      </c>
-      <c r="G28" s="2">
-        <v>1</v>
-      </c>
-      <c r="H28" s="2">
-        <v>5</v>
-      </c>
-      <c r="I28" s="2">
-        <v>50</v>
-      </c>
-      <c r="J28" s="2">
-        <v>1</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O28" s="2">
-        <v>0</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="1:16">
+      <c r="L28" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A29" s="2">
-        <v>25</v>
+        <f t="shared" si="0"/>
+        <v>1001100502</v>
       </c>
       <c r="B29" s="2">
         <v>100100</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="8">
         <v>4</v>
       </c>
       <c r="D29" s="2">
+        <v>2</v>
+      </c>
+      <c r="E29" s="2">
         <v>1</v>
       </c>
-      <c r="E29" s="2" t="b">
+      <c r="F29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="2">
+        <v>5</v>
+      </c>
+      <c r="H29" s="2">
+        <v>50</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K29" s="2">
         <v>0</v>
       </c>
-      <c r="F29" s="2">
-        <v>2</v>
-      </c>
-      <c r="G29" s="2">
-        <v>1</v>
-      </c>
-      <c r="H29" s="2">
-        <v>5</v>
-      </c>
-      <c r="I29" s="2">
-        <v>50</v>
-      </c>
-      <c r="J29" s="2">
-        <v>1</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O29" s="2">
-        <v>0</v>
-      </c>
-      <c r="P29" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="1:16">
+      <c r="L29" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A30" s="2">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>1001100503</v>
       </c>
       <c r="B30" s="2">
         <v>100100</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="8">
         <v>4</v>
       </c>
       <c r="D30" s="2">
+        <v>3</v>
+      </c>
+      <c r="E30" s="2">
         <v>1</v>
       </c>
-      <c r="E30" s="2" t="b">
+      <c r="F30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30" s="2">
+        <v>5</v>
+      </c>
+      <c r="H30" s="2">
+        <v>50</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K30" s="2">
         <v>0</v>
       </c>
-      <c r="F30" s="2">
-        <v>3</v>
-      </c>
-      <c r="G30" s="2">
-        <v>1</v>
-      </c>
-      <c r="H30" s="2">
-        <v>5</v>
-      </c>
-      <c r="I30" s="2">
-        <v>50</v>
-      </c>
-      <c r="J30" s="2">
-        <v>1</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O30" s="2">
-        <v>0</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" spans="1:16">
+      <c r="L30" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A31" s="2">
-        <v>27</v>
+        <f t="shared" si="0"/>
+        <v>1001100504</v>
       </c>
       <c r="B31" s="2">
         <v>100100</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="8">
         <v>4</v>
       </c>
       <c r="D31" s="2">
+        <v>4</v>
+      </c>
+      <c r="E31" s="2">
         <v>1</v>
       </c>
-      <c r="E31" s="2" t="b">
+      <c r="F31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G31" s="2">
+        <v>5</v>
+      </c>
+      <c r="H31" s="2">
+        <v>50</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K31" s="2">
         <v>0</v>
       </c>
-      <c r="F31" s="2">
-        <v>4</v>
-      </c>
-      <c r="G31" s="2">
-        <v>1</v>
-      </c>
-      <c r="H31" s="2">
-        <v>5</v>
-      </c>
-      <c r="I31" s="2">
-        <v>50</v>
-      </c>
-      <c r="J31" s="2">
-        <v>1</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O31" s="2">
-        <v>0</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="1:16">
+      <c r="L31" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A32" s="2">
-        <v>28</v>
+        <f t="shared" si="0"/>
+        <v>1001100505</v>
       </c>
       <c r="B32" s="2">
         <v>100100</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="8">
         <v>4</v>
       </c>
       <c r="D32" s="2">
+        <v>5</v>
+      </c>
+      <c r="E32" s="2">
         <v>1</v>
       </c>
-      <c r="E32" s="2" t="b">
+      <c r="F32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G32" s="2">
+        <v>5</v>
+      </c>
+      <c r="H32" s="2">
+        <v>50</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K32" s="2">
         <v>0</v>
       </c>
-      <c r="F32" s="2">
-        <v>5</v>
-      </c>
-      <c r="G32" s="2">
-        <v>1</v>
-      </c>
-      <c r="H32" s="2">
-        <v>5</v>
-      </c>
-      <c r="I32" s="2">
-        <v>50</v>
-      </c>
-      <c r="J32" s="2">
-        <v>1</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O32" s="2">
-        <v>0</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" spans="1:16">
+      <c r="L32" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A33" s="2">
-        <v>29</v>
+        <f t="shared" si="0"/>
+        <v>1001100506</v>
       </c>
       <c r="B33" s="2">
         <v>100100</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="8">
         <v>4</v>
       </c>
       <c r="D33" s="2">
+        <v>6</v>
+      </c>
+      <c r="E33" s="2">
         <v>1</v>
       </c>
-      <c r="E33" s="2" t="b">
+      <c r="F33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33" s="2">
+        <v>5</v>
+      </c>
+      <c r="H33" s="2">
+        <v>50</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K33" s="2">
         <v>0</v>
       </c>
-      <c r="F33" s="2">
-        <v>6</v>
-      </c>
-      <c r="G33" s="2">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2">
-        <v>5</v>
-      </c>
-      <c r="I33" s="2">
-        <v>50</v>
-      </c>
-      <c r="J33" s="2">
-        <v>1</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O33" s="2">
-        <v>0</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" spans="1:16">
+      <c r="L33" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A34" s="2">
-        <v>30</v>
+        <f t="shared" si="0"/>
+        <v>1001100507</v>
       </c>
       <c r="B34" s="2">
         <v>100100</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="8">
         <v>4</v>
       </c>
       <c r="D34" s="2">
+        <v>7</v>
+      </c>
+      <c r="E34" s="2">
         <v>1</v>
       </c>
-      <c r="E34" s="2" t="b">
+      <c r="F34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="2">
+        <v>5</v>
+      </c>
+      <c r="H34" s="2">
+        <v>100</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K34" s="2">
         <v>0</v>
       </c>
-      <c r="F34" s="2">
-        <v>7</v>
-      </c>
-      <c r="G34" s="2">
-        <v>1</v>
-      </c>
-      <c r="H34" s="2">
-        <v>5</v>
-      </c>
-      <c r="I34" s="2">
-        <v>100</v>
-      </c>
-      <c r="J34" s="2">
-        <v>1</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O34" s="2">
-        <v>0</v>
-      </c>
-      <c r="P34" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" spans="1:16">
+      <c r="L34" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A35" s="2">
-        <v>31</v>
+        <f t="shared" si="0"/>
+        <v>1001100508</v>
       </c>
       <c r="B35" s="2">
         <v>100100</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="8">
         <v>4</v>
       </c>
       <c r="D35" s="2">
+        <v>8</v>
+      </c>
+      <c r="E35" s="2">
         <v>1</v>
       </c>
-      <c r="E35" s="2" t="b">
+      <c r="F35" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" s="2">
+        <v>5</v>
+      </c>
+      <c r="H35" s="2">
+        <v>100</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" s="2">
         <v>0</v>
       </c>
-      <c r="F35" s="2">
-        <v>8</v>
-      </c>
-      <c r="G35" s="2">
-        <v>1</v>
-      </c>
-      <c r="H35" s="2">
-        <v>5</v>
-      </c>
-      <c r="I35" s="2">
-        <v>100</v>
-      </c>
-      <c r="J35" s="2">
-        <v>1</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O35" s="2">
-        <v>0</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" spans="1:16">
+      <c r="L35" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A36" s="2">
-        <v>32</v>
+        <f t="shared" si="0"/>
+        <v>1001100509</v>
       </c>
       <c r="B36" s="2">
         <v>100100</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="8">
         <v>4</v>
       </c>
       <c r="D36" s="2">
+        <v>9</v>
+      </c>
+      <c r="E36" s="2">
         <v>1</v>
       </c>
-      <c r="E36" s="2" t="b">
+      <c r="F36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="2">
+        <v>5</v>
+      </c>
+      <c r="H36" s="2">
+        <v>200</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="2">
         <v>0</v>
       </c>
-      <c r="F36" s="2">
-        <v>9</v>
-      </c>
-      <c r="G36" s="2">
-        <v>1</v>
-      </c>
-      <c r="H36" s="2">
-        <v>5</v>
-      </c>
-      <c r="I36" s="2">
-        <v>200</v>
-      </c>
-      <c r="J36" s="2">
-        <v>1</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O36" s="2">
-        <v>0</v>
-      </c>
-      <c r="P36" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" spans="1:16">
+      <c r="L36" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A37" s="2">
-        <v>33</v>
+        <f t="shared" si="0"/>
+        <v>1001100510</v>
       </c>
       <c r="B37" s="2">
         <v>100100</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="8">
         <v>4</v>
       </c>
       <c r="D37" s="2">
+        <v>10</v>
+      </c>
+      <c r="E37" s="2">
         <v>1</v>
       </c>
-      <c r="E37" s="2" t="b">
+      <c r="F37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G37" s="2">
+        <v>5</v>
+      </c>
+      <c r="H37" s="2">
+        <v>200</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K37" s="2">
         <v>0</v>
       </c>
-      <c r="F37" s="2">
-        <v>10</v>
-      </c>
-      <c r="G37" s="2">
-        <v>1</v>
-      </c>
-      <c r="H37" s="2">
-        <v>5</v>
-      </c>
-      <c r="I37" s="2">
-        <v>200</v>
-      </c>
-      <c r="J37" s="2">
-        <v>1</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O37" s="2">
-        <v>0</v>
-      </c>
-      <c r="P37" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38" s="2" customFormat="1" spans="1:16">
+      <c r="L37" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A38" s="2">
-        <v>34</v>
+        <f t="shared" si="0"/>
+        <v>1001100511</v>
       </c>
       <c r="B38" s="2">
         <v>100100</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="8">
         <v>4</v>
       </c>
       <c r="D38" s="2">
+        <v>11</v>
+      </c>
+      <c r="E38" s="2">
         <v>1</v>
       </c>
-      <c r="E38" s="2" t="b">
+      <c r="F38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38" s="2">
+        <v>5</v>
+      </c>
+      <c r="H38" s="2">
+        <v>300</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K38" s="2">
         <v>0</v>
       </c>
-      <c r="F38" s="2">
+      <c r="L38" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A39" s="2">
+        <f t="shared" si="0"/>
+        <v>1001201619</v>
+      </c>
+      <c r="B39" s="14">
+        <v>100100</v>
+      </c>
+      <c r="C39" s="8">
+        <v>4</v>
+      </c>
+      <c r="D39" s="14">
+        <v>19</v>
+      </c>
+      <c r="E39" s="14">
+        <v>2</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G39" s="14">
+        <v>16</v>
+      </c>
+      <c r="H39" s="14">
+        <v>0</v>
+      </c>
+      <c r="I39" s="26">
+        <v>30010001</v>
+      </c>
+      <c r="J39" s="14"/>
+      <c r="K39" s="27">
+        <v>4001001</v>
+      </c>
+      <c r="L39" s="28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A40" s="2">
+        <f t="shared" si="0"/>
+        <v>1001201620</v>
+      </c>
+      <c r="B40" s="14">
+        <v>100100</v>
+      </c>
+      <c r="C40" s="8">
+        <v>4</v>
+      </c>
+      <c r="D40" s="14">
+        <v>20</v>
+      </c>
+      <c r="E40" s="14">
+        <v>2</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G40" s="14">
+        <v>16</v>
+      </c>
+      <c r="H40" s="14">
+        <v>0</v>
+      </c>
+      <c r="I40" s="26">
+        <v>30010002</v>
+      </c>
+      <c r="J40" s="14"/>
+      <c r="K40" s="27">
+        <v>4001002</v>
+      </c>
+      <c r="L40" s="28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A41" s="2">
+        <f t="shared" si="0"/>
+        <v>1001201621</v>
+      </c>
+      <c r="B41" s="14">
+        <v>100100</v>
+      </c>
+      <c r="C41" s="8">
+        <v>4</v>
+      </c>
+      <c r="D41" s="14">
+        <v>21</v>
+      </c>
+      <c r="E41" s="14">
+        <v>2</v>
+      </c>
+      <c r="F41" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G41" s="14">
+        <v>16</v>
+      </c>
+      <c r="H41" s="15">
+        <v>0</v>
+      </c>
+      <c r="I41" s="26">
+        <v>30010003</v>
+      </c>
+      <c r="J41" s="14"/>
+      <c r="K41" s="27">
+        <v>4001003</v>
+      </c>
+      <c r="L41" s="28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A42" s="2">
+        <f t="shared" si="0"/>
+        <v>1001201622</v>
+      </c>
+      <c r="B42" s="14">
+        <v>100100</v>
+      </c>
+      <c r="C42" s="8">
+        <v>4</v>
+      </c>
+      <c r="D42" s="14">
+        <v>22</v>
+      </c>
+      <c r="E42" s="14">
+        <v>2</v>
+      </c>
+      <c r="F42" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42" s="14">
+        <v>16</v>
+      </c>
+      <c r="H42" s="15">
+        <v>0</v>
+      </c>
+      <c r="I42" s="26">
+        <v>30010004</v>
+      </c>
+      <c r="J42" s="14"/>
+      <c r="K42" s="27">
+        <v>4001004</v>
+      </c>
+      <c r="L42" s="28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="1:12">
+      <c r="A43" s="2">
+        <f t="shared" ref="A43:A48" si="1">(B43)*10000+D43+G43*100+E43*100000</f>
+        <v>1001201628</v>
+      </c>
+      <c r="B43" s="16">
+        <v>100100</v>
+      </c>
+      <c r="C43" s="8">
+        <v>4</v>
+      </c>
+      <c r="D43" s="16">
+        <v>28</v>
+      </c>
+      <c r="E43" s="16">
+        <v>2</v>
+      </c>
+      <c r="F43" s="16"/>
+      <c r="G43" s="16">
+        <v>16</v>
+      </c>
+      <c r="H43" s="17">
+        <v>0</v>
+      </c>
+      <c r="I43" s="29">
+        <v>30010005</v>
+      </c>
+      <c r="J43" s="16"/>
+      <c r="K43" s="16">
+        <v>0</v>
+      </c>
+      <c r="L43" s="30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="1:12">
+      <c r="A44" s="2">
+        <f t="shared" si="1"/>
+        <v>1001201528</v>
+      </c>
+      <c r="B44" s="18">
+        <v>100100</v>
+      </c>
+      <c r="C44" s="8">
+        <v>4</v>
+      </c>
+      <c r="D44" s="18">
+        <v>28</v>
+      </c>
+      <c r="E44" s="18">
+        <v>2</v>
+      </c>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18">
+        <v>15</v>
+      </c>
+      <c r="H44" s="19">
+        <v>0</v>
+      </c>
+      <c r="I44" s="31">
+        <v>30010006</v>
+      </c>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18">
+        <v>0</v>
+      </c>
+      <c r="L44" s="32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="1:12">
+      <c r="A45" s="2">
+        <f t="shared" si="1"/>
+        <v>1001400317</v>
+      </c>
+      <c r="B45" s="20">
+        <v>100100</v>
+      </c>
+      <c r="C45" s="8">
+        <v>1</v>
+      </c>
+      <c r="D45" s="20">
+        <v>17</v>
+      </c>
+      <c r="E45" s="20">
+        <v>4</v>
+      </c>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20">
+        <v>3</v>
+      </c>
+      <c r="H45" s="21">
+        <v>0</v>
+      </c>
+      <c r="I45" s="33"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="20">
+        <v>0</v>
+      </c>
+      <c r="L45" s="34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="1:12">
+      <c r="A46" s="2">
+        <f t="shared" si="1"/>
+        <v>1001400417</v>
+      </c>
+      <c r="B46" s="22">
+        <v>100100</v>
+      </c>
+      <c r="C46" s="8">
+        <v>1</v>
+      </c>
+      <c r="D46" s="22">
+        <v>17</v>
+      </c>
+      <c r="E46" s="22">
+        <v>4</v>
+      </c>
+      <c r="F46" s="22"/>
+      <c r="G46" s="22">
+        <v>4</v>
+      </c>
+      <c r="H46" s="23">
+        <v>0</v>
+      </c>
+      <c r="I46" s="35"/>
+      <c r="J46" s="22"/>
+      <c r="K46" s="22">
+        <v>0</v>
+      </c>
+      <c r="L46" s="36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="1:12">
+      <c r="A47" s="2">
+        <f t="shared" si="1"/>
+        <v>1001400517</v>
+      </c>
+      <c r="B47" s="22">
+        <v>100100</v>
+      </c>
+      <c r="C47" s="8">
+        <v>1</v>
+      </c>
+      <c r="D47" s="22">
+        <v>17</v>
+      </c>
+      <c r="E47" s="22">
+        <v>4</v>
+      </c>
+      <c r="F47" s="22"/>
+      <c r="G47" s="22">
+        <v>5</v>
+      </c>
+      <c r="H47" s="23">
+        <v>0</v>
+      </c>
+      <c r="I47" s="35"/>
+      <c r="J47" s="22"/>
+      <c r="K47" s="22">
+        <v>0</v>
+      </c>
+      <c r="L47" s="36" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A48" s="2">
+        <f t="shared" si="1"/>
+        <v>1001400130</v>
+      </c>
+      <c r="B48" s="22">
+        <v>100100</v>
+      </c>
+      <c r="C48" s="8">
+        <v>1</v>
+      </c>
+      <c r="D48" s="22">
+        <v>30</v>
+      </c>
+      <c r="E48" s="22">
+        <v>4</v>
+      </c>
+      <c r="F48" s="22"/>
+      <c r="G48" s="22">
+        <v>1</v>
+      </c>
+      <c r="H48" s="23">
+        <v>0</v>
+      </c>
+      <c r="I48" s="35">
+        <v>30010007</v>
+      </c>
+      <c r="J48" s="22"/>
+      <c r="K48" s="22">
+        <v>0</v>
+      </c>
+      <c r="L48" s="36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A49" s="2">
+        <v>1007300301</v>
+      </c>
+      <c r="B49" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C49" s="8">
+        <v>4</v>
+      </c>
+      <c r="D49" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E49" s="14">
+        <v>3</v>
+      </c>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14">
+        <v>3</v>
+      </c>
+      <c r="H49" s="15">
+        <v>2</v>
+      </c>
+      <c r="I49" s="15"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="14"/>
+      <c r="L49" s="10"/>
+    </row>
+    <row r="50" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A50" s="2">
+        <v>1007300302</v>
+      </c>
+      <c r="B50" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C50" s="8">
+        <v>4</v>
+      </c>
+      <c r="D50" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E50" s="14">
+        <v>3</v>
+      </c>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14">
+        <v>3</v>
+      </c>
+      <c r="H50" s="15">
+        <v>2</v>
+      </c>
+      <c r="I50" s="15"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="14"/>
+      <c r="L50" s="10"/>
+    </row>
+    <row r="51" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A51" s="2">
+        <v>1007300303</v>
+      </c>
+      <c r="B51" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C51" s="8">
+        <v>4</v>
+      </c>
+      <c r="D51" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="E51" s="14">
+        <v>3</v>
+      </c>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14">
+        <v>3</v>
+      </c>
+      <c r="H51" s="15">
+        <v>4</v>
+      </c>
+      <c r="I51" s="15"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="14"/>
+      <c r="L51" s="10"/>
+    </row>
+    <row r="52" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A52" s="2">
+        <v>1007300304</v>
+      </c>
+      <c r="B52" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C52" s="8">
+        <v>4</v>
+      </c>
+      <c r="D52" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E52" s="14">
+        <v>3</v>
+      </c>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14">
+        <v>3</v>
+      </c>
+      <c r="H52" s="15">
+        <v>4</v>
+      </c>
+      <c r="I52" s="15"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="14"/>
+      <c r="L52" s="10"/>
+    </row>
+    <row r="53" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A53" s="2">
+        <v>1007300305</v>
+      </c>
+      <c r="B53" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C53" s="8">
+        <v>4</v>
+      </c>
+      <c r="D53" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E53" s="14">
+        <v>3</v>
+      </c>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14">
+        <v>3</v>
+      </c>
+      <c r="H53" s="15">
+        <v>6</v>
+      </c>
+      <c r="I53" s="15"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="14"/>
+      <c r="L53" s="10"/>
+    </row>
+    <row r="54" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A54" s="2">
+        <v>1007300306</v>
+      </c>
+      <c r="B54" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C54" s="8">
+        <v>4</v>
+      </c>
+      <c r="D54" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E54" s="14">
+        <v>3</v>
+      </c>
+      <c r="F54" s="14"/>
+      <c r="G54" s="14">
+        <v>3</v>
+      </c>
+      <c r="H54" s="15">
+        <v>8</v>
+      </c>
+      <c r="I54" s="15"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="14"/>
+      <c r="L54" s="10"/>
+    </row>
+    <row r="55" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A55" s="2">
+        <v>1007300307</v>
+      </c>
+      <c r="B55" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C55" s="8">
+        <v>4</v>
+      </c>
+      <c r="D55" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E55" s="14">
+        <v>3</v>
+      </c>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14">
+        <v>3</v>
+      </c>
+      <c r="H55" s="15">
+        <v>10</v>
+      </c>
+      <c r="I55" s="15"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="14"/>
+      <c r="L55" s="10"/>
+    </row>
+    <row r="56" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A56" s="2">
+        <v>1007300308</v>
+      </c>
+      <c r="B56" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C56" s="8">
+        <v>4</v>
+      </c>
+      <c r="D56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E56" s="14">
+        <v>3</v>
+      </c>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14">
+        <v>3</v>
+      </c>
+      <c r="H56" s="15">
+        <v>15</v>
+      </c>
+      <c r="I56" s="15"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="14"/>
+      <c r="L56" s="10"/>
+    </row>
+    <row r="57" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A57" s="2">
+        <v>1007300401</v>
+      </c>
+      <c r="B57" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C57" s="8">
+        <v>4</v>
+      </c>
+      <c r="D57" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E57" s="14">
+        <v>3</v>
+      </c>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14">
+        <v>4</v>
+      </c>
+      <c r="H57" s="15">
+        <v>5</v>
+      </c>
+      <c r="I57" s="15"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="14"/>
+      <c r="L57" s="10"/>
+    </row>
+    <row r="58" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A58" s="2">
+        <v>1007300402</v>
+      </c>
+      <c r="B58" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C58" s="8">
+        <v>4</v>
+      </c>
+      <c r="D58" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E58" s="14">
+        <v>3</v>
+      </c>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14">
+        <v>4</v>
+      </c>
+      <c r="H58" s="15">
+        <v>5</v>
+      </c>
+      <c r="I58" s="15"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="14"/>
+      <c r="L58" s="10"/>
+    </row>
+    <row r="59" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A59" s="2">
+        <v>1007300403</v>
+      </c>
+      <c r="B59" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C59" s="8">
+        <v>4</v>
+      </c>
+      <c r="D59" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="E59" s="14">
+        <v>3</v>
+      </c>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14">
+        <v>4</v>
+      </c>
+      <c r="H59" s="15">
+        <v>10</v>
+      </c>
+      <c r="I59" s="15"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="14"/>
+      <c r="L59" s="10"/>
+    </row>
+    <row r="60" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A60" s="2">
+        <v>1007300404</v>
+      </c>
+      <c r="B60" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C60" s="8">
+        <v>4</v>
+      </c>
+      <c r="D60" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E60" s="14">
+        <v>3</v>
+      </c>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14">
+        <v>4</v>
+      </c>
+      <c r="H60" s="15">
+        <v>10</v>
+      </c>
+      <c r="I60" s="15"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="14"/>
+      <c r="L60" s="10"/>
+    </row>
+    <row r="61" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A61" s="2">
+        <v>1007300405</v>
+      </c>
+      <c r="B61" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C61" s="8">
+        <v>4</v>
+      </c>
+      <c r="D61" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E61" s="14">
+        <v>3</v>
+      </c>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14">
+        <v>4</v>
+      </c>
+      <c r="H61" s="15">
+        <v>15</v>
+      </c>
+      <c r="I61" s="15"/>
+      <c r="J61" s="14"/>
+      <c r="K61" s="14"/>
+      <c r="L61" s="10"/>
+    </row>
+    <row r="62" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A62" s="2">
+        <v>1007300406</v>
+      </c>
+      <c r="B62" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C62" s="8">
+        <v>4</v>
+      </c>
+      <c r="D62" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E62" s="14">
+        <v>3</v>
+      </c>
+      <c r="F62" s="14"/>
+      <c r="G62" s="14">
+        <v>4</v>
+      </c>
+      <c r="H62" s="15">
+        <v>20</v>
+      </c>
+      <c r="I62" s="15"/>
+      <c r="J62" s="14"/>
+      <c r="K62" s="14"/>
+      <c r="L62" s="10"/>
+    </row>
+    <row r="63" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A63" s="2">
+        <v>1007300407</v>
+      </c>
+      <c r="B63" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C63" s="8">
+        <v>4</v>
+      </c>
+      <c r="D63" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E63" s="14">
+        <v>3</v>
+      </c>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14">
+        <v>4</v>
+      </c>
+      <c r="H63" s="15">
+        <v>40</v>
+      </c>
+      <c r="I63" s="15"/>
+      <c r="J63" s="14"/>
+      <c r="K63" s="14"/>
+      <c r="L63" s="10"/>
+    </row>
+    <row r="64" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A64" s="2">
+        <v>1007300408</v>
+      </c>
+      <c r="B64" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C64" s="8">
+        <v>4</v>
+      </c>
+      <c r="D64" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E64" s="14">
+        <v>3</v>
+      </c>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14">
+        <v>4</v>
+      </c>
+      <c r="H64" s="15">
+        <v>60</v>
+      </c>
+      <c r="I64" s="15"/>
+      <c r="J64" s="14"/>
+      <c r="K64" s="14"/>
+      <c r="L64" s="10"/>
+    </row>
+    <row r="65" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A65" s="2">
+        <v>1007300501</v>
+      </c>
+      <c r="B65" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C65" s="8">
+        <v>4</v>
+      </c>
+      <c r="D65" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E65" s="14">
+        <v>3</v>
+      </c>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14">
+        <v>5</v>
+      </c>
+      <c r="H65" s="15">
+        <v>10</v>
+      </c>
+      <c r="I65" s="15"/>
+      <c r="J65" s="14"/>
+      <c r="K65" s="14"/>
+      <c r="L65" s="10"/>
+    </row>
+    <row r="66" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A66" s="2">
+        <v>1007300502</v>
+      </c>
+      <c r="B66" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C66" s="8">
+        <v>4</v>
+      </c>
+      <c r="D66" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E66" s="14">
+        <v>3</v>
+      </c>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14">
+        <v>5</v>
+      </c>
+      <c r="H66" s="15">
+        <v>10</v>
+      </c>
+      <c r="I66" s="15"/>
+      <c r="J66" s="14"/>
+      <c r="K66" s="14"/>
+      <c r="L66" s="10"/>
+    </row>
+    <row r="67" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A67" s="2">
+        <v>1007300503</v>
+      </c>
+      <c r="B67" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C67" s="8">
+        <v>4</v>
+      </c>
+      <c r="D67" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="E67" s="14">
+        <v>3</v>
+      </c>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14">
+        <v>5</v>
+      </c>
+      <c r="H67" s="15">
+        <v>20</v>
+      </c>
+      <c r="I67" s="15"/>
+      <c r="J67" s="14"/>
+      <c r="K67" s="14"/>
+      <c r="L67" s="10"/>
+    </row>
+    <row r="68" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A68" s="2">
+        <v>1007300504</v>
+      </c>
+      <c r="B68" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C68" s="8">
+        <v>4</v>
+      </c>
+      <c r="D68" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E68" s="14">
+        <v>3</v>
+      </c>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14">
+        <v>5</v>
+      </c>
+      <c r="H68" s="15">
+        <v>20</v>
+      </c>
+      <c r="I68" s="15"/>
+      <c r="J68" s="14"/>
+      <c r="K68" s="14"/>
+      <c r="L68" s="10"/>
+    </row>
+    <row r="69" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A69" s="2">
+        <v>1007300505</v>
+      </c>
+      <c r="B69" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C69" s="8">
+        <v>4</v>
+      </c>
+      <c r="D69" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E69" s="14">
+        <v>3</v>
+      </c>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14">
+        <v>5</v>
+      </c>
+      <c r="H69" s="15">
+        <v>30</v>
+      </c>
+      <c r="I69" s="15"/>
+      <c r="J69" s="14"/>
+      <c r="K69" s="14"/>
+      <c r="L69" s="10"/>
+    </row>
+    <row r="70" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A70" s="2">
+        <v>1007300506</v>
+      </c>
+      <c r="B70" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C70" s="8">
+        <v>4</v>
+      </c>
+      <c r="D70" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E70" s="14">
+        <v>3</v>
+      </c>
+      <c r="F70" s="14"/>
+      <c r="G70" s="14">
+        <v>5</v>
+      </c>
+      <c r="H70" s="15">
+        <v>40</v>
+      </c>
+      <c r="I70" s="15"/>
+      <c r="J70" s="14"/>
+      <c r="K70" s="14"/>
+      <c r="L70" s="10"/>
+    </row>
+    <row r="71" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A71" s="2">
+        <v>1007300507</v>
+      </c>
+      <c r="B71" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C71" s="8">
+        <v>4</v>
+      </c>
+      <c r="D71" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E71" s="14">
+        <v>3</v>
+      </c>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14">
+        <v>5</v>
+      </c>
+      <c r="H71" s="15">
+        <v>80</v>
+      </c>
+      <c r="I71" s="15"/>
+      <c r="J71" s="14"/>
+      <c r="K71" s="14"/>
+      <c r="L71" s="10"/>
+    </row>
+    <row r="72" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A72" s="2">
+        <v>1007300508</v>
+      </c>
+      <c r="B72" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C72" s="8">
+        <v>4</v>
+      </c>
+      <c r="D72" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E72" s="14">
+        <v>3</v>
+      </c>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14">
+        <v>5</v>
+      </c>
+      <c r="H72" s="15">
+        <v>120</v>
+      </c>
+      <c r="I72" s="15"/>
+      <c r="J72" s="14"/>
+      <c r="K72" s="14"/>
+      <c r="L72" s="10"/>
+    </row>
+    <row r="73" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A73" s="2">
+        <f t="shared" ref="A73:A85" si="2">(B73)*10000+D73+G73*100+E73*100000</f>
+        <v>1007400310</v>
+      </c>
+      <c r="B73" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C73" s="8">
+        <v>4</v>
+      </c>
+      <c r="D73" s="14">
+        <v>10</v>
+      </c>
+      <c r="E73" s="14">
+        <v>4</v>
+      </c>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14">
+        <v>3</v>
+      </c>
+      <c r="H73" s="15">
+        <v>0</v>
+      </c>
+      <c r="I73" s="15">
+        <v>30070001</v>
+      </c>
+      <c r="J73" s="14"/>
+      <c r="K73" s="14"/>
+      <c r="L73" s="10"/>
+    </row>
+    <row r="74" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A74" s="2">
+        <f t="shared" si="2"/>
+        <v>1007400410</v>
+      </c>
+      <c r="B74" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C74" s="8">
+        <v>4</v>
+      </c>
+      <c r="D74" s="14">
+        <v>10</v>
+      </c>
+      <c r="E74" s="14">
+        <v>4</v>
+      </c>
+      <c r="F74" s="14"/>
+      <c r="G74" s="14">
+        <v>4</v>
+      </c>
+      <c r="H74" s="15">
+        <v>0</v>
+      </c>
+      <c r="I74" s="15">
+        <v>30070002</v>
+      </c>
+      <c r="J74" s="14"/>
+      <c r="K74" s="14"/>
+      <c r="L74" s="10"/>
+    </row>
+    <row r="75" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A75" s="2">
+        <f t="shared" si="2"/>
+        <v>1014500502</v>
+      </c>
+      <c r="B75" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C75" s="8">
+        <v>4</v>
+      </c>
+      <c r="D75" s="37">
+        <v>2</v>
+      </c>
+      <c r="E75" s="37">
+        <v>5</v>
+      </c>
+      <c r="F75" s="37"/>
+      <c r="G75" s="37">
+        <v>5</v>
+      </c>
+      <c r="H75" s="38">
+        <v>1</v>
+      </c>
+      <c r="I75" s="38"/>
+      <c r="J75" s="37"/>
+      <c r="K75" s="37"/>
+      <c r="L75" s="10"/>
+    </row>
+    <row r="76" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A76" s="2">
+        <f t="shared" si="2"/>
+        <v>1014500503</v>
+      </c>
+      <c r="B76" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C76" s="8">
+        <v>4</v>
+      </c>
+      <c r="D76" s="37">
+        <v>3</v>
+      </c>
+      <c r="E76" s="37">
+        <v>5</v>
+      </c>
+      <c r="F76" s="37"/>
+      <c r="G76" s="37">
+        <v>5</v>
+      </c>
+      <c r="H76" s="38">
+        <v>1</v>
+      </c>
+      <c r="I76" s="38"/>
+      <c r="J76" s="37"/>
+      <c r="K76" s="37"/>
+      <c r="L76" s="10"/>
+    </row>
+    <row r="77" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A77" s="2">
+        <f t="shared" si="2"/>
+        <v>1014500504</v>
+      </c>
+      <c r="B77" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C77" s="8">
+        <v>4</v>
+      </c>
+      <c r="D77" s="37">
+        <v>4</v>
+      </c>
+      <c r="E77" s="37">
+        <v>5</v>
+      </c>
+      <c r="F77" s="37"/>
+      <c r="G77" s="37">
+        <v>5</v>
+      </c>
+      <c r="H77" s="38">
+        <v>1</v>
+      </c>
+      <c r="I77" s="38"/>
+      <c r="J77" s="37"/>
+      <c r="K77" s="37"/>
+      <c r="L77" s="10"/>
+    </row>
+    <row r="78" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A78" s="2">
+        <f t="shared" si="2"/>
+        <v>1014500505</v>
+      </c>
+      <c r="B78" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C78" s="8">
+        <v>4</v>
+      </c>
+      <c r="D78" s="37">
+        <v>5</v>
+      </c>
+      <c r="E78" s="37">
+        <v>5</v>
+      </c>
+      <c r="F78" s="37"/>
+      <c r="G78" s="37">
+        <v>5</v>
+      </c>
+      <c r="H78" s="38">
+        <v>2</v>
+      </c>
+      <c r="I78" s="38"/>
+      <c r="J78" s="37"/>
+      <c r="K78" s="37"/>
+      <c r="L78" s="10"/>
+    </row>
+    <row r="79" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A79" s="2">
+        <f t="shared" si="2"/>
+        <v>1014500506</v>
+      </c>
+      <c r="B79" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C79" s="8">
+        <v>4</v>
+      </c>
+      <c r="D79" s="37">
+        <v>6</v>
+      </c>
+      <c r="E79" s="37">
+        <v>5</v>
+      </c>
+      <c r="F79" s="37"/>
+      <c r="G79" s="37">
+        <v>5</v>
+      </c>
+      <c r="H79" s="38">
+        <v>2</v>
+      </c>
+      <c r="I79" s="38"/>
+      <c r="J79" s="37"/>
+      <c r="K79" s="37"/>
+      <c r="L79" s="10"/>
+    </row>
+    <row r="80" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A80" s="2">
+        <f t="shared" si="2"/>
+        <v>1014500507</v>
+      </c>
+      <c r="B80" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C80" s="8">
+        <v>4</v>
+      </c>
+      <c r="D80" s="37">
+        <v>7</v>
+      </c>
+      <c r="E80" s="37">
+        <v>5</v>
+      </c>
+      <c r="F80" s="37"/>
+      <c r="G80" s="37">
+        <v>5</v>
+      </c>
+      <c r="H80" s="38">
+        <v>2</v>
+      </c>
+      <c r="I80" s="38"/>
+      <c r="J80" s="37"/>
+      <c r="K80" s="37"/>
+      <c r="L80" s="10"/>
+    </row>
+    <row r="81" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A81" s="2">
+        <f t="shared" si="2"/>
+        <v>1014500508</v>
+      </c>
+      <c r="B81" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C81" s="8">
+        <v>4</v>
+      </c>
+      <c r="D81" s="37">
+        <v>8</v>
+      </c>
+      <c r="E81" s="37">
+        <v>5</v>
+      </c>
+      <c r="F81" s="37"/>
+      <c r="G81" s="37">
+        <v>5</v>
+      </c>
+      <c r="H81" s="38">
+        <v>3</v>
+      </c>
+      <c r="I81" s="38"/>
+      <c r="J81" s="37"/>
+      <c r="K81" s="37"/>
+      <c r="L81" s="10"/>
+    </row>
+    <row r="82" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A82" s="2">
+        <f t="shared" si="2"/>
+        <v>1014500509</v>
+      </c>
+      <c r="B82" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C82" s="8">
+        <v>4</v>
+      </c>
+      <c r="D82" s="37">
+        <v>9</v>
+      </c>
+      <c r="E82" s="37">
+        <v>5</v>
+      </c>
+      <c r="F82" s="37"/>
+      <c r="G82" s="37">
+        <v>5</v>
+      </c>
+      <c r="H82" s="38">
+        <v>3</v>
+      </c>
+      <c r="I82" s="38"/>
+      <c r="J82" s="37"/>
+      <c r="K82" s="37"/>
+      <c r="L82" s="10"/>
+    </row>
+    <row r="83" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A83" s="2">
+        <f t="shared" si="2"/>
+        <v>1014500510</v>
+      </c>
+      <c r="B83" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C83" s="8">
+        <v>4</v>
+      </c>
+      <c r="D83" s="37">
+        <v>10</v>
+      </c>
+      <c r="E83" s="37">
+        <v>5</v>
+      </c>
+      <c r="F83" s="37"/>
+      <c r="G83" s="37">
+        <v>5</v>
+      </c>
+      <c r="H83" s="38">
+        <v>4</v>
+      </c>
+      <c r="I83" s="38"/>
+      <c r="J83" s="37"/>
+      <c r="K83" s="37"/>
+      <c r="L83" s="10"/>
+    </row>
+    <row r="84" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A84" s="2">
+        <f t="shared" si="2"/>
+        <v>1014500511</v>
+      </c>
+      <c r="B84" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C84" s="8">
+        <v>4</v>
+      </c>
+      <c r="D84" s="37">
         <v>11</v>
       </c>
-      <c r="G38" s="2">
-        <v>1</v>
-      </c>
-      <c r="H38" s="2">
+      <c r="E84" s="37">
         <v>5</v>
       </c>
-      <c r="I38" s="2">
-        <v>300</v>
-      </c>
-      <c r="J38" s="2">
-        <v>1</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O38" s="2">
+      <c r="F84" s="37"/>
+      <c r="G84" s="37">
+        <v>5</v>
+      </c>
+      <c r="H84" s="38">
+        <v>5</v>
+      </c>
+      <c r="I84" s="38"/>
+      <c r="J84" s="37"/>
+      <c r="K84" s="37"/>
+      <c r="L84" s="10"/>
+    </row>
+    <row r="85" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A85" s="2">
+        <f t="shared" si="2"/>
+        <v>1014400513</v>
+      </c>
+      <c r="B85" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C85" s="8">
+        <v>4</v>
+      </c>
+      <c r="D85" s="37">
+        <v>13</v>
+      </c>
+      <c r="E85" s="37">
+        <v>4</v>
+      </c>
+      <c r="F85" s="37"/>
+      <c r="G85" s="37">
+        <v>5</v>
+      </c>
+      <c r="H85" s="38">
         <v>0</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="39" s="2" customFormat="1" spans="1:16">
-      <c r="A39" s="2">
-        <v>35</v>
-      </c>
-      <c r="B39" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C39" s="2">
-        <v>4</v>
-      </c>
-      <c r="D39" s="2">
-        <v>1</v>
-      </c>
-      <c r="E39" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F39" s="2">
-        <v>19</v>
-      </c>
-      <c r="G39" s="2">
-        <v>2</v>
-      </c>
-      <c r="H39" s="2">
-        <v>2</v>
-      </c>
-      <c r="I39" s="2">
-        <v>0</v>
-      </c>
-      <c r="J39" s="2">
-        <v>2</v>
-      </c>
-      <c r="K39" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="O39" s="2">
-        <v>0</v>
-      </c>
-      <c r="P39" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" s="2" customFormat="1" spans="1:16">
-      <c r="A40" s="2">
-        <v>36</v>
-      </c>
-      <c r="B40" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C40" s="2">
-        <v>4</v>
-      </c>
-      <c r="D40" s="2">
-        <v>1</v>
-      </c>
-      <c r="E40" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F40" s="2">
-        <v>20</v>
-      </c>
-      <c r="G40" s="2">
-        <v>2</v>
-      </c>
-      <c r="H40" s="2">
-        <v>2</v>
-      </c>
-      <c r="I40" s="2">
-        <v>0</v>
-      </c>
-      <c r="J40" s="2">
-        <v>2</v>
-      </c>
-      <c r="K40" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="O40" s="2">
-        <v>0</v>
-      </c>
-      <c r="P40" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16">
-      <c r="A41" s="2">
-        <v>37</v>
-      </c>
-      <c r="B41" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C41" s="2">
-        <v>4</v>
-      </c>
-      <c r="D41" s="2">
-        <v>1</v>
-      </c>
-      <c r="E41" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F41" s="2">
-        <v>21</v>
-      </c>
-      <c r="G41" s="2">
-        <v>2</v>
-      </c>
-      <c r="H41" s="2">
-        <v>2</v>
-      </c>
-      <c r="I41" s="5">
-        <v>0</v>
-      </c>
-      <c r="J41" s="2">
-        <v>2</v>
-      </c>
-      <c r="K41" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2">
-        <v>0</v>
-      </c>
-      <c r="P41" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16">
-      <c r="A42" s="2">
-        <v>38</v>
-      </c>
-      <c r="B42" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C42" s="2">
-        <v>4</v>
-      </c>
-      <c r="D42" s="2">
-        <v>1</v>
-      </c>
-      <c r="E42" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F42" s="2">
-        <v>22</v>
-      </c>
-      <c r="G42" s="2">
-        <v>2</v>
-      </c>
-      <c r="H42" s="2">
-        <v>2</v>
-      </c>
-      <c r="I42" s="5">
-        <v>0</v>
-      </c>
-      <c r="J42" s="2">
-        <v>2</v>
-      </c>
-      <c r="K42" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2">
-        <v>0</v>
-      </c>
-      <c r="P42" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16">
-      <c r="A43" s="2">
-        <v>39</v>
-      </c>
-      <c r="B43" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C43" s="2">
-        <v>4</v>
-      </c>
-      <c r="D43" s="2">
-        <v>1</v>
-      </c>
-      <c r="E43" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F43" s="2">
-        <v>19</v>
-      </c>
-      <c r="G43" s="2">
-        <v>2</v>
-      </c>
-      <c r="H43" s="2">
-        <v>3</v>
-      </c>
-      <c r="I43" s="2">
-        <v>0</v>
-      </c>
-      <c r="J43" s="2">
-        <v>2</v>
-      </c>
-      <c r="K43" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L43" s="2"/>
-      <c r="M43" s="2"/>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2">
-        <v>0</v>
-      </c>
-      <c r="P43" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16">
-      <c r="A44" s="2">
-        <v>40</v>
-      </c>
-      <c r="B44" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C44" s="2">
-        <v>4</v>
-      </c>
-      <c r="D44" s="2">
-        <v>1</v>
-      </c>
-      <c r="E44" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F44" s="2">
-        <v>20</v>
-      </c>
-      <c r="G44" s="2">
-        <v>2</v>
-      </c>
-      <c r="H44" s="2">
-        <v>3</v>
-      </c>
-      <c r="I44" s="2">
-        <v>0</v>
-      </c>
-      <c r="J44" s="2">
-        <v>2</v>
-      </c>
-      <c r="K44" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2">
-        <v>0</v>
-      </c>
-      <c r="P44" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16">
-      <c r="A45" s="2">
-        <v>41</v>
-      </c>
-      <c r="B45" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C45" s="2">
-        <v>4</v>
-      </c>
-      <c r="D45" s="2">
-        <v>1</v>
-      </c>
-      <c r="E45" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F45" s="2">
-        <v>21</v>
-      </c>
-      <c r="G45" s="2">
-        <v>2</v>
-      </c>
-      <c r="H45" s="2">
-        <v>3</v>
-      </c>
-      <c r="I45" s="5">
-        <v>0</v>
-      </c>
-      <c r="J45" s="2">
-        <v>2</v>
-      </c>
-      <c r="K45" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2">
-        <v>0</v>
-      </c>
-      <c r="P45" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16">
-      <c r="A46" s="2">
-        <v>42</v>
-      </c>
-      <c r="B46" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C46" s="2">
-        <v>4</v>
-      </c>
-      <c r="D46" s="2">
-        <v>1</v>
-      </c>
-      <c r="E46" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F46" s="2">
-        <v>22</v>
-      </c>
-      <c r="G46" s="2">
-        <v>2</v>
-      </c>
-      <c r="H46" s="2">
-        <v>3</v>
-      </c>
-      <c r="I46" s="5">
-        <v>0</v>
-      </c>
-      <c r="J46" s="2">
-        <v>2</v>
-      </c>
-      <c r="K46" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2">
-        <v>0</v>
-      </c>
-      <c r="P46" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16">
-      <c r="A47" s="2">
-        <v>43</v>
-      </c>
-      <c r="B47" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C47" s="2">
-        <v>4</v>
-      </c>
-      <c r="D47" s="2">
-        <v>1</v>
-      </c>
-      <c r="E47" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F47" s="2">
-        <v>19</v>
-      </c>
-      <c r="G47" s="2">
-        <v>2</v>
-      </c>
-      <c r="H47" s="2">
-        <v>4</v>
-      </c>
-      <c r="I47" s="2">
-        <v>0</v>
-      </c>
-      <c r="J47" s="2">
-        <v>2</v>
-      </c>
-      <c r="K47" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L47" s="2"/>
-      <c r="M47" s="2"/>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2">
-        <v>0</v>
-      </c>
-      <c r="P47" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16">
-      <c r="A48" s="2">
-        <v>44</v>
-      </c>
-      <c r="B48" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C48" s="2">
-        <v>4</v>
-      </c>
-      <c r="D48" s="2">
-        <v>1</v>
-      </c>
-      <c r="E48" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F48" s="2">
-        <v>20</v>
-      </c>
-      <c r="G48" s="2">
-        <v>2</v>
-      </c>
-      <c r="H48" s="2">
-        <v>4</v>
-      </c>
-      <c r="I48" s="2">
-        <v>0</v>
-      </c>
-      <c r="J48" s="2">
-        <v>2</v>
-      </c>
-      <c r="K48" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2">
-        <v>0</v>
-      </c>
-      <c r="P48" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16">
-      <c r="A49" s="2">
-        <v>45</v>
-      </c>
-      <c r="B49" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C49" s="2">
-        <v>4</v>
-      </c>
-      <c r="D49" s="2">
-        <v>1</v>
-      </c>
-      <c r="E49" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F49" s="2">
-        <v>21</v>
-      </c>
-      <c r="G49" s="2">
-        <v>2</v>
-      </c>
-      <c r="H49" s="2">
-        <v>4</v>
-      </c>
-      <c r="I49" s="5">
-        <v>0</v>
-      </c>
-      <c r="J49" s="2">
-        <v>2</v>
-      </c>
-      <c r="K49" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2">
-        <v>0</v>
-      </c>
-      <c r="P49" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16">
-      <c r="A50" s="2">
-        <v>46</v>
-      </c>
-      <c r="B50" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C50" s="2">
-        <v>4</v>
-      </c>
-      <c r="D50" s="2">
-        <v>1</v>
-      </c>
-      <c r="E50" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F50" s="2">
-        <v>22</v>
-      </c>
-      <c r="G50" s="2">
-        <v>2</v>
-      </c>
-      <c r="H50" s="2">
-        <v>4</v>
-      </c>
-      <c r="I50" s="5">
-        <v>0</v>
-      </c>
-      <c r="J50" s="2">
-        <v>2</v>
-      </c>
-      <c r="K50" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2">
-        <v>0</v>
-      </c>
-      <c r="P50" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16">
-      <c r="A51" s="2">
-        <v>47</v>
-      </c>
-      <c r="B51" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C51" s="2">
-        <v>4</v>
-      </c>
-      <c r="D51" s="2">
-        <v>1</v>
-      </c>
-      <c r="E51" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F51" s="2">
-        <v>19</v>
-      </c>
-      <c r="G51" s="2">
-        <v>2</v>
-      </c>
-      <c r="H51" s="2">
-        <v>5</v>
-      </c>
-      <c r="I51" s="2">
-        <v>0</v>
-      </c>
-      <c r="J51" s="2">
-        <v>2</v>
-      </c>
-      <c r="K51" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L51" s="2"/>
-      <c r="M51" s="2"/>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2">
-        <v>0</v>
-      </c>
-      <c r="P51" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16">
-      <c r="A52" s="2">
-        <v>48</v>
-      </c>
-      <c r="B52" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C52" s="2">
-        <v>4</v>
-      </c>
-      <c r="D52" s="2">
-        <v>1</v>
-      </c>
-      <c r="E52" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F52" s="2">
-        <v>20</v>
-      </c>
-      <c r="G52" s="2">
-        <v>2</v>
-      </c>
-      <c r="H52" s="2">
-        <v>5</v>
-      </c>
-      <c r="I52" s="2">
-        <v>0</v>
-      </c>
-      <c r="J52" s="2">
-        <v>2</v>
-      </c>
-      <c r="K52" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2">
-        <v>0</v>
-      </c>
-      <c r="P52" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16">
-      <c r="A53" s="2">
-        <v>49</v>
-      </c>
-      <c r="B53" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C53" s="2">
-        <v>4</v>
-      </c>
-      <c r="D53" s="2">
-        <v>1</v>
-      </c>
-      <c r="E53" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F53" s="2">
-        <v>21</v>
-      </c>
-      <c r="G53" s="2">
-        <v>2</v>
-      </c>
-      <c r="H53" s="2">
-        <v>5</v>
-      </c>
-      <c r="I53" s="5">
-        <v>0</v>
-      </c>
-      <c r="J53" s="2">
-        <v>2</v>
-      </c>
-      <c r="K53" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2">
-        <v>0</v>
-      </c>
-      <c r="P53" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16">
-      <c r="A54" s="2">
-        <v>50</v>
-      </c>
-      <c r="B54" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C54" s="2">
-        <v>4</v>
-      </c>
-      <c r="D54" s="2">
-        <v>1</v>
-      </c>
-      <c r="E54" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F54" s="2">
-        <v>22</v>
-      </c>
-      <c r="G54" s="2">
-        <v>2</v>
-      </c>
-      <c r="H54" s="2">
-        <v>5</v>
-      </c>
-      <c r="I54" s="5">
-        <v>0</v>
-      </c>
-      <c r="J54" s="2">
-        <v>2</v>
-      </c>
-      <c r="K54" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2">
-        <v>0</v>
-      </c>
-      <c r="P54" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16">
-      <c r="A55" s="2">
-        <v>51</v>
-      </c>
-      <c r="B55" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C55" s="2">
-        <v>4</v>
-      </c>
-      <c r="D55" s="2">
-        <v>1</v>
-      </c>
-      <c r="E55" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F55" s="2">
-        <v>15</v>
-      </c>
-      <c r="G55" s="2">
-        <v>2</v>
-      </c>
-      <c r="H55" s="2">
-        <v>1</v>
-      </c>
-      <c r="I55" s="5">
-        <v>0</v>
-      </c>
-      <c r="J55" s="2">
-        <v>2</v>
-      </c>
-      <c r="K55" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="L55" s="2"/>
-      <c r="M55" s="2"/>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2">
-        <v>0</v>
-      </c>
-      <c r="P55" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16">
-      <c r="A56" s="2">
-        <v>67</v>
-      </c>
-      <c r="B56" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C56" s="2">
-        <v>1</v>
-      </c>
-      <c r="D56" s="2">
-        <v>1</v>
-      </c>
-      <c r="E56" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F56" s="2">
-        <v>17</v>
-      </c>
-      <c r="G56" s="2">
-        <v>4</v>
-      </c>
-      <c r="H56" s="2">
-        <v>3</v>
-      </c>
-      <c r="I56" s="5">
-        <v>0</v>
-      </c>
-      <c r="J56" s="2">
-        <v>2</v>
-      </c>
-      <c r="K56" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="L56" s="2"/>
-      <c r="M56" s="2"/>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2">
-        <v>0</v>
-      </c>
-      <c r="P56" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16">
-      <c r="A57" s="2">
-        <v>68</v>
-      </c>
-      <c r="B57" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C57" s="2">
-        <v>1</v>
-      </c>
-      <c r="D57" s="2">
-        <v>1</v>
-      </c>
-      <c r="E57" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F57" s="2">
-        <v>17</v>
-      </c>
-      <c r="G57" s="2">
-        <v>4</v>
-      </c>
-      <c r="H57" s="2">
-        <v>4</v>
-      </c>
-      <c r="I57" s="5">
-        <v>0</v>
-      </c>
-      <c r="J57" s="2">
-        <v>2</v>
-      </c>
-      <c r="K57" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="L57" s="2"/>
-      <c r="M57" s="2"/>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2">
-        <v>0</v>
-      </c>
-      <c r="P57" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16">
-      <c r="A58" s="2">
-        <v>69</v>
-      </c>
-      <c r="B58" s="2">
-        <v>100100</v>
-      </c>
-      <c r="C58" s="2">
-        <v>1</v>
-      </c>
-      <c r="D58" s="2">
-        <v>1</v>
-      </c>
-      <c r="E58" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F58" s="2">
-        <v>17</v>
-      </c>
-      <c r="G58" s="2">
-        <v>4</v>
-      </c>
-      <c r="H58" s="2">
-        <v>5</v>
-      </c>
-      <c r="I58" s="5">
-        <v>0</v>
-      </c>
-      <c r="J58" s="2">
-        <v>2</v>
-      </c>
-      <c r="K58" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="L58" s="2"/>
-      <c r="M58" s="2"/>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2">
-        <v>0</v>
-      </c>
-      <c r="P58" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="I85" s="38"/>
+      <c r="J85" s="37"/>
+      <c r="K85" s="39">
+        <v>4014001</v>
+      </c>
+      <c r="L85" s="10"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:P58" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L85" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="C5:C58">
+  <conditionalFormatting sqref="B43">
+    <cfRule type="expression" dxfId="0" priority="18">
+      <formula>MOD($B43,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C43">
+    <cfRule type="expression" dxfId="0" priority="16">
+      <formula>MOD($B43,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A48">
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48">
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>MOD($B48,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C48">
     <cfRule type="expression" dxfId="0" priority="2">
+      <formula>MOD($B48,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E48:F48">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD($B48,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E73:F73">
+    <cfRule type="expression" dxfId="0" priority="44">
+      <formula>MOD($B73,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E74:F74">
+    <cfRule type="expression" dxfId="0" priority="9">
+      <formula>MOD($B74,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C85:L85">
+    <cfRule type="expression" dxfId="0" priority="45">
+      <formula>MOD($B85,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D65:D72">
+    <cfRule type="expression" dxfId="0" priority="7">
+      <formula>MOD($B65,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K39:K42">
+    <cfRule type="duplicateValues" dxfId="2" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A47 A49:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="319"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:L4">
+    <cfRule type="expression" dxfId="0" priority="318">
+      <formula>MOD($B1,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5:C42 C44:C47">
+    <cfRule type="expression" dxfId="0" priority="49">
       <formula>MOD($B5,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G56:G58">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>MOD($B56,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:P4">
-    <cfRule type="expression" dxfId="0" priority="271">
-      <formula>MOD($B1,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B41:B58 D43:E58">
-    <cfRule type="expression" dxfId="0" priority="5">
+  <conditionalFormatting sqref="D41:H42 J41:J42 L41:L42 G45:G47 D46:D47 B49:L64 E65:F72 B86:L1048576">
+    <cfRule type="expression" dxfId="0" priority="317">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D41:J42 L41:P42 H56:H58 D57:F58 B59:P1048576">
-    <cfRule type="expression" dxfId="0" priority="270">
+  <conditionalFormatting sqref="B41:B42 B44:B47">
+    <cfRule type="expression" dxfId="0" priority="52">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F45:J46 L45:P46">
-    <cfRule type="expression" dxfId="0" priority="8">
+  <conditionalFormatting sqref="D43:H43 J43:L43">
+    <cfRule type="expression" dxfId="0" priority="17">
+      <formula>MOD($B43,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D44:H44 J44:L47 H45:H47 D45:D47">
+    <cfRule type="expression" dxfId="0" priority="51">
+      <formula>MOD($B44,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E45:F47">
+    <cfRule type="expression" dxfId="0" priority="48">
       <formula>MOD($B45,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F49:J50 L49:P50">
-    <cfRule type="expression" dxfId="0" priority="6">
-      <formula>MOD($B49,2)=1</formula>
+  <conditionalFormatting sqref="G48 D48">
+    <cfRule type="expression" dxfId="0" priority="5">
+      <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F53:J55 L53:P58 I56:J58 F56:F58">
-    <cfRule type="expression" dxfId="0" priority="4">
-      <formula>MOD($B53,2)=1</formula>
+  <conditionalFormatting sqref="J48:L48 H48 D48">
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <conditionalFormatting sqref="B65:C72 G65:L72">
+    <cfRule type="expression" dxfId="0" priority="47">
+      <formula>MOD($B65,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B73:D73 G73:L73">
+    <cfRule type="expression" dxfId="0" priority="43">
+      <formula>MOD($B73,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B74:D74 G74:L74">
+    <cfRule type="expression" dxfId="0" priority="8">
+      <formula>MOD($B74,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B75:L84 B85">
+    <cfRule type="expression" dxfId="0" priority="46">
+      <formula>MOD($B75,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1">
       <formula1>"普通,免费,重转,全部"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1">
-      <formula1>"线注,线注乘倍率,总赌注"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -662,6 +662,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -669,11 +674,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="J39" s="14"/>
       <c r="K39" s="27">
-        <v>4001001</v>
+        <v>100100101</v>
       </c>
       <c r="L39" s="28" t="s">
         <v>26</v>
@@ -6153,7 +6153,7 @@
       </c>
       <c r="J40" s="14"/>
       <c r="K40" s="27">
-        <v>4001002</v>
+        <v>100100102</v>
       </c>
       <c r="L40" s="28" t="s">
         <v>27</v>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="J41" s="14"/>
       <c r="K41" s="27">
-        <v>4001003</v>
+        <v>100100103</v>
       </c>
       <c r="L41" s="28" t="s">
         <v>28</v>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="J42" s="14"/>
       <c r="K42" s="27">
-        <v>4001004</v>
+        <v>100100104</v>
       </c>
       <c r="L42" s="28" t="s">
         <v>29</v>
@@ -7488,7 +7488,7 @@
       <c r="I85" s="38"/>
       <c r="J85" s="37"/>
       <c r="K85" s="39">
-        <v>4014001</v>
+        <v>101400101</v>
       </c>
       <c r="L85" s="10"/>
     </row>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$134</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -68,31 +68,6 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">pgos:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>1.普通
-2.免费
-3.重转
-4.全部</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
           <t xml:space="preserve">Mr.M:
 </t>
         </r>
@@ -108,7 +83,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="1">
+    <comment ref="D1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -130,7 +105,30 @@
 2：指定图案_条件图案ID：条件图案出现，不需要考虑位置，一个指定图案触发一次
 3：满线图案_X连：从左至右，出现相同图案，连续X列表示X连，一个图案计算触发一次
 4：全局分散图案_数量：针对需要全局计算的元素，只考虑数量，此模式相同图案仅触发数量最多的一次
-5：满线图案_数量：从左至右，前一列出现相同图案，只统计数量，相同图案仅触发数量最多的一次</t>
+5：满线图案_数量：从左至右，前一列出现相同图案，只统计数量，相同图案仅触发数量最多的一次
+6：连线_分散数量：根据赔付线中奖，但不需要考虑连线数量，改为统计此中奖线上的图案数量，相同图案仅触发数量最多的一次</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">Mr.M:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>奖项数量</t>
         </r>
       </text>
     </comment>
@@ -152,7 +150,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>奖项数量</t>
+          <t>中奖数量对应的倍数</t>
         </r>
       </text>
     </comment>
@@ -174,11 +172,12 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>中奖数量对应的倍数</t>
+          <t>该行元素的数量触发小游戏的ID，根据小游戏配置填写
+小游戏id;</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="I1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -187,8 +186,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">Mr.M:
-</t>
+          <t>Administrator:</t>
         </r>
         <r>
           <rPr>
@@ -196,8 +194,9 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>该行元素的数量触发小游戏的ID，根据小游戏配置填写
-小游戏id;</t>
+          <t xml:space="preserve">
+0：乘法，原倍率 × 此倍率值
+1：加法，</t>
         </r>
       </text>
     </comment>
@@ -260,7 +259,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D49" authorId="2">
+    <comment ref="C61" authorId="2">
       <text>
         <r>
           <rPr>
@@ -287,15 +286,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="64">
   <si>
     <t>id</t>
   </si>
   <si>
     <t>游戏ID</t>
-  </si>
-  <si>
-    <t>旋转状态</t>
   </si>
   <si>
     <t>元素ID_相同元素_相同元素</t>
@@ -313,7 +309,10 @@
     <t>触发小游戏ID</t>
   </si>
   <si>
-    <t>额外出现元素导致倍率加成</t>
+    <t>额外元素倍率计算方式</t>
+  </si>
+  <si>
+    <t>额外出现元素导致倍率加成{元素ID_数量_倍率}</t>
   </si>
   <si>
     <t>jackpotID</t>
@@ -328,13 +327,10 @@
     <t>List&lt;int&gt;{_}</t>
   </si>
   <si>
-    <t>List&lt;List&lt;int&gt;{,}&gt;{;}</t>
+    <t>List&lt;List&lt;int&gt;{_}&gt;{|}</t>
   </si>
   <si>
     <t>gameType</t>
-  </si>
-  <si>
-    <t>rotateState</t>
   </si>
   <si>
     <t>elementId</t>
@@ -352,13 +348,16 @@
     <t>featureTriggerId</t>
   </si>
   <si>
+    <t>statisticalType</t>
+  </si>
+  <si>
     <t>betTimes</t>
   </si>
   <si>
     <t>最大连线</t>
   </si>
   <si>
-    <t>13,1,2;13,2,4;13,3,6;13,4,8;14,1,5;14,2,10;14,3,15;14,4,20</t>
+    <t>13_1_2|13_2_4|13_3_6|13_4_8|14_1_5|14_2_10|14_3_15|14_4_20</t>
   </si>
   <si>
     <t>-</t>
@@ -397,6 +396,12 @@
     <t>指定触发隐藏免费游戏，仅用于结果库生成</t>
   </si>
   <si>
+    <t>21_1_6|22_1_9|23_1_12|24_1_15|25_1_21|26_1_24|27_1_32|28_1_38|29_1_49|30_1_58|31_1_68|32_1_79|33_1_85|34_1_96|35_1_105|36_1_110|37_1_125|38_1_138|39_1_150|40_1_210</t>
+  </si>
+  <si>
+    <t>最后一列出jackpot</t>
+  </si>
+  <si>
     <t>1_11</t>
   </si>
   <si>
@@ -419,6 +424,60 @@
   </si>
   <si>
     <t>8_18</t>
+  </si>
+  <si>
+    <t>横财神第1行</t>
+  </si>
+  <si>
+    <t>横财神第2行</t>
+  </si>
+  <si>
+    <t>横财神第3行</t>
+  </si>
+  <si>
+    <t>横财神第2列</t>
+  </si>
+  <si>
+    <t>横财神第3列</t>
+  </si>
+  <si>
+    <t>横财神第4列</t>
+  </si>
+  <si>
+    <t>第2次_横财神第1行</t>
+  </si>
+  <si>
+    <t>第2次_横财神第2行</t>
+  </si>
+  <si>
+    <t>第2次_横财神第3行</t>
+  </si>
+  <si>
+    <t>第2次_横财神第2列</t>
+  </si>
+  <si>
+    <t>第2次_横财神第3列</t>
+  </si>
+  <si>
+    <t>第2次_横财神第4列</t>
+  </si>
+  <si>
+    <t>第3次_横财神第1行</t>
+  </si>
+  <si>
+    <t>第3次_横财神第2行</t>
+  </si>
+  <si>
+    <t>第3次_横财神第3行</t>
+  </si>
+  <si>
+    <t>第3次_横财神第2列</t>
+  </si>
+  <si>
+    <t>第3次_横财神第3列</t>
+  </si>
+  <si>
+    <t>第3次_横财神第4列</t>
   </si>
 </sst>
 </file>
@@ -662,11 +721,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -683,8 +737,13 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="40">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -699,13 +758,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
+        <fgColor theme="5" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.35"/>
+        <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -730,6 +795,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1080,7 +1157,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1104,16 +1181,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1122,88 +1199,88 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1219,11 +1296,11 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1237,49 +1314,128 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1288,58 +1444,16 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
@@ -4737,57 +4851,56 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L85"/>
+  <dimension ref="A1:L134"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.5" style="7"/>
+    <col min="1" max="1" width="11.5" style="10"/>
     <col min="2" max="2" width="11" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10" style="8" customWidth="1"/>
-    <col min="4" max="4" width="14.125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.25" style="2" customWidth="1"/>
-    <col min="6" max="6" width="20.875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="12.2166666666667" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.85833333333333" style="9" customWidth="1"/>
-    <col min="9" max="9" width="19.1333333333333" style="9" customWidth="1"/>
-    <col min="10" max="10" width="29.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14.125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.2166666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.85833333333333" style="11" customWidth="1"/>
+    <col min="8" max="9" width="19.1333333333333" style="11" customWidth="1"/>
+    <col min="10" max="10" width="35.875" style="12" customWidth="1"/>
     <col min="11" max="11" width="10.375" style="2"/>
-    <col min="12" max="12" width="14.5583333333333" style="10" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="7"/>
+    <col min="12" max="12" width="14.5583333333333" style="13" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="14"/>
+      <c r="F1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="25" t="s">
+      <c r="L1" s="35" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4798,31 +4911,31 @@
       <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="12" t="s">
         <v>13</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="10"/>
+      <c r="L2" s="13"/>
     </row>
     <row r="3" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A3" s="2" t="s">
@@ -4831,13 +4944,13 @@
       <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="2" t="s">
@@ -4846,90 +4959,90 @@
       <c r="H3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="12" t="s">
         <v>21</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="10"/>
-    </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C4" s="8"/>
-      <c r="L4" s="10"/>
+      <c r="L3" s="13"/>
+    </row>
+    <row r="4" s="2" customFormat="1" customHeight="1" spans="10:12">
+      <c r="J4" s="12"/>
+      <c r="L4" s="13"/>
     </row>
     <row r="5" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A5" s="2">
-        <f>(B5)*10000+D5+G5*100+E5*100000</f>
+        <f>(B5)*10000+C5+F5*100+D5*100000</f>
         <v>1001100211</v>
       </c>
       <c r="B5" s="2">
         <v>100100</v>
       </c>
-      <c r="C5" s="8">
-        <v>4</v>
+      <c r="C5" s="2">
+        <v>11</v>
       </c>
       <c r="D5" s="2">
-        <v>11</v>
-      </c>
-      <c r="E5" s="2">
         <v>1</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>22</v>
+      </c>
+      <c r="F5" s="2">
+        <v>2</v>
       </c>
       <c r="G5" s="2">
         <v>2</v>
       </c>
-      <c r="H5" s="2">
-        <v>2</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K5" s="2">
         <v>0</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="L5" s="13" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A6" s="2">
-        <f t="shared" ref="A6:A42" si="0">(B6)*10000+D6+G6*100+E6*100000</f>
+        <f t="shared" ref="A6:A42" si="0">(B6)*10000+C6+F6*100+D6*100000</f>
         <v>1001100301</v>
       </c>
       <c r="B6" s="2">
         <v>100100</v>
       </c>
-      <c r="C6" s="8">
-        <v>4</v>
+      <c r="C6" s="2">
+        <v>1</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="F6" s="2">
+        <v>3</v>
+      </c>
       <c r="G6" s="2">
-        <v>3</v>
-      </c>
-      <c r="H6" s="2">
         <v>5</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K6" s="2">
         <v>0</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="L6" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -4941,31 +5054,31 @@
       <c r="B7" s="2">
         <v>100100</v>
       </c>
-      <c r="C7" s="8">
-        <v>4</v>
+      <c r="C7" s="2">
+        <v>2</v>
       </c>
       <c r="D7" s="2">
-        <v>2</v>
-      </c>
-      <c r="E7" s="2">
         <v>1</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="F7" s="2">
+        <v>3</v>
+      </c>
       <c r="G7" s="2">
-        <v>3</v>
-      </c>
-      <c r="H7" s="2">
         <v>5</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K7" s="2">
         <v>0</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="L7" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -4977,31 +5090,31 @@
       <c r="B8" s="2">
         <v>100100</v>
       </c>
-      <c r="C8" s="8">
-        <v>4</v>
+      <c r="C8" s="2">
+        <v>3</v>
       </c>
       <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="2">
         <v>3</v>
       </c>
-      <c r="E8" s="2">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="G8" s="2">
-        <v>3</v>
-      </c>
-      <c r="H8" s="2">
         <v>5</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K8" s="2">
         <v>0</v>
       </c>
-      <c r="L8" s="10" t="s">
+      <c r="L8" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5013,31 +5126,31 @@
       <c r="B9" s="2">
         <v>100100</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="2">
         <v>4</v>
       </c>
       <c r="D9" s="2">
-        <v>4</v>
-      </c>
-      <c r="E9" s="2">
         <v>1</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="F9" s="2">
+        <v>3</v>
+      </c>
       <c r="G9" s="2">
-        <v>3</v>
-      </c>
-      <c r="H9" s="2">
         <v>5</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K9" s="2">
         <v>0</v>
       </c>
-      <c r="L9" s="10" t="s">
+      <c r="L9" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5049,31 +5162,31 @@
       <c r="B10" s="2">
         <v>100100</v>
       </c>
-      <c r="C10" s="8">
-        <v>4</v>
+      <c r="C10" s="2">
+        <v>5</v>
       </c>
       <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="2">
+        <v>3</v>
+      </c>
+      <c r="G10" s="2">
         <v>5</v>
       </c>
-      <c r="E10" s="2">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="2">
-        <v>3</v>
-      </c>
-      <c r="H10" s="2">
-        <v>5</v>
-      </c>
-      <c r="J10" s="2" t="s">
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K10" s="2">
         <v>0</v>
       </c>
-      <c r="L10" s="10" t="s">
+      <c r="L10" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5085,31 +5198,31 @@
       <c r="B11" s="2">
         <v>100100</v>
       </c>
-      <c r="C11" s="8">
-        <v>4</v>
+      <c r="C11" s="2">
+        <v>6</v>
       </c>
       <c r="D11" s="2">
-        <v>6</v>
-      </c>
-      <c r="E11" s="2">
         <v>1</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="F11" s="2">
+        <v>3</v>
+      </c>
       <c r="G11" s="2">
-        <v>3</v>
-      </c>
-      <c r="H11" s="2">
         <v>5</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K11" s="2">
         <v>0</v>
       </c>
-      <c r="L11" s="10" t="s">
+      <c r="L11" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5121,31 +5234,31 @@
       <c r="B12" s="2">
         <v>100100</v>
       </c>
-      <c r="C12" s="8">
-        <v>4</v>
+      <c r="C12" s="2">
+        <v>7</v>
       </c>
       <c r="D12" s="2">
-        <v>7</v>
-      </c>
-      <c r="E12" s="2">
         <v>1</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="F12" s="2">
+        <v>3</v>
+      </c>
       <c r="G12" s="2">
-        <v>3</v>
-      </c>
-      <c r="H12" s="2">
         <v>10</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K12" s="2">
         <v>0</v>
       </c>
-      <c r="L12" s="10" t="s">
+      <c r="L12" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5157,31 +5270,31 @@
       <c r="B13" s="2">
         <v>100100</v>
       </c>
-      <c r="C13" s="8">
-        <v>4</v>
+      <c r="C13" s="2">
+        <v>8</v>
       </c>
       <c r="D13" s="2">
-        <v>8</v>
-      </c>
-      <c r="E13" s="2">
         <v>1</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="F13" s="2">
+        <v>3</v>
+      </c>
       <c r="G13" s="2">
-        <v>3</v>
-      </c>
-      <c r="H13" s="2">
         <v>10</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K13" s="2">
         <v>0</v>
       </c>
-      <c r="L13" s="10" t="s">
+      <c r="L13" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5193,31 +5306,31 @@
       <c r="B14" s="2">
         <v>100100</v>
       </c>
-      <c r="C14" s="8">
-        <v>4</v>
+      <c r="C14" s="2">
+        <v>9</v>
       </c>
       <c r="D14" s="2">
-        <v>9</v>
-      </c>
-      <c r="E14" s="2">
         <v>1</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="F14" s="2">
+        <v>3</v>
+      </c>
       <c r="G14" s="2">
-        <v>3</v>
-      </c>
-      <c r="H14" s="2">
         <v>15</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K14" s="2">
         <v>0</v>
       </c>
-      <c r="L14" s="10" t="s">
+      <c r="L14" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5229,31 +5342,31 @@
       <c r="B15" s="2">
         <v>100100</v>
       </c>
-      <c r="C15" s="8">
-        <v>4</v>
+      <c r="C15" s="2">
+        <v>10</v>
       </c>
       <c r="D15" s="2">
-        <v>10</v>
-      </c>
-      <c r="E15" s="2">
         <v>1</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="F15" s="2">
+        <v>3</v>
+      </c>
       <c r="G15" s="2">
-        <v>3</v>
-      </c>
-      <c r="H15" s="2">
         <v>15</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K15" s="2">
         <v>0</v>
       </c>
-      <c r="L15" s="10" t="s">
+      <c r="L15" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5265,31 +5378,31 @@
       <c r="B16" s="2">
         <v>100100</v>
       </c>
-      <c r="C16" s="8">
-        <v>4</v>
+      <c r="C16" s="2">
+        <v>11</v>
       </c>
       <c r="D16" s="2">
-        <v>11</v>
-      </c>
-      <c r="E16" s="2">
         <v>1</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="F16" s="2">
+        <v>3</v>
+      </c>
       <c r="G16" s="2">
-        <v>3</v>
-      </c>
-      <c r="H16" s="2">
         <v>20</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K16" s="2">
         <v>0</v>
       </c>
-      <c r="L16" s="10" t="s">
+      <c r="L16" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5301,31 +5414,31 @@
       <c r="B17" s="2">
         <v>100100</v>
       </c>
-      <c r="C17" s="8">
-        <v>4</v>
+      <c r="C17" s="2">
+        <v>1</v>
       </c>
       <c r="D17" s="2">
         <v>1</v>
       </c>
-      <c r="E17" s="2">
-        <v>1</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="F17" s="2">
+        <v>4</v>
+      </c>
       <c r="G17" s="2">
-        <v>4</v>
-      </c>
-      <c r="H17" s="2">
         <v>15</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K17" s="2">
         <v>0</v>
       </c>
-      <c r="L17" s="10" t="s">
+      <c r="L17" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5337,31 +5450,31 @@
       <c r="B18" s="2">
         <v>100100</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="2">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="2">
         <v>4</v>
       </c>
-      <c r="D18" s="2">
-        <v>2</v>
-      </c>
-      <c r="E18" s="2">
-        <v>1</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="G18" s="2">
-        <v>4</v>
-      </c>
-      <c r="H18" s="2">
         <v>15</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K18" s="2">
         <v>0</v>
       </c>
-      <c r="L18" s="10" t="s">
+      <c r="L18" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5373,31 +5486,31 @@
       <c r="B19" s="2">
         <v>100100</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="2">
+        <v>3</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="2">
         <v>4</v>
       </c>
-      <c r="D19" s="2">
-        <v>3</v>
-      </c>
-      <c r="E19" s="2">
-        <v>1</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="G19" s="2">
-        <v>4</v>
-      </c>
-      <c r="H19" s="2">
         <v>15</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K19" s="2">
         <v>0</v>
       </c>
-      <c r="L19" s="10" t="s">
+      <c r="L19" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5409,31 +5522,31 @@
       <c r="B20" s="2">
         <v>100100</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="2">
         <v>4</v>
       </c>
       <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="2">
         <v>4</v>
       </c>
-      <c r="E20" s="2">
-        <v>1</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="G20" s="2">
-        <v>4</v>
-      </c>
-      <c r="H20" s="2">
         <v>15</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K20" s="2">
         <v>0</v>
       </c>
-      <c r="L20" s="10" t="s">
+      <c r="L20" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5445,31 +5558,31 @@
       <c r="B21" s="2">
         <v>100100</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="2">
+        <v>5</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="2">
         <v>4</v>
       </c>
-      <c r="D21" s="2">
-        <v>5</v>
-      </c>
-      <c r="E21" s="2">
-        <v>1</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="G21" s="2">
-        <v>4</v>
-      </c>
-      <c r="H21" s="2">
         <v>15</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K21" s="2">
         <v>0</v>
       </c>
-      <c r="L21" s="10" t="s">
+      <c r="L21" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5481,31 +5594,31 @@
       <c r="B22" s="2">
         <v>100100</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="2">
+        <v>6</v>
+      </c>
+      <c r="D22" s="2">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="2">
         <v>4</v>
       </c>
-      <c r="D22" s="2">
-        <v>6</v>
-      </c>
-      <c r="E22" s="2">
-        <v>1</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="G22" s="2">
-        <v>4</v>
-      </c>
-      <c r="H22" s="2">
         <v>15</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K22" s="2">
         <v>0</v>
       </c>
-      <c r="L22" s="10" t="s">
+      <c r="L22" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5517,31 +5630,31 @@
       <c r="B23" s="2">
         <v>100100</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="2">
+        <v>7</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="2">
         <v>4</v>
       </c>
-      <c r="D23" s="2">
-        <v>7</v>
-      </c>
-      <c r="E23" s="2">
-        <v>1</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="G23" s="2">
-        <v>4</v>
-      </c>
-      <c r="H23" s="2">
         <v>25</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K23" s="2">
         <v>0</v>
       </c>
-      <c r="L23" s="10" t="s">
+      <c r="L23" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5553,31 +5666,31 @@
       <c r="B24" s="2">
         <v>100100</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="2">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="2">
         <v>4</v>
       </c>
-      <c r="D24" s="2">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2">
-        <v>1</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="G24" s="2">
-        <v>4</v>
-      </c>
-      <c r="H24" s="2">
         <v>25</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K24" s="2">
         <v>0</v>
       </c>
-      <c r="L24" s="10" t="s">
+      <c r="L24" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5589,31 +5702,31 @@
       <c r="B25" s="2">
         <v>100100</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="2">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="2">
         <v>4</v>
       </c>
-      <c r="D25" s="2">
-        <v>9</v>
-      </c>
-      <c r="E25" s="2">
-        <v>1</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="G25" s="2">
-        <v>4</v>
-      </c>
-      <c r="H25" s="2">
         <v>30</v>
       </c>
-      <c r="J25" s="2" t="s">
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K25" s="2">
         <v>0</v>
       </c>
-      <c r="L25" s="10" t="s">
+      <c r="L25" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5625,31 +5738,31 @@
       <c r="B26" s="2">
         <v>100100</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="2">
+        <v>10</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="2">
         <v>4</v>
       </c>
-      <c r="D26" s="2">
-        <v>10</v>
-      </c>
-      <c r="E26" s="2">
-        <v>1</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="G26" s="2">
-        <v>4</v>
-      </c>
-      <c r="H26" s="2">
         <v>30</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K26" s="2">
         <v>0</v>
       </c>
-      <c r="L26" s="10" t="s">
+      <c r="L26" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5661,31 +5774,31 @@
       <c r="B27" s="2">
         <v>100100</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="2">
+        <v>11</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="2">
         <v>4</v>
       </c>
-      <c r="D27" s="2">
-        <v>11</v>
-      </c>
-      <c r="E27" s="2">
-        <v>1</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="G27" s="2">
-        <v>4</v>
-      </c>
-      <c r="H27" s="2">
         <v>50</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K27" s="2">
         <v>0</v>
       </c>
-      <c r="L27" s="10" t="s">
+      <c r="L27" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5697,31 +5810,31 @@
       <c r="B28" s="2">
         <v>100100</v>
       </c>
-      <c r="C28" s="8">
-        <v>4</v>
+      <c r="C28" s="2">
+        <v>1</v>
       </c>
       <c r="D28" s="2">
         <v>1</v>
       </c>
-      <c r="E28" s="2">
-        <v>1</v>
-      </c>
-      <c r="F28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="F28" s="2">
+        <v>5</v>
+      </c>
       <c r="G28" s="2">
-        <v>5</v>
-      </c>
-      <c r="H28" s="2">
         <v>50</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K28" s="2">
         <v>0</v>
       </c>
-      <c r="L28" s="10" t="s">
+      <c r="L28" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5733,31 +5846,31 @@
       <c r="B29" s="2">
         <v>100100</v>
       </c>
-      <c r="C29" s="8">
-        <v>4</v>
+      <c r="C29" s="2">
+        <v>2</v>
       </c>
       <c r="D29" s="2">
-        <v>2</v>
-      </c>
-      <c r="E29" s="2">
         <v>1</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="F29" s="2">
+        <v>5</v>
+      </c>
       <c r="G29" s="2">
-        <v>5</v>
-      </c>
-      <c r="H29" s="2">
         <v>50</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K29" s="2">
         <v>0</v>
       </c>
-      <c r="L29" s="10" t="s">
+      <c r="L29" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5769,31 +5882,31 @@
       <c r="B30" s="2">
         <v>100100</v>
       </c>
-      <c r="C30" s="8">
-        <v>4</v>
+      <c r="C30" s="2">
+        <v>3</v>
       </c>
       <c r="D30" s="2">
-        <v>3</v>
-      </c>
-      <c r="E30" s="2">
         <v>1</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="F30" s="2">
+        <v>5</v>
+      </c>
       <c r="G30" s="2">
-        <v>5</v>
-      </c>
-      <c r="H30" s="2">
         <v>50</v>
       </c>
-      <c r="J30" s="2" t="s">
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+      <c r="J30" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K30" s="2">
         <v>0</v>
       </c>
-      <c r="L30" s="10" t="s">
+      <c r="L30" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5805,31 +5918,31 @@
       <c r="B31" s="2">
         <v>100100</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="2">
         <v>4</v>
       </c>
       <c r="D31" s="2">
-        <v>4</v>
-      </c>
-      <c r="E31" s="2">
         <v>1</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="F31" s="2">
+        <v>5</v>
+      </c>
       <c r="G31" s="2">
-        <v>5</v>
-      </c>
-      <c r="H31" s="2">
         <v>50</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+      <c r="J31" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K31" s="2">
         <v>0</v>
       </c>
-      <c r="L31" s="10" t="s">
+      <c r="L31" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5841,31 +5954,31 @@
       <c r="B32" s="2">
         <v>100100</v>
       </c>
-      <c r="C32" s="8">
-        <v>4</v>
+      <c r="C32" s="2">
+        <v>5</v>
       </c>
       <c r="D32" s="2">
+        <v>1</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="2">
         <v>5</v>
       </c>
-      <c r="E32" s="2">
-        <v>1</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="G32" s="2">
-        <v>5</v>
-      </c>
-      <c r="H32" s="2">
         <v>50</v>
       </c>
-      <c r="J32" s="2" t="s">
+      <c r="I32" s="2">
+        <v>0</v>
+      </c>
+      <c r="J32" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K32" s="2">
         <v>0</v>
       </c>
-      <c r="L32" s="10" t="s">
+      <c r="L32" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5877,31 +5990,31 @@
       <c r="B33" s="2">
         <v>100100</v>
       </c>
-      <c r="C33" s="8">
-        <v>4</v>
+      <c r="C33" s="2">
+        <v>6</v>
       </c>
       <c r="D33" s="2">
-        <v>6</v>
-      </c>
-      <c r="E33" s="2">
         <v>1</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="F33" s="2">
+        <v>5</v>
+      </c>
       <c r="G33" s="2">
-        <v>5</v>
-      </c>
-      <c r="H33" s="2">
         <v>50</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="I33" s="2">
+        <v>0</v>
+      </c>
+      <c r="J33" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K33" s="2">
         <v>0</v>
       </c>
-      <c r="L33" s="10" t="s">
+      <c r="L33" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5913,31 +6026,31 @@
       <c r="B34" s="2">
         <v>100100</v>
       </c>
-      <c r="C34" s="8">
-        <v>4</v>
+      <c r="C34" s="2">
+        <v>7</v>
       </c>
       <c r="D34" s="2">
-        <v>7</v>
-      </c>
-      <c r="E34" s="2">
         <v>1</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="F34" s="2">
+        <v>5</v>
+      </c>
       <c r="G34" s="2">
-        <v>5</v>
-      </c>
-      <c r="H34" s="2">
         <v>100</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="I34" s="2">
+        <v>0</v>
+      </c>
+      <c r="J34" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K34" s="2">
         <v>0</v>
       </c>
-      <c r="L34" s="10" t="s">
+      <c r="L34" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5949,31 +6062,31 @@
       <c r="B35" s="2">
         <v>100100</v>
       </c>
-      <c r="C35" s="8">
-        <v>4</v>
+      <c r="C35" s="2">
+        <v>8</v>
       </c>
       <c r="D35" s="2">
-        <v>8</v>
-      </c>
-      <c r="E35" s="2">
         <v>1</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="F35" s="2">
+        <v>5</v>
+      </c>
       <c r="G35" s="2">
-        <v>5</v>
-      </c>
-      <c r="H35" s="2">
         <v>100</v>
       </c>
-      <c r="J35" s="2" t="s">
+      <c r="I35" s="2">
+        <v>0</v>
+      </c>
+      <c r="J35" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K35" s="2">
         <v>0</v>
       </c>
-      <c r="L35" s="10" t="s">
+      <c r="L35" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5985,31 +6098,31 @@
       <c r="B36" s="2">
         <v>100100</v>
       </c>
-      <c r="C36" s="8">
-        <v>4</v>
+      <c r="C36" s="2">
+        <v>9</v>
       </c>
       <c r="D36" s="2">
-        <v>9</v>
-      </c>
-      <c r="E36" s="2">
         <v>1</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="F36" s="2">
+        <v>5</v>
+      </c>
       <c r="G36" s="2">
-        <v>5</v>
-      </c>
-      <c r="H36" s="2">
         <v>200</v>
       </c>
-      <c r="J36" s="2" t="s">
+      <c r="I36" s="2">
+        <v>0</v>
+      </c>
+      <c r="J36" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K36" s="2">
         <v>0</v>
       </c>
-      <c r="L36" s="10" t="s">
+      <c r="L36" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -6021,31 +6134,31 @@
       <c r="B37" s="2">
         <v>100100</v>
       </c>
-      <c r="C37" s="8">
-        <v>4</v>
+      <c r="C37" s="2">
+        <v>10</v>
       </c>
       <c r="D37" s="2">
-        <v>10</v>
-      </c>
-      <c r="E37" s="2">
         <v>1</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="E37" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="F37" s="2">
+        <v>5</v>
+      </c>
       <c r="G37" s="2">
-        <v>5</v>
-      </c>
-      <c r="H37" s="2">
         <v>200</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="I37" s="2">
+        <v>0</v>
+      </c>
+      <c r="J37" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K37" s="2">
         <v>0</v>
       </c>
-      <c r="L37" s="10" t="s">
+      <c r="L37" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -6057,31 +6170,31 @@
       <c r="B38" s="2">
         <v>100100</v>
       </c>
-      <c r="C38" s="8">
-        <v>4</v>
+      <c r="C38" s="2">
+        <v>11</v>
       </c>
       <c r="D38" s="2">
-        <v>11</v>
-      </c>
-      <c r="E38" s="2">
         <v>1</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="F38" s="2">
+        <v>5</v>
+      </c>
       <c r="G38" s="2">
-        <v>5</v>
-      </c>
-      <c r="H38" s="2">
         <v>300</v>
       </c>
-      <c r="J38" s="2" t="s">
+      <c r="I38" s="2">
+        <v>0</v>
+      </c>
+      <c r="J38" s="12" t="s">
         <v>23</v>
       </c>
       <c r="K38" s="2">
         <v>0</v>
       </c>
-      <c r="L38" s="10" t="s">
+      <c r="L38" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -6090,35 +6203,35 @@
         <f t="shared" si="0"/>
         <v>1001201619</v>
       </c>
-      <c r="B39" s="14">
+      <c r="B39" s="16">
         <v>100100</v>
       </c>
-      <c r="C39" s="8">
-        <v>4</v>
-      </c>
-      <c r="D39" s="14">
+      <c r="C39" s="16">
         <v>19</v>
       </c>
-      <c r="E39" s="14">
+      <c r="D39" s="16">
         <v>2</v>
       </c>
-      <c r="F39" s="14" t="s">
+      <c r="E39" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="G39" s="14">
+      <c r="F39" s="16">
         <v>16</v>
       </c>
-      <c r="H39" s="14">
-        <v>0</v>
-      </c>
-      <c r="I39" s="26">
+      <c r="G39" s="16">
+        <v>0</v>
+      </c>
+      <c r="H39" s="17">
         <v>30010001</v>
       </c>
-      <c r="J39" s="14"/>
-      <c r="K39" s="27">
+      <c r="I39" s="2">
+        <v>0</v>
+      </c>
+      <c r="J39" s="37"/>
+      <c r="K39" s="38">
         <v>100100101</v>
       </c>
-      <c r="L39" s="28" t="s">
+      <c r="L39" s="37" t="s">
         <v>26</v>
       </c>
     </row>
@@ -6127,35 +6240,35 @@
         <f t="shared" si="0"/>
         <v>1001201620</v>
       </c>
-      <c r="B40" s="14">
+      <c r="B40" s="16">
         <v>100100</v>
       </c>
-      <c r="C40" s="8">
-        <v>4</v>
-      </c>
-      <c r="D40" s="14">
+      <c r="C40" s="16">
         <v>20</v>
       </c>
-      <c r="E40" s="14">
+      <c r="D40" s="16">
         <v>2</v>
       </c>
-      <c r="F40" s="14" t="s">
+      <c r="E40" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="G40" s="14">
+      <c r="F40" s="16">
         <v>16</v>
       </c>
-      <c r="H40" s="14">
-        <v>0</v>
-      </c>
-      <c r="I40" s="26">
+      <c r="G40" s="16">
+        <v>0</v>
+      </c>
+      <c r="H40" s="17">
         <v>30010002</v>
       </c>
-      <c r="J40" s="14"/>
-      <c r="K40" s="27">
+      <c r="I40" s="2">
+        <v>0</v>
+      </c>
+      <c r="J40" s="37"/>
+      <c r="K40" s="38">
         <v>100100102</v>
       </c>
-      <c r="L40" s="28" t="s">
+      <c r="L40" s="37" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6164,35 +6277,35 @@
         <f t="shared" si="0"/>
         <v>1001201621</v>
       </c>
-      <c r="B41" s="14">
+      <c r="B41" s="16">
         <v>100100</v>
       </c>
-      <c r="C41" s="8">
-        <v>4</v>
-      </c>
-      <c r="D41" s="14">
+      <c r="C41" s="16">
         <v>21</v>
       </c>
-      <c r="E41" s="14">
+      <c r="D41" s="16">
         <v>2</v>
       </c>
-      <c r="F41" s="14" t="s">
+      <c r="E41" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="G41" s="14">
+      <c r="F41" s="16">
         <v>16</v>
       </c>
-      <c r="H41" s="15">
-        <v>0</v>
-      </c>
-      <c r="I41" s="26">
+      <c r="G41" s="18">
+        <v>0</v>
+      </c>
+      <c r="H41" s="17">
         <v>30010003</v>
       </c>
-      <c r="J41" s="14"/>
-      <c r="K41" s="27">
+      <c r="I41" s="2">
+        <v>0</v>
+      </c>
+      <c r="J41" s="37"/>
+      <c r="K41" s="38">
         <v>100100103</v>
       </c>
-      <c r="L41" s="28" t="s">
+      <c r="L41" s="37" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6201,70 +6314,70 @@
         <f t="shared" si="0"/>
         <v>1001201622</v>
       </c>
-      <c r="B42" s="14">
+      <c r="B42" s="16">
         <v>100100</v>
       </c>
-      <c r="C42" s="8">
-        <v>4</v>
-      </c>
-      <c r="D42" s="14">
+      <c r="C42" s="16">
         <v>22</v>
       </c>
-      <c r="E42" s="14">
+      <c r="D42" s="16">
         <v>2</v>
       </c>
-      <c r="F42" s="14" t="s">
+      <c r="E42" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="G42" s="14">
+      <c r="F42" s="16">
         <v>16</v>
       </c>
-      <c r="H42" s="15">
-        <v>0</v>
-      </c>
-      <c r="I42" s="26">
+      <c r="G42" s="18">
+        <v>0</v>
+      </c>
+      <c r="H42" s="17">
         <v>30010004</v>
       </c>
-      <c r="J42" s="14"/>
-      <c r="K42" s="27">
+      <c r="I42" s="2">
+        <v>0</v>
+      </c>
+      <c r="J42" s="37"/>
+      <c r="K42" s="38">
         <v>100100104</v>
       </c>
-      <c r="L42" s="28" t="s">
+      <c r="L42" s="37" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:12">
       <c r="A43" s="2">
-        <f t="shared" ref="A43:A48" si="1">(B43)*10000+D43+G43*100+E43*100000</f>
+        <f t="shared" ref="A43:A48" si="1">(B43)*10000+C43+F43*100+D43*100000</f>
         <v>1001201628</v>
       </c>
-      <c r="B43" s="16">
+      <c r="B43" s="19">
         <v>100100</v>
       </c>
-      <c r="C43" s="8">
-        <v>4</v>
-      </c>
-      <c r="D43" s="16">
+      <c r="C43" s="19">
         <v>28</v>
       </c>
-      <c r="E43" s="16">
+      <c r="D43" s="19">
         <v>2</v>
       </c>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16">
+      <c r="E43" s="19"/>
+      <c r="F43" s="19">
         <v>16</v>
       </c>
-      <c r="H43" s="17">
-        <v>0</v>
-      </c>
-      <c r="I43" s="29">
+      <c r="G43" s="20">
+        <v>0</v>
+      </c>
+      <c r="H43" s="21">
         <v>30010005</v>
       </c>
-      <c r="J43" s="16"/>
-      <c r="K43" s="16">
-        <v>0</v>
-      </c>
-      <c r="L43" s="30" t="s">
+      <c r="I43" s="2">
+        <v>0</v>
+      </c>
+      <c r="J43" s="39"/>
+      <c r="K43" s="19">
+        <v>0</v>
+      </c>
+      <c r="L43" s="39" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6273,33 +6386,33 @@
         <f t="shared" si="1"/>
         <v>1001201528</v>
       </c>
-      <c r="B44" s="18">
+      <c r="B44" s="22">
         <v>100100</v>
       </c>
-      <c r="C44" s="8">
-        <v>4</v>
-      </c>
-      <c r="D44" s="18">
+      <c r="C44" s="22">
         <v>28</v>
       </c>
-      <c r="E44" s="18">
+      <c r="D44" s="22">
         <v>2</v>
       </c>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18">
+      <c r="E44" s="22"/>
+      <c r="F44" s="22">
         <v>15</v>
       </c>
-      <c r="H44" s="19">
-        <v>0</v>
-      </c>
-      <c r="I44" s="31">
+      <c r="G44" s="23">
+        <v>0</v>
+      </c>
+      <c r="H44" s="24">
         <v>30010006</v>
       </c>
-      <c r="J44" s="18"/>
-      <c r="K44" s="18">
-        <v>0</v>
-      </c>
-      <c r="L44" s="32" t="s">
+      <c r="I44" s="2">
+        <v>0</v>
+      </c>
+      <c r="J44" s="40"/>
+      <c r="K44" s="22">
+        <v>0</v>
+      </c>
+      <c r="L44" s="40" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6308,31 +6421,31 @@
         <f t="shared" si="1"/>
         <v>1001400317</v>
       </c>
-      <c r="B45" s="20">
+      <c r="B45" s="25">
         <v>100100</v>
       </c>
-      <c r="C45" s="8">
-        <v>1</v>
-      </c>
-      <c r="D45" s="20">
+      <c r="C45" s="25">
         <v>17</v>
       </c>
-      <c r="E45" s="20">
+      <c r="D45" s="25">
         <v>4</v>
       </c>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20">
+      <c r="E45" s="25"/>
+      <c r="F45" s="25">
         <v>3</v>
       </c>
-      <c r="H45" s="21">
-        <v>0</v>
-      </c>
-      <c r="I45" s="33"/>
-      <c r="J45" s="20"/>
-      <c r="K45" s="20">
-        <v>0</v>
-      </c>
-      <c r="L45" s="34" t="s">
+      <c r="G45" s="26">
+        <v>0</v>
+      </c>
+      <c r="H45" s="27"/>
+      <c r="I45" s="2">
+        <v>0</v>
+      </c>
+      <c r="J45" s="41"/>
+      <c r="K45" s="25">
+        <v>0</v>
+      </c>
+      <c r="L45" s="41" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6341,31 +6454,31 @@
         <f t="shared" si="1"/>
         <v>1001400417</v>
       </c>
-      <c r="B46" s="22">
+      <c r="B46" s="28">
         <v>100100</v>
       </c>
-      <c r="C46" s="8">
-        <v>1</v>
-      </c>
-      <c r="D46" s="22">
+      <c r="C46" s="28">
         <v>17</v>
       </c>
-      <c r="E46" s="22">
+      <c r="D46" s="28">
         <v>4</v>
       </c>
-      <c r="F46" s="22"/>
-      <c r="G46" s="22">
+      <c r="E46" s="28"/>
+      <c r="F46" s="28">
         <v>4</v>
       </c>
-      <c r="H46" s="23">
-        <v>0</v>
-      </c>
-      <c r="I46" s="35"/>
-      <c r="J46" s="22"/>
-      <c r="K46" s="22">
-        <v>0</v>
-      </c>
-      <c r="L46" s="36" t="s">
+      <c r="G46" s="29">
+        <v>0</v>
+      </c>
+      <c r="H46" s="30"/>
+      <c r="I46" s="2">
+        <v>0</v>
+      </c>
+      <c r="J46" s="42"/>
+      <c r="K46" s="28">
+        <v>0</v>
+      </c>
+      <c r="L46" s="42" t="s">
         <v>33</v>
       </c>
     </row>
@@ -6374,31 +6487,31 @@
         <f t="shared" si="1"/>
         <v>1001400517</v>
       </c>
-      <c r="B47" s="22">
+      <c r="B47" s="28">
         <v>100100</v>
       </c>
-      <c r="C47" s="8">
-        <v>1</v>
-      </c>
-      <c r="D47" s="22">
+      <c r="C47" s="28">
         <v>17</v>
       </c>
-      <c r="E47" s="22">
+      <c r="D47" s="28">
         <v>4</v>
       </c>
-      <c r="F47" s="22"/>
-      <c r="G47" s="22">
+      <c r="E47" s="28"/>
+      <c r="F47" s="28">
         <v>5</v>
       </c>
-      <c r="H47" s="23">
-        <v>0</v>
-      </c>
-      <c r="I47" s="35"/>
-      <c r="J47" s="22"/>
-      <c r="K47" s="22">
-        <v>0</v>
-      </c>
-      <c r="L47" s="36" t="s">
+      <c r="G47" s="29">
+        <v>0</v>
+      </c>
+      <c r="H47" s="30"/>
+      <c r="I47" s="2">
+        <v>0</v>
+      </c>
+      <c r="J47" s="42"/>
+      <c r="K47" s="28">
+        <v>0</v>
+      </c>
+      <c r="L47" s="42" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6407,1219 +6520,3123 @@
         <f t="shared" si="1"/>
         <v>1001400130</v>
       </c>
-      <c r="B48" s="22">
+      <c r="B48" s="28">
         <v>100100</v>
       </c>
-      <c r="C48" s="8">
+      <c r="C48" s="28">
+        <v>30</v>
+      </c>
+      <c r="D48" s="28">
+        <v>4</v>
+      </c>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28">
         <v>1</v>
       </c>
-      <c r="D48" s="22">
-        <v>30</v>
-      </c>
-      <c r="E48" s="22">
-        <v>4</v>
-      </c>
-      <c r="F48" s="22"/>
-      <c r="G48" s="22">
-        <v>1</v>
-      </c>
-      <c r="H48" s="23">
-        <v>0</v>
-      </c>
-      <c r="I48" s="35">
+      <c r="G48" s="29">
+        <v>0</v>
+      </c>
+      <c r="H48" s="30">
         <v>30010007</v>
       </c>
-      <c r="J48" s="22"/>
-      <c r="K48" s="22">
-        <v>0</v>
-      </c>
-      <c r="L48" s="36" t="s">
+      <c r="I48" s="2">
+        <v>0</v>
+      </c>
+      <c r="J48" s="42"/>
+      <c r="K48" s="28">
+        <v>0</v>
+      </c>
+      <c r="L48" s="42" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="49" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A49" s="2">
-        <v>1007300301</v>
-      </c>
-      <c r="B49" s="14">
-        <v>100700</v>
-      </c>
-      <c r="C49" s="8">
-        <v>4</v>
-      </c>
-      <c r="D49" s="24" t="s">
+        <f t="shared" ref="A49:A60" si="2">(B49)*10000+C49+F49*100+D49*100000</f>
+        <v>1003100301</v>
+      </c>
+      <c r="B49" s="3">
+        <v>100300</v>
+      </c>
+      <c r="C49" s="31">
+        <v>1</v>
+      </c>
+      <c r="D49" s="3">
+        <v>1</v>
+      </c>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3">
+        <v>3</v>
+      </c>
+      <c r="G49" s="32">
+        <v>1</v>
+      </c>
+      <c r="H49" s="33"/>
+      <c r="I49" s="2">
+        <v>1</v>
+      </c>
+      <c r="J49" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="E49" s="14">
-        <v>3</v>
-      </c>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14">
-        <v>3</v>
-      </c>
-      <c r="H49" s="15">
-        <v>2</v>
-      </c>
-      <c r="I49" s="15"/>
-      <c r="J49" s="14"/>
-      <c r="K49" s="14"/>
-      <c r="L49" s="10"/>
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="13"/>
     </row>
     <row r="50" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A50" s="2">
-        <v>1007300302</v>
-      </c>
-      <c r="B50" s="14">
-        <v>100700</v>
-      </c>
-      <c r="C50" s="8">
-        <v>4</v>
-      </c>
-      <c r="D50" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="E50" s="14">
+        <f t="shared" si="2"/>
+        <v>1003100302</v>
+      </c>
+      <c r="B50" s="3">
+        <v>100300</v>
+      </c>
+      <c r="C50" s="31">
+        <v>2</v>
+      </c>
+      <c r="D50" s="3">
+        <v>1</v>
+      </c>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3">
         <v>3</v>
       </c>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14">
-        <v>3</v>
-      </c>
-      <c r="H50" s="15">
+      <c r="G50" s="32">
         <v>2</v>
       </c>
-      <c r="I50" s="15"/>
-      <c r="J50" s="14"/>
-      <c r="K50" s="14"/>
-      <c r="L50" s="10"/>
+      <c r="H50" s="33"/>
+      <c r="I50" s="2">
+        <v>1</v>
+      </c>
+      <c r="J50" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="13"/>
     </row>
     <row r="51" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A51" s="2">
-        <v>1007300303</v>
-      </c>
-      <c r="B51" s="14">
-        <v>100700</v>
-      </c>
-      <c r="C51" s="8">
-        <v>4</v>
-      </c>
-      <c r="D51" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="E51" s="14">
+        <f t="shared" si="2"/>
+        <v>1003100303</v>
+      </c>
+      <c r="B51" s="3">
+        <v>100300</v>
+      </c>
+      <c r="C51" s="31">
         <v>3</v>
       </c>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14">
+      <c r="D51" s="3">
+        <v>1</v>
+      </c>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3">
         <v>3</v>
       </c>
-      <c r="H51" s="15">
-        <v>4</v>
-      </c>
-      <c r="I51" s="15"/>
-      <c r="J51" s="14"/>
-      <c r="K51" s="14"/>
-      <c r="L51" s="10"/>
+      <c r="G51" s="32">
+        <v>5</v>
+      </c>
+      <c r="H51" s="33"/>
+      <c r="I51" s="2">
+        <v>1</v>
+      </c>
+      <c r="J51" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="13"/>
     </row>
     <row r="52" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A52" s="2">
-        <v>1007300304</v>
-      </c>
-      <c r="B52" s="14">
-        <v>100700</v>
-      </c>
-      <c r="C52" s="8">
+        <f t="shared" si="2"/>
+        <v>1003100304</v>
+      </c>
+      <c r="B52" s="3">
+        <v>100300</v>
+      </c>
+      <c r="C52" s="31">
         <v>4</v>
       </c>
-      <c r="D52" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="E52" s="14">
+      <c r="D52" s="3">
+        <v>1</v>
+      </c>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3">
         <v>3</v>
       </c>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14">
-        <v>3</v>
-      </c>
-      <c r="H52" s="15">
-        <v>4</v>
-      </c>
-      <c r="I52" s="15"/>
-      <c r="J52" s="14"/>
-      <c r="K52" s="14"/>
-      <c r="L52" s="10"/>
+      <c r="G52" s="32">
+        <v>10</v>
+      </c>
+      <c r="H52" s="33"/>
+      <c r="I52" s="2">
+        <v>1</v>
+      </c>
+      <c r="J52" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="13"/>
     </row>
     <row r="53" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A53" s="2">
-        <v>1007300305</v>
-      </c>
-      <c r="B53" s="14">
-        <v>100700</v>
-      </c>
-      <c r="C53" s="8">
-        <v>4</v>
-      </c>
-      <c r="D53" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="E53" s="14">
+        <f t="shared" si="2"/>
+        <v>1003100305</v>
+      </c>
+      <c r="B53" s="3">
+        <v>100300</v>
+      </c>
+      <c r="C53" s="31">
+        <v>5</v>
+      </c>
+      <c r="D53" s="3">
+        <v>1</v>
+      </c>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3">
         <v>3</v>
       </c>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14">
-        <v>3</v>
-      </c>
-      <c r="H53" s="15">
-        <v>6</v>
-      </c>
-      <c r="I53" s="15"/>
-      <c r="J53" s="14"/>
-      <c r="K53" s="14"/>
-      <c r="L53" s="10"/>
+      <c r="G53" s="32">
+        <v>15</v>
+      </c>
+      <c r="H53" s="33"/>
+      <c r="I53" s="2">
+        <v>1</v>
+      </c>
+      <c r="J53" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="13"/>
     </row>
     <row r="54" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A54" s="2">
-        <v>1007300306</v>
-      </c>
-      <c r="B54" s="14">
-        <v>100700</v>
-      </c>
-      <c r="C54" s="8">
-        <v>4</v>
-      </c>
-      <c r="D54" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="E54" s="14">
-        <v>3</v>
-      </c>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14">
-        <v>3</v>
-      </c>
-      <c r="H54" s="15">
-        <v>8</v>
-      </c>
-      <c r="I54" s="15"/>
-      <c r="J54" s="14"/>
-      <c r="K54" s="14"/>
-      <c r="L54" s="10"/>
+        <f t="shared" si="2"/>
+        <v>1003600106</v>
+      </c>
+      <c r="B54" s="3">
+        <v>100300</v>
+      </c>
+      <c r="C54" s="3">
+        <v>6</v>
+      </c>
+      <c r="D54" s="3">
+        <v>6</v>
+      </c>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3">
+        <v>1</v>
+      </c>
+      <c r="G54" s="32">
+        <v>10</v>
+      </c>
+      <c r="H54" s="33"/>
+      <c r="I54" s="2">
+        <v>1</v>
+      </c>
+      <c r="J54" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="K54" s="3">
+        <v>0</v>
+      </c>
+      <c r="L54" s="13"/>
     </row>
     <row r="55" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A55" s="2">
-        <v>1007300307</v>
-      </c>
-      <c r="B55" s="14">
-        <v>100700</v>
-      </c>
-      <c r="C55" s="8">
-        <v>4</v>
-      </c>
-      <c r="D55" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="E55" s="14">
-        <v>3</v>
-      </c>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14">
-        <v>3</v>
-      </c>
-      <c r="H55" s="15">
-        <v>10</v>
-      </c>
-      <c r="I55" s="15"/>
-      <c r="J55" s="14"/>
-      <c r="K55" s="14"/>
-      <c r="L55" s="10"/>
+        <f t="shared" si="2"/>
+        <v>1003600206</v>
+      </c>
+      <c r="B55" s="3">
+        <v>100300</v>
+      </c>
+      <c r="C55" s="3">
+        <v>6</v>
+      </c>
+      <c r="D55" s="3">
+        <v>6</v>
+      </c>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3">
+        <v>2</v>
+      </c>
+      <c r="G55" s="32">
+        <v>20</v>
+      </c>
+      <c r="H55" s="33"/>
+      <c r="I55" s="2">
+        <v>1</v>
+      </c>
+      <c r="J55" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="K55" s="3">
+        <v>0</v>
+      </c>
+      <c r="L55" s="13"/>
     </row>
     <row r="56" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A56" s="2">
+        <f t="shared" si="2"/>
+        <v>1003600306</v>
+      </c>
+      <c r="B56" s="3">
+        <v>100300</v>
+      </c>
+      <c r="C56" s="3">
+        <v>6</v>
+      </c>
+      <c r="D56" s="3">
+        <v>6</v>
+      </c>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3">
+        <v>3</v>
+      </c>
+      <c r="G56" s="32">
+        <v>50</v>
+      </c>
+      <c r="H56" s="33"/>
+      <c r="I56" s="2">
+        <v>1</v>
+      </c>
+      <c r="J56" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="K56" s="3">
+        <v>0</v>
+      </c>
+      <c r="L56" s="13"/>
+    </row>
+    <row r="57" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A57" s="2">
+        <f t="shared" si="2"/>
+        <v>1003100107</v>
+      </c>
+      <c r="B57" s="3">
+        <v>100300</v>
+      </c>
+      <c r="C57" s="3">
+        <v>7</v>
+      </c>
+      <c r="D57" s="3">
+        <v>1</v>
+      </c>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3">
+        <v>1</v>
+      </c>
+      <c r="G57" s="32">
+        <v>0</v>
+      </c>
+      <c r="H57" s="33"/>
+      <c r="I57" s="2">
+        <v>0</v>
+      </c>
+      <c r="J57" s="13"/>
+      <c r="K57" s="3">
+        <v>100300101</v>
+      </c>
+      <c r="L57" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A58" s="2">
+        <f t="shared" si="2"/>
+        <v>1003100108</v>
+      </c>
+      <c r="B58" s="3">
+        <v>100300</v>
+      </c>
+      <c r="C58" s="3">
+        <v>8</v>
+      </c>
+      <c r="D58" s="3">
+        <v>1</v>
+      </c>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3">
+        <v>1</v>
+      </c>
+      <c r="G58" s="32">
+        <v>0</v>
+      </c>
+      <c r="H58" s="33"/>
+      <c r="I58" s="2">
+        <v>0</v>
+      </c>
+      <c r="J58" s="13"/>
+      <c r="K58" s="3">
+        <v>100300102</v>
+      </c>
+      <c r="L58" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="59" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A59" s="2">
+        <f t="shared" si="2"/>
+        <v>1003100109</v>
+      </c>
+      <c r="B59" s="3">
+        <v>100300</v>
+      </c>
+      <c r="C59" s="3">
+        <v>9</v>
+      </c>
+      <c r="D59" s="3">
+        <v>1</v>
+      </c>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3">
+        <v>1</v>
+      </c>
+      <c r="G59" s="32">
+        <v>0</v>
+      </c>
+      <c r="H59" s="33"/>
+      <c r="I59" s="2">
+        <v>0</v>
+      </c>
+      <c r="J59" s="13"/>
+      <c r="K59" s="3">
+        <v>100300103</v>
+      </c>
+      <c r="L59" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A60" s="2">
+        <f t="shared" si="2"/>
+        <v>1003100110</v>
+      </c>
+      <c r="B60" s="3">
+        <v>100300</v>
+      </c>
+      <c r="C60" s="3">
+        <v>10</v>
+      </c>
+      <c r="D60" s="3">
+        <v>1</v>
+      </c>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3">
+        <v>1</v>
+      </c>
+      <c r="G60" s="32">
+        <v>0</v>
+      </c>
+      <c r="H60" s="33"/>
+      <c r="I60" s="2">
+        <v>0</v>
+      </c>
+      <c r="J60" s="13"/>
+      <c r="K60" s="3">
+        <v>100300104</v>
+      </c>
+      <c r="L60" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="61" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A61" s="2">
+        <v>1007300301</v>
+      </c>
+      <c r="B61" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C61" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="D61" s="16">
+        <v>3</v>
+      </c>
+      <c r="E61" s="16"/>
+      <c r="F61" s="16">
+        <v>3</v>
+      </c>
+      <c r="G61" s="18">
+        <v>2</v>
+      </c>
+      <c r="H61" s="18"/>
+      <c r="I61" s="2">
+        <v>0</v>
+      </c>
+      <c r="J61" s="37"/>
+      <c r="K61" s="16"/>
+      <c r="L61" s="13"/>
+    </row>
+    <row r="62" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A62" s="2">
+        <v>1007300302</v>
+      </c>
+      <c r="B62" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C62" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="D62" s="16">
+        <v>3</v>
+      </c>
+      <c r="E62" s="16"/>
+      <c r="F62" s="16">
+        <v>3</v>
+      </c>
+      <c r="G62" s="18">
+        <v>2</v>
+      </c>
+      <c r="H62" s="18"/>
+      <c r="I62" s="2">
+        <v>0</v>
+      </c>
+      <c r="J62" s="37"/>
+      <c r="K62" s="16"/>
+      <c r="L62" s="13"/>
+    </row>
+    <row r="63" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A63" s="2">
+        <v>1007300303</v>
+      </c>
+      <c r="B63" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C63" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="D63" s="16">
+        <v>3</v>
+      </c>
+      <c r="E63" s="16"/>
+      <c r="F63" s="16">
+        <v>3</v>
+      </c>
+      <c r="G63" s="18">
+        <v>4</v>
+      </c>
+      <c r="H63" s="18"/>
+      <c r="I63" s="2">
+        <v>0</v>
+      </c>
+      <c r="J63" s="37"/>
+      <c r="K63" s="16"/>
+      <c r="L63" s="13"/>
+    </row>
+    <row r="64" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A64" s="2">
+        <v>1007300304</v>
+      </c>
+      <c r="B64" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C64" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="D64" s="16">
+        <v>3</v>
+      </c>
+      <c r="E64" s="16"/>
+      <c r="F64" s="16">
+        <v>3</v>
+      </c>
+      <c r="G64" s="18">
+        <v>4</v>
+      </c>
+      <c r="H64" s="18"/>
+      <c r="I64" s="2">
+        <v>0</v>
+      </c>
+      <c r="J64" s="37"/>
+      <c r="K64" s="16"/>
+      <c r="L64" s="13"/>
+    </row>
+    <row r="65" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A65" s="2">
+        <v>1007300305</v>
+      </c>
+      <c r="B65" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C65" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="D65" s="16">
+        <v>3</v>
+      </c>
+      <c r="E65" s="16"/>
+      <c r="F65" s="16">
+        <v>3</v>
+      </c>
+      <c r="G65" s="18">
+        <v>6</v>
+      </c>
+      <c r="H65" s="18"/>
+      <c r="I65" s="2">
+        <v>0</v>
+      </c>
+      <c r="J65" s="37"/>
+      <c r="K65" s="16"/>
+      <c r="L65" s="13"/>
+    </row>
+    <row r="66" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A66" s="2">
+        <v>1007300306</v>
+      </c>
+      <c r="B66" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C66" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="D66" s="16">
+        <v>3</v>
+      </c>
+      <c r="E66" s="16"/>
+      <c r="F66" s="16">
+        <v>3</v>
+      </c>
+      <c r="G66" s="18">
+        <v>8</v>
+      </c>
+      <c r="H66" s="18"/>
+      <c r="I66" s="2">
+        <v>0</v>
+      </c>
+      <c r="J66" s="37"/>
+      <c r="K66" s="16"/>
+      <c r="L66" s="13"/>
+    </row>
+    <row r="67" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A67" s="2">
+        <v>1007300307</v>
+      </c>
+      <c r="B67" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C67" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" s="16">
+        <v>3</v>
+      </c>
+      <c r="E67" s="16"/>
+      <c r="F67" s="16">
+        <v>3</v>
+      </c>
+      <c r="G67" s="18">
+        <v>10</v>
+      </c>
+      <c r="H67" s="18"/>
+      <c r="I67" s="2">
+        <v>0</v>
+      </c>
+      <c r="J67" s="37"/>
+      <c r="K67" s="16"/>
+      <c r="L67" s="13"/>
+    </row>
+    <row r="68" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A68" s="2">
         <v>1007300308</v>
       </c>
-      <c r="B56" s="14">
+      <c r="B68" s="16">
         <v>100700</v>
       </c>
-      <c r="C56" s="8">
+      <c r="C68" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="D68" s="16">
+        <v>3</v>
+      </c>
+      <c r="E68" s="16"/>
+      <c r="F68" s="16">
+        <v>3</v>
+      </c>
+      <c r="G68" s="18">
+        <v>15</v>
+      </c>
+      <c r="H68" s="18"/>
+      <c r="I68" s="2">
+        <v>0</v>
+      </c>
+      <c r="J68" s="37"/>
+      <c r="K68" s="16"/>
+      <c r="L68" s="13"/>
+    </row>
+    <row r="69" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A69" s="2">
+        <v>1007300401</v>
+      </c>
+      <c r="B69" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C69" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="D69" s="16">
+        <v>3</v>
+      </c>
+      <c r="E69" s="16"/>
+      <c r="F69" s="16">
         <v>4</v>
       </c>
-      <c r="D56" s="24" t="s">
+      <c r="G69" s="18">
+        <v>5</v>
+      </c>
+      <c r="H69" s="18"/>
+      <c r="I69" s="2">
+        <v>0</v>
+      </c>
+      <c r="J69" s="37"/>
+      <c r="K69" s="16"/>
+      <c r="L69" s="13"/>
+    </row>
+    <row r="70" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A70" s="2">
+        <v>1007300402</v>
+      </c>
+      <c r="B70" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C70" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="D70" s="16">
+        <v>3</v>
+      </c>
+      <c r="E70" s="16"/>
+      <c r="F70" s="16">
+        <v>4</v>
+      </c>
+      <c r="G70" s="18">
+        <v>5</v>
+      </c>
+      <c r="H70" s="18"/>
+      <c r="I70" s="2">
+        <v>0</v>
+      </c>
+      <c r="J70" s="37"/>
+      <c r="K70" s="16"/>
+      <c r="L70" s="13"/>
+    </row>
+    <row r="71" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A71" s="2">
+        <v>1007300403</v>
+      </c>
+      <c r="B71" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C71" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="D71" s="16">
+        <v>3</v>
+      </c>
+      <c r="E71" s="16"/>
+      <c r="F71" s="16">
+        <v>4</v>
+      </c>
+      <c r="G71" s="18">
+        <v>10</v>
+      </c>
+      <c r="H71" s="18"/>
+      <c r="I71" s="2">
+        <v>0</v>
+      </c>
+      <c r="J71" s="37"/>
+      <c r="K71" s="16"/>
+      <c r="L71" s="13"/>
+    </row>
+    <row r="72" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A72" s="2">
+        <v>1007300404</v>
+      </c>
+      <c r="B72" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C72" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="D72" s="16">
+        <v>3</v>
+      </c>
+      <c r="E72" s="16"/>
+      <c r="F72" s="16">
+        <v>4</v>
+      </c>
+      <c r="G72" s="18">
+        <v>10</v>
+      </c>
+      <c r="H72" s="18"/>
+      <c r="I72" s="2">
+        <v>0</v>
+      </c>
+      <c r="J72" s="37"/>
+      <c r="K72" s="16"/>
+      <c r="L72" s="13"/>
+    </row>
+    <row r="73" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A73" s="2">
+        <v>1007300405</v>
+      </c>
+      <c r="B73" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C73" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="D73" s="16">
+        <v>3</v>
+      </c>
+      <c r="E73" s="16"/>
+      <c r="F73" s="16">
+        <v>4</v>
+      </c>
+      <c r="G73" s="18">
+        <v>15</v>
+      </c>
+      <c r="H73" s="18"/>
+      <c r="I73" s="2">
+        <v>0</v>
+      </c>
+      <c r="J73" s="37"/>
+      <c r="K73" s="16"/>
+      <c r="L73" s="13"/>
+    </row>
+    <row r="74" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A74" s="2">
+        <v>1007300406</v>
+      </c>
+      <c r="B74" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C74" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E56" s="14">
+      <c r="D74" s="16">
         <v>3</v>
       </c>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14">
+      <c r="E74" s="16"/>
+      <c r="F74" s="16">
+        <v>4</v>
+      </c>
+      <c r="G74" s="18">
+        <v>20</v>
+      </c>
+      <c r="H74" s="18"/>
+      <c r="I74" s="2">
+        <v>0</v>
+      </c>
+      <c r="J74" s="37"/>
+      <c r="K74" s="16"/>
+      <c r="L74" s="13"/>
+    </row>
+    <row r="75" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A75" s="2">
+        <v>1007300407</v>
+      </c>
+      <c r="B75" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C75" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="D75" s="16">
         <v>3</v>
       </c>
-      <c r="H56" s="15">
-        <v>15</v>
-      </c>
-      <c r="I56" s="15"/>
-      <c r="J56" s="14"/>
-      <c r="K56" s="14"/>
-      <c r="L56" s="10"/>
-    </row>
-    <row r="57" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
-      <c r="A57" s="2">
-        <v>1007300401</v>
-      </c>
-      <c r="B57" s="14">
+      <c r="E75" s="16"/>
+      <c r="F75" s="16">
+        <v>4</v>
+      </c>
+      <c r="G75" s="18">
+        <v>40</v>
+      </c>
+      <c r="H75" s="18"/>
+      <c r="I75" s="2">
+        <v>0</v>
+      </c>
+      <c r="J75" s="37"/>
+      <c r="K75" s="16"/>
+      <c r="L75" s="13"/>
+    </row>
+    <row r="76" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A76" s="2">
+        <v>1007300408</v>
+      </c>
+      <c r="B76" s="16">
         <v>100700</v>
       </c>
-      <c r="C57" s="8">
+      <c r="C76" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="D76" s="16">
+        <v>3</v>
+      </c>
+      <c r="E76" s="16"/>
+      <c r="F76" s="16">
         <v>4</v>
       </c>
-      <c r="D57" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="E57" s="14">
+      <c r="G76" s="18">
+        <v>60</v>
+      </c>
+      <c r="H76" s="18"/>
+      <c r="I76" s="2">
+        <v>0</v>
+      </c>
+      <c r="J76" s="37"/>
+      <c r="K76" s="16"/>
+      <c r="L76" s="13"/>
+    </row>
+    <row r="77" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A77" s="2">
+        <v>1007300501</v>
+      </c>
+      <c r="B77" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C77" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="D77" s="16">
         <v>3</v>
       </c>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14">
-        <v>4</v>
-      </c>
-      <c r="H57" s="15">
+      <c r="E77" s="16"/>
+      <c r="F77" s="16">
         <v>5</v>
       </c>
-      <c r="I57" s="15"/>
-      <c r="J57" s="14"/>
-      <c r="K57" s="14"/>
-      <c r="L57" s="10"/>
-    </row>
-    <row r="58" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
-      <c r="A58" s="2">
-        <v>1007300402</v>
-      </c>
-      <c r="B58" s="14">
+      <c r="G77" s="18">
+        <v>10</v>
+      </c>
+      <c r="H77" s="18"/>
+      <c r="I77" s="2">
+        <v>0</v>
+      </c>
+      <c r="J77" s="37"/>
+      <c r="K77" s="16"/>
+      <c r="L77" s="13"/>
+    </row>
+    <row r="78" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A78" s="2">
+        <v>1007300502</v>
+      </c>
+      <c r="B78" s="16">
         <v>100700</v>
       </c>
-      <c r="C58" s="8">
-        <v>4</v>
-      </c>
-      <c r="D58" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="E58" s="14">
+      <c r="C78" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="D78" s="16">
         <v>3</v>
       </c>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14">
-        <v>4</v>
-      </c>
-      <c r="H58" s="15">
+      <c r="E78" s="16"/>
+      <c r="F78" s="16">
         <v>5</v>
       </c>
-      <c r="I58" s="15"/>
-      <c r="J58" s="14"/>
-      <c r="K58" s="14"/>
-      <c r="L58" s="10"/>
-    </row>
-    <row r="59" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
-      <c r="A59" s="2">
-        <v>1007300403</v>
-      </c>
-      <c r="B59" s="14">
+      <c r="G78" s="18">
+        <v>10</v>
+      </c>
+      <c r="H78" s="18"/>
+      <c r="I78" s="2">
+        <v>0</v>
+      </c>
+      <c r="J78" s="37"/>
+      <c r="K78" s="16"/>
+      <c r="L78" s="13"/>
+    </row>
+    <row r="79" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A79" s="2">
+        <v>1007300503</v>
+      </c>
+      <c r="B79" s="16">
         <v>100700</v>
       </c>
-      <c r="C59" s="8">
-        <v>4</v>
-      </c>
-      <c r="D59" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="E59" s="14">
+      <c r="C79" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="D79" s="16">
         <v>3</v>
       </c>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14">
-        <v>4</v>
-      </c>
-      <c r="H59" s="15">
-        <v>10</v>
-      </c>
-      <c r="I59" s="15"/>
-      <c r="J59" s="14"/>
-      <c r="K59" s="14"/>
-      <c r="L59" s="10"/>
-    </row>
-    <row r="60" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
-      <c r="A60" s="2">
-        <v>1007300404</v>
-      </c>
-      <c r="B60" s="14">
+      <c r="E79" s="16"/>
+      <c r="F79" s="16">
+        <v>5</v>
+      </c>
+      <c r="G79" s="18">
+        <v>20</v>
+      </c>
+      <c r="H79" s="18"/>
+      <c r="I79" s="2">
+        <v>0</v>
+      </c>
+      <c r="J79" s="37"/>
+      <c r="K79" s="16"/>
+      <c r="L79" s="13"/>
+    </row>
+    <row r="80" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A80" s="2">
+        <v>1007300504</v>
+      </c>
+      <c r="B80" s="16">
         <v>100700</v>
       </c>
-      <c r="C60" s="8">
-        <v>4</v>
-      </c>
-      <c r="D60" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="E60" s="14">
+      <c r="C80" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="D80" s="16">
         <v>3</v>
       </c>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14">
-        <v>4</v>
-      </c>
-      <c r="H60" s="15">
-        <v>10</v>
-      </c>
-      <c r="I60" s="15"/>
-      <c r="J60" s="14"/>
-      <c r="K60" s="14"/>
-      <c r="L60" s="10"/>
-    </row>
-    <row r="61" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
-      <c r="A61" s="2">
-        <v>1007300405</v>
-      </c>
-      <c r="B61" s="14">
+      <c r="E80" s="16"/>
+      <c r="F80" s="16">
+        <v>5</v>
+      </c>
+      <c r="G80" s="18">
+        <v>20</v>
+      </c>
+      <c r="H80" s="18"/>
+      <c r="I80" s="2">
+        <v>0</v>
+      </c>
+      <c r="J80" s="37"/>
+      <c r="K80" s="16"/>
+      <c r="L80" s="13"/>
+    </row>
+    <row r="81" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A81" s="2">
+        <v>1007300505</v>
+      </c>
+      <c r="B81" s="16">
         <v>100700</v>
       </c>
-      <c r="C61" s="8">
-        <v>4</v>
-      </c>
-      <c r="D61" s="24" t="s">
+      <c r="C81" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="D81" s="16">
+        <v>3</v>
+      </c>
+      <c r="E81" s="16"/>
+      <c r="F81" s="16">
+        <v>5</v>
+      </c>
+      <c r="G81" s="18">
+        <v>30</v>
+      </c>
+      <c r="H81" s="18"/>
+      <c r="I81" s="2">
+        <v>0</v>
+      </c>
+      <c r="J81" s="37"/>
+      <c r="K81" s="16"/>
+      <c r="L81" s="13"/>
+    </row>
+    <row r="82" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A82" s="2">
+        <v>1007300506</v>
+      </c>
+      <c r="B82" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C82" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="D82" s="16">
+        <v>3</v>
+      </c>
+      <c r="E82" s="16"/>
+      <c r="F82" s="16">
+        <v>5</v>
+      </c>
+      <c r="G82" s="18">
         <v>40</v>
       </c>
-      <c r="E61" s="14">
+      <c r="H82" s="18"/>
+      <c r="I82" s="2">
+        <v>0</v>
+      </c>
+      <c r="J82" s="37"/>
+      <c r="K82" s="16"/>
+      <c r="L82" s="13"/>
+    </row>
+    <row r="83" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A83" s="2">
+        <v>1007300507</v>
+      </c>
+      <c r="B83" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C83" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="D83" s="16">
         <v>3</v>
       </c>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14">
-        <v>4</v>
-      </c>
-      <c r="H61" s="15">
-        <v>15</v>
-      </c>
-      <c r="I61" s="15"/>
-      <c r="J61" s="14"/>
-      <c r="K61" s="14"/>
-      <c r="L61" s="10"/>
-    </row>
-    <row r="62" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
-      <c r="A62" s="2">
-        <v>1007300406</v>
-      </c>
-      <c r="B62" s="14">
+      <c r="E83" s="16"/>
+      <c r="F83" s="16">
+        <v>5</v>
+      </c>
+      <c r="G83" s="18">
+        <v>80</v>
+      </c>
+      <c r="H83" s="18"/>
+      <c r="I83" s="2">
+        <v>0</v>
+      </c>
+      <c r="J83" s="37"/>
+      <c r="K83" s="16"/>
+      <c r="L83" s="13"/>
+    </row>
+    <row r="84" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A84" s="2">
+        <v>1007300508</v>
+      </c>
+      <c r="B84" s="16">
         <v>100700</v>
       </c>
-      <c r="C62" s="8">
-        <v>4</v>
-      </c>
-      <c r="D62" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="E62" s="14">
+      <c r="C84" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="D84" s="16">
         <v>3</v>
       </c>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14">
-        <v>4</v>
-      </c>
-      <c r="H62" s="15">
-        <v>20</v>
-      </c>
-      <c r="I62" s="15"/>
-      <c r="J62" s="14"/>
-      <c r="K62" s="14"/>
-      <c r="L62" s="10"/>
-    </row>
-    <row r="63" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
-      <c r="A63" s="2">
-        <v>1007300407</v>
-      </c>
-      <c r="B63" s="14">
-        <v>100700</v>
-      </c>
-      <c r="C63" s="8">
-        <v>4</v>
-      </c>
-      <c r="D63" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="E63" s="14">
-        <v>3</v>
-      </c>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14">
-        <v>4</v>
-      </c>
-      <c r="H63" s="15">
-        <v>40</v>
-      </c>
-      <c r="I63" s="15"/>
-      <c r="J63" s="14"/>
-      <c r="K63" s="14"/>
-      <c r="L63" s="10"/>
-    </row>
-    <row r="64" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
-      <c r="A64" s="2">
-        <v>1007300408</v>
-      </c>
-      <c r="B64" s="14">
-        <v>100700</v>
-      </c>
-      <c r="C64" s="8">
-        <v>4</v>
-      </c>
-      <c r="D64" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="E64" s="14">
-        <v>3</v>
-      </c>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14">
-        <v>4</v>
-      </c>
-      <c r="H64" s="15">
-        <v>60</v>
-      </c>
-      <c r="I64" s="15"/>
-      <c r="J64" s="14"/>
-      <c r="K64" s="14"/>
-      <c r="L64" s="10"/>
-    </row>
-    <row r="65" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
-      <c r="A65" s="2">
-        <v>1007300501</v>
-      </c>
-      <c r="B65" s="14">
-        <v>100700</v>
-      </c>
-      <c r="C65" s="8">
-        <v>4</v>
-      </c>
-      <c r="D65" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="E65" s="14">
-        <v>3</v>
-      </c>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14">
+      <c r="E84" s="16"/>
+      <c r="F84" s="16">
         <v>5</v>
       </c>
-      <c r="H65" s="15">
-        <v>10</v>
-      </c>
-      <c r="I65" s="15"/>
-      <c r="J65" s="14"/>
-      <c r="K65" s="14"/>
-      <c r="L65" s="10"/>
-    </row>
-    <row r="66" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
-      <c r="A66" s="2">
-        <v>1007300502</v>
-      </c>
-      <c r="B66" s="14">
-        <v>100700</v>
-      </c>
-      <c r="C66" s="8">
-        <v>4</v>
-      </c>
-      <c r="D66" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="E66" s="14">
-        <v>3</v>
-      </c>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14">
-        <v>5</v>
-      </c>
-      <c r="H66" s="15">
-        <v>10</v>
-      </c>
-      <c r="I66" s="15"/>
-      <c r="J66" s="14"/>
-      <c r="K66" s="14"/>
-      <c r="L66" s="10"/>
-    </row>
-    <row r="67" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
-      <c r="A67" s="2">
-        <v>1007300503</v>
-      </c>
-      <c r="B67" s="14">
-        <v>100700</v>
-      </c>
-      <c r="C67" s="8">
-        <v>4</v>
-      </c>
-      <c r="D67" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="E67" s="14">
-        <v>3</v>
-      </c>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14">
-        <v>5</v>
-      </c>
-      <c r="H67" s="15">
-        <v>20</v>
-      </c>
-      <c r="I67" s="15"/>
-      <c r="J67" s="14"/>
-      <c r="K67" s="14"/>
-      <c r="L67" s="10"/>
-    </row>
-    <row r="68" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
-      <c r="A68" s="2">
-        <v>1007300504</v>
-      </c>
-      <c r="B68" s="14">
-        <v>100700</v>
-      </c>
-      <c r="C68" s="8">
-        <v>4</v>
-      </c>
-      <c r="D68" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="E68" s="14">
-        <v>3</v>
-      </c>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14">
-        <v>5</v>
-      </c>
-      <c r="H68" s="15">
-        <v>20</v>
-      </c>
-      <c r="I68" s="15"/>
-      <c r="J68" s="14"/>
-      <c r="K68" s="14"/>
-      <c r="L68" s="10"/>
-    </row>
-    <row r="69" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
-      <c r="A69" s="2">
-        <v>1007300505</v>
-      </c>
-      <c r="B69" s="14">
-        <v>100700</v>
-      </c>
-      <c r="C69" s="8">
-        <v>4</v>
-      </c>
-      <c r="D69" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="E69" s="14">
-        <v>3</v>
-      </c>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14">
-        <v>5</v>
-      </c>
-      <c r="H69" s="15">
-        <v>30</v>
-      </c>
-      <c r="I69" s="15"/>
-      <c r="J69" s="14"/>
-      <c r="K69" s="14"/>
-      <c r="L69" s="10"/>
-    </row>
-    <row r="70" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
-      <c r="A70" s="2">
-        <v>1007300506</v>
-      </c>
-      <c r="B70" s="14">
-        <v>100700</v>
-      </c>
-      <c r="C70" s="8">
-        <v>4</v>
-      </c>
-      <c r="D70" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="E70" s="14">
-        <v>3</v>
-      </c>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14">
-        <v>5</v>
-      </c>
-      <c r="H70" s="15">
-        <v>40</v>
-      </c>
-      <c r="I70" s="15"/>
-      <c r="J70" s="14"/>
-      <c r="K70" s="14"/>
-      <c r="L70" s="10"/>
-    </row>
-    <row r="71" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
-      <c r="A71" s="2">
-        <v>1007300507</v>
-      </c>
-      <c r="B71" s="14">
-        <v>100700</v>
-      </c>
-      <c r="C71" s="8">
-        <v>4</v>
-      </c>
-      <c r="D71" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="E71" s="14">
-        <v>3</v>
-      </c>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14">
-        <v>5</v>
-      </c>
-      <c r="H71" s="15">
-        <v>80</v>
-      </c>
-      <c r="I71" s="15"/>
-      <c r="J71" s="14"/>
-      <c r="K71" s="14"/>
-      <c r="L71" s="10"/>
-    </row>
-    <row r="72" s="5" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
-      <c r="A72" s="2">
-        <v>1007300508</v>
-      </c>
-      <c r="B72" s="14">
-        <v>100700</v>
-      </c>
-      <c r="C72" s="8">
-        <v>4</v>
-      </c>
-      <c r="D72" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="E72" s="14">
-        <v>3</v>
-      </c>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14">
-        <v>5</v>
-      </c>
-      <c r="H72" s="15">
+      <c r="G84" s="18">
         <v>120</v>
       </c>
-      <c r="I72" s="15"/>
-      <c r="J72" s="14"/>
-      <c r="K72" s="14"/>
-      <c r="L72" s="10"/>
-    </row>
-    <row r="73" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A73" s="2">
-        <f t="shared" ref="A73:A85" si="2">(B73)*10000+D73+G73*100+E73*100000</f>
-        <v>1007400310</v>
-      </c>
-      <c r="B73" s="14">
-        <v>100700</v>
-      </c>
-      <c r="C73" s="8">
-        <v>4</v>
-      </c>
-      <c r="D73" s="14">
-        <v>10</v>
-      </c>
-      <c r="E73" s="14">
-        <v>4</v>
-      </c>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14">
-        <v>3</v>
-      </c>
-      <c r="H73" s="15">
-        <v>0</v>
-      </c>
-      <c r="I73" s="15">
-        <v>30070001</v>
-      </c>
-      <c r="J73" s="14"/>
-      <c r="K73" s="14"/>
-      <c r="L73" s="10"/>
-    </row>
-    <row r="74" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A74" s="2">
-        <f t="shared" si="2"/>
-        <v>1007400410</v>
-      </c>
-      <c r="B74" s="14">
-        <v>100700</v>
-      </c>
-      <c r="C74" s="8">
-        <v>4</v>
-      </c>
-      <c r="D74" s="14">
-        <v>10</v>
-      </c>
-      <c r="E74" s="14">
-        <v>4</v>
-      </c>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14">
-        <v>4</v>
-      </c>
-      <c r="H74" s="15">
-        <v>0</v>
-      </c>
-      <c r="I74" s="15">
-        <v>30070002</v>
-      </c>
-      <c r="J74" s="14"/>
-      <c r="K74" s="14"/>
-      <c r="L74" s="10"/>
-    </row>
-    <row r="75" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A75" s="2">
-        <f t="shared" si="2"/>
-        <v>1014500502</v>
-      </c>
-      <c r="B75" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C75" s="8">
-        <v>4</v>
-      </c>
-      <c r="D75" s="37">
-        <v>2</v>
-      </c>
-      <c r="E75" s="37">
-        <v>5</v>
-      </c>
-      <c r="F75" s="37"/>
-      <c r="G75" s="37">
-        <v>5</v>
-      </c>
-      <c r="H75" s="38">
-        <v>1</v>
-      </c>
-      <c r="I75" s="38"/>
-      <c r="J75" s="37"/>
-      <c r="K75" s="37"/>
-      <c r="L75" s="10"/>
-    </row>
-    <row r="76" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A76" s="2">
-        <f t="shared" si="2"/>
-        <v>1014500503</v>
-      </c>
-      <c r="B76" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C76" s="8">
-        <v>4</v>
-      </c>
-      <c r="D76" s="37">
-        <v>3</v>
-      </c>
-      <c r="E76" s="37">
-        <v>5</v>
-      </c>
-      <c r="F76" s="37"/>
-      <c r="G76" s="37">
-        <v>5</v>
-      </c>
-      <c r="H76" s="38">
-        <v>1</v>
-      </c>
-      <c r="I76" s="38"/>
-      <c r="J76" s="37"/>
-      <c r="K76" s="37"/>
-      <c r="L76" s="10"/>
-    </row>
-    <row r="77" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A77" s="2">
-        <f t="shared" si="2"/>
-        <v>1014500504</v>
-      </c>
-      <c r="B77" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C77" s="8">
-        <v>4</v>
-      </c>
-      <c r="D77" s="37">
-        <v>4</v>
-      </c>
-      <c r="E77" s="37">
-        <v>5</v>
-      </c>
-      <c r="F77" s="37"/>
-      <c r="G77" s="37">
-        <v>5</v>
-      </c>
-      <c r="H77" s="38">
-        <v>1</v>
-      </c>
-      <c r="I77" s="38"/>
-      <c r="J77" s="37"/>
-      <c r="K77" s="37"/>
-      <c r="L77" s="10"/>
-    </row>
-    <row r="78" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A78" s="2">
-        <f t="shared" si="2"/>
-        <v>1014500505</v>
-      </c>
-      <c r="B78" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C78" s="8">
-        <v>4</v>
-      </c>
-      <c r="D78" s="37">
-        <v>5</v>
-      </c>
-      <c r="E78" s="37">
-        <v>5</v>
-      </c>
-      <c r="F78" s="37"/>
-      <c r="G78" s="37">
-        <v>5</v>
-      </c>
-      <c r="H78" s="38">
-        <v>2</v>
-      </c>
-      <c r="I78" s="38"/>
-      <c r="J78" s="37"/>
-      <c r="K78" s="37"/>
-      <c r="L78" s="10"/>
-    </row>
-    <row r="79" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A79" s="2">
-        <f t="shared" si="2"/>
-        <v>1014500506</v>
-      </c>
-      <c r="B79" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C79" s="8">
-        <v>4</v>
-      </c>
-      <c r="D79" s="37">
-        <v>6</v>
-      </c>
-      <c r="E79" s="37">
-        <v>5</v>
-      </c>
-      <c r="F79" s="37"/>
-      <c r="G79" s="37">
-        <v>5</v>
-      </c>
-      <c r="H79" s="38">
-        <v>2</v>
-      </c>
-      <c r="I79" s="38"/>
-      <c r="J79" s="37"/>
-      <c r="K79" s="37"/>
-      <c r="L79" s="10"/>
-    </row>
-    <row r="80" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A80" s="2">
-        <f t="shared" si="2"/>
-        <v>1014500507</v>
-      </c>
-      <c r="B80" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C80" s="8">
-        <v>4</v>
-      </c>
-      <c r="D80" s="37">
-        <v>7</v>
-      </c>
-      <c r="E80" s="37">
-        <v>5</v>
-      </c>
-      <c r="F80" s="37"/>
-      <c r="G80" s="37">
-        <v>5</v>
-      </c>
-      <c r="H80" s="38">
-        <v>2</v>
-      </c>
-      <c r="I80" s="38"/>
-      <c r="J80" s="37"/>
-      <c r="K80" s="37"/>
-      <c r="L80" s="10"/>
-    </row>
-    <row r="81" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A81" s="2">
-        <f t="shared" si="2"/>
-        <v>1014500508</v>
-      </c>
-      <c r="B81" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C81" s="8">
-        <v>4</v>
-      </c>
-      <c r="D81" s="37">
-        <v>8</v>
-      </c>
-      <c r="E81" s="37">
-        <v>5</v>
-      </c>
-      <c r="F81" s="37"/>
-      <c r="G81" s="37">
-        <v>5</v>
-      </c>
-      <c r="H81" s="38">
-        <v>3</v>
-      </c>
-      <c r="I81" s="38"/>
-      <c r="J81" s="37"/>
-      <c r="K81" s="37"/>
-      <c r="L81" s="10"/>
-    </row>
-    <row r="82" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A82" s="2">
-        <f t="shared" si="2"/>
-        <v>1014500509</v>
-      </c>
-      <c r="B82" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C82" s="8">
-        <v>4</v>
-      </c>
-      <c r="D82" s="37">
-        <v>9</v>
-      </c>
-      <c r="E82" s="37">
-        <v>5</v>
-      </c>
-      <c r="F82" s="37"/>
-      <c r="G82" s="37">
-        <v>5</v>
-      </c>
-      <c r="H82" s="38">
-        <v>3</v>
-      </c>
-      <c r="I82" s="38"/>
-      <c r="J82" s="37"/>
-      <c r="K82" s="37"/>
-      <c r="L82" s="10"/>
-    </row>
-    <row r="83" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A83" s="2">
-        <f t="shared" si="2"/>
-        <v>1014500510</v>
-      </c>
-      <c r="B83" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C83" s="8">
-        <v>4</v>
-      </c>
-      <c r="D83" s="37">
-        <v>10</v>
-      </c>
-      <c r="E83" s="37">
-        <v>5</v>
-      </c>
-      <c r="F83" s="37"/>
-      <c r="G83" s="37">
-        <v>5</v>
-      </c>
-      <c r="H83" s="38">
-        <v>4</v>
-      </c>
-      <c r="I83" s="38"/>
-      <c r="J83" s="37"/>
-      <c r="K83" s="37"/>
-      <c r="L83" s="10"/>
-    </row>
-    <row r="84" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A84" s="2">
-        <f t="shared" si="2"/>
-        <v>1014500511</v>
-      </c>
-      <c r="B84" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C84" s="8">
-        <v>4</v>
-      </c>
-      <c r="D84" s="37">
-        <v>11</v>
-      </c>
-      <c r="E84" s="37">
-        <v>5</v>
-      </c>
-      <c r="F84" s="37"/>
-      <c r="G84" s="37">
-        <v>5</v>
-      </c>
-      <c r="H84" s="38">
-        <v>5</v>
-      </c>
-      <c r="I84" s="38"/>
+      <c r="H84" s="18"/>
+      <c r="I84" s="2">
+        <v>0</v>
+      </c>
       <c r="J84" s="37"/>
-      <c r="K84" s="37"/>
-      <c r="L84" s="10"/>
+      <c r="K84" s="16"/>
+      <c r="L84" s="13"/>
     </row>
     <row r="85" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A85" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A85:A87" si="3">(B85)*10000+C85+F85*100+D85*100000</f>
+        <v>1007400310</v>
+      </c>
+      <c r="B85" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C85" s="16">
+        <v>10</v>
+      </c>
+      <c r="D85" s="16">
+        <v>4</v>
+      </c>
+      <c r="E85" s="16"/>
+      <c r="F85" s="16">
+        <v>3</v>
+      </c>
+      <c r="G85" s="18">
+        <v>0</v>
+      </c>
+      <c r="H85" s="18">
+        <v>30070001</v>
+      </c>
+      <c r="I85" s="2">
+        <v>0</v>
+      </c>
+      <c r="J85" s="37"/>
+      <c r="K85" s="16"/>
+      <c r="L85" s="13"/>
+    </row>
+    <row r="86" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A86" s="2">
+        <f t="shared" si="3"/>
+        <v>1007400410</v>
+      </c>
+      <c r="B86" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C86" s="16">
+        <v>10</v>
+      </c>
+      <c r="D86" s="16">
+        <v>4</v>
+      </c>
+      <c r="E86" s="16"/>
+      <c r="F86" s="16">
+        <v>4</v>
+      </c>
+      <c r="G86" s="18">
+        <v>0</v>
+      </c>
+      <c r="H86" s="18">
+        <v>30070002</v>
+      </c>
+      <c r="I86" s="2">
+        <v>0</v>
+      </c>
+      <c r="J86" s="37"/>
+      <c r="K86" s="16"/>
+      <c r="L86" s="13"/>
+    </row>
+    <row r="87" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A87" s="43">
+        <f t="shared" si="3"/>
+        <v>1012100301</v>
+      </c>
+      <c r="B87" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C87" s="43">
+        <v>1</v>
+      </c>
+      <c r="D87" s="43">
+        <v>1</v>
+      </c>
+      <c r="E87" s="43"/>
+      <c r="F87" s="43">
+        <v>3</v>
+      </c>
+      <c r="G87" s="44">
+        <v>2</v>
+      </c>
+      <c r="H87" s="44"/>
+      <c r="I87" s="43">
+        <v>0</v>
+      </c>
+      <c r="J87" s="49"/>
+      <c r="K87" s="43"/>
+      <c r="L87" s="49"/>
+    </row>
+    <row r="88" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A88" s="43">
+        <f t="shared" ref="A88:A123" si="4">(B88)*10000+C88+F88*100+D88*100000</f>
+        <v>1012200302</v>
+      </c>
+      <c r="B88" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C88" s="43">
+        <v>2</v>
+      </c>
+      <c r="D88" s="43">
+        <v>2</v>
+      </c>
+      <c r="E88" s="43"/>
+      <c r="F88" s="43">
+        <v>3</v>
+      </c>
+      <c r="G88" s="44">
+        <v>3</v>
+      </c>
+      <c r="H88" s="44"/>
+      <c r="I88" s="43">
+        <v>0</v>
+      </c>
+      <c r="J88" s="49"/>
+      <c r="K88" s="43"/>
+      <c r="L88" s="49"/>
+    </row>
+    <row r="89" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A89" s="43">
+        <f t="shared" si="4"/>
+        <v>1012300303</v>
+      </c>
+      <c r="B89" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C89" s="43">
+        <v>3</v>
+      </c>
+      <c r="D89" s="43">
+        <v>3</v>
+      </c>
+      <c r="E89" s="43"/>
+      <c r="F89" s="43">
+        <v>3</v>
+      </c>
+      <c r="G89" s="44">
+        <v>5</v>
+      </c>
+      <c r="H89" s="44"/>
+      <c r="I89" s="43">
+        <v>0</v>
+      </c>
+      <c r="J89" s="49"/>
+      <c r="K89" s="43"/>
+      <c r="L89" s="49"/>
+    </row>
+    <row r="90" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A90" s="43">
+        <f t="shared" si="4"/>
+        <v>1012400304</v>
+      </c>
+      <c r="B90" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C90" s="43">
+        <v>4</v>
+      </c>
+      <c r="D90" s="43">
+        <v>4</v>
+      </c>
+      <c r="E90" s="43"/>
+      <c r="F90" s="43">
+        <v>3</v>
+      </c>
+      <c r="G90" s="44">
+        <v>8</v>
+      </c>
+      <c r="H90" s="44"/>
+      <c r="I90" s="43">
+        <v>0</v>
+      </c>
+      <c r="J90" s="49"/>
+      <c r="K90" s="43"/>
+      <c r="L90" s="49"/>
+    </row>
+    <row r="91" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A91" s="43">
+        <f t="shared" si="4"/>
+        <v>1012500305</v>
+      </c>
+      <c r="B91" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C91" s="43">
+        <v>5</v>
+      </c>
+      <c r="D91" s="43">
+        <v>5</v>
+      </c>
+      <c r="E91" s="43"/>
+      <c r="F91" s="43">
+        <v>3</v>
+      </c>
+      <c r="G91" s="44">
+        <v>10</v>
+      </c>
+      <c r="H91" s="44"/>
+      <c r="I91" s="43">
+        <v>0</v>
+      </c>
+      <c r="J91" s="49"/>
+      <c r="K91" s="43"/>
+      <c r="L91" s="49"/>
+    </row>
+    <row r="92" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A92" s="43">
+        <f t="shared" si="4"/>
+        <v>1012600306</v>
+      </c>
+      <c r="B92" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C92" s="43">
+        <v>6</v>
+      </c>
+      <c r="D92" s="43">
+        <v>6</v>
+      </c>
+      <c r="E92" s="43"/>
+      <c r="F92" s="43">
+        <v>3</v>
+      </c>
+      <c r="G92" s="44">
+        <v>15</v>
+      </c>
+      <c r="H92" s="44"/>
+      <c r="I92" s="43">
+        <v>0</v>
+      </c>
+      <c r="J92" s="49"/>
+      <c r="K92" s="43"/>
+      <c r="L92" s="49"/>
+    </row>
+    <row r="93" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A93" s="43">
+        <f t="shared" si="4"/>
+        <v>1012100401</v>
+      </c>
+      <c r="B93" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C93" s="43">
+        <v>1</v>
+      </c>
+      <c r="D93" s="43">
+        <v>1</v>
+      </c>
+      <c r="E93" s="43"/>
+      <c r="F93" s="43">
+        <v>4</v>
+      </c>
+      <c r="G93" s="44">
+        <v>8</v>
+      </c>
+      <c r="H93" s="44"/>
+      <c r="I93" s="43">
+        <v>0</v>
+      </c>
+      <c r="J93" s="49"/>
+      <c r="K93" s="43"/>
+      <c r="L93" s="49"/>
+    </row>
+    <row r="94" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A94" s="43">
+        <f t="shared" si="4"/>
+        <v>1012200402</v>
+      </c>
+      <c r="B94" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C94" s="43">
+        <v>2</v>
+      </c>
+      <c r="D94" s="43">
+        <v>2</v>
+      </c>
+      <c r="E94" s="43"/>
+      <c r="F94" s="43">
+        <v>4</v>
+      </c>
+      <c r="G94" s="44">
+        <v>10</v>
+      </c>
+      <c r="H94" s="44"/>
+      <c r="I94" s="43">
+        <v>0</v>
+      </c>
+      <c r="J94" s="49"/>
+      <c r="K94" s="43"/>
+      <c r="L94" s="49"/>
+    </row>
+    <row r="95" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A95" s="43">
+        <f t="shared" si="4"/>
+        <v>1012300403</v>
+      </c>
+      <c r="B95" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C95" s="43">
+        <v>3</v>
+      </c>
+      <c r="D95" s="43">
+        <v>3</v>
+      </c>
+      <c r="E95" s="43"/>
+      <c r="F95" s="43">
+        <v>4</v>
+      </c>
+      <c r="G95" s="44">
+        <v>15</v>
+      </c>
+      <c r="H95" s="44"/>
+      <c r="I95" s="43">
+        <v>0</v>
+      </c>
+      <c r="J95" s="49"/>
+      <c r="K95" s="43"/>
+      <c r="L95" s="49"/>
+    </row>
+    <row r="96" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A96" s="43">
+        <f t="shared" si="4"/>
+        <v>1012400404</v>
+      </c>
+      <c r="B96" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C96" s="43">
+        <v>4</v>
+      </c>
+      <c r="D96" s="43">
+        <v>4</v>
+      </c>
+      <c r="E96" s="43"/>
+      <c r="F96" s="43">
+        <v>4</v>
+      </c>
+      <c r="G96" s="44">
+        <v>20</v>
+      </c>
+      <c r="H96" s="44"/>
+      <c r="I96" s="43">
+        <v>0</v>
+      </c>
+      <c r="J96" s="49"/>
+      <c r="K96" s="43"/>
+      <c r="L96" s="49"/>
+    </row>
+    <row r="97" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A97" s="43">
+        <f t="shared" si="4"/>
+        <v>1012500405</v>
+      </c>
+      <c r="B97" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C97" s="43">
+        <v>5</v>
+      </c>
+      <c r="D97" s="43">
+        <v>5</v>
+      </c>
+      <c r="E97" s="43"/>
+      <c r="F97" s="43">
+        <v>4</v>
+      </c>
+      <c r="G97" s="44">
+        <v>35</v>
+      </c>
+      <c r="H97" s="44"/>
+      <c r="I97" s="43">
+        <v>0</v>
+      </c>
+      <c r="J97" s="49"/>
+      <c r="K97" s="43"/>
+      <c r="L97" s="49"/>
+    </row>
+    <row r="98" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A98" s="43">
+        <f t="shared" si="4"/>
+        <v>1012600406</v>
+      </c>
+      <c r="B98" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C98" s="43">
+        <v>6</v>
+      </c>
+      <c r="D98" s="43">
+        <v>6</v>
+      </c>
+      <c r="E98" s="43"/>
+      <c r="F98" s="43">
+        <v>4</v>
+      </c>
+      <c r="G98" s="44">
+        <v>50</v>
+      </c>
+      <c r="H98" s="44"/>
+      <c r="I98" s="43">
+        <v>0</v>
+      </c>
+      <c r="J98" s="49"/>
+      <c r="K98" s="43"/>
+      <c r="L98" s="49"/>
+    </row>
+    <row r="99" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A99" s="43">
+        <f t="shared" si="4"/>
+        <v>1012100501</v>
+      </c>
+      <c r="B99" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C99" s="43">
+        <v>1</v>
+      </c>
+      <c r="D99" s="43">
+        <v>1</v>
+      </c>
+      <c r="E99" s="43"/>
+      <c r="F99" s="43">
+        <v>5</v>
+      </c>
+      <c r="G99" s="44">
+        <v>15</v>
+      </c>
+      <c r="H99" s="44"/>
+      <c r="I99" s="43">
+        <v>0</v>
+      </c>
+      <c r="J99" s="49"/>
+      <c r="K99" s="43"/>
+      <c r="L99" s="49"/>
+    </row>
+    <row r="100" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A100" s="43">
+        <f t="shared" si="4"/>
+        <v>1012200502</v>
+      </c>
+      <c r="B100" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C100" s="43">
+        <v>2</v>
+      </c>
+      <c r="D100" s="43">
+        <v>2</v>
+      </c>
+      <c r="E100" s="43"/>
+      <c r="F100" s="43">
+        <v>5</v>
+      </c>
+      <c r="G100" s="44">
+        <v>30</v>
+      </c>
+      <c r="H100" s="44"/>
+      <c r="I100" s="43">
+        <v>0</v>
+      </c>
+      <c r="J100" s="49"/>
+      <c r="K100" s="43"/>
+      <c r="L100" s="49"/>
+    </row>
+    <row r="101" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A101" s="43">
+        <f t="shared" si="4"/>
+        <v>1012300503</v>
+      </c>
+      <c r="B101" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C101" s="43">
+        <v>3</v>
+      </c>
+      <c r="D101" s="43">
+        <v>3</v>
+      </c>
+      <c r="E101" s="43"/>
+      <c r="F101" s="43">
+        <v>5</v>
+      </c>
+      <c r="G101" s="44">
+        <v>50</v>
+      </c>
+      <c r="H101" s="44"/>
+      <c r="I101" s="43">
+        <v>0</v>
+      </c>
+      <c r="J101" s="49"/>
+      <c r="K101" s="43"/>
+      <c r="L101" s="49"/>
+    </row>
+    <row r="102" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A102" s="43">
+        <f t="shared" si="4"/>
+        <v>1012400504</v>
+      </c>
+      <c r="B102" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C102" s="43">
+        <v>4</v>
+      </c>
+      <c r="D102" s="43">
+        <v>4</v>
+      </c>
+      <c r="E102" s="43"/>
+      <c r="F102" s="43">
+        <v>5</v>
+      </c>
+      <c r="G102" s="44">
+        <v>100</v>
+      </c>
+      <c r="H102" s="44"/>
+      <c r="I102" s="43">
+        <v>0</v>
+      </c>
+      <c r="J102" s="49"/>
+      <c r="K102" s="43"/>
+      <c r="L102" s="49"/>
+    </row>
+    <row r="103" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A103" s="43">
+        <f t="shared" si="4"/>
+        <v>1012500505</v>
+      </c>
+      <c r="B103" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C103" s="43">
+        <v>5</v>
+      </c>
+      <c r="D103" s="43">
+        <v>5</v>
+      </c>
+      <c r="E103" s="43"/>
+      <c r="F103" s="43">
+        <v>5</v>
+      </c>
+      <c r="G103" s="44">
+        <v>150</v>
+      </c>
+      <c r="H103" s="44"/>
+      <c r="I103" s="43">
+        <v>0</v>
+      </c>
+      <c r="J103" s="49"/>
+      <c r="K103" s="43"/>
+      <c r="L103" s="49"/>
+    </row>
+    <row r="104" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A104" s="43">
+        <f t="shared" si="4"/>
+        <v>1012600506</v>
+      </c>
+      <c r="B104" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C104" s="43">
+        <v>6</v>
+      </c>
+      <c r="D104" s="43">
+        <v>6</v>
+      </c>
+      <c r="E104" s="43"/>
+      <c r="F104" s="43">
+        <v>5</v>
+      </c>
+      <c r="G104" s="44">
+        <v>300</v>
+      </c>
+      <c r="H104" s="44"/>
+      <c r="I104" s="43">
+        <v>0</v>
+      </c>
+      <c r="J104" s="49"/>
+      <c r="K104" s="43"/>
+      <c r="L104" s="49"/>
+    </row>
+    <row r="105" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A105" s="43">
+        <f t="shared" si="4"/>
+        <v>1012400509</v>
+      </c>
+      <c r="B105" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C105" s="43">
+        <v>9</v>
+      </c>
+      <c r="D105" s="43">
+        <v>4</v>
+      </c>
+      <c r="E105" s="43"/>
+      <c r="F105" s="43">
+        <v>5</v>
+      </c>
+      <c r="G105" s="44">
+        <v>0</v>
+      </c>
+      <c r="H105" s="44"/>
+      <c r="I105" s="43">
+        <v>0</v>
+      </c>
+      <c r="J105" s="49"/>
+      <c r="K105" s="43">
+        <v>101200101</v>
+      </c>
+      <c r="L105" s="49"/>
+    </row>
+    <row r="106" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A106" s="43">
+        <f t="shared" si="4"/>
+        <v>1012400111</v>
+      </c>
+      <c r="B106" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C106" s="43">
+        <v>11</v>
+      </c>
+      <c r="D106" s="43">
+        <v>4</v>
+      </c>
+      <c r="E106" s="43"/>
+      <c r="F106" s="43">
+        <v>1</v>
+      </c>
+      <c r="G106" s="44">
+        <v>0</v>
+      </c>
+      <c r="H106" s="44">
+        <v>30120001</v>
+      </c>
+      <c r="I106" s="43">
+        <v>0</v>
+      </c>
+      <c r="J106" s="49"/>
+      <c r="K106" s="43"/>
+      <c r="L106" s="49" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="107" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A107" s="43">
+        <f t="shared" si="4"/>
+        <v>1012400112</v>
+      </c>
+      <c r="B107" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C107" s="43">
+        <v>12</v>
+      </c>
+      <c r="D107" s="43">
+        <v>4</v>
+      </c>
+      <c r="E107" s="43"/>
+      <c r="F107" s="43">
+        <v>1</v>
+      </c>
+      <c r="G107" s="44">
+        <v>0</v>
+      </c>
+      <c r="H107" s="44">
+        <v>30120002</v>
+      </c>
+      <c r="I107" s="43">
+        <v>0</v>
+      </c>
+      <c r="J107" s="49"/>
+      <c r="K107" s="43"/>
+      <c r="L107" s="49" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="108" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A108" s="43">
+        <f t="shared" si="4"/>
+        <v>1012400113</v>
+      </c>
+      <c r="B108" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C108" s="43">
+        <v>13</v>
+      </c>
+      <c r="D108" s="43">
+        <v>4</v>
+      </c>
+      <c r="E108" s="43"/>
+      <c r="F108" s="43">
+        <v>1</v>
+      </c>
+      <c r="G108" s="44">
+        <v>0</v>
+      </c>
+      <c r="H108" s="44">
+        <v>30120003</v>
+      </c>
+      <c r="I108" s="43">
+        <v>0</v>
+      </c>
+      <c r="J108" s="49"/>
+      <c r="K108" s="43"/>
+      <c r="L108" s="49" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="109" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A109" s="43">
+        <f t="shared" si="4"/>
+        <v>1012400114</v>
+      </c>
+      <c r="B109" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C109" s="43">
+        <v>14</v>
+      </c>
+      <c r="D109" s="43">
+        <v>4</v>
+      </c>
+      <c r="E109" s="43"/>
+      <c r="F109" s="43">
+        <v>1</v>
+      </c>
+      <c r="G109" s="44">
+        <v>0</v>
+      </c>
+      <c r="H109" s="44">
+        <v>30120004</v>
+      </c>
+      <c r="I109" s="43">
+        <v>0</v>
+      </c>
+      <c r="J109" s="49"/>
+      <c r="K109" s="43"/>
+      <c r="L109" s="49" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="110" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A110" s="43">
+        <f t="shared" si="4"/>
+        <v>1012400115</v>
+      </c>
+      <c r="B110" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C110" s="43">
+        <v>15</v>
+      </c>
+      <c r="D110" s="43">
+        <v>4</v>
+      </c>
+      <c r="E110" s="43"/>
+      <c r="F110" s="43">
+        <v>1</v>
+      </c>
+      <c r="G110" s="44">
+        <v>0</v>
+      </c>
+      <c r="H110" s="44">
+        <v>30120005</v>
+      </c>
+      <c r="I110" s="43">
+        <v>0</v>
+      </c>
+      <c r="J110" s="49"/>
+      <c r="K110" s="43"/>
+      <c r="L110" s="49" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="111" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A111" s="43">
+        <f t="shared" si="4"/>
+        <v>1012400116</v>
+      </c>
+      <c r="B111" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C111" s="43">
+        <v>16</v>
+      </c>
+      <c r="D111" s="43">
+        <v>4</v>
+      </c>
+      <c r="E111" s="43"/>
+      <c r="F111" s="43">
+        <v>1</v>
+      </c>
+      <c r="G111" s="44">
+        <v>0</v>
+      </c>
+      <c r="H111" s="44">
+        <v>30120006</v>
+      </c>
+      <c r="I111" s="43">
+        <v>0</v>
+      </c>
+      <c r="J111" s="49"/>
+      <c r="K111" s="43"/>
+      <c r="L111" s="49" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="112" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A112" s="43">
+        <f t="shared" si="4"/>
+        <v>1012400121</v>
+      </c>
+      <c r="B112" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C112" s="43">
+        <v>21</v>
+      </c>
+      <c r="D112" s="43">
+        <v>4</v>
+      </c>
+      <c r="E112" s="43"/>
+      <c r="F112" s="43">
+        <v>1</v>
+      </c>
+      <c r="G112" s="44">
+        <v>0</v>
+      </c>
+      <c r="H112" s="44">
+        <v>30120011</v>
+      </c>
+      <c r="I112" s="43">
+        <v>0</v>
+      </c>
+      <c r="J112" s="49"/>
+      <c r="K112" s="43"/>
+      <c r="L112" s="49" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="113" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A113" s="43">
+        <f t="shared" si="4"/>
+        <v>1012400122</v>
+      </c>
+      <c r="B113" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C113" s="43">
+        <v>22</v>
+      </c>
+      <c r="D113" s="43">
+        <v>4</v>
+      </c>
+      <c r="E113" s="43"/>
+      <c r="F113" s="43">
+        <v>1</v>
+      </c>
+      <c r="G113" s="44">
+        <v>0</v>
+      </c>
+      <c r="H113" s="44">
+        <v>30120012</v>
+      </c>
+      <c r="I113" s="43">
+        <v>0</v>
+      </c>
+      <c r="J113" s="49"/>
+      <c r="K113" s="43"/>
+      <c r="L113" s="49" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="114" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A114" s="43">
+        <f t="shared" si="4"/>
+        <v>1012400123</v>
+      </c>
+      <c r="B114" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C114" s="43">
+        <v>23</v>
+      </c>
+      <c r="D114" s="43">
+        <v>4</v>
+      </c>
+      <c r="E114" s="43"/>
+      <c r="F114" s="43">
+        <v>1</v>
+      </c>
+      <c r="G114" s="44">
+        <v>0</v>
+      </c>
+      <c r="H114" s="44">
+        <v>30120013</v>
+      </c>
+      <c r="I114" s="43">
+        <v>0</v>
+      </c>
+      <c r="J114" s="49"/>
+      <c r="K114" s="43"/>
+      <c r="L114" s="49" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="115" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A115" s="43">
+        <f t="shared" si="4"/>
+        <v>1012400124</v>
+      </c>
+      <c r="B115" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C115" s="43">
+        <v>24</v>
+      </c>
+      <c r="D115" s="43">
+        <v>4</v>
+      </c>
+      <c r="E115" s="43"/>
+      <c r="F115" s="43">
+        <v>1</v>
+      </c>
+      <c r="G115" s="44">
+        <v>0</v>
+      </c>
+      <c r="H115" s="44">
+        <v>30120014</v>
+      </c>
+      <c r="I115" s="43">
+        <v>0</v>
+      </c>
+      <c r="J115" s="49"/>
+      <c r="K115" s="43"/>
+      <c r="L115" s="49" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="116" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A116" s="43">
+        <f t="shared" si="4"/>
+        <v>1012400125</v>
+      </c>
+      <c r="B116" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C116" s="43">
+        <v>25</v>
+      </c>
+      <c r="D116" s="43">
+        <v>4</v>
+      </c>
+      <c r="E116" s="43"/>
+      <c r="F116" s="43">
+        <v>1</v>
+      </c>
+      <c r="G116" s="44">
+        <v>0</v>
+      </c>
+      <c r="H116" s="44">
+        <v>30120015</v>
+      </c>
+      <c r="I116" s="43">
+        <v>0</v>
+      </c>
+      <c r="J116" s="49"/>
+      <c r="K116" s="43"/>
+      <c r="L116" s="49" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="117" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A117" s="43">
+        <f t="shared" si="4"/>
+        <v>1012400126</v>
+      </c>
+      <c r="B117" s="43">
+        <v>101200</v>
+      </c>
+      <c r="C117" s="43">
+        <v>26</v>
+      </c>
+      <c r="D117" s="43">
+        <v>4</v>
+      </c>
+      <c r="E117" s="43"/>
+      <c r="F117" s="43">
+        <v>1</v>
+      </c>
+      <c r="G117" s="44">
+        <v>0</v>
+      </c>
+      <c r="H117" s="44">
+        <v>30120016</v>
+      </c>
+      <c r="I117" s="43">
+        <v>0</v>
+      </c>
+      <c r="J117" s="49"/>
+      <c r="K117" s="43"/>
+      <c r="L117" s="49" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="118" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A118" s="45">
+        <f t="shared" si="4"/>
+        <v>1012400131</v>
+      </c>
+      <c r="B118" s="45">
+        <v>101200</v>
+      </c>
+      <c r="C118" s="45">
+        <v>31</v>
+      </c>
+      <c r="D118" s="45">
+        <v>4</v>
+      </c>
+      <c r="E118" s="45"/>
+      <c r="F118" s="45">
+        <v>1</v>
+      </c>
+      <c r="G118" s="46">
+        <v>0</v>
+      </c>
+      <c r="H118" s="46">
+        <v>30120021</v>
+      </c>
+      <c r="I118" s="45">
+        <v>0</v>
+      </c>
+      <c r="J118" s="50"/>
+      <c r="K118" s="45"/>
+      <c r="L118" s="50" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="119" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A119" s="45">
+        <f t="shared" si="4"/>
+        <v>1012400132</v>
+      </c>
+      <c r="B119" s="45">
+        <v>101200</v>
+      </c>
+      <c r="C119" s="45">
+        <v>32</v>
+      </c>
+      <c r="D119" s="45">
+        <v>4</v>
+      </c>
+      <c r="E119" s="45"/>
+      <c r="F119" s="45">
+        <v>1</v>
+      </c>
+      <c r="G119" s="46">
+        <v>0</v>
+      </c>
+      <c r="H119" s="46">
+        <v>30120022</v>
+      </c>
+      <c r="I119" s="45">
+        <v>0</v>
+      </c>
+      <c r="J119" s="50"/>
+      <c r="K119" s="45"/>
+      <c r="L119" s="50" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="120" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A120" s="45">
+        <f t="shared" si="4"/>
+        <v>1012400133</v>
+      </c>
+      <c r="B120" s="45">
+        <v>101200</v>
+      </c>
+      <c r="C120" s="45">
+        <v>33</v>
+      </c>
+      <c r="D120" s="45">
+        <v>4</v>
+      </c>
+      <c r="E120" s="45"/>
+      <c r="F120" s="45">
+        <v>1</v>
+      </c>
+      <c r="G120" s="46">
+        <v>0</v>
+      </c>
+      <c r="H120" s="46">
+        <v>30120023</v>
+      </c>
+      <c r="I120" s="45">
+        <v>0</v>
+      </c>
+      <c r="J120" s="50"/>
+      <c r="K120" s="45"/>
+      <c r="L120" s="50" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="121" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A121" s="45">
+        <f t="shared" si="4"/>
+        <v>1012400134</v>
+      </c>
+      <c r="B121" s="45">
+        <v>101200</v>
+      </c>
+      <c r="C121" s="45">
+        <v>34</v>
+      </c>
+      <c r="D121" s="45">
+        <v>4</v>
+      </c>
+      <c r="E121" s="45"/>
+      <c r="F121" s="45">
+        <v>1</v>
+      </c>
+      <c r="G121" s="46">
+        <v>0</v>
+      </c>
+      <c r="H121" s="46">
+        <v>30120024</v>
+      </c>
+      <c r="I121" s="45">
+        <v>0</v>
+      </c>
+      <c r="J121" s="50"/>
+      <c r="K121" s="45"/>
+      <c r="L121" s="50" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="122" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A122" s="45">
+        <f t="shared" si="4"/>
+        <v>1012400135</v>
+      </c>
+      <c r="B122" s="45">
+        <v>101200</v>
+      </c>
+      <c r="C122" s="45">
+        <v>35</v>
+      </c>
+      <c r="D122" s="45">
+        <v>4</v>
+      </c>
+      <c r="E122" s="45"/>
+      <c r="F122" s="45">
+        <v>1</v>
+      </c>
+      <c r="G122" s="46">
+        <v>0</v>
+      </c>
+      <c r="H122" s="46">
+        <v>30120025</v>
+      </c>
+      <c r="I122" s="45">
+        <v>0</v>
+      </c>
+      <c r="J122" s="50"/>
+      <c r="K122" s="45"/>
+      <c r="L122" s="50" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="123" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A123" s="45">
+        <f t="shared" si="4"/>
+        <v>1012400136</v>
+      </c>
+      <c r="B123" s="45">
+        <v>101200</v>
+      </c>
+      <c r="C123" s="45">
+        <v>36</v>
+      </c>
+      <c r="D123" s="45">
+        <v>4</v>
+      </c>
+      <c r="E123" s="45"/>
+      <c r="F123" s="45">
+        <v>1</v>
+      </c>
+      <c r="G123" s="46">
+        <v>0</v>
+      </c>
+      <c r="H123" s="46">
+        <v>30120026</v>
+      </c>
+      <c r="I123" s="45">
+        <v>0</v>
+      </c>
+      <c r="J123" s="50"/>
+      <c r="K123" s="45"/>
+      <c r="L123" s="50" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="124" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A124" s="2">
+        <f t="shared" ref="A124:A134" si="5">(B124)*10000+C124+F124*100+D124*100000</f>
+        <v>1014500502</v>
+      </c>
+      <c r="B124" s="47">
+        <v>101400</v>
+      </c>
+      <c r="C124" s="47">
+        <v>2</v>
+      </c>
+      <c r="D124" s="47">
+        <v>5</v>
+      </c>
+      <c r="E124" s="47"/>
+      <c r="F124" s="47">
+        <v>5</v>
+      </c>
+      <c r="G124" s="48">
+        <v>1</v>
+      </c>
+      <c r="H124" s="48"/>
+      <c r="I124" s="2">
+        <v>0</v>
+      </c>
+      <c r="J124" s="51"/>
+      <c r="K124" s="47"/>
+      <c r="L124" s="13"/>
+    </row>
+    <row r="125" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A125" s="2">
+        <f t="shared" si="5"/>
+        <v>1014500503</v>
+      </c>
+      <c r="B125" s="47">
+        <v>101400</v>
+      </c>
+      <c r="C125" s="47">
+        <v>3</v>
+      </c>
+      <c r="D125" s="47">
+        <v>5</v>
+      </c>
+      <c r="E125" s="47"/>
+      <c r="F125" s="47">
+        <v>5</v>
+      </c>
+      <c r="G125" s="48">
+        <v>1</v>
+      </c>
+      <c r="H125" s="48"/>
+      <c r="I125" s="2">
+        <v>0</v>
+      </c>
+      <c r="J125" s="51"/>
+      <c r="K125" s="47"/>
+      <c r="L125" s="13"/>
+    </row>
+    <row r="126" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A126" s="2">
+        <f t="shared" si="5"/>
+        <v>1014500504</v>
+      </c>
+      <c r="B126" s="47">
+        <v>101400</v>
+      </c>
+      <c r="C126" s="47">
+        <v>4</v>
+      </c>
+      <c r="D126" s="47">
+        <v>5</v>
+      </c>
+      <c r="E126" s="47"/>
+      <c r="F126" s="47">
+        <v>5</v>
+      </c>
+      <c r="G126" s="48">
+        <v>1</v>
+      </c>
+      <c r="H126" s="48"/>
+      <c r="I126" s="2">
+        <v>0</v>
+      </c>
+      <c r="J126" s="51"/>
+      <c r="K126" s="47"/>
+      <c r="L126" s="13"/>
+    </row>
+    <row r="127" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A127" s="2">
+        <f t="shared" si="5"/>
+        <v>1014500505</v>
+      </c>
+      <c r="B127" s="47">
+        <v>101400</v>
+      </c>
+      <c r="C127" s="47">
+        <v>5</v>
+      </c>
+      <c r="D127" s="47">
+        <v>5</v>
+      </c>
+      <c r="E127" s="47"/>
+      <c r="F127" s="47">
+        <v>5</v>
+      </c>
+      <c r="G127" s="48">
+        <v>2</v>
+      </c>
+      <c r="H127" s="48"/>
+      <c r="I127" s="2">
+        <v>0</v>
+      </c>
+      <c r="J127" s="51"/>
+      <c r="K127" s="47"/>
+      <c r="L127" s="13"/>
+    </row>
+    <row r="128" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A128" s="2">
+        <f t="shared" si="5"/>
+        <v>1014500506</v>
+      </c>
+      <c r="B128" s="47">
+        <v>101400</v>
+      </c>
+      <c r="C128" s="47">
+        <v>6</v>
+      </c>
+      <c r="D128" s="47">
+        <v>5</v>
+      </c>
+      <c r="E128" s="47"/>
+      <c r="F128" s="47">
+        <v>5</v>
+      </c>
+      <c r="G128" s="48">
+        <v>2</v>
+      </c>
+      <c r="H128" s="48"/>
+      <c r="I128" s="2">
+        <v>0</v>
+      </c>
+      <c r="J128" s="51"/>
+      <c r="K128" s="47"/>
+      <c r="L128" s="13"/>
+    </row>
+    <row r="129" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A129" s="2">
+        <f t="shared" si="5"/>
+        <v>1014500507</v>
+      </c>
+      <c r="B129" s="47">
+        <v>101400</v>
+      </c>
+      <c r="C129" s="47">
+        <v>7</v>
+      </c>
+      <c r="D129" s="47">
+        <v>5</v>
+      </c>
+      <c r="E129" s="47"/>
+      <c r="F129" s="47">
+        <v>5</v>
+      </c>
+      <c r="G129" s="48">
+        <v>2</v>
+      </c>
+      <c r="H129" s="48"/>
+      <c r="I129" s="2">
+        <v>0</v>
+      </c>
+      <c r="J129" s="51"/>
+      <c r="K129" s="47"/>
+      <c r="L129" s="13"/>
+    </row>
+    <row r="130" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A130" s="2">
+        <f t="shared" si="5"/>
+        <v>1014500508</v>
+      </c>
+      <c r="B130" s="47">
+        <v>101400</v>
+      </c>
+      <c r="C130" s="47">
+        <v>8</v>
+      </c>
+      <c r="D130" s="47">
+        <v>5</v>
+      </c>
+      <c r="E130" s="47"/>
+      <c r="F130" s="47">
+        <v>5</v>
+      </c>
+      <c r="G130" s="48">
+        <v>3</v>
+      </c>
+      <c r="H130" s="48"/>
+      <c r="I130" s="2">
+        <v>0</v>
+      </c>
+      <c r="J130" s="51"/>
+      <c r="K130" s="47"/>
+      <c r="L130" s="13"/>
+    </row>
+    <row r="131" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A131" s="2">
+        <f t="shared" si="5"/>
+        <v>1014500509</v>
+      </c>
+      <c r="B131" s="47">
+        <v>101400</v>
+      </c>
+      <c r="C131" s="47">
+        <v>9</v>
+      </c>
+      <c r="D131" s="47">
+        <v>5</v>
+      </c>
+      <c r="E131" s="47"/>
+      <c r="F131" s="47">
+        <v>5</v>
+      </c>
+      <c r="G131" s="48">
+        <v>3</v>
+      </c>
+      <c r="H131" s="48"/>
+      <c r="I131" s="2">
+        <v>0</v>
+      </c>
+      <c r="J131" s="51"/>
+      <c r="K131" s="47"/>
+      <c r="L131" s="13"/>
+    </row>
+    <row r="132" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A132" s="2">
+        <f t="shared" si="5"/>
+        <v>1014500510</v>
+      </c>
+      <c r="B132" s="47">
+        <v>101400</v>
+      </c>
+      <c r="C132" s="47">
+        <v>10</v>
+      </c>
+      <c r="D132" s="47">
+        <v>5</v>
+      </c>
+      <c r="E132" s="47"/>
+      <c r="F132" s="47">
+        <v>5</v>
+      </c>
+      <c r="G132" s="48">
+        <v>4</v>
+      </c>
+      <c r="H132" s="48"/>
+      <c r="I132" s="2">
+        <v>0</v>
+      </c>
+      <c r="J132" s="51"/>
+      <c r="K132" s="47"/>
+      <c r="L132" s="13"/>
+    </row>
+    <row r="133" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A133" s="2">
+        <f t="shared" si="5"/>
+        <v>1014500511</v>
+      </c>
+      <c r="B133" s="47">
+        <v>101400</v>
+      </c>
+      <c r="C133" s="47">
+        <v>11</v>
+      </c>
+      <c r="D133" s="47">
+        <v>5</v>
+      </c>
+      <c r="E133" s="47"/>
+      <c r="F133" s="47">
+        <v>5</v>
+      </c>
+      <c r="G133" s="48">
+        <v>5</v>
+      </c>
+      <c r="H133" s="48"/>
+      <c r="I133" s="2">
+        <v>0</v>
+      </c>
+      <c r="J133" s="51"/>
+      <c r="K133" s="47"/>
+      <c r="L133" s="13"/>
+    </row>
+    <row r="134" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A134" s="2">
+        <f t="shared" si="5"/>
         <v>1014400513</v>
       </c>
-      <c r="B85" s="37">
+      <c r="B134" s="47">
         <v>101400</v>
       </c>
-      <c r="C85" s="8">
+      <c r="C134" s="47">
+        <v>13</v>
+      </c>
+      <c r="D134" s="47">
         <v>4</v>
       </c>
-      <c r="D85" s="37">
-        <v>13</v>
-      </c>
-      <c r="E85" s="37">
-        <v>4</v>
-      </c>
-      <c r="F85" s="37"/>
-      <c r="G85" s="37">
+      <c r="E134" s="47"/>
+      <c r="F134" s="47">
         <v>5</v>
       </c>
-      <c r="H85" s="38">
-        <v>0</v>
-      </c>
-      <c r="I85" s="38"/>
-      <c r="J85" s="37"/>
-      <c r="K85" s="39">
+      <c r="G134" s="48">
+        <v>0</v>
+      </c>
+      <c r="H134" s="48"/>
+      <c r="I134" s="2">
+        <v>0</v>
+      </c>
+      <c r="J134" s="51"/>
+      <c r="K134" s="52">
         <v>101400101</v>
       </c>
-      <c r="L85" s="10"/>
+      <c r="L134" s="13"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L85" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L134" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="0" priority="18">
+    <cfRule type="expression" dxfId="0" priority="103">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C43">
+  <conditionalFormatting sqref="D85:E85">
+    <cfRule type="expression" dxfId="0" priority="129">
+      <formula>MOD($B85,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D86:E86">
+    <cfRule type="expression" dxfId="0" priority="94">
+      <formula>MOD($B86,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A105">
+    <cfRule type="duplicateValues" dxfId="1" priority="75"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D105:E105">
+    <cfRule type="expression" dxfId="0" priority="74">
+      <formula>MOD($B105,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I105">
+    <cfRule type="expression" dxfId="0" priority="76">
+      <formula>MOD($B105,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A106">
+    <cfRule type="duplicateValues" dxfId="1" priority="71"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D106:E106">
+    <cfRule type="expression" dxfId="0" priority="70">
+      <formula>MOD($B106,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I106">
+    <cfRule type="expression" dxfId="0" priority="72">
+      <formula>MOD($B106,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A107">
+    <cfRule type="duplicateValues" dxfId="1" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D107:E107">
+    <cfRule type="expression" dxfId="0" priority="66">
+      <formula>MOD($B107,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I107">
+    <cfRule type="expression" dxfId="0" priority="68">
+      <formula>MOD($B107,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A108">
+    <cfRule type="duplicateValues" dxfId="1" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D108:E108">
+    <cfRule type="expression" dxfId="0" priority="62">
+      <formula>MOD($B108,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I108">
+    <cfRule type="expression" dxfId="0" priority="64">
+      <formula>MOD($B108,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A109">
+    <cfRule type="duplicateValues" dxfId="1" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D109:E109">
+    <cfRule type="expression" dxfId="0" priority="58">
+      <formula>MOD($B109,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I109">
+    <cfRule type="expression" dxfId="0" priority="60">
+      <formula>MOD($B109,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A110">
+    <cfRule type="duplicateValues" dxfId="1" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D110:E110">
+    <cfRule type="expression" dxfId="0" priority="54">
+      <formula>MOD($B110,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I110">
+    <cfRule type="expression" dxfId="0" priority="56">
+      <formula>MOD($B110,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A111">
+    <cfRule type="duplicateValues" dxfId="1" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D111:E111">
+    <cfRule type="expression" dxfId="0" priority="50">
+      <formula>MOD($B111,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I111">
+    <cfRule type="expression" dxfId="0" priority="52">
+      <formula>MOD($B111,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A112">
+    <cfRule type="duplicateValues" dxfId="1" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D112:E112">
+    <cfRule type="expression" dxfId="0" priority="46">
+      <formula>MOD($B112,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I112">
+    <cfRule type="expression" dxfId="0" priority="48">
+      <formula>MOD($B112,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A113">
+    <cfRule type="duplicateValues" dxfId="1" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D113:E113">
+    <cfRule type="expression" dxfId="0" priority="42">
+      <formula>MOD($B113,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I113">
+    <cfRule type="expression" dxfId="0" priority="44">
+      <formula>MOD($B113,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A114">
+    <cfRule type="duplicateValues" dxfId="1" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D114:E114">
+    <cfRule type="expression" dxfId="0" priority="38">
+      <formula>MOD($B114,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I114">
+    <cfRule type="expression" dxfId="0" priority="40">
+      <formula>MOD($B114,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A115">
+    <cfRule type="duplicateValues" dxfId="1" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D115:E115">
+    <cfRule type="expression" dxfId="0" priority="34">
+      <formula>MOD($B115,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I115">
+    <cfRule type="expression" dxfId="0" priority="36">
+      <formula>MOD($B115,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A116">
+    <cfRule type="duplicateValues" dxfId="1" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D116:E116">
+    <cfRule type="expression" dxfId="0" priority="30">
+      <formula>MOD($B116,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I116">
+    <cfRule type="expression" dxfId="0" priority="32">
+      <formula>MOD($B116,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A117">
+    <cfRule type="duplicateValues" dxfId="1" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D117:E117">
+    <cfRule type="expression" dxfId="0" priority="26">
+      <formula>MOD($B117,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I117">
+    <cfRule type="expression" dxfId="0" priority="28">
+      <formula>MOD($B117,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A118">
+    <cfRule type="duplicateValues" dxfId="1" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D118:E118">
+    <cfRule type="expression" dxfId="0" priority="22">
+      <formula>MOD($B118,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I118">
+    <cfRule type="expression" dxfId="0" priority="24">
+      <formula>MOD($B118,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A119">
+    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D119:E119">
+    <cfRule type="expression" dxfId="0" priority="18">
+      <formula>MOD($B119,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I119">
+    <cfRule type="expression" dxfId="0" priority="20">
+      <formula>MOD($B119,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A120">
+    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D120:E120">
+    <cfRule type="expression" dxfId="0" priority="14">
+      <formula>MOD($B120,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I120">
     <cfRule type="expression" dxfId="0" priority="16">
+      <formula>MOD($B120,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A121">
+    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D121:E121">
+    <cfRule type="expression" dxfId="0" priority="10">
+      <formula>MOD($B121,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I121">
+    <cfRule type="expression" dxfId="0" priority="12">
+      <formula>MOD($B121,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A122">
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D122:E122">
+    <cfRule type="expression" dxfId="0" priority="6">
+      <formula>MOD($B122,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I122">
+    <cfRule type="expression" dxfId="0" priority="8">
+      <formula>MOD($B122,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A123">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D123:E123">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>MOD($B123,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I123">
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>MOD($B123,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C134:L134">
+    <cfRule type="expression" dxfId="0" priority="130">
+      <formula>MOD($B134,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A48:A60">
+    <cfRule type="duplicateValues" dxfId="1" priority="91"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A87:A92">
+    <cfRule type="duplicateValues" dxfId="1" priority="85"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A93:A98">
+    <cfRule type="duplicateValues" dxfId="1" priority="82"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A99:A104">
+    <cfRule type="duplicateValues" dxfId="1" priority="79"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48:B60">
+    <cfRule type="expression" dxfId="0" priority="89">
+      <formula>MOD($B48,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C77:C84">
+    <cfRule type="expression" dxfId="0" priority="92">
+      <formula>MOD($B77,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K39:K42">
+    <cfRule type="duplicateValues" dxfId="2" priority="105"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="404"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:L4">
+    <cfRule type="expression" dxfId="0" priority="403">
+      <formula>MOD($B1,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B41:B42 B44:B47">
+    <cfRule type="expression" dxfId="0" priority="137">
+      <formula>MOD($B41,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 B135:L1048576">
+    <cfRule type="expression" dxfId="0" priority="402">
+      <formula>MOD($B41,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C43:G43 J43:L43">
+    <cfRule type="expression" dxfId="0" priority="102">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A48">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
-    <cfRule type="expression" dxfId="0" priority="4">
+  <conditionalFormatting sqref="C44:G44 J44:L47 G45:G47 C45:C47">
+    <cfRule type="expression" dxfId="0" priority="136">
+      <formula>MOD($B44,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D45:E47">
+    <cfRule type="expression" dxfId="0" priority="133">
+      <formula>MOD($B45,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F48:F60 C48:C60">
+    <cfRule type="expression" dxfId="0" priority="90">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C48">
-    <cfRule type="expression" dxfId="0" priority="2">
+  <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
+    <cfRule type="expression" dxfId="0" priority="88">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E48:F48">
-    <cfRule type="expression" dxfId="0" priority="1">
+  <conditionalFormatting sqref="D48:E60">
+    <cfRule type="expression" dxfId="0" priority="86">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E73:F73">
-    <cfRule type="expression" dxfId="0" priority="44">
-      <formula>MOD($B73,2)=1</formula>
+  <conditionalFormatting sqref="B77:B84 F77:L84">
+    <cfRule type="expression" dxfId="0" priority="132">
+      <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E74:F74">
-    <cfRule type="expression" dxfId="0" priority="9">
-      <formula>MOD($B74,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C85:L85">
-    <cfRule type="expression" dxfId="0" priority="45">
+  <conditionalFormatting sqref="B85:C85 F85:L85">
+    <cfRule type="expression" dxfId="0" priority="128">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D65:D72">
-    <cfRule type="expression" dxfId="0" priority="7">
-      <formula>MOD($B65,2)=1</formula>
+  <conditionalFormatting sqref="B86:C86 F86:L86">
+    <cfRule type="expression" dxfId="0" priority="93">
+      <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K39:K42">
-    <cfRule type="duplicateValues" dxfId="2" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A47 A49:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="319"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:L4">
-    <cfRule type="expression" dxfId="0" priority="318">
-      <formula>MOD($B1,2)=1</formula>
+  <conditionalFormatting sqref="B87:C92 F87:L92 I93:I104">
+    <cfRule type="expression" dxfId="0" priority="83">
+      <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C5:C42 C44:C47">
+  <conditionalFormatting sqref="D87:E92">
+    <cfRule type="expression" dxfId="0" priority="84">
+      <formula>MOD($B87,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B93:C98 F93:H98 J93:L98">
+    <cfRule type="expression" dxfId="0" priority="80">
+      <formula>MOD($B93,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D93:E98">
+    <cfRule type="expression" dxfId="0" priority="81">
+      <formula>MOD($B93,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B99:C104 F99:H104 J99:L104">
+    <cfRule type="expression" dxfId="0" priority="77">
+      <formula>MOD($B99,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D99:E104">
+    <cfRule type="expression" dxfId="0" priority="78">
+      <formula>MOD($B99,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B105:C105 F105:H105 J105:L105">
+    <cfRule type="expression" dxfId="0" priority="73">
+      <formula>MOD($B105,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B106:C106 F106:H106 J106:L106 H107:H111 C107:C111">
+    <cfRule type="expression" dxfId="0" priority="69">
+      <formula>MOD($B106,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B107 F107:G107 J107:L107">
+    <cfRule type="expression" dxfId="0" priority="65">
+      <formula>MOD($B107,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B108 F108:G108 J108:L108">
+    <cfRule type="expression" dxfId="0" priority="61">
+      <formula>MOD($B108,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B109 F109:G109 J109:L109">
+    <cfRule type="expression" dxfId="0" priority="57">
+      <formula>MOD($B109,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B110 F110:G110 J110:L110">
+    <cfRule type="expression" dxfId="0" priority="53">
+      <formula>MOD($B110,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B111 F111:G111 J111:L111">
     <cfRule type="expression" dxfId="0" priority="49">
-      <formula>MOD($B5,2)=1</formula>
+      <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D41:H42 J41:J42 L41:L42 G45:G47 D46:D47 B49:L64 E65:F72 B86:L1048576">
-    <cfRule type="expression" dxfId="0" priority="317">
-      <formula>MOD($B41,2)=1</formula>
+  <conditionalFormatting sqref="B112:C112 F112:H112 J112:L112 H113:H117 C113:C117">
+    <cfRule type="expression" dxfId="0" priority="45">
+      <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B41:B42 B44:B47">
-    <cfRule type="expression" dxfId="0" priority="52">
-      <formula>MOD($B41,2)=1</formula>
+  <conditionalFormatting sqref="B113 F113:G113 J113:L113">
+    <cfRule type="expression" dxfId="0" priority="41">
+      <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D43:H43 J43:L43">
+  <conditionalFormatting sqref="B114 F114:G114 J114:L114">
+    <cfRule type="expression" dxfId="0" priority="37">
+      <formula>MOD($B114,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B115 F115:G115 J115:L115">
+    <cfRule type="expression" dxfId="0" priority="33">
+      <formula>MOD($B115,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B116 F116:G116 J116:L116">
+    <cfRule type="expression" dxfId="0" priority="29">
+      <formula>MOD($B116,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B117 F117:G117 J117:L117">
+    <cfRule type="expression" dxfId="0" priority="25">
+      <formula>MOD($B117,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B118:C118 F118:H118 J118:L118 H119:H123 C119:C123">
+    <cfRule type="expression" dxfId="0" priority="21">
+      <formula>MOD($B118,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B119 F119:G119 J119:L119">
     <cfRule type="expression" dxfId="0" priority="17">
-      <formula>MOD($B43,2)=1</formula>
+      <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D44:H44 J44:L47 H45:H47 D45:D47">
-    <cfRule type="expression" dxfId="0" priority="51">
-      <formula>MOD($B44,2)=1</formula>
+  <conditionalFormatting sqref="B120 F120:G120 J120:L120">
+    <cfRule type="expression" dxfId="0" priority="13">
+      <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E45:F47">
-    <cfRule type="expression" dxfId="0" priority="48">
-      <formula>MOD($B45,2)=1</formula>
+  <conditionalFormatting sqref="B121 F121:G121 J121:L121">
+    <cfRule type="expression" dxfId="0" priority="9">
+      <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G48 D48">
+  <conditionalFormatting sqref="B122 F122:G122 J122:L122">
     <cfRule type="expression" dxfId="0" priority="5">
-      <formula>MOD($B48,2)=1</formula>
+      <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J48:L48 H48 D48">
-    <cfRule type="expression" dxfId="0" priority="3">
-      <formula>MOD($B48,2)=1</formula>
+  <conditionalFormatting sqref="B123 F123:G123 J123:L123">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B65:C72 G65:L72">
-    <cfRule type="expression" dxfId="0" priority="47">
-      <formula>MOD($B65,2)=1</formula>
+  <conditionalFormatting sqref="B124:L133 B134">
+    <cfRule type="expression" dxfId="0" priority="131">
+      <formula>MOD($B124,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B73:D73 G73:L73">
-    <cfRule type="expression" dxfId="0" priority="43">
-      <formula>MOD($B73,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B74:D74 G74:L74">
-    <cfRule type="expression" dxfId="0" priority="8">
-      <formula>MOD($B74,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B75:L84 B85">
-    <cfRule type="expression" dxfId="0" priority="46">
-      <formula>MOD($B75,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1">
-      <formula1>"普通,免费,重转,全部"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -286,7 +286,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="65">
   <si>
     <t>id</t>
   </si>
@@ -424,6 +424,9 @@
   </si>
   <si>
     <t>8_18</t>
+  </si>
+  <si>
+    <t>5个大财神</t>
   </si>
   <si>
     <t>横财神第1行</t>
@@ -721,12 +724,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -738,7 +741,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -7712,7 +7715,7 @@
     <row r="88" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A88" s="43">
         <f t="shared" ref="A88:A123" si="4">(B88)*10000+C88+F88*100+D88*100000</f>
-        <v>1012200302</v>
+        <v>1012100302</v>
       </c>
       <c r="B88" s="43">
         <v>101200</v>
@@ -7721,7 +7724,7 @@
         <v>2</v>
       </c>
       <c r="D88" s="43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" s="43"/>
       <c r="F88" s="43">
@@ -7741,7 +7744,7 @@
     <row r="89" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A89" s="43">
         <f t="shared" si="4"/>
-        <v>1012300303</v>
+        <v>1012100303</v>
       </c>
       <c r="B89" s="43">
         <v>101200</v>
@@ -7750,7 +7753,7 @@
         <v>3</v>
       </c>
       <c r="D89" s="43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E89" s="43"/>
       <c r="F89" s="43">
@@ -7770,7 +7773,7 @@
     <row r="90" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A90" s="43">
         <f t="shared" si="4"/>
-        <v>1012400304</v>
+        <v>1012100304</v>
       </c>
       <c r="B90" s="43">
         <v>101200</v>
@@ -7779,7 +7782,7 @@
         <v>4</v>
       </c>
       <c r="D90" s="43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E90" s="43"/>
       <c r="F90" s="43">
@@ -7799,7 +7802,7 @@
     <row r="91" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A91" s="43">
         <f t="shared" si="4"/>
-        <v>1012500305</v>
+        <v>1012100305</v>
       </c>
       <c r="B91" s="43">
         <v>101200</v>
@@ -7808,7 +7811,7 @@
         <v>5</v>
       </c>
       <c r="D91" s="43">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E91" s="43"/>
       <c r="F91" s="43">
@@ -7828,7 +7831,7 @@
     <row r="92" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A92" s="43">
         <f t="shared" si="4"/>
-        <v>1012600306</v>
+        <v>1012100306</v>
       </c>
       <c r="B92" s="43">
         <v>101200</v>
@@ -7837,7 +7840,7 @@
         <v>6</v>
       </c>
       <c r="D92" s="43">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E92" s="43"/>
       <c r="F92" s="43">
@@ -7886,7 +7889,7 @@
     <row r="94" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A94" s="43">
         <f t="shared" si="4"/>
-        <v>1012200402</v>
+        <v>1012100402</v>
       </c>
       <c r="B94" s="43">
         <v>101200</v>
@@ -7895,7 +7898,7 @@
         <v>2</v>
       </c>
       <c r="D94" s="43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" s="43"/>
       <c r="F94" s="43">
@@ -7915,7 +7918,7 @@
     <row r="95" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A95" s="43">
         <f t="shared" si="4"/>
-        <v>1012300403</v>
+        <v>1012100403</v>
       </c>
       <c r="B95" s="43">
         <v>101200</v>
@@ -7924,7 +7927,7 @@
         <v>3</v>
       </c>
       <c r="D95" s="43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E95" s="43"/>
       <c r="F95" s="43">
@@ -7944,7 +7947,7 @@
     <row r="96" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A96" s="43">
         <f t="shared" si="4"/>
-        <v>1012400404</v>
+        <v>1012100404</v>
       </c>
       <c r="B96" s="43">
         <v>101200</v>
@@ -7953,7 +7956,7 @@
         <v>4</v>
       </c>
       <c r="D96" s="43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E96" s="43"/>
       <c r="F96" s="43">
@@ -7973,7 +7976,7 @@
     <row r="97" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A97" s="43">
         <f t="shared" si="4"/>
-        <v>1012500405</v>
+        <v>1012100405</v>
       </c>
       <c r="B97" s="43">
         <v>101200</v>
@@ -7982,7 +7985,7 @@
         <v>5</v>
       </c>
       <c r="D97" s="43">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E97" s="43"/>
       <c r="F97" s="43">
@@ -8002,7 +8005,7 @@
     <row r="98" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A98" s="43">
         <f t="shared" si="4"/>
-        <v>1012600406</v>
+        <v>1012100406</v>
       </c>
       <c r="B98" s="43">
         <v>101200</v>
@@ -8011,7 +8014,7 @@
         <v>6</v>
       </c>
       <c r="D98" s="43">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E98" s="43"/>
       <c r="F98" s="43">
@@ -8060,7 +8063,7 @@
     <row r="100" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A100" s="43">
         <f t="shared" si="4"/>
-        <v>1012200502</v>
+        <v>1012100502</v>
       </c>
       <c r="B100" s="43">
         <v>101200</v>
@@ -8069,7 +8072,7 @@
         <v>2</v>
       </c>
       <c r="D100" s="43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" s="43"/>
       <c r="F100" s="43">
@@ -8089,7 +8092,7 @@
     <row r="101" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A101" s="43">
         <f t="shared" si="4"/>
-        <v>1012300503</v>
+        <v>1012100503</v>
       </c>
       <c r="B101" s="43">
         <v>101200</v>
@@ -8098,7 +8101,7 @@
         <v>3</v>
       </c>
       <c r="D101" s="43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E101" s="43"/>
       <c r="F101" s="43">
@@ -8118,7 +8121,7 @@
     <row r="102" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A102" s="43">
         <f t="shared" si="4"/>
-        <v>1012400504</v>
+        <v>1012100504</v>
       </c>
       <c r="B102" s="43">
         <v>101200</v>
@@ -8127,7 +8130,7 @@
         <v>4</v>
       </c>
       <c r="D102" s="43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E102" s="43"/>
       <c r="F102" s="43">
@@ -8147,7 +8150,7 @@
     <row r="103" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A103" s="43">
         <f t="shared" si="4"/>
-        <v>1012500505</v>
+        <v>1012100505</v>
       </c>
       <c r="B103" s="43">
         <v>101200</v>
@@ -8156,7 +8159,7 @@
         <v>5</v>
       </c>
       <c r="D103" s="43">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E103" s="43"/>
       <c r="F103" s="43">
@@ -8176,7 +8179,7 @@
     <row r="104" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A104" s="43">
         <f t="shared" si="4"/>
-        <v>1012600506</v>
+        <v>1012100506</v>
       </c>
       <c r="B104" s="43">
         <v>101200</v>
@@ -8185,7 +8188,7 @@
         <v>6</v>
       </c>
       <c r="D104" s="43">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E104" s="43"/>
       <c r="F104" s="43">
@@ -8231,7 +8234,9 @@
       <c r="K105" s="43">
         <v>101200101</v>
       </c>
-      <c r="L105" s="49"/>
+      <c r="L105" s="49" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="106" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A106" s="43">
@@ -8263,7 +8268,7 @@
       <c r="J106" s="49"/>
       <c r="K106" s="43"/>
       <c r="L106" s="49" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="107" s="7" customFormat="1" customHeight="1" spans="1:12">
@@ -8296,7 +8301,7 @@
       <c r="J107" s="49"/>
       <c r="K107" s="43"/>
       <c r="L107" s="49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="108" s="7" customFormat="1" customHeight="1" spans="1:12">
@@ -8329,7 +8334,7 @@
       <c r="J108" s="49"/>
       <c r="K108" s="43"/>
       <c r="L108" s="49" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="109" s="7" customFormat="1" customHeight="1" spans="1:12">
@@ -8362,7 +8367,7 @@
       <c r="J109" s="49"/>
       <c r="K109" s="43"/>
       <c r="L109" s="49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="110" s="7" customFormat="1" customHeight="1" spans="1:12">
@@ -8395,7 +8400,7 @@
       <c r="J110" s="49"/>
       <c r="K110" s="43"/>
       <c r="L110" s="49" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="111" s="7" customFormat="1" customHeight="1" spans="1:12">
@@ -8428,7 +8433,7 @@
       <c r="J111" s="49"/>
       <c r="K111" s="43"/>
       <c r="L111" s="49" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="112" s="7" customFormat="1" customHeight="1" spans="1:12">
@@ -8461,7 +8466,7 @@
       <c r="J112" s="49"/>
       <c r="K112" s="43"/>
       <c r="L112" s="49" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="113" s="7" customFormat="1" customHeight="1" spans="1:12">
@@ -8494,7 +8499,7 @@
       <c r="J113" s="49"/>
       <c r="K113" s="43"/>
       <c r="L113" s="49" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="114" s="7" customFormat="1" customHeight="1" spans="1:12">
@@ -8527,7 +8532,7 @@
       <c r="J114" s="49"/>
       <c r="K114" s="43"/>
       <c r="L114" s="49" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="115" s="7" customFormat="1" customHeight="1" spans="1:12">
@@ -8560,7 +8565,7 @@
       <c r="J115" s="49"/>
       <c r="K115" s="43"/>
       <c r="L115" s="49" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="116" s="7" customFormat="1" customHeight="1" spans="1:12">
@@ -8593,7 +8598,7 @@
       <c r="J116" s="49"/>
       <c r="K116" s="43"/>
       <c r="L116" s="49" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="117" s="7" customFormat="1" customHeight="1" spans="1:12">
@@ -8626,7 +8631,7 @@
       <c r="J117" s="49"/>
       <c r="K117" s="43"/>
       <c r="L117" s="49" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="118" s="8" customFormat="1" customHeight="1" spans="1:12">
@@ -8659,7 +8664,7 @@
       <c r="J118" s="50"/>
       <c r="K118" s="45"/>
       <c r="L118" s="50" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="119" s="8" customFormat="1" customHeight="1" spans="1:12">
@@ -8692,7 +8697,7 @@
       <c r="J119" s="50"/>
       <c r="K119" s="45"/>
       <c r="L119" s="50" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="120" s="8" customFormat="1" customHeight="1" spans="1:12">
@@ -8725,7 +8730,7 @@
       <c r="J120" s="50"/>
       <c r="K120" s="45"/>
       <c r="L120" s="50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="121" s="8" customFormat="1" customHeight="1" spans="1:12">
@@ -8758,7 +8763,7 @@
       <c r="J121" s="50"/>
       <c r="K121" s="45"/>
       <c r="L121" s="50" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="122" s="8" customFormat="1" customHeight="1" spans="1:12">
@@ -8791,7 +8796,7 @@
       <c r="J122" s="50"/>
       <c r="K122" s="45"/>
       <c r="L122" s="50" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="123" s="8" customFormat="1" customHeight="1" spans="1:12">
@@ -8824,7 +8829,7 @@
       <c r="J123" s="50"/>
       <c r="K123" s="45"/>
       <c r="L123" s="50" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="124" s="9" customFormat="1" customHeight="1" spans="1:12">
@@ -9441,6 +9446,16 @@
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E93:E98">
+    <cfRule type="expression" dxfId="0" priority="81">
+      <formula>MOD($B93,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E99:E104">
+    <cfRule type="expression" dxfId="0" priority="78">
+      <formula>MOD($B99,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K39:K42">
     <cfRule type="duplicateValues" dxfId="2" priority="105"/>
   </conditionalFormatting>
@@ -9512,7 +9527,7 @@
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D87:E92">
+  <conditionalFormatting sqref="D87:E92 D93:D104">
     <cfRule type="expression" dxfId="0" priority="84">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
@@ -9522,18 +9537,8 @@
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D93:E98">
-    <cfRule type="expression" dxfId="0" priority="81">
-      <formula>MOD($B93,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B99:C104 F99:H104 J99:L104">
     <cfRule type="expression" dxfId="0" priority="77">
-      <formula>MOD($B99,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D99:E104">
-    <cfRule type="expression" dxfId="0" priority="78">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -730,13 +730,13 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -724,7 +724,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -735,13 +741,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -6820,7 +6820,7 @@
     <row r="57" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A57" s="2">
         <f t="shared" si="2"/>
-        <v>1003100107</v>
+        <v>1003600107</v>
       </c>
       <c r="B57" s="3">
         <v>100300</v>
@@ -6829,7 +6829,7 @@
         <v>7</v>
       </c>
       <c r="D57" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3">
@@ -6853,7 +6853,7 @@
     <row r="58" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A58" s="2">
         <f t="shared" si="2"/>
-        <v>1003100108</v>
+        <v>1003600108</v>
       </c>
       <c r="B58" s="3">
         <v>100300</v>
@@ -6862,7 +6862,7 @@
         <v>8</v>
       </c>
       <c r="D58" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3">
@@ -6886,7 +6886,7 @@
     <row r="59" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A59" s="2">
         <f t="shared" si="2"/>
-        <v>1003100109</v>
+        <v>1003600109</v>
       </c>
       <c r="B59" s="3">
         <v>100300</v>
@@ -6895,7 +6895,7 @@
         <v>9</v>
       </c>
       <c r="D59" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3">
@@ -6919,7 +6919,7 @@
     <row r="60" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A60" s="2">
         <f t="shared" si="2"/>
-        <v>1003100110</v>
+        <v>1003600110</v>
       </c>
       <c r="B60" s="3">
         <v>100300</v>
@@ -6928,7 +6928,7 @@
         <v>10</v>
       </c>
       <c r="D60" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3">

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
@@ -281,12 +281,35 @@
         </r>
       </text>
     </comment>
+    <comment ref="J135" authorId="2">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+13是wild×2
+14是wild×5</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="65">
   <si>
     <t>id</t>
   </si>
@@ -724,23 +747,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4591,6 +4614,926 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9428167" cy="9611543"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="876300" y="32575500"/>
+          <a:ext cx="9427845" cy="9611360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9361385" cy="9524761"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="876300" y="32575500"/>
+          <a:ext cx="9361170" cy="9524365"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9371440" cy="9381886"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="876300" y="32575500"/>
+          <a:ext cx="9371330" cy="9381490"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9370910" cy="9508885"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="876300" y="32575500"/>
+          <a:ext cx="9370695" cy="9508490"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9370910" cy="9239011"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="876300" y="32575500"/>
+          <a:ext cx="9370695" cy="9238615"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9361170" cy="9789160"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="876300" y="32575500"/>
+          <a:ext cx="9361170" cy="9789160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9361170" cy="9789160"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="876300" y="32575500"/>
+          <a:ext cx="9361170" cy="9789160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9428167" cy="9611543"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="876300" y="32575500"/>
+          <a:ext cx="9427845" cy="9611360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9361170" cy="9789160"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="876300" y="32575500"/>
+          <a:ext cx="9361170" cy="9789160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9428167" cy="9611543"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="876300" y="32575500"/>
+          <a:ext cx="9427845" cy="9611360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9361170" cy="9789160"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="876300" y="32575500"/>
+          <a:ext cx="9361170" cy="9789160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9428167" cy="9611543"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="876300" y="32575500"/>
+          <a:ext cx="9427845" cy="9611360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9361170" cy="9789160"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="876300" y="32575500"/>
+          <a:ext cx="9361170" cy="9789160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9428167" cy="9611543"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="876300" y="32575500"/>
+          <a:ext cx="9427845" cy="9611360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9361170" cy="9524365"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="876300" y="32575500"/>
+          <a:ext cx="9361170" cy="9524365"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9371440" cy="9381886"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="876300" y="32575500"/>
+          <a:ext cx="9371330" cy="9381490"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9370910" cy="9508885"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="876300" y="32575500"/>
+          <a:ext cx="9370695" cy="9508490"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9370910" cy="9239011"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="876300" y="32575500"/>
+          <a:ext cx="9370695" cy="9238615"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9361170" cy="9789160"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="876300" y="32575500"/>
+          <a:ext cx="9361170" cy="9789160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9428167" cy="9611543"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="876300" y="32575500"/>
+          <a:ext cx="9427845" cy="9611360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4854,7 +5797,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L134"/>
+  <dimension ref="A1:L178"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="10"/>
@@ -4865,7 +5808,7 @@
     <col min="6" max="6" width="12.2166666666667" style="2" customWidth="1"/>
     <col min="7" max="7" width="9.85833333333333" style="11" customWidth="1"/>
     <col min="8" max="9" width="19.1333333333333" style="11" customWidth="1"/>
-    <col min="10" max="10" width="35.875" style="12" customWidth="1"/>
+    <col min="10" max="10" width="66.625" style="12" customWidth="1"/>
     <col min="11" max="11" width="10.375" style="2"/>
     <col min="12" max="12" width="14.5583333333333" style="13" customWidth="1"/>
     <col min="13" max="16384" width="9" style="10"/>
@@ -8834,7 +9777,7 @@
     </row>
     <row r="124" s="9" customFormat="1" customHeight="1" spans="1:12">
       <c r="A124" s="2">
-        <f t="shared" ref="A124:A134" si="5">(B124)*10000+C124+F124*100+D124*100000</f>
+        <f t="shared" ref="A124:A178" si="5">(B124)*10000+C124+F124*100+D124*100000</f>
         <v>1014500502</v>
       </c>
       <c r="B124" s="47">
@@ -9152,494 +10095,2129 @@
         <v>101400101</v>
       </c>
       <c r="L134" s="13"/>
+    </row>
+    <row r="135" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A135" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100211</v>
+      </c>
+      <c r="B135" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C135" s="2">
+        <v>11</v>
+      </c>
+      <c r="D135" s="2">
+        <v>1</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F135" s="2">
+        <v>2</v>
+      </c>
+      <c r="G135" s="2">
+        <v>2</v>
+      </c>
+      <c r="I135" s="2">
+        <v>0</v>
+      </c>
+      <c r="J135" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K135" s="2">
+        <v>0</v>
+      </c>
+      <c r="L135" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="136" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A136" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100301</v>
+      </c>
+      <c r="B136" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C136" s="2">
+        <v>1</v>
+      </c>
+      <c r="D136" s="2">
+        <v>1</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F136" s="2">
+        <v>3</v>
+      </c>
+      <c r="G136" s="2">
+        <v>5</v>
+      </c>
+      <c r="I136" s="2">
+        <v>0</v>
+      </c>
+      <c r="J136" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K136" s="2">
+        <v>0</v>
+      </c>
+      <c r="L136" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="137" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A137" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100302</v>
+      </c>
+      <c r="B137" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C137" s="2">
+        <v>2</v>
+      </c>
+      <c r="D137" s="2">
+        <v>1</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F137" s="2">
+        <v>3</v>
+      </c>
+      <c r="G137" s="2">
+        <v>5</v>
+      </c>
+      <c r="I137" s="2">
+        <v>0</v>
+      </c>
+      <c r="J137" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K137" s="2">
+        <v>0</v>
+      </c>
+      <c r="L137" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="138" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A138" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100303</v>
+      </c>
+      <c r="B138" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C138" s="2">
+        <v>3</v>
+      </c>
+      <c r="D138" s="2">
+        <v>1</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F138" s="2">
+        <v>3</v>
+      </c>
+      <c r="G138" s="2">
+        <v>5</v>
+      </c>
+      <c r="I138" s="2">
+        <v>0</v>
+      </c>
+      <c r="J138" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K138" s="2">
+        <v>0</v>
+      </c>
+      <c r="L138" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="139" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A139" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100304</v>
+      </c>
+      <c r="B139" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C139" s="2">
+        <v>4</v>
+      </c>
+      <c r="D139" s="2">
+        <v>1</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F139" s="2">
+        <v>3</v>
+      </c>
+      <c r="G139" s="2">
+        <v>5</v>
+      </c>
+      <c r="I139" s="2">
+        <v>0</v>
+      </c>
+      <c r="J139" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K139" s="2">
+        <v>0</v>
+      </c>
+      <c r="L139" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="140" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A140" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100305</v>
+      </c>
+      <c r="B140" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C140" s="2">
+        <v>5</v>
+      </c>
+      <c r="D140" s="2">
+        <v>1</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F140" s="2">
+        <v>3</v>
+      </c>
+      <c r="G140" s="2">
+        <v>5</v>
+      </c>
+      <c r="I140" s="2">
+        <v>0</v>
+      </c>
+      <c r="J140" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K140" s="2">
+        <v>0</v>
+      </c>
+      <c r="L140" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="141" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A141" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100306</v>
+      </c>
+      <c r="B141" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C141" s="2">
+        <v>6</v>
+      </c>
+      <c r="D141" s="2">
+        <v>1</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F141" s="2">
+        <v>3</v>
+      </c>
+      <c r="G141" s="2">
+        <v>5</v>
+      </c>
+      <c r="I141" s="2">
+        <v>0</v>
+      </c>
+      <c r="J141" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K141" s="2">
+        <v>0</v>
+      </c>
+      <c r="L141" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="142" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A142" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100307</v>
+      </c>
+      <c r="B142" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C142" s="2">
+        <v>7</v>
+      </c>
+      <c r="D142" s="2">
+        <v>1</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F142" s="2">
+        <v>3</v>
+      </c>
+      <c r="G142" s="2">
+        <v>10</v>
+      </c>
+      <c r="I142" s="2">
+        <v>0</v>
+      </c>
+      <c r="J142" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K142" s="2">
+        <v>0</v>
+      </c>
+      <c r="L142" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="143" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A143" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100308</v>
+      </c>
+      <c r="B143" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C143" s="2">
+        <v>8</v>
+      </c>
+      <c r="D143" s="2">
+        <v>1</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F143" s="2">
+        <v>3</v>
+      </c>
+      <c r="G143" s="2">
+        <v>10</v>
+      </c>
+      <c r="I143" s="2">
+        <v>0</v>
+      </c>
+      <c r="J143" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K143" s="2">
+        <v>0</v>
+      </c>
+      <c r="L143" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="144" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A144" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100309</v>
+      </c>
+      <c r="B144" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C144" s="2">
+        <v>9</v>
+      </c>
+      <c r="D144" s="2">
+        <v>1</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F144" s="2">
+        <v>3</v>
+      </c>
+      <c r="G144" s="2">
+        <v>15</v>
+      </c>
+      <c r="I144" s="2">
+        <v>0</v>
+      </c>
+      <c r="J144" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K144" s="2">
+        <v>0</v>
+      </c>
+      <c r="L144" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="145" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A145" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100310</v>
+      </c>
+      <c r="B145" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C145" s="2">
+        <v>10</v>
+      </c>
+      <c r="D145" s="2">
+        <v>1</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F145" s="2">
+        <v>3</v>
+      </c>
+      <c r="G145" s="2">
+        <v>15</v>
+      </c>
+      <c r="I145" s="2">
+        <v>0</v>
+      </c>
+      <c r="J145" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K145" s="2">
+        <v>0</v>
+      </c>
+      <c r="L145" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="146" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A146" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100311</v>
+      </c>
+      <c r="B146" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C146" s="2">
+        <v>11</v>
+      </c>
+      <c r="D146" s="2">
+        <v>1</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F146" s="2">
+        <v>3</v>
+      </c>
+      <c r="G146" s="2">
+        <v>20</v>
+      </c>
+      <c r="I146" s="2">
+        <v>0</v>
+      </c>
+      <c r="J146" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K146" s="2">
+        <v>0</v>
+      </c>
+      <c r="L146" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="147" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A147" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100401</v>
+      </c>
+      <c r="B147" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C147" s="2">
+        <v>1</v>
+      </c>
+      <c r="D147" s="2">
+        <v>1</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F147" s="2">
+        <v>4</v>
+      </c>
+      <c r="G147" s="2">
+        <v>15</v>
+      </c>
+      <c r="I147" s="2">
+        <v>0</v>
+      </c>
+      <c r="J147" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K147" s="2">
+        <v>0</v>
+      </c>
+      <c r="L147" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="148" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A148" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100402</v>
+      </c>
+      <c r="B148" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C148" s="2">
+        <v>2</v>
+      </c>
+      <c r="D148" s="2">
+        <v>1</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F148" s="2">
+        <v>4</v>
+      </c>
+      <c r="G148" s="2">
+        <v>15</v>
+      </c>
+      <c r="I148" s="2">
+        <v>0</v>
+      </c>
+      <c r="J148" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K148" s="2">
+        <v>0</v>
+      </c>
+      <c r="L148" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="149" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A149" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100403</v>
+      </c>
+      <c r="B149" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C149" s="2">
+        <v>3</v>
+      </c>
+      <c r="D149" s="2">
+        <v>1</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F149" s="2">
+        <v>4</v>
+      </c>
+      <c r="G149" s="2">
+        <v>15</v>
+      </c>
+      <c r="I149" s="2">
+        <v>0</v>
+      </c>
+      <c r="J149" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K149" s="2">
+        <v>0</v>
+      </c>
+      <c r="L149" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="150" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A150" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100404</v>
+      </c>
+      <c r="B150" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C150" s="2">
+        <v>4</v>
+      </c>
+      <c r="D150" s="2">
+        <v>1</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F150" s="2">
+        <v>4</v>
+      </c>
+      <c r="G150" s="2">
+        <v>15</v>
+      </c>
+      <c r="I150" s="2">
+        <v>0</v>
+      </c>
+      <c r="J150" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K150" s="2">
+        <v>0</v>
+      </c>
+      <c r="L150" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="151" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A151" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100405</v>
+      </c>
+      <c r="B151" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C151" s="2">
+        <v>5</v>
+      </c>
+      <c r="D151" s="2">
+        <v>1</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F151" s="2">
+        <v>4</v>
+      </c>
+      <c r="G151" s="2">
+        <v>15</v>
+      </c>
+      <c r="I151" s="2">
+        <v>0</v>
+      </c>
+      <c r="J151" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K151" s="2">
+        <v>0</v>
+      </c>
+      <c r="L151" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="152" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A152" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100406</v>
+      </c>
+      <c r="B152" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C152" s="2">
+        <v>6</v>
+      </c>
+      <c r="D152" s="2">
+        <v>1</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F152" s="2">
+        <v>4</v>
+      </c>
+      <c r="G152" s="2">
+        <v>15</v>
+      </c>
+      <c r="I152" s="2">
+        <v>0</v>
+      </c>
+      <c r="J152" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K152" s="2">
+        <v>0</v>
+      </c>
+      <c r="L152" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="153" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A153" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100407</v>
+      </c>
+      <c r="B153" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C153" s="2">
+        <v>7</v>
+      </c>
+      <c r="D153" s="2">
+        <v>1</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F153" s="2">
+        <v>4</v>
+      </c>
+      <c r="G153" s="2">
+        <v>25</v>
+      </c>
+      <c r="I153" s="2">
+        <v>0</v>
+      </c>
+      <c r="J153" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K153" s="2">
+        <v>0</v>
+      </c>
+      <c r="L153" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="154" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A154" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100408</v>
+      </c>
+      <c r="B154" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C154" s="2">
+        <v>8</v>
+      </c>
+      <c r="D154" s="2">
+        <v>1</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F154" s="2">
+        <v>4</v>
+      </c>
+      <c r="G154" s="2">
+        <v>25</v>
+      </c>
+      <c r="I154" s="2">
+        <v>0</v>
+      </c>
+      <c r="J154" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K154" s="2">
+        <v>0</v>
+      </c>
+      <c r="L154" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="155" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A155" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100409</v>
+      </c>
+      <c r="B155" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C155" s="2">
+        <v>9</v>
+      </c>
+      <c r="D155" s="2">
+        <v>1</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F155" s="2">
+        <v>4</v>
+      </c>
+      <c r="G155" s="2">
+        <v>30</v>
+      </c>
+      <c r="I155" s="2">
+        <v>0</v>
+      </c>
+      <c r="J155" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K155" s="2">
+        <v>0</v>
+      </c>
+      <c r="L155" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="156" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A156" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100410</v>
+      </c>
+      <c r="B156" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C156" s="2">
+        <v>10</v>
+      </c>
+      <c r="D156" s="2">
+        <v>1</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F156" s="2">
+        <v>4</v>
+      </c>
+      <c r="G156" s="2">
+        <v>30</v>
+      </c>
+      <c r="I156" s="2">
+        <v>0</v>
+      </c>
+      <c r="J156" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K156" s="2">
+        <v>0</v>
+      </c>
+      <c r="L156" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="157" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A157" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100411</v>
+      </c>
+      <c r="B157" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C157" s="2">
+        <v>11</v>
+      </c>
+      <c r="D157" s="2">
+        <v>1</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F157" s="2">
+        <v>4</v>
+      </c>
+      <c r="G157" s="2">
+        <v>50</v>
+      </c>
+      <c r="I157" s="2">
+        <v>0</v>
+      </c>
+      <c r="J157" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K157" s="2">
+        <v>0</v>
+      </c>
+      <c r="L157" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="158" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A158" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100501</v>
+      </c>
+      <c r="B158" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C158" s="2">
+        <v>1</v>
+      </c>
+      <c r="D158" s="2">
+        <v>1</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F158" s="2">
+        <v>5</v>
+      </c>
+      <c r="G158" s="2">
+        <v>50</v>
+      </c>
+      <c r="I158" s="2">
+        <v>0</v>
+      </c>
+      <c r="J158" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K158" s="2">
+        <v>0</v>
+      </c>
+      <c r="L158" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="159" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A159" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100502</v>
+      </c>
+      <c r="B159" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C159" s="2">
+        <v>2</v>
+      </c>
+      <c r="D159" s="2">
+        <v>1</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F159" s="2">
+        <v>5</v>
+      </c>
+      <c r="G159" s="2">
+        <v>50</v>
+      </c>
+      <c r="I159" s="2">
+        <v>0</v>
+      </c>
+      <c r="J159" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K159" s="2">
+        <v>0</v>
+      </c>
+      <c r="L159" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="160" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A160" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100503</v>
+      </c>
+      <c r="B160" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C160" s="2">
+        <v>3</v>
+      </c>
+      <c r="D160" s="2">
+        <v>1</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F160" s="2">
+        <v>5</v>
+      </c>
+      <c r="G160" s="2">
+        <v>50</v>
+      </c>
+      <c r="I160" s="2">
+        <v>0</v>
+      </c>
+      <c r="J160" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K160" s="2">
+        <v>0</v>
+      </c>
+      <c r="L160" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="161" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A161" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100504</v>
+      </c>
+      <c r="B161" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C161" s="2">
+        <v>4</v>
+      </c>
+      <c r="D161" s="2">
+        <v>1</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F161" s="2">
+        <v>5</v>
+      </c>
+      <c r="G161" s="2">
+        <v>50</v>
+      </c>
+      <c r="I161" s="2">
+        <v>0</v>
+      </c>
+      <c r="J161" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K161" s="2">
+        <v>0</v>
+      </c>
+      <c r="L161" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="162" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A162" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100505</v>
+      </c>
+      <c r="B162" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C162" s="2">
+        <v>5</v>
+      </c>
+      <c r="D162" s="2">
+        <v>1</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F162" s="2">
+        <v>5</v>
+      </c>
+      <c r="G162" s="2">
+        <v>50</v>
+      </c>
+      <c r="I162" s="2">
+        <v>0</v>
+      </c>
+      <c r="J162" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K162" s="2">
+        <v>0</v>
+      </c>
+      <c r="L162" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="163" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A163" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100506</v>
+      </c>
+      <c r="B163" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C163" s="2">
+        <v>6</v>
+      </c>
+      <c r="D163" s="2">
+        <v>1</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F163" s="2">
+        <v>5</v>
+      </c>
+      <c r="G163" s="2">
+        <v>50</v>
+      </c>
+      <c r="I163" s="2">
+        <v>0</v>
+      </c>
+      <c r="J163" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K163" s="2">
+        <v>0</v>
+      </c>
+      <c r="L163" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="164" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A164" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100507</v>
+      </c>
+      <c r="B164" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C164" s="2">
+        <v>7</v>
+      </c>
+      <c r="D164" s="2">
+        <v>1</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F164" s="2">
+        <v>5</v>
+      </c>
+      <c r="G164" s="2">
+        <v>100</v>
+      </c>
+      <c r="I164" s="2">
+        <v>0</v>
+      </c>
+      <c r="J164" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K164" s="2">
+        <v>0</v>
+      </c>
+      <c r="L164" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="165" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A165" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100508</v>
+      </c>
+      <c r="B165" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C165" s="2">
+        <v>8</v>
+      </c>
+      <c r="D165" s="2">
+        <v>1</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F165" s="2">
+        <v>5</v>
+      </c>
+      <c r="G165" s="2">
+        <v>100</v>
+      </c>
+      <c r="I165" s="2">
+        <v>0</v>
+      </c>
+      <c r="J165" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K165" s="2">
+        <v>0</v>
+      </c>
+      <c r="L165" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="166" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A166" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100509</v>
+      </c>
+      <c r="B166" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C166" s="2">
+        <v>9</v>
+      </c>
+      <c r="D166" s="2">
+        <v>1</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F166" s="2">
+        <v>5</v>
+      </c>
+      <c r="G166" s="2">
+        <v>200</v>
+      </c>
+      <c r="I166" s="2">
+        <v>0</v>
+      </c>
+      <c r="J166" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K166" s="2">
+        <v>0</v>
+      </c>
+      <c r="L166" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="167" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A167" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100510</v>
+      </c>
+      <c r="B167" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C167" s="2">
+        <v>10</v>
+      </c>
+      <c r="D167" s="2">
+        <v>1</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F167" s="2">
+        <v>5</v>
+      </c>
+      <c r="G167" s="2">
+        <v>200</v>
+      </c>
+      <c r="I167" s="2">
+        <v>0</v>
+      </c>
+      <c r="J167" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K167" s="2">
+        <v>0</v>
+      </c>
+      <c r="L167" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="168" s="2" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
+      <c r="A168" s="2">
+        <f t="shared" si="5"/>
+        <v>1024100511</v>
+      </c>
+      <c r="B168" s="2">
+        <v>102400</v>
+      </c>
+      <c r="C168" s="2">
+        <v>11</v>
+      </c>
+      <c r="D168" s="2">
+        <v>1</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F168" s="2">
+        <v>5</v>
+      </c>
+      <c r="G168" s="2">
+        <v>300</v>
+      </c>
+      <c r="I168" s="2">
+        <v>0</v>
+      </c>
+      <c r="J168" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K168" s="2">
+        <v>0</v>
+      </c>
+      <c r="L168" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="169" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A169" s="2">
+        <f t="shared" si="5"/>
+        <v>1024201619</v>
+      </c>
+      <c r="B169" s="16">
+        <v>102400</v>
+      </c>
+      <c r="C169" s="16">
+        <v>19</v>
+      </c>
+      <c r="D169" s="16">
+        <v>2</v>
+      </c>
+      <c r="E169" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F169" s="16">
+        <v>16</v>
+      </c>
+      <c r="G169" s="16">
+        <v>0</v>
+      </c>
+      <c r="H169" s="17">
+        <v>30010001</v>
+      </c>
+      <c r="I169" s="2">
+        <v>0</v>
+      </c>
+      <c r="J169" s="37"/>
+      <c r="K169" s="38">
+        <v>102400101</v>
+      </c>
+      <c r="L169" s="37" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="170" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A170" s="2">
+        <f t="shared" si="5"/>
+        <v>1024201620</v>
+      </c>
+      <c r="B170" s="16">
+        <v>102400</v>
+      </c>
+      <c r="C170" s="16">
+        <v>20</v>
+      </c>
+      <c r="D170" s="16">
+        <v>2</v>
+      </c>
+      <c r="E170" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F170" s="16">
+        <v>16</v>
+      </c>
+      <c r="G170" s="16">
+        <v>0</v>
+      </c>
+      <c r="H170" s="17">
+        <v>30010002</v>
+      </c>
+      <c r="I170" s="2">
+        <v>0</v>
+      </c>
+      <c r="J170" s="37"/>
+      <c r="K170" s="38">
+        <v>102400102</v>
+      </c>
+      <c r="L170" s="37" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="171" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A171" s="2">
+        <f t="shared" si="5"/>
+        <v>1024201621</v>
+      </c>
+      <c r="B171" s="16">
+        <v>102400</v>
+      </c>
+      <c r="C171" s="16">
+        <v>21</v>
+      </c>
+      <c r="D171" s="16">
+        <v>2</v>
+      </c>
+      <c r="E171" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F171" s="16">
+        <v>16</v>
+      </c>
+      <c r="G171" s="18">
+        <v>0</v>
+      </c>
+      <c r="H171" s="17">
+        <v>30010003</v>
+      </c>
+      <c r="I171" s="2">
+        <v>0</v>
+      </c>
+      <c r="J171" s="37"/>
+      <c r="K171" s="38">
+        <v>102400103</v>
+      </c>
+      <c r="L171" s="37" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="172" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A172" s="2">
+        <f t="shared" si="5"/>
+        <v>1024201622</v>
+      </c>
+      <c r="B172" s="16">
+        <v>102400</v>
+      </c>
+      <c r="C172" s="16">
+        <v>22</v>
+      </c>
+      <c r="D172" s="16">
+        <v>2</v>
+      </c>
+      <c r="E172" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F172" s="16">
+        <v>16</v>
+      </c>
+      <c r="G172" s="18">
+        <v>0</v>
+      </c>
+      <c r="H172" s="17">
+        <v>30010004</v>
+      </c>
+      <c r="I172" s="2">
+        <v>0</v>
+      </c>
+      <c r="J172" s="37"/>
+      <c r="K172" s="38">
+        <v>102400104</v>
+      </c>
+      <c r="L172" s="37" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="173" customHeight="1" spans="1:12">
+      <c r="A173" s="2">
+        <f t="shared" si="5"/>
+        <v>1024201628</v>
+      </c>
+      <c r="B173" s="19">
+        <v>102400</v>
+      </c>
+      <c r="C173" s="19">
+        <v>28</v>
+      </c>
+      <c r="D173" s="19">
+        <v>2</v>
+      </c>
+      <c r="E173" s="19"/>
+      <c r="F173" s="19">
+        <v>16</v>
+      </c>
+      <c r="G173" s="20">
+        <v>0</v>
+      </c>
+      <c r="H173" s="21">
+        <v>30010005</v>
+      </c>
+      <c r="I173" s="2">
+        <v>0</v>
+      </c>
+      <c r="J173" s="39"/>
+      <c r="K173" s="19">
+        <v>0</v>
+      </c>
+      <c r="L173" s="39" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="174" customHeight="1" spans="1:12">
+      <c r="A174" s="2">
+        <f t="shared" si="5"/>
+        <v>1024201528</v>
+      </c>
+      <c r="B174" s="22">
+        <v>102400</v>
+      </c>
+      <c r="C174" s="22">
+        <v>28</v>
+      </c>
+      <c r="D174" s="22">
+        <v>2</v>
+      </c>
+      <c r="E174" s="22"/>
+      <c r="F174" s="22">
+        <v>15</v>
+      </c>
+      <c r="G174" s="23">
+        <v>0</v>
+      </c>
+      <c r="H174" s="24">
+        <v>30010006</v>
+      </c>
+      <c r="I174" s="2">
+        <v>0</v>
+      </c>
+      <c r="J174" s="40"/>
+      <c r="K174" s="22">
+        <v>0</v>
+      </c>
+      <c r="L174" s="40" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="175" customHeight="1" spans="1:12">
+      <c r="A175" s="2">
+        <f t="shared" si="5"/>
+        <v>1024400317</v>
+      </c>
+      <c r="B175" s="25">
+        <v>102400</v>
+      </c>
+      <c r="C175" s="25">
+        <v>17</v>
+      </c>
+      <c r="D175" s="25">
+        <v>4</v>
+      </c>
+      <c r="E175" s="25"/>
+      <c r="F175" s="25">
+        <v>3</v>
+      </c>
+      <c r="G175" s="26">
+        <v>0</v>
+      </c>
+      <c r="H175" s="27"/>
+      <c r="I175" s="2">
+        <v>0</v>
+      </c>
+      <c r="J175" s="41"/>
+      <c r="K175" s="25">
+        <v>0</v>
+      </c>
+      <c r="L175" s="41" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="176" customHeight="1" spans="1:12">
+      <c r="A176" s="2">
+        <f t="shared" si="5"/>
+        <v>1024400417</v>
+      </c>
+      <c r="B176" s="28">
+        <v>102400</v>
+      </c>
+      <c r="C176" s="28">
+        <v>17</v>
+      </c>
+      <c r="D176" s="28">
+        <v>4</v>
+      </c>
+      <c r="E176" s="28"/>
+      <c r="F176" s="28">
+        <v>4</v>
+      </c>
+      <c r="G176" s="29">
+        <v>0</v>
+      </c>
+      <c r="H176" s="30"/>
+      <c r="I176" s="2">
+        <v>0</v>
+      </c>
+      <c r="J176" s="42"/>
+      <c r="K176" s="28">
+        <v>0</v>
+      </c>
+      <c r="L176" s="42" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="177" customHeight="1" spans="1:12">
+      <c r="A177" s="2">
+        <f t="shared" si="5"/>
+        <v>1024400517</v>
+      </c>
+      <c r="B177" s="28">
+        <v>102400</v>
+      </c>
+      <c r="C177" s="28">
+        <v>17</v>
+      </c>
+      <c r="D177" s="28">
+        <v>4</v>
+      </c>
+      <c r="E177" s="28"/>
+      <c r="F177" s="28">
+        <v>5</v>
+      </c>
+      <c r="G177" s="29">
+        <v>0</v>
+      </c>
+      <c r="H177" s="30"/>
+      <c r="I177" s="2">
+        <v>0</v>
+      </c>
+      <c r="J177" s="42"/>
+      <c r="K177" s="28">
+        <v>0</v>
+      </c>
+      <c r="L177" s="42" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="178" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A178" s="2">
+        <f t="shared" si="5"/>
+        <v>1024400130</v>
+      </c>
+      <c r="B178" s="28">
+        <v>102400</v>
+      </c>
+      <c r="C178" s="28">
+        <v>30</v>
+      </c>
+      <c r="D178" s="28">
+        <v>4</v>
+      </c>
+      <c r="E178" s="28"/>
+      <c r="F178" s="28">
+        <v>1</v>
+      </c>
+      <c r="G178" s="29">
+        <v>0</v>
+      </c>
+      <c r="H178" s="30">
+        <v>30010007</v>
+      </c>
+      <c r="I178" s="2">
+        <v>0</v>
+      </c>
+      <c r="J178" s="42"/>
+      <c r="K178" s="28">
+        <v>0</v>
+      </c>
+      <c r="L178" s="42" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L134" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="0" priority="103">
+    <cfRule type="expression" dxfId="0" priority="116">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D85:E85">
-    <cfRule type="expression" dxfId="0" priority="129">
+    <cfRule type="expression" dxfId="0" priority="142">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D86:E86">
-    <cfRule type="expression" dxfId="0" priority="94">
+    <cfRule type="expression" dxfId="0" priority="107">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105">
-    <cfRule type="duplicateValues" dxfId="1" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105:E105">
-    <cfRule type="expression" dxfId="0" priority="74">
+    <cfRule type="expression" dxfId="0" priority="87">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I105">
-    <cfRule type="expression" dxfId="0" priority="76">
+    <cfRule type="expression" dxfId="0" priority="89">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A106">
-    <cfRule type="duplicateValues" dxfId="1" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D106:E106">
-    <cfRule type="expression" dxfId="0" priority="70">
+    <cfRule type="expression" dxfId="0" priority="83">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I106">
-    <cfRule type="expression" dxfId="0" priority="72">
+    <cfRule type="expression" dxfId="0" priority="85">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="1" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D107:E107">
-    <cfRule type="expression" dxfId="0" priority="66">
+    <cfRule type="expression" dxfId="0" priority="79">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I107">
-    <cfRule type="expression" dxfId="0" priority="68">
+    <cfRule type="expression" dxfId="0" priority="81">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108">
-    <cfRule type="duplicateValues" dxfId="1" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D108:E108">
-    <cfRule type="expression" dxfId="0" priority="62">
+    <cfRule type="expression" dxfId="0" priority="75">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I108">
-    <cfRule type="expression" dxfId="0" priority="64">
+    <cfRule type="expression" dxfId="0" priority="77">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" dxfId="1" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D109:E109">
-    <cfRule type="expression" dxfId="0" priority="58">
+    <cfRule type="expression" dxfId="0" priority="71">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I109">
-    <cfRule type="expression" dxfId="0" priority="60">
+    <cfRule type="expression" dxfId="0" priority="73">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110">
-    <cfRule type="duplicateValues" dxfId="1" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D110:E110">
-    <cfRule type="expression" dxfId="0" priority="54">
+    <cfRule type="expression" dxfId="0" priority="67">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I110">
-    <cfRule type="expression" dxfId="0" priority="56">
+    <cfRule type="expression" dxfId="0" priority="69">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A111">
-    <cfRule type="duplicateValues" dxfId="1" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D111:E111">
-    <cfRule type="expression" dxfId="0" priority="50">
+    <cfRule type="expression" dxfId="0" priority="63">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I111">
-    <cfRule type="expression" dxfId="0" priority="52">
+    <cfRule type="expression" dxfId="0" priority="65">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112">
-    <cfRule type="duplicateValues" dxfId="1" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D112:E112">
-    <cfRule type="expression" dxfId="0" priority="46">
+    <cfRule type="expression" dxfId="0" priority="59">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I112">
-    <cfRule type="expression" dxfId="0" priority="48">
+    <cfRule type="expression" dxfId="0" priority="61">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A113">
-    <cfRule type="duplicateValues" dxfId="1" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D113:E113">
-    <cfRule type="expression" dxfId="0" priority="42">
+    <cfRule type="expression" dxfId="0" priority="55">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I113">
-    <cfRule type="expression" dxfId="0" priority="44">
+    <cfRule type="expression" dxfId="0" priority="57">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114">
-    <cfRule type="duplicateValues" dxfId="1" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D114:E114">
-    <cfRule type="expression" dxfId="0" priority="38">
+    <cfRule type="expression" dxfId="0" priority="51">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I114">
-    <cfRule type="expression" dxfId="0" priority="40">
+    <cfRule type="expression" dxfId="0" priority="53">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A115">
-    <cfRule type="duplicateValues" dxfId="1" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D115:E115">
-    <cfRule type="expression" dxfId="0" priority="34">
+    <cfRule type="expression" dxfId="0" priority="47">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I115">
-    <cfRule type="expression" dxfId="0" priority="36">
+    <cfRule type="expression" dxfId="0" priority="49">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A116">
-    <cfRule type="duplicateValues" dxfId="1" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D116:E116">
-    <cfRule type="expression" dxfId="0" priority="30">
+    <cfRule type="expression" dxfId="0" priority="43">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I116">
-    <cfRule type="expression" dxfId="0" priority="32">
+    <cfRule type="expression" dxfId="0" priority="45">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117">
-    <cfRule type="duplicateValues" dxfId="1" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D117:E117">
-    <cfRule type="expression" dxfId="0" priority="26">
+    <cfRule type="expression" dxfId="0" priority="39">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I117">
-    <cfRule type="expression" dxfId="0" priority="28">
+    <cfRule type="expression" dxfId="0" priority="41">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A118">
-    <cfRule type="duplicateValues" dxfId="1" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D118:E118">
-    <cfRule type="expression" dxfId="0" priority="22">
+    <cfRule type="expression" dxfId="0" priority="35">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I118">
-    <cfRule type="expression" dxfId="0" priority="24">
+    <cfRule type="expression" dxfId="0" priority="37">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A119">
-    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D119:E119">
-    <cfRule type="expression" dxfId="0" priority="18">
+    <cfRule type="expression" dxfId="0" priority="31">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I119">
-    <cfRule type="expression" dxfId="0" priority="20">
+    <cfRule type="expression" dxfId="0" priority="33">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A120">
-    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D120:E120">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="0" priority="27">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I120">
-    <cfRule type="expression" dxfId="0" priority="16">
+    <cfRule type="expression" dxfId="0" priority="29">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A121">
-    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D121:E121">
-    <cfRule type="expression" dxfId="0" priority="10">
+    <cfRule type="expression" dxfId="0" priority="23">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I121">
-    <cfRule type="expression" dxfId="0" priority="12">
+    <cfRule type="expression" dxfId="0" priority="25">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A122">
-    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D122:E122">
-    <cfRule type="expression" dxfId="0" priority="6">
+    <cfRule type="expression" dxfId="0" priority="19">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I122">
-    <cfRule type="expression" dxfId="0" priority="8">
+    <cfRule type="expression" dxfId="0" priority="21">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A123">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D123:E123">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="0" priority="15">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I123">
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="0" priority="17">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C134:L134">
-    <cfRule type="expression" dxfId="0" priority="130">
+    <cfRule type="expression" dxfId="0" priority="143">
       <formula>MOD($B134,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B173">
+    <cfRule type="expression" dxfId="0" priority="7">
+      <formula>MOD($B173,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A178">
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B178">
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>MOD($B178,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D178:E178">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD($B178,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A48:A60">
-    <cfRule type="duplicateValues" dxfId="1" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A87:A92">
-    <cfRule type="duplicateValues" dxfId="1" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A93:A98">
-    <cfRule type="duplicateValues" dxfId="1" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99:A104">
-    <cfRule type="duplicateValues" dxfId="1" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="92"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A135:A177">
+    <cfRule type="duplicateValues" dxfId="1" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B60">
-    <cfRule type="expression" dxfId="0" priority="89">
+    <cfRule type="expression" dxfId="0" priority="102">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C84">
-    <cfRule type="expression" dxfId="0" priority="92">
+    <cfRule type="expression" dxfId="0" priority="105">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E93:E98">
-    <cfRule type="expression" dxfId="0" priority="81">
+    <cfRule type="expression" dxfId="0" priority="94">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E99:E104">
-    <cfRule type="expression" dxfId="0" priority="78">
+    <cfRule type="expression" dxfId="0" priority="91">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39:K42">
-    <cfRule type="duplicateValues" dxfId="2" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="118"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="404"/>
+  <conditionalFormatting sqref="K169:K172">
+    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="417"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L4">
-    <cfRule type="expression" dxfId="0" priority="403">
+    <cfRule type="expression" dxfId="0" priority="416">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41:B42 B44:B47">
-    <cfRule type="expression" dxfId="0" priority="137">
+    <cfRule type="expression" dxfId="0" priority="150">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 B135:L1048576">
-    <cfRule type="expression" dxfId="0" priority="402">
+  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 B179:L1048576">
+    <cfRule type="expression" dxfId="0" priority="415">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43:G43 J43:L43">
-    <cfRule type="expression" dxfId="0" priority="102">
+    <cfRule type="expression" dxfId="0" priority="115">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44:G44 J44:L47 G45:G47 C45:C47">
-    <cfRule type="expression" dxfId="0" priority="136">
+    <cfRule type="expression" dxfId="0" priority="149">
       <formula>MOD($B44,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45:E47">
-    <cfRule type="expression" dxfId="0" priority="133">
+    <cfRule type="expression" dxfId="0" priority="146">
       <formula>MOD($B45,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F60 C48:C60">
-    <cfRule type="expression" dxfId="0" priority="90">
+    <cfRule type="expression" dxfId="0" priority="103">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
-    <cfRule type="expression" dxfId="0" priority="88">
+    <cfRule type="expression" dxfId="0" priority="101">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D48:E60">
-    <cfRule type="expression" dxfId="0" priority="86">
+    <cfRule type="expression" dxfId="0" priority="99">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B77:B84 F77:L84">
-    <cfRule type="expression" dxfId="0" priority="132">
+    <cfRule type="expression" dxfId="0" priority="145">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85:C85 F85:L85">
-    <cfRule type="expression" dxfId="0" priority="128">
+    <cfRule type="expression" dxfId="0" priority="141">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B86:C86 F86:L86">
-    <cfRule type="expression" dxfId="0" priority="93">
+    <cfRule type="expression" dxfId="0" priority="106">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87:C92 F87:L92 I93:I104">
-    <cfRule type="expression" dxfId="0" priority="83">
+    <cfRule type="expression" dxfId="0" priority="96">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87:E92 D93:D104">
-    <cfRule type="expression" dxfId="0" priority="84">
+    <cfRule type="expression" dxfId="0" priority="97">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:C98 F93:H98 J93:L98">
-    <cfRule type="expression" dxfId="0" priority="80">
+    <cfRule type="expression" dxfId="0" priority="93">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99:C104 F99:H104 J99:L104">
-    <cfRule type="expression" dxfId="0" priority="77">
+    <cfRule type="expression" dxfId="0" priority="90">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:C105 F105:H105 J105:L105">
-    <cfRule type="expression" dxfId="0" priority="73">
+    <cfRule type="expression" dxfId="0" priority="86">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106:C106 F106:H106 J106:L106 H107:H111 C107:C111">
-    <cfRule type="expression" dxfId="0" priority="69">
+    <cfRule type="expression" dxfId="0" priority="82">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107 F107:G107 J107:L107">
-    <cfRule type="expression" dxfId="0" priority="65">
+    <cfRule type="expression" dxfId="0" priority="78">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B108 F108:G108 J108:L108">
-    <cfRule type="expression" dxfId="0" priority="61">
+    <cfRule type="expression" dxfId="0" priority="74">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B109 F109:G109 J109:L109">
-    <cfRule type="expression" dxfId="0" priority="57">
+    <cfRule type="expression" dxfId="0" priority="70">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B110 F110:G110 J110:L110">
-    <cfRule type="expression" dxfId="0" priority="53">
+    <cfRule type="expression" dxfId="0" priority="66">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111 F111:G111 J111:L111">
-    <cfRule type="expression" dxfId="0" priority="49">
+    <cfRule type="expression" dxfId="0" priority="62">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112:C112 F112:H112 J112:L112 H113:H117 C113:C117">
-    <cfRule type="expression" dxfId="0" priority="45">
+    <cfRule type="expression" dxfId="0" priority="58">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113 F113:G113 J113:L113">
-    <cfRule type="expression" dxfId="0" priority="41">
+    <cfRule type="expression" dxfId="0" priority="54">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114 F114:G114 J114:L114">
-    <cfRule type="expression" dxfId="0" priority="37">
+    <cfRule type="expression" dxfId="0" priority="50">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115 F115:G115 J115:L115">
-    <cfRule type="expression" dxfId="0" priority="33">
+    <cfRule type="expression" dxfId="0" priority="46">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B116 F116:G116 J116:L116">
-    <cfRule type="expression" dxfId="0" priority="29">
+    <cfRule type="expression" dxfId="0" priority="42">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117 F117:G117 J117:L117">
-    <cfRule type="expression" dxfId="0" priority="25">
+    <cfRule type="expression" dxfId="0" priority="38">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118:C118 F118:H118 J118:L118 H119:H123 C119:C123">
-    <cfRule type="expression" dxfId="0" priority="21">
+    <cfRule type="expression" dxfId="0" priority="34">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119 F119:G119 J119:L119">
-    <cfRule type="expression" dxfId="0" priority="17">
+    <cfRule type="expression" dxfId="0" priority="30">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120 F120:G120 J120:L120">
-    <cfRule type="expression" dxfId="0" priority="13">
+    <cfRule type="expression" dxfId="0" priority="26">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121 F121:G121 J121:L121">
-    <cfRule type="expression" dxfId="0" priority="9">
+    <cfRule type="expression" dxfId="0" priority="22">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122 F122:G122 J122:L122">
-    <cfRule type="expression" dxfId="0" priority="5">
+    <cfRule type="expression" dxfId="0" priority="18">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123 F123:G123 J123:L123">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="0" priority="14">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B124:L133 B134">
-    <cfRule type="expression" dxfId="0" priority="131">
+    <cfRule type="expression" dxfId="0" priority="144">
       <formula>MOD($B124,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B171:B172 B174:B177">
+    <cfRule type="expression" dxfId="0" priority="11">
+      <formula>MOD($B171,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C171:G172 J171:J172 L171:L172 F175:F177 C176:C177">
+    <cfRule type="expression" dxfId="0" priority="12">
+      <formula>MOD($B171,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C173:G173 J173:L173">
+    <cfRule type="expression" dxfId="0" priority="6">
+      <formula>MOD($B173,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C174:G174 J174:L177 G175:G177 C175:C177">
+    <cfRule type="expression" dxfId="0" priority="10">
+      <formula>MOD($B174,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D175:E177">
+    <cfRule type="expression" dxfId="0" priority="9">
+      <formula>MOD($B175,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F178 C178">
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>MOD($B178,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J178:L178 G178 C178">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$254</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="70">
   <si>
     <t>id</t>
   </si>
@@ -504,6 +504,21 @@
   </si>
   <si>
     <t>第3次_横财神第4列</t>
+  </si>
+  <si>
+    <t>MINI</t>
+  </si>
+  <si>
+    <t>MINOR</t>
+  </si>
+  <si>
+    <t>MAJOR</t>
+  </si>
+  <si>
+    <t>GRAND</t>
+  </si>
+  <si>
+    <t>13_1_3</t>
   </si>
 </sst>
 </file>
@@ -748,12 +763,13 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -763,7 +779,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -808,6 +823,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -827,12 +848,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1326,7 +1341,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1368,8 +1383,14 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1377,16 +1398,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1398,14 +1416,8 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1416,7 +1428,34 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1428,35 +1467,14 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1464,23 +1482,23 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="56">
@@ -5797,7 +5815,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L178"/>
+  <dimension ref="A1:L254"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="10"/>
@@ -5840,13 +5858,13 @@
       <c r="I1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="35" t="s">
+      <c r="J1" s="15" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="35" t="s">
+      <c r="L1" s="15" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5857,7 +5875,7 @@
       <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="16" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -5869,10 +5887,10 @@
       <c r="G2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="36" t="s">
+      <c r="I2" s="17" t="s">
         <v>11</v>
       </c>
       <c r="J2" s="12" t="s">
@@ -5905,7 +5923,7 @@
       <c r="H3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="36" t="s">
+      <c r="I3" s="17" t="s">
         <v>20</v>
       </c>
       <c r="J3" s="12" t="s">
@@ -5916,7 +5934,7 @@
       </c>
       <c r="L3" s="13"/>
     </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="10:12">
+    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="J4" s="12"/>
       <c r="L4" s="13"/>
     </row>
@@ -7149,35 +7167,35 @@
         <f t="shared" si="0"/>
         <v>1001201619</v>
       </c>
-      <c r="B39" s="16">
+      <c r="B39" s="18">
         <v>100100</v>
       </c>
-      <c r="C39" s="16">
+      <c r="C39" s="18">
         <v>19</v>
       </c>
-      <c r="D39" s="16">
+      <c r="D39" s="18">
         <v>2</v>
       </c>
-      <c r="E39" s="16" t="s">
+      <c r="E39" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="18">
         <v>16</v>
       </c>
-      <c r="G39" s="16">
-        <v>0</v>
-      </c>
-      <c r="H39" s="17">
+      <c r="G39" s="18">
+        <v>0</v>
+      </c>
+      <c r="H39" s="19">
         <v>30010001</v>
       </c>
       <c r="I39" s="2">
         <v>0</v>
       </c>
-      <c r="J39" s="37"/>
-      <c r="K39" s="38">
+      <c r="J39" s="20"/>
+      <c r="K39" s="21">
         <v>100100101</v>
       </c>
-      <c r="L39" s="37" t="s">
+      <c r="L39" s="20" t="s">
         <v>26</v>
       </c>
     </row>
@@ -7186,35 +7204,35 @@
         <f t="shared" si="0"/>
         <v>1001201620</v>
       </c>
-      <c r="B40" s="16">
+      <c r="B40" s="18">
         <v>100100</v>
       </c>
-      <c r="C40" s="16">
+      <c r="C40" s="18">
         <v>20</v>
       </c>
-      <c r="D40" s="16">
+      <c r="D40" s="18">
         <v>2</v>
       </c>
-      <c r="E40" s="16" t="s">
+      <c r="E40" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="18">
         <v>16</v>
       </c>
-      <c r="G40" s="16">
-        <v>0</v>
-      </c>
-      <c r="H40" s="17">
+      <c r="G40" s="18">
+        <v>0</v>
+      </c>
+      <c r="H40" s="19">
         <v>30010002</v>
       </c>
       <c r="I40" s="2">
         <v>0</v>
       </c>
-      <c r="J40" s="37"/>
-      <c r="K40" s="38">
+      <c r="J40" s="20"/>
+      <c r="K40" s="21">
         <v>100100102</v>
       </c>
-      <c r="L40" s="37" t="s">
+      <c r="L40" s="20" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7223,35 +7241,35 @@
         <f t="shared" si="0"/>
         <v>1001201621</v>
       </c>
-      <c r="B41" s="16">
+      <c r="B41" s="18">
         <v>100100</v>
       </c>
-      <c r="C41" s="16">
+      <c r="C41" s="18">
         <v>21</v>
       </c>
-      <c r="D41" s="16">
+      <c r="D41" s="18">
         <v>2</v>
       </c>
-      <c r="E41" s="16" t="s">
+      <c r="E41" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="F41" s="16">
+      <c r="F41" s="18">
         <v>16</v>
       </c>
-      <c r="G41" s="18">
-        <v>0</v>
-      </c>
-      <c r="H41" s="17">
+      <c r="G41" s="22">
+        <v>0</v>
+      </c>
+      <c r="H41" s="19">
         <v>30010003</v>
       </c>
       <c r="I41" s="2">
         <v>0</v>
       </c>
-      <c r="J41" s="37"/>
-      <c r="K41" s="38">
+      <c r="J41" s="20"/>
+      <c r="K41" s="21">
         <v>100100103</v>
       </c>
-      <c r="L41" s="37" t="s">
+      <c r="L41" s="20" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7260,35 +7278,35 @@
         <f t="shared" si="0"/>
         <v>1001201622</v>
       </c>
-      <c r="B42" s="16">
+      <c r="B42" s="18">
         <v>100100</v>
       </c>
-      <c r="C42" s="16">
+      <c r="C42" s="18">
         <v>22</v>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="18">
         <v>2</v>
       </c>
-      <c r="E42" s="16" t="s">
+      <c r="E42" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="18">
         <v>16</v>
       </c>
-      <c r="G42" s="18">
-        <v>0</v>
-      </c>
-      <c r="H42" s="17">
+      <c r="G42" s="22">
+        <v>0</v>
+      </c>
+      <c r="H42" s="19">
         <v>30010004</v>
       </c>
       <c r="I42" s="2">
         <v>0</v>
       </c>
-      <c r="J42" s="37"/>
-      <c r="K42" s="38">
+      <c r="J42" s="20"/>
+      <c r="K42" s="21">
         <v>100100104</v>
       </c>
-      <c r="L42" s="37" t="s">
+      <c r="L42" s="20" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7297,33 +7315,33 @@
         <f t="shared" ref="A43:A48" si="1">(B43)*10000+C43+F43*100+D43*100000</f>
         <v>1001201628</v>
       </c>
-      <c r="B43" s="19">
+      <c r="B43" s="23">
         <v>100100</v>
       </c>
-      <c r="C43" s="19">
+      <c r="C43" s="23">
         <v>28</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="23">
         <v>2</v>
       </c>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19">
+      <c r="E43" s="23"/>
+      <c r="F43" s="23">
         <v>16</v>
       </c>
-      <c r="G43" s="20">
-        <v>0</v>
-      </c>
-      <c r="H43" s="21">
+      <c r="G43" s="24">
+        <v>0</v>
+      </c>
+      <c r="H43" s="25">
         <v>30010005</v>
       </c>
       <c r="I43" s="2">
         <v>0</v>
       </c>
-      <c r="J43" s="39"/>
-      <c r="K43" s="19">
-        <v>0</v>
-      </c>
-      <c r="L43" s="39" t="s">
+      <c r="J43" s="26"/>
+      <c r="K43" s="23">
+        <v>0</v>
+      </c>
+      <c r="L43" s="26" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7332,33 +7350,33 @@
         <f t="shared" si="1"/>
         <v>1001201528</v>
       </c>
-      <c r="B44" s="22">
+      <c r="B44" s="27">
         <v>100100</v>
       </c>
-      <c r="C44" s="22">
+      <c r="C44" s="27">
         <v>28</v>
       </c>
-      <c r="D44" s="22">
+      <c r="D44" s="27">
         <v>2</v>
       </c>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22">
+      <c r="E44" s="27"/>
+      <c r="F44" s="27">
         <v>15</v>
       </c>
-      <c r="G44" s="23">
-        <v>0</v>
-      </c>
-      <c r="H44" s="24">
+      <c r="G44" s="28">
+        <v>0</v>
+      </c>
+      <c r="H44" s="29">
         <v>30010006</v>
       </c>
       <c r="I44" s="2">
         <v>0</v>
       </c>
-      <c r="J44" s="40"/>
-      <c r="K44" s="22">
-        <v>0</v>
-      </c>
-      <c r="L44" s="40" t="s">
+      <c r="J44" s="30"/>
+      <c r="K44" s="27">
+        <v>0</v>
+      </c>
+      <c r="L44" s="30" t="s">
         <v>31</v>
       </c>
     </row>
@@ -7367,31 +7385,31 @@
         <f t="shared" si="1"/>
         <v>1001400317</v>
       </c>
-      <c r="B45" s="25">
+      <c r="B45" s="31">
         <v>100100</v>
       </c>
-      <c r="C45" s="25">
+      <c r="C45" s="31">
         <v>17</v>
       </c>
-      <c r="D45" s="25">
+      <c r="D45" s="31">
         <v>4</v>
       </c>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25">
+      <c r="E45" s="31"/>
+      <c r="F45" s="31">
         <v>3</v>
       </c>
-      <c r="G45" s="26">
-        <v>0</v>
-      </c>
-      <c r="H45" s="27"/>
+      <c r="G45" s="32">
+        <v>0</v>
+      </c>
+      <c r="H45" s="33"/>
       <c r="I45" s="2">
         <v>0</v>
       </c>
-      <c r="J45" s="41"/>
-      <c r="K45" s="25">
-        <v>0</v>
-      </c>
-      <c r="L45" s="41" t="s">
+      <c r="J45" s="34"/>
+      <c r="K45" s="31">
+        <v>0</v>
+      </c>
+      <c r="L45" s="34" t="s">
         <v>32</v>
       </c>
     </row>
@@ -7400,31 +7418,31 @@
         <f t="shared" si="1"/>
         <v>1001400417</v>
       </c>
-      <c r="B46" s="28">
+      <c r="B46" s="35">
         <v>100100</v>
       </c>
-      <c r="C46" s="28">
+      <c r="C46" s="35">
         <v>17</v>
       </c>
-      <c r="D46" s="28">
+      <c r="D46" s="35">
         <v>4</v>
       </c>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28">
+      <c r="E46" s="35"/>
+      <c r="F46" s="35">
         <v>4</v>
       </c>
-      <c r="G46" s="29">
-        <v>0</v>
-      </c>
-      <c r="H46" s="30"/>
+      <c r="G46" s="36">
+        <v>0</v>
+      </c>
+      <c r="H46" s="37"/>
       <c r="I46" s="2">
         <v>0</v>
       </c>
-      <c r="J46" s="42"/>
-      <c r="K46" s="28">
-        <v>0</v>
-      </c>
-      <c r="L46" s="42" t="s">
+      <c r="J46" s="38"/>
+      <c r="K46" s="35">
+        <v>0</v>
+      </c>
+      <c r="L46" s="38" t="s">
         <v>33</v>
       </c>
     </row>
@@ -7433,31 +7451,31 @@
         <f t="shared" si="1"/>
         <v>1001400517</v>
       </c>
-      <c r="B47" s="28">
+      <c r="B47" s="35">
         <v>100100</v>
       </c>
-      <c r="C47" s="28">
+      <c r="C47" s="35">
         <v>17</v>
       </c>
-      <c r="D47" s="28">
+      <c r="D47" s="35">
         <v>4</v>
       </c>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28">
+      <c r="E47" s="35"/>
+      <c r="F47" s="35">
         <v>5</v>
       </c>
-      <c r="G47" s="29">
-        <v>0</v>
-      </c>
-      <c r="H47" s="30"/>
+      <c r="G47" s="36">
+        <v>0</v>
+      </c>
+      <c r="H47" s="37"/>
       <c r="I47" s="2">
         <v>0</v>
       </c>
-      <c r="J47" s="42"/>
-      <c r="K47" s="28">
-        <v>0</v>
-      </c>
-      <c r="L47" s="42" t="s">
+      <c r="J47" s="38"/>
+      <c r="K47" s="35">
+        <v>0</v>
+      </c>
+      <c r="L47" s="38" t="s">
         <v>34</v>
       </c>
     </row>
@@ -7466,33 +7484,33 @@
         <f t="shared" si="1"/>
         <v>1001400130</v>
       </c>
-      <c r="B48" s="28">
+      <c r="B48" s="35">
         <v>100100</v>
       </c>
-      <c r="C48" s="28">
+      <c r="C48" s="35">
         <v>30</v>
       </c>
-      <c r="D48" s="28">
+      <c r="D48" s="35">
         <v>4</v>
       </c>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28">
-        <v>1</v>
-      </c>
-      <c r="G48" s="29">
-        <v>0</v>
-      </c>
-      <c r="H48" s="30">
+      <c r="E48" s="35"/>
+      <c r="F48" s="35">
+        <v>1</v>
+      </c>
+      <c r="G48" s="36">
+        <v>0</v>
+      </c>
+      <c r="H48" s="37">
         <v>30010007</v>
       </c>
       <c r="I48" s="2">
         <v>0</v>
       </c>
-      <c r="J48" s="42"/>
-      <c r="K48" s="28">
-        <v>0</v>
-      </c>
-      <c r="L48" s="42" t="s">
+      <c r="J48" s="38"/>
+      <c r="K48" s="35">
+        <v>0</v>
+      </c>
+      <c r="L48" s="38" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7504,7 +7522,7 @@
       <c r="B49" s="3">
         <v>100300</v>
       </c>
-      <c r="C49" s="31">
+      <c r="C49" s="39">
         <v>1</v>
       </c>
       <c r="D49" s="3">
@@ -7514,10 +7532,10 @@
       <c r="F49" s="3">
         <v>3</v>
       </c>
-      <c r="G49" s="32">
-        <v>1</v>
-      </c>
-      <c r="H49" s="33"/>
+      <c r="G49" s="40">
+        <v>1</v>
+      </c>
+      <c r="H49" s="41"/>
       <c r="I49" s="2">
         <v>1</v>
       </c>
@@ -7537,7 +7555,7 @@
       <c r="B50" s="3">
         <v>100300</v>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="39">
         <v>2</v>
       </c>
       <c r="D50" s="3">
@@ -7547,10 +7565,10 @@
       <c r="F50" s="3">
         <v>3</v>
       </c>
-      <c r="G50" s="32">
+      <c r="G50" s="40">
         <v>2</v>
       </c>
-      <c r="H50" s="33"/>
+      <c r="H50" s="41"/>
       <c r="I50" s="2">
         <v>1</v>
       </c>
@@ -7570,7 +7588,7 @@
       <c r="B51" s="3">
         <v>100300</v>
       </c>
-      <c r="C51" s="31">
+      <c r="C51" s="39">
         <v>3</v>
       </c>
       <c r="D51" s="3">
@@ -7580,10 +7598,10 @@
       <c r="F51" s="3">
         <v>3</v>
       </c>
-      <c r="G51" s="32">
+      <c r="G51" s="40">
         <v>5</v>
       </c>
-      <c r="H51" s="33"/>
+      <c r="H51" s="41"/>
       <c r="I51" s="2">
         <v>1</v>
       </c>
@@ -7603,7 +7621,7 @@
       <c r="B52" s="3">
         <v>100300</v>
       </c>
-      <c r="C52" s="31">
+      <c r="C52" s="39">
         <v>4</v>
       </c>
       <c r="D52" s="3">
@@ -7613,10 +7631,10 @@
       <c r="F52" s="3">
         <v>3</v>
       </c>
-      <c r="G52" s="32">
+      <c r="G52" s="40">
         <v>10</v>
       </c>
-      <c r="H52" s="33"/>
+      <c r="H52" s="41"/>
       <c r="I52" s="2">
         <v>1</v>
       </c>
@@ -7636,7 +7654,7 @@
       <c r="B53" s="3">
         <v>100300</v>
       </c>
-      <c r="C53" s="31">
+      <c r="C53" s="39">
         <v>5</v>
       </c>
       <c r="D53" s="3">
@@ -7646,10 +7664,10 @@
       <c r="F53" s="3">
         <v>3</v>
       </c>
-      <c r="G53" s="32">
+      <c r="G53" s="40">
         <v>15</v>
       </c>
-      <c r="H53" s="33"/>
+      <c r="H53" s="41"/>
       <c r="I53" s="2">
         <v>1</v>
       </c>
@@ -7679,10 +7697,10 @@
       <c r="F54" s="3">
         <v>1</v>
       </c>
-      <c r="G54" s="32">
+      <c r="G54" s="40">
         <v>10</v>
       </c>
-      <c r="H54" s="33"/>
+      <c r="H54" s="41"/>
       <c r="I54" s="2">
         <v>1</v>
       </c>
@@ -7712,10 +7730,10 @@
       <c r="F55" s="3">
         <v>2</v>
       </c>
-      <c r="G55" s="32">
+      <c r="G55" s="40">
         <v>20</v>
       </c>
-      <c r="H55" s="33"/>
+      <c r="H55" s="41"/>
       <c r="I55" s="2">
         <v>1</v>
       </c>
@@ -7745,10 +7763,10 @@
       <c r="F56" s="3">
         <v>3</v>
       </c>
-      <c r="G56" s="32">
+      <c r="G56" s="40">
         <v>50</v>
       </c>
-      <c r="H56" s="33"/>
+      <c r="H56" s="41"/>
       <c r="I56" s="2">
         <v>1</v>
       </c>
@@ -7778,10 +7796,10 @@
       <c r="F57" s="3">
         <v>1</v>
       </c>
-      <c r="G57" s="32">
-        <v>0</v>
-      </c>
-      <c r="H57" s="33"/>
+      <c r="G57" s="40">
+        <v>0</v>
+      </c>
+      <c r="H57" s="41"/>
       <c r="I57" s="2">
         <v>0</v>
       </c>
@@ -7811,10 +7829,10 @@
       <c r="F58" s="3">
         <v>1</v>
       </c>
-      <c r="G58" s="32">
-        <v>0</v>
-      </c>
-      <c r="H58" s="33"/>
+      <c r="G58" s="40">
+        <v>0</v>
+      </c>
+      <c r="H58" s="41"/>
       <c r="I58" s="2">
         <v>0</v>
       </c>
@@ -7844,10 +7862,10 @@
       <c r="F59" s="3">
         <v>1</v>
       </c>
-      <c r="G59" s="32">
-        <v>0</v>
-      </c>
-      <c r="H59" s="33"/>
+      <c r="G59" s="40">
+        <v>0</v>
+      </c>
+      <c r="H59" s="41"/>
       <c r="I59" s="2">
         <v>0</v>
       </c>
@@ -7877,10 +7895,10 @@
       <c r="F60" s="3">
         <v>1</v>
       </c>
-      <c r="G60" s="32">
-        <v>0</v>
-      </c>
-      <c r="H60" s="33"/>
+      <c r="G60" s="40">
+        <v>0</v>
+      </c>
+      <c r="H60" s="41"/>
       <c r="I60" s="2">
         <v>0</v>
       </c>
@@ -7896,672 +7914,672 @@
       <c r="A61" s="2">
         <v>1007300301</v>
       </c>
-      <c r="B61" s="16">
+      <c r="B61" s="18">
         <v>100700</v>
       </c>
-      <c r="C61" s="34" t="s">
+      <c r="C61" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="D61" s="16">
+      <c r="D61" s="18">
         <v>3</v>
       </c>
-      <c r="E61" s="16"/>
-      <c r="F61" s="16">
+      <c r="E61" s="18"/>
+      <c r="F61" s="18">
         <v>3</v>
       </c>
-      <c r="G61" s="18">
+      <c r="G61" s="22">
         <v>2</v>
       </c>
-      <c r="H61" s="18"/>
+      <c r="H61" s="22"/>
       <c r="I61" s="2">
         <v>0</v>
       </c>
-      <c r="J61" s="37"/>
-      <c r="K61" s="16"/>
+      <c r="J61" s="20"/>
+      <c r="K61" s="18"/>
       <c r="L61" s="13"/>
     </row>
     <row r="62" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A62" s="2">
         <v>1007300302</v>
       </c>
-      <c r="B62" s="16">
+      <c r="B62" s="18">
         <v>100700</v>
       </c>
-      <c r="C62" s="34" t="s">
+      <c r="C62" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="D62" s="16">
+      <c r="D62" s="18">
         <v>3</v>
       </c>
-      <c r="E62" s="16"/>
-      <c r="F62" s="16">
+      <c r="E62" s="18"/>
+      <c r="F62" s="18">
         <v>3</v>
       </c>
-      <c r="G62" s="18">
+      <c r="G62" s="22">
         <v>2</v>
       </c>
-      <c r="H62" s="18"/>
+      <c r="H62" s="22"/>
       <c r="I62" s="2">
         <v>0</v>
       </c>
-      <c r="J62" s="37"/>
-      <c r="K62" s="16"/>
+      <c r="J62" s="20"/>
+      <c r="K62" s="18"/>
       <c r="L62" s="13"/>
     </row>
     <row r="63" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A63" s="2">
         <v>1007300303</v>
       </c>
-      <c r="B63" s="16">
+      <c r="B63" s="18">
         <v>100700</v>
       </c>
-      <c r="C63" s="34" t="s">
+      <c r="C63" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="D63" s="16">
+      <c r="D63" s="18">
         <v>3</v>
       </c>
-      <c r="E63" s="16"/>
-      <c r="F63" s="16">
+      <c r="E63" s="18"/>
+      <c r="F63" s="18">
         <v>3</v>
       </c>
-      <c r="G63" s="18">
+      <c r="G63" s="22">
         <v>4</v>
       </c>
-      <c r="H63" s="18"/>
+      <c r="H63" s="22"/>
       <c r="I63" s="2">
         <v>0</v>
       </c>
-      <c r="J63" s="37"/>
-      <c r="K63" s="16"/>
+      <c r="J63" s="20"/>
+      <c r="K63" s="18"/>
       <c r="L63" s="13"/>
     </row>
     <row r="64" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A64" s="2">
         <v>1007300304</v>
       </c>
-      <c r="B64" s="16">
+      <c r="B64" s="18">
         <v>100700</v>
       </c>
-      <c r="C64" s="34" t="s">
+      <c r="C64" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="D64" s="16">
+      <c r="D64" s="18">
         <v>3</v>
       </c>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16">
+      <c r="E64" s="18"/>
+      <c r="F64" s="18">
         <v>3</v>
       </c>
-      <c r="G64" s="18">
+      <c r="G64" s="22">
         <v>4</v>
       </c>
-      <c r="H64" s="18"/>
+      <c r="H64" s="22"/>
       <c r="I64" s="2">
         <v>0</v>
       </c>
-      <c r="J64" s="37"/>
-      <c r="K64" s="16"/>
+      <c r="J64" s="20"/>
+      <c r="K64" s="18"/>
       <c r="L64" s="13"/>
     </row>
     <row r="65" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A65" s="2">
         <v>1007300305</v>
       </c>
-      <c r="B65" s="16">
+      <c r="B65" s="18">
         <v>100700</v>
       </c>
-      <c r="C65" s="34" t="s">
+      <c r="C65" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="D65" s="16">
+      <c r="D65" s="18">
         <v>3</v>
       </c>
-      <c r="E65" s="16"/>
-      <c r="F65" s="16">
+      <c r="E65" s="18"/>
+      <c r="F65" s="18">
         <v>3</v>
       </c>
-      <c r="G65" s="18">
+      <c r="G65" s="22">
         <v>6</v>
       </c>
-      <c r="H65" s="18"/>
+      <c r="H65" s="22"/>
       <c r="I65" s="2">
         <v>0</v>
       </c>
-      <c r="J65" s="37"/>
-      <c r="K65" s="16"/>
+      <c r="J65" s="20"/>
+      <c r="K65" s="18"/>
       <c r="L65" s="13"/>
     </row>
     <row r="66" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A66" s="2">
         <v>1007300306</v>
       </c>
-      <c r="B66" s="16">
+      <c r="B66" s="18">
         <v>100700</v>
       </c>
-      <c r="C66" s="34" t="s">
+      <c r="C66" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="D66" s="16">
+      <c r="D66" s="18">
         <v>3</v>
       </c>
-      <c r="E66" s="16"/>
-      <c r="F66" s="16">
+      <c r="E66" s="18"/>
+      <c r="F66" s="18">
         <v>3</v>
       </c>
-      <c r="G66" s="18">
+      <c r="G66" s="22">
         <v>8</v>
       </c>
-      <c r="H66" s="18"/>
+      <c r="H66" s="22"/>
       <c r="I66" s="2">
         <v>0</v>
       </c>
-      <c r="J66" s="37"/>
-      <c r="K66" s="16"/>
+      <c r="J66" s="20"/>
+      <c r="K66" s="18"/>
       <c r="L66" s="13"/>
     </row>
     <row r="67" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A67" s="2">
         <v>1007300307</v>
       </c>
-      <c r="B67" s="16">
+      <c r="B67" s="18">
         <v>100700</v>
       </c>
-      <c r="C67" s="34" t="s">
+      <c r="C67" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="D67" s="16">
+      <c r="D67" s="18">
         <v>3</v>
       </c>
-      <c r="E67" s="16"/>
-      <c r="F67" s="16">
+      <c r="E67" s="18"/>
+      <c r="F67" s="18">
         <v>3</v>
       </c>
-      <c r="G67" s="18">
+      <c r="G67" s="22">
         <v>10</v>
       </c>
-      <c r="H67" s="18"/>
+      <c r="H67" s="22"/>
       <c r="I67" s="2">
         <v>0</v>
       </c>
-      <c r="J67" s="37"/>
-      <c r="K67" s="16"/>
+      <c r="J67" s="20"/>
+      <c r="K67" s="18"/>
       <c r="L67" s="13"/>
     </row>
     <row r="68" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A68" s="2">
         <v>1007300308</v>
       </c>
-      <c r="B68" s="16">
+      <c r="B68" s="18">
         <v>100700</v>
       </c>
-      <c r="C68" s="34" t="s">
+      <c r="C68" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="D68" s="16">
+      <c r="D68" s="18">
         <v>3</v>
       </c>
-      <c r="E68" s="16"/>
-      <c r="F68" s="16">
+      <c r="E68" s="18"/>
+      <c r="F68" s="18">
         <v>3</v>
       </c>
-      <c r="G68" s="18">
+      <c r="G68" s="22">
         <v>15</v>
       </c>
-      <c r="H68" s="18"/>
+      <c r="H68" s="22"/>
       <c r="I68" s="2">
         <v>0</v>
       </c>
-      <c r="J68" s="37"/>
-      <c r="K68" s="16"/>
+      <c r="J68" s="20"/>
+      <c r="K68" s="18"/>
       <c r="L68" s="13"/>
     </row>
     <row r="69" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A69" s="2">
         <v>1007300401</v>
       </c>
-      <c r="B69" s="16">
+      <c r="B69" s="18">
         <v>100700</v>
       </c>
-      <c r="C69" s="34" t="s">
+      <c r="C69" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="D69" s="16">
+      <c r="D69" s="18">
         <v>3</v>
       </c>
-      <c r="E69" s="16"/>
-      <c r="F69" s="16">
+      <c r="E69" s="18"/>
+      <c r="F69" s="18">
         <v>4</v>
       </c>
-      <c r="G69" s="18">
+      <c r="G69" s="22">
         <v>5</v>
       </c>
-      <c r="H69" s="18"/>
+      <c r="H69" s="22"/>
       <c r="I69" s="2">
         <v>0</v>
       </c>
-      <c r="J69" s="37"/>
-      <c r="K69" s="16"/>
+      <c r="J69" s="20"/>
+      <c r="K69" s="18"/>
       <c r="L69" s="13"/>
     </row>
     <row r="70" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A70" s="2">
         <v>1007300402</v>
       </c>
-      <c r="B70" s="16">
+      <c r="B70" s="18">
         <v>100700</v>
       </c>
-      <c r="C70" s="34" t="s">
+      <c r="C70" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="D70" s="16">
+      <c r="D70" s="18">
         <v>3</v>
       </c>
-      <c r="E70" s="16"/>
-      <c r="F70" s="16">
+      <c r="E70" s="18"/>
+      <c r="F70" s="18">
         <v>4</v>
       </c>
-      <c r="G70" s="18">
+      <c r="G70" s="22">
         <v>5</v>
       </c>
-      <c r="H70" s="18"/>
+      <c r="H70" s="22"/>
       <c r="I70" s="2">
         <v>0</v>
       </c>
-      <c r="J70" s="37"/>
-      <c r="K70" s="16"/>
+      <c r="J70" s="20"/>
+      <c r="K70" s="18"/>
       <c r="L70" s="13"/>
     </row>
     <row r="71" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A71" s="2">
         <v>1007300403</v>
       </c>
-      <c r="B71" s="16">
+      <c r="B71" s="18">
         <v>100700</v>
       </c>
-      <c r="C71" s="34" t="s">
+      <c r="C71" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="D71" s="16">
+      <c r="D71" s="18">
         <v>3</v>
       </c>
-      <c r="E71" s="16"/>
-      <c r="F71" s="16">
+      <c r="E71" s="18"/>
+      <c r="F71" s="18">
         <v>4</v>
       </c>
-      <c r="G71" s="18">
+      <c r="G71" s="22">
         <v>10</v>
       </c>
-      <c r="H71" s="18"/>
+      <c r="H71" s="22"/>
       <c r="I71" s="2">
         <v>0</v>
       </c>
-      <c r="J71" s="37"/>
-      <c r="K71" s="16"/>
+      <c r="J71" s="20"/>
+      <c r="K71" s="18"/>
       <c r="L71" s="13"/>
     </row>
     <row r="72" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A72" s="2">
         <v>1007300404</v>
       </c>
-      <c r="B72" s="16">
+      <c r="B72" s="18">
         <v>100700</v>
       </c>
-      <c r="C72" s="34" t="s">
+      <c r="C72" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="D72" s="16">
+      <c r="D72" s="18">
         <v>3</v>
       </c>
-      <c r="E72" s="16"/>
-      <c r="F72" s="16">
+      <c r="E72" s="18"/>
+      <c r="F72" s="18">
         <v>4</v>
       </c>
-      <c r="G72" s="18">
+      <c r="G72" s="22">
         <v>10</v>
       </c>
-      <c r="H72" s="18"/>
+      <c r="H72" s="22"/>
       <c r="I72" s="2">
         <v>0</v>
       </c>
-      <c r="J72" s="37"/>
-      <c r="K72" s="16"/>
+      <c r="J72" s="20"/>
+      <c r="K72" s="18"/>
       <c r="L72" s="13"/>
     </row>
     <row r="73" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A73" s="2">
         <v>1007300405</v>
       </c>
-      <c r="B73" s="16">
+      <c r="B73" s="18">
         <v>100700</v>
       </c>
-      <c r="C73" s="34" t="s">
+      <c r="C73" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="D73" s="16">
+      <c r="D73" s="18">
         <v>3</v>
       </c>
-      <c r="E73" s="16"/>
-      <c r="F73" s="16">
+      <c r="E73" s="18"/>
+      <c r="F73" s="18">
         <v>4</v>
       </c>
-      <c r="G73" s="18">
+      <c r="G73" s="22">
         <v>15</v>
       </c>
-      <c r="H73" s="18"/>
+      <c r="H73" s="22"/>
       <c r="I73" s="2">
         <v>0</v>
       </c>
-      <c r="J73" s="37"/>
-      <c r="K73" s="16"/>
+      <c r="J73" s="20"/>
+      <c r="K73" s="18"/>
       <c r="L73" s="13"/>
     </row>
     <row r="74" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A74" s="2">
         <v>1007300406</v>
       </c>
-      <c r="B74" s="16">
+      <c r="B74" s="18">
         <v>100700</v>
       </c>
-      <c r="C74" s="34" t="s">
+      <c r="C74" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="D74" s="16">
+      <c r="D74" s="18">
         <v>3</v>
       </c>
-      <c r="E74" s="16"/>
-      <c r="F74" s="16">
+      <c r="E74" s="18"/>
+      <c r="F74" s="18">
         <v>4</v>
       </c>
-      <c r="G74" s="18">
+      <c r="G74" s="22">
         <v>20</v>
       </c>
-      <c r="H74" s="18"/>
+      <c r="H74" s="22"/>
       <c r="I74" s="2">
         <v>0</v>
       </c>
-      <c r="J74" s="37"/>
-      <c r="K74" s="16"/>
+      <c r="J74" s="20"/>
+      <c r="K74" s="18"/>
       <c r="L74" s="13"/>
     </row>
     <row r="75" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A75" s="2">
         <v>1007300407</v>
       </c>
-      <c r="B75" s="16">
+      <c r="B75" s="18">
         <v>100700</v>
       </c>
-      <c r="C75" s="34" t="s">
+      <c r="C75" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="D75" s="16">
+      <c r="D75" s="18">
         <v>3</v>
       </c>
-      <c r="E75" s="16"/>
-      <c r="F75" s="16">
+      <c r="E75" s="18"/>
+      <c r="F75" s="18">
         <v>4</v>
       </c>
-      <c r="G75" s="18">
+      <c r="G75" s="22">
         <v>40</v>
       </c>
-      <c r="H75" s="18"/>
+      <c r="H75" s="22"/>
       <c r="I75" s="2">
         <v>0</v>
       </c>
-      <c r="J75" s="37"/>
-      <c r="K75" s="16"/>
+      <c r="J75" s="20"/>
+      <c r="K75" s="18"/>
       <c r="L75" s="13"/>
     </row>
     <row r="76" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A76" s="2">
         <v>1007300408</v>
       </c>
-      <c r="B76" s="16">
+      <c r="B76" s="18">
         <v>100700</v>
       </c>
-      <c r="C76" s="34" t="s">
+      <c r="C76" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="D76" s="16">
+      <c r="D76" s="18">
         <v>3</v>
       </c>
-      <c r="E76" s="16"/>
-      <c r="F76" s="16">
+      <c r="E76" s="18"/>
+      <c r="F76" s="18">
         <v>4</v>
       </c>
-      <c r="G76" s="18">
+      <c r="G76" s="22">
         <v>60</v>
       </c>
-      <c r="H76" s="18"/>
+      <c r="H76" s="22"/>
       <c r="I76" s="2">
         <v>0</v>
       </c>
-      <c r="J76" s="37"/>
-      <c r="K76" s="16"/>
+      <c r="J76" s="20"/>
+      <c r="K76" s="18"/>
       <c r="L76" s="13"/>
     </row>
     <row r="77" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A77" s="2">
         <v>1007300501</v>
       </c>
-      <c r="B77" s="16">
+      <c r="B77" s="18">
         <v>100700</v>
       </c>
-      <c r="C77" s="34" t="s">
+      <c r="C77" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="D77" s="16">
+      <c r="D77" s="18">
         <v>3</v>
       </c>
-      <c r="E77" s="16"/>
-      <c r="F77" s="16">
+      <c r="E77" s="18"/>
+      <c r="F77" s="18">
         <v>5</v>
       </c>
-      <c r="G77" s="18">
+      <c r="G77" s="22">
         <v>10</v>
       </c>
-      <c r="H77" s="18"/>
+      <c r="H77" s="22"/>
       <c r="I77" s="2">
         <v>0</v>
       </c>
-      <c r="J77" s="37"/>
-      <c r="K77" s="16"/>
+      <c r="J77" s="20"/>
+      <c r="K77" s="18"/>
       <c r="L77" s="13"/>
     </row>
     <row r="78" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A78" s="2">
         <v>1007300502</v>
       </c>
-      <c r="B78" s="16">
+      <c r="B78" s="18">
         <v>100700</v>
       </c>
-      <c r="C78" s="34" t="s">
+      <c r="C78" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="D78" s="16">
+      <c r="D78" s="18">
         <v>3</v>
       </c>
-      <c r="E78" s="16"/>
-      <c r="F78" s="16">
+      <c r="E78" s="18"/>
+      <c r="F78" s="18">
         <v>5</v>
       </c>
-      <c r="G78" s="18">
+      <c r="G78" s="22">
         <v>10</v>
       </c>
-      <c r="H78" s="18"/>
+      <c r="H78" s="22"/>
       <c r="I78" s="2">
         <v>0</v>
       </c>
-      <c r="J78" s="37"/>
-      <c r="K78" s="16"/>
+      <c r="J78" s="20"/>
+      <c r="K78" s="18"/>
       <c r="L78" s="13"/>
     </row>
     <row r="79" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A79" s="2">
         <v>1007300503</v>
       </c>
-      <c r="B79" s="16">
+      <c r="B79" s="18">
         <v>100700</v>
       </c>
-      <c r="C79" s="34" t="s">
+      <c r="C79" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="D79" s="16">
+      <c r="D79" s="18">
         <v>3</v>
       </c>
-      <c r="E79" s="16"/>
-      <c r="F79" s="16">
+      <c r="E79" s="18"/>
+      <c r="F79" s="18">
         <v>5</v>
       </c>
-      <c r="G79" s="18">
+      <c r="G79" s="22">
         <v>20</v>
       </c>
-      <c r="H79" s="18"/>
+      <c r="H79" s="22"/>
       <c r="I79" s="2">
         <v>0</v>
       </c>
-      <c r="J79" s="37"/>
-      <c r="K79" s="16"/>
+      <c r="J79" s="20"/>
+      <c r="K79" s="18"/>
       <c r="L79" s="13"/>
     </row>
     <row r="80" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A80" s="2">
         <v>1007300504</v>
       </c>
-      <c r="B80" s="16">
+      <c r="B80" s="18">
         <v>100700</v>
       </c>
-      <c r="C80" s="34" t="s">
+      <c r="C80" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="D80" s="16">
+      <c r="D80" s="18">
         <v>3</v>
       </c>
-      <c r="E80" s="16"/>
-      <c r="F80" s="16">
+      <c r="E80" s="18"/>
+      <c r="F80" s="18">
         <v>5</v>
       </c>
-      <c r="G80" s="18">
+      <c r="G80" s="22">
         <v>20</v>
       </c>
-      <c r="H80" s="18"/>
+      <c r="H80" s="22"/>
       <c r="I80" s="2">
         <v>0</v>
       </c>
-      <c r="J80" s="37"/>
-      <c r="K80" s="16"/>
+      <c r="J80" s="20"/>
+      <c r="K80" s="18"/>
       <c r="L80" s="13"/>
     </row>
     <row r="81" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A81" s="2">
         <v>1007300505</v>
       </c>
-      <c r="B81" s="16">
+      <c r="B81" s="18">
         <v>100700</v>
       </c>
-      <c r="C81" s="34" t="s">
+      <c r="C81" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="D81" s="16">
+      <c r="D81" s="18">
         <v>3</v>
       </c>
-      <c r="E81" s="16"/>
-      <c r="F81" s="16">
+      <c r="E81" s="18"/>
+      <c r="F81" s="18">
         <v>5</v>
       </c>
-      <c r="G81" s="18">
+      <c r="G81" s="22">
         <v>30</v>
       </c>
-      <c r="H81" s="18"/>
+      <c r="H81" s="22"/>
       <c r="I81" s="2">
         <v>0</v>
       </c>
-      <c r="J81" s="37"/>
-      <c r="K81" s="16"/>
+      <c r="J81" s="20"/>
+      <c r="K81" s="18"/>
       <c r="L81" s="13"/>
     </row>
     <row r="82" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A82" s="2">
         <v>1007300506</v>
       </c>
-      <c r="B82" s="16">
+      <c r="B82" s="18">
         <v>100700</v>
       </c>
-      <c r="C82" s="34" t="s">
+      <c r="C82" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="D82" s="16">
+      <c r="D82" s="18">
         <v>3</v>
       </c>
-      <c r="E82" s="16"/>
-      <c r="F82" s="16">
+      <c r="E82" s="18"/>
+      <c r="F82" s="18">
         <v>5</v>
       </c>
-      <c r="G82" s="18">
+      <c r="G82" s="22">
         <v>40</v>
       </c>
-      <c r="H82" s="18"/>
+      <c r="H82" s="22"/>
       <c r="I82" s="2">
         <v>0</v>
       </c>
-      <c r="J82" s="37"/>
-      <c r="K82" s="16"/>
+      <c r="J82" s="20"/>
+      <c r="K82" s="18"/>
       <c r="L82" s="13"/>
     </row>
     <row r="83" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A83" s="2">
         <v>1007300507</v>
       </c>
-      <c r="B83" s="16">
+      <c r="B83" s="18">
         <v>100700</v>
       </c>
-      <c r="C83" s="34" t="s">
+      <c r="C83" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="D83" s="16">
+      <c r="D83" s="18">
         <v>3</v>
       </c>
-      <c r="E83" s="16"/>
-      <c r="F83" s="16">
+      <c r="E83" s="18"/>
+      <c r="F83" s="18">
         <v>5</v>
       </c>
-      <c r="G83" s="18">
+      <c r="G83" s="22">
         <v>80</v>
       </c>
-      <c r="H83" s="18"/>
+      <c r="H83" s="22"/>
       <c r="I83" s="2">
         <v>0</v>
       </c>
-      <c r="J83" s="37"/>
-      <c r="K83" s="16"/>
+      <c r="J83" s="20"/>
+      <c r="K83" s="18"/>
       <c r="L83" s="13"/>
     </row>
     <row r="84" s="6" customFormat="1" customHeight="1" outlineLevel="1" spans="1:12">
       <c r="A84" s="2">
         <v>1007300508</v>
       </c>
-      <c r="B84" s="16">
+      <c r="B84" s="18">
         <v>100700</v>
       </c>
-      <c r="C84" s="34" t="s">
+      <c r="C84" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="D84" s="16">
+      <c r="D84" s="18">
         <v>3</v>
       </c>
-      <c r="E84" s="16"/>
-      <c r="F84" s="16">
+      <c r="E84" s="18"/>
+      <c r="F84" s="18">
         <v>5</v>
       </c>
-      <c r="G84" s="18">
+      <c r="G84" s="22">
         <v>120</v>
       </c>
-      <c r="H84" s="18"/>
+      <c r="H84" s="22"/>
       <c r="I84" s="2">
         <v>0</v>
       </c>
-      <c r="J84" s="37"/>
-      <c r="K84" s="16"/>
+      <c r="J84" s="20"/>
+      <c r="K84" s="18"/>
       <c r="L84" s="13"/>
     </row>
     <row r="85" s="6" customFormat="1" customHeight="1" spans="1:12">
@@ -8569,30 +8587,30 @@
         <f t="shared" ref="A85:A87" si="3">(B85)*10000+C85+F85*100+D85*100000</f>
         <v>1007400310</v>
       </c>
-      <c r="B85" s="16">
+      <c r="B85" s="18">
         <v>100700</v>
       </c>
-      <c r="C85" s="16">
+      <c r="C85" s="18">
         <v>10</v>
       </c>
-      <c r="D85" s="16">
+      <c r="D85" s="18">
         <v>4</v>
       </c>
-      <c r="E85" s="16"/>
-      <c r="F85" s="16">
+      <c r="E85" s="18"/>
+      <c r="F85" s="18">
         <v>3</v>
       </c>
-      <c r="G85" s="18">
-        <v>0</v>
-      </c>
-      <c r="H85" s="18">
+      <c r="G85" s="22">
+        <v>0</v>
+      </c>
+      <c r="H85" s="22">
         <v>30070001</v>
       </c>
       <c r="I85" s="2">
         <v>0</v>
       </c>
-      <c r="J85" s="37"/>
-      <c r="K85" s="16"/>
+      <c r="J85" s="20"/>
+      <c r="K85" s="18"/>
       <c r="L85" s="13"/>
     </row>
     <row r="86" s="6" customFormat="1" customHeight="1" spans="1:12">
@@ -8600,30 +8618,30 @@
         <f t="shared" si="3"/>
         <v>1007400410</v>
       </c>
-      <c r="B86" s="16">
+      <c r="B86" s="18">
         <v>100700</v>
       </c>
-      <c r="C86" s="16">
+      <c r="C86" s="18">
         <v>10</v>
       </c>
-      <c r="D86" s="16">
+      <c r="D86" s="18">
         <v>4</v>
       </c>
-      <c r="E86" s="16"/>
-      <c r="F86" s="16">
+      <c r="E86" s="18"/>
+      <c r="F86" s="18">
         <v>4</v>
       </c>
-      <c r="G86" s="18">
-        <v>0</v>
-      </c>
-      <c r="H86" s="18">
+      <c r="G86" s="22">
+        <v>0</v>
+      </c>
+      <c r="H86" s="22">
         <v>30070002</v>
       </c>
       <c r="I86" s="2">
         <v>0</v>
       </c>
-      <c r="J86" s="37"/>
-      <c r="K86" s="16"/>
+      <c r="J86" s="20"/>
+      <c r="K86" s="18"/>
       <c r="L86" s="13"/>
     </row>
     <row r="87" s="7" customFormat="1" customHeight="1" spans="1:12">
@@ -8651,9 +8669,9 @@
       <c r="I87" s="43">
         <v>0</v>
       </c>
-      <c r="J87" s="49"/>
+      <c r="J87" s="45"/>
       <c r="K87" s="43"/>
-      <c r="L87" s="49"/>
+      <c r="L87" s="45"/>
     </row>
     <row r="88" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A88" s="43">
@@ -8680,9 +8698,9 @@
       <c r="I88" s="43">
         <v>0</v>
       </c>
-      <c r="J88" s="49"/>
+      <c r="J88" s="45"/>
       <c r="K88" s="43"/>
-      <c r="L88" s="49"/>
+      <c r="L88" s="45"/>
     </row>
     <row r="89" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A89" s="43">
@@ -8709,9 +8727,9 @@
       <c r="I89" s="43">
         <v>0</v>
       </c>
-      <c r="J89" s="49"/>
+      <c r="J89" s="45"/>
       <c r="K89" s="43"/>
-      <c r="L89" s="49"/>
+      <c r="L89" s="45"/>
     </row>
     <row r="90" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A90" s="43">
@@ -8738,9 +8756,9 @@
       <c r="I90" s="43">
         <v>0</v>
       </c>
-      <c r="J90" s="49"/>
+      <c r="J90" s="45"/>
       <c r="K90" s="43"/>
-      <c r="L90" s="49"/>
+      <c r="L90" s="45"/>
     </row>
     <row r="91" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A91" s="43">
@@ -8767,9 +8785,9 @@
       <c r="I91" s="43">
         <v>0</v>
       </c>
-      <c r="J91" s="49"/>
+      <c r="J91" s="45"/>
       <c r="K91" s="43"/>
-      <c r="L91" s="49"/>
+      <c r="L91" s="45"/>
     </row>
     <row r="92" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A92" s="43">
@@ -8796,9 +8814,9 @@
       <c r="I92" s="43">
         <v>0</v>
       </c>
-      <c r="J92" s="49"/>
+      <c r="J92" s="45"/>
       <c r="K92" s="43"/>
-      <c r="L92" s="49"/>
+      <c r="L92" s="45"/>
     </row>
     <row r="93" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A93" s="43">
@@ -8825,9 +8843,9 @@
       <c r="I93" s="43">
         <v>0</v>
       </c>
-      <c r="J93" s="49"/>
+      <c r="J93" s="45"/>
       <c r="K93" s="43"/>
-      <c r="L93" s="49"/>
+      <c r="L93" s="45"/>
     </row>
     <row r="94" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A94" s="43">
@@ -8854,9 +8872,9 @@
       <c r="I94" s="43">
         <v>0</v>
       </c>
-      <c r="J94" s="49"/>
+      <c r="J94" s="45"/>
       <c r="K94" s="43"/>
-      <c r="L94" s="49"/>
+      <c r="L94" s="45"/>
     </row>
     <row r="95" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A95" s="43">
@@ -8883,9 +8901,9 @@
       <c r="I95" s="43">
         <v>0</v>
       </c>
-      <c r="J95" s="49"/>
+      <c r="J95" s="45"/>
       <c r="K95" s="43"/>
-      <c r="L95" s="49"/>
+      <c r="L95" s="45"/>
     </row>
     <row r="96" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A96" s="43">
@@ -8912,9 +8930,9 @@
       <c r="I96" s="43">
         <v>0</v>
       </c>
-      <c r="J96" s="49"/>
+      <c r="J96" s="45"/>
       <c r="K96" s="43"/>
-      <c r="L96" s="49"/>
+      <c r="L96" s="45"/>
     </row>
     <row r="97" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A97" s="43">
@@ -8941,9 +8959,9 @@
       <c r="I97" s="43">
         <v>0</v>
       </c>
-      <c r="J97" s="49"/>
+      <c r="J97" s="45"/>
       <c r="K97" s="43"/>
-      <c r="L97" s="49"/>
+      <c r="L97" s="45"/>
     </row>
     <row r="98" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A98" s="43">
@@ -8970,9 +8988,9 @@
       <c r="I98" s="43">
         <v>0</v>
       </c>
-      <c r="J98" s="49"/>
+      <c r="J98" s="45"/>
       <c r="K98" s="43"/>
-      <c r="L98" s="49"/>
+      <c r="L98" s="45"/>
     </row>
     <row r="99" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A99" s="43">
@@ -8999,9 +9017,9 @@
       <c r="I99" s="43">
         <v>0</v>
       </c>
-      <c r="J99" s="49"/>
+      <c r="J99" s="45"/>
       <c r="K99" s="43"/>
-      <c r="L99" s="49"/>
+      <c r="L99" s="45"/>
     </row>
     <row r="100" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A100" s="43">
@@ -9028,9 +9046,9 @@
       <c r="I100" s="43">
         <v>0</v>
       </c>
-      <c r="J100" s="49"/>
+      <c r="J100" s="45"/>
       <c r="K100" s="43"/>
-      <c r="L100" s="49"/>
+      <c r="L100" s="45"/>
     </row>
     <row r="101" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A101" s="43">
@@ -9057,9 +9075,9 @@
       <c r="I101" s="43">
         <v>0</v>
       </c>
-      <c r="J101" s="49"/>
+      <c r="J101" s="45"/>
       <c r="K101" s="43"/>
-      <c r="L101" s="49"/>
+      <c r="L101" s="45"/>
     </row>
     <row r="102" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A102" s="43">
@@ -9086,9 +9104,9 @@
       <c r="I102" s="43">
         <v>0</v>
       </c>
-      <c r="J102" s="49"/>
+      <c r="J102" s="45"/>
       <c r="K102" s="43"/>
-      <c r="L102" s="49"/>
+      <c r="L102" s="45"/>
     </row>
     <row r="103" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A103" s="43">
@@ -9115,9 +9133,9 @@
       <c r="I103" s="43">
         <v>0</v>
       </c>
-      <c r="J103" s="49"/>
+      <c r="J103" s="45"/>
       <c r="K103" s="43"/>
-      <c r="L103" s="49"/>
+      <c r="L103" s="45"/>
     </row>
     <row r="104" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A104" s="43">
@@ -9144,9 +9162,9 @@
       <c r="I104" s="43">
         <v>0</v>
       </c>
-      <c r="J104" s="49"/>
+      <c r="J104" s="45"/>
       <c r="K104" s="43"/>
-      <c r="L104" s="49"/>
+      <c r="L104" s="45"/>
     </row>
     <row r="105" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A105" s="43">
@@ -9173,11 +9191,11 @@
       <c r="I105" s="43">
         <v>0</v>
       </c>
-      <c r="J105" s="49"/>
+      <c r="J105" s="45"/>
       <c r="K105" s="43">
         <v>101200101</v>
       </c>
-      <c r="L105" s="49" t="s">
+      <c r="L105" s="45" t="s">
         <v>46</v>
       </c>
     </row>
@@ -9208,9 +9226,9 @@
       <c r="I106" s="43">
         <v>0</v>
       </c>
-      <c r="J106" s="49"/>
+      <c r="J106" s="45"/>
       <c r="K106" s="43"/>
-      <c r="L106" s="49" t="s">
+      <c r="L106" s="45" t="s">
         <v>47</v>
       </c>
     </row>
@@ -9241,9 +9259,9 @@
       <c r="I107" s="43">
         <v>0</v>
       </c>
-      <c r="J107" s="49"/>
+      <c r="J107" s="45"/>
       <c r="K107" s="43"/>
-      <c r="L107" s="49" t="s">
+      <c r="L107" s="45" t="s">
         <v>48</v>
       </c>
     </row>
@@ -9274,9 +9292,9 @@
       <c r="I108" s="43">
         <v>0</v>
       </c>
-      <c r="J108" s="49"/>
+      <c r="J108" s="45"/>
       <c r="K108" s="43"/>
-      <c r="L108" s="49" t="s">
+      <c r="L108" s="45" t="s">
         <v>49</v>
       </c>
     </row>
@@ -9307,9 +9325,9 @@
       <c r="I109" s="43">
         <v>0</v>
       </c>
-      <c r="J109" s="49"/>
+      <c r="J109" s="45"/>
       <c r="K109" s="43"/>
-      <c r="L109" s="49" t="s">
+      <c r="L109" s="45" t="s">
         <v>50</v>
       </c>
     </row>
@@ -9340,9 +9358,9 @@
       <c r="I110" s="43">
         <v>0</v>
       </c>
-      <c r="J110" s="49"/>
+      <c r="J110" s="45"/>
       <c r="K110" s="43"/>
-      <c r="L110" s="49" t="s">
+      <c r="L110" s="45" t="s">
         <v>51</v>
       </c>
     </row>
@@ -9373,9 +9391,9 @@
       <c r="I111" s="43">
         <v>0</v>
       </c>
-      <c r="J111" s="49"/>
+      <c r="J111" s="45"/>
       <c r="K111" s="43"/>
-      <c r="L111" s="49" t="s">
+      <c r="L111" s="45" t="s">
         <v>52</v>
       </c>
     </row>
@@ -9406,9 +9424,9 @@
       <c r="I112" s="43">
         <v>0</v>
       </c>
-      <c r="J112" s="49"/>
+      <c r="J112" s="45"/>
       <c r="K112" s="43"/>
-      <c r="L112" s="49" t="s">
+      <c r="L112" s="45" t="s">
         <v>53</v>
       </c>
     </row>
@@ -9439,9 +9457,9 @@
       <c r="I113" s="43">
         <v>0</v>
       </c>
-      <c r="J113" s="49"/>
+      <c r="J113" s="45"/>
       <c r="K113" s="43"/>
-      <c r="L113" s="49" t="s">
+      <c r="L113" s="45" t="s">
         <v>54</v>
       </c>
     </row>
@@ -9472,9 +9490,9 @@
       <c r="I114" s="43">
         <v>0</v>
       </c>
-      <c r="J114" s="49"/>
+      <c r="J114" s="45"/>
       <c r="K114" s="43"/>
-      <c r="L114" s="49" t="s">
+      <c r="L114" s="45" t="s">
         <v>55</v>
       </c>
     </row>
@@ -9505,9 +9523,9 @@
       <c r="I115" s="43">
         <v>0</v>
       </c>
-      <c r="J115" s="49"/>
+      <c r="J115" s="45"/>
       <c r="K115" s="43"/>
-      <c r="L115" s="49" t="s">
+      <c r="L115" s="45" t="s">
         <v>56</v>
       </c>
     </row>
@@ -9538,9 +9556,9 @@
       <c r="I116" s="43">
         <v>0</v>
       </c>
-      <c r="J116" s="49"/>
+      <c r="J116" s="45"/>
       <c r="K116" s="43"/>
-      <c r="L116" s="49" t="s">
+      <c r="L116" s="45" t="s">
         <v>57</v>
       </c>
     </row>
@@ -9571,207 +9589,207 @@
       <c r="I117" s="43">
         <v>0</v>
       </c>
-      <c r="J117" s="49"/>
+      <c r="J117" s="45"/>
       <c r="K117" s="43"/>
-      <c r="L117" s="49" t="s">
+      <c r="L117" s="45" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="118" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A118" s="45">
+      <c r="A118" s="46">
         <f t="shared" si="4"/>
         <v>1012400131</v>
       </c>
-      <c r="B118" s="45">
+      <c r="B118" s="46">
         <v>101200</v>
       </c>
-      <c r="C118" s="45">
+      <c r="C118" s="46">
         <v>31</v>
       </c>
-      <c r="D118" s="45">
+      <c r="D118" s="46">
         <v>4</v>
       </c>
-      <c r="E118" s="45"/>
-      <c r="F118" s="45">
-        <v>1</v>
-      </c>
-      <c r="G118" s="46">
-        <v>0</v>
-      </c>
-      <c r="H118" s="46">
+      <c r="E118" s="46"/>
+      <c r="F118" s="46">
+        <v>1</v>
+      </c>
+      <c r="G118" s="47">
+        <v>0</v>
+      </c>
+      <c r="H118" s="47">
         <v>30120021</v>
       </c>
-      <c r="I118" s="45">
-        <v>0</v>
-      </c>
-      <c r="J118" s="50"/>
-      <c r="K118" s="45"/>
-      <c r="L118" s="50" t="s">
+      <c r="I118" s="46">
+        <v>0</v>
+      </c>
+      <c r="J118" s="48"/>
+      <c r="K118" s="46"/>
+      <c r="L118" s="48" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="119" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A119" s="45">
+      <c r="A119" s="46">
         <f t="shared" si="4"/>
         <v>1012400132</v>
       </c>
-      <c r="B119" s="45">
+      <c r="B119" s="46">
         <v>101200</v>
       </c>
-      <c r="C119" s="45">
+      <c r="C119" s="46">
         <v>32</v>
       </c>
-      <c r="D119" s="45">
+      <c r="D119" s="46">
         <v>4</v>
       </c>
-      <c r="E119" s="45"/>
-      <c r="F119" s="45">
-        <v>1</v>
-      </c>
-      <c r="G119" s="46">
-        <v>0</v>
-      </c>
-      <c r="H119" s="46">
+      <c r="E119" s="46"/>
+      <c r="F119" s="46">
+        <v>1</v>
+      </c>
+      <c r="G119" s="47">
+        <v>0</v>
+      </c>
+      <c r="H119" s="47">
         <v>30120022</v>
       </c>
-      <c r="I119" s="45">
-        <v>0</v>
-      </c>
-      <c r="J119" s="50"/>
-      <c r="K119" s="45"/>
-      <c r="L119" s="50" t="s">
+      <c r="I119" s="46">
+        <v>0</v>
+      </c>
+      <c r="J119" s="48"/>
+      <c r="K119" s="46"/>
+      <c r="L119" s="48" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="120" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A120" s="45">
+      <c r="A120" s="46">
         <f t="shared" si="4"/>
         <v>1012400133</v>
       </c>
-      <c r="B120" s="45">
+      <c r="B120" s="46">
         <v>101200</v>
       </c>
-      <c r="C120" s="45">
+      <c r="C120" s="46">
         <v>33</v>
       </c>
-      <c r="D120" s="45">
+      <c r="D120" s="46">
         <v>4</v>
       </c>
-      <c r="E120" s="45"/>
-      <c r="F120" s="45">
-        <v>1</v>
-      </c>
-      <c r="G120" s="46">
-        <v>0</v>
-      </c>
-      <c r="H120" s="46">
+      <c r="E120" s="46"/>
+      <c r="F120" s="46">
+        <v>1</v>
+      </c>
+      <c r="G120" s="47">
+        <v>0</v>
+      </c>
+      <c r="H120" s="47">
         <v>30120023</v>
       </c>
-      <c r="I120" s="45">
-        <v>0</v>
-      </c>
-      <c r="J120" s="50"/>
-      <c r="K120" s="45"/>
-      <c r="L120" s="50" t="s">
+      <c r="I120" s="46">
+        <v>0</v>
+      </c>
+      <c r="J120" s="48"/>
+      <c r="K120" s="46"/>
+      <c r="L120" s="48" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="121" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A121" s="45">
+      <c r="A121" s="46">
         <f t="shared" si="4"/>
         <v>1012400134</v>
       </c>
-      <c r="B121" s="45">
+      <c r="B121" s="46">
         <v>101200</v>
       </c>
-      <c r="C121" s="45">
+      <c r="C121" s="46">
         <v>34</v>
       </c>
-      <c r="D121" s="45">
+      <c r="D121" s="46">
         <v>4</v>
       </c>
-      <c r="E121" s="45"/>
-      <c r="F121" s="45">
-        <v>1</v>
-      </c>
-      <c r="G121" s="46">
-        <v>0</v>
-      </c>
-      <c r="H121" s="46">
+      <c r="E121" s="46"/>
+      <c r="F121" s="46">
+        <v>1</v>
+      </c>
+      <c r="G121" s="47">
+        <v>0</v>
+      </c>
+      <c r="H121" s="47">
         <v>30120024</v>
       </c>
-      <c r="I121" s="45">
-        <v>0</v>
-      </c>
-      <c r="J121" s="50"/>
-      <c r="K121" s="45"/>
-      <c r="L121" s="50" t="s">
+      <c r="I121" s="46">
+        <v>0</v>
+      </c>
+      <c r="J121" s="48"/>
+      <c r="K121" s="46"/>
+      <c r="L121" s="48" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="122" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A122" s="45">
+      <c r="A122" s="46">
         <f t="shared" si="4"/>
         <v>1012400135</v>
       </c>
-      <c r="B122" s="45">
+      <c r="B122" s="46">
         <v>101200</v>
       </c>
-      <c r="C122" s="45">
+      <c r="C122" s="46">
         <v>35</v>
       </c>
-      <c r="D122" s="45">
+      <c r="D122" s="46">
         <v>4</v>
       </c>
-      <c r="E122" s="45"/>
-      <c r="F122" s="45">
-        <v>1</v>
-      </c>
-      <c r="G122" s="46">
-        <v>0</v>
-      </c>
-      <c r="H122" s="46">
+      <c r="E122" s="46"/>
+      <c r="F122" s="46">
+        <v>1</v>
+      </c>
+      <c r="G122" s="47">
+        <v>0</v>
+      </c>
+      <c r="H122" s="47">
         <v>30120025</v>
       </c>
-      <c r="I122" s="45">
-        <v>0</v>
-      </c>
-      <c r="J122" s="50"/>
-      <c r="K122" s="45"/>
-      <c r="L122" s="50" t="s">
+      <c r="I122" s="46">
+        <v>0</v>
+      </c>
+      <c r="J122" s="48"/>
+      <c r="K122" s="46"/>
+      <c r="L122" s="48" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="123" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A123" s="45">
+      <c r="A123" s="46">
         <f t="shared" si="4"/>
         <v>1012400136</v>
       </c>
-      <c r="B123" s="45">
+      <c r="B123" s="46">
         <v>101200</v>
       </c>
-      <c r="C123" s="45">
+      <c r="C123" s="46">
         <v>36</v>
       </c>
-      <c r="D123" s="45">
+      <c r="D123" s="46">
         <v>4</v>
       </c>
-      <c r="E123" s="45"/>
-      <c r="F123" s="45">
-        <v>1</v>
-      </c>
-      <c r="G123" s="46">
-        <v>0</v>
-      </c>
-      <c r="H123" s="46">
+      <c r="E123" s="46"/>
+      <c r="F123" s="46">
+        <v>1</v>
+      </c>
+      <c r="G123" s="47">
+        <v>0</v>
+      </c>
+      <c r="H123" s="47">
         <v>30120026</v>
       </c>
-      <c r="I123" s="45">
-        <v>0</v>
-      </c>
-      <c r="J123" s="50"/>
-      <c r="K123" s="45"/>
-      <c r="L123" s="50" t="s">
+      <c r="I123" s="46">
+        <v>0</v>
+      </c>
+      <c r="J123" s="48"/>
+      <c r="K123" s="46"/>
+      <c r="L123" s="48" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9780,28 +9798,28 @@
         <f t="shared" ref="A124:A178" si="5">(B124)*10000+C124+F124*100+D124*100000</f>
         <v>1014500502</v>
       </c>
-      <c r="B124" s="47">
+      <c r="B124" s="49">
         <v>101400</v>
       </c>
-      <c r="C124" s="47">
+      <c r="C124" s="49">
         <v>2</v>
       </c>
-      <c r="D124" s="47">
+      <c r="D124" s="49">
         <v>5</v>
       </c>
-      <c r="E124" s="47"/>
-      <c r="F124" s="47">
+      <c r="E124" s="49"/>
+      <c r="F124" s="49">
         <v>5</v>
       </c>
-      <c r="G124" s="48">
-        <v>1</v>
-      </c>
-      <c r="H124" s="48"/>
+      <c r="G124" s="50">
+        <v>1</v>
+      </c>
+      <c r="H124" s="50"/>
       <c r="I124" s="2">
         <v>0</v>
       </c>
       <c r="J124" s="51"/>
-      <c r="K124" s="47"/>
+      <c r="K124" s="49"/>
       <c r="L124" s="13"/>
     </row>
     <row r="125" s="9" customFormat="1" customHeight="1" spans="1:12">
@@ -9809,28 +9827,28 @@
         <f t="shared" si="5"/>
         <v>1014500503</v>
       </c>
-      <c r="B125" s="47">
+      <c r="B125" s="49">
         <v>101400</v>
       </c>
-      <c r="C125" s="47">
+      <c r="C125" s="49">
         <v>3</v>
       </c>
-      <c r="D125" s="47">
+      <c r="D125" s="49">
         <v>5</v>
       </c>
-      <c r="E125" s="47"/>
-      <c r="F125" s="47">
+      <c r="E125" s="49"/>
+      <c r="F125" s="49">
         <v>5</v>
       </c>
-      <c r="G125" s="48">
-        <v>1</v>
-      </c>
-      <c r="H125" s="48"/>
+      <c r="G125" s="50">
+        <v>1</v>
+      </c>
+      <c r="H125" s="50"/>
       <c r="I125" s="2">
         <v>0</v>
       </c>
       <c r="J125" s="51"/>
-      <c r="K125" s="47"/>
+      <c r="K125" s="49"/>
       <c r="L125" s="13"/>
     </row>
     <row r="126" s="9" customFormat="1" customHeight="1" spans="1:12">
@@ -9838,28 +9856,28 @@
         <f t="shared" si="5"/>
         <v>1014500504</v>
       </c>
-      <c r="B126" s="47">
+      <c r="B126" s="49">
         <v>101400</v>
       </c>
-      <c r="C126" s="47">
+      <c r="C126" s="49">
         <v>4</v>
       </c>
-      <c r="D126" s="47">
+      <c r="D126" s="49">
         <v>5</v>
       </c>
-      <c r="E126" s="47"/>
-      <c r="F126" s="47">
+      <c r="E126" s="49"/>
+      <c r="F126" s="49">
         <v>5</v>
       </c>
-      <c r="G126" s="48">
-        <v>1</v>
-      </c>
-      <c r="H126" s="48"/>
+      <c r="G126" s="50">
+        <v>1</v>
+      </c>
+      <c r="H126" s="50"/>
       <c r="I126" s="2">
         <v>0</v>
       </c>
       <c r="J126" s="51"/>
-      <c r="K126" s="47"/>
+      <c r="K126" s="49"/>
       <c r="L126" s="13"/>
     </row>
     <row r="127" s="9" customFormat="1" customHeight="1" spans="1:12">
@@ -9867,28 +9885,28 @@
         <f t="shared" si="5"/>
         <v>1014500505</v>
       </c>
-      <c r="B127" s="47">
+      <c r="B127" s="49">
         <v>101400</v>
       </c>
-      <c r="C127" s="47">
+      <c r="C127" s="49">
         <v>5</v>
       </c>
-      <c r="D127" s="47">
+      <c r="D127" s="49">
         <v>5</v>
       </c>
-      <c r="E127" s="47"/>
-      <c r="F127" s="47">
+      <c r="E127" s="49"/>
+      <c r="F127" s="49">
         <v>5</v>
       </c>
-      <c r="G127" s="48">
+      <c r="G127" s="50">
         <v>2</v>
       </c>
-      <c r="H127" s="48"/>
+      <c r="H127" s="50"/>
       <c r="I127" s="2">
         <v>0</v>
       </c>
       <c r="J127" s="51"/>
-      <c r="K127" s="47"/>
+      <c r="K127" s="49"/>
       <c r="L127" s="13"/>
     </row>
     <row r="128" s="9" customFormat="1" customHeight="1" spans="1:12">
@@ -9896,28 +9914,28 @@
         <f t="shared" si="5"/>
         <v>1014500506</v>
       </c>
-      <c r="B128" s="47">
+      <c r="B128" s="49">
         <v>101400</v>
       </c>
-      <c r="C128" s="47">
+      <c r="C128" s="49">
         <v>6</v>
       </c>
-      <c r="D128" s="47">
+      <c r="D128" s="49">
         <v>5</v>
       </c>
-      <c r="E128" s="47"/>
-      <c r="F128" s="47">
+      <c r="E128" s="49"/>
+      <c r="F128" s="49">
         <v>5</v>
       </c>
-      <c r="G128" s="48">
+      <c r="G128" s="50">
         <v>2</v>
       </c>
-      <c r="H128" s="48"/>
+      <c r="H128" s="50"/>
       <c r="I128" s="2">
         <v>0</v>
       </c>
       <c r="J128" s="51"/>
-      <c r="K128" s="47"/>
+      <c r="K128" s="49"/>
       <c r="L128" s="13"/>
     </row>
     <row r="129" s="9" customFormat="1" customHeight="1" spans="1:12">
@@ -9925,28 +9943,28 @@
         <f t="shared" si="5"/>
         <v>1014500507</v>
       </c>
-      <c r="B129" s="47">
+      <c r="B129" s="49">
         <v>101400</v>
       </c>
-      <c r="C129" s="47">
+      <c r="C129" s="49">
         <v>7</v>
       </c>
-      <c r="D129" s="47">
+      <c r="D129" s="49">
         <v>5</v>
       </c>
-      <c r="E129" s="47"/>
-      <c r="F129" s="47">
+      <c r="E129" s="49"/>
+      <c r="F129" s="49">
         <v>5</v>
       </c>
-      <c r="G129" s="48">
+      <c r="G129" s="50">
         <v>2</v>
       </c>
-      <c r="H129" s="48"/>
+      <c r="H129" s="50"/>
       <c r="I129" s="2">
         <v>0</v>
       </c>
       <c r="J129" s="51"/>
-      <c r="K129" s="47"/>
+      <c r="K129" s="49"/>
       <c r="L129" s="13"/>
     </row>
     <row r="130" s="9" customFormat="1" customHeight="1" spans="1:12">
@@ -9954,28 +9972,28 @@
         <f t="shared" si="5"/>
         <v>1014500508</v>
       </c>
-      <c r="B130" s="47">
+      <c r="B130" s="49">
         <v>101400</v>
       </c>
-      <c r="C130" s="47">
+      <c r="C130" s="49">
         <v>8</v>
       </c>
-      <c r="D130" s="47">
+      <c r="D130" s="49">
         <v>5</v>
       </c>
-      <c r="E130" s="47"/>
-      <c r="F130" s="47">
+      <c r="E130" s="49"/>
+      <c r="F130" s="49">
         <v>5</v>
       </c>
-      <c r="G130" s="48">
+      <c r="G130" s="50">
         <v>3</v>
       </c>
-      <c r="H130" s="48"/>
+      <c r="H130" s="50"/>
       <c r="I130" s="2">
         <v>0</v>
       </c>
       <c r="J130" s="51"/>
-      <c r="K130" s="47"/>
+      <c r="K130" s="49"/>
       <c r="L130" s="13"/>
     </row>
     <row r="131" s="9" customFormat="1" customHeight="1" spans="1:12">
@@ -9983,28 +10001,28 @@
         <f t="shared" si="5"/>
         <v>1014500509</v>
       </c>
-      <c r="B131" s="47">
+      <c r="B131" s="49">
         <v>101400</v>
       </c>
-      <c r="C131" s="47">
+      <c r="C131" s="49">
         <v>9</v>
       </c>
-      <c r="D131" s="47">
+      <c r="D131" s="49">
         <v>5</v>
       </c>
-      <c r="E131" s="47"/>
-      <c r="F131" s="47">
+      <c r="E131" s="49"/>
+      <c r="F131" s="49">
         <v>5</v>
       </c>
-      <c r="G131" s="48">
+      <c r="G131" s="50">
         <v>3</v>
       </c>
-      <c r="H131" s="48"/>
+      <c r="H131" s="50"/>
       <c r="I131" s="2">
         <v>0</v>
       </c>
       <c r="J131" s="51"/>
-      <c r="K131" s="47"/>
+      <c r="K131" s="49"/>
       <c r="L131" s="13"/>
     </row>
     <row r="132" s="9" customFormat="1" customHeight="1" spans="1:12">
@@ -10012,28 +10030,28 @@
         <f t="shared" si="5"/>
         <v>1014500510</v>
       </c>
-      <c r="B132" s="47">
+      <c r="B132" s="49">
         <v>101400</v>
       </c>
-      <c r="C132" s="47">
+      <c r="C132" s="49">
         <v>10</v>
       </c>
-      <c r="D132" s="47">
+      <c r="D132" s="49">
         <v>5</v>
       </c>
-      <c r="E132" s="47"/>
-      <c r="F132" s="47">
+      <c r="E132" s="49"/>
+      <c r="F132" s="49">
         <v>5</v>
       </c>
-      <c r="G132" s="48">
+      <c r="G132" s="50">
         <v>4</v>
       </c>
-      <c r="H132" s="48"/>
+      <c r="H132" s="50"/>
       <c r="I132" s="2">
         <v>0</v>
       </c>
       <c r="J132" s="51"/>
-      <c r="K132" s="47"/>
+      <c r="K132" s="49"/>
       <c r="L132" s="13"/>
     </row>
     <row r="133" s="9" customFormat="1" customHeight="1" spans="1:12">
@@ -10041,28 +10059,28 @@
         <f t="shared" si="5"/>
         <v>1014500511</v>
       </c>
-      <c r="B133" s="47">
+      <c r="B133" s="49">
         <v>101400</v>
       </c>
-      <c r="C133" s="47">
+      <c r="C133" s="49">
         <v>11</v>
       </c>
-      <c r="D133" s="47">
+      <c r="D133" s="49">
         <v>5</v>
       </c>
-      <c r="E133" s="47"/>
-      <c r="F133" s="47">
+      <c r="E133" s="49"/>
+      <c r="F133" s="49">
         <v>5</v>
       </c>
-      <c r="G133" s="48">
+      <c r="G133" s="50">
         <v>5</v>
       </c>
-      <c r="H133" s="48"/>
+      <c r="H133" s="50"/>
       <c r="I133" s="2">
         <v>0</v>
       </c>
       <c r="J133" s="51"/>
-      <c r="K133" s="47"/>
+      <c r="K133" s="49"/>
       <c r="L133" s="13"/>
     </row>
     <row r="134" s="9" customFormat="1" customHeight="1" spans="1:12">
@@ -10070,23 +10088,23 @@
         <f t="shared" si="5"/>
         <v>1014400513</v>
       </c>
-      <c r="B134" s="47">
+      <c r="B134" s="49">
         <v>101400</v>
       </c>
-      <c r="C134" s="47">
+      <c r="C134" s="49">
         <v>13</v>
       </c>
-      <c r="D134" s="47">
+      <c r="D134" s="49">
         <v>4</v>
       </c>
-      <c r="E134" s="47"/>
-      <c r="F134" s="47">
+      <c r="E134" s="49"/>
+      <c r="F134" s="49">
         <v>5</v>
       </c>
-      <c r="G134" s="48">
-        <v>0</v>
-      </c>
-      <c r="H134" s="48"/>
+      <c r="G134" s="50">
+        <v>0</v>
+      </c>
+      <c r="H134" s="50"/>
       <c r="I134" s="2">
         <v>0</v>
       </c>
@@ -11325,35 +11343,35 @@
         <f t="shared" si="5"/>
         <v>1024201619</v>
       </c>
-      <c r="B169" s="16">
+      <c r="B169" s="18">
         <v>102400</v>
       </c>
-      <c r="C169" s="16">
+      <c r="C169" s="18">
         <v>19</v>
       </c>
-      <c r="D169" s="16">
+      <c r="D169" s="18">
         <v>2</v>
       </c>
-      <c r="E169" s="16" t="s">
+      <c r="E169" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="F169" s="16">
+      <c r="F169" s="18">
         <v>16</v>
       </c>
-      <c r="G169" s="16">
-        <v>0</v>
-      </c>
-      <c r="H169" s="17">
+      <c r="G169" s="18">
+        <v>0</v>
+      </c>
+      <c r="H169" s="19">
         <v>30010001</v>
       </c>
       <c r="I169" s="2">
         <v>0</v>
       </c>
-      <c r="J169" s="37"/>
-      <c r="K169" s="38">
+      <c r="J169" s="20"/>
+      <c r="K169" s="21">
         <v>102400101</v>
       </c>
-      <c r="L169" s="37" t="s">
+      <c r="L169" s="20" t="s">
         <v>26</v>
       </c>
     </row>
@@ -11362,35 +11380,35 @@
         <f t="shared" si="5"/>
         <v>1024201620</v>
       </c>
-      <c r="B170" s="16">
+      <c r="B170" s="18">
         <v>102400</v>
       </c>
-      <c r="C170" s="16">
+      <c r="C170" s="18">
         <v>20</v>
       </c>
-      <c r="D170" s="16">
+      <c r="D170" s="18">
         <v>2</v>
       </c>
-      <c r="E170" s="16" t="s">
+      <c r="E170" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="F170" s="16">
+      <c r="F170" s="18">
         <v>16</v>
       </c>
-      <c r="G170" s="16">
-        <v>0</v>
-      </c>
-      <c r="H170" s="17">
+      <c r="G170" s="18">
+        <v>0</v>
+      </c>
+      <c r="H170" s="19">
         <v>30010002</v>
       </c>
       <c r="I170" s="2">
         <v>0</v>
       </c>
-      <c r="J170" s="37"/>
-      <c r="K170" s="38">
+      <c r="J170" s="20"/>
+      <c r="K170" s="21">
         <v>102400102</v>
       </c>
-      <c r="L170" s="37" t="s">
+      <c r="L170" s="20" t="s">
         <v>27</v>
       </c>
     </row>
@@ -11399,35 +11417,35 @@
         <f t="shared" si="5"/>
         <v>1024201621</v>
       </c>
-      <c r="B171" s="16">
+      <c r="B171" s="18">
         <v>102400</v>
       </c>
-      <c r="C171" s="16">
+      <c r="C171" s="18">
         <v>21</v>
       </c>
-      <c r="D171" s="16">
+      <c r="D171" s="18">
         <v>2</v>
       </c>
-      <c r="E171" s="16" t="s">
+      <c r="E171" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="F171" s="16">
+      <c r="F171" s="18">
         <v>16</v>
       </c>
-      <c r="G171" s="18">
-        <v>0</v>
-      </c>
-      <c r="H171" s="17">
+      <c r="G171" s="22">
+        <v>0</v>
+      </c>
+      <c r="H171" s="19">
         <v>30010003</v>
       </c>
       <c r="I171" s="2">
         <v>0</v>
       </c>
-      <c r="J171" s="37"/>
-      <c r="K171" s="38">
+      <c r="J171" s="20"/>
+      <c r="K171" s="21">
         <v>102400103</v>
       </c>
-      <c r="L171" s="37" t="s">
+      <c r="L171" s="20" t="s">
         <v>28</v>
       </c>
     </row>
@@ -11436,35 +11454,35 @@
         <f t="shared" si="5"/>
         <v>1024201622</v>
       </c>
-      <c r="B172" s="16">
+      <c r="B172" s="18">
         <v>102400</v>
       </c>
-      <c r="C172" s="16">
+      <c r="C172" s="18">
         <v>22</v>
       </c>
-      <c r="D172" s="16">
+      <c r="D172" s="18">
         <v>2</v>
       </c>
-      <c r="E172" s="16" t="s">
+      <c r="E172" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="F172" s="16">
+      <c r="F172" s="18">
         <v>16</v>
       </c>
-      <c r="G172" s="18">
-        <v>0</v>
-      </c>
-      <c r="H172" s="17">
+      <c r="G172" s="22">
+        <v>0</v>
+      </c>
+      <c r="H172" s="19">
         <v>30010004</v>
       </c>
       <c r="I172" s="2">
         <v>0</v>
       </c>
-      <c r="J172" s="37"/>
-      <c r="K172" s="38">
+      <c r="J172" s="20"/>
+      <c r="K172" s="21">
         <v>102400104</v>
       </c>
-      <c r="L172" s="37" t="s">
+      <c r="L172" s="20" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11473,33 +11491,33 @@
         <f t="shared" si="5"/>
         <v>1024201628</v>
       </c>
-      <c r="B173" s="19">
+      <c r="B173" s="23">
         <v>102400</v>
       </c>
-      <c r="C173" s="19">
+      <c r="C173" s="23">
         <v>28</v>
       </c>
-      <c r="D173" s="19">
+      <c r="D173" s="23">
         <v>2</v>
       </c>
-      <c r="E173" s="19"/>
-      <c r="F173" s="19">
+      <c r="E173" s="23"/>
+      <c r="F173" s="23">
         <v>16</v>
       </c>
-      <c r="G173" s="20">
-        <v>0</v>
-      </c>
-      <c r="H173" s="21">
+      <c r="G173" s="24">
+        <v>0</v>
+      </c>
+      <c r="H173" s="25">
         <v>30010005</v>
       </c>
       <c r="I173" s="2">
         <v>0</v>
       </c>
-      <c r="J173" s="39"/>
-      <c r="K173" s="19">
-        <v>0</v>
-      </c>
-      <c r="L173" s="39" t="s">
+      <c r="J173" s="26"/>
+      <c r="K173" s="23">
+        <v>0</v>
+      </c>
+      <c r="L173" s="26" t="s">
         <v>30</v>
       </c>
     </row>
@@ -11508,33 +11526,33 @@
         <f t="shared" si="5"/>
         <v>1024201528</v>
       </c>
-      <c r="B174" s="22">
+      <c r="B174" s="27">
         <v>102400</v>
       </c>
-      <c r="C174" s="22">
+      <c r="C174" s="27">
         <v>28</v>
       </c>
-      <c r="D174" s="22">
+      <c r="D174" s="27">
         <v>2</v>
       </c>
-      <c r="E174" s="22"/>
-      <c r="F174" s="22">
+      <c r="E174" s="27"/>
+      <c r="F174" s="27">
         <v>15</v>
       </c>
-      <c r="G174" s="23">
-        <v>0</v>
-      </c>
-      <c r="H174" s="24">
+      <c r="G174" s="28">
+        <v>0</v>
+      </c>
+      <c r="H174" s="29">
         <v>30010006</v>
       </c>
       <c r="I174" s="2">
         <v>0</v>
       </c>
-      <c r="J174" s="40"/>
-      <c r="K174" s="22">
-        <v>0</v>
-      </c>
-      <c r="L174" s="40" t="s">
+      <c r="J174" s="30"/>
+      <c r="K174" s="27">
+        <v>0</v>
+      </c>
+      <c r="L174" s="30" t="s">
         <v>31</v>
       </c>
     </row>
@@ -11543,31 +11561,31 @@
         <f t="shared" si="5"/>
         <v>1024400317</v>
       </c>
-      <c r="B175" s="25">
+      <c r="B175" s="31">
         <v>102400</v>
       </c>
-      <c r="C175" s="25">
+      <c r="C175" s="31">
         <v>17</v>
       </c>
-      <c r="D175" s="25">
+      <c r="D175" s="31">
         <v>4</v>
       </c>
-      <c r="E175" s="25"/>
-      <c r="F175" s="25">
+      <c r="E175" s="31"/>
+      <c r="F175" s="31">
         <v>3</v>
       </c>
-      <c r="G175" s="26">
-        <v>0</v>
-      </c>
-      <c r="H175" s="27"/>
+      <c r="G175" s="32">
+        <v>0</v>
+      </c>
+      <c r="H175" s="33"/>
       <c r="I175" s="2">
         <v>0</v>
       </c>
-      <c r="J175" s="41"/>
-      <c r="K175" s="25">
-        <v>0</v>
-      </c>
-      <c r="L175" s="41" t="s">
+      <c r="J175" s="34"/>
+      <c r="K175" s="31">
+        <v>0</v>
+      </c>
+      <c r="L175" s="34" t="s">
         <v>32</v>
       </c>
     </row>
@@ -11576,31 +11594,31 @@
         <f t="shared" si="5"/>
         <v>1024400417</v>
       </c>
-      <c r="B176" s="28">
+      <c r="B176" s="35">
         <v>102400</v>
       </c>
-      <c r="C176" s="28">
+      <c r="C176" s="35">
         <v>17</v>
       </c>
-      <c r="D176" s="28">
+      <c r="D176" s="35">
         <v>4</v>
       </c>
-      <c r="E176" s="28"/>
-      <c r="F176" s="28">
+      <c r="E176" s="35"/>
+      <c r="F176" s="35">
         <v>4</v>
       </c>
-      <c r="G176" s="29">
-        <v>0</v>
-      </c>
-      <c r="H176" s="30"/>
+      <c r="G176" s="36">
+        <v>0</v>
+      </c>
+      <c r="H176" s="37"/>
       <c r="I176" s="2">
         <v>0</v>
       </c>
-      <c r="J176" s="42"/>
-      <c r="K176" s="28">
-        <v>0</v>
-      </c>
-      <c r="L176" s="42" t="s">
+      <c r="J176" s="38"/>
+      <c r="K176" s="35">
+        <v>0</v>
+      </c>
+      <c r="L176" s="38" t="s">
         <v>33</v>
       </c>
     </row>
@@ -11609,31 +11627,31 @@
         <f t="shared" si="5"/>
         <v>1024400517</v>
       </c>
-      <c r="B177" s="28">
+      <c r="B177" s="35">
         <v>102400</v>
       </c>
-      <c r="C177" s="28">
+      <c r="C177" s="35">
         <v>17</v>
       </c>
-      <c r="D177" s="28">
+      <c r="D177" s="35">
         <v>4</v>
       </c>
-      <c r="E177" s="28"/>
-      <c r="F177" s="28">
+      <c r="E177" s="35"/>
+      <c r="F177" s="35">
         <v>5</v>
       </c>
-      <c r="G177" s="29">
-        <v>0</v>
-      </c>
-      <c r="H177" s="30"/>
+      <c r="G177" s="36">
+        <v>0</v>
+      </c>
+      <c r="H177" s="37"/>
       <c r="I177" s="2">
         <v>0</v>
       </c>
-      <c r="J177" s="42"/>
-      <c r="K177" s="28">
-        <v>0</v>
-      </c>
-      <c r="L177" s="42" t="s">
+      <c r="J177" s="38"/>
+      <c r="K177" s="35">
+        <v>0</v>
+      </c>
+      <c r="L177" s="38" t="s">
         <v>34</v>
       </c>
     </row>
@@ -11642,582 +11660,2466 @@
         <f t="shared" si="5"/>
         <v>1024400130</v>
       </c>
-      <c r="B178" s="28">
+      <c r="B178" s="35">
         <v>102400</v>
       </c>
-      <c r="C178" s="28">
+      <c r="C178" s="35">
         <v>30</v>
       </c>
-      <c r="D178" s="28">
+      <c r="D178" s="35">
         <v>4</v>
       </c>
-      <c r="E178" s="28"/>
-      <c r="F178" s="28">
-        <v>1</v>
-      </c>
-      <c r="G178" s="29">
-        <v>0</v>
-      </c>
-      <c r="H178" s="30">
+      <c r="E178" s="35"/>
+      <c r="F178" s="35">
+        <v>1</v>
+      </c>
+      <c r="G178" s="36">
+        <v>0</v>
+      </c>
+      <c r="H178" s="37">
         <v>30010007</v>
       </c>
       <c r="I178" s="2">
         <v>0</v>
       </c>
-      <c r="J178" s="42"/>
-      <c r="K178" s="28">
-        <v>0</v>
-      </c>
-      <c r="L178" s="42" t="s">
+      <c r="J178" s="38"/>
+      <c r="K178" s="35">
+        <v>0</v>
+      </c>
+      <c r="L178" s="38" t="s">
         <v>35</v>
       </c>
     </row>
+    <row r="179" customHeight="1" spans="1:12">
+      <c r="A179" s="53">
+        <v>1017300301</v>
+      </c>
+      <c r="B179" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D179" s="2">
+        <v>3</v>
+      </c>
+      <c r="F179" s="2">
+        <v>3</v>
+      </c>
+      <c r="G179" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="180" customHeight="1" spans="1:12">
+      <c r="A180" s="53">
+        <v>1017300302</v>
+      </c>
+      <c r="B180" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D180" s="2">
+        <v>3</v>
+      </c>
+      <c r="F180" s="2">
+        <v>3</v>
+      </c>
+      <c r="G180" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181" customHeight="1" spans="1:12">
+      <c r="A181" s="53">
+        <v>1017300303</v>
+      </c>
+      <c r="B181" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D181" s="2">
+        <v>3</v>
+      </c>
+      <c r="F181" s="2">
+        <v>3</v>
+      </c>
+      <c r="G181" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" customHeight="1" spans="1:12">
+      <c r="A182" s="53">
+        <v>1017300304</v>
+      </c>
+      <c r="B182" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D182" s="2">
+        <v>3</v>
+      </c>
+      <c r="F182" s="2">
+        <v>3</v>
+      </c>
+      <c r="G182" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" customHeight="1" spans="1:12">
+      <c r="A183" s="53">
+        <v>1017300305</v>
+      </c>
+      <c r="B183" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D183" s="2">
+        <v>3</v>
+      </c>
+      <c r="F183" s="2">
+        <v>3</v>
+      </c>
+      <c r="G183" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="184" customHeight="1" spans="1:12">
+      <c r="A184" s="53">
+        <v>1017300306</v>
+      </c>
+      <c r="B184" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D184" s="2">
+        <v>3</v>
+      </c>
+      <c r="F184" s="2">
+        <v>3</v>
+      </c>
+      <c r="G184" s="11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="185" customHeight="1" spans="1:12">
+      <c r="A185" s="53">
+        <v>1017300307</v>
+      </c>
+      <c r="B185" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D185" s="2">
+        <v>3</v>
+      </c>
+      <c r="F185" s="2">
+        <v>3</v>
+      </c>
+      <c r="G185" s="11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="186" customHeight="1" spans="1:12">
+      <c r="A186" s="53">
+        <v>1017300308</v>
+      </c>
+      <c r="B186" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D186" s="2">
+        <v>3</v>
+      </c>
+      <c r="F186" s="2">
+        <v>3</v>
+      </c>
+      <c r="G186" s="11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="187" customHeight="1" spans="1:12">
+      <c r="A187" s="53">
+        <v>1017300401</v>
+      </c>
+      <c r="B187" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D187" s="2">
+        <v>3</v>
+      </c>
+      <c r="F187" s="2">
+        <v>4</v>
+      </c>
+      <c r="G187" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" customHeight="1" spans="1:12">
+      <c r="A188" s="53">
+        <v>1017300402</v>
+      </c>
+      <c r="B188" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D188" s="2">
+        <v>3</v>
+      </c>
+      <c r="F188" s="2">
+        <v>4</v>
+      </c>
+      <c r="G188" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189" customHeight="1" spans="1:12">
+      <c r="A189" s="53">
+        <v>1017300403</v>
+      </c>
+      <c r="B189" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D189" s="2">
+        <v>3</v>
+      </c>
+      <c r="F189" s="2">
+        <v>4</v>
+      </c>
+      <c r="G189" s="11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="190" customHeight="1" spans="1:12">
+      <c r="A190" s="53">
+        <v>1017300404</v>
+      </c>
+      <c r="B190" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D190" s="2">
+        <v>3</v>
+      </c>
+      <c r="F190" s="2">
+        <v>4</v>
+      </c>
+      <c r="G190" s="11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="191" customHeight="1" spans="1:12">
+      <c r="A191" s="53">
+        <v>1017300405</v>
+      </c>
+      <c r="B191" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D191" s="2">
+        <v>3</v>
+      </c>
+      <c r="F191" s="2">
+        <v>4</v>
+      </c>
+      <c r="G191" s="11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="192" customHeight="1" spans="1:12">
+      <c r="A192" s="53">
+        <v>1017300406</v>
+      </c>
+      <c r="B192" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D192" s="2">
+        <v>3</v>
+      </c>
+      <c r="F192" s="2">
+        <v>4</v>
+      </c>
+      <c r="G192" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="193" customHeight="1" spans="1:12">
+      <c r="A193" s="53">
+        <v>1017300407</v>
+      </c>
+      <c r="B193" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D193" s="2">
+        <v>3</v>
+      </c>
+      <c r="F193" s="2">
+        <v>4</v>
+      </c>
+      <c r="G193" s="11">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="194" customHeight="1" spans="1:12">
+      <c r="A194" s="53">
+        <v>1017300408</v>
+      </c>
+      <c r="B194" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D194" s="2">
+        <v>3</v>
+      </c>
+      <c r="F194" s="2">
+        <v>4</v>
+      </c>
+      <c r="G194" s="11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="195" customHeight="1" spans="1:12">
+      <c r="A195" s="53">
+        <v>1017300501</v>
+      </c>
+      <c r="B195" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D195" s="2">
+        <v>3</v>
+      </c>
+      <c r="F195" s="2">
+        <v>5</v>
+      </c>
+      <c r="G195" s="11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="196" customHeight="1" spans="1:12">
+      <c r="A196" s="53">
+        <v>1017300502</v>
+      </c>
+      <c r="B196" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D196" s="2">
+        <v>3</v>
+      </c>
+      <c r="F196" s="2">
+        <v>5</v>
+      </c>
+      <c r="G196" s="11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="197" customHeight="1" spans="1:12">
+      <c r="A197" s="53">
+        <v>1017300503</v>
+      </c>
+      <c r="B197" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D197" s="2">
+        <v>3</v>
+      </c>
+      <c r="F197" s="2">
+        <v>5</v>
+      </c>
+      <c r="G197" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="198" customHeight="1" spans="1:12">
+      <c r="A198" s="53">
+        <v>1017300504</v>
+      </c>
+      <c r="B198" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D198" s="2">
+        <v>3</v>
+      </c>
+      <c r="F198" s="2">
+        <v>5</v>
+      </c>
+      <c r="G198" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="199" customHeight="1" spans="1:12">
+      <c r="A199" s="53">
+        <v>1017300505</v>
+      </c>
+      <c r="B199" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D199" s="2">
+        <v>3</v>
+      </c>
+      <c r="F199" s="2">
+        <v>5</v>
+      </c>
+      <c r="G199" s="11">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="200" customHeight="1" spans="1:12">
+      <c r="A200" s="53">
+        <v>1017300506</v>
+      </c>
+      <c r="B200" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D200" s="2">
+        <v>3</v>
+      </c>
+      <c r="F200" s="2">
+        <v>5</v>
+      </c>
+      <c r="G200" s="11">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="201" customHeight="1" spans="1:12">
+      <c r="A201" s="53">
+        <v>1017300507</v>
+      </c>
+      <c r="B201" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D201" s="2">
+        <v>3</v>
+      </c>
+      <c r="F201" s="2">
+        <v>5</v>
+      </c>
+      <c r="G201" s="11">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="202" customHeight="1" spans="1:12">
+      <c r="A202" s="53">
+        <v>1017300508</v>
+      </c>
+      <c r="B202" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D202" s="2">
+        <v>3</v>
+      </c>
+      <c r="F202" s="2">
+        <v>5</v>
+      </c>
+      <c r="G202" s="11">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="203" customHeight="1" spans="1:12">
+      <c r="A203" s="53">
+        <v>1017400310</v>
+      </c>
+      <c r="B203" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C203" s="2">
+        <v>10</v>
+      </c>
+      <c r="D203" s="2">
+        <v>4</v>
+      </c>
+      <c r="F203" s="2">
+        <v>3</v>
+      </c>
+      <c r="G203" s="11">
+        <v>0</v>
+      </c>
+      <c r="H203" s="11">
+        <v>30170001</v>
+      </c>
+    </row>
+    <row r="204" customHeight="1" spans="1:12">
+      <c r="A204" s="53">
+        <v>1017400410</v>
+      </c>
+      <c r="B204" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C204" s="2">
+        <v>10</v>
+      </c>
+      <c r="D204" s="2">
+        <v>4</v>
+      </c>
+      <c r="F204" s="2">
+        <v>4</v>
+      </c>
+      <c r="G204" s="11">
+        <v>0</v>
+      </c>
+      <c r="H204" s="11">
+        <v>30170002</v>
+      </c>
+    </row>
+    <row r="205" customHeight="1" spans="1:12">
+      <c r="A205" s="53">
+        <v>1017500119</v>
+      </c>
+      <c r="B205" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C205" s="2">
+        <v>19</v>
+      </c>
+      <c r="D205" s="2">
+        <v>4</v>
+      </c>
+      <c r="F205" s="2">
+        <v>1</v>
+      </c>
+      <c r="G205" s="11">
+        <v>0</v>
+      </c>
+      <c r="K205" s="11">
+        <v>10170003</v>
+      </c>
+      <c r="L205" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="206" customHeight="1" spans="1:12">
+      <c r="A206" s="53">
+        <v>1017500120</v>
+      </c>
+      <c r="B206" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C206" s="2">
+        <v>20</v>
+      </c>
+      <c r="D206" s="2">
+        <v>4</v>
+      </c>
+      <c r="F206" s="2">
+        <v>1</v>
+      </c>
+      <c r="G206" s="11">
+        <v>0</v>
+      </c>
+      <c r="K206" s="11">
+        <v>10170004</v>
+      </c>
+      <c r="L206" s="13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="207" customHeight="1" spans="1:12">
+      <c r="A207" s="53">
+        <v>1017500121</v>
+      </c>
+      <c r="B207" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C207" s="2">
+        <v>21</v>
+      </c>
+      <c r="D207" s="2">
+        <v>4</v>
+      </c>
+      <c r="F207" s="2">
+        <v>1</v>
+      </c>
+      <c r="G207" s="11">
+        <v>0</v>
+      </c>
+      <c r="K207" s="11">
+        <v>10170005</v>
+      </c>
+      <c r="L207" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="208" customHeight="1" spans="1:12">
+      <c r="A208" s="53">
+        <v>1017500122</v>
+      </c>
+      <c r="B208" s="2">
+        <v>101700</v>
+      </c>
+      <c r="C208" s="2">
+        <v>22</v>
+      </c>
+      <c r="D208" s="2">
+        <v>4</v>
+      </c>
+      <c r="F208" s="2">
+        <v>1</v>
+      </c>
+      <c r="G208" s="11">
+        <v>0</v>
+      </c>
+      <c r="K208" s="11">
+        <v>10170006</v>
+      </c>
+      <c r="L208" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="209" customHeight="1" spans="1:10">
+      <c r="A209" s="2">
+        <f>(B209)*10000+C209+F209*100+D209*100000</f>
+        <v>1022100301</v>
+      </c>
+      <c r="B209" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C209" s="2">
+        <v>1</v>
+      </c>
+      <c r="D209" s="2">
+        <v>1</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F209" s="2">
+        <v>3</v>
+      </c>
+      <c r="G209" s="11">
+        <v>5</v>
+      </c>
+      <c r="J209" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="210" customHeight="1" spans="1:10">
+      <c r="A210" s="2">
+        <f t="shared" ref="A210:A254" si="6">(B210)*10000+C210+F210*100+D210*100000</f>
+        <v>1022100302</v>
+      </c>
+      <c r="B210" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C210" s="2">
+        <v>2</v>
+      </c>
+      <c r="D210" s="2">
+        <v>1</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F210" s="2">
+        <v>3</v>
+      </c>
+      <c r="G210" s="11">
+        <v>5</v>
+      </c>
+      <c r="J210" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="211" customHeight="1" spans="1:10">
+      <c r="A211" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100303</v>
+      </c>
+      <c r="B211" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C211" s="2">
+        <v>3</v>
+      </c>
+      <c r="D211" s="2">
+        <v>1</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F211" s="2">
+        <v>3</v>
+      </c>
+      <c r="G211" s="11">
+        <v>5</v>
+      </c>
+      <c r="J211" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="212" customHeight="1" spans="1:10">
+      <c r="A212" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100304</v>
+      </c>
+      <c r="B212" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C212" s="2">
+        <v>4</v>
+      </c>
+      <c r="D212" s="2">
+        <v>1</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F212" s="2">
+        <v>3</v>
+      </c>
+      <c r="G212" s="11">
+        <v>10</v>
+      </c>
+      <c r="J212" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="213" customHeight="1" spans="1:10">
+      <c r="A213" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100305</v>
+      </c>
+      <c r="B213" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C213" s="2">
+        <v>5</v>
+      </c>
+      <c r="D213" s="2">
+        <v>1</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F213" s="2">
+        <v>3</v>
+      </c>
+      <c r="G213" s="11">
+        <v>10</v>
+      </c>
+      <c r="J213" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="214" customHeight="1" spans="1:10">
+      <c r="A214" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100306</v>
+      </c>
+      <c r="B214" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C214" s="2">
+        <v>6</v>
+      </c>
+      <c r="D214" s="2">
+        <v>1</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F214" s="2">
+        <v>3</v>
+      </c>
+      <c r="G214" s="11">
+        <v>20</v>
+      </c>
+      <c r="J214" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="215" customHeight="1" spans="1:10">
+      <c r="A215" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100307</v>
+      </c>
+      <c r="B215" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C215" s="2">
+        <v>7</v>
+      </c>
+      <c r="D215" s="2">
+        <v>1</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F215" s="2">
+        <v>3</v>
+      </c>
+      <c r="G215" s="11">
+        <v>20</v>
+      </c>
+      <c r="J215" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="216" customHeight="1" spans="1:10">
+      <c r="A216" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100308</v>
+      </c>
+      <c r="B216" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C216" s="2">
+        <v>8</v>
+      </c>
+      <c r="D216" s="2">
+        <v>1</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F216" s="2">
+        <v>3</v>
+      </c>
+      <c r="G216" s="11">
+        <v>25</v>
+      </c>
+      <c r="J216" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="217" customHeight="1" spans="1:10">
+      <c r="A217" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100309</v>
+      </c>
+      <c r="B217" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C217" s="2">
+        <v>9</v>
+      </c>
+      <c r="D217" s="2">
+        <v>1</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F217" s="2">
+        <v>3</v>
+      </c>
+      <c r="G217" s="11">
+        <v>30</v>
+      </c>
+      <c r="J217" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="218" customHeight="1" spans="1:10">
+      <c r="A218" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100310</v>
+      </c>
+      <c r="B218" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C218" s="2">
+        <v>10</v>
+      </c>
+      <c r="D218" s="2">
+        <v>1</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F218" s="2">
+        <v>3</v>
+      </c>
+      <c r="G218" s="11">
+        <v>50</v>
+      </c>
+      <c r="J218" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="219" customHeight="1" spans="1:10">
+      <c r="A219" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100311</v>
+      </c>
+      <c r="B219" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C219" s="2">
+        <v>11</v>
+      </c>
+      <c r="D219" s="2">
+        <v>1</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F219" s="2">
+        <v>3</v>
+      </c>
+      <c r="G219" s="11">
+        <v>500</v>
+      </c>
+      <c r="J219" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="220" customHeight="1" spans="1:10">
+      <c r="A220" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100312</v>
+      </c>
+      <c r="B220" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C220" s="2">
+        <v>12</v>
+      </c>
+      <c r="D220" s="2">
+        <v>1</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F220" s="2">
+        <v>3</v>
+      </c>
+      <c r="G220" s="11">
+        <v>500</v>
+      </c>
+      <c r="J220" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="221" customHeight="1" spans="1:10">
+      <c r="A221" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100313</v>
+      </c>
+      <c r="B221" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C221" s="2">
+        <v>13</v>
+      </c>
+      <c r="D221" s="2">
+        <v>1</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F221" s="2">
+        <v>3</v>
+      </c>
+      <c r="G221" s="11">
+        <v>500</v>
+      </c>
+      <c r="J221" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="222" customHeight="1" spans="1:10">
+      <c r="A222" s="2">
+        <f t="shared" si="6"/>
+        <v>1022400314</v>
+      </c>
+      <c r="B222" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C222" s="2">
+        <v>14</v>
+      </c>
+      <c r="D222" s="2">
+        <v>4</v>
+      </c>
+      <c r="F222" s="2">
+        <v>3</v>
+      </c>
+      <c r="G222" s="11">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="223" customHeight="1" spans="1:10">
+      <c r="A223" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100401</v>
+      </c>
+      <c r="B223" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C223" s="2">
+        <v>1</v>
+      </c>
+      <c r="D223" s="2">
+        <v>1</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F223" s="2">
+        <v>4</v>
+      </c>
+      <c r="G223" s="11">
+        <v>20</v>
+      </c>
+      <c r="J223" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="224" customHeight="1" spans="1:10">
+      <c r="A224" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100402</v>
+      </c>
+      <c r="B224" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C224" s="2">
+        <v>2</v>
+      </c>
+      <c r="D224" s="2">
+        <v>1</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F224" s="2">
+        <v>4</v>
+      </c>
+      <c r="G224" s="11">
+        <v>20</v>
+      </c>
+      <c r="J224" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="225" customHeight="1" spans="1:10">
+      <c r="A225" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100403</v>
+      </c>
+      <c r="B225" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C225" s="2">
+        <v>3</v>
+      </c>
+      <c r="D225" s="2">
+        <v>1</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F225" s="2">
+        <v>4</v>
+      </c>
+      <c r="G225" s="11">
+        <v>20</v>
+      </c>
+      <c r="J225" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="226" customHeight="1" spans="1:10">
+      <c r="A226" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100404</v>
+      </c>
+      <c r="B226" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C226" s="2">
+        <v>4</v>
+      </c>
+      <c r="D226" s="2">
+        <v>1</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F226" s="2">
+        <v>4</v>
+      </c>
+      <c r="G226" s="11">
+        <v>50</v>
+      </c>
+      <c r="J226" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="227" customHeight="1" spans="1:10">
+      <c r="A227" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100405</v>
+      </c>
+      <c r="B227" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C227" s="2">
+        <v>5</v>
+      </c>
+      <c r="D227" s="2">
+        <v>1</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F227" s="2">
+        <v>4</v>
+      </c>
+      <c r="G227" s="11">
+        <v>50</v>
+      </c>
+      <c r="J227" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="228" customHeight="1" spans="1:10">
+      <c r="A228" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100406</v>
+      </c>
+      <c r="B228" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C228" s="2">
+        <v>6</v>
+      </c>
+      <c r="D228" s="2">
+        <v>1</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F228" s="2">
+        <v>4</v>
+      </c>
+      <c r="G228" s="11">
+        <v>75</v>
+      </c>
+      <c r="J228" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="229" customHeight="1" spans="1:10">
+      <c r="A229" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100407</v>
+      </c>
+      <c r="B229" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C229" s="2">
+        <v>7</v>
+      </c>
+      <c r="D229" s="2">
+        <v>1</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F229" s="2">
+        <v>4</v>
+      </c>
+      <c r="G229" s="11">
+        <v>75</v>
+      </c>
+      <c r="J229" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="230" customHeight="1" spans="1:10">
+      <c r="A230" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100408</v>
+      </c>
+      <c r="B230" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C230" s="2">
+        <v>8</v>
+      </c>
+      <c r="D230" s="2">
+        <v>1</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F230" s="2">
+        <v>4</v>
+      </c>
+      <c r="G230" s="11">
+        <v>150</v>
+      </c>
+      <c r="J230" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="231" customHeight="1" spans="1:10">
+      <c r="A231" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100409</v>
+      </c>
+      <c r="B231" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C231" s="2">
+        <v>9</v>
+      </c>
+      <c r="D231" s="2">
+        <v>1</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F231" s="2">
+        <v>4</v>
+      </c>
+      <c r="G231" s="11">
+        <v>200</v>
+      </c>
+      <c r="J231" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="232" customHeight="1" spans="1:10">
+      <c r="A232" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100410</v>
+      </c>
+      <c r="B232" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C232" s="2">
+        <v>10</v>
+      </c>
+      <c r="D232" s="2">
+        <v>1</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F232" s="2">
+        <v>4</v>
+      </c>
+      <c r="G232" s="11">
+        <v>200</v>
+      </c>
+      <c r="J232" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="233" customHeight="1" spans="1:10">
+      <c r="A233" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100411</v>
+      </c>
+      <c r="B233" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C233" s="2">
+        <v>11</v>
+      </c>
+      <c r="D233" s="2">
+        <v>1</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F233" s="2">
+        <v>4</v>
+      </c>
+      <c r="G233" s="11">
+        <v>1000</v>
+      </c>
+      <c r="J233" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="234" customHeight="1" spans="1:10">
+      <c r="A234" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100412</v>
+      </c>
+      <c r="B234" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C234" s="2">
+        <v>12</v>
+      </c>
+      <c r="D234" s="2">
+        <v>1</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F234" s="2">
+        <v>4</v>
+      </c>
+      <c r="G234" s="11">
+        <v>1000</v>
+      </c>
+      <c r="J234" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="235" customHeight="1" spans="1:10">
+      <c r="A235" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100413</v>
+      </c>
+      <c r="B235" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C235" s="2">
+        <v>13</v>
+      </c>
+      <c r="D235" s="2">
+        <v>1</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F235" s="2">
+        <v>4</v>
+      </c>
+      <c r="G235" s="11">
+        <v>1000</v>
+      </c>
+      <c r="J235" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="236" customHeight="1" spans="1:10">
+      <c r="A236" s="2">
+        <f t="shared" si="6"/>
+        <v>1022400414</v>
+      </c>
+      <c r="B236" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C236" s="2">
+        <v>14</v>
+      </c>
+      <c r="D236" s="2">
+        <v>4</v>
+      </c>
+      <c r="F236" s="2">
+        <v>4</v>
+      </c>
+      <c r="G236" s="11">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="237" customHeight="1" spans="1:10">
+      <c r="A237" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100501</v>
+      </c>
+      <c r="B237" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C237" s="2">
+        <v>1</v>
+      </c>
+      <c r="D237" s="2">
+        <v>1</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F237" s="2">
+        <v>5</v>
+      </c>
+      <c r="G237" s="11">
+        <v>100</v>
+      </c>
+      <c r="J237" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="238" customHeight="1" spans="1:10">
+      <c r="A238" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100502</v>
+      </c>
+      <c r="B238" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C238" s="2">
+        <v>2</v>
+      </c>
+      <c r="D238" s="2">
+        <v>1</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F238" s="2">
+        <v>5</v>
+      </c>
+      <c r="G238" s="11">
+        <v>150</v>
+      </c>
+      <c r="J238" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="239" customHeight="1" spans="1:10">
+      <c r="A239" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100503</v>
+      </c>
+      <c r="B239" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C239" s="2">
+        <v>3</v>
+      </c>
+      <c r="D239" s="2">
+        <v>1</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F239" s="2">
+        <v>5</v>
+      </c>
+      <c r="G239" s="11">
+        <v>150</v>
+      </c>
+      <c r="J239" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="240" customHeight="1" spans="1:10">
+      <c r="A240" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100504</v>
+      </c>
+      <c r="B240" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C240" s="2">
+        <v>4</v>
+      </c>
+      <c r="D240" s="2">
+        <v>1</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F240" s="2">
+        <v>5</v>
+      </c>
+      <c r="G240" s="11">
+        <v>200</v>
+      </c>
+      <c r="J240" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="241" customHeight="1" spans="1:12">
+      <c r="A241" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100505</v>
+      </c>
+      <c r="B241" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C241" s="2">
+        <v>5</v>
+      </c>
+      <c r="D241" s="2">
+        <v>1</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F241" s="2">
+        <v>5</v>
+      </c>
+      <c r="G241" s="11">
+        <v>200</v>
+      </c>
+      <c r="J241" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="242" customHeight="1" spans="1:12">
+      <c r="A242" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100506</v>
+      </c>
+      <c r="B242" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C242" s="2">
+        <v>6</v>
+      </c>
+      <c r="D242" s="2">
+        <v>1</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F242" s="2">
+        <v>5</v>
+      </c>
+      <c r="G242" s="11">
+        <v>400</v>
+      </c>
+      <c r="J242" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="243" customHeight="1" spans="1:12">
+      <c r="A243" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100507</v>
+      </c>
+      <c r="B243" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C243" s="2">
+        <v>7</v>
+      </c>
+      <c r="D243" s="2">
+        <v>1</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F243" s="2">
+        <v>5</v>
+      </c>
+      <c r="G243" s="11">
+        <v>400</v>
+      </c>
+      <c r="J243" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="244" customHeight="1" spans="1:12">
+      <c r="A244" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100508</v>
+      </c>
+      <c r="B244" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C244" s="2">
+        <v>8</v>
+      </c>
+      <c r="D244" s="2">
+        <v>1</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F244" s="2">
+        <v>5</v>
+      </c>
+      <c r="G244" s="11">
+        <v>600</v>
+      </c>
+      <c r="J244" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="245" customHeight="1" spans="1:12">
+      <c r="A245" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100509</v>
+      </c>
+      <c r="B245" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C245" s="2">
+        <v>9</v>
+      </c>
+      <c r="D245" s="2">
+        <v>1</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F245" s="2">
+        <v>5</v>
+      </c>
+      <c r="G245" s="11">
+        <v>800</v>
+      </c>
+      <c r="J245" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="246" customHeight="1" spans="1:12">
+      <c r="A246" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100510</v>
+      </c>
+      <c r="B246" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C246" s="2">
+        <v>10</v>
+      </c>
+      <c r="D246" s="2">
+        <v>1</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F246" s="2">
+        <v>5</v>
+      </c>
+      <c r="G246" s="11">
+        <v>1000</v>
+      </c>
+      <c r="J246" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="247" customHeight="1" spans="1:12">
+      <c r="A247" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100511</v>
+      </c>
+      <c r="B247" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C247" s="2">
+        <v>11</v>
+      </c>
+      <c r="D247" s="2">
+        <v>1</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F247" s="2">
+        <v>5</v>
+      </c>
+      <c r="G247" s="11">
+        <v>2000</v>
+      </c>
+      <c r="J247" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="248" customHeight="1" spans="1:12">
+      <c r="A248" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100512</v>
+      </c>
+      <c r="B248" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C248" s="2">
+        <v>12</v>
+      </c>
+      <c r="D248" s="2">
+        <v>1</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F248" s="2">
+        <v>5</v>
+      </c>
+      <c r="G248" s="11">
+        <v>2000</v>
+      </c>
+      <c r="J248" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="249" customHeight="1" spans="1:12">
+      <c r="A249" s="2">
+        <f t="shared" si="6"/>
+        <v>1022100513</v>
+      </c>
+      <c r="B249" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C249" s="2">
+        <v>13</v>
+      </c>
+      <c r="D249" s="2">
+        <v>1</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F249" s="2">
+        <v>5</v>
+      </c>
+      <c r="G249" s="11">
+        <v>2000</v>
+      </c>
+      <c r="J249" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="250" customHeight="1" spans="1:12">
+      <c r="A250" s="2">
+        <f t="shared" si="6"/>
+        <v>1022400514</v>
+      </c>
+      <c r="B250" s="2">
+        <v>102200</v>
+      </c>
+      <c r="C250" s="2">
+        <v>14</v>
+      </c>
+      <c r="D250" s="2">
+        <v>4</v>
+      </c>
+      <c r="F250" s="2">
+        <v>5</v>
+      </c>
+      <c r="G250" s="11">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="251" customHeight="1" spans="1:12">
+      <c r="A251" s="2">
+        <f t="shared" si="6"/>
+        <v>1022420115</v>
+      </c>
+      <c r="B251" s="2">
+        <v>102202</v>
+      </c>
+      <c r="C251" s="2">
+        <v>15</v>
+      </c>
+      <c r="D251" s="2">
+        <v>4</v>
+      </c>
+      <c r="F251" s="2">
+        <v>1</v>
+      </c>
+      <c r="G251" s="11">
+        <v>0</v>
+      </c>
+      <c r="K251" s="2">
+        <v>102200101</v>
+      </c>
+      <c r="L251" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="252" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A252" s="3">
+        <f t="shared" si="6"/>
+        <v>1022430116</v>
+      </c>
+      <c r="B252" s="3">
+        <v>102203</v>
+      </c>
+      <c r="C252" s="3">
+        <v>16</v>
+      </c>
+      <c r="D252" s="3">
+        <v>4</v>
+      </c>
+      <c r="E252" s="3"/>
+      <c r="F252" s="3">
+        <v>1</v>
+      </c>
+      <c r="G252" s="40">
+        <v>0</v>
+      </c>
+      <c r="H252" s="40"/>
+      <c r="I252" s="40"/>
+      <c r="J252" s="13"/>
+      <c r="K252" s="3">
+        <v>102200102</v>
+      </c>
+      <c r="L252" s="13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="253" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A253" s="3">
+        <f t="shared" si="6"/>
+        <v>1022440117</v>
+      </c>
+      <c r="B253" s="3">
+        <v>102204</v>
+      </c>
+      <c r="C253" s="3">
+        <v>17</v>
+      </c>
+      <c r="D253" s="3">
+        <v>4</v>
+      </c>
+      <c r="E253" s="3"/>
+      <c r="F253" s="3">
+        <v>1</v>
+      </c>
+      <c r="G253" s="40">
+        <v>0</v>
+      </c>
+      <c r="H253" s="40"/>
+      <c r="I253" s="40"/>
+      <c r="J253" s="13"/>
+      <c r="K253" s="3">
+        <v>102200103</v>
+      </c>
+      <c r="L253" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="254" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A254" s="3">
+        <f t="shared" si="6"/>
+        <v>1022450118</v>
+      </c>
+      <c r="B254" s="3">
+        <v>102205</v>
+      </c>
+      <c r="C254" s="3">
+        <v>18</v>
+      </c>
+      <c r="D254" s="3">
+        <v>4</v>
+      </c>
+      <c r="E254" s="3"/>
+      <c r="F254" s="3">
+        <v>1</v>
+      </c>
+      <c r="G254" s="40">
+        <v>0</v>
+      </c>
+      <c r="H254" s="40"/>
+      <c r="I254" s="40"/>
+      <c r="J254" s="13"/>
+      <c r="K254" s="3">
+        <v>102200104</v>
+      </c>
+      <c r="L254" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L134" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L254" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="0" priority="116">
+    <cfRule type="expression" dxfId="0" priority="120">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D85:E85">
-    <cfRule type="expression" dxfId="0" priority="142">
+    <cfRule type="expression" dxfId="0" priority="146">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D86:E86">
-    <cfRule type="expression" dxfId="0" priority="107">
+    <cfRule type="expression" dxfId="0" priority="111">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105">
-    <cfRule type="duplicateValues" dxfId="1" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105:E105">
-    <cfRule type="expression" dxfId="0" priority="87">
+    <cfRule type="expression" dxfId="0" priority="91">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I105">
-    <cfRule type="expression" dxfId="0" priority="89">
+    <cfRule type="expression" dxfId="0" priority="93">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A106">
-    <cfRule type="duplicateValues" dxfId="1" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D106:E106">
-    <cfRule type="expression" dxfId="0" priority="83">
+    <cfRule type="expression" dxfId="0" priority="87">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I106">
-    <cfRule type="expression" dxfId="0" priority="85">
+    <cfRule type="expression" dxfId="0" priority="89">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="1" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D107:E107">
-    <cfRule type="expression" dxfId="0" priority="79">
+    <cfRule type="expression" dxfId="0" priority="83">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I107">
-    <cfRule type="expression" dxfId="0" priority="81">
+    <cfRule type="expression" dxfId="0" priority="85">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108">
-    <cfRule type="duplicateValues" dxfId="1" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D108:E108">
-    <cfRule type="expression" dxfId="0" priority="75">
+    <cfRule type="expression" dxfId="0" priority="79">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I108">
-    <cfRule type="expression" dxfId="0" priority="77">
+    <cfRule type="expression" dxfId="0" priority="81">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" dxfId="1" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D109:E109">
-    <cfRule type="expression" dxfId="0" priority="71">
+    <cfRule type="expression" dxfId="0" priority="75">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I109">
-    <cfRule type="expression" dxfId="0" priority="73">
+    <cfRule type="expression" dxfId="0" priority="77">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110">
-    <cfRule type="duplicateValues" dxfId="1" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D110:E110">
-    <cfRule type="expression" dxfId="0" priority="67">
+    <cfRule type="expression" dxfId="0" priority="71">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I110">
-    <cfRule type="expression" dxfId="0" priority="69">
+    <cfRule type="expression" dxfId="0" priority="73">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A111">
-    <cfRule type="duplicateValues" dxfId="1" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D111:E111">
-    <cfRule type="expression" dxfId="0" priority="63">
+    <cfRule type="expression" dxfId="0" priority="67">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I111">
-    <cfRule type="expression" dxfId="0" priority="65">
+    <cfRule type="expression" dxfId="0" priority="69">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112">
-    <cfRule type="duplicateValues" dxfId="1" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D112:E112">
-    <cfRule type="expression" dxfId="0" priority="59">
+    <cfRule type="expression" dxfId="0" priority="63">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I112">
-    <cfRule type="expression" dxfId="0" priority="61">
+    <cfRule type="expression" dxfId="0" priority="65">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A113">
-    <cfRule type="duplicateValues" dxfId="1" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D113:E113">
-    <cfRule type="expression" dxfId="0" priority="55">
+    <cfRule type="expression" dxfId="0" priority="59">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I113">
-    <cfRule type="expression" dxfId="0" priority="57">
+    <cfRule type="expression" dxfId="0" priority="61">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114">
-    <cfRule type="duplicateValues" dxfId="1" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D114:E114">
-    <cfRule type="expression" dxfId="0" priority="51">
+    <cfRule type="expression" dxfId="0" priority="55">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I114">
-    <cfRule type="expression" dxfId="0" priority="53">
+    <cfRule type="expression" dxfId="0" priority="57">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A115">
-    <cfRule type="duplicateValues" dxfId="1" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D115:E115">
-    <cfRule type="expression" dxfId="0" priority="47">
+    <cfRule type="expression" dxfId="0" priority="51">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I115">
-    <cfRule type="expression" dxfId="0" priority="49">
+    <cfRule type="expression" dxfId="0" priority="53">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A116">
-    <cfRule type="duplicateValues" dxfId="1" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D116:E116">
-    <cfRule type="expression" dxfId="0" priority="43">
+    <cfRule type="expression" dxfId="0" priority="47">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I116">
-    <cfRule type="expression" dxfId="0" priority="45">
+    <cfRule type="expression" dxfId="0" priority="49">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117">
-    <cfRule type="duplicateValues" dxfId="1" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D117:E117">
-    <cfRule type="expression" dxfId="0" priority="39">
+    <cfRule type="expression" dxfId="0" priority="43">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I117">
-    <cfRule type="expression" dxfId="0" priority="41">
+    <cfRule type="expression" dxfId="0" priority="45">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A118">
-    <cfRule type="duplicateValues" dxfId="1" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D118:E118">
-    <cfRule type="expression" dxfId="0" priority="35">
+    <cfRule type="expression" dxfId="0" priority="39">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I118">
-    <cfRule type="expression" dxfId="0" priority="37">
+    <cfRule type="expression" dxfId="0" priority="41">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A119">
-    <cfRule type="duplicateValues" dxfId="1" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D119:E119">
-    <cfRule type="expression" dxfId="0" priority="31">
+    <cfRule type="expression" dxfId="0" priority="35">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I119">
-    <cfRule type="expression" dxfId="0" priority="33">
+    <cfRule type="expression" dxfId="0" priority="37">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A120">
-    <cfRule type="duplicateValues" dxfId="1" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D120:E120">
-    <cfRule type="expression" dxfId="0" priority="27">
+    <cfRule type="expression" dxfId="0" priority="31">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I120">
-    <cfRule type="expression" dxfId="0" priority="29">
+    <cfRule type="expression" dxfId="0" priority="33">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A121">
-    <cfRule type="duplicateValues" dxfId="1" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D121:E121">
-    <cfRule type="expression" dxfId="0" priority="23">
+    <cfRule type="expression" dxfId="0" priority="27">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I121">
-    <cfRule type="expression" dxfId="0" priority="25">
+    <cfRule type="expression" dxfId="0" priority="29">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A122">
-    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D122:E122">
-    <cfRule type="expression" dxfId="0" priority="19">
+    <cfRule type="expression" dxfId="0" priority="23">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I122">
-    <cfRule type="expression" dxfId="0" priority="21">
+    <cfRule type="expression" dxfId="0" priority="25">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A123">
-    <cfRule type="duplicateValues" dxfId="1" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D123:E123">
-    <cfRule type="expression" dxfId="0" priority="15">
+    <cfRule type="expression" dxfId="0" priority="19">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I123">
-    <cfRule type="expression" dxfId="0" priority="17">
+    <cfRule type="expression" dxfId="0" priority="21">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C134:L134">
-    <cfRule type="expression" dxfId="0" priority="143">
+    <cfRule type="expression" dxfId="0" priority="147">
       <formula>MOD($B134,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="expression" dxfId="0" priority="7">
+    <cfRule type="expression" dxfId="0" priority="11">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A178">
-    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B178">
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="0" priority="7">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D178:E178">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="0" priority="5">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:A60">
-    <cfRule type="duplicateValues" dxfId="1" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A87:A92">
-    <cfRule type="duplicateValues" dxfId="1" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A93:A98">
-    <cfRule type="duplicateValues" dxfId="1" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99:A104">
-    <cfRule type="duplicateValues" dxfId="1" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A135:A177">
-    <cfRule type="duplicateValues" dxfId="1" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A209:A254">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B60">
-    <cfRule type="expression" dxfId="0" priority="102">
+    <cfRule type="expression" dxfId="0" priority="106">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C84">
-    <cfRule type="expression" dxfId="0" priority="105">
+    <cfRule type="expression" dxfId="0" priority="109">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E93:E98">
-    <cfRule type="expression" dxfId="0" priority="94">
+    <cfRule type="expression" dxfId="0" priority="98">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E99:E104">
-    <cfRule type="expression" dxfId="0" priority="91">
+    <cfRule type="expression" dxfId="0" priority="95">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39:K42">
-    <cfRule type="duplicateValues" dxfId="2" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K169:K172">
-    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="417"/>
+  <conditionalFormatting sqref="L205:L208">
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>MOD($B205,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A255:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="421"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L4">
-    <cfRule type="expression" dxfId="0" priority="416">
+    <cfRule type="expression" dxfId="0" priority="420">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41:B42 B44:B47">
-    <cfRule type="expression" dxfId="0" priority="150">
+    <cfRule type="expression" dxfId="0" priority="154">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 B179:L1048576">
-    <cfRule type="expression" dxfId="0" priority="415">
+  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 H179:L204 B179:G208 I205:K208 B255:L1048576">
+    <cfRule type="expression" dxfId="0" priority="419">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43:G43 J43:L43">
-    <cfRule type="expression" dxfId="0" priority="115">
+    <cfRule type="expression" dxfId="0" priority="119">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44:G44 J44:L47 G45:G47 C45:C47">
-    <cfRule type="expression" dxfId="0" priority="149">
+    <cfRule type="expression" dxfId="0" priority="153">
       <formula>MOD($B44,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45:E47">
-    <cfRule type="expression" dxfId="0" priority="146">
+    <cfRule type="expression" dxfId="0" priority="150">
       <formula>MOD($B45,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F60 C48:C60">
+    <cfRule type="expression" dxfId="0" priority="107">
+      <formula>MOD($B48,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
+    <cfRule type="expression" dxfId="0" priority="105">
+      <formula>MOD($B48,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D48:E60">
     <cfRule type="expression" dxfId="0" priority="103">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
-    <cfRule type="expression" dxfId="0" priority="101">
-      <formula>MOD($B48,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D48:E60">
-    <cfRule type="expression" dxfId="0" priority="99">
-      <formula>MOD($B48,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B77:B84 F77:L84">
-    <cfRule type="expression" dxfId="0" priority="145">
+    <cfRule type="expression" dxfId="0" priority="149">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85:C85 F85:L85">
-    <cfRule type="expression" dxfId="0" priority="141">
+    <cfRule type="expression" dxfId="0" priority="145">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B86:C86 F86:L86">
-    <cfRule type="expression" dxfId="0" priority="106">
+    <cfRule type="expression" dxfId="0" priority="110">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87:C92 F87:L92 I93:I104">
-    <cfRule type="expression" dxfId="0" priority="96">
+    <cfRule type="expression" dxfId="0" priority="100">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87:E92 D93:D104">
-    <cfRule type="expression" dxfId="0" priority="97">
+    <cfRule type="expression" dxfId="0" priority="101">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:C98 F93:H98 J93:L98">
-    <cfRule type="expression" dxfId="0" priority="93">
+    <cfRule type="expression" dxfId="0" priority="97">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99:C104 F99:H104 J99:L104">
-    <cfRule type="expression" dxfId="0" priority="90">
+    <cfRule type="expression" dxfId="0" priority="94">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:C105 F105:H105 J105:L105">
-    <cfRule type="expression" dxfId="0" priority="86">
+    <cfRule type="expression" dxfId="0" priority="90">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106:C106 F106:H106 J106:L106 H107:H111 C107:C111">
-    <cfRule type="expression" dxfId="0" priority="82">
+    <cfRule type="expression" dxfId="0" priority="86">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107 F107:G107 J107:L107">
-    <cfRule type="expression" dxfId="0" priority="78">
+    <cfRule type="expression" dxfId="0" priority="82">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B108 F108:G108 J108:L108">
-    <cfRule type="expression" dxfId="0" priority="74">
+    <cfRule type="expression" dxfId="0" priority="78">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B109 F109:G109 J109:L109">
-    <cfRule type="expression" dxfId="0" priority="70">
+    <cfRule type="expression" dxfId="0" priority="74">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B110 F110:G110 J110:L110">
-    <cfRule type="expression" dxfId="0" priority="66">
+    <cfRule type="expression" dxfId="0" priority="70">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111 F111:G111 J111:L111">
-    <cfRule type="expression" dxfId="0" priority="62">
+    <cfRule type="expression" dxfId="0" priority="66">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112:C112 F112:H112 J112:L112 H113:H117 C113:C117">
-    <cfRule type="expression" dxfId="0" priority="58">
+    <cfRule type="expression" dxfId="0" priority="62">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113 F113:G113 J113:L113">
-    <cfRule type="expression" dxfId="0" priority="54">
+    <cfRule type="expression" dxfId="0" priority="58">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114 F114:G114 J114:L114">
-    <cfRule type="expression" dxfId="0" priority="50">
+    <cfRule type="expression" dxfId="0" priority="54">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115 F115:G115 J115:L115">
-    <cfRule type="expression" dxfId="0" priority="46">
+    <cfRule type="expression" dxfId="0" priority="50">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B116 F116:G116 J116:L116">
-    <cfRule type="expression" dxfId="0" priority="42">
+    <cfRule type="expression" dxfId="0" priority="46">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117 F117:G117 J117:L117">
-    <cfRule type="expression" dxfId="0" priority="38">
+    <cfRule type="expression" dxfId="0" priority="42">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118:C118 F118:H118 J118:L118 H119:H123 C119:C123">
-    <cfRule type="expression" dxfId="0" priority="34">
+    <cfRule type="expression" dxfId="0" priority="38">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119 F119:G119 J119:L119">
-    <cfRule type="expression" dxfId="0" priority="30">
+    <cfRule type="expression" dxfId="0" priority="34">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120 F120:G120 J120:L120">
-    <cfRule type="expression" dxfId="0" priority="26">
+    <cfRule type="expression" dxfId="0" priority="30">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121 F121:G121 J121:L121">
-    <cfRule type="expression" dxfId="0" priority="22">
+    <cfRule type="expression" dxfId="0" priority="26">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122 F122:G122 J122:L122">
-    <cfRule type="expression" dxfId="0" priority="18">
+    <cfRule type="expression" dxfId="0" priority="22">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123 F123:G123 J123:L123">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="0" priority="18">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B124:L133 B134">
-    <cfRule type="expression" dxfId="0" priority="144">
+    <cfRule type="expression" dxfId="0" priority="148">
       <formula>MOD($B124,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171:B172 B174:B177">
-    <cfRule type="expression" dxfId="0" priority="11">
+    <cfRule type="expression" dxfId="0" priority="15">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171:G172 J171:J172 L171:L172 F175:F177 C176:C177">
-    <cfRule type="expression" dxfId="0" priority="12">
+    <cfRule type="expression" dxfId="0" priority="16">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173:G173 J173:L173">
-    <cfRule type="expression" dxfId="0" priority="6">
+    <cfRule type="expression" dxfId="0" priority="10">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174:G174 J174:L177 G175:G177 C175:C177">
-    <cfRule type="expression" dxfId="0" priority="10">
+    <cfRule type="expression" dxfId="0" priority="14">
       <formula>MOD($B174,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D175:E177">
-    <cfRule type="expression" dxfId="0" priority="9">
+    <cfRule type="expression" dxfId="0" priority="13">
       <formula>MOD($B175,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F178 C178">
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J178:L178 G178 C178">
+    <cfRule type="expression" dxfId="0" priority="6">
+      <formula>MOD($B178,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B209:D209 F209:L209 B210:L250">
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>MOD($B209,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B251:L254">
     <cfRule type="expression" dxfId="0" priority="2">
-      <formula>MOD($B178,2)=1</formula>
+      <formula>MOD($B251,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -763,13 +763,13 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -13439,10 +13439,10 @@
     <row r="251" customHeight="1" spans="1:12">
       <c r="A251" s="2">
         <f t="shared" si="6"/>
-        <v>1022420115</v>
+        <v>1022400115</v>
       </c>
       <c r="B251" s="2">
-        <v>102202</v>
+        <v>102200</v>
       </c>
       <c r="C251" s="2">
         <v>15</v>
@@ -13466,10 +13466,10 @@
     <row r="252" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A252" s="3">
         <f t="shared" si="6"/>
-        <v>1022430116</v>
+        <v>1022400116</v>
       </c>
       <c r="B252" s="3">
-        <v>102203</v>
+        <v>102200</v>
       </c>
       <c r="C252" s="3">
         <v>16</v>
@@ -13497,10 +13497,10 @@
     <row r="253" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A253" s="3">
         <f t="shared" si="6"/>
-        <v>1022440117</v>
+        <v>1022400117</v>
       </c>
       <c r="B253" s="3">
-        <v>102204</v>
+        <v>102200</v>
       </c>
       <c r="C253" s="3">
         <v>17</v>
@@ -13528,10 +13528,10 @@
     <row r="254" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A254" s="3">
         <f t="shared" si="6"/>
-        <v>1022450118</v>
+        <v>1022400118</v>
       </c>
       <c r="B254" s="3">
-        <v>102205</v>
+        <v>102200</v>
       </c>
       <c r="C254" s="3">
         <v>18</v>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$254</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$268</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="70">
   <si>
     <t>id</t>
   </si>
@@ -5815,7 +5815,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L254"/>
+  <dimension ref="A1:L294"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="10"/>
@@ -11709,6 +11709,9 @@
       <c r="G179" s="11">
         <v>2</v>
       </c>
+      <c r="I179" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="180" customHeight="1" spans="1:12">
       <c r="A180" s="53">
@@ -11729,6 +11732,9 @@
       <c r="G180" s="11">
         <v>2</v>
       </c>
+      <c r="I180" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="181" customHeight="1" spans="1:12">
       <c r="A181" s="53">
@@ -11749,6 +11755,9 @@
       <c r="G181" s="11">
         <v>4</v>
       </c>
+      <c r="I181" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="182" customHeight="1" spans="1:12">
       <c r="A182" s="53">
@@ -11769,6 +11778,9 @@
       <c r="G182" s="11">
         <v>4</v>
       </c>
+      <c r="I182" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="183" customHeight="1" spans="1:12">
       <c r="A183" s="53">
@@ -11789,6 +11801,9 @@
       <c r="G183" s="11">
         <v>6</v>
       </c>
+      <c r="I183" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="184" customHeight="1" spans="1:12">
       <c r="A184" s="53">
@@ -11809,6 +11824,9 @@
       <c r="G184" s="11">
         <v>8</v>
       </c>
+      <c r="I184" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="185" customHeight="1" spans="1:12">
       <c r="A185" s="53">
@@ -11829,6 +11847,9 @@
       <c r="G185" s="11">
         <v>10</v>
       </c>
+      <c r="I185" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="186" customHeight="1" spans="1:12">
       <c r="A186" s="53">
@@ -11849,6 +11870,9 @@
       <c r="G186" s="11">
         <v>15</v>
       </c>
+      <c r="I186" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="187" customHeight="1" spans="1:12">
       <c r="A187" s="53">
@@ -11869,6 +11893,9 @@
       <c r="G187" s="11">
         <v>5</v>
       </c>
+      <c r="I187" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="188" customHeight="1" spans="1:12">
       <c r="A188" s="53">
@@ -11889,6 +11916,9 @@
       <c r="G188" s="11">
         <v>5</v>
       </c>
+      <c r="I188" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="189" customHeight="1" spans="1:12">
       <c r="A189" s="53">
@@ -11909,6 +11939,9 @@
       <c r="G189" s="11">
         <v>10</v>
       </c>
+      <c r="I189" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="190" customHeight="1" spans="1:12">
       <c r="A190" s="53">
@@ -11929,6 +11962,9 @@
       <c r="G190" s="11">
         <v>10</v>
       </c>
+      <c r="I190" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="191" customHeight="1" spans="1:12">
       <c r="A191" s="53">
@@ -11949,6 +11985,9 @@
       <c r="G191" s="11">
         <v>15</v>
       </c>
+      <c r="I191" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="192" customHeight="1" spans="1:12">
       <c r="A192" s="53">
@@ -11969,6 +12008,9 @@
       <c r="G192" s="11">
         <v>20</v>
       </c>
+      <c r="I192" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="193" customHeight="1" spans="1:12">
       <c r="A193" s="53">
@@ -11989,6 +12031,9 @@
       <c r="G193" s="11">
         <v>40</v>
       </c>
+      <c r="I193" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="194" customHeight="1" spans="1:12">
       <c r="A194" s="53">
@@ -12009,6 +12054,9 @@
       <c r="G194" s="11">
         <v>60</v>
       </c>
+      <c r="I194" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="195" customHeight="1" spans="1:12">
       <c r="A195" s="53">
@@ -12029,6 +12077,9 @@
       <c r="G195" s="11">
         <v>10</v>
       </c>
+      <c r="I195" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="196" customHeight="1" spans="1:12">
       <c r="A196" s="53">
@@ -12049,6 +12100,9 @@
       <c r="G196" s="11">
         <v>10</v>
       </c>
+      <c r="I196" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="197" customHeight="1" spans="1:12">
       <c r="A197" s="53">
@@ -12069,6 +12123,9 @@
       <c r="G197" s="11">
         <v>20</v>
       </c>
+      <c r="I197" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="198" customHeight="1" spans="1:12">
       <c r="A198" s="53">
@@ -12089,6 +12146,9 @@
       <c r="G198" s="11">
         <v>20</v>
       </c>
+      <c r="I198" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="199" customHeight="1" spans="1:12">
       <c r="A199" s="53">
@@ -12109,6 +12169,9 @@
       <c r="G199" s="11">
         <v>30</v>
       </c>
+      <c r="I199" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="200" customHeight="1" spans="1:12">
       <c r="A200" s="53">
@@ -12129,6 +12192,9 @@
       <c r="G200" s="11">
         <v>40</v>
       </c>
+      <c r="I200" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="201" customHeight="1" spans="1:12">
       <c r="A201" s="53">
@@ -12149,6 +12215,9 @@
       <c r="G201" s="11">
         <v>80</v>
       </c>
+      <c r="I201" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="202" customHeight="1" spans="1:12">
       <c r="A202" s="53">
@@ -12169,6 +12238,9 @@
       <c r="G202" s="11">
         <v>120</v>
       </c>
+      <c r="I202" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="203" customHeight="1" spans="1:12">
       <c r="A203" s="53">
@@ -12192,6 +12264,9 @@
       <c r="H203" s="11">
         <v>30170001</v>
       </c>
+      <c r="I203" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="204" customHeight="1" spans="1:12">
       <c r="A204" s="53">
@@ -12215,6 +12290,9 @@
       <c r="H204" s="11">
         <v>30170002</v>
       </c>
+      <c r="I204" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="205" customHeight="1" spans="1:12">
       <c r="A205" s="53">
@@ -12235,6 +12313,9 @@
       <c r="G205" s="11">
         <v>0</v>
       </c>
+      <c r="I205" s="2">
+        <v>0</v>
+      </c>
       <c r="K205" s="11">
         <v>10170003</v>
       </c>
@@ -12261,6 +12342,9 @@
       <c r="G206" s="11">
         <v>0</v>
       </c>
+      <c r="I206" s="2">
+        <v>0</v>
+      </c>
       <c r="K206" s="11">
         <v>10170004</v>
       </c>
@@ -12287,6 +12371,9 @@
       <c r="G207" s="11">
         <v>0</v>
       </c>
+      <c r="I207" s="2">
+        <v>0</v>
+      </c>
       <c r="K207" s="11">
         <v>10170005</v>
       </c>
@@ -12311,6 +12398,9 @@
         <v>1</v>
       </c>
       <c r="G208" s="11">
+        <v>0</v>
+      </c>
+      <c r="I208" s="2">
         <v>0</v>
       </c>
       <c r="K208" s="11">
@@ -12343,6 +12433,9 @@
       <c r="G209" s="11">
         <v>5</v>
       </c>
+      <c r="I209" s="2">
+        <v>0</v>
+      </c>
       <c r="J209" s="12" t="s">
         <v>69</v>
       </c>
@@ -12370,6 +12463,9 @@
       <c r="G210" s="11">
         <v>5</v>
       </c>
+      <c r="I210" s="2">
+        <v>0</v>
+      </c>
       <c r="J210" s="12" t="s">
         <v>69</v>
       </c>
@@ -12397,6 +12493,9 @@
       <c r="G211" s="11">
         <v>5</v>
       </c>
+      <c r="I211" s="2">
+        <v>0</v>
+      </c>
       <c r="J211" s="12" t="s">
         <v>69</v>
       </c>
@@ -12424,6 +12523,9 @@
       <c r="G212" s="11">
         <v>10</v>
       </c>
+      <c r="I212" s="2">
+        <v>0</v>
+      </c>
       <c r="J212" s="12" t="s">
         <v>69</v>
       </c>
@@ -12451,6 +12553,9 @@
       <c r="G213" s="11">
         <v>10</v>
       </c>
+      <c r="I213" s="2">
+        <v>0</v>
+      </c>
       <c r="J213" s="12" t="s">
         <v>69</v>
       </c>
@@ -12478,6 +12583,9 @@
       <c r="G214" s="11">
         <v>20</v>
       </c>
+      <c r="I214" s="2">
+        <v>0</v>
+      </c>
       <c r="J214" s="12" t="s">
         <v>69</v>
       </c>
@@ -12505,6 +12613,9 @@
       <c r="G215" s="11">
         <v>20</v>
       </c>
+      <c r="I215" s="2">
+        <v>0</v>
+      </c>
       <c r="J215" s="12" t="s">
         <v>69</v>
       </c>
@@ -12532,6 +12643,9 @@
       <c r="G216" s="11">
         <v>25</v>
       </c>
+      <c r="I216" s="2">
+        <v>0</v>
+      </c>
       <c r="J216" s="12" t="s">
         <v>69</v>
       </c>
@@ -12559,6 +12673,9 @@
       <c r="G217" s="11">
         <v>30</v>
       </c>
+      <c r="I217" s="2">
+        <v>0</v>
+      </c>
       <c r="J217" s="12" t="s">
         <v>69</v>
       </c>
@@ -12586,6 +12703,9 @@
       <c r="G218" s="11">
         <v>50</v>
       </c>
+      <c r="I218" s="2">
+        <v>0</v>
+      </c>
       <c r="J218" s="12" t="s">
         <v>69</v>
       </c>
@@ -12613,6 +12733,9 @@
       <c r="G219" s="11">
         <v>500</v>
       </c>
+      <c r="I219" s="2">
+        <v>0</v>
+      </c>
       <c r="J219" s="12" t="s">
         <v>69</v>
       </c>
@@ -12640,6 +12763,9 @@
       <c r="G220" s="11">
         <v>500</v>
       </c>
+      <c r="I220" s="2">
+        <v>0</v>
+      </c>
       <c r="J220" s="12" t="s">
         <v>69</v>
       </c>
@@ -12667,6 +12793,9 @@
       <c r="G221" s="11">
         <v>500</v>
       </c>
+      <c r="I221" s="2">
+        <v>0</v>
+      </c>
       <c r="J221" s="12" t="s">
         <v>69</v>
       </c>
@@ -12691,6 +12820,9 @@
       <c r="G222" s="11">
         <v>250</v>
       </c>
+      <c r="I222" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="223" customHeight="1" spans="1:10">
       <c r="A223" s="2">
@@ -12715,6 +12847,9 @@
       <c r="G223" s="11">
         <v>20</v>
       </c>
+      <c r="I223" s="2">
+        <v>0</v>
+      </c>
       <c r="J223" s="12" t="s">
         <v>69</v>
       </c>
@@ -12742,6 +12877,9 @@
       <c r="G224" s="11">
         <v>20</v>
       </c>
+      <c r="I224" s="2">
+        <v>0</v>
+      </c>
       <c r="J224" s="12" t="s">
         <v>69</v>
       </c>
@@ -12769,6 +12907,9 @@
       <c r="G225" s="11">
         <v>20</v>
       </c>
+      <c r="I225" s="2">
+        <v>0</v>
+      </c>
       <c r="J225" s="12" t="s">
         <v>69</v>
       </c>
@@ -12796,6 +12937,9 @@
       <c r="G226" s="11">
         <v>50</v>
       </c>
+      <c r="I226" s="2">
+        <v>0</v>
+      </c>
       <c r="J226" s="12" t="s">
         <v>69</v>
       </c>
@@ -12823,6 +12967,9 @@
       <c r="G227" s="11">
         <v>50</v>
       </c>
+      <c r="I227" s="2">
+        <v>0</v>
+      </c>
       <c r="J227" s="12" t="s">
         <v>69</v>
       </c>
@@ -12850,6 +12997,9 @@
       <c r="G228" s="11">
         <v>75</v>
       </c>
+      <c r="I228" s="2">
+        <v>0</v>
+      </c>
       <c r="J228" s="12" t="s">
         <v>69</v>
       </c>
@@ -12877,6 +13027,9 @@
       <c r="G229" s="11">
         <v>75</v>
       </c>
+      <c r="I229" s="2">
+        <v>0</v>
+      </c>
       <c r="J229" s="12" t="s">
         <v>69</v>
       </c>
@@ -12904,6 +13057,9 @@
       <c r="G230" s="11">
         <v>150</v>
       </c>
+      <c r="I230" s="2">
+        <v>0</v>
+      </c>
       <c r="J230" s="12" t="s">
         <v>69</v>
       </c>
@@ -12931,6 +13087,9 @@
       <c r="G231" s="11">
         <v>200</v>
       </c>
+      <c r="I231" s="2">
+        <v>0</v>
+      </c>
       <c r="J231" s="12" t="s">
         <v>69</v>
       </c>
@@ -12958,6 +13117,9 @@
       <c r="G232" s="11">
         <v>200</v>
       </c>
+      <c r="I232" s="2">
+        <v>0</v>
+      </c>
       <c r="J232" s="12" t="s">
         <v>69</v>
       </c>
@@ -12985,6 +13147,9 @@
       <c r="G233" s="11">
         <v>1000</v>
       </c>
+      <c r="I233" s="2">
+        <v>0</v>
+      </c>
       <c r="J233" s="12" t="s">
         <v>69</v>
       </c>
@@ -13012,6 +13177,9 @@
       <c r="G234" s="11">
         <v>1000</v>
       </c>
+      <c r="I234" s="2">
+        <v>0</v>
+      </c>
       <c r="J234" s="12" t="s">
         <v>69</v>
       </c>
@@ -13039,6 +13207,9 @@
       <c r="G235" s="11">
         <v>1000</v>
       </c>
+      <c r="I235" s="2">
+        <v>0</v>
+      </c>
       <c r="J235" s="12" t="s">
         <v>69</v>
       </c>
@@ -13063,6 +13234,9 @@
       <c r="G236" s="11">
         <v>500</v>
       </c>
+      <c r="I236" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="237" customHeight="1" spans="1:10">
       <c r="A237" s="2">
@@ -13087,6 +13261,9 @@
       <c r="G237" s="11">
         <v>100</v>
       </c>
+      <c r="I237" s="2">
+        <v>0</v>
+      </c>
       <c r="J237" s="12" t="s">
         <v>69</v>
       </c>
@@ -13114,6 +13291,9 @@
       <c r="G238" s="11">
         <v>150</v>
       </c>
+      <c r="I238" s="2">
+        <v>0</v>
+      </c>
       <c r="J238" s="12" t="s">
         <v>69</v>
       </c>
@@ -13141,6 +13321,9 @@
       <c r="G239" s="11">
         <v>150</v>
       </c>
+      <c r="I239" s="2">
+        <v>0</v>
+      </c>
       <c r="J239" s="12" t="s">
         <v>69</v>
       </c>
@@ -13168,6 +13351,9 @@
       <c r="G240" s="11">
         <v>200</v>
       </c>
+      <c r="I240" s="2">
+        <v>0</v>
+      </c>
       <c r="J240" s="12" t="s">
         <v>69</v>
       </c>
@@ -13195,6 +13381,9 @@
       <c r="G241" s="11">
         <v>200</v>
       </c>
+      <c r="I241" s="2">
+        <v>0</v>
+      </c>
       <c r="J241" s="12" t="s">
         <v>69</v>
       </c>
@@ -13222,6 +13411,9 @@
       <c r="G242" s="11">
         <v>400</v>
       </c>
+      <c r="I242" s="2">
+        <v>0</v>
+      </c>
       <c r="J242" s="12" t="s">
         <v>69</v>
       </c>
@@ -13249,6 +13441,9 @@
       <c r="G243" s="11">
         <v>400</v>
       </c>
+      <c r="I243" s="2">
+        <v>0</v>
+      </c>
       <c r="J243" s="12" t="s">
         <v>69</v>
       </c>
@@ -13276,6 +13471,9 @@
       <c r="G244" s="11">
         <v>600</v>
       </c>
+      <c r="I244" s="2">
+        <v>0</v>
+      </c>
       <c r="J244" s="12" t="s">
         <v>69</v>
       </c>
@@ -13303,6 +13501,9 @@
       <c r="G245" s="11">
         <v>800</v>
       </c>
+      <c r="I245" s="2">
+        <v>0</v>
+      </c>
       <c r="J245" s="12" t="s">
         <v>69</v>
       </c>
@@ -13330,6 +13531,9 @@
       <c r="G246" s="11">
         <v>1000</v>
       </c>
+      <c r="I246" s="2">
+        <v>0</v>
+      </c>
       <c r="J246" s="12" t="s">
         <v>69</v>
       </c>
@@ -13357,6 +13561,9 @@
       <c r="G247" s="11">
         <v>2000</v>
       </c>
+      <c r="I247" s="2">
+        <v>0</v>
+      </c>
       <c r="J247" s="12" t="s">
         <v>69</v>
       </c>
@@ -13384,6 +13591,9 @@
       <c r="G248" s="11">
         <v>2000</v>
       </c>
+      <c r="I248" s="2">
+        <v>0</v>
+      </c>
       <c r="J248" s="12" t="s">
         <v>69</v>
       </c>
@@ -13411,6 +13621,9 @@
       <c r="G249" s="11">
         <v>2000</v>
       </c>
+      <c r="I249" s="2">
+        <v>0</v>
+      </c>
       <c r="J249" s="12" t="s">
         <v>69</v>
       </c>
@@ -13435,6 +13648,9 @@
       <c r="G250" s="11">
         <v>1250</v>
       </c>
+      <c r="I250" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="251" customHeight="1" spans="1:12">
       <c r="A251" s="2">
@@ -13456,6 +13672,9 @@
       <c r="G251" s="11">
         <v>0</v>
       </c>
+      <c r="I251" s="2">
+        <v>0</v>
+      </c>
       <c r="K251" s="2">
         <v>102200101</v>
       </c>
@@ -13485,7 +13704,9 @@
         <v>0</v>
       </c>
       <c r="H252" s="40"/>
-      <c r="I252" s="40"/>
+      <c r="I252" s="2">
+        <v>0</v>
+      </c>
       <c r="J252" s="13"/>
       <c r="K252" s="3">
         <v>102200102</v>
@@ -13516,7 +13737,9 @@
         <v>0</v>
       </c>
       <c r="H253" s="40"/>
-      <c r="I253" s="40"/>
+      <c r="I253" s="2">
+        <v>0</v>
+      </c>
       <c r="J253" s="13"/>
       <c r="K253" s="3">
         <v>102200103</v>
@@ -13547,7 +13770,9 @@
         <v>0</v>
       </c>
       <c r="H254" s="40"/>
-      <c r="I254" s="40"/>
+      <c r="I254" s="2">
+        <v>0</v>
+      </c>
       <c r="J254" s="13"/>
       <c r="K254" s="3">
         <v>102200104</v>
@@ -13556,570 +13781,1694 @@
         <v>68</v>
       </c>
     </row>
+    <row r="255" customHeight="1" spans="1:12">
+      <c r="A255" s="3">
+        <f t="shared" ref="A255:A290" si="7">(B255)*10000+C255+F255*100+D255*100000</f>
+        <v>1021300207</v>
+      </c>
+      <c r="B255" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C255" s="2">
+        <v>7</v>
+      </c>
+      <c r="D255" s="2">
+        <v>3</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F255" s="2">
+        <v>2</v>
+      </c>
+      <c r="G255" s="11">
+        <v>1</v>
+      </c>
+      <c r="I255" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" customHeight="1" spans="1:12">
+      <c r="A256" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300208</v>
+      </c>
+      <c r="B256" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C256" s="2">
+        <v>8</v>
+      </c>
+      <c r="D256" s="2">
+        <v>3</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F256" s="2">
+        <v>2</v>
+      </c>
+      <c r="G256" s="11">
+        <v>1</v>
+      </c>
+      <c r="I256" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" customHeight="1" spans="1:9">
+      <c r="A257" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300209</v>
+      </c>
+      <c r="B257" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C257" s="2">
+        <v>9</v>
+      </c>
+      <c r="D257" s="2">
+        <v>3</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F257" s="2">
+        <v>2</v>
+      </c>
+      <c r="G257" s="11">
+        <v>2</v>
+      </c>
+      <c r="I257" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" customHeight="1" spans="1:9">
+      <c r="A258" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300301</v>
+      </c>
+      <c r="B258" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C258" s="2">
+        <v>1</v>
+      </c>
+      <c r="D258" s="2">
+        <v>3</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F258" s="2">
+        <v>3</v>
+      </c>
+      <c r="G258" s="11">
+        <v>2</v>
+      </c>
+      <c r="I258" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" customHeight="1" spans="1:9">
+      <c r="A259" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300302</v>
+      </c>
+      <c r="B259" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C259" s="2">
+        <v>2</v>
+      </c>
+      <c r="D259" s="2">
+        <v>3</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F259" s="2">
+        <v>3</v>
+      </c>
+      <c r="G259" s="11">
+        <v>2</v>
+      </c>
+      <c r="I259" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" customHeight="1" spans="1:9">
+      <c r="A260" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300303</v>
+      </c>
+      <c r="B260" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C260" s="2">
+        <v>3</v>
+      </c>
+      <c r="D260" s="2">
+        <v>3</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F260" s="2">
+        <v>3</v>
+      </c>
+      <c r="G260" s="11">
+        <v>2</v>
+      </c>
+      <c r="I260" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" customHeight="1" spans="1:9">
+      <c r="A261" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300304</v>
+      </c>
+      <c r="B261" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C261" s="2">
+        <v>4</v>
+      </c>
+      <c r="D261" s="2">
+        <v>3</v>
+      </c>
+      <c r="E261" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F261" s="2">
+        <v>3</v>
+      </c>
+      <c r="G261" s="11">
+        <v>2</v>
+      </c>
+      <c r="I261" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" customHeight="1" spans="1:9">
+      <c r="A262" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300305</v>
+      </c>
+      <c r="B262" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C262" s="2">
+        <v>5</v>
+      </c>
+      <c r="D262" s="2">
+        <v>3</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F262" s="2">
+        <v>3</v>
+      </c>
+      <c r="G262" s="11">
+        <v>4</v>
+      </c>
+      <c r="I262" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" customHeight="1" spans="1:9">
+      <c r="A263" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300306</v>
+      </c>
+      <c r="B263" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C263" s="2">
+        <v>6</v>
+      </c>
+      <c r="D263" s="2">
+        <v>3</v>
+      </c>
+      <c r="E263" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F263" s="2">
+        <v>3</v>
+      </c>
+      <c r="G263" s="11">
+        <v>4</v>
+      </c>
+      <c r="I263" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" customHeight="1" spans="1:9">
+      <c r="A264" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300307</v>
+      </c>
+      <c r="B264" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C264" s="2">
+        <v>7</v>
+      </c>
+      <c r="D264" s="2">
+        <v>3</v>
+      </c>
+      <c r="E264" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F264" s="2">
+        <v>3</v>
+      </c>
+      <c r="G264" s="11">
+        <v>8</v>
+      </c>
+      <c r="I264" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" customHeight="1" spans="1:9">
+      <c r="A265" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300308</v>
+      </c>
+      <c r="B265" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C265" s="2">
+        <v>8</v>
+      </c>
+      <c r="D265" s="2">
+        <v>3</v>
+      </c>
+      <c r="E265" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F265" s="2">
+        <v>3</v>
+      </c>
+      <c r="G265" s="11">
+        <v>8</v>
+      </c>
+      <c r="I265" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" customHeight="1" spans="1:9">
+      <c r="A266" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300309</v>
+      </c>
+      <c r="B266" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C266" s="2">
+        <v>9</v>
+      </c>
+      <c r="D266" s="2">
+        <v>3</v>
+      </c>
+      <c r="E266" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F266" s="2">
+        <v>3</v>
+      </c>
+      <c r="G266" s="11">
+        <v>8</v>
+      </c>
+      <c r="I266" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" customHeight="1" spans="1:9">
+      <c r="A267" s="3">
+        <f t="shared" si="7"/>
+        <v>1021400310</v>
+      </c>
+      <c r="B267" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C267" s="2">
+        <v>10</v>
+      </c>
+      <c r="D267" s="2">
+        <v>4</v>
+      </c>
+      <c r="F267" s="2">
+        <v>3</v>
+      </c>
+      <c r="G267" s="11">
+        <v>0</v>
+      </c>
+      <c r="I267" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" customHeight="1" spans="1:9">
+      <c r="A268" s="3">
+        <f t="shared" si="7"/>
+        <v>1021400312</v>
+      </c>
+      <c r="B268" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C268" s="2">
+        <v>12</v>
+      </c>
+      <c r="D268" s="2">
+        <v>4</v>
+      </c>
+      <c r="F268" s="2">
+        <v>3</v>
+      </c>
+      <c r="G268" s="11">
+        <v>0</v>
+      </c>
+      <c r="I268" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" customHeight="1" spans="1:9">
+      <c r="A269" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300401</v>
+      </c>
+      <c r="B269" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C269" s="2">
+        <v>1</v>
+      </c>
+      <c r="D269" s="2">
+        <v>3</v>
+      </c>
+      <c r="E269" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F269" s="2">
+        <v>4</v>
+      </c>
+      <c r="G269" s="11">
+        <v>6</v>
+      </c>
+      <c r="I269" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" customHeight="1" spans="1:9">
+      <c r="A270" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300402</v>
+      </c>
+      <c r="B270" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C270" s="2">
+        <v>2</v>
+      </c>
+      <c r="D270" s="2">
+        <v>3</v>
+      </c>
+      <c r="E270" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F270" s="2">
+        <v>4</v>
+      </c>
+      <c r="G270" s="11">
+        <v>6</v>
+      </c>
+      <c r="I270" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" customHeight="1" spans="1:9">
+      <c r="A271" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300403</v>
+      </c>
+      <c r="B271" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C271" s="2">
+        <v>3</v>
+      </c>
+      <c r="D271" s="2">
+        <v>3</v>
+      </c>
+      <c r="E271" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F271" s="2">
+        <v>4</v>
+      </c>
+      <c r="G271" s="11">
+        <v>8</v>
+      </c>
+      <c r="I271" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" customHeight="1" spans="1:9">
+      <c r="A272" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300404</v>
+      </c>
+      <c r="B272" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C272" s="2">
+        <v>4</v>
+      </c>
+      <c r="D272" s="2">
+        <v>3</v>
+      </c>
+      <c r="E272" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F272" s="2">
+        <v>4</v>
+      </c>
+      <c r="G272" s="11">
+        <v>8</v>
+      </c>
+      <c r="I272" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" customHeight="1" spans="1:9">
+      <c r="A273" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300405</v>
+      </c>
+      <c r="B273" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C273" s="2">
+        <v>5</v>
+      </c>
+      <c r="D273" s="2">
+        <v>3</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F273" s="2">
+        <v>4</v>
+      </c>
+      <c r="G273" s="11">
+        <v>12</v>
+      </c>
+      <c r="I273" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" customHeight="1" spans="1:9">
+      <c r="A274" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300406</v>
+      </c>
+      <c r="B274" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C274" s="2">
+        <v>6</v>
+      </c>
+      <c r="D274" s="2">
+        <v>3</v>
+      </c>
+      <c r="E274" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F274" s="2">
+        <v>4</v>
+      </c>
+      <c r="G274" s="11">
+        <v>12</v>
+      </c>
+      <c r="I274" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" customHeight="1" spans="1:9">
+      <c r="A275" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300407</v>
+      </c>
+      <c r="B275" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C275" s="2">
+        <v>7</v>
+      </c>
+      <c r="D275" s="2">
+        <v>3</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F275" s="2">
+        <v>4</v>
+      </c>
+      <c r="G275" s="11">
+        <v>40</v>
+      </c>
+      <c r="I275" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" customHeight="1" spans="1:9">
+      <c r="A276" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300408</v>
+      </c>
+      <c r="B276" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C276" s="2">
+        <v>8</v>
+      </c>
+      <c r="D276" s="2">
+        <v>3</v>
+      </c>
+      <c r="E276" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F276" s="2">
+        <v>4</v>
+      </c>
+      <c r="G276" s="11">
+        <v>40</v>
+      </c>
+      <c r="I276" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" customHeight="1" spans="1:9">
+      <c r="A277" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300409</v>
+      </c>
+      <c r="B277" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C277" s="2">
+        <v>9</v>
+      </c>
+      <c r="D277" s="2">
+        <v>3</v>
+      </c>
+      <c r="E277" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F277" s="2">
+        <v>4</v>
+      </c>
+      <c r="G277" s="11">
+        <v>100</v>
+      </c>
+      <c r="I277" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" customHeight="1" spans="1:9">
+      <c r="A278" s="3">
+        <f t="shared" si="7"/>
+        <v>1021400410</v>
+      </c>
+      <c r="B278" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C278" s="2">
+        <v>10</v>
+      </c>
+      <c r="D278" s="2">
+        <v>4</v>
+      </c>
+      <c r="F278" s="2">
+        <v>4</v>
+      </c>
+      <c r="G278" s="11">
+        <v>0</v>
+      </c>
+      <c r="I278" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" customHeight="1" spans="1:9">
+      <c r="A279" s="3">
+        <f t="shared" si="7"/>
+        <v>1021400412</v>
+      </c>
+      <c r="B279" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C279" s="2">
+        <v>12</v>
+      </c>
+      <c r="D279" s="2">
+        <v>4</v>
+      </c>
+      <c r="F279" s="2">
+        <v>4</v>
+      </c>
+      <c r="G279" s="11">
+        <v>0</v>
+      </c>
+      <c r="I279" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" customHeight="1" spans="1:9">
+      <c r="A280" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300501</v>
+      </c>
+      <c r="B280" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C280" s="2">
+        <v>1</v>
+      </c>
+      <c r="D280" s="2">
+        <v>3</v>
+      </c>
+      <c r="E280" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F280" s="2">
+        <v>5</v>
+      </c>
+      <c r="G280" s="11">
+        <v>40</v>
+      </c>
+      <c r="I280" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" customHeight="1" spans="1:9">
+      <c r="A281" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300502</v>
+      </c>
+      <c r="B281" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C281" s="2">
+        <v>2</v>
+      </c>
+      <c r="D281" s="2">
+        <v>3</v>
+      </c>
+      <c r="E281" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F281" s="2">
+        <v>5</v>
+      </c>
+      <c r="G281" s="11">
+        <v>40</v>
+      </c>
+      <c r="I281" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" customHeight="1" spans="1:9">
+      <c r="A282" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300503</v>
+      </c>
+      <c r="B282" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C282" s="2">
+        <v>3</v>
+      </c>
+      <c r="D282" s="2">
+        <v>3</v>
+      </c>
+      <c r="E282" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F282" s="2">
+        <v>5</v>
+      </c>
+      <c r="G282" s="11">
+        <v>80</v>
+      </c>
+      <c r="I282" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" customHeight="1" spans="1:9">
+      <c r="A283" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300504</v>
+      </c>
+      <c r="B283" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C283" s="2">
+        <v>4</v>
+      </c>
+      <c r="D283" s="2">
+        <v>3</v>
+      </c>
+      <c r="E283" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F283" s="2">
+        <v>5</v>
+      </c>
+      <c r="G283" s="11">
+        <v>80</v>
+      </c>
+      <c r="I283" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" customHeight="1" spans="1:9">
+      <c r="A284" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300505</v>
+      </c>
+      <c r="B284" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C284" s="2">
+        <v>5</v>
+      </c>
+      <c r="D284" s="2">
+        <v>3</v>
+      </c>
+      <c r="E284" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F284" s="2">
+        <v>5</v>
+      </c>
+      <c r="G284" s="11">
+        <v>200</v>
+      </c>
+      <c r="I284" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" customHeight="1" spans="1:9">
+      <c r="A285" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300506</v>
+      </c>
+      <c r="B285" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C285" s="2">
+        <v>6</v>
+      </c>
+      <c r="D285" s="2">
+        <v>3</v>
+      </c>
+      <c r="E285" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F285" s="2">
+        <v>5</v>
+      </c>
+      <c r="G285" s="11">
+        <v>200</v>
+      </c>
+      <c r="I285" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" customHeight="1" spans="1:9">
+      <c r="A286" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300507</v>
+      </c>
+      <c r="B286" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C286" s="2">
+        <v>7</v>
+      </c>
+      <c r="D286" s="2">
+        <v>3</v>
+      </c>
+      <c r="E286" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F286" s="2">
+        <v>5</v>
+      </c>
+      <c r="G286" s="11">
+        <v>400</v>
+      </c>
+      <c r="I286" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" customHeight="1" spans="1:9">
+      <c r="A287" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300508</v>
+      </c>
+      <c r="B287" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C287" s="2">
+        <v>8</v>
+      </c>
+      <c r="D287" s="2">
+        <v>3</v>
+      </c>
+      <c r="E287" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F287" s="2">
+        <v>5</v>
+      </c>
+      <c r="G287" s="11">
+        <v>400</v>
+      </c>
+      <c r="I287" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" customHeight="1" spans="1:9">
+      <c r="A288" s="3">
+        <f t="shared" si="7"/>
+        <v>1021300509</v>
+      </c>
+      <c r="B288" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C288" s="2">
+        <v>9</v>
+      </c>
+      <c r="D288" s="2">
+        <v>3</v>
+      </c>
+      <c r="E288" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F288" s="2">
+        <v>5</v>
+      </c>
+      <c r="G288" s="11">
+        <v>1000</v>
+      </c>
+      <c r="I288" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" customHeight="1" spans="1:12">
+      <c r="A289" s="3">
+        <f t="shared" si="7"/>
+        <v>1021400510</v>
+      </c>
+      <c r="B289" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C289" s="2">
+        <v>10</v>
+      </c>
+      <c r="D289" s="2">
+        <v>4</v>
+      </c>
+      <c r="F289" s="2">
+        <v>5</v>
+      </c>
+      <c r="G289" s="11">
+        <v>0</v>
+      </c>
+      <c r="I289" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" customHeight="1" spans="1:12">
+      <c r="A290" s="3">
+        <f t="shared" si="7"/>
+        <v>1021400512</v>
+      </c>
+      <c r="B290" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C290" s="2">
+        <v>12</v>
+      </c>
+      <c r="D290" s="2">
+        <v>4</v>
+      </c>
+      <c r="F290" s="2">
+        <v>5</v>
+      </c>
+      <c r="G290" s="11">
+        <v>0</v>
+      </c>
+      <c r="I290" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" customHeight="1" spans="1:12">
+      <c r="A291" s="3">
+        <f>(B291)*10000+C291+F291*100+D291*100000</f>
+        <v>1021400113</v>
+      </c>
+      <c r="B291" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C291" s="2">
+        <v>13</v>
+      </c>
+      <c r="D291" s="2">
+        <v>4</v>
+      </c>
+      <c r="F291" s="2">
+        <v>1</v>
+      </c>
+      <c r="G291" s="11">
+        <v>0</v>
+      </c>
+      <c r="I291" s="11">
+        <v>0</v>
+      </c>
+      <c r="K291" s="2">
+        <v>102100101</v>
+      </c>
+      <c r="L291" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="292" customHeight="1" spans="1:12">
+      <c r="A292" s="3">
+        <f>(B292)*10000+C292+F292*100+D292*100000</f>
+        <v>1021400114</v>
+      </c>
+      <c r="B292" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C292" s="2">
+        <v>14</v>
+      </c>
+      <c r="D292" s="2">
+        <v>4</v>
+      </c>
+      <c r="F292" s="2">
+        <v>1</v>
+      </c>
+      <c r="G292" s="11">
+        <v>0</v>
+      </c>
+      <c r="I292" s="11">
+        <v>0</v>
+      </c>
+      <c r="K292" s="3">
+        <v>102100102</v>
+      </c>
+      <c r="L292" s="13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="293" customHeight="1" spans="1:12">
+      <c r="A293" s="3">
+        <f>(B293)*10000+C293+F293*100+D293*100000</f>
+        <v>1021400115</v>
+      </c>
+      <c r="B293" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C293" s="2">
+        <v>15</v>
+      </c>
+      <c r="D293" s="2">
+        <v>4</v>
+      </c>
+      <c r="F293" s="2">
+        <v>1</v>
+      </c>
+      <c r="G293" s="11">
+        <v>0</v>
+      </c>
+      <c r="I293" s="11">
+        <v>0</v>
+      </c>
+      <c r="K293" s="3">
+        <v>102100103</v>
+      </c>
+      <c r="L293" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="294" customHeight="1" spans="1:12">
+      <c r="A294" s="3">
+        <f>(B294)*10000+C294+F294*100+D294*100000</f>
+        <v>1021400116</v>
+      </c>
+      <c r="B294" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C294" s="2">
+        <v>16</v>
+      </c>
+      <c r="D294" s="2">
+        <v>4</v>
+      </c>
+      <c r="F294" s="2">
+        <v>1</v>
+      </c>
+      <c r="G294" s="11">
+        <v>0</v>
+      </c>
+      <c r="I294" s="11">
+        <v>0</v>
+      </c>
+      <c r="K294" s="3">
+        <v>102100104</v>
+      </c>
+      <c r="L294" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L254" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L268" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="0" priority="120">
+    <cfRule type="expression" dxfId="0" priority="128">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D85:E85">
-    <cfRule type="expression" dxfId="0" priority="146">
+    <cfRule type="expression" dxfId="0" priority="154">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D86:E86">
-    <cfRule type="expression" dxfId="0" priority="111">
+    <cfRule type="expression" dxfId="0" priority="119">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105">
-    <cfRule type="duplicateValues" dxfId="1" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105:E105">
-    <cfRule type="expression" dxfId="0" priority="91">
+    <cfRule type="expression" dxfId="0" priority="99">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I105">
-    <cfRule type="expression" dxfId="0" priority="93">
+    <cfRule type="expression" dxfId="0" priority="101">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A106">
-    <cfRule type="duplicateValues" dxfId="1" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D106:E106">
-    <cfRule type="expression" dxfId="0" priority="87">
+    <cfRule type="expression" dxfId="0" priority="95">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I106">
-    <cfRule type="expression" dxfId="0" priority="89">
+    <cfRule type="expression" dxfId="0" priority="97">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="1" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D107:E107">
-    <cfRule type="expression" dxfId="0" priority="83">
+    <cfRule type="expression" dxfId="0" priority="91">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I107">
-    <cfRule type="expression" dxfId="0" priority="85">
+    <cfRule type="expression" dxfId="0" priority="93">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108">
-    <cfRule type="duplicateValues" dxfId="1" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D108:E108">
-    <cfRule type="expression" dxfId="0" priority="79">
+    <cfRule type="expression" dxfId="0" priority="87">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I108">
-    <cfRule type="expression" dxfId="0" priority="81">
+    <cfRule type="expression" dxfId="0" priority="89">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" dxfId="1" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D109:E109">
-    <cfRule type="expression" dxfId="0" priority="75">
+    <cfRule type="expression" dxfId="0" priority="83">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I109">
-    <cfRule type="expression" dxfId="0" priority="77">
+    <cfRule type="expression" dxfId="0" priority="85">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110">
-    <cfRule type="duplicateValues" dxfId="1" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D110:E110">
-    <cfRule type="expression" dxfId="0" priority="71">
+    <cfRule type="expression" dxfId="0" priority="79">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I110">
-    <cfRule type="expression" dxfId="0" priority="73">
+    <cfRule type="expression" dxfId="0" priority="81">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A111">
-    <cfRule type="duplicateValues" dxfId="1" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D111:E111">
-    <cfRule type="expression" dxfId="0" priority="67">
+    <cfRule type="expression" dxfId="0" priority="75">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I111">
-    <cfRule type="expression" dxfId="0" priority="69">
+    <cfRule type="expression" dxfId="0" priority="77">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112">
-    <cfRule type="duplicateValues" dxfId="1" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D112:E112">
-    <cfRule type="expression" dxfId="0" priority="63">
+    <cfRule type="expression" dxfId="0" priority="71">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I112">
-    <cfRule type="expression" dxfId="0" priority="65">
+    <cfRule type="expression" dxfId="0" priority="73">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A113">
-    <cfRule type="duplicateValues" dxfId="1" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D113:E113">
-    <cfRule type="expression" dxfId="0" priority="59">
+    <cfRule type="expression" dxfId="0" priority="67">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I113">
-    <cfRule type="expression" dxfId="0" priority="61">
+    <cfRule type="expression" dxfId="0" priority="69">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114">
-    <cfRule type="duplicateValues" dxfId="1" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D114:E114">
-    <cfRule type="expression" dxfId="0" priority="55">
+    <cfRule type="expression" dxfId="0" priority="63">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I114">
-    <cfRule type="expression" dxfId="0" priority="57">
+    <cfRule type="expression" dxfId="0" priority="65">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A115">
-    <cfRule type="duplicateValues" dxfId="1" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D115:E115">
-    <cfRule type="expression" dxfId="0" priority="51">
+    <cfRule type="expression" dxfId="0" priority="59">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I115">
-    <cfRule type="expression" dxfId="0" priority="53">
+    <cfRule type="expression" dxfId="0" priority="61">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A116">
-    <cfRule type="duplicateValues" dxfId="1" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D116:E116">
-    <cfRule type="expression" dxfId="0" priority="47">
+    <cfRule type="expression" dxfId="0" priority="55">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I116">
-    <cfRule type="expression" dxfId="0" priority="49">
+    <cfRule type="expression" dxfId="0" priority="57">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117">
-    <cfRule type="duplicateValues" dxfId="1" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D117:E117">
-    <cfRule type="expression" dxfId="0" priority="43">
+    <cfRule type="expression" dxfId="0" priority="51">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I117">
-    <cfRule type="expression" dxfId="0" priority="45">
+    <cfRule type="expression" dxfId="0" priority="53">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A118">
-    <cfRule type="duplicateValues" dxfId="1" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D118:E118">
-    <cfRule type="expression" dxfId="0" priority="39">
+    <cfRule type="expression" dxfId="0" priority="47">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I118">
-    <cfRule type="expression" dxfId="0" priority="41">
+    <cfRule type="expression" dxfId="0" priority="49">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A119">
-    <cfRule type="duplicateValues" dxfId="1" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D119:E119">
-    <cfRule type="expression" dxfId="0" priority="35">
+    <cfRule type="expression" dxfId="0" priority="43">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I119">
-    <cfRule type="expression" dxfId="0" priority="37">
+    <cfRule type="expression" dxfId="0" priority="45">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A120">
-    <cfRule type="duplicateValues" dxfId="1" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D120:E120">
-    <cfRule type="expression" dxfId="0" priority="31">
+    <cfRule type="expression" dxfId="0" priority="39">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I120">
-    <cfRule type="expression" dxfId="0" priority="33">
+    <cfRule type="expression" dxfId="0" priority="41">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A121">
-    <cfRule type="duplicateValues" dxfId="1" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D121:E121">
-    <cfRule type="expression" dxfId="0" priority="27">
+    <cfRule type="expression" dxfId="0" priority="35">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I121">
-    <cfRule type="expression" dxfId="0" priority="29">
+    <cfRule type="expression" dxfId="0" priority="37">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A122">
-    <cfRule type="duplicateValues" dxfId="1" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D122:E122">
-    <cfRule type="expression" dxfId="0" priority="23">
+    <cfRule type="expression" dxfId="0" priority="31">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I122">
-    <cfRule type="expression" dxfId="0" priority="25">
+    <cfRule type="expression" dxfId="0" priority="33">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A123">
-    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D123:E123">
-    <cfRule type="expression" dxfId="0" priority="19">
+    <cfRule type="expression" dxfId="0" priority="27">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I123">
-    <cfRule type="expression" dxfId="0" priority="21">
+    <cfRule type="expression" dxfId="0" priority="29">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C134:L134">
-    <cfRule type="expression" dxfId="0" priority="147">
+    <cfRule type="expression" dxfId="0" priority="155">
       <formula>MOD($B134,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="expression" dxfId="0" priority="11">
+    <cfRule type="expression" dxfId="0" priority="19">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A178">
-    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B178">
-    <cfRule type="expression" dxfId="0" priority="7">
+    <cfRule type="expression" dxfId="0" priority="15">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D178:E178">
-    <cfRule type="expression" dxfId="0" priority="5">
+    <cfRule type="expression" dxfId="0" priority="13">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:A60">
-    <cfRule type="duplicateValues" dxfId="1" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A87:A92">
-    <cfRule type="duplicateValues" dxfId="1" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A93:A98">
-    <cfRule type="duplicateValues" dxfId="1" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99:A104">
-    <cfRule type="duplicateValues" dxfId="1" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A135:A177">
-    <cfRule type="duplicateValues" dxfId="1" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A209:A254">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  <conditionalFormatting sqref="A209:A294">
+    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B60">
-    <cfRule type="expression" dxfId="0" priority="106">
+    <cfRule type="expression" dxfId="0" priority="114">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C84">
-    <cfRule type="expression" dxfId="0" priority="109">
+    <cfRule type="expression" dxfId="0" priority="117">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C280:C294">
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>MOD($B280,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E93:E98">
-    <cfRule type="expression" dxfId="0" priority="98">
+    <cfRule type="expression" dxfId="0" priority="106">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E99:E104">
-    <cfRule type="expression" dxfId="0" priority="95">
+    <cfRule type="expression" dxfId="0" priority="103">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E255:E266">
+    <cfRule type="expression" dxfId="0" priority="7">
+      <formula>MOD($B255,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E269:E277">
+    <cfRule type="expression" dxfId="0" priority="5">
+      <formula>MOD($B269,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E280:E288">
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>MOD($B280,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K39:K42">
-    <cfRule type="duplicateValues" dxfId="2" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K169:K172">
-    <cfRule type="duplicateValues" dxfId="2" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K291:K294">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD($B291,2)=1</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L205:L208">
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="0" priority="12">
       <formula>MOD($B205,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A255:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="421"/>
+  <conditionalFormatting sqref="L291:L294">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>MOD($B291,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A295:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="429"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L4">
-    <cfRule type="expression" dxfId="0" priority="420">
+    <cfRule type="expression" dxfId="0" priority="428">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41:B42 B44:B47">
-    <cfRule type="expression" dxfId="0" priority="154">
+    <cfRule type="expression" dxfId="0" priority="162">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 H179:L204 B179:G208 I205:K208 B255:L1048576">
-    <cfRule type="expression" dxfId="0" priority="419">
+  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 H179:L204 B179:G208 I205:K208 B257:D266 F257:L266 B267:L268 B269:B294 D269:D277 F269:L277 D278:L279 D280:D288 F280:L288 D289:L290 D291:J294 B295:L1048576 I209:I254 B256">
+    <cfRule type="expression" dxfId="0" priority="427">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43:G43 J43:L43">
-    <cfRule type="expression" dxfId="0" priority="119">
+    <cfRule type="expression" dxfId="0" priority="127">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44:G44 J44:L47 G45:G47 C45:C47">
-    <cfRule type="expression" dxfId="0" priority="153">
+    <cfRule type="expression" dxfId="0" priority="161">
       <formula>MOD($B44,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45:E47">
-    <cfRule type="expression" dxfId="0" priority="150">
+    <cfRule type="expression" dxfId="0" priority="158">
       <formula>MOD($B45,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F60 C48:C60">
-    <cfRule type="expression" dxfId="0" priority="107">
+    <cfRule type="expression" dxfId="0" priority="115">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
-    <cfRule type="expression" dxfId="0" priority="105">
+    <cfRule type="expression" dxfId="0" priority="113">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D48:E60">
-    <cfRule type="expression" dxfId="0" priority="103">
+    <cfRule type="expression" dxfId="0" priority="111">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B77:B84 F77:L84">
-    <cfRule type="expression" dxfId="0" priority="149">
+    <cfRule type="expression" dxfId="0" priority="157">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85:C85 F85:L85">
-    <cfRule type="expression" dxfId="0" priority="145">
+    <cfRule type="expression" dxfId="0" priority="153">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B86:C86 F86:L86">
-    <cfRule type="expression" dxfId="0" priority="110">
+    <cfRule type="expression" dxfId="0" priority="118">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87:C92 F87:L92 I93:I104">
-    <cfRule type="expression" dxfId="0" priority="100">
+    <cfRule type="expression" dxfId="0" priority="108">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87:E92 D93:D104">
-    <cfRule type="expression" dxfId="0" priority="101">
+    <cfRule type="expression" dxfId="0" priority="109">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:C98 F93:H98 J93:L98">
-    <cfRule type="expression" dxfId="0" priority="97">
+    <cfRule type="expression" dxfId="0" priority="105">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99:C104 F99:H104 J99:L104">
-    <cfRule type="expression" dxfId="0" priority="94">
+    <cfRule type="expression" dxfId="0" priority="102">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:C105 F105:H105 J105:L105">
-    <cfRule type="expression" dxfId="0" priority="90">
+    <cfRule type="expression" dxfId="0" priority="98">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106:C106 F106:H106 J106:L106 H107:H111 C107:C111">
-    <cfRule type="expression" dxfId="0" priority="86">
+    <cfRule type="expression" dxfId="0" priority="94">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107 F107:G107 J107:L107">
-    <cfRule type="expression" dxfId="0" priority="82">
+    <cfRule type="expression" dxfId="0" priority="90">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B108 F108:G108 J108:L108">
-    <cfRule type="expression" dxfId="0" priority="78">
+    <cfRule type="expression" dxfId="0" priority="86">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B109 F109:G109 J109:L109">
-    <cfRule type="expression" dxfId="0" priority="74">
+    <cfRule type="expression" dxfId="0" priority="82">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B110 F110:G110 J110:L110">
-    <cfRule type="expression" dxfId="0" priority="70">
+    <cfRule type="expression" dxfId="0" priority="78">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111 F111:G111 J111:L111">
-    <cfRule type="expression" dxfId="0" priority="66">
+    <cfRule type="expression" dxfId="0" priority="74">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112:C112 F112:H112 J112:L112 H113:H117 C113:C117">
-    <cfRule type="expression" dxfId="0" priority="62">
+    <cfRule type="expression" dxfId="0" priority="70">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113 F113:G113 J113:L113">
-    <cfRule type="expression" dxfId="0" priority="58">
+    <cfRule type="expression" dxfId="0" priority="66">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114 F114:G114 J114:L114">
-    <cfRule type="expression" dxfId="0" priority="54">
+    <cfRule type="expression" dxfId="0" priority="62">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115 F115:G115 J115:L115">
-    <cfRule type="expression" dxfId="0" priority="50">
+    <cfRule type="expression" dxfId="0" priority="58">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B116 F116:G116 J116:L116">
-    <cfRule type="expression" dxfId="0" priority="46">
+    <cfRule type="expression" dxfId="0" priority="54">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117 F117:G117 J117:L117">
-    <cfRule type="expression" dxfId="0" priority="42">
+    <cfRule type="expression" dxfId="0" priority="50">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118:C118 F118:H118 J118:L118 H119:H123 C119:C123">
-    <cfRule type="expression" dxfId="0" priority="38">
+    <cfRule type="expression" dxfId="0" priority="46">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119 F119:G119 J119:L119">
-    <cfRule type="expression" dxfId="0" priority="34">
+    <cfRule type="expression" dxfId="0" priority="42">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120 F120:G120 J120:L120">
-    <cfRule type="expression" dxfId="0" priority="30">
+    <cfRule type="expression" dxfId="0" priority="38">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121 F121:G121 J121:L121">
-    <cfRule type="expression" dxfId="0" priority="26">
+    <cfRule type="expression" dxfId="0" priority="34">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122 F122:G122 J122:L122">
-    <cfRule type="expression" dxfId="0" priority="22">
+    <cfRule type="expression" dxfId="0" priority="30">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123 F123:G123 J123:L123">
-    <cfRule type="expression" dxfId="0" priority="18">
+    <cfRule type="expression" dxfId="0" priority="26">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B124:L133 B134">
-    <cfRule type="expression" dxfId="0" priority="148">
+    <cfRule type="expression" dxfId="0" priority="156">
       <formula>MOD($B124,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171:B172 B174:B177">
-    <cfRule type="expression" dxfId="0" priority="15">
+    <cfRule type="expression" dxfId="0" priority="23">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171:G172 J171:J172 L171:L172 F175:F177 C176:C177">
-    <cfRule type="expression" dxfId="0" priority="16">
+    <cfRule type="expression" dxfId="0" priority="24">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173:G173 J173:L173">
-    <cfRule type="expression" dxfId="0" priority="10">
+    <cfRule type="expression" dxfId="0" priority="18">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174:G174 J174:L177 G175:G177 C175:C177">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="0" priority="22">
       <formula>MOD($B174,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D175:E177">
-    <cfRule type="expression" dxfId="0" priority="13">
+    <cfRule type="expression" dxfId="0" priority="21">
       <formula>MOD($B175,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F178 C178">
-    <cfRule type="expression" dxfId="0" priority="8">
+    <cfRule type="expression" dxfId="0" priority="16">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J178:L178 G178 C178">
-    <cfRule type="expression" dxfId="0" priority="6">
+    <cfRule type="expression" dxfId="0" priority="14">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B209:D209 F209:L209 B210:L250">
-    <cfRule type="expression" dxfId="0" priority="3">
+  <conditionalFormatting sqref="B209:D209 F209:H209 J209:L250 B210:H250">
+    <cfRule type="expression" dxfId="0" priority="11">
       <formula>MOD($B209,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B251:L254">
-    <cfRule type="expression" dxfId="0" priority="2">
+  <conditionalFormatting sqref="B251:H254 J251:L254">
+    <cfRule type="expression" dxfId="0" priority="10">
       <formula>MOD($B251,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B255 B257 B259 B261 B263 B265 B267 B269 B271 B273 B275 B277 B279 B281 B283 B285 B287 B289 B291 B293">
+    <cfRule type="expression" dxfId="0" priority="8">
+      <formula>MOD($B255,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C255:D255 F255:L255">
+    <cfRule type="expression" dxfId="0" priority="431">
+      <formula>MOD($B256,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C256:D256 F256:L256 D258 D260 D262 D264 D266 I258 I260 I262 I264 I266 I268 I270 I272 I274 I276 I278 I280 I282 I284 I286 I288 I290">
+    <cfRule type="expression" dxfId="0" priority="430">
+      <formula>MOD(#REF!,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C269:C277 C278:C279">
+    <cfRule type="expression" dxfId="0" priority="6">
+      <formula>MOD($B269,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$268</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$294</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -763,13 +763,13 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -11362,7 +11362,7 @@
         <v>0</v>
       </c>
       <c r="H169" s="19">
-        <v>30010001</v>
+        <v>30240001</v>
       </c>
       <c r="I169" s="2">
         <v>0</v>
@@ -11399,7 +11399,7 @@
         <v>0</v>
       </c>
       <c r="H170" s="19">
-        <v>30010002</v>
+        <v>30240002</v>
       </c>
       <c r="I170" s="2">
         <v>0</v>
@@ -11436,7 +11436,7 @@
         <v>0</v>
       </c>
       <c r="H171" s="19">
-        <v>30010003</v>
+        <v>30240003</v>
       </c>
       <c r="I171" s="2">
         <v>0</v>
@@ -11473,7 +11473,7 @@
         <v>0</v>
       </c>
       <c r="H172" s="19">
-        <v>30010004</v>
+        <v>30240004</v>
       </c>
       <c r="I172" s="2">
         <v>0</v>
@@ -11508,7 +11508,7 @@
         <v>0</v>
       </c>
       <c r="H173" s="25">
-        <v>30010005</v>
+        <v>30240005</v>
       </c>
       <c r="I173" s="2">
         <v>0</v>
@@ -11543,7 +11543,7 @@
         <v>0</v>
       </c>
       <c r="H174" s="29">
-        <v>30010006</v>
+        <v>30240006</v>
       </c>
       <c r="I174" s="2">
         <v>0</v>
@@ -11677,7 +11677,7 @@
         <v>0</v>
       </c>
       <c r="H178" s="37">
-        <v>30010007</v>
+        <v>30240007</v>
       </c>
       <c r="I178" s="2">
         <v>0</v>
@@ -13783,7 +13783,7 @@
     </row>
     <row r="255" customHeight="1" spans="1:12">
       <c r="A255" s="3">
-        <f t="shared" ref="A255:A290" si="7">(B255)*10000+C255+F255*100+D255*100000</f>
+        <f t="shared" ref="A255:A294" si="7">(B255)*10000+C255+F255*100+D255*100000</f>
         <v>1021300207</v>
       </c>
       <c r="B255" s="2">
@@ -14125,6 +14125,9 @@
       <c r="G267" s="11">
         <v>0</v>
       </c>
+      <c r="H267" s="11">
+        <v>30210002</v>
+      </c>
       <c r="I267" s="11">
         <v>0</v>
       </c>
@@ -14149,6 +14152,9 @@
       <c r="G268" s="11">
         <v>0</v>
       </c>
+      <c r="H268" s="11">
+        <v>30210001</v>
+      </c>
       <c r="I268" s="11">
         <v>0</v>
       </c>
@@ -14416,6 +14422,9 @@
       <c r="G278" s="11">
         <v>0</v>
       </c>
+      <c r="H278" s="11">
+        <v>30210002</v>
+      </c>
       <c r="I278" s="11">
         <v>0</v>
       </c>
@@ -14440,6 +14449,9 @@
       <c r="G279" s="11">
         <v>0</v>
       </c>
+      <c r="H279" s="11">
+        <v>30210001</v>
+      </c>
       <c r="I279" s="11">
         <v>0</v>
       </c>
@@ -14707,6 +14719,9 @@
       <c r="G289" s="11">
         <v>0</v>
       </c>
+      <c r="H289" s="11">
+        <v>30210002</v>
+      </c>
       <c r="I289" s="11">
         <v>0</v>
       </c>
@@ -14731,13 +14746,16 @@
       <c r="G290" s="11">
         <v>0</v>
       </c>
+      <c r="H290" s="11">
+        <v>30210001</v>
+      </c>
       <c r="I290" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="291" customHeight="1" spans="1:12">
       <c r="A291" s="3">
-        <f>(B291)*10000+C291+F291*100+D291*100000</f>
+        <f t="shared" si="7"/>
         <v>1021400113</v>
       </c>
       <c r="B291" s="2">
@@ -14767,7 +14785,7 @@
     </row>
     <row r="292" customHeight="1" spans="1:12">
       <c r="A292" s="3">
-        <f>(B292)*10000+C292+F292*100+D292*100000</f>
+        <f t="shared" si="7"/>
         <v>1021400114</v>
       </c>
       <c r="B292" s="2">
@@ -14797,7 +14815,7 @@
     </row>
     <row r="293" customHeight="1" spans="1:12">
       <c r="A293" s="3">
-        <f>(B293)*10000+C293+F293*100+D293*100000</f>
+        <f t="shared" si="7"/>
         <v>1021400115</v>
       </c>
       <c r="B293" s="2">
@@ -14827,7 +14845,7 @@
     </row>
     <row r="294" customHeight="1" spans="1:12">
       <c r="A294" s="3">
-        <f>(B294)*10000+C294+F294*100+D294*100000</f>
+        <f t="shared" si="7"/>
         <v>1021400116</v>
       </c>
       <c r="B294" s="2">
@@ -14856,7 +14874,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L268" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L294" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$268</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$294</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -762,14 +762,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -779,6 +778,7 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -13783,7 +13783,7 @@
     </row>
     <row r="255" customHeight="1" spans="1:12">
       <c r="A255" s="3">
-        <f t="shared" ref="A255:A290" si="7">(B255)*10000+C255+F255*100+D255*100000</f>
+        <f t="shared" ref="A255:A294" si="7">(B255)*10000+C255+F255*100+D255*100000</f>
         <v>1021300207</v>
       </c>
       <c r="B255" s="2">
@@ -14125,6 +14125,9 @@
       <c r="G267" s="11">
         <v>0</v>
       </c>
+      <c r="H267" s="11">
+        <v>30210002</v>
+      </c>
       <c r="I267" s="11">
         <v>0</v>
       </c>
@@ -14149,6 +14152,9 @@
       <c r="G268" s="11">
         <v>0</v>
       </c>
+      <c r="H268" s="11">
+        <v>30210001</v>
+      </c>
       <c r="I268" s="11">
         <v>0</v>
       </c>
@@ -14416,6 +14422,9 @@
       <c r="G278" s="11">
         <v>0</v>
       </c>
+      <c r="H278" s="11">
+        <v>30210002</v>
+      </c>
       <c r="I278" s="11">
         <v>0</v>
       </c>
@@ -14440,6 +14449,9 @@
       <c r="G279" s="11">
         <v>0</v>
       </c>
+      <c r="H279" s="11">
+        <v>30210001</v>
+      </c>
       <c r="I279" s="11">
         <v>0</v>
       </c>
@@ -14707,6 +14719,9 @@
       <c r="G289" s="11">
         <v>0</v>
       </c>
+      <c r="H289" s="11">
+        <v>30210002</v>
+      </c>
       <c r="I289" s="11">
         <v>0</v>
       </c>
@@ -14731,13 +14746,16 @@
       <c r="G290" s="11">
         <v>0</v>
       </c>
+      <c r="H290" s="11">
+        <v>30210001</v>
+      </c>
       <c r="I290" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="291" customHeight="1" spans="1:12">
       <c r="A291" s="3">
-        <f>(B291)*10000+C291+F291*100+D291*100000</f>
+        <f t="shared" si="7"/>
         <v>1021400113</v>
       </c>
       <c r="B291" s="2">
@@ -14767,7 +14785,7 @@
     </row>
     <row r="292" customHeight="1" spans="1:12">
       <c r="A292" s="3">
-        <f>(B292)*10000+C292+F292*100+D292*100000</f>
+        <f t="shared" si="7"/>
         <v>1021400114</v>
       </c>
       <c r="B292" s="2">
@@ -14797,7 +14815,7 @@
     </row>
     <row r="293" customHeight="1" spans="1:12">
       <c r="A293" s="3">
-        <f>(B293)*10000+C293+F293*100+D293*100000</f>
+        <f t="shared" si="7"/>
         <v>1021400115</v>
       </c>
       <c r="B293" s="2">
@@ -14827,7 +14845,7 @@
     </row>
     <row r="294" customHeight="1" spans="1:12">
       <c r="A294" s="3">
-        <f>(B294)*10000+C294+F294*100+D294*100000</f>
+        <f t="shared" si="7"/>
         <v>1021400116</v>
       </c>
       <c r="B294" s="2">
@@ -14856,7 +14874,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L268" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L294" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$294</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$296</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="71">
   <si>
     <t>id</t>
   </si>
@@ -519,6 +519,9 @@
   </si>
   <si>
     <t>13_1_3</t>
+  </si>
+  <si>
+    <t>+1免费符号</t>
   </si>
 </sst>
 </file>
@@ -762,11 +765,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -779,6 +777,11 @@
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1500,6 +1503,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="56">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5815,7 +5821,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L294"/>
+  <dimension ref="A1:L350"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="10"/>
@@ -11362,7 +11368,7 @@
         <v>0</v>
       </c>
       <c r="H169" s="19">
-        <v>30010001</v>
+        <v>30240001</v>
       </c>
       <c r="I169" s="2">
         <v>0</v>
@@ -11399,7 +11405,7 @@
         <v>0</v>
       </c>
       <c r="H170" s="19">
-        <v>30010002</v>
+        <v>30240002</v>
       </c>
       <c r="I170" s="2">
         <v>0</v>
@@ -11436,7 +11442,7 @@
         <v>0</v>
       </c>
       <c r="H171" s="19">
-        <v>30010003</v>
+        <v>30240003</v>
       </c>
       <c r="I171" s="2">
         <v>0</v>
@@ -11473,7 +11479,7 @@
         <v>0</v>
       </c>
       <c r="H172" s="19">
-        <v>30010004</v>
+        <v>30240004</v>
       </c>
       <c r="I172" s="2">
         <v>0</v>
@@ -11508,7 +11514,7 @@
         <v>0</v>
       </c>
       <c r="H173" s="25">
-        <v>30010005</v>
+        <v>30240005</v>
       </c>
       <c r="I173" s="2">
         <v>0</v>
@@ -11543,7 +11549,7 @@
         <v>0</v>
       </c>
       <c r="H174" s="29">
-        <v>30010006</v>
+        <v>30240006</v>
       </c>
       <c r="I174" s="2">
         <v>0</v>
@@ -11677,7 +11683,7 @@
         <v>0</v>
       </c>
       <c r="H178" s="37">
-        <v>30010007</v>
+        <v>30240007</v>
       </c>
       <c r="I178" s="2">
         <v>0</v>
@@ -12442,7 +12448,7 @@
     </row>
     <row r="210" customHeight="1" spans="1:10">
       <c r="A210" s="2">
-        <f t="shared" ref="A210:A254" si="6">(B210)*10000+C210+F210*100+D210*100000</f>
+        <f t="shared" ref="A210:A256" si="6">(B210)*10000+C210+F210*100+D210*100000</f>
         <v>1022100302</v>
       </c>
       <c r="B210" s="2">
@@ -13781,70 +13787,78 @@
         <v>68</v>
       </c>
     </row>
-    <row r="255" customHeight="1" spans="1:12">
+    <row r="255" customFormat="1" customHeight="1" spans="1:12">
       <c r="A255" s="3">
-        <f t="shared" ref="A255:A294" si="7">(B255)*10000+C255+F255*100+D255*100000</f>
-        <v>1021300207</v>
+        <f t="shared" si="6"/>
+        <v>1022400119</v>
       </c>
       <c r="B255" s="2">
-        <v>102100</v>
+        <v>102200</v>
       </c>
       <c r="C255" s="2">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D255" s="2">
-        <v>3</v>
-      </c>
-      <c r="E255" s="2" t="s">
-        <v>22</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E255" s="2"/>
       <c r="F255" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G255" s="11">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H255" s="11">
+        <v>30220001</v>
       </c>
       <c r="I255" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="256" customHeight="1" spans="1:12">
+      <c r="J255" s="12"/>
+      <c r="K255" s="2"/>
+      <c r="L255" s="13"/>
+    </row>
+    <row r="256" customFormat="1" customHeight="1" spans="1:12">
       <c r="A256" s="3">
-        <f t="shared" si="7"/>
-        <v>1021300208</v>
+        <f t="shared" si="6"/>
+        <v>1022400120</v>
       </c>
       <c r="B256" s="2">
-        <v>102100</v>
+        <v>102200</v>
       </c>
       <c r="C256" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D256" s="2">
-        <v>3</v>
-      </c>
-      <c r="E256" s="2" t="s">
-        <v>22</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E256" s="2"/>
       <c r="F256" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G256" s="11">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H256" s="11">
+        <v>30220002</v>
       </c>
       <c r="I256" s="11">
         <v>0</v>
       </c>
+      <c r="J256" s="12"/>
+      <c r="K256" s="2"/>
+      <c r="L256" s="13"/>
     </row>
     <row r="257" customHeight="1" spans="1:9">
       <c r="A257" s="3">
-        <f t="shared" si="7"/>
-        <v>1021300209</v>
+        <f t="shared" ref="A257:A296" si="7">(B257)*10000+C257+F257*100+D257*100000</f>
+        <v>1021300207</v>
       </c>
       <c r="B257" s="2">
         <v>102100</v>
       </c>
       <c r="C257" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D257" s="2">
         <v>3</v>
@@ -13856,7 +13870,7 @@
         <v>2</v>
       </c>
       <c r="G257" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I257" s="11">
         <v>0</v>
@@ -13865,13 +13879,13 @@
     <row r="258" customHeight="1" spans="1:9">
       <c r="A258" s="3">
         <f t="shared" si="7"/>
-        <v>1021300301</v>
+        <v>1021300208</v>
       </c>
       <c r="B258" s="2">
         <v>102100</v>
       </c>
       <c r="C258" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D258" s="2">
         <v>3</v>
@@ -13880,10 +13894,10 @@
         <v>22</v>
       </c>
       <c r="F258" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G258" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I258" s="11">
         <v>0</v>
@@ -13892,13 +13906,13 @@
     <row r="259" customHeight="1" spans="1:9">
       <c r="A259" s="3">
         <f t="shared" si="7"/>
-        <v>1021300302</v>
+        <v>1021300209</v>
       </c>
       <c r="B259" s="2">
         <v>102100</v>
       </c>
       <c r="C259" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D259" s="2">
         <v>3</v>
@@ -13907,7 +13921,7 @@
         <v>22</v>
       </c>
       <c r="F259" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G259" s="11">
         <v>2</v>
@@ -13919,13 +13933,13 @@
     <row r="260" customHeight="1" spans="1:9">
       <c r="A260" s="3">
         <f t="shared" si="7"/>
-        <v>1021300303</v>
+        <v>1021300301</v>
       </c>
       <c r="B260" s="2">
         <v>102100</v>
       </c>
       <c r="C260" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D260" s="2">
         <v>3</v>
@@ -13946,13 +13960,13 @@
     <row r="261" customHeight="1" spans="1:9">
       <c r="A261" s="3">
         <f t="shared" si="7"/>
-        <v>1021300304</v>
+        <v>1021300302</v>
       </c>
       <c r="B261" s="2">
         <v>102100</v>
       </c>
       <c r="C261" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D261" s="2">
         <v>3</v>
@@ -13973,13 +13987,13 @@
     <row r="262" customHeight="1" spans="1:9">
       <c r="A262" s="3">
         <f t="shared" si="7"/>
-        <v>1021300305</v>
+        <v>1021300303</v>
       </c>
       <c r="B262" s="2">
         <v>102100</v>
       </c>
       <c r="C262" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D262" s="2">
         <v>3</v>
@@ -13991,7 +14005,7 @@
         <v>3</v>
       </c>
       <c r="G262" s="11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I262" s="11">
         <v>0</v>
@@ -14000,13 +14014,13 @@
     <row r="263" customHeight="1" spans="1:9">
       <c r="A263" s="3">
         <f t="shared" si="7"/>
-        <v>1021300306</v>
+        <v>1021300304</v>
       </c>
       <c r="B263" s="2">
         <v>102100</v>
       </c>
       <c r="C263" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D263" s="2">
         <v>3</v>
@@ -14018,7 +14032,7 @@
         <v>3</v>
       </c>
       <c r="G263" s="11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I263" s="11">
         <v>0</v>
@@ -14027,13 +14041,13 @@
     <row r="264" customHeight="1" spans="1:9">
       <c r="A264" s="3">
         <f t="shared" si="7"/>
-        <v>1021300307</v>
+        <v>1021300305</v>
       </c>
       <c r="B264" s="2">
         <v>102100</v>
       </c>
       <c r="C264" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D264" s="2">
         <v>3</v>
@@ -14045,7 +14059,7 @@
         <v>3</v>
       </c>
       <c r="G264" s="11">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I264" s="11">
         <v>0</v>
@@ -14054,13 +14068,13 @@
     <row r="265" customHeight="1" spans="1:9">
       <c r="A265" s="3">
         <f t="shared" si="7"/>
-        <v>1021300308</v>
+        <v>1021300306</v>
       </c>
       <c r="B265" s="2">
         <v>102100</v>
       </c>
       <c r="C265" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D265" s="2">
         <v>3</v>
@@ -14072,7 +14086,7 @@
         <v>3</v>
       </c>
       <c r="G265" s="11">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I265" s="11">
         <v>0</v>
@@ -14081,13 +14095,13 @@
     <row r="266" customHeight="1" spans="1:9">
       <c r="A266" s="3">
         <f t="shared" si="7"/>
-        <v>1021300309</v>
+        <v>1021300307</v>
       </c>
       <c r="B266" s="2">
         <v>102100</v>
       </c>
       <c r="C266" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D266" s="2">
         <v>3</v>
@@ -14108,25 +14122,25 @@
     <row r="267" customHeight="1" spans="1:9">
       <c r="A267" s="3">
         <f t="shared" si="7"/>
-        <v>1021400310</v>
+        <v>1021300308</v>
       </c>
       <c r="B267" s="2">
         <v>102100</v>
       </c>
       <c r="C267" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D267" s="2">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="E267" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="F267" s="2">
         <v>3</v>
       </c>
       <c r="G267" s="11">
-        <v>0</v>
-      </c>
-      <c r="H267" s="11">
-        <v>30210002</v>
+        <v>8</v>
       </c>
       <c r="I267" s="11">
         <v>0</v>
@@ -14135,25 +14149,25 @@
     <row r="268" customHeight="1" spans="1:9">
       <c r="A268" s="3">
         <f t="shared" si="7"/>
-        <v>1021400312</v>
+        <v>1021300309</v>
       </c>
       <c r="B268" s="2">
         <v>102100</v>
       </c>
       <c r="C268" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D268" s="2">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="E268" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="F268" s="2">
         <v>3</v>
       </c>
       <c r="G268" s="11">
-        <v>0</v>
-      </c>
-      <c r="H268" s="11">
-        <v>30210001</v>
+        <v>8</v>
       </c>
       <c r="I268" s="11">
         <v>0</v>
@@ -14162,25 +14176,25 @@
     <row r="269" customHeight="1" spans="1:9">
       <c r="A269" s="3">
         <f t="shared" si="7"/>
-        <v>1021300401</v>
+        <v>1021400310</v>
       </c>
       <c r="B269" s="2">
         <v>102100</v>
       </c>
       <c r="C269" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D269" s="2">
-        <v>3</v>
-      </c>
-      <c r="E269" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F269" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G269" s="11">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="H269" s="11">
+        <v>30210002</v>
       </c>
       <c r="I269" s="11">
         <v>0</v>
@@ -14189,25 +14203,25 @@
     <row r="270" customHeight="1" spans="1:9">
       <c r="A270" s="3">
         <f t="shared" si="7"/>
-        <v>1021300402</v>
+        <v>1021400312</v>
       </c>
       <c r="B270" s="2">
         <v>102100</v>
       </c>
       <c r="C270" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D270" s="2">
-        <v>3</v>
-      </c>
-      <c r="E270" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F270" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G270" s="11">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="H270" s="11">
+        <v>30210001</v>
       </c>
       <c r="I270" s="11">
         <v>0</v>
@@ -14216,13 +14230,13 @@
     <row r="271" customHeight="1" spans="1:9">
       <c r="A271" s="3">
         <f t="shared" si="7"/>
-        <v>1021300403</v>
+        <v>1021300401</v>
       </c>
       <c r="B271" s="2">
         <v>102100</v>
       </c>
       <c r="C271" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D271" s="2">
         <v>3</v>
@@ -14234,7 +14248,7 @@
         <v>4</v>
       </c>
       <c r="G271" s="11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I271" s="11">
         <v>0</v>
@@ -14243,13 +14257,13 @@
     <row r="272" customHeight="1" spans="1:9">
       <c r="A272" s="3">
         <f t="shared" si="7"/>
-        <v>1021300404</v>
+        <v>1021300402</v>
       </c>
       <c r="B272" s="2">
         <v>102100</v>
       </c>
       <c r="C272" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D272" s="2">
         <v>3</v>
@@ -14261,7 +14275,7 @@
         <v>4</v>
       </c>
       <c r="G272" s="11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I272" s="11">
         <v>0</v>
@@ -14270,13 +14284,13 @@
     <row r="273" customHeight="1" spans="1:9">
       <c r="A273" s="3">
         <f t="shared" si="7"/>
-        <v>1021300405</v>
+        <v>1021300403</v>
       </c>
       <c r="B273" s="2">
         <v>102100</v>
       </c>
       <c r="C273" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D273" s="2">
         <v>3</v>
@@ -14288,7 +14302,7 @@
         <v>4</v>
       </c>
       <c r="G273" s="11">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I273" s="11">
         <v>0</v>
@@ -14297,13 +14311,13 @@
     <row r="274" customHeight="1" spans="1:9">
       <c r="A274" s="3">
         <f t="shared" si="7"/>
-        <v>1021300406</v>
+        <v>1021300404</v>
       </c>
       <c r="B274" s="2">
         <v>102100</v>
       </c>
       <c r="C274" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D274" s="2">
         <v>3</v>
@@ -14315,7 +14329,7 @@
         <v>4</v>
       </c>
       <c r="G274" s="11">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I274" s="11">
         <v>0</v>
@@ -14324,13 +14338,13 @@
     <row r="275" customHeight="1" spans="1:9">
       <c r="A275" s="3">
         <f t="shared" si="7"/>
-        <v>1021300407</v>
+        <v>1021300405</v>
       </c>
       <c r="B275" s="2">
         <v>102100</v>
       </c>
       <c r="C275" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D275" s="2">
         <v>3</v>
@@ -14342,7 +14356,7 @@
         <v>4</v>
       </c>
       <c r="G275" s="11">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="I275" s="11">
         <v>0</v>
@@ -14351,13 +14365,13 @@
     <row r="276" customHeight="1" spans="1:9">
       <c r="A276" s="3">
         <f t="shared" si="7"/>
-        <v>1021300408</v>
+        <v>1021300406</v>
       </c>
       <c r="B276" s="2">
         <v>102100</v>
       </c>
       <c r="C276" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D276" s="2">
         <v>3</v>
@@ -14369,7 +14383,7 @@
         <v>4</v>
       </c>
       <c r="G276" s="11">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="I276" s="11">
         <v>0</v>
@@ -14378,13 +14392,13 @@
     <row r="277" customHeight="1" spans="1:9">
       <c r="A277" s="3">
         <f t="shared" si="7"/>
-        <v>1021300409</v>
+        <v>1021300407</v>
       </c>
       <c r="B277" s="2">
         <v>102100</v>
       </c>
       <c r="C277" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D277" s="2">
         <v>3</v>
@@ -14396,7 +14410,7 @@
         <v>4</v>
       </c>
       <c r="G277" s="11">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I277" s="11">
         <v>0</v>
@@ -14405,25 +14419,25 @@
     <row r="278" customHeight="1" spans="1:9">
       <c r="A278" s="3">
         <f t="shared" si="7"/>
-        <v>1021400410</v>
+        <v>1021300408</v>
       </c>
       <c r="B278" s="2">
         <v>102100</v>
       </c>
       <c r="C278" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D278" s="2">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="E278" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="F278" s="2">
         <v>4</v>
       </c>
       <c r="G278" s="11">
-        <v>0</v>
-      </c>
-      <c r="H278" s="11">
-        <v>30210002</v>
+        <v>40</v>
       </c>
       <c r="I278" s="11">
         <v>0</v>
@@ -14432,25 +14446,25 @@
     <row r="279" customHeight="1" spans="1:9">
       <c r="A279" s="3">
         <f t="shared" si="7"/>
-        <v>1021400412</v>
+        <v>1021300409</v>
       </c>
       <c r="B279" s="2">
         <v>102100</v>
       </c>
       <c r="C279" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D279" s="2">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="E279" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="F279" s="2">
         <v>4</v>
       </c>
       <c r="G279" s="11">
-        <v>0</v>
-      </c>
-      <c r="H279" s="11">
-        <v>30210001</v>
+        <v>100</v>
       </c>
       <c r="I279" s="11">
         <v>0</v>
@@ -14459,25 +14473,25 @@
     <row r="280" customHeight="1" spans="1:9">
       <c r="A280" s="3">
         <f t="shared" si="7"/>
-        <v>1021300501</v>
+        <v>1021400410</v>
       </c>
       <c r="B280" s="2">
         <v>102100</v>
       </c>
       <c r="C280" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D280" s="2">
-        <v>3</v>
-      </c>
-      <c r="E280" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F280" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G280" s="11">
-        <v>40</v>
+        <v>0</v>
+      </c>
+      <c r="H280" s="11">
+        <v>30210002</v>
       </c>
       <c r="I280" s="11">
         <v>0</v>
@@ -14486,25 +14500,25 @@
     <row r="281" customHeight="1" spans="1:9">
       <c r="A281" s="3">
         <f t="shared" si="7"/>
-        <v>1021300502</v>
+        <v>1021400412</v>
       </c>
       <c r="B281" s="2">
         <v>102100</v>
       </c>
       <c r="C281" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D281" s="2">
-        <v>3</v>
-      </c>
-      <c r="E281" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F281" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G281" s="11">
-        <v>40</v>
+        <v>0</v>
+      </c>
+      <c r="H281" s="11">
+        <v>30210001</v>
       </c>
       <c r="I281" s="11">
         <v>0</v>
@@ -14513,13 +14527,13 @@
     <row r="282" customHeight="1" spans="1:9">
       <c r="A282" s="3">
         <f t="shared" si="7"/>
-        <v>1021300503</v>
+        <v>1021300501</v>
       </c>
       <c r="B282" s="2">
         <v>102100</v>
       </c>
       <c r="C282" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D282" s="2">
         <v>3</v>
@@ -14531,7 +14545,7 @@
         <v>5</v>
       </c>
       <c r="G282" s="11">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I282" s="11">
         <v>0</v>
@@ -14540,13 +14554,13 @@
     <row r="283" customHeight="1" spans="1:9">
       <c r="A283" s="3">
         <f t="shared" si="7"/>
-        <v>1021300504</v>
+        <v>1021300502</v>
       </c>
       <c r="B283" s="2">
         <v>102100</v>
       </c>
       <c r="C283" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D283" s="2">
         <v>3</v>
@@ -14558,7 +14572,7 @@
         <v>5</v>
       </c>
       <c r="G283" s="11">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I283" s="11">
         <v>0</v>
@@ -14567,13 +14581,13 @@
     <row r="284" customHeight="1" spans="1:9">
       <c r="A284" s="3">
         <f t="shared" si="7"/>
-        <v>1021300505</v>
+        <v>1021300503</v>
       </c>
       <c r="B284" s="2">
         <v>102100</v>
       </c>
       <c r="C284" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D284" s="2">
         <v>3</v>
@@ -14585,7 +14599,7 @@
         <v>5</v>
       </c>
       <c r="G284" s="11">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="I284" s="11">
         <v>0</v>
@@ -14594,13 +14608,13 @@
     <row r="285" customHeight="1" spans="1:9">
       <c r="A285" s="3">
         <f t="shared" si="7"/>
-        <v>1021300506</v>
+        <v>1021300504</v>
       </c>
       <c r="B285" s="2">
         <v>102100</v>
       </c>
       <c r="C285" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D285" s="2">
         <v>3</v>
@@ -14612,7 +14626,7 @@
         <v>5</v>
       </c>
       <c r="G285" s="11">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="I285" s="11">
         <v>0</v>
@@ -14621,13 +14635,13 @@
     <row r="286" customHeight="1" spans="1:9">
       <c r="A286" s="3">
         <f t="shared" si="7"/>
-        <v>1021300507</v>
+        <v>1021300505</v>
       </c>
       <c r="B286" s="2">
         <v>102100</v>
       </c>
       <c r="C286" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D286" s="2">
         <v>3</v>
@@ -14639,7 +14653,7 @@
         <v>5</v>
       </c>
       <c r="G286" s="11">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="I286" s="11">
         <v>0</v>
@@ -14648,13 +14662,13 @@
     <row r="287" customHeight="1" spans="1:9">
       <c r="A287" s="3">
         <f t="shared" si="7"/>
-        <v>1021300508</v>
+        <v>1021300506</v>
       </c>
       <c r="B287" s="2">
         <v>102100</v>
       </c>
       <c r="C287" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D287" s="2">
         <v>3</v>
@@ -14666,7 +14680,7 @@
         <v>5</v>
       </c>
       <c r="G287" s="11">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="I287" s="11">
         <v>0</v>
@@ -14675,13 +14689,13 @@
     <row r="288" customHeight="1" spans="1:9">
       <c r="A288" s="3">
         <f t="shared" si="7"/>
-        <v>1021300509</v>
+        <v>1021300507</v>
       </c>
       <c r="B288" s="2">
         <v>102100</v>
       </c>
       <c r="C288" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D288" s="2">
         <v>3</v>
@@ -14693,7 +14707,7 @@
         <v>5</v>
       </c>
       <c r="G288" s="11">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="I288" s="11">
         <v>0</v>
@@ -14702,25 +14716,25 @@
     <row r="289" customHeight="1" spans="1:12">
       <c r="A289" s="3">
         <f t="shared" si="7"/>
-        <v>1021400510</v>
+        <v>1021300508</v>
       </c>
       <c r="B289" s="2">
         <v>102100</v>
       </c>
       <c r="C289" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D289" s="2">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="F289" s="2">
         <v>5</v>
       </c>
       <c r="G289" s="11">
-        <v>0</v>
-      </c>
-      <c r="H289" s="11">
-        <v>30210002</v>
+        <v>400</v>
       </c>
       <c r="I289" s="11">
         <v>0</v>
@@ -14729,25 +14743,25 @@
     <row r="290" customHeight="1" spans="1:12">
       <c r="A290" s="3">
         <f t="shared" si="7"/>
-        <v>1021400512</v>
+        <v>1021300509</v>
       </c>
       <c r="B290" s="2">
         <v>102100</v>
       </c>
       <c r="C290" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D290" s="2">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="F290" s="2">
         <v>5</v>
       </c>
       <c r="G290" s="11">
-        <v>0</v>
-      </c>
-      <c r="H290" s="11">
-        <v>30210001</v>
+        <v>1000</v>
       </c>
       <c r="I290" s="11">
         <v>0</v>
@@ -14756,73 +14770,67 @@
     <row r="291" customHeight="1" spans="1:12">
       <c r="A291" s="3">
         <f t="shared" si="7"/>
-        <v>1021400113</v>
+        <v>1021400510</v>
       </c>
       <c r="B291" s="2">
         <v>102100</v>
       </c>
       <c r="C291" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D291" s="2">
         <v>4</v>
       </c>
       <c r="F291" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G291" s="11">
         <v>0</v>
       </c>
+      <c r="H291" s="11">
+        <v>30210002</v>
+      </c>
       <c r="I291" s="11">
         <v>0</v>
-      </c>
-      <c r="K291" s="2">
-        <v>102100101</v>
-      </c>
-      <c r="L291" s="13" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="292" customHeight="1" spans="1:12">
       <c r="A292" s="3">
         <f t="shared" si="7"/>
-        <v>1021400114</v>
+        <v>1021400512</v>
       </c>
       <c r="B292" s="2">
         <v>102100</v>
       </c>
       <c r="C292" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D292" s="2">
         <v>4</v>
       </c>
       <c r="F292" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G292" s="11">
         <v>0</v>
       </c>
+      <c r="H292" s="11">
+        <v>30210001</v>
+      </c>
       <c r="I292" s="11">
         <v>0</v>
-      </c>
-      <c r="K292" s="3">
-        <v>102100102</v>
-      </c>
-      <c r="L292" s="13" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="293" customHeight="1" spans="1:12">
       <c r="A293" s="3">
         <f t="shared" si="7"/>
-        <v>1021400115</v>
+        <v>1021400113</v>
       </c>
       <c r="B293" s="2">
         <v>102100</v>
       </c>
       <c r="C293" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D293" s="2">
         <v>4</v>
@@ -14836,657 +14844,2050 @@
       <c r="I293" s="11">
         <v>0</v>
       </c>
-      <c r="K293" s="3">
-        <v>102100103</v>
+      <c r="K293" s="2">
+        <v>102100101</v>
       </c>
       <c r="L293" s="13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="294" customHeight="1" spans="1:12">
       <c r="A294" s="3">
         <f t="shared" si="7"/>
-        <v>1021400116</v>
+        <v>1021400114</v>
       </c>
       <c r="B294" s="2">
         <v>102100</v>
       </c>
       <c r="C294" s="2">
+        <v>14</v>
+      </c>
+      <c r="D294" s="2">
+        <v>4</v>
+      </c>
+      <c r="F294" s="2">
+        <v>1</v>
+      </c>
+      <c r="G294" s="11">
+        <v>0</v>
+      </c>
+      <c r="I294" s="11">
+        <v>0</v>
+      </c>
+      <c r="K294" s="3">
+        <v>102100102</v>
+      </c>
+      <c r="L294" s="13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="295" customHeight="1" spans="1:12">
+      <c r="A295" s="3">
+        <f t="shared" si="7"/>
+        <v>1021400115</v>
+      </c>
+      <c r="B295" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C295" s="2">
+        <v>15</v>
+      </c>
+      <c r="D295" s="2">
+        <v>4</v>
+      </c>
+      <c r="F295" s="2">
+        <v>1</v>
+      </c>
+      <c r="G295" s="11">
+        <v>0</v>
+      </c>
+      <c r="I295" s="11">
+        <v>0</v>
+      </c>
+      <c r="K295" s="3">
+        <v>102100103</v>
+      </c>
+      <c r="L295" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="296" customHeight="1" spans="1:12">
+      <c r="A296" s="3">
+        <f t="shared" si="7"/>
+        <v>1021400116</v>
+      </c>
+      <c r="B296" s="2">
+        <v>102100</v>
+      </c>
+      <c r="C296" s="2">
         <v>16</v>
       </c>
-      <c r="D294" s="2">
-        <v>4</v>
-      </c>
-      <c r="F294" s="2">
-        <v>1</v>
-      </c>
-      <c r="G294" s="11">
-        <v>0</v>
-      </c>
-      <c r="I294" s="11">
-        <v>0</v>
-      </c>
-      <c r="K294" s="3">
+      <c r="D296" s="2">
+        <v>4</v>
+      </c>
+      <c r="F296" s="2">
+        <v>1</v>
+      </c>
+      <c r="G296" s="11">
+        <v>0</v>
+      </c>
+      <c r="I296" s="11">
+        <v>0</v>
+      </c>
+      <c r="K296" s="3">
         <v>102100104</v>
       </c>
-      <c r="L294" s="13" t="s">
+      <c r="L296" s="13" t="s">
         <v>68</v>
       </c>
     </row>
+    <row r="297" customHeight="1" spans="1:12">
+      <c r="A297" s="3">
+        <f>(B297)*10000+C297+F297*100+D297*100000</f>
+        <v>1018300210</v>
+      </c>
+      <c r="B297" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C297" s="2">
+        <v>10</v>
+      </c>
+      <c r="D297" s="2">
+        <v>3</v>
+      </c>
+      <c r="F297" s="2">
+        <v>2</v>
+      </c>
+      <c r="G297" s="11">
+        <v>10</v>
+      </c>
+      <c r="I297" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" customHeight="1" spans="1:12">
+      <c r="A298" s="3">
+        <f t="shared" ref="A298:A307" si="8">(B298)*10000+C298+F298*100+D298*100000</f>
+        <v>1018300301</v>
+      </c>
+      <c r="B298" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C298" s="2">
+        <v>1</v>
+      </c>
+      <c r="D298" s="2">
+        <v>3</v>
+      </c>
+      <c r="F298" s="2">
+        <v>3</v>
+      </c>
+      <c r="G298" s="11">
+        <v>2</v>
+      </c>
+      <c r="I298" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" customHeight="1" spans="1:12">
+      <c r="A299" s="3">
+        <f t="shared" si="8"/>
+        <v>1018300302</v>
+      </c>
+      <c r="B299" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C299" s="2">
+        <v>2</v>
+      </c>
+      <c r="D299" s="2">
+        <v>3</v>
+      </c>
+      <c r="F299" s="2">
+        <v>3</v>
+      </c>
+      <c r="G299" s="11">
+        <v>2</v>
+      </c>
+      <c r="I299" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" customHeight="1" spans="1:12">
+      <c r="A300" s="3">
+        <f t="shared" si="8"/>
+        <v>1018300303</v>
+      </c>
+      <c r="B300" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C300" s="2">
+        <v>3</v>
+      </c>
+      <c r="D300" s="2">
+        <v>3</v>
+      </c>
+      <c r="F300" s="2">
+        <v>3</v>
+      </c>
+      <c r="G300" s="11">
+        <v>2</v>
+      </c>
+      <c r="I300" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" customHeight="1" spans="1:12">
+      <c r="A301" s="3">
+        <f t="shared" si="8"/>
+        <v>1018300304</v>
+      </c>
+      <c r="B301" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C301" s="2">
+        <v>4</v>
+      </c>
+      <c r="D301" s="2">
+        <v>3</v>
+      </c>
+      <c r="F301" s="2">
+        <v>3</v>
+      </c>
+      <c r="G301" s="11">
+        <v>2</v>
+      </c>
+      <c r="I301" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" customHeight="1" spans="1:12">
+      <c r="A302" s="3">
+        <f t="shared" si="8"/>
+        <v>1018300305</v>
+      </c>
+      <c r="B302" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C302" s="2">
+        <v>5</v>
+      </c>
+      <c r="D302" s="2">
+        <v>3</v>
+      </c>
+      <c r="F302" s="2">
+        <v>3</v>
+      </c>
+      <c r="G302" s="11">
+        <v>2</v>
+      </c>
+      <c r="I302" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" customHeight="1" spans="1:12">
+      <c r="A303" s="3">
+        <f t="shared" si="8"/>
+        <v>1018300306</v>
+      </c>
+      <c r="B303" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C303" s="2">
+        <v>6</v>
+      </c>
+      <c r="D303" s="2">
+        <v>3</v>
+      </c>
+      <c r="F303" s="2">
+        <v>3</v>
+      </c>
+      <c r="G303" s="11">
+        <v>3</v>
+      </c>
+      <c r="I303" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" customHeight="1" spans="1:12">
+      <c r="A304" s="3">
+        <f t="shared" si="8"/>
+        <v>1018300307</v>
+      </c>
+      <c r="B304" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C304" s="2">
+        <v>7</v>
+      </c>
+      <c r="D304" s="2">
+        <v>3</v>
+      </c>
+      <c r="F304" s="2">
+        <v>3</v>
+      </c>
+      <c r="G304" s="11">
+        <v>4</v>
+      </c>
+      <c r="I304" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" customHeight="1" spans="1:9">
+      <c r="A305" s="3">
+        <f t="shared" si="8"/>
+        <v>1018300308</v>
+      </c>
+      <c r="B305" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C305" s="2">
+        <v>8</v>
+      </c>
+      <c r="D305" s="2">
+        <v>3</v>
+      </c>
+      <c r="F305" s="2">
+        <v>3</v>
+      </c>
+      <c r="G305" s="11">
+        <v>4</v>
+      </c>
+      <c r="I305" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" customHeight="1" spans="1:9">
+      <c r="A306" s="3">
+        <f t="shared" si="8"/>
+        <v>1018300309</v>
+      </c>
+      <c r="B306" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C306" s="2">
+        <v>9</v>
+      </c>
+      <c r="D306" s="2">
+        <v>3</v>
+      </c>
+      <c r="F306" s="2">
+        <v>3</v>
+      </c>
+      <c r="G306" s="11">
+        <v>6</v>
+      </c>
+      <c r="I306" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" customHeight="1" spans="1:9">
+      <c r="A307" s="3">
+        <f t="shared" si="8"/>
+        <v>1018300310</v>
+      </c>
+      <c r="B307" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C307" s="2">
+        <v>10</v>
+      </c>
+      <c r="D307" s="2">
+        <v>3</v>
+      </c>
+      <c r="F307" s="2">
+        <v>3</v>
+      </c>
+      <c r="G307" s="11">
+        <v>25</v>
+      </c>
+      <c r="I307" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" customHeight="1" spans="1:9">
+      <c r="A308" s="3">
+        <f t="shared" ref="A308:A317" si="9">(B308)*10000+C308+F308*100+D308*100000</f>
+        <v>1018400311</v>
+      </c>
+      <c r="B308" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C308" s="2">
+        <v>11</v>
+      </c>
+      <c r="D308" s="2">
+        <v>4</v>
+      </c>
+      <c r="F308" s="2">
+        <v>3</v>
+      </c>
+      <c r="G308" s="11">
+        <v>0</v>
+      </c>
+      <c r="I308" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" customHeight="1" spans="1:9">
+      <c r="A309" s="3">
+        <f t="shared" si="9"/>
+        <v>1018400312</v>
+      </c>
+      <c r="B309" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C309" s="2">
+        <v>12</v>
+      </c>
+      <c r="D309" s="2">
+        <v>4</v>
+      </c>
+      <c r="F309" s="2">
+        <v>3</v>
+      </c>
+      <c r="G309" s="11">
+        <v>100</v>
+      </c>
+      <c r="I309" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" customHeight="1" spans="1:9">
+      <c r="A310" s="3">
+        <f t="shared" si="9"/>
+        <v>1018300401</v>
+      </c>
+      <c r="B310" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C310" s="2">
+        <v>1</v>
+      </c>
+      <c r="D310" s="2">
+        <v>3</v>
+      </c>
+      <c r="F310" s="2">
+        <v>4</v>
+      </c>
+      <c r="G310" s="11">
+        <v>4</v>
+      </c>
+      <c r="I310" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" customHeight="1" spans="1:9">
+      <c r="A311" s="3">
+        <f t="shared" si="9"/>
+        <v>1018300402</v>
+      </c>
+      <c r="B311" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C311" s="2">
+        <v>2</v>
+      </c>
+      <c r="D311" s="2">
+        <v>3</v>
+      </c>
+      <c r="F311" s="2">
+        <v>4</v>
+      </c>
+      <c r="G311" s="11">
+        <v>4</v>
+      </c>
+      <c r="I311" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" customHeight="1" spans="1:9">
+      <c r="A312" s="3">
+        <f t="shared" si="9"/>
+        <v>1018300403</v>
+      </c>
+      <c r="B312" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C312" s="2">
+        <v>3</v>
+      </c>
+      <c r="D312" s="2">
+        <v>3</v>
+      </c>
+      <c r="F312" s="2">
+        <v>4</v>
+      </c>
+      <c r="G312" s="11">
+        <v>5</v>
+      </c>
+      <c r="I312" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" customHeight="1" spans="1:9">
+      <c r="A313" s="3">
+        <f t="shared" si="9"/>
+        <v>1018300404</v>
+      </c>
+      <c r="B313" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C313" s="2">
+        <v>4</v>
+      </c>
+      <c r="D313" s="2">
+        <v>3</v>
+      </c>
+      <c r="F313" s="2">
+        <v>4</v>
+      </c>
+      <c r="G313" s="11">
+        <v>5</v>
+      </c>
+      <c r="I313" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" customHeight="1" spans="1:9">
+      <c r="A314" s="3">
+        <f t="shared" si="9"/>
+        <v>1018300405</v>
+      </c>
+      <c r="B314" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C314" s="2">
+        <v>5</v>
+      </c>
+      <c r="D314" s="2">
+        <v>3</v>
+      </c>
+      <c r="F314" s="2">
+        <v>4</v>
+      </c>
+      <c r="G314" s="11">
+        <v>6</v>
+      </c>
+      <c r="I314" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" customHeight="1" spans="1:9">
+      <c r="A315" s="3">
+        <f t="shared" si="9"/>
+        <v>1018300406</v>
+      </c>
+      <c r="B315" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C315" s="2">
+        <v>6</v>
+      </c>
+      <c r="D315" s="2">
+        <v>3</v>
+      </c>
+      <c r="F315" s="2">
+        <v>4</v>
+      </c>
+      <c r="G315" s="11">
+        <v>8</v>
+      </c>
+      <c r="I315" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" customHeight="1" spans="1:9">
+      <c r="A316" s="3">
+        <f t="shared" si="9"/>
+        <v>1018300407</v>
+      </c>
+      <c r="B316" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C316" s="2">
+        <v>7</v>
+      </c>
+      <c r="D316" s="2">
+        <v>3</v>
+      </c>
+      <c r="F316" s="2">
+        <v>4</v>
+      </c>
+      <c r="G316" s="11">
+        <v>10</v>
+      </c>
+      <c r="I316" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" customHeight="1" spans="1:9">
+      <c r="A317" s="3">
+        <f t="shared" si="9"/>
+        <v>1018300408</v>
+      </c>
+      <c r="B317" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C317" s="2">
+        <v>8</v>
+      </c>
+      <c r="D317" s="2">
+        <v>3</v>
+      </c>
+      <c r="F317" s="2">
+        <v>4</v>
+      </c>
+      <c r="G317" s="11">
+        <v>12</v>
+      </c>
+      <c r="I317" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" customHeight="1" spans="1:9">
+      <c r="A318" s="3">
+        <f>(B318)*10000+C318+F318*100+D318*100000</f>
+        <v>1018300409</v>
+      </c>
+      <c r="B318" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C318" s="2">
+        <v>9</v>
+      </c>
+      <c r="D318" s="2">
+        <v>3</v>
+      </c>
+      <c r="F318" s="2">
+        <v>4</v>
+      </c>
+      <c r="G318" s="11">
+        <v>15</v>
+      </c>
+      <c r="I318" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" customHeight="1" spans="1:9">
+      <c r="A319" s="3">
+        <f>(B319)*10000+C319+F319*100+D319*100000</f>
+        <v>1018300410</v>
+      </c>
+      <c r="B319" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C319" s="2">
+        <v>10</v>
+      </c>
+      <c r="D319" s="2">
+        <v>3</v>
+      </c>
+      <c r="F319" s="2">
+        <v>4</v>
+      </c>
+      <c r="G319" s="11">
+        <v>75</v>
+      </c>
+      <c r="I319" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" customHeight="1" spans="1:9">
+      <c r="A320" s="3">
+        <f>(B320)*10000+C320+F320*100+D320*100000</f>
+        <v>1018400411</v>
+      </c>
+      <c r="B320" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C320" s="2">
+        <v>11</v>
+      </c>
+      <c r="D320" s="2">
+        <v>4</v>
+      </c>
+      <c r="F320" s="2">
+        <v>4</v>
+      </c>
+      <c r="G320" s="11">
+        <v>0</v>
+      </c>
+      <c r="I320" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" customHeight="1" spans="1:9">
+      <c r="A321" s="3">
+        <f>(B321)*10000+C321+F321*100+D321*100000</f>
+        <v>1018400412</v>
+      </c>
+      <c r="B321" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C321" s="2">
+        <v>12</v>
+      </c>
+      <c r="D321" s="2">
+        <v>4</v>
+      </c>
+      <c r="F321" s="2">
+        <v>4</v>
+      </c>
+      <c r="G321" s="11">
+        <v>400</v>
+      </c>
+      <c r="I321" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" customHeight="1" spans="1:9">
+      <c r="A322" s="3">
+        <f t="shared" ref="A322:A333" si="10">(B322)*10000+C322+F322*100+D322*100000</f>
+        <v>1018300501</v>
+      </c>
+      <c r="B322" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C322" s="2">
+        <v>1</v>
+      </c>
+      <c r="D322" s="2">
+        <v>3</v>
+      </c>
+      <c r="F322" s="2">
+        <v>5</v>
+      </c>
+      <c r="G322" s="11">
+        <v>8</v>
+      </c>
+      <c r="I322" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" customHeight="1" spans="1:9">
+      <c r="A323" s="3">
+        <f t="shared" si="10"/>
+        <v>1018300502</v>
+      </c>
+      <c r="B323" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C323" s="2">
+        <v>2</v>
+      </c>
+      <c r="D323" s="2">
+        <v>3</v>
+      </c>
+      <c r="F323" s="2">
+        <v>5</v>
+      </c>
+      <c r="G323" s="11">
+        <v>8</v>
+      </c>
+      <c r="I323" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" customHeight="1" spans="1:9">
+      <c r="A324" s="3">
+        <f t="shared" si="10"/>
+        <v>1018300503</v>
+      </c>
+      <c r="B324" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C324" s="2">
+        <v>3</v>
+      </c>
+      <c r="D324" s="2">
+        <v>3</v>
+      </c>
+      <c r="F324" s="2">
+        <v>5</v>
+      </c>
+      <c r="G324" s="11">
+        <v>12</v>
+      </c>
+      <c r="I324" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" customHeight="1" spans="1:9">
+      <c r="A325" s="3">
+        <f t="shared" si="10"/>
+        <v>1018300504</v>
+      </c>
+      <c r="B325" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C325" s="2">
+        <v>4</v>
+      </c>
+      <c r="D325" s="2">
+        <v>3</v>
+      </c>
+      <c r="F325" s="2">
+        <v>5</v>
+      </c>
+      <c r="G325" s="11">
+        <v>12</v>
+      </c>
+      <c r="I325" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" customHeight="1" spans="1:9">
+      <c r="A326" s="3">
+        <f t="shared" si="10"/>
+        <v>1018300505</v>
+      </c>
+      <c r="B326" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C326" s="2">
+        <v>5</v>
+      </c>
+      <c r="D326" s="2">
+        <v>3</v>
+      </c>
+      <c r="F326" s="2">
+        <v>5</v>
+      </c>
+      <c r="G326" s="11">
+        <v>15</v>
+      </c>
+      <c r="I326" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" customHeight="1" spans="1:9">
+      <c r="A327" s="3">
+        <f t="shared" si="10"/>
+        <v>1018300506</v>
+      </c>
+      <c r="B327" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C327" s="2">
+        <v>6</v>
+      </c>
+      <c r="D327" s="2">
+        <v>3</v>
+      </c>
+      <c r="F327" s="2">
+        <v>5</v>
+      </c>
+      <c r="G327" s="11">
+        <v>20</v>
+      </c>
+      <c r="I327" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" customHeight="1" spans="1:9">
+      <c r="A328" s="3">
+        <f t="shared" si="10"/>
+        <v>1018300507</v>
+      </c>
+      <c r="B328" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C328" s="2">
+        <v>7</v>
+      </c>
+      <c r="D328" s="2">
+        <v>3</v>
+      </c>
+      <c r="F328" s="2">
+        <v>5</v>
+      </c>
+      <c r="G328" s="11">
+        <v>20</v>
+      </c>
+      <c r="I328" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" customHeight="1" spans="1:9">
+      <c r="A329" s="3">
+        <f t="shared" si="10"/>
+        <v>1018300508</v>
+      </c>
+      <c r="B329" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C329" s="2">
+        <v>8</v>
+      </c>
+      <c r="D329" s="2">
+        <v>3</v>
+      </c>
+      <c r="F329" s="2">
+        <v>5</v>
+      </c>
+      <c r="G329" s="11">
+        <v>20</v>
+      </c>
+      <c r="I329" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" customHeight="1" spans="1:9">
+      <c r="A330" s="3">
+        <f t="shared" si="10"/>
+        <v>1018300509</v>
+      </c>
+      <c r="B330" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C330" s="2">
+        <v>9</v>
+      </c>
+      <c r="D330" s="2">
+        <v>3</v>
+      </c>
+      <c r="F330" s="2">
+        <v>5</v>
+      </c>
+      <c r="G330" s="11">
+        <v>50</v>
+      </c>
+      <c r="I330" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" customHeight="1" spans="1:9">
+      <c r="A331" s="3">
+        <f t="shared" si="10"/>
+        <v>1018300510</v>
+      </c>
+      <c r="B331" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C331" s="2">
+        <v>10</v>
+      </c>
+      <c r="D331" s="2">
+        <v>3</v>
+      </c>
+      <c r="F331" s="2">
+        <v>5</v>
+      </c>
+      <c r="G331" s="11">
+        <v>200</v>
+      </c>
+      <c r="I331" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" customHeight="1" spans="1:9">
+      <c r="A332" s="3">
+        <f t="shared" si="10"/>
+        <v>1018400511</v>
+      </c>
+      <c r="B332" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C332" s="2">
+        <v>11</v>
+      </c>
+      <c r="D332" s="2">
+        <v>4</v>
+      </c>
+      <c r="F332" s="2">
+        <v>5</v>
+      </c>
+      <c r="G332" s="11">
+        <v>0</v>
+      </c>
+      <c r="I332" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" customHeight="1" spans="1:9">
+      <c r="A333" s="3">
+        <f t="shared" si="10"/>
+        <v>1018400512</v>
+      </c>
+      <c r="B333" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C333" s="2">
+        <v>12</v>
+      </c>
+      <c r="D333" s="2">
+        <v>4</v>
+      </c>
+      <c r="F333" s="2">
+        <v>5</v>
+      </c>
+      <c r="G333" s="11">
+        <v>1000</v>
+      </c>
+      <c r="I333" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" customHeight="1" spans="1:9">
+      <c r="A334" s="3">
+        <f t="shared" ref="A334:A345" si="11">(B334)*10000+C334+F334*100+D334*100000</f>
+        <v>1018300601</v>
+      </c>
+      <c r="B334" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C334" s="2">
+        <v>1</v>
+      </c>
+      <c r="D334" s="2">
+        <v>3</v>
+      </c>
+      <c r="F334" s="2">
+        <v>6</v>
+      </c>
+      <c r="G334" s="11">
+        <v>10</v>
+      </c>
+      <c r="I334" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" customHeight="1" spans="1:9">
+      <c r="A335" s="3">
+        <f t="shared" si="11"/>
+        <v>1018300602</v>
+      </c>
+      <c r="B335" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C335" s="2">
+        <v>2</v>
+      </c>
+      <c r="D335" s="2">
+        <v>3</v>
+      </c>
+      <c r="F335" s="2">
+        <v>6</v>
+      </c>
+      <c r="G335" s="11">
+        <v>10</v>
+      </c>
+      <c r="I335" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" customHeight="1" spans="1:9">
+      <c r="A336" s="3">
+        <f t="shared" si="11"/>
+        <v>1018300603</v>
+      </c>
+      <c r="B336" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C336" s="2">
+        <v>3</v>
+      </c>
+      <c r="D336" s="2">
+        <v>3</v>
+      </c>
+      <c r="F336" s="2">
+        <v>6</v>
+      </c>
+      <c r="G336" s="11">
+        <v>15</v>
+      </c>
+      <c r="I336" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" customHeight="1" spans="1:12">
+      <c r="A337" s="3">
+        <f t="shared" si="11"/>
+        <v>1018300604</v>
+      </c>
+      <c r="B337" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C337" s="2">
+        <v>4</v>
+      </c>
+      <c r="D337" s="2">
+        <v>3</v>
+      </c>
+      <c r="F337" s="2">
+        <v>6</v>
+      </c>
+      <c r="G337" s="11">
+        <v>15</v>
+      </c>
+      <c r="I337" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" customHeight="1" spans="1:12">
+      <c r="A338" s="3">
+        <f t="shared" si="11"/>
+        <v>1018300605</v>
+      </c>
+      <c r="B338" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C338" s="2">
+        <v>5</v>
+      </c>
+      <c r="D338" s="2">
+        <v>3</v>
+      </c>
+      <c r="F338" s="2">
+        <v>6</v>
+      </c>
+      <c r="G338" s="11">
+        <v>20</v>
+      </c>
+      <c r="I338" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" customHeight="1" spans="1:12">
+      <c r="A339" s="3">
+        <f t="shared" si="11"/>
+        <v>1018300606</v>
+      </c>
+      <c r="B339" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C339" s="2">
+        <v>6</v>
+      </c>
+      <c r="D339" s="2">
+        <v>3</v>
+      </c>
+      <c r="F339" s="2">
+        <v>6</v>
+      </c>
+      <c r="G339" s="11">
+        <v>25</v>
+      </c>
+      <c r="I339" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" customHeight="1" spans="1:12">
+      <c r="A340" s="3">
+        <f t="shared" si="11"/>
+        <v>1018300607</v>
+      </c>
+      <c r="B340" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C340" s="2">
+        <v>7</v>
+      </c>
+      <c r="D340" s="2">
+        <v>3</v>
+      </c>
+      <c r="F340" s="2">
+        <v>6</v>
+      </c>
+      <c r="G340" s="11">
+        <v>30</v>
+      </c>
+      <c r="I340" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" customHeight="1" spans="1:12">
+      <c r="A341" s="3">
+        <f t="shared" si="11"/>
+        <v>1018300608</v>
+      </c>
+      <c r="B341" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C341" s="2">
+        <v>8</v>
+      </c>
+      <c r="D341" s="2">
+        <v>3</v>
+      </c>
+      <c r="F341" s="2">
+        <v>6</v>
+      </c>
+      <c r="G341" s="11">
+        <v>30</v>
+      </c>
+      <c r="I341" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" customHeight="1" spans="1:12">
+      <c r="A342" s="3">
+        <f t="shared" si="11"/>
+        <v>1018300609</v>
+      </c>
+      <c r="B342" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C342" s="2">
+        <v>9</v>
+      </c>
+      <c r="D342" s="2">
+        <v>3</v>
+      </c>
+      <c r="F342" s="2">
+        <v>6</v>
+      </c>
+      <c r="G342" s="11">
+        <v>100</v>
+      </c>
+      <c r="I342" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" customHeight="1" spans="1:12">
+      <c r="A343" s="3">
+        <f t="shared" si="11"/>
+        <v>1018300610</v>
+      </c>
+      <c r="B343" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C343" s="2">
+        <v>10</v>
+      </c>
+      <c r="D343" s="2">
+        <v>3</v>
+      </c>
+      <c r="F343" s="2">
+        <v>6</v>
+      </c>
+      <c r="G343" s="11">
+        <v>500</v>
+      </c>
+      <c r="I343" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" customHeight="1" spans="1:12">
+      <c r="A344" s="3">
+        <f t="shared" si="11"/>
+        <v>1018400611</v>
+      </c>
+      <c r="B344" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C344" s="2">
+        <v>11</v>
+      </c>
+      <c r="D344" s="2">
+        <v>4</v>
+      </c>
+      <c r="F344" s="2">
+        <v>6</v>
+      </c>
+      <c r="G344" s="11">
+        <v>0</v>
+      </c>
+      <c r="I344" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" customHeight="1" spans="1:12">
+      <c r="A345" s="3">
+        <f t="shared" si="11"/>
+        <v>1018400612</v>
+      </c>
+      <c r="B345" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C345" s="2">
+        <v>12</v>
+      </c>
+      <c r="D345" s="2">
+        <v>4</v>
+      </c>
+      <c r="F345" s="2">
+        <v>6</v>
+      </c>
+      <c r="G345" s="11">
+        <v>2000</v>
+      </c>
+      <c r="I345" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" customHeight="1" spans="1:12">
+      <c r="A346" s="3">
+        <f>(B346)*10000+C346+F346*100+D346*100000</f>
+        <v>1018400113</v>
+      </c>
+      <c r="B346" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C346" s="2">
+        <v>13</v>
+      </c>
+      <c r="D346" s="2">
+        <v>4</v>
+      </c>
+      <c r="F346" s="2">
+        <v>1</v>
+      </c>
+      <c r="G346" s="11">
+        <v>0</v>
+      </c>
+      <c r="I346" s="11">
+        <v>0</v>
+      </c>
+      <c r="K346" s="2">
+        <v>101800101</v>
+      </c>
+      <c r="L346" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="347" customHeight="1" spans="1:12">
+      <c r="A347" s="3">
+        <f>(B347)*10000+C347+F347*100+D347*100000</f>
+        <v>1018400114</v>
+      </c>
+      <c r="B347" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C347" s="2">
+        <v>14</v>
+      </c>
+      <c r="D347" s="2">
+        <v>4</v>
+      </c>
+      <c r="F347" s="2">
+        <v>1</v>
+      </c>
+      <c r="G347" s="11">
+        <v>0</v>
+      </c>
+      <c r="I347" s="11">
+        <v>0</v>
+      </c>
+      <c r="K347" s="2">
+        <v>101800102</v>
+      </c>
+      <c r="L347" s="13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="348" customHeight="1" spans="1:12">
+      <c r="A348" s="3">
+        <f>(B348)*10000+C348+F348*100+D348*100000</f>
+        <v>1018400115</v>
+      </c>
+      <c r="B348" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C348" s="2">
+        <v>15</v>
+      </c>
+      <c r="D348" s="2">
+        <v>4</v>
+      </c>
+      <c r="F348" s="2">
+        <v>1</v>
+      </c>
+      <c r="G348" s="11">
+        <v>0</v>
+      </c>
+      <c r="I348" s="11">
+        <v>0</v>
+      </c>
+      <c r="K348" s="2">
+        <v>101800103</v>
+      </c>
+      <c r="L348" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="349" customHeight="1" spans="1:12">
+      <c r="A349" s="3">
+        <f>(B349)*10000+C349+F349*100+D349*100000</f>
+        <v>1018400116</v>
+      </c>
+      <c r="B349" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C349" s="2">
+        <v>16</v>
+      </c>
+      <c r="D349" s="2">
+        <v>4</v>
+      </c>
+      <c r="F349" s="2">
+        <v>1</v>
+      </c>
+      <c r="G349" s="11">
+        <v>0</v>
+      </c>
+      <c r="I349" s="11">
+        <v>0</v>
+      </c>
+      <c r="K349" s="2">
+        <v>101800104</v>
+      </c>
+      <c r="L349" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="350" customHeight="1" spans="1:12">
+      <c r="A350" s="3">
+        <f>(B350)*10000+C350+F350*100+D350*100000</f>
+        <v>1018400117</v>
+      </c>
+      <c r="B350" s="2">
+        <v>101800</v>
+      </c>
+      <c r="C350" s="2">
+        <v>17</v>
+      </c>
+      <c r="D350" s="2">
+        <v>4</v>
+      </c>
+      <c r="F350" s="2">
+        <v>1</v>
+      </c>
+      <c r="G350" s="11">
+        <v>0</v>
+      </c>
+      <c r="I350" s="11">
+        <v>0</v>
+      </c>
+      <c r="L350" s="54" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L294" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L296" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="0" priority="128">
+    <cfRule type="expression" dxfId="0" priority="130">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D85:E85">
-    <cfRule type="expression" dxfId="0" priority="154">
+    <cfRule type="expression" dxfId="0" priority="156">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D86:E86">
-    <cfRule type="expression" dxfId="0" priority="119">
+    <cfRule type="expression" dxfId="0" priority="121">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105">
-    <cfRule type="duplicateValues" dxfId="1" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105:E105">
-    <cfRule type="expression" dxfId="0" priority="99">
+    <cfRule type="expression" dxfId="0" priority="101">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I105">
-    <cfRule type="expression" dxfId="0" priority="101">
+    <cfRule type="expression" dxfId="0" priority="103">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A106">
-    <cfRule type="duplicateValues" dxfId="1" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D106:E106">
-    <cfRule type="expression" dxfId="0" priority="95">
+    <cfRule type="expression" dxfId="0" priority="97">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I106">
-    <cfRule type="expression" dxfId="0" priority="97">
+    <cfRule type="expression" dxfId="0" priority="99">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="1" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D107:E107">
-    <cfRule type="expression" dxfId="0" priority="91">
+    <cfRule type="expression" dxfId="0" priority="93">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I107">
-    <cfRule type="expression" dxfId="0" priority="93">
+    <cfRule type="expression" dxfId="0" priority="95">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108">
-    <cfRule type="duplicateValues" dxfId="1" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D108:E108">
-    <cfRule type="expression" dxfId="0" priority="87">
+    <cfRule type="expression" dxfId="0" priority="89">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I108">
-    <cfRule type="expression" dxfId="0" priority="89">
+    <cfRule type="expression" dxfId="0" priority="91">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" dxfId="1" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D109:E109">
-    <cfRule type="expression" dxfId="0" priority="83">
+    <cfRule type="expression" dxfId="0" priority="85">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I109">
-    <cfRule type="expression" dxfId="0" priority="85">
+    <cfRule type="expression" dxfId="0" priority="87">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110">
-    <cfRule type="duplicateValues" dxfId="1" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D110:E110">
-    <cfRule type="expression" dxfId="0" priority="79">
+    <cfRule type="expression" dxfId="0" priority="81">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I110">
-    <cfRule type="expression" dxfId="0" priority="81">
+    <cfRule type="expression" dxfId="0" priority="83">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A111">
-    <cfRule type="duplicateValues" dxfId="1" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D111:E111">
-    <cfRule type="expression" dxfId="0" priority="75">
+    <cfRule type="expression" dxfId="0" priority="77">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I111">
-    <cfRule type="expression" dxfId="0" priority="77">
+    <cfRule type="expression" dxfId="0" priority="79">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112">
-    <cfRule type="duplicateValues" dxfId="1" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D112:E112">
-    <cfRule type="expression" dxfId="0" priority="71">
+    <cfRule type="expression" dxfId="0" priority="73">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I112">
-    <cfRule type="expression" dxfId="0" priority="73">
+    <cfRule type="expression" dxfId="0" priority="75">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A113">
-    <cfRule type="duplicateValues" dxfId="1" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D113:E113">
-    <cfRule type="expression" dxfId="0" priority="67">
+    <cfRule type="expression" dxfId="0" priority="69">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I113">
-    <cfRule type="expression" dxfId="0" priority="69">
+    <cfRule type="expression" dxfId="0" priority="71">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114">
-    <cfRule type="duplicateValues" dxfId="1" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D114:E114">
-    <cfRule type="expression" dxfId="0" priority="63">
+    <cfRule type="expression" dxfId="0" priority="65">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I114">
-    <cfRule type="expression" dxfId="0" priority="65">
+    <cfRule type="expression" dxfId="0" priority="67">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A115">
-    <cfRule type="duplicateValues" dxfId="1" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D115:E115">
-    <cfRule type="expression" dxfId="0" priority="59">
+    <cfRule type="expression" dxfId="0" priority="61">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I115">
-    <cfRule type="expression" dxfId="0" priority="61">
+    <cfRule type="expression" dxfId="0" priority="63">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A116">
-    <cfRule type="duplicateValues" dxfId="1" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D116:E116">
-    <cfRule type="expression" dxfId="0" priority="55">
+    <cfRule type="expression" dxfId="0" priority="57">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I116">
-    <cfRule type="expression" dxfId="0" priority="57">
+    <cfRule type="expression" dxfId="0" priority="59">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117">
-    <cfRule type="duplicateValues" dxfId="1" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D117:E117">
-    <cfRule type="expression" dxfId="0" priority="51">
+    <cfRule type="expression" dxfId="0" priority="53">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I117">
-    <cfRule type="expression" dxfId="0" priority="53">
+    <cfRule type="expression" dxfId="0" priority="55">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A118">
-    <cfRule type="duplicateValues" dxfId="1" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D118:E118">
-    <cfRule type="expression" dxfId="0" priority="47">
+    <cfRule type="expression" dxfId="0" priority="49">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I118">
-    <cfRule type="expression" dxfId="0" priority="49">
+    <cfRule type="expression" dxfId="0" priority="51">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A119">
-    <cfRule type="duplicateValues" dxfId="1" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D119:E119">
-    <cfRule type="expression" dxfId="0" priority="43">
+    <cfRule type="expression" dxfId="0" priority="45">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I119">
-    <cfRule type="expression" dxfId="0" priority="45">
+    <cfRule type="expression" dxfId="0" priority="47">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A120">
-    <cfRule type="duplicateValues" dxfId="1" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D120:E120">
-    <cfRule type="expression" dxfId="0" priority="39">
+    <cfRule type="expression" dxfId="0" priority="41">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I120">
-    <cfRule type="expression" dxfId="0" priority="41">
+    <cfRule type="expression" dxfId="0" priority="43">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A121">
-    <cfRule type="duplicateValues" dxfId="1" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D121:E121">
-    <cfRule type="expression" dxfId="0" priority="35">
+    <cfRule type="expression" dxfId="0" priority="37">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I121">
-    <cfRule type="expression" dxfId="0" priority="37">
+    <cfRule type="expression" dxfId="0" priority="39">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A122">
-    <cfRule type="duplicateValues" dxfId="1" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D122:E122">
-    <cfRule type="expression" dxfId="0" priority="31">
+    <cfRule type="expression" dxfId="0" priority="33">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I122">
-    <cfRule type="expression" dxfId="0" priority="33">
+    <cfRule type="expression" dxfId="0" priority="35">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A123">
-    <cfRule type="duplicateValues" dxfId="1" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D123:E123">
-    <cfRule type="expression" dxfId="0" priority="27">
+    <cfRule type="expression" dxfId="0" priority="29">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I123">
-    <cfRule type="expression" dxfId="0" priority="29">
+    <cfRule type="expression" dxfId="0" priority="31">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C134:L134">
-    <cfRule type="expression" dxfId="0" priority="155">
+    <cfRule type="expression" dxfId="0" priority="157">
       <formula>MOD($B134,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="expression" dxfId="0" priority="19">
+    <cfRule type="expression" dxfId="0" priority="21">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A178">
-    <cfRule type="duplicateValues" dxfId="1" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B178">
+    <cfRule type="expression" dxfId="0" priority="17">
+      <formula>MOD($B178,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D178:E178">
     <cfRule type="expression" dxfId="0" priority="15">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D178:E178">
-    <cfRule type="expression" dxfId="0" priority="13">
-      <formula>MOD($B178,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A48:A60">
-    <cfRule type="duplicateValues" dxfId="1" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A87:A92">
-    <cfRule type="duplicateValues" dxfId="1" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A93:A98">
-    <cfRule type="duplicateValues" dxfId="1" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99:A104">
-    <cfRule type="duplicateValues" dxfId="1" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A135:A177">
-    <cfRule type="duplicateValues" dxfId="1" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A209:A294">
-    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
+  <conditionalFormatting sqref="A209:A350">
+    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B60">
-    <cfRule type="expression" dxfId="0" priority="114">
+    <cfRule type="expression" dxfId="0" priority="116">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C84">
-    <cfRule type="expression" dxfId="0" priority="117">
+    <cfRule type="expression" dxfId="0" priority="119">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C280:C294">
-    <cfRule type="expression" dxfId="0" priority="4">
-      <formula>MOD($B280,2)=1</formula>
+  <conditionalFormatting sqref="C271:C281">
+    <cfRule type="expression" dxfId="0" priority="8">
+      <formula>MOD($B271,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C282:C296">
+    <cfRule type="expression" dxfId="0" priority="6">
+      <formula>MOD($B282,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E93:E98">
-    <cfRule type="expression" dxfId="0" priority="106">
+    <cfRule type="expression" dxfId="0" priority="108">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E99:E104">
-    <cfRule type="expression" dxfId="0" priority="103">
+    <cfRule type="expression" dxfId="0" priority="105">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E255:E266">
-    <cfRule type="expression" dxfId="0" priority="7">
-      <formula>MOD($B255,2)=1</formula>
+  <conditionalFormatting sqref="E257:E268">
+    <cfRule type="expression" dxfId="0" priority="9">
+      <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E269:E277">
-    <cfRule type="expression" dxfId="0" priority="5">
-      <formula>MOD($B269,2)=1</formula>
+  <conditionalFormatting sqref="E271:E279">
+    <cfRule type="expression" dxfId="0" priority="7">
+      <formula>MOD($B271,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E280:E288">
-    <cfRule type="expression" dxfId="0" priority="3">
-      <formula>MOD($B280,2)=1</formula>
+  <conditionalFormatting sqref="E282:E290">
+    <cfRule type="expression" dxfId="0" priority="5">
+      <formula>MOD($B282,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39:K42">
-    <cfRule type="duplicateValues" dxfId="2" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K169:K172">
-    <cfRule type="duplicateValues" dxfId="2" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K291:K294">
+  <conditionalFormatting sqref="K293:K296">
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>MOD($B293,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K346:K349">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>MOD($B291,2)=1</formula>
+      <formula>MOD($B346,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L205:L208">
-    <cfRule type="expression" dxfId="0" priority="12">
+    <cfRule type="expression" dxfId="0" priority="14">
       <formula>MOD($B205,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L291:L294">
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>MOD($B291,2)=1</formula>
+  <conditionalFormatting sqref="L293:L296">
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>MOD($B293,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A295:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="429"/>
+  <conditionalFormatting sqref="L346:L349">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>MOD($B346,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A351:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="431"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L4">
-    <cfRule type="expression" dxfId="0" priority="428">
+    <cfRule type="expression" dxfId="0" priority="430">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41:B42 B44:B47">
-    <cfRule type="expression" dxfId="0" priority="162">
+    <cfRule type="expression" dxfId="0" priority="164">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 H179:L204 B179:G208 I205:K208 B257:D266 F257:L266 B267:L268 B269:B294 D269:D277 F269:L277 D278:L279 D280:D288 F280:L288 D289:L290 D291:J294 B295:L1048576 I209:I254 B256">
-    <cfRule type="expression" dxfId="0" priority="427">
+  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 H179:L204 B179:G208 I205:K208 I209:I256 B259:D268 F259:L268 B269:L270 B271:B296 D271:D279 F271:L279 D280:L281 D282:D290 F282:L290 D291:L292 D293:J296 B297:L345 B346:J349 B350:L1048576 B258">
+    <cfRule type="expression" dxfId="0" priority="429">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43:G43 J43:L43">
-    <cfRule type="expression" dxfId="0" priority="127">
+    <cfRule type="expression" dxfId="0" priority="129">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44:G44 J44:L47 G45:G47 C45:C47">
-    <cfRule type="expression" dxfId="0" priority="161">
+    <cfRule type="expression" dxfId="0" priority="163">
       <formula>MOD($B44,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45:E47">
-    <cfRule type="expression" dxfId="0" priority="158">
+    <cfRule type="expression" dxfId="0" priority="160">
       <formula>MOD($B45,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F60 C48:C60">
+    <cfRule type="expression" dxfId="0" priority="117">
+      <formula>MOD($B48,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
     <cfRule type="expression" dxfId="0" priority="115">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
+  <conditionalFormatting sqref="D48:E60">
     <cfRule type="expression" dxfId="0" priority="113">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D48:E60">
-    <cfRule type="expression" dxfId="0" priority="111">
-      <formula>MOD($B48,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B77:B84 F77:L84">
-    <cfRule type="expression" dxfId="0" priority="157">
+    <cfRule type="expression" dxfId="0" priority="159">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85:C85 F85:L85">
-    <cfRule type="expression" dxfId="0" priority="153">
+    <cfRule type="expression" dxfId="0" priority="155">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B86:C86 F86:L86">
-    <cfRule type="expression" dxfId="0" priority="118">
+    <cfRule type="expression" dxfId="0" priority="120">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87:C92 F87:L92 I93:I104">
-    <cfRule type="expression" dxfId="0" priority="108">
+    <cfRule type="expression" dxfId="0" priority="110">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87:E92 D93:D104">
-    <cfRule type="expression" dxfId="0" priority="109">
+    <cfRule type="expression" dxfId="0" priority="111">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:C98 F93:H98 J93:L98">
-    <cfRule type="expression" dxfId="0" priority="105">
+    <cfRule type="expression" dxfId="0" priority="107">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99:C104 F99:H104 J99:L104">
-    <cfRule type="expression" dxfId="0" priority="102">
+    <cfRule type="expression" dxfId="0" priority="104">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:C105 F105:H105 J105:L105">
-    <cfRule type="expression" dxfId="0" priority="98">
+    <cfRule type="expression" dxfId="0" priority="100">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106:C106 F106:H106 J106:L106 H107:H111 C107:C111">
-    <cfRule type="expression" dxfId="0" priority="94">
+    <cfRule type="expression" dxfId="0" priority="96">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107 F107:G107 J107:L107">
-    <cfRule type="expression" dxfId="0" priority="90">
+    <cfRule type="expression" dxfId="0" priority="92">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B108 F108:G108 J108:L108">
-    <cfRule type="expression" dxfId="0" priority="86">
+    <cfRule type="expression" dxfId="0" priority="88">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B109 F109:G109 J109:L109">
-    <cfRule type="expression" dxfId="0" priority="82">
+    <cfRule type="expression" dxfId="0" priority="84">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B110 F110:G110 J110:L110">
-    <cfRule type="expression" dxfId="0" priority="78">
+    <cfRule type="expression" dxfId="0" priority="80">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111 F111:G111 J111:L111">
-    <cfRule type="expression" dxfId="0" priority="74">
+    <cfRule type="expression" dxfId="0" priority="76">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112:C112 F112:H112 J112:L112 H113:H117 C113:C117">
-    <cfRule type="expression" dxfId="0" priority="70">
+    <cfRule type="expression" dxfId="0" priority="72">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113 F113:G113 J113:L113">
-    <cfRule type="expression" dxfId="0" priority="66">
+    <cfRule type="expression" dxfId="0" priority="68">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114 F114:G114 J114:L114">
-    <cfRule type="expression" dxfId="0" priority="62">
+    <cfRule type="expression" dxfId="0" priority="64">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115 F115:G115 J115:L115">
-    <cfRule type="expression" dxfId="0" priority="58">
+    <cfRule type="expression" dxfId="0" priority="60">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B116 F116:G116 J116:L116">
-    <cfRule type="expression" dxfId="0" priority="54">
+    <cfRule type="expression" dxfId="0" priority="56">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117 F117:G117 J117:L117">
-    <cfRule type="expression" dxfId="0" priority="50">
+    <cfRule type="expression" dxfId="0" priority="52">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118:C118 F118:H118 J118:L118 H119:H123 C119:C123">
-    <cfRule type="expression" dxfId="0" priority="46">
+    <cfRule type="expression" dxfId="0" priority="48">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119 F119:G119 J119:L119">
-    <cfRule type="expression" dxfId="0" priority="42">
+    <cfRule type="expression" dxfId="0" priority="44">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120 F120:G120 J120:L120">
-    <cfRule type="expression" dxfId="0" priority="38">
+    <cfRule type="expression" dxfId="0" priority="40">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121 F121:G121 J121:L121">
-    <cfRule type="expression" dxfId="0" priority="34">
+    <cfRule type="expression" dxfId="0" priority="36">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122 F122:G122 J122:L122">
-    <cfRule type="expression" dxfId="0" priority="30">
+    <cfRule type="expression" dxfId="0" priority="32">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123 F123:G123 J123:L123">
-    <cfRule type="expression" dxfId="0" priority="26">
+    <cfRule type="expression" dxfId="0" priority="28">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B124:L133 B134">
-    <cfRule type="expression" dxfId="0" priority="156">
+    <cfRule type="expression" dxfId="0" priority="158">
       <formula>MOD($B124,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171:B172 B174:B177">
-    <cfRule type="expression" dxfId="0" priority="23">
+    <cfRule type="expression" dxfId="0" priority="25">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171:G172 J171:J172 L171:L172 F175:F177 C176:C177">
-    <cfRule type="expression" dxfId="0" priority="24">
+    <cfRule type="expression" dxfId="0" priority="26">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173:G173 J173:L173">
-    <cfRule type="expression" dxfId="0" priority="18">
+    <cfRule type="expression" dxfId="0" priority="20">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174:G174 J174:L177 G175:G177 C175:C177">
-    <cfRule type="expression" dxfId="0" priority="22">
+    <cfRule type="expression" dxfId="0" priority="24">
       <formula>MOD($B174,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D175:E177">
-    <cfRule type="expression" dxfId="0" priority="21">
+    <cfRule type="expression" dxfId="0" priority="23">
       <formula>MOD($B175,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F178 C178">
+    <cfRule type="expression" dxfId="0" priority="18">
+      <formula>MOD($B178,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J178:L178 G178 C178">
     <cfRule type="expression" dxfId="0" priority="16">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J178:L178 G178 C178">
-    <cfRule type="expression" dxfId="0" priority="14">
-      <formula>MOD($B178,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B209:D209 F209:H209 J209:L250 B210:H250">
-    <cfRule type="expression" dxfId="0" priority="11">
+    <cfRule type="expression" dxfId="0" priority="13">
       <formula>MOD($B209,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B251:H254 J251:L254">
-    <cfRule type="expression" dxfId="0" priority="10">
+  <conditionalFormatting sqref="B251:H256 J251:L256">
+    <cfRule type="expression" dxfId="0" priority="12">
       <formula>MOD($B251,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B255 B257 B259 B261 B263 B265 B267 B269 B271 B273 B275 B277 B279 B281 B283 B285 B287 B289 B291 B293">
-    <cfRule type="expression" dxfId="0" priority="8">
-      <formula>MOD($B255,2)=1</formula>
+  <conditionalFormatting sqref="B257 B259 B261 B263 B265 B267 B269 B271 B273 B275 B277 B279 B281 B283 B285 B287 B289 B291 B293 B295">
+    <cfRule type="expression" dxfId="0" priority="10">
+      <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C255:D255 F255:L255">
-    <cfRule type="expression" dxfId="0" priority="431">
-      <formula>MOD($B256,2)=1</formula>
+  <conditionalFormatting sqref="C257:D257 F257:L257">
+    <cfRule type="expression" dxfId="0" priority="433">
+      <formula>MOD($B258,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C256:D256 F256:L256 D258 D260 D262 D264 D266 I258 I260 I262 I264 I266 I268 I270 I272 I274 I276 I278 I280 I282 I284 I286 I288 I290">
-    <cfRule type="expression" dxfId="0" priority="430">
+  <conditionalFormatting sqref="C258:D258 I292 I290 I288 I286 I284 I282 I280 I278 I276 I274 I272 I270 I268 I266 I264 I262 I260 D268 D266 D264 D262 D260 F258:L258">
+    <cfRule type="expression" dxfId="0" priority="432">
       <formula>MOD(#REF!,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C269:C277 C278:C279">
-    <cfRule type="expression" dxfId="0" priority="6">
-      <formula>MOD($B269,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$296</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$350</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -765,6 +765,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -777,11 +782,6 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -13851,7 +13851,7 @@
     </row>
     <row r="257" customHeight="1" spans="1:9">
       <c r="A257" s="3">
-        <f t="shared" ref="A257:A296" si="7">(B257)*10000+C257+F257*100+D257*100000</f>
+        <f t="shared" ref="A257:A297" si="7">(B257)*10000+C257+F257*100+D257*100000</f>
         <v>1021300207</v>
       </c>
       <c r="B257" s="2">
@@ -14943,7 +14943,7 @@
     </row>
     <row r="297" customHeight="1" spans="1:12">
       <c r="A297" s="3">
-        <f>(B297)*10000+C297+F297*100+D297*100000</f>
+        <f t="shared" si="7"/>
         <v>1018300210</v>
       </c>
       <c r="B297" s="2">
@@ -15207,7 +15207,7 @@
     </row>
     <row r="308" customHeight="1" spans="1:9">
       <c r="A308" s="3">
-        <f t="shared" ref="A308:A317" si="9">(B308)*10000+C308+F308*100+D308*100000</f>
+        <f t="shared" ref="A308:A321" si="9">(B308)*10000+C308+F308*100+D308*100000</f>
         <v>1018400311</v>
       </c>
       <c r="B308" s="2">
@@ -15249,6 +15249,9 @@
       <c r="G309" s="11">
         <v>100</v>
       </c>
+      <c r="H309" s="11">
+        <v>30180001</v>
+      </c>
       <c r="I309" s="11">
         <v>0</v>
       </c>
@@ -15447,7 +15450,7 @@
     </row>
     <row r="318" customHeight="1" spans="1:9">
       <c r="A318" s="3">
-        <f>(B318)*10000+C318+F318*100+D318*100000</f>
+        <f t="shared" si="9"/>
         <v>1018300409</v>
       </c>
       <c r="B318" s="2">
@@ -15471,7 +15474,7 @@
     </row>
     <row r="319" customHeight="1" spans="1:9">
       <c r="A319" s="3">
-        <f>(B319)*10000+C319+F319*100+D319*100000</f>
+        <f t="shared" si="9"/>
         <v>1018300410</v>
       </c>
       <c r="B319" s="2">
@@ -15495,7 +15498,7 @@
     </row>
     <row r="320" customHeight="1" spans="1:9">
       <c r="A320" s="3">
-        <f>(B320)*10000+C320+F320*100+D320*100000</f>
+        <f t="shared" si="9"/>
         <v>1018400411</v>
       </c>
       <c r="B320" s="2">
@@ -15519,7 +15522,7 @@
     </row>
     <row r="321" customHeight="1" spans="1:9">
       <c r="A321" s="3">
-        <f>(B321)*10000+C321+F321*100+D321*100000</f>
+        <f t="shared" si="9"/>
         <v>1018400412</v>
       </c>
       <c r="B321" s="2">
@@ -15536,6 +15539,9 @@
       </c>
       <c r="G321" s="11">
         <v>400</v>
+      </c>
+      <c r="H321" s="11">
+        <v>30180001</v>
       </c>
       <c r="I321" s="11">
         <v>0</v>
@@ -15825,13 +15831,16 @@
       <c r="G333" s="11">
         <v>1000</v>
       </c>
+      <c r="H333" s="11">
+        <v>30180001</v>
+      </c>
       <c r="I333" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="334" customHeight="1" spans="1:9">
       <c r="A334" s="3">
-        <f t="shared" ref="A334:A345" si="11">(B334)*10000+C334+F334*100+D334*100000</f>
+        <f t="shared" ref="A334:A350" si="11">(B334)*10000+C334+F334*100+D334*100000</f>
         <v>1018300601</v>
       </c>
       <c r="B334" s="2">
@@ -16113,13 +16122,16 @@
       <c r="G345" s="11">
         <v>2000</v>
       </c>
+      <c r="H345" s="11">
+        <v>30180001</v>
+      </c>
       <c r="I345" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="346" customHeight="1" spans="1:12">
       <c r="A346" s="3">
-        <f>(B346)*10000+C346+F346*100+D346*100000</f>
+        <f t="shared" si="11"/>
         <v>1018400113</v>
       </c>
       <c r="B346" s="2">
@@ -16149,7 +16161,7 @@
     </row>
     <row r="347" customHeight="1" spans="1:12">
       <c r="A347" s="3">
-        <f>(B347)*10000+C347+F347*100+D347*100000</f>
+        <f t="shared" si="11"/>
         <v>1018400114</v>
       </c>
       <c r="B347" s="2">
@@ -16179,7 +16191,7 @@
     </row>
     <row r="348" customHeight="1" spans="1:12">
       <c r="A348" s="3">
-        <f>(B348)*10000+C348+F348*100+D348*100000</f>
+        <f t="shared" si="11"/>
         <v>1018400115</v>
       </c>
       <c r="B348" s="2">
@@ -16209,7 +16221,7 @@
     </row>
     <row r="349" customHeight="1" spans="1:12">
       <c r="A349" s="3">
-        <f>(B349)*10000+C349+F349*100+D349*100000</f>
+        <f t="shared" si="11"/>
         <v>1018400116</v>
       </c>
       <c r="B349" s="2">
@@ -16239,7 +16251,7 @@
     </row>
     <row r="350" customHeight="1" spans="1:12">
       <c r="A350" s="3">
-        <f>(B350)*10000+C350+F350*100+D350*100000</f>
+        <f t="shared" si="11"/>
         <v>1018400117</v>
       </c>
       <c r="B350" s="2">
@@ -16265,7 +16277,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L296" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L350" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">
@@ -16553,6 +16565,16 @@
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H309">
+    <cfRule type="expression" dxfId="0" priority="435">
+      <formula>MOD($B308,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H321">
+    <cfRule type="expression" dxfId="0" priority="434">
+      <formula>MOD($B320,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A48:A60">
     <cfRule type="duplicateValues" dxfId="1" priority="118"/>
   </conditionalFormatting>
@@ -16660,7 +16682,7 @@
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 H179:L204 B179:G208 I205:K208 I209:I256 B259:D268 F259:L268 B269:L270 B271:B296 D271:D279 F271:L279 D280:L281 D282:D290 F282:L290 D291:L292 D293:J296 B297:L345 B346:J349 B350:L1048576 B258">
+  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 H179:L204 B179:G208 I205:K208 I209:I256 B259:D268 F259:L268 B269:L270 B271:B296 D271:D279 F271:L279 D280:L281 D282:D290 F282:L290 D291:L292 D293:J296 H297:L307 H310:L319 I320:L321 B322:L345 B297:G321 B258 B346:J349 B350:L1048576 I308:L309">
     <cfRule type="expression" dxfId="0" priority="429">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="71">
   <si>
     <t>id</t>
   </si>
@@ -5821,7 +5821,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L350"/>
+  <dimension ref="A1:L387"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="10"/>
@@ -16276,639 +16276,1561 @@
         <v>70</v>
       </c>
     </row>
+    <row r="351" customHeight="1" spans="1:12">
+      <c r="A351" s="3">
+        <f t="shared" ref="A351:A361" si="12">(B351)*10000+C351+F351*100+D351*100000</f>
+        <v>1025100301</v>
+      </c>
+      <c r="B351" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C351" s="2">
+        <v>1</v>
+      </c>
+      <c r="D351" s="2">
+        <v>1</v>
+      </c>
+      <c r="F351" s="2">
+        <v>3</v>
+      </c>
+      <c r="G351" s="11">
+        <v>10</v>
+      </c>
+      <c r="I351" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" customHeight="1" spans="1:12">
+      <c r="A352" s="3">
+        <f t="shared" si="12"/>
+        <v>1025100302</v>
+      </c>
+      <c r="B352" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C352" s="2">
+        <v>2</v>
+      </c>
+      <c r="D352" s="2">
+        <v>1</v>
+      </c>
+      <c r="F352" s="2">
+        <v>3</v>
+      </c>
+      <c r="G352" s="11">
+        <v>10</v>
+      </c>
+      <c r="I352" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" customHeight="1" spans="1:9">
+      <c r="A353" s="3">
+        <f t="shared" si="12"/>
+        <v>1025100303</v>
+      </c>
+      <c r="B353" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C353" s="2">
+        <v>3</v>
+      </c>
+      <c r="D353" s="2">
+        <v>1</v>
+      </c>
+      <c r="F353" s="2">
+        <v>3</v>
+      </c>
+      <c r="G353" s="11">
+        <v>20</v>
+      </c>
+      <c r="I353" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" customHeight="1" spans="1:9">
+      <c r="A354" s="3">
+        <f t="shared" si="12"/>
+        <v>1025100304</v>
+      </c>
+      <c r="B354" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C354" s="2">
+        <v>4</v>
+      </c>
+      <c r="D354" s="2">
+        <v>1</v>
+      </c>
+      <c r="F354" s="2">
+        <v>3</v>
+      </c>
+      <c r="G354" s="11">
+        <v>20</v>
+      </c>
+      <c r="I354" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" customHeight="1" spans="1:9">
+      <c r="A355" s="3">
+        <f t="shared" si="12"/>
+        <v>1025100305</v>
+      </c>
+      <c r="B355" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C355" s="2">
+        <v>5</v>
+      </c>
+      <c r="D355" s="2">
+        <v>1</v>
+      </c>
+      <c r="F355" s="2">
+        <v>3</v>
+      </c>
+      <c r="G355" s="11">
+        <v>30</v>
+      </c>
+      <c r="I355" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" customHeight="1" spans="1:9">
+      <c r="A356" s="3">
+        <f t="shared" si="12"/>
+        <v>1025100306</v>
+      </c>
+      <c r="B356" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C356" s="2">
+        <v>6</v>
+      </c>
+      <c r="D356" s="2">
+        <v>1</v>
+      </c>
+      <c r="F356" s="2">
+        <v>3</v>
+      </c>
+      <c r="G356" s="11">
+        <v>30</v>
+      </c>
+      <c r="I356" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" customHeight="1" spans="1:9">
+      <c r="A357" s="3">
+        <f t="shared" si="12"/>
+        <v>1025100307</v>
+      </c>
+      <c r="B357" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C357" s="2">
+        <v>7</v>
+      </c>
+      <c r="D357" s="2">
+        <v>1</v>
+      </c>
+      <c r="F357" s="2">
+        <v>3</v>
+      </c>
+      <c r="G357" s="11">
+        <v>50</v>
+      </c>
+      <c r="I357" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" customHeight="1" spans="1:9">
+      <c r="A358" s="3">
+        <f t="shared" si="12"/>
+        <v>1025100308</v>
+      </c>
+      <c r="B358" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C358" s="2">
+        <v>8</v>
+      </c>
+      <c r="D358" s="2">
+        <v>1</v>
+      </c>
+      <c r="F358" s="2">
+        <v>3</v>
+      </c>
+      <c r="G358" s="11">
+        <v>50</v>
+      </c>
+      <c r="I358" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" customHeight="1" spans="1:9">
+      <c r="A359" s="3">
+        <f t="shared" si="12"/>
+        <v>1025100309</v>
+      </c>
+      <c r="B359" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C359" s="2">
+        <v>9</v>
+      </c>
+      <c r="D359" s="2">
+        <v>1</v>
+      </c>
+      <c r="F359" s="2">
+        <v>3</v>
+      </c>
+      <c r="G359" s="11">
+        <v>100</v>
+      </c>
+      <c r="I359" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" customHeight="1" spans="1:9">
+      <c r="A360" s="3">
+        <f t="shared" si="12"/>
+        <v>1025100310</v>
+      </c>
+      <c r="B360" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C360" s="2">
+        <v>10</v>
+      </c>
+      <c r="D360" s="2">
+        <v>1</v>
+      </c>
+      <c r="F360" s="2">
+        <v>3</v>
+      </c>
+      <c r="G360" s="11">
+        <v>0</v>
+      </c>
+      <c r="I360" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" customHeight="1" spans="1:9">
+      <c r="A361" s="3">
+        <f t="shared" si="12"/>
+        <v>1025400311</v>
+      </c>
+      <c r="B361" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C361" s="2">
+        <v>11</v>
+      </c>
+      <c r="D361" s="2">
+        <v>4</v>
+      </c>
+      <c r="F361" s="2">
+        <v>3</v>
+      </c>
+      <c r="G361" s="11">
+        <v>500</v>
+      </c>
+      <c r="I361" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" customHeight="1" spans="1:9">
+      <c r="A362" s="3">
+        <f t="shared" ref="A362:A372" si="13">(B362)*10000+C362+F362*100+D362*100000</f>
+        <v>1025100401</v>
+      </c>
+      <c r="B362" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C362" s="2">
+        <v>1</v>
+      </c>
+      <c r="D362" s="2">
+        <v>1</v>
+      </c>
+      <c r="F362" s="2">
+        <v>4</v>
+      </c>
+      <c r="G362" s="11">
+        <v>50</v>
+      </c>
+      <c r="I362" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" customHeight="1" spans="1:9">
+      <c r="A363" s="3">
+        <f t="shared" si="13"/>
+        <v>1025100402</v>
+      </c>
+      <c r="B363" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C363" s="2">
+        <v>2</v>
+      </c>
+      <c r="D363" s="2">
+        <v>1</v>
+      </c>
+      <c r="F363" s="2">
+        <v>4</v>
+      </c>
+      <c r="G363" s="11">
+        <v>50</v>
+      </c>
+      <c r="I363" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" customHeight="1" spans="1:9">
+      <c r="A364" s="3">
+        <f t="shared" si="13"/>
+        <v>1025100403</v>
+      </c>
+      <c r="B364" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C364" s="2">
+        <v>3</v>
+      </c>
+      <c r="D364" s="2">
+        <v>1</v>
+      </c>
+      <c r="F364" s="2">
+        <v>4</v>
+      </c>
+      <c r="G364" s="11">
+        <v>80</v>
+      </c>
+      <c r="I364" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" customHeight="1" spans="1:9">
+      <c r="A365" s="3">
+        <f t="shared" si="13"/>
+        <v>1025100404</v>
+      </c>
+      <c r="B365" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C365" s="2">
+        <v>4</v>
+      </c>
+      <c r="D365" s="2">
+        <v>1</v>
+      </c>
+      <c r="F365" s="2">
+        <v>4</v>
+      </c>
+      <c r="G365" s="11">
+        <v>80</v>
+      </c>
+      <c r="I365" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" customHeight="1" spans="1:9">
+      <c r="A366" s="3">
+        <f t="shared" si="13"/>
+        <v>1025100405</v>
+      </c>
+      <c r="B366" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C366" s="2">
+        <v>5</v>
+      </c>
+      <c r="D366" s="2">
+        <v>1</v>
+      </c>
+      <c r="F366" s="2">
+        <v>4</v>
+      </c>
+      <c r="G366" s="11">
+        <v>100</v>
+      </c>
+      <c r="I366" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" customHeight="1" spans="1:9">
+      <c r="A367" s="3">
+        <f t="shared" si="13"/>
+        <v>1025100406</v>
+      </c>
+      <c r="B367" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C367" s="2">
+        <v>6</v>
+      </c>
+      <c r="D367" s="2">
+        <v>1</v>
+      </c>
+      <c r="F367" s="2">
+        <v>4</v>
+      </c>
+      <c r="G367" s="11">
+        <v>100</v>
+      </c>
+      <c r="I367" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" customHeight="1" spans="1:9">
+      <c r="A368" s="3">
+        <f t="shared" si="13"/>
+        <v>1025100407</v>
+      </c>
+      <c r="B368" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C368" s="2">
+        <v>7</v>
+      </c>
+      <c r="D368" s="2">
+        <v>1</v>
+      </c>
+      <c r="F368" s="2">
+        <v>4</v>
+      </c>
+      <c r="G368" s="11">
+        <v>200</v>
+      </c>
+      <c r="I368" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" customHeight="1" spans="1:12">
+      <c r="A369" s="3">
+        <f t="shared" si="13"/>
+        <v>1025100408</v>
+      </c>
+      <c r="B369" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C369" s="2">
+        <v>8</v>
+      </c>
+      <c r="D369" s="2">
+        <v>1</v>
+      </c>
+      <c r="F369" s="2">
+        <v>4</v>
+      </c>
+      <c r="G369" s="11">
+        <v>200</v>
+      </c>
+      <c r="I369" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" customHeight="1" spans="1:12">
+      <c r="A370" s="3">
+        <f t="shared" si="13"/>
+        <v>1025100409</v>
+      </c>
+      <c r="B370" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C370" s="2">
+        <v>9</v>
+      </c>
+      <c r="D370" s="2">
+        <v>1</v>
+      </c>
+      <c r="F370" s="2">
+        <v>4</v>
+      </c>
+      <c r="G370" s="11">
+        <v>300</v>
+      </c>
+      <c r="I370" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" customHeight="1" spans="1:12">
+      <c r="A371" s="3">
+        <f t="shared" si="13"/>
+        <v>1025100410</v>
+      </c>
+      <c r="B371" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C371" s="2">
+        <v>10</v>
+      </c>
+      <c r="D371" s="2">
+        <v>1</v>
+      </c>
+      <c r="F371" s="2">
+        <v>4</v>
+      </c>
+      <c r="G371" s="11">
+        <v>0</v>
+      </c>
+      <c r="I371" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" customHeight="1" spans="1:12">
+      <c r="A372" s="3">
+        <f t="shared" si="13"/>
+        <v>1025400411</v>
+      </c>
+      <c r="B372" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C372" s="2">
+        <v>11</v>
+      </c>
+      <c r="D372" s="2">
+        <v>4</v>
+      </c>
+      <c r="F372" s="2">
+        <v>4</v>
+      </c>
+      <c r="G372" s="11">
+        <v>2500</v>
+      </c>
+      <c r="I372" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" customHeight="1" spans="1:12">
+      <c r="A373" s="3">
+        <f t="shared" ref="A373:A383" si="14">(B373)*10000+C373+F373*100+D373*100000</f>
+        <v>1025100501</v>
+      </c>
+      <c r="B373" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C373" s="2">
+        <v>1</v>
+      </c>
+      <c r="D373" s="2">
+        <v>1</v>
+      </c>
+      <c r="F373" s="2">
+        <v>5</v>
+      </c>
+      <c r="G373" s="11">
+        <v>100</v>
+      </c>
+      <c r="I373" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" customHeight="1" spans="1:12">
+      <c r="A374" s="3">
+        <f t="shared" si="14"/>
+        <v>1025100502</v>
+      </c>
+      <c r="B374" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C374" s="2">
+        <v>2</v>
+      </c>
+      <c r="D374" s="2">
+        <v>1</v>
+      </c>
+      <c r="F374" s="2">
+        <v>5</v>
+      </c>
+      <c r="G374" s="11">
+        <v>100</v>
+      </c>
+      <c r="I374" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" customHeight="1" spans="1:12">
+      <c r="A375" s="3">
+        <f t="shared" si="14"/>
+        <v>1025100503</v>
+      </c>
+      <c r="B375" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C375" s="2">
+        <v>3</v>
+      </c>
+      <c r="D375" s="2">
+        <v>1</v>
+      </c>
+      <c r="F375" s="2">
+        <v>5</v>
+      </c>
+      <c r="G375" s="11">
+        <v>300</v>
+      </c>
+      <c r="I375" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" customHeight="1" spans="1:12">
+      <c r="A376" s="3">
+        <f t="shared" si="14"/>
+        <v>1025100504</v>
+      </c>
+      <c r="B376" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C376" s="2">
+        <v>4</v>
+      </c>
+      <c r="D376" s="2">
+        <v>1</v>
+      </c>
+      <c r="F376" s="2">
+        <v>5</v>
+      </c>
+      <c r="G376" s="11">
+        <v>300</v>
+      </c>
+      <c r="I376" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" customHeight="1" spans="1:12">
+      <c r="A377" s="3">
+        <f t="shared" si="14"/>
+        <v>1025100505</v>
+      </c>
+      <c r="B377" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C377" s="2">
+        <v>5</v>
+      </c>
+      <c r="D377" s="2">
+        <v>1</v>
+      </c>
+      <c r="F377" s="2">
+        <v>5</v>
+      </c>
+      <c r="G377" s="11">
+        <v>500</v>
+      </c>
+      <c r="I377" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" customHeight="1" spans="1:12">
+      <c r="A378" s="3">
+        <f t="shared" si="14"/>
+        <v>1025100506</v>
+      </c>
+      <c r="B378" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C378" s="2">
+        <v>6</v>
+      </c>
+      <c r="D378" s="2">
+        <v>1</v>
+      </c>
+      <c r="F378" s="2">
+        <v>5</v>
+      </c>
+      <c r="G378" s="11">
+        <v>500</v>
+      </c>
+      <c r="I378" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" customHeight="1" spans="1:12">
+      <c r="A379" s="3">
+        <f t="shared" si="14"/>
+        <v>1025100507</v>
+      </c>
+      <c r="B379" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C379" s="2">
+        <v>7</v>
+      </c>
+      <c r="D379" s="2">
+        <v>1</v>
+      </c>
+      <c r="F379" s="2">
+        <v>5</v>
+      </c>
+      <c r="G379" s="11">
+        <v>1000</v>
+      </c>
+      <c r="I379" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" customHeight="1" spans="1:12">
+      <c r="A380" s="3">
+        <f t="shared" si="14"/>
+        <v>1025100508</v>
+      </c>
+      <c r="B380" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C380" s="2">
+        <v>8</v>
+      </c>
+      <c r="D380" s="2">
+        <v>1</v>
+      </c>
+      <c r="F380" s="2">
+        <v>5</v>
+      </c>
+      <c r="G380" s="11">
+        <v>1000</v>
+      </c>
+      <c r="I380" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" customHeight="1" spans="1:12">
+      <c r="A381" s="3">
+        <f t="shared" si="14"/>
+        <v>1025100509</v>
+      </c>
+      <c r="B381" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C381" s="2">
+        <v>9</v>
+      </c>
+      <c r="D381" s="2">
+        <v>1</v>
+      </c>
+      <c r="F381" s="2">
+        <v>5</v>
+      </c>
+      <c r="G381" s="11">
+        <v>2000</v>
+      </c>
+      <c r="I381" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" customHeight="1" spans="1:12">
+      <c r="A382" s="3">
+        <f t="shared" si="14"/>
+        <v>1025100510</v>
+      </c>
+      <c r="B382" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C382" s="2">
+        <v>10</v>
+      </c>
+      <c r="D382" s="2">
+        <v>1</v>
+      </c>
+      <c r="F382" s="2">
+        <v>5</v>
+      </c>
+      <c r="G382" s="11">
+        <v>0</v>
+      </c>
+      <c r="I382" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" customHeight="1" spans="1:12">
+      <c r="A383" s="3">
+        <f t="shared" si="14"/>
+        <v>1025400511</v>
+      </c>
+      <c r="B383" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C383" s="2">
+        <v>11</v>
+      </c>
+      <c r="D383" s="2">
+        <v>4</v>
+      </c>
+      <c r="F383" s="2">
+        <v>5</v>
+      </c>
+      <c r="G383" s="11">
+        <v>5000</v>
+      </c>
+      <c r="I383" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" customHeight="1" spans="1:12">
+      <c r="A384" s="3">
+        <f>(B384)*10000+C384+F384*100+D384*100000</f>
+        <v>1025400112</v>
+      </c>
+      <c r="B384" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C384" s="2">
+        <v>12</v>
+      </c>
+      <c r="D384" s="2">
+        <v>4</v>
+      </c>
+      <c r="F384" s="2">
+        <v>1</v>
+      </c>
+      <c r="G384" s="11">
+        <v>0</v>
+      </c>
+      <c r="I384" s="11">
+        <v>0</v>
+      </c>
+      <c r="K384" s="2">
+        <v>102500101</v>
+      </c>
+      <c r="L384" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="385" customHeight="1" spans="1:12">
+      <c r="A385" s="3">
+        <f>(B385)*10000+C385+F385*100+D385*100000</f>
+        <v>1025400113</v>
+      </c>
+      <c r="B385" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C385" s="2">
+        <v>13</v>
+      </c>
+      <c r="D385" s="2">
+        <v>4</v>
+      </c>
+      <c r="F385" s="2">
+        <v>1</v>
+      </c>
+      <c r="G385" s="11">
+        <v>0</v>
+      </c>
+      <c r="I385" s="11">
+        <v>0</v>
+      </c>
+      <c r="K385" s="2">
+        <v>102500102</v>
+      </c>
+      <c r="L385" s="13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="386" customHeight="1" spans="1:12">
+      <c r="A386" s="3">
+        <f>(B386)*10000+C386+F386*100+D386*100000</f>
+        <v>1025400114</v>
+      </c>
+      <c r="B386" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C386" s="2">
+        <v>14</v>
+      </c>
+      <c r="D386" s="2">
+        <v>4</v>
+      </c>
+      <c r="F386" s="2">
+        <v>1</v>
+      </c>
+      <c r="G386" s="11">
+        <v>0</v>
+      </c>
+      <c r="I386" s="11">
+        <v>0</v>
+      </c>
+      <c r="K386" s="2">
+        <v>102500103</v>
+      </c>
+      <c r="L386" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="387" customHeight="1" spans="1:12">
+      <c r="A387" s="3">
+        <f>(B387)*10000+C387+F387*100+D387*100000</f>
+        <v>1025400115</v>
+      </c>
+      <c r="B387" s="2">
+        <v>102500</v>
+      </c>
+      <c r="C387" s="2">
+        <v>15</v>
+      </c>
+      <c r="D387" s="2">
+        <v>4</v>
+      </c>
+      <c r="F387" s="2">
+        <v>1</v>
+      </c>
+      <c r="G387" s="11">
+        <v>0</v>
+      </c>
+      <c r="I387" s="11">
+        <v>0</v>
+      </c>
+      <c r="K387" s="2">
+        <v>102500104</v>
+      </c>
+      <c r="L387" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L350" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="0" priority="130">
+    <cfRule type="expression" dxfId="0" priority="132">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D85:E85">
-    <cfRule type="expression" dxfId="0" priority="156">
+    <cfRule type="expression" dxfId="0" priority="158">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D86:E86">
-    <cfRule type="expression" dxfId="0" priority="121">
+    <cfRule type="expression" dxfId="0" priority="123">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105">
-    <cfRule type="duplicateValues" dxfId="1" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105:E105">
-    <cfRule type="expression" dxfId="0" priority="101">
+    <cfRule type="expression" dxfId="0" priority="103">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I105">
-    <cfRule type="expression" dxfId="0" priority="103">
+    <cfRule type="expression" dxfId="0" priority="105">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A106">
-    <cfRule type="duplicateValues" dxfId="1" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D106:E106">
-    <cfRule type="expression" dxfId="0" priority="97">
+    <cfRule type="expression" dxfId="0" priority="99">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I106">
-    <cfRule type="expression" dxfId="0" priority="99">
+    <cfRule type="expression" dxfId="0" priority="101">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="1" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D107:E107">
-    <cfRule type="expression" dxfId="0" priority="93">
+    <cfRule type="expression" dxfId="0" priority="95">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I107">
-    <cfRule type="expression" dxfId="0" priority="95">
+    <cfRule type="expression" dxfId="0" priority="97">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108">
-    <cfRule type="duplicateValues" dxfId="1" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D108:E108">
-    <cfRule type="expression" dxfId="0" priority="89">
+    <cfRule type="expression" dxfId="0" priority="91">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I108">
-    <cfRule type="expression" dxfId="0" priority="91">
+    <cfRule type="expression" dxfId="0" priority="93">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" dxfId="1" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D109:E109">
-    <cfRule type="expression" dxfId="0" priority="85">
+    <cfRule type="expression" dxfId="0" priority="87">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I109">
-    <cfRule type="expression" dxfId="0" priority="87">
+    <cfRule type="expression" dxfId="0" priority="89">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110">
-    <cfRule type="duplicateValues" dxfId="1" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D110:E110">
-    <cfRule type="expression" dxfId="0" priority="81">
+    <cfRule type="expression" dxfId="0" priority="83">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I110">
-    <cfRule type="expression" dxfId="0" priority="83">
+    <cfRule type="expression" dxfId="0" priority="85">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A111">
-    <cfRule type="duplicateValues" dxfId="1" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D111:E111">
-    <cfRule type="expression" dxfId="0" priority="77">
+    <cfRule type="expression" dxfId="0" priority="79">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I111">
-    <cfRule type="expression" dxfId="0" priority="79">
+    <cfRule type="expression" dxfId="0" priority="81">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112">
-    <cfRule type="duplicateValues" dxfId="1" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D112:E112">
-    <cfRule type="expression" dxfId="0" priority="73">
+    <cfRule type="expression" dxfId="0" priority="75">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I112">
-    <cfRule type="expression" dxfId="0" priority="75">
+    <cfRule type="expression" dxfId="0" priority="77">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A113">
-    <cfRule type="duplicateValues" dxfId="1" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D113:E113">
-    <cfRule type="expression" dxfId="0" priority="69">
+    <cfRule type="expression" dxfId="0" priority="71">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I113">
-    <cfRule type="expression" dxfId="0" priority="71">
+    <cfRule type="expression" dxfId="0" priority="73">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114">
-    <cfRule type="duplicateValues" dxfId="1" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D114:E114">
-    <cfRule type="expression" dxfId="0" priority="65">
+    <cfRule type="expression" dxfId="0" priority="67">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I114">
-    <cfRule type="expression" dxfId="0" priority="67">
+    <cfRule type="expression" dxfId="0" priority="69">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A115">
-    <cfRule type="duplicateValues" dxfId="1" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D115:E115">
-    <cfRule type="expression" dxfId="0" priority="61">
+    <cfRule type="expression" dxfId="0" priority="63">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I115">
-    <cfRule type="expression" dxfId="0" priority="63">
+    <cfRule type="expression" dxfId="0" priority="65">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A116">
-    <cfRule type="duplicateValues" dxfId="1" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D116:E116">
-    <cfRule type="expression" dxfId="0" priority="57">
+    <cfRule type="expression" dxfId="0" priority="59">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I116">
-    <cfRule type="expression" dxfId="0" priority="59">
+    <cfRule type="expression" dxfId="0" priority="61">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117">
-    <cfRule type="duplicateValues" dxfId="1" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D117:E117">
-    <cfRule type="expression" dxfId="0" priority="53">
+    <cfRule type="expression" dxfId="0" priority="55">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I117">
-    <cfRule type="expression" dxfId="0" priority="55">
+    <cfRule type="expression" dxfId="0" priority="57">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A118">
-    <cfRule type="duplicateValues" dxfId="1" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D118:E118">
-    <cfRule type="expression" dxfId="0" priority="49">
+    <cfRule type="expression" dxfId="0" priority="51">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I118">
-    <cfRule type="expression" dxfId="0" priority="51">
+    <cfRule type="expression" dxfId="0" priority="53">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A119">
-    <cfRule type="duplicateValues" dxfId="1" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D119:E119">
-    <cfRule type="expression" dxfId="0" priority="45">
+    <cfRule type="expression" dxfId="0" priority="47">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I119">
-    <cfRule type="expression" dxfId="0" priority="47">
+    <cfRule type="expression" dxfId="0" priority="49">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A120">
-    <cfRule type="duplicateValues" dxfId="1" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D120:E120">
-    <cfRule type="expression" dxfId="0" priority="41">
+    <cfRule type="expression" dxfId="0" priority="43">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I120">
-    <cfRule type="expression" dxfId="0" priority="43">
+    <cfRule type="expression" dxfId="0" priority="45">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A121">
-    <cfRule type="duplicateValues" dxfId="1" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D121:E121">
-    <cfRule type="expression" dxfId="0" priority="37">
+    <cfRule type="expression" dxfId="0" priority="39">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I121">
-    <cfRule type="expression" dxfId="0" priority="39">
+    <cfRule type="expression" dxfId="0" priority="41">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A122">
-    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D122:E122">
-    <cfRule type="expression" dxfId="0" priority="33">
+    <cfRule type="expression" dxfId="0" priority="35">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I122">
-    <cfRule type="expression" dxfId="0" priority="35">
+    <cfRule type="expression" dxfId="0" priority="37">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A123">
-    <cfRule type="duplicateValues" dxfId="1" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D123:E123">
-    <cfRule type="expression" dxfId="0" priority="29">
+    <cfRule type="expression" dxfId="0" priority="31">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I123">
-    <cfRule type="expression" dxfId="0" priority="31">
+    <cfRule type="expression" dxfId="0" priority="33">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C134:L134">
-    <cfRule type="expression" dxfId="0" priority="157">
+    <cfRule type="expression" dxfId="0" priority="159">
       <formula>MOD($B134,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="expression" dxfId="0" priority="21">
+    <cfRule type="expression" dxfId="0" priority="23">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A178">
-    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B178">
+    <cfRule type="expression" dxfId="0" priority="19">
+      <formula>MOD($B178,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D178:E178">
     <cfRule type="expression" dxfId="0" priority="17">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D178:E178">
-    <cfRule type="expression" dxfId="0" priority="15">
-      <formula>MOD($B178,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H309">
-    <cfRule type="expression" dxfId="0" priority="435">
+    <cfRule type="expression" dxfId="0" priority="437">
       <formula>MOD($B308,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H321">
-    <cfRule type="expression" dxfId="0" priority="434">
+    <cfRule type="expression" dxfId="0" priority="436">
       <formula>MOD($B320,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:A60">
-    <cfRule type="duplicateValues" dxfId="1" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A87:A92">
-    <cfRule type="duplicateValues" dxfId="1" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A93:A98">
-    <cfRule type="duplicateValues" dxfId="1" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99:A104">
-    <cfRule type="duplicateValues" dxfId="1" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A135:A177">
-    <cfRule type="duplicateValues" dxfId="1" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A209:A350">
-    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
+  <conditionalFormatting sqref="A209:A387">
+    <cfRule type="duplicateValues" dxfId="1" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B60">
-    <cfRule type="expression" dxfId="0" priority="116">
+    <cfRule type="expression" dxfId="0" priority="118">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C84">
-    <cfRule type="expression" dxfId="0" priority="119">
+    <cfRule type="expression" dxfId="0" priority="121">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C271:C281">
-    <cfRule type="expression" dxfId="0" priority="8">
+    <cfRule type="expression" dxfId="0" priority="10">
       <formula>MOD($B271,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C282:C296">
-    <cfRule type="expression" dxfId="0" priority="6">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>MOD($B282,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E93:E98">
-    <cfRule type="expression" dxfId="0" priority="108">
+    <cfRule type="expression" dxfId="0" priority="110">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E99:E104">
-    <cfRule type="expression" dxfId="0" priority="105">
+    <cfRule type="expression" dxfId="0" priority="107">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E257:E268">
-    <cfRule type="expression" dxfId="0" priority="9">
+    <cfRule type="expression" dxfId="0" priority="11">
       <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E271:E279">
-    <cfRule type="expression" dxfId="0" priority="7">
+    <cfRule type="expression" dxfId="0" priority="9">
       <formula>MOD($B271,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E282:E290">
-    <cfRule type="expression" dxfId="0" priority="5">
+    <cfRule type="expression" dxfId="0" priority="7">
       <formula>MOD($B282,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39:K42">
-    <cfRule type="duplicateValues" dxfId="2" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K169:K172">
-    <cfRule type="duplicateValues" dxfId="2" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K293:K296">
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="0" priority="5">
       <formula>MOD($B293,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K346:K349">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>MOD($B346,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K384:K387">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD($B384,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L205:L208">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="0" priority="16">
       <formula>MOD($B205,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L293:L296">
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="0" priority="6">
       <formula>MOD($B293,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L346:L349">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>MOD($B346,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A351:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="431"/>
+  <conditionalFormatting sqref="L384:L387">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>MOD($B384,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A388:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="433"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L4">
-    <cfRule type="expression" dxfId="0" priority="430">
+    <cfRule type="expression" dxfId="0" priority="432">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41:B42 B44:B47">
-    <cfRule type="expression" dxfId="0" priority="164">
+    <cfRule type="expression" dxfId="0" priority="166">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 H179:L204 B179:G208 I205:K208 I209:I256 B259:D268 F259:L268 B269:L270 B271:B296 D271:D279 F271:L279 D280:L281 D282:D290 F282:L290 D291:L292 D293:J296 H297:L307 H310:L319 I320:L321 B322:L345 B297:G321 B258 B346:J349 B350:L1048576 I308:L309">
-    <cfRule type="expression" dxfId="0" priority="429">
+  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 H179:L204 B179:G208 I205:K208 I209:I256 B259:D268 F259:L268 B269:L270 B271:B296 D271:D279 F271:L279 D280:L281 D282:D290 F282:L290 D291:L292 D293:J296 H297:L307 H310:L319 I320:L321 B322:L345 B297:G321 B258 B346:J349 B350:L383 B384:J387 B388:L1048576 I308:L309">
+    <cfRule type="expression" dxfId="0" priority="431">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43:G43 J43:L43">
-    <cfRule type="expression" dxfId="0" priority="129">
+    <cfRule type="expression" dxfId="0" priority="131">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44:G44 J44:L47 G45:G47 C45:C47">
-    <cfRule type="expression" dxfId="0" priority="163">
+    <cfRule type="expression" dxfId="0" priority="165">
       <formula>MOD($B44,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45:E47">
-    <cfRule type="expression" dxfId="0" priority="160">
+    <cfRule type="expression" dxfId="0" priority="162">
       <formula>MOD($B45,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F60 C48:C60">
+    <cfRule type="expression" dxfId="0" priority="119">
+      <formula>MOD($B48,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
     <cfRule type="expression" dxfId="0" priority="117">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
+  <conditionalFormatting sqref="D48:E60">
     <cfRule type="expression" dxfId="0" priority="115">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D48:E60">
-    <cfRule type="expression" dxfId="0" priority="113">
-      <formula>MOD($B48,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B77:B84 F77:L84">
-    <cfRule type="expression" dxfId="0" priority="159">
+    <cfRule type="expression" dxfId="0" priority="161">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85:C85 F85:L85">
-    <cfRule type="expression" dxfId="0" priority="155">
+    <cfRule type="expression" dxfId="0" priority="157">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B86:C86 F86:L86">
-    <cfRule type="expression" dxfId="0" priority="120">
+    <cfRule type="expression" dxfId="0" priority="122">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87:C92 F87:L92 I93:I104">
-    <cfRule type="expression" dxfId="0" priority="110">
+    <cfRule type="expression" dxfId="0" priority="112">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87:E92 D93:D104">
-    <cfRule type="expression" dxfId="0" priority="111">
+    <cfRule type="expression" dxfId="0" priority="113">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:C98 F93:H98 J93:L98">
-    <cfRule type="expression" dxfId="0" priority="107">
+    <cfRule type="expression" dxfId="0" priority="109">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99:C104 F99:H104 J99:L104">
-    <cfRule type="expression" dxfId="0" priority="104">
+    <cfRule type="expression" dxfId="0" priority="106">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:C105 F105:H105 J105:L105">
-    <cfRule type="expression" dxfId="0" priority="100">
+    <cfRule type="expression" dxfId="0" priority="102">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106:C106 F106:H106 J106:L106 H107:H111 C107:C111">
-    <cfRule type="expression" dxfId="0" priority="96">
+    <cfRule type="expression" dxfId="0" priority="98">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107 F107:G107 J107:L107">
-    <cfRule type="expression" dxfId="0" priority="92">
+    <cfRule type="expression" dxfId="0" priority="94">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B108 F108:G108 J108:L108">
-    <cfRule type="expression" dxfId="0" priority="88">
+    <cfRule type="expression" dxfId="0" priority="90">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B109 F109:G109 J109:L109">
-    <cfRule type="expression" dxfId="0" priority="84">
+    <cfRule type="expression" dxfId="0" priority="86">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B110 F110:G110 J110:L110">
-    <cfRule type="expression" dxfId="0" priority="80">
+    <cfRule type="expression" dxfId="0" priority="82">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111 F111:G111 J111:L111">
-    <cfRule type="expression" dxfId="0" priority="76">
+    <cfRule type="expression" dxfId="0" priority="78">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112:C112 F112:H112 J112:L112 H113:H117 C113:C117">
-    <cfRule type="expression" dxfId="0" priority="72">
+    <cfRule type="expression" dxfId="0" priority="74">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113 F113:G113 J113:L113">
-    <cfRule type="expression" dxfId="0" priority="68">
+    <cfRule type="expression" dxfId="0" priority="70">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114 F114:G114 J114:L114">
-    <cfRule type="expression" dxfId="0" priority="64">
+    <cfRule type="expression" dxfId="0" priority="66">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115 F115:G115 J115:L115">
-    <cfRule type="expression" dxfId="0" priority="60">
+    <cfRule type="expression" dxfId="0" priority="62">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B116 F116:G116 J116:L116">
-    <cfRule type="expression" dxfId="0" priority="56">
+    <cfRule type="expression" dxfId="0" priority="58">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117 F117:G117 J117:L117">
-    <cfRule type="expression" dxfId="0" priority="52">
+    <cfRule type="expression" dxfId="0" priority="54">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118:C118 F118:H118 J118:L118 H119:H123 C119:C123">
-    <cfRule type="expression" dxfId="0" priority="48">
+    <cfRule type="expression" dxfId="0" priority="50">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119 F119:G119 J119:L119">
-    <cfRule type="expression" dxfId="0" priority="44">
+    <cfRule type="expression" dxfId="0" priority="46">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120 F120:G120 J120:L120">
-    <cfRule type="expression" dxfId="0" priority="40">
+    <cfRule type="expression" dxfId="0" priority="42">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121 F121:G121 J121:L121">
-    <cfRule type="expression" dxfId="0" priority="36">
+    <cfRule type="expression" dxfId="0" priority="38">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122 F122:G122 J122:L122">
-    <cfRule type="expression" dxfId="0" priority="32">
+    <cfRule type="expression" dxfId="0" priority="34">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123 F123:G123 J123:L123">
-    <cfRule type="expression" dxfId="0" priority="28">
+    <cfRule type="expression" dxfId="0" priority="30">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B124:L133 B134">
-    <cfRule type="expression" dxfId="0" priority="158">
+    <cfRule type="expression" dxfId="0" priority="160">
       <formula>MOD($B124,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171:B172 B174:B177">
-    <cfRule type="expression" dxfId="0" priority="25">
+    <cfRule type="expression" dxfId="0" priority="27">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171:G172 J171:J172 L171:L172 F175:F177 C176:C177">
-    <cfRule type="expression" dxfId="0" priority="26">
+    <cfRule type="expression" dxfId="0" priority="28">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173:G173 J173:L173">
-    <cfRule type="expression" dxfId="0" priority="20">
+    <cfRule type="expression" dxfId="0" priority="22">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174:G174 J174:L177 G175:G177 C175:C177">
-    <cfRule type="expression" dxfId="0" priority="24">
+    <cfRule type="expression" dxfId="0" priority="26">
       <formula>MOD($B174,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D175:E177">
-    <cfRule type="expression" dxfId="0" priority="23">
+    <cfRule type="expression" dxfId="0" priority="25">
       <formula>MOD($B175,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F178 C178">
+    <cfRule type="expression" dxfId="0" priority="20">
+      <formula>MOD($B178,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J178:L178 G178 C178">
     <cfRule type="expression" dxfId="0" priority="18">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J178:L178 G178 C178">
-    <cfRule type="expression" dxfId="0" priority="16">
-      <formula>MOD($B178,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B209:D209 F209:H209 J209:L250 B210:H250">
-    <cfRule type="expression" dxfId="0" priority="13">
+    <cfRule type="expression" dxfId="0" priority="15">
       <formula>MOD($B209,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B251:H256 J251:L256">
-    <cfRule type="expression" dxfId="0" priority="12">
+    <cfRule type="expression" dxfId="0" priority="14">
       <formula>MOD($B251,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B257 B259 B261 B263 B265 B267 B269 B271 B273 B275 B277 B279 B281 B283 B285 B287 B289 B291 B293 B295">
-    <cfRule type="expression" dxfId="0" priority="10">
+    <cfRule type="expression" dxfId="0" priority="12">
       <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C257:D257 F257:L257">
-    <cfRule type="expression" dxfId="0" priority="433">
+    <cfRule type="expression" dxfId="0" priority="435">
       <formula>MOD($B258,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C258:D258 I292 I290 I288 I286 I284 I282 I280 I278 I276 I274 I272 I270 I268 I266 I264 I262 I260 D268 D266 D264 D262 D260 F258:L258">
-    <cfRule type="expression" dxfId="0" priority="432">
+    <cfRule type="expression" dxfId="0" priority="434">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$350</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$387</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -765,11 +765,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -782,6 +777,11 @@
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -16536,6 +16536,9 @@
       <c r="G361" s="11">
         <v>500</v>
       </c>
+      <c r="H361" s="11">
+        <v>30250001</v>
+      </c>
       <c r="I361" s="11">
         <v>0</v>
       </c>
@@ -16800,13 +16803,16 @@
       <c r="G372" s="11">
         <v>2500</v>
       </c>
+      <c r="H372" s="11">
+        <v>30250002</v>
+      </c>
       <c r="I372" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="373" customHeight="1" spans="1:12">
       <c r="A373" s="3">
-        <f t="shared" ref="A373:A383" si="14">(B373)*10000+C373+F373*100+D373*100000</f>
+        <f t="shared" ref="A373:A387" si="14">(B373)*10000+C373+F373*100+D373*100000</f>
         <v>1025100501</v>
       </c>
       <c r="B373" s="2">
@@ -17064,13 +17070,16 @@
       <c r="G383" s="11">
         <v>5000</v>
       </c>
+      <c r="H383" s="11">
+        <v>30250003</v>
+      </c>
       <c r="I383" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="384" customHeight="1" spans="1:12">
       <c r="A384" s="3">
-        <f>(B384)*10000+C384+F384*100+D384*100000</f>
+        <f t="shared" si="14"/>
         <v>1025400112</v>
       </c>
       <c r="B384" s="2">
@@ -17100,7 +17109,7 @@
     </row>
     <row r="385" customHeight="1" spans="1:12">
       <c r="A385" s="3">
-        <f>(B385)*10000+C385+F385*100+D385*100000</f>
+        <f t="shared" si="14"/>
         <v>1025400113</v>
       </c>
       <c r="B385" s="2">
@@ -17130,7 +17139,7 @@
     </row>
     <row r="386" customHeight="1" spans="1:12">
       <c r="A386" s="3">
-        <f>(B386)*10000+C386+F386*100+D386*100000</f>
+        <f t="shared" si="14"/>
         <v>1025400114</v>
       </c>
       <c r="B386" s="2">
@@ -17160,7 +17169,7 @@
     </row>
     <row r="387" customHeight="1" spans="1:12">
       <c r="A387" s="3">
-        <f>(B387)*10000+C387+F387*100+D387*100000</f>
+        <f t="shared" si="14"/>
         <v>1025400115</v>
       </c>
       <c r="B387" s="2">
@@ -17189,7 +17198,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L350" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L387" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$387</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$425</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="71">
   <si>
     <t>id</t>
   </si>
@@ -5821,7 +5821,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L387"/>
+  <dimension ref="A1:L425"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="10"/>
@@ -16152,11 +16152,8 @@
       <c r="I346" s="11">
         <v>0</v>
       </c>
-      <c r="K346" s="2">
-        <v>101800101</v>
-      </c>
-      <c r="L346" s="13" t="s">
-        <v>65</v>
+      <c r="L346" s="54" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="347" customHeight="1" spans="1:12">
@@ -16183,10 +16180,10 @@
         <v>0</v>
       </c>
       <c r="K347" s="2">
-        <v>101800102</v>
+        <v>101800101</v>
       </c>
       <c r="L347" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="348" customHeight="1" spans="1:12">
@@ -16213,10 +16210,10 @@
         <v>0</v>
       </c>
       <c r="K348" s="2">
-        <v>101800103</v>
+        <v>101800102</v>
       </c>
       <c r="L348" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="349" customHeight="1" spans="1:12">
@@ -16243,10 +16240,10 @@
         <v>0</v>
       </c>
       <c r="K349" s="2">
-        <v>101800104</v>
+        <v>101800103</v>
       </c>
       <c r="L349" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="350" customHeight="1" spans="1:12">
@@ -16272,8 +16269,11 @@
       <c r="I350" s="11">
         <v>0</v>
       </c>
-      <c r="L350" s="54" t="s">
-        <v>70</v>
+      <c r="K350" s="2">
+        <v>101800104</v>
+      </c>
+      <c r="L350" s="13" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="351" customHeight="1" spans="1:12">
@@ -17197,649 +17197,1600 @@
         <v>68</v>
       </c>
     </row>
+    <row r="388" customHeight="1" spans="1:12">
+      <c r="A388" s="3">
+        <f t="shared" ref="A388:A398" si="15">(B388)*10000+C388+F388*100+D388*100000</f>
+        <v>1023300301</v>
+      </c>
+      <c r="B388" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C388" s="2">
+        <v>1</v>
+      </c>
+      <c r="D388" s="2">
+        <v>3</v>
+      </c>
+      <c r="F388" s="2">
+        <v>3</v>
+      </c>
+      <c r="G388" s="11">
+        <v>2</v>
+      </c>
+      <c r="I388" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" customHeight="1" spans="1:12">
+      <c r="A389" s="3">
+        <f t="shared" si="15"/>
+        <v>1023300302</v>
+      </c>
+      <c r="B389" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C389" s="2">
+        <v>2</v>
+      </c>
+      <c r="D389" s="2">
+        <v>3</v>
+      </c>
+      <c r="F389" s="2">
+        <v>3</v>
+      </c>
+      <c r="G389" s="11">
+        <v>2</v>
+      </c>
+      <c r="I389" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" customHeight="1" spans="1:12">
+      <c r="A390" s="3">
+        <f t="shared" si="15"/>
+        <v>1023300303</v>
+      </c>
+      <c r="B390" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C390" s="2">
+        <v>3</v>
+      </c>
+      <c r="D390" s="2">
+        <v>3</v>
+      </c>
+      <c r="F390" s="2">
+        <v>3</v>
+      </c>
+      <c r="G390" s="11">
+        <v>2</v>
+      </c>
+      <c r="I390" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" customHeight="1" spans="1:12">
+      <c r="A391" s="3">
+        <f t="shared" si="15"/>
+        <v>1023300304</v>
+      </c>
+      <c r="B391" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C391" s="2">
+        <v>4</v>
+      </c>
+      <c r="D391" s="2">
+        <v>3</v>
+      </c>
+      <c r="F391" s="2">
+        <v>3</v>
+      </c>
+      <c r="G391" s="11">
+        <v>3</v>
+      </c>
+      <c r="I391" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" customHeight="1" spans="1:12">
+      <c r="A392" s="3">
+        <f t="shared" si="15"/>
+        <v>1023300305</v>
+      </c>
+      <c r="B392" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C392" s="2">
+        <v>5</v>
+      </c>
+      <c r="D392" s="2">
+        <v>3</v>
+      </c>
+      <c r="F392" s="2">
+        <v>3</v>
+      </c>
+      <c r="G392" s="11">
+        <v>3</v>
+      </c>
+      <c r="I392" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" customHeight="1" spans="1:12">
+      <c r="A393" s="3">
+        <f t="shared" si="15"/>
+        <v>1023300306</v>
+      </c>
+      <c r="B393" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C393" s="2">
+        <v>6</v>
+      </c>
+      <c r="D393" s="2">
+        <v>3</v>
+      </c>
+      <c r="F393" s="2">
+        <v>3</v>
+      </c>
+      <c r="G393" s="11">
+        <v>4</v>
+      </c>
+      <c r="I393" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" customHeight="1" spans="1:12">
+      <c r="A394" s="3">
+        <f t="shared" si="15"/>
+        <v>1023300307</v>
+      </c>
+      <c r="B394" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C394" s="2">
+        <v>7</v>
+      </c>
+      <c r="D394" s="2">
+        <v>3</v>
+      </c>
+      <c r="F394" s="2">
+        <v>3</v>
+      </c>
+      <c r="G394" s="11">
+        <v>4</v>
+      </c>
+      <c r="I394" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" customHeight="1" spans="1:12">
+      <c r="A395" s="3">
+        <f t="shared" si="15"/>
+        <v>1023300308</v>
+      </c>
+      <c r="B395" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C395" s="2">
+        <v>8</v>
+      </c>
+      <c r="D395" s="2">
+        <v>3</v>
+      </c>
+      <c r="F395" s="2">
+        <v>3</v>
+      </c>
+      <c r="G395" s="11">
+        <v>5</v>
+      </c>
+      <c r="I395" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" customHeight="1" spans="1:12">
+      <c r="A396" s="3">
+        <f t="shared" si="15"/>
+        <v>1023300309</v>
+      </c>
+      <c r="B396" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C396" s="2">
+        <v>9</v>
+      </c>
+      <c r="D396" s="2">
+        <v>3</v>
+      </c>
+      <c r="F396" s="2">
+        <v>3</v>
+      </c>
+      <c r="G396" s="11">
+        <v>5</v>
+      </c>
+      <c r="I396" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" customHeight="1" spans="1:12">
+      <c r="A397" s="3">
+        <f t="shared" si="15"/>
+        <v>1023300310</v>
+      </c>
+      <c r="B397" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C397" s="2">
+        <v>10</v>
+      </c>
+      <c r="D397" s="2">
+        <v>3</v>
+      </c>
+      <c r="F397" s="2">
+        <v>3</v>
+      </c>
+      <c r="G397" s="11">
+        <v>10</v>
+      </c>
+      <c r="I397" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" customHeight="1" spans="1:12">
+      <c r="A398" s="3">
+        <f t="shared" si="15"/>
+        <v>1023400311</v>
+      </c>
+      <c r="B398" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C398" s="2">
+        <v>11</v>
+      </c>
+      <c r="D398" s="2">
+        <v>4</v>
+      </c>
+      <c r="F398" s="2">
+        <v>3</v>
+      </c>
+      <c r="G398" s="11">
+        <v>0</v>
+      </c>
+      <c r="I398" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" customHeight="1" spans="1:12">
+      <c r="A399" s="3">
+        <f t="shared" ref="A399:A425" si="16">(B399)*10000+C399+F399*100+D399*100000</f>
+        <v>1023300401</v>
+      </c>
+      <c r="B399" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C399" s="2">
+        <v>1</v>
+      </c>
+      <c r="D399" s="2">
+        <v>3</v>
+      </c>
+      <c r="F399" s="2">
+        <v>4</v>
+      </c>
+      <c r="G399" s="11">
+        <v>5</v>
+      </c>
+      <c r="I399" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" customHeight="1" spans="1:12">
+      <c r="A400" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300402</v>
+      </c>
+      <c r="B400" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C400" s="2">
+        <v>2</v>
+      </c>
+      <c r="D400" s="2">
+        <v>3</v>
+      </c>
+      <c r="F400" s="2">
+        <v>4</v>
+      </c>
+      <c r="G400" s="11">
+        <v>5</v>
+      </c>
+      <c r="I400" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" customHeight="1" spans="1:9">
+      <c r="A401" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300403</v>
+      </c>
+      <c r="B401" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C401" s="2">
+        <v>3</v>
+      </c>
+      <c r="D401" s="2">
+        <v>3</v>
+      </c>
+      <c r="F401" s="2">
+        <v>4</v>
+      </c>
+      <c r="G401" s="11">
+        <v>5</v>
+      </c>
+      <c r="I401" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" customHeight="1" spans="1:9">
+      <c r="A402" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300404</v>
+      </c>
+      <c r="B402" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C402" s="2">
+        <v>4</v>
+      </c>
+      <c r="D402" s="2">
+        <v>3</v>
+      </c>
+      <c r="F402" s="2">
+        <v>4</v>
+      </c>
+      <c r="G402" s="11">
+        <v>10</v>
+      </c>
+      <c r="I402" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" customHeight="1" spans="1:9">
+      <c r="A403" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300405</v>
+      </c>
+      <c r="B403" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C403" s="2">
+        <v>5</v>
+      </c>
+      <c r="D403" s="2">
+        <v>3</v>
+      </c>
+      <c r="F403" s="2">
+        <v>4</v>
+      </c>
+      <c r="G403" s="11">
+        <v>10</v>
+      </c>
+      <c r="I403" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" customHeight="1" spans="1:9">
+      <c r="A404" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300406</v>
+      </c>
+      <c r="B404" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C404" s="2">
+        <v>6</v>
+      </c>
+      <c r="D404" s="2">
+        <v>3</v>
+      </c>
+      <c r="F404" s="2">
+        <v>4</v>
+      </c>
+      <c r="G404" s="11">
+        <v>15</v>
+      </c>
+      <c r="I404" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" customHeight="1" spans="1:9">
+      <c r="A405" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300407</v>
+      </c>
+      <c r="B405" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C405" s="2">
+        <v>7</v>
+      </c>
+      <c r="D405" s="2">
+        <v>3</v>
+      </c>
+      <c r="F405" s="2">
+        <v>4</v>
+      </c>
+      <c r="G405" s="11">
+        <v>20</v>
+      </c>
+      <c r="I405" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" customHeight="1" spans="1:9">
+      <c r="A406" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300408</v>
+      </c>
+      <c r="B406" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C406" s="2">
+        <v>8</v>
+      </c>
+      <c r="D406" s="2">
+        <v>3</v>
+      </c>
+      <c r="F406" s="2">
+        <v>4</v>
+      </c>
+      <c r="G406" s="11">
+        <v>25</v>
+      </c>
+      <c r="I406" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" customHeight="1" spans="1:9">
+      <c r="A407" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300409</v>
+      </c>
+      <c r="B407" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C407" s="2">
+        <v>9</v>
+      </c>
+      <c r="D407" s="2">
+        <v>3</v>
+      </c>
+      <c r="F407" s="2">
+        <v>4</v>
+      </c>
+      <c r="G407" s="11">
+        <v>30</v>
+      </c>
+      <c r="I407" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" customHeight="1" spans="1:9">
+      <c r="A408" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300410</v>
+      </c>
+      <c r="B408" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C408" s="2">
+        <v>10</v>
+      </c>
+      <c r="D408" s="2">
+        <v>3</v>
+      </c>
+      <c r="F408" s="2">
+        <v>4</v>
+      </c>
+      <c r="G408" s="11">
+        <v>50</v>
+      </c>
+      <c r="I408" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" customHeight="1" spans="1:9">
+      <c r="A409" s="3">
+        <f t="shared" si="16"/>
+        <v>1023400411</v>
+      </c>
+      <c r="B409" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C409" s="2">
+        <v>11</v>
+      </c>
+      <c r="D409" s="2">
+        <v>4</v>
+      </c>
+      <c r="F409" s="2">
+        <v>4</v>
+      </c>
+      <c r="G409" s="11">
+        <v>0</v>
+      </c>
+      <c r="I409" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" customHeight="1" spans="1:9">
+      <c r="A410" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300501</v>
+      </c>
+      <c r="B410" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C410" s="2">
+        <v>1</v>
+      </c>
+      <c r="D410" s="2">
+        <v>3</v>
+      </c>
+      <c r="F410" s="2">
+        <v>5</v>
+      </c>
+      <c r="G410" s="11">
+        <v>10</v>
+      </c>
+      <c r="I410" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" customHeight="1" spans="1:9">
+      <c r="A411" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300502</v>
+      </c>
+      <c r="B411" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C411" s="2">
+        <v>2</v>
+      </c>
+      <c r="D411" s="2">
+        <v>3</v>
+      </c>
+      <c r="F411" s="2">
+        <v>5</v>
+      </c>
+      <c r="G411" s="11">
+        <v>10</v>
+      </c>
+      <c r="I411" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" customHeight="1" spans="1:9">
+      <c r="A412" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300503</v>
+      </c>
+      <c r="B412" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C412" s="2">
+        <v>3</v>
+      </c>
+      <c r="D412" s="2">
+        <v>3</v>
+      </c>
+      <c r="F412" s="2">
+        <v>5</v>
+      </c>
+      <c r="G412" s="11">
+        <v>10</v>
+      </c>
+      <c r="I412" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" customHeight="1" spans="1:9">
+      <c r="A413" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300504</v>
+      </c>
+      <c r="B413" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C413" s="2">
+        <v>4</v>
+      </c>
+      <c r="D413" s="2">
+        <v>3</v>
+      </c>
+      <c r="F413" s="2">
+        <v>5</v>
+      </c>
+      <c r="G413" s="11">
+        <v>20</v>
+      </c>
+      <c r="I413" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" customHeight="1" spans="1:9">
+      <c r="A414" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300505</v>
+      </c>
+      <c r="B414" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C414" s="2">
+        <v>5</v>
+      </c>
+      <c r="D414" s="2">
+        <v>3</v>
+      </c>
+      <c r="F414" s="2">
+        <v>5</v>
+      </c>
+      <c r="G414" s="11">
+        <v>20</v>
+      </c>
+      <c r="I414" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" customHeight="1" spans="1:9">
+      <c r="A415" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300506</v>
+      </c>
+      <c r="B415" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C415" s="2">
+        <v>6</v>
+      </c>
+      <c r="D415" s="2">
+        <v>3</v>
+      </c>
+      <c r="F415" s="2">
+        <v>5</v>
+      </c>
+      <c r="G415" s="11">
+        <v>30</v>
+      </c>
+      <c r="I415" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" customHeight="1" spans="1:9">
+      <c r="A416" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300507</v>
+      </c>
+      <c r="B416" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C416" s="2">
+        <v>7</v>
+      </c>
+      <c r="D416" s="2">
+        <v>3</v>
+      </c>
+      <c r="F416" s="2">
+        <v>5</v>
+      </c>
+      <c r="G416" s="11">
+        <v>40</v>
+      </c>
+      <c r="I416" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" customHeight="1" spans="1:12">
+      <c r="A417" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300508</v>
+      </c>
+      <c r="B417" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C417" s="2">
+        <v>8</v>
+      </c>
+      <c r="D417" s="2">
+        <v>3</v>
+      </c>
+      <c r="F417" s="2">
+        <v>5</v>
+      </c>
+      <c r="G417" s="11">
+        <v>50</v>
+      </c>
+      <c r="I417" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" customHeight="1" spans="1:12">
+      <c r="A418" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300509</v>
+      </c>
+      <c r="B418" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C418" s="2">
+        <v>9</v>
+      </c>
+      <c r="D418" s="2">
+        <v>3</v>
+      </c>
+      <c r="F418" s="2">
+        <v>5</v>
+      </c>
+      <c r="G418" s="11">
+        <v>60</v>
+      </c>
+      <c r="I418" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" customHeight="1" spans="1:12">
+      <c r="A419" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300510</v>
+      </c>
+      <c r="B419" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C419" s="2">
+        <v>10</v>
+      </c>
+      <c r="D419" s="2">
+        <v>3</v>
+      </c>
+      <c r="F419" s="2">
+        <v>5</v>
+      </c>
+      <c r="G419" s="11">
+        <v>100</v>
+      </c>
+      <c r="I419" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" customHeight="1" spans="1:12">
+      <c r="A420" s="3">
+        <f t="shared" si="16"/>
+        <v>1023400511</v>
+      </c>
+      <c r="B420" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C420" s="2">
+        <v>11</v>
+      </c>
+      <c r="D420" s="2">
+        <v>4</v>
+      </c>
+      <c r="F420" s="2">
+        <v>5</v>
+      </c>
+      <c r="G420" s="11">
+        <v>0</v>
+      </c>
+      <c r="I420" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" customHeight="1" spans="1:12">
+      <c r="A421" s="3">
+        <f t="shared" si="16"/>
+        <v>1023400112</v>
+      </c>
+      <c r="B421" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C421" s="2">
+        <v>12</v>
+      </c>
+      <c r="D421" s="2">
+        <v>4</v>
+      </c>
+      <c r="F421" s="2">
+        <v>1</v>
+      </c>
+      <c r="G421" s="11">
+        <v>0</v>
+      </c>
+      <c r="I421" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" customHeight="1" spans="1:12">
+      <c r="A422" s="3">
+        <f t="shared" si="16"/>
+        <v>1023400113</v>
+      </c>
+      <c r="B422" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C422" s="2">
+        <v>13</v>
+      </c>
+      <c r="D422" s="2">
+        <v>4</v>
+      </c>
+      <c r="F422" s="2">
+        <v>1</v>
+      </c>
+      <c r="G422" s="11">
+        <v>0</v>
+      </c>
+      <c r="I422" s="11">
+        <v>0</v>
+      </c>
+      <c r="K422" s="2">
+        <v>102300101</v>
+      </c>
+      <c r="L422" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="423" customHeight="1" spans="1:12">
+      <c r="A423" s="3">
+        <f t="shared" si="16"/>
+        <v>1023400114</v>
+      </c>
+      <c r="B423" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C423" s="2">
+        <v>14</v>
+      </c>
+      <c r="D423" s="2">
+        <v>4</v>
+      </c>
+      <c r="F423" s="2">
+        <v>1</v>
+      </c>
+      <c r="G423" s="11">
+        <v>0</v>
+      </c>
+      <c r="I423" s="11">
+        <v>0</v>
+      </c>
+      <c r="K423" s="2">
+        <v>102300102</v>
+      </c>
+      <c r="L423" s="13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="424" customHeight="1" spans="1:12">
+      <c r="A424" s="3">
+        <f t="shared" si="16"/>
+        <v>1023400115</v>
+      </c>
+      <c r="B424" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C424" s="2">
+        <v>15</v>
+      </c>
+      <c r="D424" s="2">
+        <v>4</v>
+      </c>
+      <c r="F424" s="2">
+        <v>1</v>
+      </c>
+      <c r="G424" s="11">
+        <v>0</v>
+      </c>
+      <c r="I424" s="11">
+        <v>0</v>
+      </c>
+      <c r="K424" s="2">
+        <v>102300103</v>
+      </c>
+      <c r="L424" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="425" customHeight="1" spans="1:12">
+      <c r="A425" s="3">
+        <f t="shared" si="16"/>
+        <v>1023400116</v>
+      </c>
+      <c r="B425" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C425" s="2">
+        <v>16</v>
+      </c>
+      <c r="D425" s="2">
+        <v>4</v>
+      </c>
+      <c r="F425" s="2">
+        <v>1</v>
+      </c>
+      <c r="G425" s="11">
+        <v>0</v>
+      </c>
+      <c r="I425" s="11">
+        <v>0</v>
+      </c>
+      <c r="K425" s="2">
+        <v>102300104</v>
+      </c>
+      <c r="L425" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L387" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L425" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="0" priority="132">
+    <cfRule type="expression" dxfId="0" priority="134">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D85:E85">
-    <cfRule type="expression" dxfId="0" priority="158">
+    <cfRule type="expression" dxfId="0" priority="160">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D86:E86">
-    <cfRule type="expression" dxfId="0" priority="123">
+    <cfRule type="expression" dxfId="0" priority="125">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105">
-    <cfRule type="duplicateValues" dxfId="1" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105:E105">
-    <cfRule type="expression" dxfId="0" priority="103">
+    <cfRule type="expression" dxfId="0" priority="105">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I105">
-    <cfRule type="expression" dxfId="0" priority="105">
+    <cfRule type="expression" dxfId="0" priority="107">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A106">
-    <cfRule type="duplicateValues" dxfId="1" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D106:E106">
-    <cfRule type="expression" dxfId="0" priority="99">
+    <cfRule type="expression" dxfId="0" priority="101">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I106">
-    <cfRule type="expression" dxfId="0" priority="101">
+    <cfRule type="expression" dxfId="0" priority="103">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="1" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D107:E107">
-    <cfRule type="expression" dxfId="0" priority="95">
+    <cfRule type="expression" dxfId="0" priority="97">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I107">
-    <cfRule type="expression" dxfId="0" priority="97">
+    <cfRule type="expression" dxfId="0" priority="99">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108">
-    <cfRule type="duplicateValues" dxfId="1" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D108:E108">
-    <cfRule type="expression" dxfId="0" priority="91">
+    <cfRule type="expression" dxfId="0" priority="93">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I108">
-    <cfRule type="expression" dxfId="0" priority="93">
+    <cfRule type="expression" dxfId="0" priority="95">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" dxfId="1" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D109:E109">
-    <cfRule type="expression" dxfId="0" priority="87">
+    <cfRule type="expression" dxfId="0" priority="89">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I109">
-    <cfRule type="expression" dxfId="0" priority="89">
+    <cfRule type="expression" dxfId="0" priority="91">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110">
-    <cfRule type="duplicateValues" dxfId="1" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D110:E110">
-    <cfRule type="expression" dxfId="0" priority="83">
+    <cfRule type="expression" dxfId="0" priority="85">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I110">
-    <cfRule type="expression" dxfId="0" priority="85">
+    <cfRule type="expression" dxfId="0" priority="87">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A111">
-    <cfRule type="duplicateValues" dxfId="1" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D111:E111">
-    <cfRule type="expression" dxfId="0" priority="79">
+    <cfRule type="expression" dxfId="0" priority="81">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I111">
-    <cfRule type="expression" dxfId="0" priority="81">
+    <cfRule type="expression" dxfId="0" priority="83">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112">
-    <cfRule type="duplicateValues" dxfId="1" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D112:E112">
-    <cfRule type="expression" dxfId="0" priority="75">
+    <cfRule type="expression" dxfId="0" priority="77">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I112">
-    <cfRule type="expression" dxfId="0" priority="77">
+    <cfRule type="expression" dxfId="0" priority="79">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A113">
-    <cfRule type="duplicateValues" dxfId="1" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D113:E113">
-    <cfRule type="expression" dxfId="0" priority="71">
+    <cfRule type="expression" dxfId="0" priority="73">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I113">
-    <cfRule type="expression" dxfId="0" priority="73">
+    <cfRule type="expression" dxfId="0" priority="75">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114">
-    <cfRule type="duplicateValues" dxfId="1" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D114:E114">
-    <cfRule type="expression" dxfId="0" priority="67">
+    <cfRule type="expression" dxfId="0" priority="69">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I114">
-    <cfRule type="expression" dxfId="0" priority="69">
+    <cfRule type="expression" dxfId="0" priority="71">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A115">
-    <cfRule type="duplicateValues" dxfId="1" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D115:E115">
-    <cfRule type="expression" dxfId="0" priority="63">
+    <cfRule type="expression" dxfId="0" priority="65">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I115">
-    <cfRule type="expression" dxfId="0" priority="65">
+    <cfRule type="expression" dxfId="0" priority="67">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A116">
-    <cfRule type="duplicateValues" dxfId="1" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D116:E116">
-    <cfRule type="expression" dxfId="0" priority="59">
+    <cfRule type="expression" dxfId="0" priority="61">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I116">
-    <cfRule type="expression" dxfId="0" priority="61">
+    <cfRule type="expression" dxfId="0" priority="63">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117">
-    <cfRule type="duplicateValues" dxfId="1" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D117:E117">
-    <cfRule type="expression" dxfId="0" priority="55">
+    <cfRule type="expression" dxfId="0" priority="57">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I117">
-    <cfRule type="expression" dxfId="0" priority="57">
+    <cfRule type="expression" dxfId="0" priority="59">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A118">
-    <cfRule type="duplicateValues" dxfId="1" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D118:E118">
-    <cfRule type="expression" dxfId="0" priority="51">
+    <cfRule type="expression" dxfId="0" priority="53">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I118">
-    <cfRule type="expression" dxfId="0" priority="53">
+    <cfRule type="expression" dxfId="0" priority="55">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A119">
-    <cfRule type="duplicateValues" dxfId="1" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D119:E119">
-    <cfRule type="expression" dxfId="0" priority="47">
+    <cfRule type="expression" dxfId="0" priority="49">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I119">
-    <cfRule type="expression" dxfId="0" priority="49">
+    <cfRule type="expression" dxfId="0" priority="51">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A120">
-    <cfRule type="duplicateValues" dxfId="1" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D120:E120">
-    <cfRule type="expression" dxfId="0" priority="43">
+    <cfRule type="expression" dxfId="0" priority="45">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I120">
-    <cfRule type="expression" dxfId="0" priority="45">
+    <cfRule type="expression" dxfId="0" priority="47">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A121">
-    <cfRule type="duplicateValues" dxfId="1" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D121:E121">
-    <cfRule type="expression" dxfId="0" priority="39">
+    <cfRule type="expression" dxfId="0" priority="41">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I121">
-    <cfRule type="expression" dxfId="0" priority="41">
+    <cfRule type="expression" dxfId="0" priority="43">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A122">
-    <cfRule type="duplicateValues" dxfId="1" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D122:E122">
-    <cfRule type="expression" dxfId="0" priority="35">
+    <cfRule type="expression" dxfId="0" priority="37">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I122">
-    <cfRule type="expression" dxfId="0" priority="37">
+    <cfRule type="expression" dxfId="0" priority="39">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A123">
-    <cfRule type="duplicateValues" dxfId="1" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D123:E123">
-    <cfRule type="expression" dxfId="0" priority="31">
+    <cfRule type="expression" dxfId="0" priority="33">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I123">
-    <cfRule type="expression" dxfId="0" priority="33">
+    <cfRule type="expression" dxfId="0" priority="35">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C134:L134">
-    <cfRule type="expression" dxfId="0" priority="159">
+    <cfRule type="expression" dxfId="0" priority="161">
       <formula>MOD($B134,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="expression" dxfId="0" priority="23">
+    <cfRule type="expression" dxfId="0" priority="25">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A178">
-    <cfRule type="duplicateValues" dxfId="1" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B178">
+    <cfRule type="expression" dxfId="0" priority="21">
+      <formula>MOD($B178,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D178:E178">
     <cfRule type="expression" dxfId="0" priority="19">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D178:E178">
-    <cfRule type="expression" dxfId="0" priority="17">
-      <formula>MOD($B178,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H309">
-    <cfRule type="expression" dxfId="0" priority="437">
+    <cfRule type="expression" dxfId="0" priority="439">
       <formula>MOD($B308,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H321">
-    <cfRule type="expression" dxfId="0" priority="436">
+    <cfRule type="expression" dxfId="0" priority="438">
       <formula>MOD($B320,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="L346">
+    <cfRule type="expression" dxfId="0" priority="440">
+      <formula>MOD($B350,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A48:A60">
-    <cfRule type="duplicateValues" dxfId="1" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A87:A92">
-    <cfRule type="duplicateValues" dxfId="1" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A93:A98">
-    <cfRule type="duplicateValues" dxfId="1" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99:A104">
-    <cfRule type="duplicateValues" dxfId="1" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A135:A177">
-    <cfRule type="duplicateValues" dxfId="1" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A209:A387">
-    <cfRule type="duplicateValues" dxfId="1" priority="13"/>
+  <conditionalFormatting sqref="A209:A425">
+    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B60">
-    <cfRule type="expression" dxfId="0" priority="118">
+    <cfRule type="expression" dxfId="0" priority="120">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C84">
-    <cfRule type="expression" dxfId="0" priority="121">
+    <cfRule type="expression" dxfId="0" priority="123">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C271:C281">
-    <cfRule type="expression" dxfId="0" priority="10">
+    <cfRule type="expression" dxfId="0" priority="12">
       <formula>MOD($B271,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C282:C296">
-    <cfRule type="expression" dxfId="0" priority="8">
+    <cfRule type="expression" dxfId="0" priority="10">
       <formula>MOD($B282,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E93:E98">
-    <cfRule type="expression" dxfId="0" priority="110">
+    <cfRule type="expression" dxfId="0" priority="112">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E99:E104">
-    <cfRule type="expression" dxfId="0" priority="107">
+    <cfRule type="expression" dxfId="0" priority="109">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E257:E268">
-    <cfRule type="expression" dxfId="0" priority="11">
+    <cfRule type="expression" dxfId="0" priority="13">
       <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E271:E279">
-    <cfRule type="expression" dxfId="0" priority="9">
+    <cfRule type="expression" dxfId="0" priority="11">
       <formula>MOD($B271,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E282:E290">
-    <cfRule type="expression" dxfId="0" priority="7">
+    <cfRule type="expression" dxfId="0" priority="9">
       <formula>MOD($B282,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39:K42">
-    <cfRule type="duplicateValues" dxfId="2" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K169:K172">
-    <cfRule type="duplicateValues" dxfId="2" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K293:K296">
-    <cfRule type="expression" dxfId="0" priority="5">
+    <cfRule type="expression" dxfId="0" priority="7">
       <formula>MOD($B293,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K346:K349">
-    <cfRule type="expression" dxfId="0" priority="3">
+  <conditionalFormatting sqref="K347:K350">
+    <cfRule type="expression" dxfId="0" priority="5">
       <formula>MOD($B346,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K384:K387">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>MOD($B384,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K422:K425">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD($B422,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L205:L208">
-    <cfRule type="expression" dxfId="0" priority="16">
+    <cfRule type="expression" dxfId="0" priority="18">
       <formula>MOD($B205,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L293:L296">
-    <cfRule type="expression" dxfId="0" priority="6">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>MOD($B293,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L346:L349">
-    <cfRule type="expression" dxfId="0" priority="4">
+  <conditionalFormatting sqref="L347:L350">
+    <cfRule type="expression" dxfId="0" priority="6">
       <formula>MOD($B346,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L384:L387">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>MOD($B384,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A388:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="433"/>
+  <conditionalFormatting sqref="L422:L425">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>MOD($B422,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A426:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="435"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L4">
-    <cfRule type="expression" dxfId="0" priority="432">
+    <cfRule type="expression" dxfId="0" priority="434">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41:B42 B44:B47">
-    <cfRule type="expression" dxfId="0" priority="166">
+    <cfRule type="expression" dxfId="0" priority="168">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 H179:L204 B179:G208 I205:K208 I209:I256 B259:D268 F259:L268 B269:L270 B271:B296 D271:D279 F271:L279 D280:L281 D282:D290 F282:L290 D291:L292 D293:J296 H297:L307 H310:L319 I320:L321 B322:L345 B297:G321 B258 B346:J349 B350:L383 B384:J387 B388:L1048576 I308:L309">
-    <cfRule type="expression" dxfId="0" priority="431">
+  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 H179:L204 B179:G208 I205:K208 I209:I256 B259:D268 F259:L268 B269:L270 B271:B296 D271:D279 F271:L279 D280:L281 D282:D290 F282:L290 D291:L292 D293:J296 H297:L307 H310:L319 I320:L321 B322:L343 B345:L345 B297:G321 B258 K351:L383 B346:J387 B388:L421 B422:J425 B426:L1048576 I308:L309 B344:K344">
+    <cfRule type="expression" dxfId="0" priority="433">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43:G43 J43:L43">
-    <cfRule type="expression" dxfId="0" priority="131">
+    <cfRule type="expression" dxfId="0" priority="133">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44:G44 J44:L47 G45:G47 C45:C47">
-    <cfRule type="expression" dxfId="0" priority="165">
+    <cfRule type="expression" dxfId="0" priority="167">
       <formula>MOD($B44,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45:E47">
-    <cfRule type="expression" dxfId="0" priority="162">
+    <cfRule type="expression" dxfId="0" priority="164">
       <formula>MOD($B45,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F60 C48:C60">
+    <cfRule type="expression" dxfId="0" priority="121">
+      <formula>MOD($B48,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
     <cfRule type="expression" dxfId="0" priority="119">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
+  <conditionalFormatting sqref="D48:E60">
     <cfRule type="expression" dxfId="0" priority="117">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D48:E60">
-    <cfRule type="expression" dxfId="0" priority="115">
-      <formula>MOD($B48,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B77:B84 F77:L84">
-    <cfRule type="expression" dxfId="0" priority="161">
+    <cfRule type="expression" dxfId="0" priority="163">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85:C85 F85:L85">
-    <cfRule type="expression" dxfId="0" priority="157">
+    <cfRule type="expression" dxfId="0" priority="159">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B86:C86 F86:L86">
-    <cfRule type="expression" dxfId="0" priority="122">
+    <cfRule type="expression" dxfId="0" priority="124">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87:C92 F87:L92 I93:I104">
-    <cfRule type="expression" dxfId="0" priority="112">
+    <cfRule type="expression" dxfId="0" priority="114">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87:E92 D93:D104">
-    <cfRule type="expression" dxfId="0" priority="113">
+    <cfRule type="expression" dxfId="0" priority="115">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:C98 F93:H98 J93:L98">
-    <cfRule type="expression" dxfId="0" priority="109">
+    <cfRule type="expression" dxfId="0" priority="111">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99:C104 F99:H104 J99:L104">
-    <cfRule type="expression" dxfId="0" priority="106">
+    <cfRule type="expression" dxfId="0" priority="108">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:C105 F105:H105 J105:L105">
-    <cfRule type="expression" dxfId="0" priority="102">
+    <cfRule type="expression" dxfId="0" priority="104">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106:C106 F106:H106 J106:L106 H107:H111 C107:C111">
-    <cfRule type="expression" dxfId="0" priority="98">
+    <cfRule type="expression" dxfId="0" priority="100">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107 F107:G107 J107:L107">
-    <cfRule type="expression" dxfId="0" priority="94">
+    <cfRule type="expression" dxfId="0" priority="96">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B108 F108:G108 J108:L108">
-    <cfRule type="expression" dxfId="0" priority="90">
+    <cfRule type="expression" dxfId="0" priority="92">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B109 F109:G109 J109:L109">
-    <cfRule type="expression" dxfId="0" priority="86">
+    <cfRule type="expression" dxfId="0" priority="88">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B110 F110:G110 J110:L110">
-    <cfRule type="expression" dxfId="0" priority="82">
+    <cfRule type="expression" dxfId="0" priority="84">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111 F111:G111 J111:L111">
-    <cfRule type="expression" dxfId="0" priority="78">
+    <cfRule type="expression" dxfId="0" priority="80">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112:C112 F112:H112 J112:L112 H113:H117 C113:C117">
-    <cfRule type="expression" dxfId="0" priority="74">
+    <cfRule type="expression" dxfId="0" priority="76">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113 F113:G113 J113:L113">
-    <cfRule type="expression" dxfId="0" priority="70">
+    <cfRule type="expression" dxfId="0" priority="72">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114 F114:G114 J114:L114">
-    <cfRule type="expression" dxfId="0" priority="66">
+    <cfRule type="expression" dxfId="0" priority="68">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115 F115:G115 J115:L115">
-    <cfRule type="expression" dxfId="0" priority="62">
+    <cfRule type="expression" dxfId="0" priority="64">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B116 F116:G116 J116:L116">
-    <cfRule type="expression" dxfId="0" priority="58">
+    <cfRule type="expression" dxfId="0" priority="60">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117 F117:G117 J117:L117">
-    <cfRule type="expression" dxfId="0" priority="54">
+    <cfRule type="expression" dxfId="0" priority="56">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118:C118 F118:H118 J118:L118 H119:H123 C119:C123">
-    <cfRule type="expression" dxfId="0" priority="50">
+    <cfRule type="expression" dxfId="0" priority="52">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119 F119:G119 J119:L119">
-    <cfRule type="expression" dxfId="0" priority="46">
+    <cfRule type="expression" dxfId="0" priority="48">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120 F120:G120 J120:L120">
-    <cfRule type="expression" dxfId="0" priority="42">
+    <cfRule type="expression" dxfId="0" priority="44">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121 F121:G121 J121:L121">
-    <cfRule type="expression" dxfId="0" priority="38">
+    <cfRule type="expression" dxfId="0" priority="40">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122 F122:G122 J122:L122">
-    <cfRule type="expression" dxfId="0" priority="34">
+    <cfRule type="expression" dxfId="0" priority="36">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123 F123:G123 J123:L123">
-    <cfRule type="expression" dxfId="0" priority="30">
+    <cfRule type="expression" dxfId="0" priority="32">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B124:L133 B134">
-    <cfRule type="expression" dxfId="0" priority="160">
+    <cfRule type="expression" dxfId="0" priority="162">
       <formula>MOD($B124,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171:B172 B174:B177">
-    <cfRule type="expression" dxfId="0" priority="27">
+    <cfRule type="expression" dxfId="0" priority="29">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171:G172 J171:J172 L171:L172 F175:F177 C176:C177">
-    <cfRule type="expression" dxfId="0" priority="28">
+    <cfRule type="expression" dxfId="0" priority="30">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173:G173 J173:L173">
-    <cfRule type="expression" dxfId="0" priority="22">
+    <cfRule type="expression" dxfId="0" priority="24">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174:G174 J174:L177 G175:G177 C175:C177">
-    <cfRule type="expression" dxfId="0" priority="26">
+    <cfRule type="expression" dxfId="0" priority="28">
       <formula>MOD($B174,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D175:E177">
-    <cfRule type="expression" dxfId="0" priority="25">
+    <cfRule type="expression" dxfId="0" priority="27">
       <formula>MOD($B175,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F178 C178">
+    <cfRule type="expression" dxfId="0" priority="22">
+      <formula>MOD($B178,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J178:L178 G178 C178">
     <cfRule type="expression" dxfId="0" priority="20">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J178:L178 G178 C178">
-    <cfRule type="expression" dxfId="0" priority="18">
-      <formula>MOD($B178,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B209:D209 F209:H209 J209:L250 B210:H250">
-    <cfRule type="expression" dxfId="0" priority="15">
+    <cfRule type="expression" dxfId="0" priority="17">
       <formula>MOD($B209,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B251:H256 J251:L256">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="0" priority="16">
       <formula>MOD($B251,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B257 B259 B261 B263 B265 B267 B269 B271 B273 B275 B277 B279 B281 B283 B285 B287 B289 B291 B293 B295">
-    <cfRule type="expression" dxfId="0" priority="12">
+    <cfRule type="expression" dxfId="0" priority="14">
       <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C257:D257 F257:L257">
-    <cfRule type="expression" dxfId="0" priority="435">
+    <cfRule type="expression" dxfId="0" priority="437">
       <formula>MOD($B258,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C258:D258 I292 I290 I288 I286 I284 I282 I280 I278 I276 I274 I272 I270 I268 I266 I264 I262 I260 D268 D266 D264 D262 D260 F258:L258">
-    <cfRule type="expression" dxfId="0" priority="434">
+    <cfRule type="expression" dxfId="0" priority="436">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -765,12 +765,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -17457,6 +17457,9 @@
       <c r="G398" s="11">
         <v>0</v>
       </c>
+      <c r="H398" s="11">
+        <v>30230001</v>
+      </c>
       <c r="I398" s="11">
         <v>0</v>
       </c>
@@ -17721,6 +17724,9 @@
       <c r="G409" s="11">
         <v>0</v>
       </c>
+      <c r="H409" s="11">
+        <v>30230002</v>
+      </c>
       <c r="I409" s="11">
         <v>0</v>
       </c>
@@ -17984,6 +17990,9 @@
       </c>
       <c r="G420" s="11">
         <v>0</v>
+      </c>
+      <c r="H420" s="11">
+        <v>30230003</v>
       </c>
       <c r="I420" s="11">
         <v>0</v>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -765,23 +765,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5821,7 +5821,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L425"/>
+  <dimension ref="A1:L432"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="10"/>
@@ -18140,6 +18140,174 @@
       </c>
       <c r="L425" s="13" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="426" customHeight="1" spans="1:12">
+      <c r="A426" s="3">
+        <f>(B426)*10000+C426+F426*100+D426*100000</f>
+        <v>1034100301</v>
+      </c>
+      <c r="B426" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C426" s="2">
+        <v>1</v>
+      </c>
+      <c r="D426" s="2">
+        <v>1</v>
+      </c>
+      <c r="F426" s="2">
+        <v>3</v>
+      </c>
+      <c r="G426" s="11">
+        <v>3</v>
+      </c>
+      <c r="I426" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" customHeight="1" spans="1:12">
+      <c r="A427" s="3">
+        <f t="shared" ref="A427:A432" si="17">(B427)*10000+C427+F427*100+D427*100000</f>
+        <v>1034100302</v>
+      </c>
+      <c r="B427" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C427" s="2">
+        <v>2</v>
+      </c>
+      <c r="D427" s="2">
+        <v>1</v>
+      </c>
+      <c r="F427" s="2">
+        <v>3</v>
+      </c>
+      <c r="G427" s="11">
+        <v>5</v>
+      </c>
+      <c r="I427" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" customHeight="1" spans="1:12">
+      <c r="A428" s="3">
+        <f t="shared" si="17"/>
+        <v>1034100303</v>
+      </c>
+      <c r="B428" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C428" s="2">
+        <v>3</v>
+      </c>
+      <c r="D428" s="2">
+        <v>1</v>
+      </c>
+      <c r="F428" s="2">
+        <v>3</v>
+      </c>
+      <c r="G428" s="11">
+        <v>8</v>
+      </c>
+      <c r="I428" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" customHeight="1" spans="1:12">
+      <c r="A429" s="3">
+        <f t="shared" si="17"/>
+        <v>1034100304</v>
+      </c>
+      <c r="B429" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C429" s="2">
+        <v>4</v>
+      </c>
+      <c r="D429" s="2">
+        <v>1</v>
+      </c>
+      <c r="F429" s="2">
+        <v>3</v>
+      </c>
+      <c r="G429" s="11">
+        <v>10</v>
+      </c>
+      <c r="I429" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" customHeight="1" spans="1:12">
+      <c r="A430" s="3">
+        <f t="shared" si="17"/>
+        <v>1034100305</v>
+      </c>
+      <c r="B430" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C430" s="2">
+        <v>5</v>
+      </c>
+      <c r="D430" s="2">
+        <v>1</v>
+      </c>
+      <c r="F430" s="2">
+        <v>3</v>
+      </c>
+      <c r="G430" s="11">
+        <v>25</v>
+      </c>
+      <c r="I430" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" customHeight="1" spans="1:12">
+      <c r="A431" s="3">
+        <f t="shared" si="17"/>
+        <v>1034100306</v>
+      </c>
+      <c r="B431" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C431" s="2">
+        <v>6</v>
+      </c>
+      <c r="D431" s="2">
+        <v>1</v>
+      </c>
+      <c r="F431" s="2">
+        <v>3</v>
+      </c>
+      <c r="G431" s="11">
+        <v>100</v>
+      </c>
+      <c r="I431" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" customHeight="1" spans="1:12">
+      <c r="A432" s="3">
+        <f t="shared" si="17"/>
+        <v>1034100307</v>
+      </c>
+      <c r="B432" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C432" s="2">
+        <v>7</v>
+      </c>
+      <c r="D432" s="2">
+        <v>1</v>
+      </c>
+      <c r="F432" s="2">
+        <v>3</v>
+      </c>
+      <c r="G432" s="11">
+        <v>250</v>
+      </c>
+      <c r="I432" s="11">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -18461,7 +18629,7 @@
   <conditionalFormatting sqref="A135:A177">
     <cfRule type="duplicateValues" dxfId="1" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A209:A425">
+  <conditionalFormatting sqref="A209:A432">
     <cfRule type="duplicateValues" dxfId="1" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B60">
@@ -18560,7 +18728,7 @@
       <formula>MOD($B422,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A426:A1048576">
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A433:A1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="435"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L4">

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="71">
   <si>
     <t>id</t>
   </si>
@@ -776,12 +776,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5821,7 +5821,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L387"/>
+  <dimension ref="A1:L425"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="10"/>
@@ -17197,649 +17197,1595 @@
         <v>68</v>
       </c>
     </row>
+    <row r="388" customHeight="1" spans="1:12">
+      <c r="A388" s="3">
+        <f t="shared" ref="A388:A398" si="15">(B388)*10000+C388+F388*100+D388*100000</f>
+        <v>1023300301</v>
+      </c>
+      <c r="B388" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C388" s="2">
+        <v>1</v>
+      </c>
+      <c r="D388" s="2">
+        <v>3</v>
+      </c>
+      <c r="F388" s="2">
+        <v>3</v>
+      </c>
+      <c r="G388" s="11">
+        <v>2</v>
+      </c>
+      <c r="I388" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" customHeight="1" spans="1:12">
+      <c r="A389" s="3">
+        <f t="shared" si="15"/>
+        <v>1023300302</v>
+      </c>
+      <c r="B389" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C389" s="2">
+        <v>2</v>
+      </c>
+      <c r="D389" s="2">
+        <v>3</v>
+      </c>
+      <c r="F389" s="2">
+        <v>3</v>
+      </c>
+      <c r="G389" s="11">
+        <v>2</v>
+      </c>
+      <c r="I389" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" customHeight="1" spans="1:12">
+      <c r="A390" s="3">
+        <f t="shared" si="15"/>
+        <v>1023300303</v>
+      </c>
+      <c r="B390" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C390" s="2">
+        <v>3</v>
+      </c>
+      <c r="D390" s="2">
+        <v>3</v>
+      </c>
+      <c r="F390" s="2">
+        <v>3</v>
+      </c>
+      <c r="G390" s="11">
+        <v>2</v>
+      </c>
+      <c r="I390" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" customHeight="1" spans="1:12">
+      <c r="A391" s="3">
+        <f t="shared" si="15"/>
+        <v>1023300304</v>
+      </c>
+      <c r="B391" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C391" s="2">
+        <v>4</v>
+      </c>
+      <c r="D391" s="2">
+        <v>3</v>
+      </c>
+      <c r="F391" s="2">
+        <v>3</v>
+      </c>
+      <c r="G391" s="11">
+        <v>3</v>
+      </c>
+      <c r="I391" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" customHeight="1" spans="1:12">
+      <c r="A392" s="3">
+        <f t="shared" si="15"/>
+        <v>1023300305</v>
+      </c>
+      <c r="B392" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C392" s="2">
+        <v>5</v>
+      </c>
+      <c r="D392" s="2">
+        <v>3</v>
+      </c>
+      <c r="F392" s="2">
+        <v>3</v>
+      </c>
+      <c r="G392" s="11">
+        <v>3</v>
+      </c>
+      <c r="I392" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" customHeight="1" spans="1:12">
+      <c r="A393" s="3">
+        <f t="shared" si="15"/>
+        <v>1023300306</v>
+      </c>
+      <c r="B393" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C393" s="2">
+        <v>6</v>
+      </c>
+      <c r="D393" s="2">
+        <v>3</v>
+      </c>
+      <c r="F393" s="2">
+        <v>3</v>
+      </c>
+      <c r="G393" s="11">
+        <v>4</v>
+      </c>
+      <c r="I393" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" customHeight="1" spans="1:12">
+      <c r="A394" s="3">
+        <f t="shared" si="15"/>
+        <v>1023300307</v>
+      </c>
+      <c r="B394" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C394" s="2">
+        <v>7</v>
+      </c>
+      <c r="D394" s="2">
+        <v>3</v>
+      </c>
+      <c r="F394" s="2">
+        <v>3</v>
+      </c>
+      <c r="G394" s="11">
+        <v>4</v>
+      </c>
+      <c r="I394" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" customHeight="1" spans="1:12">
+      <c r="A395" s="3">
+        <f t="shared" si="15"/>
+        <v>1023300308</v>
+      </c>
+      <c r="B395" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C395" s="2">
+        <v>8</v>
+      </c>
+      <c r="D395" s="2">
+        <v>3</v>
+      </c>
+      <c r="F395" s="2">
+        <v>3</v>
+      </c>
+      <c r="G395" s="11">
+        <v>5</v>
+      </c>
+      <c r="I395" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" customHeight="1" spans="1:12">
+      <c r="A396" s="3">
+        <f t="shared" si="15"/>
+        <v>1023300309</v>
+      </c>
+      <c r="B396" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C396" s="2">
+        <v>9</v>
+      </c>
+      <c r="D396" s="2">
+        <v>3</v>
+      </c>
+      <c r="F396" s="2">
+        <v>3</v>
+      </c>
+      <c r="G396" s="11">
+        <v>5</v>
+      </c>
+      <c r="I396" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" customHeight="1" spans="1:12">
+      <c r="A397" s="3">
+        <f t="shared" si="15"/>
+        <v>1023300310</v>
+      </c>
+      <c r="B397" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C397" s="2">
+        <v>10</v>
+      </c>
+      <c r="D397" s="2">
+        <v>3</v>
+      </c>
+      <c r="F397" s="2">
+        <v>3</v>
+      </c>
+      <c r="G397" s="11">
+        <v>10</v>
+      </c>
+      <c r="I397" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" customHeight="1" spans="1:12">
+      <c r="A398" s="3">
+        <f t="shared" si="15"/>
+        <v>1023400311</v>
+      </c>
+      <c r="B398" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C398" s="2">
+        <v>11</v>
+      </c>
+      <c r="D398" s="2">
+        <v>4</v>
+      </c>
+      <c r="F398" s="2">
+        <v>3</v>
+      </c>
+      <c r="G398" s="11">
+        <v>0</v>
+      </c>
+      <c r="I398" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" customHeight="1" spans="1:12">
+      <c r="A399" s="3">
+        <f t="shared" ref="A399:A420" si="16">(B399)*10000+C399+F399*100+D399*100000</f>
+        <v>1023300401</v>
+      </c>
+      <c r="B399" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C399" s="2">
+        <v>1</v>
+      </c>
+      <c r="D399" s="2">
+        <v>3</v>
+      </c>
+      <c r="F399" s="2">
+        <v>4</v>
+      </c>
+      <c r="G399" s="11">
+        <v>5</v>
+      </c>
+      <c r="I399" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" customHeight="1" spans="1:12">
+      <c r="A400" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300402</v>
+      </c>
+      <c r="B400" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C400" s="2">
+        <v>2</v>
+      </c>
+      <c r="D400" s="2">
+        <v>3</v>
+      </c>
+      <c r="F400" s="2">
+        <v>4</v>
+      </c>
+      <c r="G400" s="11">
+        <v>5</v>
+      </c>
+      <c r="I400" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" customHeight="1" spans="1:9">
+      <c r="A401" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300403</v>
+      </c>
+      <c r="B401" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C401" s="2">
+        <v>3</v>
+      </c>
+      <c r="D401" s="2">
+        <v>3</v>
+      </c>
+      <c r="F401" s="2">
+        <v>4</v>
+      </c>
+      <c r="G401" s="11">
+        <v>5</v>
+      </c>
+      <c r="I401" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" customHeight="1" spans="1:9">
+      <c r="A402" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300404</v>
+      </c>
+      <c r="B402" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C402" s="2">
+        <v>4</v>
+      </c>
+      <c r="D402" s="2">
+        <v>3</v>
+      </c>
+      <c r="F402" s="2">
+        <v>4</v>
+      </c>
+      <c r="G402" s="11">
+        <v>10</v>
+      </c>
+      <c r="I402" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" customHeight="1" spans="1:9">
+      <c r="A403" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300405</v>
+      </c>
+      <c r="B403" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C403" s="2">
+        <v>5</v>
+      </c>
+      <c r="D403" s="2">
+        <v>3</v>
+      </c>
+      <c r="F403" s="2">
+        <v>4</v>
+      </c>
+      <c r="G403" s="11">
+        <v>10</v>
+      </c>
+      <c r="I403" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" customHeight="1" spans="1:9">
+      <c r="A404" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300406</v>
+      </c>
+      <c r="B404" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C404" s="2">
+        <v>6</v>
+      </c>
+      <c r="D404" s="2">
+        <v>3</v>
+      </c>
+      <c r="F404" s="2">
+        <v>4</v>
+      </c>
+      <c r="G404" s="11">
+        <v>15</v>
+      </c>
+      <c r="I404" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" customHeight="1" spans="1:9">
+      <c r="A405" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300407</v>
+      </c>
+      <c r="B405" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C405" s="2">
+        <v>7</v>
+      </c>
+      <c r="D405" s="2">
+        <v>3</v>
+      </c>
+      <c r="F405" s="2">
+        <v>4</v>
+      </c>
+      <c r="G405" s="11">
+        <v>20</v>
+      </c>
+      <c r="I405" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" customHeight="1" spans="1:9">
+      <c r="A406" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300408</v>
+      </c>
+      <c r="B406" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C406" s="2">
+        <v>8</v>
+      </c>
+      <c r="D406" s="2">
+        <v>3</v>
+      </c>
+      <c r="F406" s="2">
+        <v>4</v>
+      </c>
+      <c r="G406" s="11">
+        <v>25</v>
+      </c>
+      <c r="I406" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" customHeight="1" spans="1:9">
+      <c r="A407" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300409</v>
+      </c>
+      <c r="B407" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C407" s="2">
+        <v>9</v>
+      </c>
+      <c r="D407" s="2">
+        <v>3</v>
+      </c>
+      <c r="F407" s="2">
+        <v>4</v>
+      </c>
+      <c r="G407" s="11">
+        <v>30</v>
+      </c>
+      <c r="I407" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" customHeight="1" spans="1:9">
+      <c r="A408" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300410</v>
+      </c>
+      <c r="B408" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C408" s="2">
+        <v>10</v>
+      </c>
+      <c r="D408" s="2">
+        <v>3</v>
+      </c>
+      <c r="F408" s="2">
+        <v>4</v>
+      </c>
+      <c r="G408" s="11">
+        <v>50</v>
+      </c>
+      <c r="I408" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" customHeight="1" spans="1:9">
+      <c r="A409" s="3">
+        <f t="shared" si="16"/>
+        <v>1023400411</v>
+      </c>
+      <c r="B409" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C409" s="2">
+        <v>11</v>
+      </c>
+      <c r="D409" s="2">
+        <v>4</v>
+      </c>
+      <c r="F409" s="2">
+        <v>4</v>
+      </c>
+      <c r="G409" s="11">
+        <v>0</v>
+      </c>
+      <c r="I409" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" customHeight="1" spans="1:9">
+      <c r="A410" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300501</v>
+      </c>
+      <c r="B410" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C410" s="2">
+        <v>1</v>
+      </c>
+      <c r="D410" s="2">
+        <v>3</v>
+      </c>
+      <c r="F410" s="2">
+        <v>5</v>
+      </c>
+      <c r="G410" s="11">
+        <v>10</v>
+      </c>
+      <c r="I410" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" customHeight="1" spans="1:9">
+      <c r="A411" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300502</v>
+      </c>
+      <c r="B411" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C411" s="2">
+        <v>2</v>
+      </c>
+      <c r="D411" s="2">
+        <v>3</v>
+      </c>
+      <c r="F411" s="2">
+        <v>5</v>
+      </c>
+      <c r="G411" s="11">
+        <v>10</v>
+      </c>
+      <c r="I411" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" customHeight="1" spans="1:9">
+      <c r="A412" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300503</v>
+      </c>
+      <c r="B412" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C412" s="2">
+        <v>3</v>
+      </c>
+      <c r="D412" s="2">
+        <v>3</v>
+      </c>
+      <c r="F412" s="2">
+        <v>5</v>
+      </c>
+      <c r="G412" s="11">
+        <v>10</v>
+      </c>
+      <c r="I412" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" customHeight="1" spans="1:9">
+      <c r="A413" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300504</v>
+      </c>
+      <c r="B413" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C413" s="2">
+        <v>4</v>
+      </c>
+      <c r="D413" s="2">
+        <v>3</v>
+      </c>
+      <c r="F413" s="2">
+        <v>5</v>
+      </c>
+      <c r="G413" s="11">
+        <v>20</v>
+      </c>
+      <c r="I413" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" customHeight="1" spans="1:9">
+      <c r="A414" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300505</v>
+      </c>
+      <c r="B414" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C414" s="2">
+        <v>5</v>
+      </c>
+      <c r="D414" s="2">
+        <v>3</v>
+      </c>
+      <c r="F414" s="2">
+        <v>5</v>
+      </c>
+      <c r="G414" s="11">
+        <v>20</v>
+      </c>
+      <c r="I414" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" customHeight="1" spans="1:9">
+      <c r="A415" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300506</v>
+      </c>
+      <c r="B415" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C415" s="2">
+        <v>6</v>
+      </c>
+      <c r="D415" s="2">
+        <v>3</v>
+      </c>
+      <c r="F415" s="2">
+        <v>5</v>
+      </c>
+      <c r="G415" s="11">
+        <v>30</v>
+      </c>
+      <c r="I415" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" customHeight="1" spans="1:9">
+      <c r="A416" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300507</v>
+      </c>
+      <c r="B416" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C416" s="2">
+        <v>7</v>
+      </c>
+      <c r="D416" s="2">
+        <v>3</v>
+      </c>
+      <c r="F416" s="2">
+        <v>5</v>
+      </c>
+      <c r="G416" s="11">
+        <v>40</v>
+      </c>
+      <c r="I416" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" customHeight="1" spans="1:12">
+      <c r="A417" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300508</v>
+      </c>
+      <c r="B417" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C417" s="2">
+        <v>8</v>
+      </c>
+      <c r="D417" s="2">
+        <v>3</v>
+      </c>
+      <c r="F417" s="2">
+        <v>5</v>
+      </c>
+      <c r="G417" s="11">
+        <v>50</v>
+      </c>
+      <c r="I417" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" customHeight="1" spans="1:12">
+      <c r="A418" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300509</v>
+      </c>
+      <c r="B418" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C418" s="2">
+        <v>9</v>
+      </c>
+      <c r="D418" s="2">
+        <v>3</v>
+      </c>
+      <c r="F418" s="2">
+        <v>5</v>
+      </c>
+      <c r="G418" s="11">
+        <v>60</v>
+      </c>
+      <c r="I418" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" customHeight="1" spans="1:12">
+      <c r="A419" s="3">
+        <f t="shared" si="16"/>
+        <v>1023300510</v>
+      </c>
+      <c r="B419" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C419" s="2">
+        <v>10</v>
+      </c>
+      <c r="D419" s="2">
+        <v>3</v>
+      </c>
+      <c r="F419" s="2">
+        <v>5</v>
+      </c>
+      <c r="G419" s="11">
+        <v>100</v>
+      </c>
+      <c r="I419" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" customHeight="1" spans="1:12">
+      <c r="A420" s="3">
+        <f t="shared" si="16"/>
+        <v>1023400511</v>
+      </c>
+      <c r="B420" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C420" s="2">
+        <v>11</v>
+      </c>
+      <c r="D420" s="2">
+        <v>4</v>
+      </c>
+      <c r="F420" s="2">
+        <v>5</v>
+      </c>
+      <c r="G420" s="11">
+        <v>0</v>
+      </c>
+      <c r="I420" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" customHeight="1" spans="1:12">
+      <c r="A421" s="3">
+        <f>(B421)*10000+C421+F421*100+D421*100000</f>
+        <v>1023400112</v>
+      </c>
+      <c r="B421" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C421" s="2">
+        <v>12</v>
+      </c>
+      <c r="D421" s="2">
+        <v>4</v>
+      </c>
+      <c r="F421" s="2">
+        <v>1</v>
+      </c>
+      <c r="G421" s="11">
+        <v>0</v>
+      </c>
+      <c r="I421" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" customHeight="1" spans="1:12">
+      <c r="A422" s="3">
+        <f>(B422)*10000+C422+F422*100+D422*100000</f>
+        <v>1023400113</v>
+      </c>
+      <c r="B422" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C422" s="2">
+        <v>13</v>
+      </c>
+      <c r="D422" s="2">
+        <v>4</v>
+      </c>
+      <c r="F422" s="2">
+        <v>1</v>
+      </c>
+      <c r="G422" s="11">
+        <v>0</v>
+      </c>
+      <c r="I422" s="11">
+        <v>0</v>
+      </c>
+      <c r="K422" s="2">
+        <v>102300101</v>
+      </c>
+      <c r="L422" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="423" customHeight="1" spans="1:12">
+      <c r="A423" s="3">
+        <f>(B423)*10000+C423+F423*100+D423*100000</f>
+        <v>1023400114</v>
+      </c>
+      <c r="B423" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C423" s="2">
+        <v>14</v>
+      </c>
+      <c r="D423" s="2">
+        <v>4</v>
+      </c>
+      <c r="F423" s="2">
+        <v>1</v>
+      </c>
+      <c r="G423" s="11">
+        <v>0</v>
+      </c>
+      <c r="I423" s="11">
+        <v>0</v>
+      </c>
+      <c r="K423" s="2">
+        <v>102300102</v>
+      </c>
+      <c r="L423" s="13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="424" customHeight="1" spans="1:12">
+      <c r="A424" s="3">
+        <f>(B424)*10000+C424+F424*100+D424*100000</f>
+        <v>1023400115</v>
+      </c>
+      <c r="B424" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C424" s="2">
+        <v>15</v>
+      </c>
+      <c r="D424" s="2">
+        <v>4</v>
+      </c>
+      <c r="F424" s="2">
+        <v>1</v>
+      </c>
+      <c r="G424" s="11">
+        <v>0</v>
+      </c>
+      <c r="I424" s="11">
+        <v>0</v>
+      </c>
+      <c r="K424" s="2">
+        <v>102300103</v>
+      </c>
+      <c r="L424" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="425" customHeight="1" spans="1:12">
+      <c r="A425" s="3">
+        <f>(B425)*10000+C425+F425*100+D425*100000</f>
+        <v>1023400116</v>
+      </c>
+      <c r="B425" s="2">
+        <v>102300</v>
+      </c>
+      <c r="C425" s="2">
+        <v>16</v>
+      </c>
+      <c r="D425" s="2">
+        <v>4</v>
+      </c>
+      <c r="F425" s="2">
+        <v>1</v>
+      </c>
+      <c r="G425" s="11">
+        <v>0</v>
+      </c>
+      <c r="I425" s="11">
+        <v>0</v>
+      </c>
+      <c r="K425" s="2">
+        <v>102300104</v>
+      </c>
+      <c r="L425" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L387" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="0" priority="132">
+    <cfRule type="expression" dxfId="0" priority="134">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D85:E85">
-    <cfRule type="expression" dxfId="0" priority="158">
+    <cfRule type="expression" dxfId="0" priority="160">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D86:E86">
-    <cfRule type="expression" dxfId="0" priority="123">
+    <cfRule type="expression" dxfId="0" priority="125">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105">
-    <cfRule type="duplicateValues" dxfId="1" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105:E105">
-    <cfRule type="expression" dxfId="0" priority="103">
+    <cfRule type="expression" dxfId="0" priority="105">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I105">
-    <cfRule type="expression" dxfId="0" priority="105">
+    <cfRule type="expression" dxfId="0" priority="107">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A106">
-    <cfRule type="duplicateValues" dxfId="1" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D106:E106">
-    <cfRule type="expression" dxfId="0" priority="99">
+    <cfRule type="expression" dxfId="0" priority="101">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I106">
-    <cfRule type="expression" dxfId="0" priority="101">
+    <cfRule type="expression" dxfId="0" priority="103">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="1" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D107:E107">
-    <cfRule type="expression" dxfId="0" priority="95">
+    <cfRule type="expression" dxfId="0" priority="97">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I107">
-    <cfRule type="expression" dxfId="0" priority="97">
+    <cfRule type="expression" dxfId="0" priority="99">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108">
-    <cfRule type="duplicateValues" dxfId="1" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D108:E108">
-    <cfRule type="expression" dxfId="0" priority="91">
+    <cfRule type="expression" dxfId="0" priority="93">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I108">
-    <cfRule type="expression" dxfId="0" priority="93">
+    <cfRule type="expression" dxfId="0" priority="95">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" dxfId="1" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D109:E109">
-    <cfRule type="expression" dxfId="0" priority="87">
+    <cfRule type="expression" dxfId="0" priority="89">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I109">
-    <cfRule type="expression" dxfId="0" priority="89">
+    <cfRule type="expression" dxfId="0" priority="91">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110">
-    <cfRule type="duplicateValues" dxfId="1" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D110:E110">
-    <cfRule type="expression" dxfId="0" priority="83">
+    <cfRule type="expression" dxfId="0" priority="85">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I110">
-    <cfRule type="expression" dxfId="0" priority="85">
+    <cfRule type="expression" dxfId="0" priority="87">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A111">
-    <cfRule type="duplicateValues" dxfId="1" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D111:E111">
-    <cfRule type="expression" dxfId="0" priority="79">
+    <cfRule type="expression" dxfId="0" priority="81">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I111">
-    <cfRule type="expression" dxfId="0" priority="81">
+    <cfRule type="expression" dxfId="0" priority="83">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112">
-    <cfRule type="duplicateValues" dxfId="1" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D112:E112">
-    <cfRule type="expression" dxfId="0" priority="75">
+    <cfRule type="expression" dxfId="0" priority="77">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I112">
-    <cfRule type="expression" dxfId="0" priority="77">
+    <cfRule type="expression" dxfId="0" priority="79">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A113">
-    <cfRule type="duplicateValues" dxfId="1" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D113:E113">
-    <cfRule type="expression" dxfId="0" priority="71">
+    <cfRule type="expression" dxfId="0" priority="73">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I113">
-    <cfRule type="expression" dxfId="0" priority="73">
+    <cfRule type="expression" dxfId="0" priority="75">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114">
-    <cfRule type="duplicateValues" dxfId="1" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D114:E114">
-    <cfRule type="expression" dxfId="0" priority="67">
+    <cfRule type="expression" dxfId="0" priority="69">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I114">
-    <cfRule type="expression" dxfId="0" priority="69">
+    <cfRule type="expression" dxfId="0" priority="71">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A115">
-    <cfRule type="duplicateValues" dxfId="1" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D115:E115">
-    <cfRule type="expression" dxfId="0" priority="63">
+    <cfRule type="expression" dxfId="0" priority="65">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I115">
-    <cfRule type="expression" dxfId="0" priority="65">
+    <cfRule type="expression" dxfId="0" priority="67">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A116">
-    <cfRule type="duplicateValues" dxfId="1" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D116:E116">
-    <cfRule type="expression" dxfId="0" priority="59">
+    <cfRule type="expression" dxfId="0" priority="61">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I116">
-    <cfRule type="expression" dxfId="0" priority="61">
+    <cfRule type="expression" dxfId="0" priority="63">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117">
-    <cfRule type="duplicateValues" dxfId="1" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D117:E117">
-    <cfRule type="expression" dxfId="0" priority="55">
+    <cfRule type="expression" dxfId="0" priority="57">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I117">
-    <cfRule type="expression" dxfId="0" priority="57">
+    <cfRule type="expression" dxfId="0" priority="59">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A118">
-    <cfRule type="duplicateValues" dxfId="1" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D118:E118">
-    <cfRule type="expression" dxfId="0" priority="51">
+    <cfRule type="expression" dxfId="0" priority="53">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I118">
-    <cfRule type="expression" dxfId="0" priority="53">
+    <cfRule type="expression" dxfId="0" priority="55">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A119">
-    <cfRule type="duplicateValues" dxfId="1" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D119:E119">
-    <cfRule type="expression" dxfId="0" priority="47">
+    <cfRule type="expression" dxfId="0" priority="49">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I119">
-    <cfRule type="expression" dxfId="0" priority="49">
+    <cfRule type="expression" dxfId="0" priority="51">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A120">
-    <cfRule type="duplicateValues" dxfId="1" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D120:E120">
-    <cfRule type="expression" dxfId="0" priority="43">
+    <cfRule type="expression" dxfId="0" priority="45">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I120">
-    <cfRule type="expression" dxfId="0" priority="45">
+    <cfRule type="expression" dxfId="0" priority="47">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A121">
-    <cfRule type="duplicateValues" dxfId="1" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D121:E121">
-    <cfRule type="expression" dxfId="0" priority="39">
+    <cfRule type="expression" dxfId="0" priority="41">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I121">
-    <cfRule type="expression" dxfId="0" priority="41">
+    <cfRule type="expression" dxfId="0" priority="43">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A122">
-    <cfRule type="duplicateValues" dxfId="1" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D122:E122">
-    <cfRule type="expression" dxfId="0" priority="35">
+    <cfRule type="expression" dxfId="0" priority="37">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I122">
-    <cfRule type="expression" dxfId="0" priority="37">
+    <cfRule type="expression" dxfId="0" priority="39">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A123">
-    <cfRule type="duplicateValues" dxfId="1" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D123:E123">
-    <cfRule type="expression" dxfId="0" priority="31">
+    <cfRule type="expression" dxfId="0" priority="33">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I123">
-    <cfRule type="expression" dxfId="0" priority="33">
+    <cfRule type="expression" dxfId="0" priority="35">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C134:L134">
-    <cfRule type="expression" dxfId="0" priority="159">
+    <cfRule type="expression" dxfId="0" priority="161">
       <formula>MOD($B134,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="expression" dxfId="0" priority="23">
+    <cfRule type="expression" dxfId="0" priority="25">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A178">
-    <cfRule type="duplicateValues" dxfId="1" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B178">
+    <cfRule type="expression" dxfId="0" priority="21">
+      <formula>MOD($B178,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D178:E178">
     <cfRule type="expression" dxfId="0" priority="19">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D178:E178">
-    <cfRule type="expression" dxfId="0" priority="17">
-      <formula>MOD($B178,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H309">
-    <cfRule type="expression" dxfId="0" priority="437">
+    <cfRule type="expression" dxfId="0" priority="439">
       <formula>MOD($B308,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H321">
-    <cfRule type="expression" dxfId="0" priority="436">
+    <cfRule type="expression" dxfId="0" priority="438">
       <formula>MOD($B320,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:A60">
-    <cfRule type="duplicateValues" dxfId="1" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A87:A92">
-    <cfRule type="duplicateValues" dxfId="1" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A93:A98">
-    <cfRule type="duplicateValues" dxfId="1" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99:A104">
-    <cfRule type="duplicateValues" dxfId="1" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A135:A177">
-    <cfRule type="duplicateValues" dxfId="1" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A209:A387">
-    <cfRule type="duplicateValues" dxfId="1" priority="13"/>
+  <conditionalFormatting sqref="A209:A425">
+    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B60">
-    <cfRule type="expression" dxfId="0" priority="118">
+    <cfRule type="expression" dxfId="0" priority="120">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C84">
-    <cfRule type="expression" dxfId="0" priority="121">
+    <cfRule type="expression" dxfId="0" priority="123">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C271:C281">
-    <cfRule type="expression" dxfId="0" priority="10">
+    <cfRule type="expression" dxfId="0" priority="12">
       <formula>MOD($B271,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C282:C296">
-    <cfRule type="expression" dxfId="0" priority="8">
+    <cfRule type="expression" dxfId="0" priority="10">
       <formula>MOD($B282,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E93:E98">
-    <cfRule type="expression" dxfId="0" priority="110">
+    <cfRule type="expression" dxfId="0" priority="112">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E99:E104">
-    <cfRule type="expression" dxfId="0" priority="107">
+    <cfRule type="expression" dxfId="0" priority="109">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E257:E268">
-    <cfRule type="expression" dxfId="0" priority="11">
+    <cfRule type="expression" dxfId="0" priority="13">
       <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E271:E279">
-    <cfRule type="expression" dxfId="0" priority="9">
+    <cfRule type="expression" dxfId="0" priority="11">
       <formula>MOD($B271,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E282:E290">
-    <cfRule type="expression" dxfId="0" priority="7">
+    <cfRule type="expression" dxfId="0" priority="9">
       <formula>MOD($B282,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39:K42">
-    <cfRule type="duplicateValues" dxfId="2" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K169:K172">
-    <cfRule type="duplicateValues" dxfId="2" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K293:K296">
-    <cfRule type="expression" dxfId="0" priority="5">
+    <cfRule type="expression" dxfId="0" priority="7">
       <formula>MOD($B293,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K346:K349">
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="0" priority="5">
       <formula>MOD($B346,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K384:K387">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>MOD($B384,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K422:K425">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD($B422,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L205:L208">
-    <cfRule type="expression" dxfId="0" priority="16">
+    <cfRule type="expression" dxfId="0" priority="18">
       <formula>MOD($B205,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L293:L296">
-    <cfRule type="expression" dxfId="0" priority="6">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>MOD($B293,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L346:L349">
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="0" priority="6">
       <formula>MOD($B346,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L384:L387">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>MOD($B384,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A388:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="433"/>
+  <conditionalFormatting sqref="L422:L425">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>MOD($B422,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A426:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="435"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L4">
-    <cfRule type="expression" dxfId="0" priority="432">
+    <cfRule type="expression" dxfId="0" priority="434">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41:B42 B44:B47">
-    <cfRule type="expression" dxfId="0" priority="166">
+    <cfRule type="expression" dxfId="0" priority="168">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 H179:L204 B179:G208 I205:K208 I209:I256 B259:D268 F259:L268 B269:L270 B271:B296 D271:D279 F271:L279 D280:L281 D282:D290 F282:L290 D291:L292 D293:J296 H297:L307 H310:L319 I320:L321 B322:L345 B297:G321 B258 B346:J349 B350:L383 B384:J387 B388:L1048576 I308:L309">
-    <cfRule type="expression" dxfId="0" priority="431">
+  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 H179:L204 B179:G208 I205:K208 I209:I256 B259:D268 F259:L268 B269:L270 B271:B296 D271:D279 F271:L279 D280:L281 D282:D290 F282:L290 D291:L292 D293:J296 H297:L307 H310:L319 I320:L321 B322:L345 B297:G321 B258 B346:J349 B350:L383 B384:J387 B388:L421 B422:J425 B426:L1048576 I308:L309">
+    <cfRule type="expression" dxfId="0" priority="433">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43:G43 J43:L43">
-    <cfRule type="expression" dxfId="0" priority="131">
+    <cfRule type="expression" dxfId="0" priority="133">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44:G44 J44:L47 G45:G47 C45:C47">
-    <cfRule type="expression" dxfId="0" priority="165">
+    <cfRule type="expression" dxfId="0" priority="167">
       <formula>MOD($B44,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45:E47">
-    <cfRule type="expression" dxfId="0" priority="162">
+    <cfRule type="expression" dxfId="0" priority="164">
       <formula>MOD($B45,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F60 C48:C60">
+    <cfRule type="expression" dxfId="0" priority="121">
+      <formula>MOD($B48,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
     <cfRule type="expression" dxfId="0" priority="119">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
+  <conditionalFormatting sqref="D48:E60">
     <cfRule type="expression" dxfId="0" priority="117">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D48:E60">
-    <cfRule type="expression" dxfId="0" priority="115">
-      <formula>MOD($B48,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B77:B84 F77:L84">
-    <cfRule type="expression" dxfId="0" priority="161">
+    <cfRule type="expression" dxfId="0" priority="163">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85:C85 F85:L85">
-    <cfRule type="expression" dxfId="0" priority="157">
+    <cfRule type="expression" dxfId="0" priority="159">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B86:C86 F86:L86">
-    <cfRule type="expression" dxfId="0" priority="122">
+    <cfRule type="expression" dxfId="0" priority="124">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87:C92 F87:L92 I93:I104">
-    <cfRule type="expression" dxfId="0" priority="112">
+    <cfRule type="expression" dxfId="0" priority="114">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87:E92 D93:D104">
-    <cfRule type="expression" dxfId="0" priority="113">
+    <cfRule type="expression" dxfId="0" priority="115">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:C98 F93:H98 J93:L98">
-    <cfRule type="expression" dxfId="0" priority="109">
+    <cfRule type="expression" dxfId="0" priority="111">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99:C104 F99:H104 J99:L104">
-    <cfRule type="expression" dxfId="0" priority="106">
+    <cfRule type="expression" dxfId="0" priority="108">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:C105 F105:H105 J105:L105">
-    <cfRule type="expression" dxfId="0" priority="102">
+    <cfRule type="expression" dxfId="0" priority="104">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106:C106 F106:H106 J106:L106 H107:H111 C107:C111">
-    <cfRule type="expression" dxfId="0" priority="98">
+    <cfRule type="expression" dxfId="0" priority="100">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107 F107:G107 J107:L107">
-    <cfRule type="expression" dxfId="0" priority="94">
+    <cfRule type="expression" dxfId="0" priority="96">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B108 F108:G108 J108:L108">
-    <cfRule type="expression" dxfId="0" priority="90">
+    <cfRule type="expression" dxfId="0" priority="92">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B109 F109:G109 J109:L109">
-    <cfRule type="expression" dxfId="0" priority="86">
+    <cfRule type="expression" dxfId="0" priority="88">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B110 F110:G110 J110:L110">
-    <cfRule type="expression" dxfId="0" priority="82">
+    <cfRule type="expression" dxfId="0" priority="84">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111 F111:G111 J111:L111">
-    <cfRule type="expression" dxfId="0" priority="78">
+    <cfRule type="expression" dxfId="0" priority="80">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112:C112 F112:H112 J112:L112 H113:H117 C113:C117">
-    <cfRule type="expression" dxfId="0" priority="74">
+    <cfRule type="expression" dxfId="0" priority="76">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113 F113:G113 J113:L113">
-    <cfRule type="expression" dxfId="0" priority="70">
+    <cfRule type="expression" dxfId="0" priority="72">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114 F114:G114 J114:L114">
-    <cfRule type="expression" dxfId="0" priority="66">
+    <cfRule type="expression" dxfId="0" priority="68">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115 F115:G115 J115:L115">
-    <cfRule type="expression" dxfId="0" priority="62">
+    <cfRule type="expression" dxfId="0" priority="64">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B116 F116:G116 J116:L116">
-    <cfRule type="expression" dxfId="0" priority="58">
+    <cfRule type="expression" dxfId="0" priority="60">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117 F117:G117 J117:L117">
-    <cfRule type="expression" dxfId="0" priority="54">
+    <cfRule type="expression" dxfId="0" priority="56">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118:C118 F118:H118 J118:L118 H119:H123 C119:C123">
-    <cfRule type="expression" dxfId="0" priority="50">
+    <cfRule type="expression" dxfId="0" priority="52">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119 F119:G119 J119:L119">
-    <cfRule type="expression" dxfId="0" priority="46">
+    <cfRule type="expression" dxfId="0" priority="48">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120 F120:G120 J120:L120">
-    <cfRule type="expression" dxfId="0" priority="42">
+    <cfRule type="expression" dxfId="0" priority="44">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121 F121:G121 J121:L121">
-    <cfRule type="expression" dxfId="0" priority="38">
+    <cfRule type="expression" dxfId="0" priority="40">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122 F122:G122 J122:L122">
-    <cfRule type="expression" dxfId="0" priority="34">
+    <cfRule type="expression" dxfId="0" priority="36">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123 F123:G123 J123:L123">
-    <cfRule type="expression" dxfId="0" priority="30">
+    <cfRule type="expression" dxfId="0" priority="32">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B124:L133 B134">
-    <cfRule type="expression" dxfId="0" priority="160">
+    <cfRule type="expression" dxfId="0" priority="162">
       <formula>MOD($B124,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171:B172 B174:B177">
-    <cfRule type="expression" dxfId="0" priority="27">
+    <cfRule type="expression" dxfId="0" priority="29">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171:G172 J171:J172 L171:L172 F175:F177 C176:C177">
-    <cfRule type="expression" dxfId="0" priority="28">
+    <cfRule type="expression" dxfId="0" priority="30">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173:G173 J173:L173">
-    <cfRule type="expression" dxfId="0" priority="22">
+    <cfRule type="expression" dxfId="0" priority="24">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174:G174 J174:L177 G175:G177 C175:C177">
-    <cfRule type="expression" dxfId="0" priority="26">
+    <cfRule type="expression" dxfId="0" priority="28">
       <formula>MOD($B174,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D175:E177">
-    <cfRule type="expression" dxfId="0" priority="25">
+    <cfRule type="expression" dxfId="0" priority="27">
       <formula>MOD($B175,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F178 C178">
+    <cfRule type="expression" dxfId="0" priority="22">
+      <formula>MOD($B178,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J178:L178 G178 C178">
     <cfRule type="expression" dxfId="0" priority="20">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J178:L178 G178 C178">
-    <cfRule type="expression" dxfId="0" priority="18">
-      <formula>MOD($B178,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B209:D209 F209:H209 J209:L250 B210:H250">
-    <cfRule type="expression" dxfId="0" priority="15">
+    <cfRule type="expression" dxfId="0" priority="17">
       <formula>MOD($B209,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B251:H256 J251:L256">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="0" priority="16">
       <formula>MOD($B251,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B257 B259 B261 B263 B265 B267 B269 B271 B273 B275 B277 B279 B281 B283 B285 B287 B289 B291 B293 B295">
-    <cfRule type="expression" dxfId="0" priority="12">
+    <cfRule type="expression" dxfId="0" priority="14">
       <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C257:D257 F257:L257">
-    <cfRule type="expression" dxfId="0" priority="435">
+    <cfRule type="expression" dxfId="0" priority="437">
       <formula>MOD($B258,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C258:D258 I292 I290 I288 I286 I284 I282 I280 I278 I276 I274 I272 I270 I268 I266 I264 I262 I260 D268 D266 D264 D262 D260 F258:L258">
-    <cfRule type="expression" dxfId="0" priority="434">
+    <cfRule type="expression" dxfId="0" priority="436">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$387</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$432</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="72">
   <si>
     <t>id</t>
   </si>
@@ -522,6 +522,9 @@
   </si>
   <si>
     <t>+1免费符号</t>
+  </si>
+  <si>
+    <t>触发全屏奖</t>
   </si>
 </sst>
 </file>
@@ -5821,7 +5824,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L425"/>
+  <dimension ref="A1:L433"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="10"/>
@@ -16152,11 +16155,8 @@
       <c r="I346" s="11">
         <v>0</v>
       </c>
-      <c r="K346" s="2">
-        <v>101800101</v>
-      </c>
-      <c r="L346" s="13" t="s">
-        <v>65</v>
+      <c r="L346" s="54" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="347" customHeight="1" spans="1:12">
@@ -16183,10 +16183,10 @@
         <v>0</v>
       </c>
       <c r="K347" s="2">
-        <v>101800102</v>
+        <v>101800101</v>
       </c>
       <c r="L347" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="348" customHeight="1" spans="1:12">
@@ -16213,10 +16213,10 @@
         <v>0</v>
       </c>
       <c r="K348" s="2">
-        <v>101800103</v>
+        <v>101800102</v>
       </c>
       <c r="L348" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="349" customHeight="1" spans="1:12">
@@ -16243,10 +16243,10 @@
         <v>0</v>
       </c>
       <c r="K349" s="2">
-        <v>101800104</v>
+        <v>101800103</v>
       </c>
       <c r="L349" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="350" customHeight="1" spans="1:12">
@@ -16272,8 +16272,11 @@
       <c r="I350" s="11">
         <v>0</v>
       </c>
-      <c r="L350" s="54" t="s">
-        <v>70</v>
+      <c r="K350" s="2">
+        <v>101800104</v>
+      </c>
+      <c r="L350" s="13" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="351" customHeight="1" spans="1:12">
@@ -17457,13 +17460,16 @@
       <c r="G398" s="11">
         <v>0</v>
       </c>
+      <c r="H398" s="11">
+        <v>30230001</v>
+      </c>
       <c r="I398" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="399" customHeight="1" spans="1:12">
       <c r="A399" s="3">
-        <f t="shared" ref="A399:A420" si="16">(B399)*10000+C399+F399*100+D399*100000</f>
+        <f t="shared" ref="A399:A426" si="16">(B399)*10000+C399+F399*100+D399*100000</f>
         <v>1023300401</v>
       </c>
       <c r="B399" s="2">
@@ -17721,6 +17727,9 @@
       <c r="G409" s="11">
         <v>0</v>
       </c>
+      <c r="H409" s="11">
+        <v>30230002</v>
+      </c>
       <c r="I409" s="11">
         <v>0</v>
       </c>
@@ -17985,13 +17994,16 @@
       <c r="G420" s="11">
         <v>0</v>
       </c>
+      <c r="H420" s="11">
+        <v>30230003</v>
+      </c>
       <c r="I420" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="421" customHeight="1" spans="1:12">
       <c r="A421" s="3">
-        <f>(B421)*10000+C421+F421*100+D421*100000</f>
+        <f t="shared" si="16"/>
         <v>1023400112</v>
       </c>
       <c r="B421" s="2">
@@ -18015,7 +18027,7 @@
     </row>
     <row r="422" customHeight="1" spans="1:12">
       <c r="A422" s="3">
-        <f>(B422)*10000+C422+F422*100+D422*100000</f>
+        <f t="shared" si="16"/>
         <v>1023400113</v>
       </c>
       <c r="B422" s="2">
@@ -18045,7 +18057,7 @@
     </row>
     <row r="423" customHeight="1" spans="1:12">
       <c r="A423" s="3">
-        <f>(B423)*10000+C423+F423*100+D423*100000</f>
+        <f t="shared" si="16"/>
         <v>1023400114</v>
       </c>
       <c r="B423" s="2">
@@ -18075,7 +18087,7 @@
     </row>
     <row r="424" customHeight="1" spans="1:12">
       <c r="A424" s="3">
-        <f>(B424)*10000+C424+F424*100+D424*100000</f>
+        <f t="shared" si="16"/>
         <v>1023400115</v>
       </c>
       <c r="B424" s="2">
@@ -18105,7 +18117,7 @@
     </row>
     <row r="425" customHeight="1" spans="1:12">
       <c r="A425" s="3">
-        <f>(B425)*10000+C425+F425*100+D425*100000</f>
+        <f t="shared" si="16"/>
         <v>1023400116</v>
       </c>
       <c r="B425" s="2">
@@ -18133,8 +18145,206 @@
         <v>68</v>
       </c>
     </row>
+    <row r="426" customHeight="1" spans="1:12">
+      <c r="A426" s="3">
+        <f t="shared" si="16"/>
+        <v>1034100301</v>
+      </c>
+      <c r="B426" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C426" s="2">
+        <v>1</v>
+      </c>
+      <c r="D426" s="2">
+        <v>1</v>
+      </c>
+      <c r="F426" s="2">
+        <v>3</v>
+      </c>
+      <c r="G426" s="11">
+        <v>3</v>
+      </c>
+      <c r="I426" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" customHeight="1" spans="1:12">
+      <c r="A427" s="3">
+        <f t="shared" ref="A427:A432" si="17">(B427)*10000+C427+F427*100+D427*100000</f>
+        <v>1034100302</v>
+      </c>
+      <c r="B427" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C427" s="2">
+        <v>2</v>
+      </c>
+      <c r="D427" s="2">
+        <v>1</v>
+      </c>
+      <c r="F427" s="2">
+        <v>3</v>
+      </c>
+      <c r="G427" s="11">
+        <v>5</v>
+      </c>
+      <c r="I427" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" customHeight="1" spans="1:12">
+      <c r="A428" s="3">
+        <f t="shared" si="17"/>
+        <v>1034100303</v>
+      </c>
+      <c r="B428" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C428" s="2">
+        <v>3</v>
+      </c>
+      <c r="D428" s="2">
+        <v>1</v>
+      </c>
+      <c r="F428" s="2">
+        <v>3</v>
+      </c>
+      <c r="G428" s="11">
+        <v>8</v>
+      </c>
+      <c r="I428" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" customHeight="1" spans="1:12">
+      <c r="A429" s="3">
+        <f t="shared" si="17"/>
+        <v>1034100304</v>
+      </c>
+      <c r="B429" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C429" s="2">
+        <v>4</v>
+      </c>
+      <c r="D429" s="2">
+        <v>1</v>
+      </c>
+      <c r="F429" s="2">
+        <v>3</v>
+      </c>
+      <c r="G429" s="11">
+        <v>10</v>
+      </c>
+      <c r="I429" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" customHeight="1" spans="1:12">
+      <c r="A430" s="3">
+        <f t="shared" si="17"/>
+        <v>1034100305</v>
+      </c>
+      <c r="B430" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C430" s="2">
+        <v>5</v>
+      </c>
+      <c r="D430" s="2">
+        <v>1</v>
+      </c>
+      <c r="F430" s="2">
+        <v>3</v>
+      </c>
+      <c r="G430" s="11">
+        <v>25</v>
+      </c>
+      <c r="I430" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" customHeight="1" spans="1:12">
+      <c r="A431" s="3">
+        <f t="shared" si="17"/>
+        <v>1034100306</v>
+      </c>
+      <c r="B431" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C431" s="2">
+        <v>6</v>
+      </c>
+      <c r="D431" s="2">
+        <v>1</v>
+      </c>
+      <c r="F431" s="2">
+        <v>3</v>
+      </c>
+      <c r="G431" s="11">
+        <v>100</v>
+      </c>
+      <c r="I431" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" customHeight="1" spans="1:12">
+      <c r="A432" s="3">
+        <f t="shared" si="17"/>
+        <v>1034100307</v>
+      </c>
+      <c r="B432" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C432" s="2">
+        <v>7</v>
+      </c>
+      <c r="D432" s="2">
+        <v>1</v>
+      </c>
+      <c r="F432" s="2">
+        <v>3</v>
+      </c>
+      <c r="G432" s="11">
+        <v>250</v>
+      </c>
+      <c r="I432" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" customHeight="1" spans="1:12">
+      <c r="A433" s="3">
+        <f>(B433)*10000+C433+F433*100+D433*100000</f>
+        <v>1034400108</v>
+      </c>
+      <c r="B433" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C433" s="2">
+        <v>8</v>
+      </c>
+      <c r="D433" s="2">
+        <v>4</v>
+      </c>
+      <c r="F433" s="2">
+        <v>1</v>
+      </c>
+      <c r="G433" s="11">
+        <v>0</v>
+      </c>
+      <c r="I433" s="11">
+        <v>0</v>
+      </c>
+      <c r="K433" s="2">
+        <v>103400101</v>
+      </c>
+      <c r="L433" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L387" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L432" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">
@@ -18432,6 +18642,11 @@
       <formula>MOD($B320,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="L346">
+    <cfRule type="expression" dxfId="0" priority="440">
+      <formula>MOD($B350,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A48:A60">
     <cfRule type="duplicateValues" dxfId="1" priority="122"/>
   </conditionalFormatting>
@@ -18447,7 +18662,7 @@
   <conditionalFormatting sqref="A135:A177">
     <cfRule type="duplicateValues" dxfId="1" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A209:A425">
+  <conditionalFormatting sqref="A209:A433">
     <cfRule type="duplicateValues" dxfId="1" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B60">
@@ -18506,7 +18721,7 @@
       <formula>MOD($B293,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K346:K349">
+  <conditionalFormatting sqref="K347:K350">
     <cfRule type="expression" dxfId="0" priority="5">
       <formula>MOD($B346,2)=1</formula>
     </cfRule>
@@ -18531,7 +18746,7 @@
       <formula>MOD($B293,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L346:L349">
+  <conditionalFormatting sqref="L347:L350">
     <cfRule type="expression" dxfId="0" priority="6">
       <formula>MOD($B346,2)=1</formula>
     </cfRule>
@@ -18546,7 +18761,7 @@
       <formula>MOD($B422,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A426:A1048576">
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A434:A1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="435"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L4">
@@ -18559,7 +18774,7 @@
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 H179:L204 B179:G208 I205:K208 I209:I256 B259:D268 F259:L268 B269:L270 B271:B296 D271:D279 F271:L279 D280:L281 D282:D290 F282:L290 D291:L292 D293:J296 H297:L307 H310:L319 I320:L321 B322:L345 B297:G321 B258 B346:J349 B350:L383 B384:J387 B388:L421 B422:J425 B426:L1048576 I308:L309">
+  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 H179:L204 B179:G208 I205:K208 I209:I256 B259:D268 F259:L268 B269:L270 B271:B296 D271:D279 F271:L279 D280:L281 D282:D290 F282:L290 D291:L292 D293:J296 H297:L307 H310:L319 I320:L321 B322:L343 B345:L345 B297:G321 B258 K351:L383 B346:J387 B388:L421 B422:J425 B426:L1048576 I308:L309 B344:K344">
     <cfRule type="expression" dxfId="0" priority="433">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$387</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$458</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="72">
   <si>
     <t>id</t>
   </si>
@@ -522,6 +522,9 @@
   </si>
   <si>
     <t>+1免费符号</t>
+  </si>
+  <si>
+    <t>触发全屏奖</t>
   </si>
 </sst>
 </file>
@@ -766,6 +769,12 @@
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -776,12 +785,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5821,7 +5824,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L425"/>
+  <dimension ref="A1:L461"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="10"/>
@@ -16152,11 +16155,8 @@
       <c r="I346" s="11">
         <v>0</v>
       </c>
-      <c r="K346" s="2">
-        <v>101800101</v>
-      </c>
-      <c r="L346" s="13" t="s">
-        <v>65</v>
+      <c r="L346" s="54" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="347" customHeight="1" spans="1:12">
@@ -16183,10 +16183,10 @@
         <v>0</v>
       </c>
       <c r="K347" s="2">
-        <v>101800102</v>
+        <v>101800101</v>
       </c>
       <c r="L347" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="348" customHeight="1" spans="1:12">
@@ -16213,10 +16213,10 @@
         <v>0</v>
       </c>
       <c r="K348" s="2">
-        <v>101800103</v>
+        <v>101800102</v>
       </c>
       <c r="L348" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="349" customHeight="1" spans="1:12">
@@ -16243,10 +16243,10 @@
         <v>0</v>
       </c>
       <c r="K349" s="2">
-        <v>101800104</v>
+        <v>101800103</v>
       </c>
       <c r="L349" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="350" customHeight="1" spans="1:12">
@@ -16272,8 +16272,11 @@
       <c r="I350" s="11">
         <v>0</v>
       </c>
-      <c r="L350" s="54" t="s">
-        <v>70</v>
+      <c r="K350" s="2">
+        <v>101800104</v>
+      </c>
+      <c r="L350" s="13" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="351" customHeight="1" spans="1:12">
@@ -17457,13 +17460,16 @@
       <c r="G398" s="11">
         <v>0</v>
       </c>
+      <c r="H398" s="11">
+        <v>30230001</v>
+      </c>
       <c r="I398" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="399" customHeight="1" spans="1:12">
       <c r="A399" s="3">
-        <f t="shared" ref="A399:A420" si="16">(B399)*10000+C399+F399*100+D399*100000</f>
+        <f t="shared" ref="A399:A426" si="16">(B399)*10000+C399+F399*100+D399*100000</f>
         <v>1023300401</v>
       </c>
       <c r="B399" s="2">
@@ -17721,6 +17727,9 @@
       <c r="G409" s="11">
         <v>0</v>
       </c>
+      <c r="H409" s="11">
+        <v>30230002</v>
+      </c>
       <c r="I409" s="11">
         <v>0</v>
       </c>
@@ -17985,13 +17994,16 @@
       <c r="G420" s="11">
         <v>0</v>
       </c>
+      <c r="H420" s="11">
+        <v>30230003</v>
+      </c>
       <c r="I420" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="421" customHeight="1" spans="1:12">
       <c r="A421" s="3">
-        <f>(B421)*10000+C421+F421*100+D421*100000</f>
+        <f t="shared" si="16"/>
         <v>1023400112</v>
       </c>
       <c r="B421" s="2">
@@ -18015,7 +18027,7 @@
     </row>
     <row r="422" customHeight="1" spans="1:12">
       <c r="A422" s="3">
-        <f>(B422)*10000+C422+F422*100+D422*100000</f>
+        <f t="shared" si="16"/>
         <v>1023400113</v>
       </c>
       <c r="B422" s="2">
@@ -18045,7 +18057,7 @@
     </row>
     <row r="423" customHeight="1" spans="1:12">
       <c r="A423" s="3">
-        <f>(B423)*10000+C423+F423*100+D423*100000</f>
+        <f t="shared" si="16"/>
         <v>1023400114</v>
       </c>
       <c r="B423" s="2">
@@ -18075,7 +18087,7 @@
     </row>
     <row r="424" customHeight="1" spans="1:12">
       <c r="A424" s="3">
-        <f>(B424)*10000+C424+F424*100+D424*100000</f>
+        <f t="shared" si="16"/>
         <v>1023400115</v>
       </c>
       <c r="B424" s="2">
@@ -18105,7 +18117,7 @@
     </row>
     <row r="425" customHeight="1" spans="1:12">
       <c r="A425" s="3">
-        <f>(B425)*10000+C425+F425*100+D425*100000</f>
+        <f t="shared" si="16"/>
         <v>1023400116</v>
       </c>
       <c r="B425" s="2">
@@ -18133,659 +18145,1610 @@
         <v>68</v>
       </c>
     </row>
+    <row r="426" customHeight="1" spans="1:12">
+      <c r="A426" s="3">
+        <f t="shared" si="16"/>
+        <v>1034100301</v>
+      </c>
+      <c r="B426" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C426" s="2">
+        <v>1</v>
+      </c>
+      <c r="D426" s="2">
+        <v>1</v>
+      </c>
+      <c r="F426" s="2">
+        <v>3</v>
+      </c>
+      <c r="G426" s="11">
+        <v>3</v>
+      </c>
+      <c r="I426" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" customHeight="1" spans="1:12">
+      <c r="A427" s="3">
+        <f t="shared" ref="A427:A433" si="17">(B427)*10000+C427+F427*100+D427*100000</f>
+        <v>1034100302</v>
+      </c>
+      <c r="B427" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C427" s="2">
+        <v>2</v>
+      </c>
+      <c r="D427" s="2">
+        <v>1</v>
+      </c>
+      <c r="F427" s="2">
+        <v>3</v>
+      </c>
+      <c r="G427" s="11">
+        <v>5</v>
+      </c>
+      <c r="I427" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" customHeight="1" spans="1:12">
+      <c r="A428" s="3">
+        <f t="shared" si="17"/>
+        <v>1034100303</v>
+      </c>
+      <c r="B428" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C428" s="2">
+        <v>3</v>
+      </c>
+      <c r="D428" s="2">
+        <v>1</v>
+      </c>
+      <c r="F428" s="2">
+        <v>3</v>
+      </c>
+      <c r="G428" s="11">
+        <v>8</v>
+      </c>
+      <c r="I428" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" customHeight="1" spans="1:12">
+      <c r="A429" s="3">
+        <f t="shared" si="17"/>
+        <v>1034100304</v>
+      </c>
+      <c r="B429" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C429" s="2">
+        <v>4</v>
+      </c>
+      <c r="D429" s="2">
+        <v>1</v>
+      </c>
+      <c r="F429" s="2">
+        <v>3</v>
+      </c>
+      <c r="G429" s="11">
+        <v>10</v>
+      </c>
+      <c r="I429" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" customHeight="1" spans="1:12">
+      <c r="A430" s="3">
+        <f t="shared" si="17"/>
+        <v>1034100305</v>
+      </c>
+      <c r="B430" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C430" s="2">
+        <v>5</v>
+      </c>
+      <c r="D430" s="2">
+        <v>1</v>
+      </c>
+      <c r="F430" s="2">
+        <v>3</v>
+      </c>
+      <c r="G430" s="11">
+        <v>25</v>
+      </c>
+      <c r="I430" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" customHeight="1" spans="1:12">
+      <c r="A431" s="3">
+        <f t="shared" si="17"/>
+        <v>1034100306</v>
+      </c>
+      <c r="B431" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C431" s="2">
+        <v>6</v>
+      </c>
+      <c r="D431" s="2">
+        <v>1</v>
+      </c>
+      <c r="F431" s="2">
+        <v>3</v>
+      </c>
+      <c r="G431" s="11">
+        <v>100</v>
+      </c>
+      <c r="I431" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" customHeight="1" spans="1:12">
+      <c r="A432" s="3">
+        <f t="shared" si="17"/>
+        <v>1034100307</v>
+      </c>
+      <c r="B432" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C432" s="2">
+        <v>7</v>
+      </c>
+      <c r="D432" s="2">
+        <v>1</v>
+      </c>
+      <c r="F432" s="2">
+        <v>3</v>
+      </c>
+      <c r="G432" s="11">
+        <v>250</v>
+      </c>
+      <c r="I432" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" customHeight="1" spans="1:12">
+      <c r="A433" s="3">
+        <f t="shared" si="17"/>
+        <v>1034400108</v>
+      </c>
+      <c r="B433" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C433" s="2">
+        <v>8</v>
+      </c>
+      <c r="D433" s="2">
+        <v>4</v>
+      </c>
+      <c r="F433" s="2">
+        <v>1</v>
+      </c>
+      <c r="G433" s="11">
+        <v>0</v>
+      </c>
+      <c r="I433" s="11">
+        <v>0</v>
+      </c>
+      <c r="K433" s="2">
+        <v>103400101</v>
+      </c>
+      <c r="L433" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="434" customHeight="1" spans="1:12">
+      <c r="A434" s="3">
+        <f t="shared" ref="A434:A444" si="18">(B434)*10000+C434+F434*100+D434*100000</f>
+        <v>1035100301</v>
+      </c>
+      <c r="B434" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C434" s="2">
+        <v>1</v>
+      </c>
+      <c r="D434" s="2">
+        <v>1</v>
+      </c>
+      <c r="F434" s="2">
+        <v>3</v>
+      </c>
+      <c r="G434" s="11">
+        <v>2</v>
+      </c>
+      <c r="I434" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" customHeight="1" spans="1:12">
+      <c r="A435" s="3">
+        <f t="shared" si="18"/>
+        <v>1035100302</v>
+      </c>
+      <c r="B435" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C435" s="2">
+        <v>2</v>
+      </c>
+      <c r="D435" s="2">
+        <v>1</v>
+      </c>
+      <c r="F435" s="2">
+        <v>3</v>
+      </c>
+      <c r="G435" s="11">
+        <v>3</v>
+      </c>
+      <c r="I435" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" customHeight="1" spans="1:12">
+      <c r="A436" s="3">
+        <f t="shared" si="18"/>
+        <v>1035100303</v>
+      </c>
+      <c r="B436" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C436" s="2">
+        <v>3</v>
+      </c>
+      <c r="D436" s="2">
+        <v>1</v>
+      </c>
+      <c r="F436" s="2">
+        <v>3</v>
+      </c>
+      <c r="G436" s="11">
+        <v>5</v>
+      </c>
+      <c r="I436" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" customHeight="1" spans="1:12">
+      <c r="A437" s="3">
+        <f t="shared" si="18"/>
+        <v>1035100304</v>
+      </c>
+      <c r="B437" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C437" s="2">
+        <v>4</v>
+      </c>
+      <c r="D437" s="2">
+        <v>1</v>
+      </c>
+      <c r="F437" s="2">
+        <v>3</v>
+      </c>
+      <c r="G437" s="11">
+        <v>10</v>
+      </c>
+      <c r="I437" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" customHeight="1" spans="1:12">
+      <c r="A438" s="3">
+        <f t="shared" si="18"/>
+        <v>1035100305</v>
+      </c>
+      <c r="B438" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C438" s="2">
+        <v>5</v>
+      </c>
+      <c r="D438" s="2">
+        <v>1</v>
+      </c>
+      <c r="F438" s="2">
+        <v>3</v>
+      </c>
+      <c r="G438" s="11">
+        <v>50</v>
+      </c>
+      <c r="I438" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" customHeight="1" spans="1:12">
+      <c r="A439" s="3">
+        <f t="shared" si="18"/>
+        <v>1035100306</v>
+      </c>
+      <c r="B439" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C439" s="2">
+        <v>6</v>
+      </c>
+      <c r="D439" s="2">
+        <v>1</v>
+      </c>
+      <c r="F439" s="2">
+        <v>3</v>
+      </c>
+      <c r="G439" s="11">
+        <v>100</v>
+      </c>
+      <c r="I439" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" customHeight="1" spans="1:12">
+      <c r="A440" s="3">
+        <f t="shared" si="18"/>
+        <v>1035100307</v>
+      </c>
+      <c r="B440" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C440" s="2">
+        <v>7</v>
+      </c>
+      <c r="D440" s="2">
+        <v>1</v>
+      </c>
+      <c r="F440" s="2">
+        <v>3</v>
+      </c>
+      <c r="G440" s="11">
+        <v>200</v>
+      </c>
+      <c r="I440" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" customHeight="1" spans="1:12">
+      <c r="A441" s="3">
+        <f t="shared" si="18"/>
+        <v>1035400109</v>
+      </c>
+      <c r="B441" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C441" s="2">
+        <v>9</v>
+      </c>
+      <c r="D441" s="2">
+        <v>4</v>
+      </c>
+      <c r="F441" s="2">
+        <v>1</v>
+      </c>
+      <c r="G441" s="11">
+        <v>0</v>
+      </c>
+      <c r="I441" s="11">
+        <v>0</v>
+      </c>
+      <c r="K441" s="2">
+        <v>103500101</v>
+      </c>
+      <c r="L441" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="442" customHeight="1" spans="1:12">
+      <c r="A442" s="3">
+        <f t="shared" si="18"/>
+        <v>1035400110</v>
+      </c>
+      <c r="B442" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C442" s="2">
+        <v>10</v>
+      </c>
+      <c r="D442" s="2">
+        <v>4</v>
+      </c>
+      <c r="F442" s="2">
+        <v>1</v>
+      </c>
+      <c r="G442" s="11">
+        <v>0</v>
+      </c>
+      <c r="I442" s="11">
+        <v>0</v>
+      </c>
+      <c r="K442" s="2">
+        <v>103500102</v>
+      </c>
+      <c r="L442" s="13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="443" customHeight="1" spans="1:12">
+      <c r="A443" s="3">
+        <f t="shared" si="18"/>
+        <v>1035400111</v>
+      </c>
+      <c r="B443" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C443" s="2">
+        <v>11</v>
+      </c>
+      <c r="D443" s="2">
+        <v>4</v>
+      </c>
+      <c r="F443" s="2">
+        <v>1</v>
+      </c>
+      <c r="G443" s="11">
+        <v>0</v>
+      </c>
+      <c r="I443" s="11">
+        <v>0</v>
+      </c>
+      <c r="K443" s="2">
+        <v>103500103</v>
+      </c>
+      <c r="L443" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="444" customHeight="1" spans="1:12">
+      <c r="A444" s="3">
+        <f t="shared" si="18"/>
+        <v>1035400112</v>
+      </c>
+      <c r="B444" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C444" s="2">
+        <v>12</v>
+      </c>
+      <c r="D444" s="2">
+        <v>4</v>
+      </c>
+      <c r="F444" s="2">
+        <v>1</v>
+      </c>
+      <c r="G444" s="11">
+        <v>0</v>
+      </c>
+      <c r="I444" s="11">
+        <v>0</v>
+      </c>
+      <c r="K444" s="2">
+        <v>103500104</v>
+      </c>
+      <c r="L444" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="445" customHeight="1" spans="1:12">
+      <c r="A445" s="3">
+        <f>(B445)*10000+C445+F445*100+D445*100000</f>
+        <v>1035400508</v>
+      </c>
+      <c r="B445" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C445" s="2">
+        <v>8</v>
+      </c>
+      <c r="D445" s="2">
+        <v>4</v>
+      </c>
+      <c r="F445" s="2">
+        <v>5</v>
+      </c>
+      <c r="G445" s="11">
+        <v>0</v>
+      </c>
+      <c r="H445" s="11">
+        <v>30350002</v>
+      </c>
+      <c r="I445" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" customHeight="1" spans="1:12">
+      <c r="A446" s="3">
+        <f>(B446)*10000+C446+F446*100+D446*100000</f>
+        <v>1035400608</v>
+      </c>
+      <c r="B446" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C446" s="2">
+        <v>8</v>
+      </c>
+      <c r="D446" s="2">
+        <v>4</v>
+      </c>
+      <c r="F446" s="2">
+        <v>6</v>
+      </c>
+      <c r="G446" s="11">
+        <v>0</v>
+      </c>
+      <c r="H446" s="11">
+        <v>30350002</v>
+      </c>
+      <c r="I446" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" customHeight="1" spans="1:12">
+      <c r="A447" s="3">
+        <f>(B447)*10000+C447+F447*100+D447*100000</f>
+        <v>1035400114</v>
+      </c>
+      <c r="B447" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C447" s="2">
+        <v>14</v>
+      </c>
+      <c r="D447" s="2">
+        <v>4</v>
+      </c>
+      <c r="F447" s="2">
+        <v>1</v>
+      </c>
+      <c r="G447" s="11">
+        <v>0</v>
+      </c>
+      <c r="H447" s="11">
+        <v>30350001</v>
+      </c>
+      <c r="I447" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" customHeight="1" spans="1:12">
+      <c r="A448" s="3">
+        <f t="shared" ref="A448:A458" si="19">(B448)*10000+C448+F448*100+D448*100000</f>
+        <v>1035110301</v>
+      </c>
+      <c r="B448" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C448" s="2">
+        <v>1</v>
+      </c>
+      <c r="D448" s="2">
+        <v>1</v>
+      </c>
+      <c r="F448" s="2">
+        <v>3</v>
+      </c>
+      <c r="G448" s="11">
+        <v>2</v>
+      </c>
+      <c r="I448" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" customHeight="1" spans="1:12">
+      <c r="A449" s="3">
+        <f t="shared" si="19"/>
+        <v>1035110302</v>
+      </c>
+      <c r="B449" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C449" s="2">
+        <v>2</v>
+      </c>
+      <c r="D449" s="2">
+        <v>1</v>
+      </c>
+      <c r="F449" s="2">
+        <v>3</v>
+      </c>
+      <c r="G449" s="11">
+        <v>3</v>
+      </c>
+      <c r="I449" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" customHeight="1" spans="1:12">
+      <c r="A450" s="3">
+        <f t="shared" si="19"/>
+        <v>1035110303</v>
+      </c>
+      <c r="B450" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C450" s="2">
+        <v>3</v>
+      </c>
+      <c r="D450" s="2">
+        <v>1</v>
+      </c>
+      <c r="F450" s="2">
+        <v>3</v>
+      </c>
+      <c r="G450" s="11">
+        <v>5</v>
+      </c>
+      <c r="I450" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" customHeight="1" spans="1:12">
+      <c r="A451" s="3">
+        <f t="shared" si="19"/>
+        <v>1035110304</v>
+      </c>
+      <c r="B451" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C451" s="2">
+        <v>4</v>
+      </c>
+      <c r="D451" s="2">
+        <v>1</v>
+      </c>
+      <c r="F451" s="2">
+        <v>3</v>
+      </c>
+      <c r="G451" s="11">
+        <v>10</v>
+      </c>
+      <c r="I451" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" customHeight="1" spans="1:12">
+      <c r="A452" s="3">
+        <f t="shared" si="19"/>
+        <v>1035110305</v>
+      </c>
+      <c r="B452" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C452" s="2">
+        <v>5</v>
+      </c>
+      <c r="D452" s="2">
+        <v>1</v>
+      </c>
+      <c r="F452" s="2">
+        <v>3</v>
+      </c>
+      <c r="G452" s="11">
+        <v>50</v>
+      </c>
+      <c r="I452" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" customHeight="1" spans="1:12">
+      <c r="A453" s="3">
+        <f t="shared" si="19"/>
+        <v>1035110306</v>
+      </c>
+      <c r="B453" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C453" s="2">
+        <v>6</v>
+      </c>
+      <c r="D453" s="2">
+        <v>1</v>
+      </c>
+      <c r="F453" s="2">
+        <v>3</v>
+      </c>
+      <c r="G453" s="11">
+        <v>100</v>
+      </c>
+      <c r="I453" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" customHeight="1" spans="1:12">
+      <c r="A454" s="3">
+        <f t="shared" si="19"/>
+        <v>1035110307</v>
+      </c>
+      <c r="B454" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C454" s="2">
+        <v>7</v>
+      </c>
+      <c r="D454" s="2">
+        <v>1</v>
+      </c>
+      <c r="F454" s="2">
+        <v>3</v>
+      </c>
+      <c r="G454" s="11">
+        <v>200</v>
+      </c>
+      <c r="I454" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" customHeight="1" spans="1:12">
+      <c r="A455" s="3">
+        <f t="shared" si="19"/>
+        <v>1035410109</v>
+      </c>
+      <c r="B455" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C455" s="2">
+        <v>9</v>
+      </c>
+      <c r="D455" s="2">
+        <v>4</v>
+      </c>
+      <c r="F455" s="2">
+        <v>1</v>
+      </c>
+      <c r="G455" s="11">
+        <v>0</v>
+      </c>
+      <c r="I455" s="11">
+        <v>0</v>
+      </c>
+      <c r="K455" s="2">
+        <v>103501101</v>
+      </c>
+      <c r="L455" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="456" customHeight="1" spans="1:12">
+      <c r="A456" s="3">
+        <f t="shared" si="19"/>
+        <v>1035410110</v>
+      </c>
+      <c r="B456" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C456" s="2">
+        <v>10</v>
+      </c>
+      <c r="D456" s="2">
+        <v>4</v>
+      </c>
+      <c r="F456" s="2">
+        <v>1</v>
+      </c>
+      <c r="G456" s="11">
+        <v>0</v>
+      </c>
+      <c r="I456" s="11">
+        <v>0</v>
+      </c>
+      <c r="K456" s="2">
+        <v>103501102</v>
+      </c>
+      <c r="L456" s="13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="457" customHeight="1" spans="1:12">
+      <c r="A457" s="3">
+        <f t="shared" si="19"/>
+        <v>1035410111</v>
+      </c>
+      <c r="B457" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C457" s="2">
+        <v>11</v>
+      </c>
+      <c r="D457" s="2">
+        <v>4</v>
+      </c>
+      <c r="F457" s="2">
+        <v>1</v>
+      </c>
+      <c r="G457" s="11">
+        <v>0</v>
+      </c>
+      <c r="I457" s="11">
+        <v>0</v>
+      </c>
+      <c r="K457" s="2">
+        <v>103501103</v>
+      </c>
+      <c r="L457" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="458" customHeight="1" spans="1:12">
+      <c r="A458" s="3">
+        <f t="shared" si="19"/>
+        <v>1035410112</v>
+      </c>
+      <c r="B458" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C458" s="2">
+        <v>12</v>
+      </c>
+      <c r="D458" s="2">
+        <v>4</v>
+      </c>
+      <c r="F458" s="2">
+        <v>1</v>
+      </c>
+      <c r="G458" s="11">
+        <v>0</v>
+      </c>
+      <c r="I458" s="11">
+        <v>0</v>
+      </c>
+      <c r="K458" s="2">
+        <v>103501104</v>
+      </c>
+      <c r="L458" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="459" customHeight="1" spans="1:12">
+      <c r="A459" s="3">
+        <f>(B459)*10000+C459+F459*100+D459*100000</f>
+        <v>1035410508</v>
+      </c>
+      <c r="B459" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C459" s="2">
+        <v>8</v>
+      </c>
+      <c r="D459" s="2">
+        <v>4</v>
+      </c>
+      <c r="F459" s="2">
+        <v>5</v>
+      </c>
+      <c r="G459" s="11">
+        <v>0</v>
+      </c>
+      <c r="H459" s="11">
+        <v>30350102</v>
+      </c>
+      <c r="I459" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" customHeight="1" spans="1:12">
+      <c r="A460" s="3">
+        <f>(B460)*10000+C460+F460*100+D460*100000</f>
+        <v>1035410608</v>
+      </c>
+      <c r="B460" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C460" s="2">
+        <v>8</v>
+      </c>
+      <c r="D460" s="2">
+        <v>4</v>
+      </c>
+      <c r="F460" s="2">
+        <v>6</v>
+      </c>
+      <c r="G460" s="11">
+        <v>0</v>
+      </c>
+      <c r="H460" s="11">
+        <v>30350102</v>
+      </c>
+      <c r="I460" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461" customHeight="1" spans="1:12">
+      <c r="A461" s="3">
+        <f>(B461)*10000+C461+F461*100+D461*100000</f>
+        <v>1035410114</v>
+      </c>
+      <c r="B461" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C461" s="2">
+        <v>14</v>
+      </c>
+      <c r="D461" s="2">
+        <v>4</v>
+      </c>
+      <c r="F461" s="2">
+        <v>1</v>
+      </c>
+      <c r="G461" s="11">
+        <v>0</v>
+      </c>
+      <c r="H461" s="11">
+        <v>30350101</v>
+      </c>
+      <c r="I461" s="11">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L387" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L458" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="0" priority="134">
+    <cfRule type="expression" dxfId="0" priority="136">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D85:E85">
-    <cfRule type="expression" dxfId="0" priority="160">
+    <cfRule type="expression" dxfId="0" priority="162">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D86:E86">
-    <cfRule type="expression" dxfId="0" priority="125">
+    <cfRule type="expression" dxfId="0" priority="127">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105">
-    <cfRule type="duplicateValues" dxfId="1" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105:E105">
-    <cfRule type="expression" dxfId="0" priority="105">
+    <cfRule type="expression" dxfId="0" priority="107">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I105">
-    <cfRule type="expression" dxfId="0" priority="107">
+    <cfRule type="expression" dxfId="0" priority="109">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A106">
-    <cfRule type="duplicateValues" dxfId="1" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D106:E106">
-    <cfRule type="expression" dxfId="0" priority="101">
+    <cfRule type="expression" dxfId="0" priority="103">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I106">
-    <cfRule type="expression" dxfId="0" priority="103">
+    <cfRule type="expression" dxfId="0" priority="105">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="1" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D107:E107">
-    <cfRule type="expression" dxfId="0" priority="97">
+    <cfRule type="expression" dxfId="0" priority="99">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I107">
-    <cfRule type="expression" dxfId="0" priority="99">
+    <cfRule type="expression" dxfId="0" priority="101">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108">
-    <cfRule type="duplicateValues" dxfId="1" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D108:E108">
-    <cfRule type="expression" dxfId="0" priority="93">
+    <cfRule type="expression" dxfId="0" priority="95">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I108">
-    <cfRule type="expression" dxfId="0" priority="95">
+    <cfRule type="expression" dxfId="0" priority="97">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" dxfId="1" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D109:E109">
-    <cfRule type="expression" dxfId="0" priority="89">
+    <cfRule type="expression" dxfId="0" priority="91">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I109">
-    <cfRule type="expression" dxfId="0" priority="91">
+    <cfRule type="expression" dxfId="0" priority="93">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110">
-    <cfRule type="duplicateValues" dxfId="1" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D110:E110">
-    <cfRule type="expression" dxfId="0" priority="85">
+    <cfRule type="expression" dxfId="0" priority="87">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I110">
-    <cfRule type="expression" dxfId="0" priority="87">
+    <cfRule type="expression" dxfId="0" priority="89">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A111">
-    <cfRule type="duplicateValues" dxfId="1" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D111:E111">
-    <cfRule type="expression" dxfId="0" priority="81">
+    <cfRule type="expression" dxfId="0" priority="83">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I111">
-    <cfRule type="expression" dxfId="0" priority="83">
+    <cfRule type="expression" dxfId="0" priority="85">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112">
-    <cfRule type="duplicateValues" dxfId="1" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D112:E112">
-    <cfRule type="expression" dxfId="0" priority="77">
+    <cfRule type="expression" dxfId="0" priority="79">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I112">
-    <cfRule type="expression" dxfId="0" priority="79">
+    <cfRule type="expression" dxfId="0" priority="81">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A113">
-    <cfRule type="duplicateValues" dxfId="1" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D113:E113">
-    <cfRule type="expression" dxfId="0" priority="73">
+    <cfRule type="expression" dxfId="0" priority="75">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I113">
-    <cfRule type="expression" dxfId="0" priority="75">
+    <cfRule type="expression" dxfId="0" priority="77">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114">
-    <cfRule type="duplicateValues" dxfId="1" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D114:E114">
-    <cfRule type="expression" dxfId="0" priority="69">
+    <cfRule type="expression" dxfId="0" priority="71">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I114">
-    <cfRule type="expression" dxfId="0" priority="71">
+    <cfRule type="expression" dxfId="0" priority="73">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A115">
-    <cfRule type="duplicateValues" dxfId="1" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D115:E115">
-    <cfRule type="expression" dxfId="0" priority="65">
+    <cfRule type="expression" dxfId="0" priority="67">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I115">
-    <cfRule type="expression" dxfId="0" priority="67">
+    <cfRule type="expression" dxfId="0" priority="69">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A116">
-    <cfRule type="duplicateValues" dxfId="1" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D116:E116">
-    <cfRule type="expression" dxfId="0" priority="61">
+    <cfRule type="expression" dxfId="0" priority="63">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I116">
-    <cfRule type="expression" dxfId="0" priority="63">
+    <cfRule type="expression" dxfId="0" priority="65">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117">
-    <cfRule type="duplicateValues" dxfId="1" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D117:E117">
-    <cfRule type="expression" dxfId="0" priority="57">
+    <cfRule type="expression" dxfId="0" priority="59">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I117">
-    <cfRule type="expression" dxfId="0" priority="59">
+    <cfRule type="expression" dxfId="0" priority="61">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A118">
-    <cfRule type="duplicateValues" dxfId="1" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D118:E118">
-    <cfRule type="expression" dxfId="0" priority="53">
+    <cfRule type="expression" dxfId="0" priority="55">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I118">
-    <cfRule type="expression" dxfId="0" priority="55">
+    <cfRule type="expression" dxfId="0" priority="57">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A119">
-    <cfRule type="duplicateValues" dxfId="1" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D119:E119">
-    <cfRule type="expression" dxfId="0" priority="49">
+    <cfRule type="expression" dxfId="0" priority="51">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I119">
-    <cfRule type="expression" dxfId="0" priority="51">
+    <cfRule type="expression" dxfId="0" priority="53">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A120">
-    <cfRule type="duplicateValues" dxfId="1" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D120:E120">
-    <cfRule type="expression" dxfId="0" priority="45">
+    <cfRule type="expression" dxfId="0" priority="47">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I120">
-    <cfRule type="expression" dxfId="0" priority="47">
+    <cfRule type="expression" dxfId="0" priority="49">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A121">
-    <cfRule type="duplicateValues" dxfId="1" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D121:E121">
-    <cfRule type="expression" dxfId="0" priority="41">
+    <cfRule type="expression" dxfId="0" priority="43">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I121">
-    <cfRule type="expression" dxfId="0" priority="43">
+    <cfRule type="expression" dxfId="0" priority="45">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A122">
-    <cfRule type="duplicateValues" dxfId="1" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D122:E122">
-    <cfRule type="expression" dxfId="0" priority="37">
+    <cfRule type="expression" dxfId="0" priority="39">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I122">
-    <cfRule type="expression" dxfId="0" priority="39">
+    <cfRule type="expression" dxfId="0" priority="41">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A123">
-    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D123:E123">
-    <cfRule type="expression" dxfId="0" priority="33">
+    <cfRule type="expression" dxfId="0" priority="35">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I123">
-    <cfRule type="expression" dxfId="0" priority="35">
+    <cfRule type="expression" dxfId="0" priority="37">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C134:L134">
-    <cfRule type="expression" dxfId="0" priority="161">
+    <cfRule type="expression" dxfId="0" priority="163">
       <formula>MOD($B134,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="expression" dxfId="0" priority="25">
+    <cfRule type="expression" dxfId="0" priority="27">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A178">
-    <cfRule type="duplicateValues" dxfId="1" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B178">
+    <cfRule type="expression" dxfId="0" priority="23">
+      <formula>MOD($B178,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D178:E178">
     <cfRule type="expression" dxfId="0" priority="21">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D178:E178">
-    <cfRule type="expression" dxfId="0" priority="19">
-      <formula>MOD($B178,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H309">
-    <cfRule type="expression" dxfId="0" priority="439">
+    <cfRule type="expression" dxfId="0" priority="441">
       <formula>MOD($B308,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H321">
-    <cfRule type="expression" dxfId="0" priority="438">
+    <cfRule type="expression" dxfId="0" priority="440">
       <formula>MOD($B320,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="L346">
+    <cfRule type="expression" dxfId="0" priority="442">
+      <formula>MOD($B350,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A48:A60">
-    <cfRule type="duplicateValues" dxfId="1" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A87:A92">
-    <cfRule type="duplicateValues" dxfId="1" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A93:A98">
-    <cfRule type="duplicateValues" dxfId="1" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99:A104">
-    <cfRule type="duplicateValues" dxfId="1" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A135:A177">
-    <cfRule type="duplicateValues" dxfId="1" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A209:A425">
-    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
+  <conditionalFormatting sqref="A209:A461">
+    <cfRule type="duplicateValues" dxfId="1" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B60">
-    <cfRule type="expression" dxfId="0" priority="120">
+    <cfRule type="expression" dxfId="0" priority="122">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C84">
-    <cfRule type="expression" dxfId="0" priority="123">
+    <cfRule type="expression" dxfId="0" priority="125">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C271:C281">
-    <cfRule type="expression" dxfId="0" priority="12">
+    <cfRule type="expression" dxfId="0" priority="14">
       <formula>MOD($B271,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C282:C296">
-    <cfRule type="expression" dxfId="0" priority="10">
+    <cfRule type="expression" dxfId="0" priority="12">
       <formula>MOD($B282,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E93:E98">
-    <cfRule type="expression" dxfId="0" priority="112">
+    <cfRule type="expression" dxfId="0" priority="114">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E99:E104">
-    <cfRule type="expression" dxfId="0" priority="109">
+    <cfRule type="expression" dxfId="0" priority="111">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E257:E268">
-    <cfRule type="expression" dxfId="0" priority="13">
+    <cfRule type="expression" dxfId="0" priority="15">
       <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E271:E279">
-    <cfRule type="expression" dxfId="0" priority="11">
+    <cfRule type="expression" dxfId="0" priority="13">
       <formula>MOD($B271,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E282:E290">
-    <cfRule type="expression" dxfId="0" priority="9">
+    <cfRule type="expression" dxfId="0" priority="11">
       <formula>MOD($B282,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39:K42">
-    <cfRule type="duplicateValues" dxfId="2" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K169:K172">
-    <cfRule type="duplicateValues" dxfId="2" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K293:K296">
-    <cfRule type="expression" dxfId="0" priority="7">
+    <cfRule type="expression" dxfId="0" priority="9">
       <formula>MOD($B293,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K346:K349">
-    <cfRule type="expression" dxfId="0" priority="5">
+  <conditionalFormatting sqref="K347:K350">
+    <cfRule type="expression" dxfId="0" priority="7">
       <formula>MOD($B346,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K384:K387">
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="0" priority="5">
       <formula>MOD($B384,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K422:K425">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>MOD($B422,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L205:L208">
-    <cfRule type="expression" dxfId="0" priority="18">
+    <cfRule type="expression" dxfId="0" priority="20">
       <formula>MOD($B205,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L293:L296">
-    <cfRule type="expression" dxfId="0" priority="8">
+    <cfRule type="expression" dxfId="0" priority="10">
       <formula>MOD($B293,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L346:L349">
-    <cfRule type="expression" dxfId="0" priority="6">
+  <conditionalFormatting sqref="L347:L350">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>MOD($B346,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L384:L387">
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="0" priority="6">
       <formula>MOD($B384,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L422:L425">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>MOD($B422,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A426:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="435"/>
+  <conditionalFormatting sqref="L441:L447">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>MOD($B441,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L455:L458">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD($B455,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A462:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="437"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L4">
-    <cfRule type="expression" dxfId="0" priority="434">
+    <cfRule type="expression" dxfId="0" priority="436">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41:B42 B44:B47">
-    <cfRule type="expression" dxfId="0" priority="168">
+    <cfRule type="expression" dxfId="0" priority="170">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 H179:L204 B179:G208 I205:K208 I209:I256 B259:D268 F259:L268 B269:L270 B271:B296 D271:D279 F271:L279 D280:L281 D282:D290 F282:L290 D291:L292 D293:J296 H297:L307 H310:L319 I320:L321 B322:L345 B297:G321 B258 B346:J349 B350:L383 B384:J387 B388:L421 B422:J425 B426:L1048576 I308:L309">
-    <cfRule type="expression" dxfId="0" priority="433">
+  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 H179:L204 B179:G208 I205:K208 I209:I256 B259:D268 F259:L268 B269:L270 B271:B296 D271:D279 F271:L279 D280:L281 D282:D290 F282:L290 D291:L292 D293:J296 H297:L307 H310:L319 I320:L321 B322:L343 B345:L345 B297:G321 B258 K351:L383 B346:J387 B388:L421 B422:J425 B426:L440 B441:K447 I308:L309 B344:K344 B448:L454 B455:K458 B459:L1048576">
+    <cfRule type="expression" dxfId="0" priority="435">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43:G43 J43:L43">
-    <cfRule type="expression" dxfId="0" priority="133">
+    <cfRule type="expression" dxfId="0" priority="135">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44:G44 J44:L47 G45:G47 C45:C47">
-    <cfRule type="expression" dxfId="0" priority="167">
+    <cfRule type="expression" dxfId="0" priority="169">
       <formula>MOD($B44,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45:E47">
-    <cfRule type="expression" dxfId="0" priority="164">
+    <cfRule type="expression" dxfId="0" priority="166">
       <formula>MOD($B45,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F60 C48:C60">
+    <cfRule type="expression" dxfId="0" priority="123">
+      <formula>MOD($B48,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
     <cfRule type="expression" dxfId="0" priority="121">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
+  <conditionalFormatting sqref="D48:E60">
     <cfRule type="expression" dxfId="0" priority="119">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D48:E60">
-    <cfRule type="expression" dxfId="0" priority="117">
-      <formula>MOD($B48,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B77:B84 F77:L84">
-    <cfRule type="expression" dxfId="0" priority="163">
+    <cfRule type="expression" dxfId="0" priority="165">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85:C85 F85:L85">
-    <cfRule type="expression" dxfId="0" priority="159">
+    <cfRule type="expression" dxfId="0" priority="161">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B86:C86 F86:L86">
-    <cfRule type="expression" dxfId="0" priority="124">
+    <cfRule type="expression" dxfId="0" priority="126">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87:C92 F87:L92 I93:I104">
-    <cfRule type="expression" dxfId="0" priority="114">
+    <cfRule type="expression" dxfId="0" priority="116">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87:E92 D93:D104">
-    <cfRule type="expression" dxfId="0" priority="115">
+    <cfRule type="expression" dxfId="0" priority="117">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:C98 F93:H98 J93:L98">
-    <cfRule type="expression" dxfId="0" priority="111">
+    <cfRule type="expression" dxfId="0" priority="113">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99:C104 F99:H104 J99:L104">
-    <cfRule type="expression" dxfId="0" priority="108">
+    <cfRule type="expression" dxfId="0" priority="110">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:C105 F105:H105 J105:L105">
-    <cfRule type="expression" dxfId="0" priority="104">
+    <cfRule type="expression" dxfId="0" priority="106">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106:C106 F106:H106 J106:L106 H107:H111 C107:C111">
-    <cfRule type="expression" dxfId="0" priority="100">
+    <cfRule type="expression" dxfId="0" priority="102">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107 F107:G107 J107:L107">
-    <cfRule type="expression" dxfId="0" priority="96">
+    <cfRule type="expression" dxfId="0" priority="98">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B108 F108:G108 J108:L108">
-    <cfRule type="expression" dxfId="0" priority="92">
+    <cfRule type="expression" dxfId="0" priority="94">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B109 F109:G109 J109:L109">
-    <cfRule type="expression" dxfId="0" priority="88">
+    <cfRule type="expression" dxfId="0" priority="90">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B110 F110:G110 J110:L110">
-    <cfRule type="expression" dxfId="0" priority="84">
+    <cfRule type="expression" dxfId="0" priority="86">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111 F111:G111 J111:L111">
-    <cfRule type="expression" dxfId="0" priority="80">
+    <cfRule type="expression" dxfId="0" priority="82">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112:C112 F112:H112 J112:L112 H113:H117 C113:C117">
-    <cfRule type="expression" dxfId="0" priority="76">
+    <cfRule type="expression" dxfId="0" priority="78">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113 F113:G113 J113:L113">
-    <cfRule type="expression" dxfId="0" priority="72">
+    <cfRule type="expression" dxfId="0" priority="74">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114 F114:G114 J114:L114">
-    <cfRule type="expression" dxfId="0" priority="68">
+    <cfRule type="expression" dxfId="0" priority="70">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115 F115:G115 J115:L115">
-    <cfRule type="expression" dxfId="0" priority="64">
+    <cfRule type="expression" dxfId="0" priority="66">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B116 F116:G116 J116:L116">
-    <cfRule type="expression" dxfId="0" priority="60">
+    <cfRule type="expression" dxfId="0" priority="62">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117 F117:G117 J117:L117">
-    <cfRule type="expression" dxfId="0" priority="56">
+    <cfRule type="expression" dxfId="0" priority="58">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118:C118 F118:H118 J118:L118 H119:H123 C119:C123">
-    <cfRule type="expression" dxfId="0" priority="52">
+    <cfRule type="expression" dxfId="0" priority="54">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119 F119:G119 J119:L119">
-    <cfRule type="expression" dxfId="0" priority="48">
+    <cfRule type="expression" dxfId="0" priority="50">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120 F120:G120 J120:L120">
-    <cfRule type="expression" dxfId="0" priority="44">
+    <cfRule type="expression" dxfId="0" priority="46">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121 F121:G121 J121:L121">
-    <cfRule type="expression" dxfId="0" priority="40">
+    <cfRule type="expression" dxfId="0" priority="42">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122 F122:G122 J122:L122">
-    <cfRule type="expression" dxfId="0" priority="36">
+    <cfRule type="expression" dxfId="0" priority="38">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123 F123:G123 J123:L123">
-    <cfRule type="expression" dxfId="0" priority="32">
+    <cfRule type="expression" dxfId="0" priority="34">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B124:L133 B134">
-    <cfRule type="expression" dxfId="0" priority="162">
+    <cfRule type="expression" dxfId="0" priority="164">
       <formula>MOD($B124,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171:B172 B174:B177">
-    <cfRule type="expression" dxfId="0" priority="29">
+    <cfRule type="expression" dxfId="0" priority="31">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171:G172 J171:J172 L171:L172 F175:F177 C176:C177">
-    <cfRule type="expression" dxfId="0" priority="30">
+    <cfRule type="expression" dxfId="0" priority="32">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173:G173 J173:L173">
-    <cfRule type="expression" dxfId="0" priority="24">
+    <cfRule type="expression" dxfId="0" priority="26">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174:G174 J174:L177 G175:G177 C175:C177">
-    <cfRule type="expression" dxfId="0" priority="28">
+    <cfRule type="expression" dxfId="0" priority="30">
       <formula>MOD($B174,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D175:E177">
-    <cfRule type="expression" dxfId="0" priority="27">
+    <cfRule type="expression" dxfId="0" priority="29">
       <formula>MOD($B175,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F178 C178">
+    <cfRule type="expression" dxfId="0" priority="24">
+      <formula>MOD($B178,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J178:L178 G178 C178">
     <cfRule type="expression" dxfId="0" priority="22">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J178:L178 G178 C178">
-    <cfRule type="expression" dxfId="0" priority="20">
-      <formula>MOD($B178,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B209:D209 F209:H209 J209:L250 B210:H250">
-    <cfRule type="expression" dxfId="0" priority="17">
+    <cfRule type="expression" dxfId="0" priority="19">
       <formula>MOD($B209,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B251:H256 J251:L256">
-    <cfRule type="expression" dxfId="0" priority="16">
+    <cfRule type="expression" dxfId="0" priority="18">
       <formula>MOD($B251,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B257 B259 B261 B263 B265 B267 B269 B271 B273 B275 B277 B279 B281 B283 B285 B287 B289 B291 B293 B295">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="0" priority="16">
       <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C257:D257 F257:L257">
-    <cfRule type="expression" dxfId="0" priority="437">
+    <cfRule type="expression" dxfId="0" priority="439">
       <formula>MOD($B258,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C258:D258 I292 I290 I288 I286 I284 I282 I280 I278 I276 I274 I272 I270 I268 I266 I264 I262 I260 D268 D266 D264 D262 D260 F258:L258">
-    <cfRule type="expression" dxfId="0" priority="436">
+    <cfRule type="expression" dxfId="0" priority="438">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$432</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$458</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="72">
   <si>
     <t>id</t>
   </si>
@@ -769,6 +769,12 @@
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -779,12 +785,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5824,7 +5824,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L433"/>
+  <dimension ref="A1:L461"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="10"/>
@@ -18171,7 +18171,7 @@
     </row>
     <row r="427" customHeight="1" spans="1:12">
       <c r="A427" s="3">
-        <f t="shared" ref="A427:A432" si="17">(B427)*10000+C427+F427*100+D427*100000</f>
+        <f t="shared" ref="A427:A433" si="17">(B427)*10000+C427+F427*100+D427*100000</f>
         <v>1034100302</v>
       </c>
       <c r="B427" s="2">
@@ -18315,7 +18315,7 @@
     </row>
     <row r="433" customHeight="1" spans="1:12">
       <c r="A433" s="3">
-        <f>(B433)*10000+C433+F433*100+D433*100000</f>
+        <f t="shared" si="17"/>
         <v>1034400108</v>
       </c>
       <c r="B433" s="2">
@@ -18343,664 +18343,1412 @@
         <v>71</v>
       </c>
     </row>
+    <row r="434" customHeight="1" spans="1:12">
+      <c r="A434" s="3">
+        <f t="shared" ref="A434:A444" si="18">(B434)*10000+C434+F434*100+D434*100000</f>
+        <v>1035100301</v>
+      </c>
+      <c r="B434" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C434" s="2">
+        <v>1</v>
+      </c>
+      <c r="D434" s="2">
+        <v>1</v>
+      </c>
+      <c r="F434" s="2">
+        <v>3</v>
+      </c>
+      <c r="G434" s="11">
+        <v>2</v>
+      </c>
+      <c r="I434" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" customHeight="1" spans="1:12">
+      <c r="A435" s="3">
+        <f t="shared" si="18"/>
+        <v>1035100302</v>
+      </c>
+      <c r="B435" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C435" s="2">
+        <v>2</v>
+      </c>
+      <c r="D435" s="2">
+        <v>1</v>
+      </c>
+      <c r="F435" s="2">
+        <v>3</v>
+      </c>
+      <c r="G435" s="11">
+        <v>3</v>
+      </c>
+      <c r="I435" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" customHeight="1" spans="1:12">
+      <c r="A436" s="3">
+        <f t="shared" si="18"/>
+        <v>1035100303</v>
+      </c>
+      <c r="B436" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C436" s="2">
+        <v>3</v>
+      </c>
+      <c r="D436" s="2">
+        <v>1</v>
+      </c>
+      <c r="F436" s="2">
+        <v>3</v>
+      </c>
+      <c r="G436" s="11">
+        <v>5</v>
+      </c>
+      <c r="I436" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" customHeight="1" spans="1:12">
+      <c r="A437" s="3">
+        <f t="shared" si="18"/>
+        <v>1035100304</v>
+      </c>
+      <c r="B437" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C437" s="2">
+        <v>4</v>
+      </c>
+      <c r="D437" s="2">
+        <v>1</v>
+      </c>
+      <c r="F437" s="2">
+        <v>3</v>
+      </c>
+      <c r="G437" s="11">
+        <v>10</v>
+      </c>
+      <c r="I437" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" customHeight="1" spans="1:12">
+      <c r="A438" s="3">
+        <f t="shared" si="18"/>
+        <v>1035100305</v>
+      </c>
+      <c r="B438" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C438" s="2">
+        <v>5</v>
+      </c>
+      <c r="D438" s="2">
+        <v>1</v>
+      </c>
+      <c r="F438" s="2">
+        <v>3</v>
+      </c>
+      <c r="G438" s="11">
+        <v>50</v>
+      </c>
+      <c r="I438" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" customHeight="1" spans="1:12">
+      <c r="A439" s="3">
+        <f t="shared" si="18"/>
+        <v>1035100306</v>
+      </c>
+      <c r="B439" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C439" s="2">
+        <v>6</v>
+      </c>
+      <c r="D439" s="2">
+        <v>1</v>
+      </c>
+      <c r="F439" s="2">
+        <v>3</v>
+      </c>
+      <c r="G439" s="11">
+        <v>100</v>
+      </c>
+      <c r="I439" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" customHeight="1" spans="1:12">
+      <c r="A440" s="3">
+        <f t="shared" si="18"/>
+        <v>1035100307</v>
+      </c>
+      <c r="B440" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C440" s="2">
+        <v>7</v>
+      </c>
+      <c r="D440" s="2">
+        <v>1</v>
+      </c>
+      <c r="F440" s="2">
+        <v>3</v>
+      </c>
+      <c r="G440" s="11">
+        <v>200</v>
+      </c>
+      <c r="I440" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" customHeight="1" spans="1:12">
+      <c r="A441" s="3">
+        <f t="shared" si="18"/>
+        <v>1035400109</v>
+      </c>
+      <c r="B441" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C441" s="2">
+        <v>9</v>
+      </c>
+      <c r="D441" s="2">
+        <v>4</v>
+      </c>
+      <c r="F441" s="2">
+        <v>1</v>
+      </c>
+      <c r="G441" s="11">
+        <v>0</v>
+      </c>
+      <c r="I441" s="11">
+        <v>0</v>
+      </c>
+      <c r="K441" s="2">
+        <v>103500101</v>
+      </c>
+      <c r="L441" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="442" customHeight="1" spans="1:12">
+      <c r="A442" s="3">
+        <f t="shared" si="18"/>
+        <v>1035400110</v>
+      </c>
+      <c r="B442" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C442" s="2">
+        <v>10</v>
+      </c>
+      <c r="D442" s="2">
+        <v>4</v>
+      </c>
+      <c r="F442" s="2">
+        <v>1</v>
+      </c>
+      <c r="G442" s="11">
+        <v>0</v>
+      </c>
+      <c r="I442" s="11">
+        <v>0</v>
+      </c>
+      <c r="K442" s="2">
+        <v>103500102</v>
+      </c>
+      <c r="L442" s="13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="443" customHeight="1" spans="1:12">
+      <c r="A443" s="3">
+        <f t="shared" si="18"/>
+        <v>1035400111</v>
+      </c>
+      <c r="B443" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C443" s="2">
+        <v>11</v>
+      </c>
+      <c r="D443" s="2">
+        <v>4</v>
+      </c>
+      <c r="F443" s="2">
+        <v>1</v>
+      </c>
+      <c r="G443" s="11">
+        <v>0</v>
+      </c>
+      <c r="I443" s="11">
+        <v>0</v>
+      </c>
+      <c r="K443" s="2">
+        <v>103500103</v>
+      </c>
+      <c r="L443" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="444" customHeight="1" spans="1:12">
+      <c r="A444" s="3">
+        <f t="shared" si="18"/>
+        <v>1035400112</v>
+      </c>
+      <c r="B444" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C444" s="2">
+        <v>12</v>
+      </c>
+      <c r="D444" s="2">
+        <v>4</v>
+      </c>
+      <c r="F444" s="2">
+        <v>1</v>
+      </c>
+      <c r="G444" s="11">
+        <v>0</v>
+      </c>
+      <c r="I444" s="11">
+        <v>0</v>
+      </c>
+      <c r="K444" s="2">
+        <v>103500104</v>
+      </c>
+      <c r="L444" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="445" customHeight="1" spans="1:12">
+      <c r="A445" s="3">
+        <f>(B445)*10000+C445+F445*100+D445*100000</f>
+        <v>1035400508</v>
+      </c>
+      <c r="B445" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C445" s="2">
+        <v>8</v>
+      </c>
+      <c r="D445" s="2">
+        <v>4</v>
+      </c>
+      <c r="F445" s="2">
+        <v>5</v>
+      </c>
+      <c r="G445" s="11">
+        <v>0</v>
+      </c>
+      <c r="H445" s="11">
+        <v>30350002</v>
+      </c>
+      <c r="I445" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" customHeight="1" spans="1:12">
+      <c r="A446" s="3">
+        <f>(B446)*10000+C446+F446*100+D446*100000</f>
+        <v>1035400608</v>
+      </c>
+      <c r="B446" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C446" s="2">
+        <v>8</v>
+      </c>
+      <c r="D446" s="2">
+        <v>4</v>
+      </c>
+      <c r="F446" s="2">
+        <v>6</v>
+      </c>
+      <c r="G446" s="11">
+        <v>0</v>
+      </c>
+      <c r="H446" s="11">
+        <v>30350002</v>
+      </c>
+      <c r="I446" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" customHeight="1" spans="1:12">
+      <c r="A447" s="3">
+        <f>(B447)*10000+C447+F447*100+D447*100000</f>
+        <v>1035400114</v>
+      </c>
+      <c r="B447" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C447" s="2">
+        <v>14</v>
+      </c>
+      <c r="D447" s="2">
+        <v>4</v>
+      </c>
+      <c r="F447" s="2">
+        <v>1</v>
+      </c>
+      <c r="G447" s="11">
+        <v>0</v>
+      </c>
+      <c r="H447" s="11">
+        <v>30350001</v>
+      </c>
+      <c r="I447" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" customHeight="1" spans="1:12">
+      <c r="A448" s="3">
+        <f t="shared" ref="A448:A458" si="19">(B448)*10000+C448+F448*100+D448*100000</f>
+        <v>1035110301</v>
+      </c>
+      <c r="B448" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C448" s="2">
+        <v>1</v>
+      </c>
+      <c r="D448" s="2">
+        <v>1</v>
+      </c>
+      <c r="F448" s="2">
+        <v>3</v>
+      </c>
+      <c r="G448" s="11">
+        <v>2</v>
+      </c>
+      <c r="I448" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" customHeight="1" spans="1:12">
+      <c r="A449" s="3">
+        <f t="shared" si="19"/>
+        <v>1035110302</v>
+      </c>
+      <c r="B449" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C449" s="2">
+        <v>2</v>
+      </c>
+      <c r="D449" s="2">
+        <v>1</v>
+      </c>
+      <c r="F449" s="2">
+        <v>3</v>
+      </c>
+      <c r="G449" s="11">
+        <v>3</v>
+      </c>
+      <c r="I449" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" customHeight="1" spans="1:12">
+      <c r="A450" s="3">
+        <f t="shared" si="19"/>
+        <v>1035110303</v>
+      </c>
+      <c r="B450" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C450" s="2">
+        <v>3</v>
+      </c>
+      <c r="D450" s="2">
+        <v>1</v>
+      </c>
+      <c r="F450" s="2">
+        <v>3</v>
+      </c>
+      <c r="G450" s="11">
+        <v>5</v>
+      </c>
+      <c r="I450" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" customHeight="1" spans="1:12">
+      <c r="A451" s="3">
+        <f t="shared" si="19"/>
+        <v>1035110304</v>
+      </c>
+      <c r="B451" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C451" s="2">
+        <v>4</v>
+      </c>
+      <c r="D451" s="2">
+        <v>1</v>
+      </c>
+      <c r="F451" s="2">
+        <v>3</v>
+      </c>
+      <c r="G451" s="11">
+        <v>10</v>
+      </c>
+      <c r="I451" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" customHeight="1" spans="1:12">
+      <c r="A452" s="3">
+        <f t="shared" si="19"/>
+        <v>1035110305</v>
+      </c>
+      <c r="B452" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C452" s="2">
+        <v>5</v>
+      </c>
+      <c r="D452" s="2">
+        <v>1</v>
+      </c>
+      <c r="F452" s="2">
+        <v>3</v>
+      </c>
+      <c r="G452" s="11">
+        <v>50</v>
+      </c>
+      <c r="I452" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" customHeight="1" spans="1:12">
+      <c r="A453" s="3">
+        <f t="shared" si="19"/>
+        <v>1035110306</v>
+      </c>
+      <c r="B453" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C453" s="2">
+        <v>6</v>
+      </c>
+      <c r="D453" s="2">
+        <v>1</v>
+      </c>
+      <c r="F453" s="2">
+        <v>3</v>
+      </c>
+      <c r="G453" s="11">
+        <v>100</v>
+      </c>
+      <c r="I453" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" customHeight="1" spans="1:12">
+      <c r="A454" s="3">
+        <f t="shared" si="19"/>
+        <v>1035110307</v>
+      </c>
+      <c r="B454" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C454" s="2">
+        <v>7</v>
+      </c>
+      <c r="D454" s="2">
+        <v>1</v>
+      </c>
+      <c r="F454" s="2">
+        <v>3</v>
+      </c>
+      <c r="G454" s="11">
+        <v>200</v>
+      </c>
+      <c r="I454" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" customHeight="1" spans="1:12">
+      <c r="A455" s="3">
+        <f t="shared" si="19"/>
+        <v>1035410109</v>
+      </c>
+      <c r="B455" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C455" s="2">
+        <v>9</v>
+      </c>
+      <c r="D455" s="2">
+        <v>4</v>
+      </c>
+      <c r="F455" s="2">
+        <v>1</v>
+      </c>
+      <c r="G455" s="11">
+        <v>0</v>
+      </c>
+      <c r="I455" s="11">
+        <v>0</v>
+      </c>
+      <c r="K455" s="2">
+        <v>103501101</v>
+      </c>
+      <c r="L455" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="456" customHeight="1" spans="1:12">
+      <c r="A456" s="3">
+        <f t="shared" si="19"/>
+        <v>1035410110</v>
+      </c>
+      <c r="B456" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C456" s="2">
+        <v>10</v>
+      </c>
+      <c r="D456" s="2">
+        <v>4</v>
+      </c>
+      <c r="F456" s="2">
+        <v>1</v>
+      </c>
+      <c r="G456" s="11">
+        <v>0</v>
+      </c>
+      <c r="I456" s="11">
+        <v>0</v>
+      </c>
+      <c r="K456" s="2">
+        <v>103501102</v>
+      </c>
+      <c r="L456" s="13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="457" customHeight="1" spans="1:12">
+      <c r="A457" s="3">
+        <f t="shared" si="19"/>
+        <v>1035410111</v>
+      </c>
+      <c r="B457" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C457" s="2">
+        <v>11</v>
+      </c>
+      <c r="D457" s="2">
+        <v>4</v>
+      </c>
+      <c r="F457" s="2">
+        <v>1</v>
+      </c>
+      <c r="G457" s="11">
+        <v>0</v>
+      </c>
+      <c r="I457" s="11">
+        <v>0</v>
+      </c>
+      <c r="K457" s="2">
+        <v>103501103</v>
+      </c>
+      <c r="L457" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="458" customHeight="1" spans="1:12">
+      <c r="A458" s="3">
+        <f t="shared" si="19"/>
+        <v>1035410112</v>
+      </c>
+      <c r="B458" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C458" s="2">
+        <v>12</v>
+      </c>
+      <c r="D458" s="2">
+        <v>4</v>
+      </c>
+      <c r="F458" s="2">
+        <v>1</v>
+      </c>
+      <c r="G458" s="11">
+        <v>0</v>
+      </c>
+      <c r="I458" s="11">
+        <v>0</v>
+      </c>
+      <c r="K458" s="2">
+        <v>103501104</v>
+      </c>
+      <c r="L458" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="459" customHeight="1" spans="1:12">
+      <c r="A459" s="3">
+        <f>(B459)*10000+C459+F459*100+D459*100000</f>
+        <v>1035410508</v>
+      </c>
+      <c r="B459" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C459" s="2">
+        <v>8</v>
+      </c>
+      <c r="D459" s="2">
+        <v>4</v>
+      </c>
+      <c r="F459" s="2">
+        <v>5</v>
+      </c>
+      <c r="G459" s="11">
+        <v>0</v>
+      </c>
+      <c r="H459" s="11">
+        <v>30350102</v>
+      </c>
+      <c r="I459" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" customHeight="1" spans="1:12">
+      <c r="A460" s="3">
+        <f>(B460)*10000+C460+F460*100+D460*100000</f>
+        <v>1035410608</v>
+      </c>
+      <c r="B460" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C460" s="2">
+        <v>8</v>
+      </c>
+      <c r="D460" s="2">
+        <v>4</v>
+      </c>
+      <c r="F460" s="2">
+        <v>6</v>
+      </c>
+      <c r="G460" s="11">
+        <v>0</v>
+      </c>
+      <c r="H460" s="11">
+        <v>30350102</v>
+      </c>
+      <c r="I460" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461" customHeight="1" spans="1:12">
+      <c r="A461" s="3">
+        <f>(B461)*10000+C461+F461*100+D461*100000</f>
+        <v>1035410114</v>
+      </c>
+      <c r="B461" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C461" s="2">
+        <v>14</v>
+      </c>
+      <c r="D461" s="2">
+        <v>4</v>
+      </c>
+      <c r="F461" s="2">
+        <v>1</v>
+      </c>
+      <c r="G461" s="11">
+        <v>0</v>
+      </c>
+      <c r="H461" s="11">
+        <v>30350101</v>
+      </c>
+      <c r="I461" s="11">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L432" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L458" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="0" priority="134">
+    <cfRule type="expression" dxfId="0" priority="136">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D85:E85">
-    <cfRule type="expression" dxfId="0" priority="160">
+    <cfRule type="expression" dxfId="0" priority="162">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D86:E86">
-    <cfRule type="expression" dxfId="0" priority="125">
+    <cfRule type="expression" dxfId="0" priority="127">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105">
-    <cfRule type="duplicateValues" dxfId="1" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105:E105">
-    <cfRule type="expression" dxfId="0" priority="105">
+    <cfRule type="expression" dxfId="0" priority="107">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I105">
-    <cfRule type="expression" dxfId="0" priority="107">
+    <cfRule type="expression" dxfId="0" priority="109">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A106">
-    <cfRule type="duplicateValues" dxfId="1" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D106:E106">
-    <cfRule type="expression" dxfId="0" priority="101">
+    <cfRule type="expression" dxfId="0" priority="103">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I106">
-    <cfRule type="expression" dxfId="0" priority="103">
+    <cfRule type="expression" dxfId="0" priority="105">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="1" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D107:E107">
-    <cfRule type="expression" dxfId="0" priority="97">
+    <cfRule type="expression" dxfId="0" priority="99">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I107">
-    <cfRule type="expression" dxfId="0" priority="99">
+    <cfRule type="expression" dxfId="0" priority="101">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108">
-    <cfRule type="duplicateValues" dxfId="1" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D108:E108">
-    <cfRule type="expression" dxfId="0" priority="93">
+    <cfRule type="expression" dxfId="0" priority="95">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I108">
-    <cfRule type="expression" dxfId="0" priority="95">
+    <cfRule type="expression" dxfId="0" priority="97">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" dxfId="1" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D109:E109">
-    <cfRule type="expression" dxfId="0" priority="89">
+    <cfRule type="expression" dxfId="0" priority="91">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I109">
-    <cfRule type="expression" dxfId="0" priority="91">
+    <cfRule type="expression" dxfId="0" priority="93">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110">
-    <cfRule type="duplicateValues" dxfId="1" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D110:E110">
-    <cfRule type="expression" dxfId="0" priority="85">
+    <cfRule type="expression" dxfId="0" priority="87">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I110">
-    <cfRule type="expression" dxfId="0" priority="87">
+    <cfRule type="expression" dxfId="0" priority="89">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A111">
-    <cfRule type="duplicateValues" dxfId="1" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D111:E111">
-    <cfRule type="expression" dxfId="0" priority="81">
+    <cfRule type="expression" dxfId="0" priority="83">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I111">
-    <cfRule type="expression" dxfId="0" priority="83">
+    <cfRule type="expression" dxfId="0" priority="85">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112">
-    <cfRule type="duplicateValues" dxfId="1" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D112:E112">
-    <cfRule type="expression" dxfId="0" priority="77">
+    <cfRule type="expression" dxfId="0" priority="79">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I112">
-    <cfRule type="expression" dxfId="0" priority="79">
+    <cfRule type="expression" dxfId="0" priority="81">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A113">
-    <cfRule type="duplicateValues" dxfId="1" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D113:E113">
-    <cfRule type="expression" dxfId="0" priority="73">
+    <cfRule type="expression" dxfId="0" priority="75">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I113">
-    <cfRule type="expression" dxfId="0" priority="75">
+    <cfRule type="expression" dxfId="0" priority="77">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114">
-    <cfRule type="duplicateValues" dxfId="1" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D114:E114">
-    <cfRule type="expression" dxfId="0" priority="69">
+    <cfRule type="expression" dxfId="0" priority="71">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I114">
-    <cfRule type="expression" dxfId="0" priority="71">
+    <cfRule type="expression" dxfId="0" priority="73">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A115">
-    <cfRule type="duplicateValues" dxfId="1" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D115:E115">
-    <cfRule type="expression" dxfId="0" priority="65">
+    <cfRule type="expression" dxfId="0" priority="67">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I115">
-    <cfRule type="expression" dxfId="0" priority="67">
+    <cfRule type="expression" dxfId="0" priority="69">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A116">
-    <cfRule type="duplicateValues" dxfId="1" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D116:E116">
-    <cfRule type="expression" dxfId="0" priority="61">
+    <cfRule type="expression" dxfId="0" priority="63">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I116">
-    <cfRule type="expression" dxfId="0" priority="63">
+    <cfRule type="expression" dxfId="0" priority="65">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117">
-    <cfRule type="duplicateValues" dxfId="1" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D117:E117">
-    <cfRule type="expression" dxfId="0" priority="57">
+    <cfRule type="expression" dxfId="0" priority="59">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I117">
-    <cfRule type="expression" dxfId="0" priority="59">
+    <cfRule type="expression" dxfId="0" priority="61">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A118">
-    <cfRule type="duplicateValues" dxfId="1" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D118:E118">
-    <cfRule type="expression" dxfId="0" priority="53">
+    <cfRule type="expression" dxfId="0" priority="55">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I118">
-    <cfRule type="expression" dxfId="0" priority="55">
+    <cfRule type="expression" dxfId="0" priority="57">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A119">
-    <cfRule type="duplicateValues" dxfId="1" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D119:E119">
-    <cfRule type="expression" dxfId="0" priority="49">
+    <cfRule type="expression" dxfId="0" priority="51">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I119">
-    <cfRule type="expression" dxfId="0" priority="51">
+    <cfRule type="expression" dxfId="0" priority="53">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A120">
-    <cfRule type="duplicateValues" dxfId="1" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D120:E120">
-    <cfRule type="expression" dxfId="0" priority="45">
+    <cfRule type="expression" dxfId="0" priority="47">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I120">
-    <cfRule type="expression" dxfId="0" priority="47">
+    <cfRule type="expression" dxfId="0" priority="49">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A121">
-    <cfRule type="duplicateValues" dxfId="1" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D121:E121">
-    <cfRule type="expression" dxfId="0" priority="41">
+    <cfRule type="expression" dxfId="0" priority="43">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I121">
-    <cfRule type="expression" dxfId="0" priority="43">
+    <cfRule type="expression" dxfId="0" priority="45">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A122">
-    <cfRule type="duplicateValues" dxfId="1" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D122:E122">
-    <cfRule type="expression" dxfId="0" priority="37">
+    <cfRule type="expression" dxfId="0" priority="39">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I122">
-    <cfRule type="expression" dxfId="0" priority="39">
+    <cfRule type="expression" dxfId="0" priority="41">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A123">
-    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D123:E123">
-    <cfRule type="expression" dxfId="0" priority="33">
+    <cfRule type="expression" dxfId="0" priority="35">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I123">
-    <cfRule type="expression" dxfId="0" priority="35">
+    <cfRule type="expression" dxfId="0" priority="37">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C134:L134">
-    <cfRule type="expression" dxfId="0" priority="161">
+    <cfRule type="expression" dxfId="0" priority="163">
       <formula>MOD($B134,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="expression" dxfId="0" priority="25">
+    <cfRule type="expression" dxfId="0" priority="27">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A178">
-    <cfRule type="duplicateValues" dxfId="1" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B178">
+    <cfRule type="expression" dxfId="0" priority="23">
+      <formula>MOD($B178,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D178:E178">
     <cfRule type="expression" dxfId="0" priority="21">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D178:E178">
-    <cfRule type="expression" dxfId="0" priority="19">
-      <formula>MOD($B178,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H309">
-    <cfRule type="expression" dxfId="0" priority="439">
+    <cfRule type="expression" dxfId="0" priority="441">
       <formula>MOD($B308,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H321">
-    <cfRule type="expression" dxfId="0" priority="438">
+    <cfRule type="expression" dxfId="0" priority="440">
       <formula>MOD($B320,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L346">
-    <cfRule type="expression" dxfId="0" priority="440">
+    <cfRule type="expression" dxfId="0" priority="442">
       <formula>MOD($B350,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:A60">
-    <cfRule type="duplicateValues" dxfId="1" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A87:A92">
-    <cfRule type="duplicateValues" dxfId="1" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A93:A98">
-    <cfRule type="duplicateValues" dxfId="1" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99:A104">
-    <cfRule type="duplicateValues" dxfId="1" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A135:A177">
-    <cfRule type="duplicateValues" dxfId="1" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A209:A433">
-    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
+  <conditionalFormatting sqref="A209:A461">
+    <cfRule type="duplicateValues" dxfId="1" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B60">
-    <cfRule type="expression" dxfId="0" priority="120">
+    <cfRule type="expression" dxfId="0" priority="122">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C84">
-    <cfRule type="expression" dxfId="0" priority="123">
+    <cfRule type="expression" dxfId="0" priority="125">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C271:C281">
-    <cfRule type="expression" dxfId="0" priority="12">
+    <cfRule type="expression" dxfId="0" priority="14">
       <formula>MOD($B271,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C282:C296">
-    <cfRule type="expression" dxfId="0" priority="10">
+    <cfRule type="expression" dxfId="0" priority="12">
       <formula>MOD($B282,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E93:E98">
-    <cfRule type="expression" dxfId="0" priority="112">
+    <cfRule type="expression" dxfId="0" priority="114">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E99:E104">
-    <cfRule type="expression" dxfId="0" priority="109">
+    <cfRule type="expression" dxfId="0" priority="111">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E257:E268">
-    <cfRule type="expression" dxfId="0" priority="13">
+    <cfRule type="expression" dxfId="0" priority="15">
       <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E271:E279">
-    <cfRule type="expression" dxfId="0" priority="11">
+    <cfRule type="expression" dxfId="0" priority="13">
       <formula>MOD($B271,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E282:E290">
-    <cfRule type="expression" dxfId="0" priority="9">
+    <cfRule type="expression" dxfId="0" priority="11">
       <formula>MOD($B282,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39:K42">
-    <cfRule type="duplicateValues" dxfId="2" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K169:K172">
-    <cfRule type="duplicateValues" dxfId="2" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K293:K296">
-    <cfRule type="expression" dxfId="0" priority="7">
+    <cfRule type="expression" dxfId="0" priority="9">
       <formula>MOD($B293,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K347:K350">
-    <cfRule type="expression" dxfId="0" priority="5">
+    <cfRule type="expression" dxfId="0" priority="7">
       <formula>MOD($B346,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K384:K387">
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="0" priority="5">
       <formula>MOD($B384,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K422:K425">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>MOD($B422,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L205:L208">
-    <cfRule type="expression" dxfId="0" priority="18">
+    <cfRule type="expression" dxfId="0" priority="20">
       <formula>MOD($B205,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L293:L296">
-    <cfRule type="expression" dxfId="0" priority="8">
+    <cfRule type="expression" dxfId="0" priority="10">
       <formula>MOD($B293,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L347:L350">
-    <cfRule type="expression" dxfId="0" priority="6">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>MOD($B346,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L384:L387">
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="0" priority="6">
       <formula>MOD($B384,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L422:L425">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>MOD($B422,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A434:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="435"/>
+  <conditionalFormatting sqref="L441:L447">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>MOD($B441,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L455:L458">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD($B455,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A462:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="437"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L4">
-    <cfRule type="expression" dxfId="0" priority="434">
+    <cfRule type="expression" dxfId="0" priority="436">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41:B42 B44:B47">
-    <cfRule type="expression" dxfId="0" priority="168">
+    <cfRule type="expression" dxfId="0" priority="170">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 H179:L204 B179:G208 I205:K208 I209:I256 B259:D268 F259:L268 B269:L270 B271:B296 D271:D279 F271:L279 D280:L281 D282:D290 F282:L290 D291:L292 D293:J296 H297:L307 H310:L319 I320:L321 B322:L343 B345:L345 B297:G321 B258 K351:L383 B346:J387 B388:L421 B422:J425 B426:L1048576 I308:L309 B344:K344">
-    <cfRule type="expression" dxfId="0" priority="433">
+  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 H179:L204 B179:G208 I205:K208 I209:I256 B259:D268 F259:L268 B269:L270 B271:B296 D271:D279 F271:L279 D280:L281 D282:D290 F282:L290 D291:L292 D293:J296 H297:L307 H310:L319 I320:L321 B322:L343 B345:L345 B297:G321 B258 K351:L383 B346:J387 B388:L421 B422:J425 B426:L440 B441:K447 I308:L309 B344:K344 B448:L454 B455:K458 B459:L1048576">
+    <cfRule type="expression" dxfId="0" priority="435">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43:G43 J43:L43">
-    <cfRule type="expression" dxfId="0" priority="133">
+    <cfRule type="expression" dxfId="0" priority="135">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44:G44 J44:L47 G45:G47 C45:C47">
-    <cfRule type="expression" dxfId="0" priority="167">
+    <cfRule type="expression" dxfId="0" priority="169">
       <formula>MOD($B44,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45:E47">
-    <cfRule type="expression" dxfId="0" priority="164">
+    <cfRule type="expression" dxfId="0" priority="166">
       <formula>MOD($B45,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F60 C48:C60">
+    <cfRule type="expression" dxfId="0" priority="123">
+      <formula>MOD($B48,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
     <cfRule type="expression" dxfId="0" priority="121">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
+  <conditionalFormatting sqref="D48:E60">
     <cfRule type="expression" dxfId="0" priority="119">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D48:E60">
-    <cfRule type="expression" dxfId="0" priority="117">
-      <formula>MOD($B48,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B77:B84 F77:L84">
-    <cfRule type="expression" dxfId="0" priority="163">
+    <cfRule type="expression" dxfId="0" priority="165">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85:C85 F85:L85">
-    <cfRule type="expression" dxfId="0" priority="159">
+    <cfRule type="expression" dxfId="0" priority="161">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B86:C86 F86:L86">
-    <cfRule type="expression" dxfId="0" priority="124">
+    <cfRule type="expression" dxfId="0" priority="126">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87:C92 F87:L92 I93:I104">
-    <cfRule type="expression" dxfId="0" priority="114">
+    <cfRule type="expression" dxfId="0" priority="116">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87:E92 D93:D104">
-    <cfRule type="expression" dxfId="0" priority="115">
+    <cfRule type="expression" dxfId="0" priority="117">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:C98 F93:H98 J93:L98">
-    <cfRule type="expression" dxfId="0" priority="111">
+    <cfRule type="expression" dxfId="0" priority="113">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99:C104 F99:H104 J99:L104">
-    <cfRule type="expression" dxfId="0" priority="108">
+    <cfRule type="expression" dxfId="0" priority="110">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:C105 F105:H105 J105:L105">
-    <cfRule type="expression" dxfId="0" priority="104">
+    <cfRule type="expression" dxfId="0" priority="106">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106:C106 F106:H106 J106:L106 H107:H111 C107:C111">
-    <cfRule type="expression" dxfId="0" priority="100">
+    <cfRule type="expression" dxfId="0" priority="102">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107 F107:G107 J107:L107">
-    <cfRule type="expression" dxfId="0" priority="96">
+    <cfRule type="expression" dxfId="0" priority="98">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B108 F108:G108 J108:L108">
-    <cfRule type="expression" dxfId="0" priority="92">
+    <cfRule type="expression" dxfId="0" priority="94">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B109 F109:G109 J109:L109">
-    <cfRule type="expression" dxfId="0" priority="88">
+    <cfRule type="expression" dxfId="0" priority="90">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B110 F110:G110 J110:L110">
-    <cfRule type="expression" dxfId="0" priority="84">
+    <cfRule type="expression" dxfId="0" priority="86">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111 F111:G111 J111:L111">
-    <cfRule type="expression" dxfId="0" priority="80">
+    <cfRule type="expression" dxfId="0" priority="82">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112:C112 F112:H112 J112:L112 H113:H117 C113:C117">
-    <cfRule type="expression" dxfId="0" priority="76">
+    <cfRule type="expression" dxfId="0" priority="78">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113 F113:G113 J113:L113">
-    <cfRule type="expression" dxfId="0" priority="72">
+    <cfRule type="expression" dxfId="0" priority="74">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114 F114:G114 J114:L114">
-    <cfRule type="expression" dxfId="0" priority="68">
+    <cfRule type="expression" dxfId="0" priority="70">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115 F115:G115 J115:L115">
-    <cfRule type="expression" dxfId="0" priority="64">
+    <cfRule type="expression" dxfId="0" priority="66">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B116 F116:G116 J116:L116">
-    <cfRule type="expression" dxfId="0" priority="60">
+    <cfRule type="expression" dxfId="0" priority="62">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117 F117:G117 J117:L117">
-    <cfRule type="expression" dxfId="0" priority="56">
+    <cfRule type="expression" dxfId="0" priority="58">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118:C118 F118:H118 J118:L118 H119:H123 C119:C123">
-    <cfRule type="expression" dxfId="0" priority="52">
+    <cfRule type="expression" dxfId="0" priority="54">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119 F119:G119 J119:L119">
-    <cfRule type="expression" dxfId="0" priority="48">
+    <cfRule type="expression" dxfId="0" priority="50">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120 F120:G120 J120:L120">
-    <cfRule type="expression" dxfId="0" priority="44">
+    <cfRule type="expression" dxfId="0" priority="46">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121 F121:G121 J121:L121">
-    <cfRule type="expression" dxfId="0" priority="40">
+    <cfRule type="expression" dxfId="0" priority="42">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122 F122:G122 J122:L122">
-    <cfRule type="expression" dxfId="0" priority="36">
+    <cfRule type="expression" dxfId="0" priority="38">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123 F123:G123 J123:L123">
-    <cfRule type="expression" dxfId="0" priority="32">
+    <cfRule type="expression" dxfId="0" priority="34">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B124:L133 B134">
-    <cfRule type="expression" dxfId="0" priority="162">
+    <cfRule type="expression" dxfId="0" priority="164">
       <formula>MOD($B124,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171:B172 B174:B177">
-    <cfRule type="expression" dxfId="0" priority="29">
+    <cfRule type="expression" dxfId="0" priority="31">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171:G172 J171:J172 L171:L172 F175:F177 C176:C177">
-    <cfRule type="expression" dxfId="0" priority="30">
+    <cfRule type="expression" dxfId="0" priority="32">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173:G173 J173:L173">
-    <cfRule type="expression" dxfId="0" priority="24">
+    <cfRule type="expression" dxfId="0" priority="26">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174:G174 J174:L177 G175:G177 C175:C177">
-    <cfRule type="expression" dxfId="0" priority="28">
+    <cfRule type="expression" dxfId="0" priority="30">
       <formula>MOD($B174,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D175:E177">
-    <cfRule type="expression" dxfId="0" priority="27">
+    <cfRule type="expression" dxfId="0" priority="29">
       <formula>MOD($B175,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F178 C178">
+    <cfRule type="expression" dxfId="0" priority="24">
+      <formula>MOD($B178,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J178:L178 G178 C178">
     <cfRule type="expression" dxfId="0" priority="22">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J178:L178 G178 C178">
-    <cfRule type="expression" dxfId="0" priority="20">
-      <formula>MOD($B178,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B209:D209 F209:H209 J209:L250 B210:H250">
-    <cfRule type="expression" dxfId="0" priority="17">
+    <cfRule type="expression" dxfId="0" priority="19">
       <formula>MOD($B209,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B251:H256 J251:L256">
-    <cfRule type="expression" dxfId="0" priority="16">
+    <cfRule type="expression" dxfId="0" priority="18">
       <formula>MOD($B251,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B257 B259 B261 B263 B265 B267 B269 B271 B273 B275 B277 B279 B281 B283 B285 B287 B289 B291 B293 B295">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="0" priority="16">
       <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C257:D257 F257:L257">
-    <cfRule type="expression" dxfId="0" priority="437">
+    <cfRule type="expression" dxfId="0" priority="439">
       <formula>MOD($B258,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C258:D258 I292 I290 I288 I286 I284 I282 I280 I278 I276 I274 I272 I270 I268 I266 I264 I262 I260 D268 D266 D264 D262 D260 F258:L258">
-    <cfRule type="expression" dxfId="0" priority="436">
+    <cfRule type="expression" dxfId="0" priority="438">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$458</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$469</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="73">
   <si>
     <t>id</t>
   </si>
@@ -525,6 +525,9 @@
   </si>
   <si>
     <t>触发全屏奖</t>
+  </si>
+  <si>
+    <t>Jackpot</t>
   </si>
 </sst>
 </file>
@@ -769,18 +772,18 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -5824,7 +5827,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L461"/>
+  <dimension ref="A1:L469"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="10"/>
@@ -18345,7 +18348,7 @@
     </row>
     <row r="434" customHeight="1" spans="1:12">
       <c r="A434" s="3">
-        <f t="shared" ref="A434:A444" si="18">(B434)*10000+C434+F434*100+D434*100000</f>
+        <f t="shared" ref="A434:A447" si="18">(B434)*10000+C434+F434*100+D434*100000</f>
         <v>1035100301</v>
       </c>
       <c r="B434" s="2">
@@ -18633,7 +18636,7 @@
     </row>
     <row r="445" customHeight="1" spans="1:12">
       <c r="A445" s="3">
-        <f>(B445)*10000+C445+F445*100+D445*100000</f>
+        <f t="shared" si="18"/>
         <v>1035400508</v>
       </c>
       <c r="B445" s="2">
@@ -18660,7 +18663,7 @@
     </row>
     <row r="446" customHeight="1" spans="1:12">
       <c r="A446" s="3">
-        <f>(B446)*10000+C446+F446*100+D446*100000</f>
+        <f t="shared" si="18"/>
         <v>1035400608</v>
       </c>
       <c r="B446" s="2">
@@ -18687,7 +18690,7 @@
     </row>
     <row r="447" customHeight="1" spans="1:12">
       <c r="A447" s="3">
-        <f>(B447)*10000+C447+F447*100+D447*100000</f>
+        <f t="shared" si="18"/>
         <v>1035400114</v>
       </c>
       <c r="B447" s="2">
@@ -18714,7 +18717,7 @@
     </row>
     <row r="448" customHeight="1" spans="1:12">
       <c r="A448" s="3">
-        <f t="shared" ref="A448:A458" si="19">(B448)*10000+C448+F448*100+D448*100000</f>
+        <f t="shared" ref="A448:A461" si="19">(B448)*10000+C448+F448*100+D448*100000</f>
         <v>1035110301</v>
       </c>
       <c r="B448" s="2">
@@ -19002,7 +19005,7 @@
     </row>
     <row r="459" customHeight="1" spans="1:12">
       <c r="A459" s="3">
-        <f>(B459)*10000+C459+F459*100+D459*100000</f>
+        <f t="shared" si="19"/>
         <v>1035410508</v>
       </c>
       <c r="B459" s="2">
@@ -19029,7 +19032,7 @@
     </row>
     <row r="460" customHeight="1" spans="1:12">
       <c r="A460" s="3">
-        <f>(B460)*10000+C460+F460*100+D460*100000</f>
+        <f t="shared" si="19"/>
         <v>1035410608</v>
       </c>
       <c r="B460" s="2">
@@ -19056,7 +19059,7 @@
     </row>
     <row r="461" customHeight="1" spans="1:12">
       <c r="A461" s="3">
-        <f>(B461)*10000+C461+F461*100+D461*100000</f>
+        <f t="shared" si="19"/>
         <v>1035410114</v>
       </c>
       <c r="B461" s="2">
@@ -19081,8 +19084,206 @@
         <v>0</v>
       </c>
     </row>
+    <row r="462" customHeight="1" spans="1:12">
+      <c r="A462" s="3">
+        <f t="shared" ref="A462:A469" si="20">(B462)*10000+C462+F462*100+D462*100000</f>
+        <v>1036100301</v>
+      </c>
+      <c r="B462" s="2">
+        <v>103600</v>
+      </c>
+      <c r="C462" s="2">
+        <v>1</v>
+      </c>
+      <c r="D462" s="2">
+        <v>1</v>
+      </c>
+      <c r="F462" s="2">
+        <v>3</v>
+      </c>
+      <c r="G462" s="11">
+        <v>3</v>
+      </c>
+      <c r="I462" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" customHeight="1" spans="1:12">
+      <c r="A463" s="3">
+        <f t="shared" si="20"/>
+        <v>1036100302</v>
+      </c>
+      <c r="B463" s="2">
+        <v>103600</v>
+      </c>
+      <c r="C463" s="2">
+        <v>2</v>
+      </c>
+      <c r="D463" s="2">
+        <v>1</v>
+      </c>
+      <c r="F463" s="2">
+        <v>3</v>
+      </c>
+      <c r="G463" s="11">
+        <v>5</v>
+      </c>
+      <c r="I463" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464" customHeight="1" spans="1:12">
+      <c r="A464" s="3">
+        <f t="shared" si="20"/>
+        <v>1036100303</v>
+      </c>
+      <c r="B464" s="2">
+        <v>103600</v>
+      </c>
+      <c r="C464" s="2">
+        <v>3</v>
+      </c>
+      <c r="D464" s="2">
+        <v>1</v>
+      </c>
+      <c r="F464" s="2">
+        <v>3</v>
+      </c>
+      <c r="G464" s="11">
+        <v>15</v>
+      </c>
+      <c r="I464" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465" customHeight="1" spans="1:12">
+      <c r="A465" s="3">
+        <f t="shared" si="20"/>
+        <v>1036100304</v>
+      </c>
+      <c r="B465" s="2">
+        <v>103600</v>
+      </c>
+      <c r="C465" s="2">
+        <v>4</v>
+      </c>
+      <c r="D465" s="2">
+        <v>1</v>
+      </c>
+      <c r="F465" s="2">
+        <v>3</v>
+      </c>
+      <c r="G465" s="11">
+        <v>30</v>
+      </c>
+      <c r="I465" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" customHeight="1" spans="1:12">
+      <c r="A466" s="3">
+        <f t="shared" si="20"/>
+        <v>1036100305</v>
+      </c>
+      <c r="B466" s="2">
+        <v>103600</v>
+      </c>
+      <c r="C466" s="2">
+        <v>5</v>
+      </c>
+      <c r="D466" s="2">
+        <v>1</v>
+      </c>
+      <c r="F466" s="2">
+        <v>3</v>
+      </c>
+      <c r="G466" s="11">
+        <v>50</v>
+      </c>
+      <c r="I466" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" customHeight="1" spans="1:12">
+      <c r="A467" s="3">
+        <f t="shared" si="20"/>
+        <v>1036100306</v>
+      </c>
+      <c r="B467" s="2">
+        <v>103600</v>
+      </c>
+      <c r="C467" s="2">
+        <v>6</v>
+      </c>
+      <c r="D467" s="2">
+        <v>1</v>
+      </c>
+      <c r="F467" s="2">
+        <v>3</v>
+      </c>
+      <c r="G467" s="11">
+        <v>100</v>
+      </c>
+      <c r="I467" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" customHeight="1" spans="1:12">
+      <c r="A468" s="3">
+        <f t="shared" si="20"/>
+        <v>1036100307</v>
+      </c>
+      <c r="B468" s="2">
+        <v>103600</v>
+      </c>
+      <c r="C468" s="2">
+        <v>7</v>
+      </c>
+      <c r="D468" s="2">
+        <v>1</v>
+      </c>
+      <c r="F468" s="2">
+        <v>3</v>
+      </c>
+      <c r="G468" s="11">
+        <v>300</v>
+      </c>
+      <c r="I468" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" customHeight="1" spans="1:12">
+      <c r="A469" s="3">
+        <f t="shared" si="20"/>
+        <v>1036400308</v>
+      </c>
+      <c r="B469" s="2">
+        <v>103600</v>
+      </c>
+      <c r="C469" s="2">
+        <v>8</v>
+      </c>
+      <c r="D469" s="2">
+        <v>4</v>
+      </c>
+      <c r="F469" s="2">
+        <v>3</v>
+      </c>
+      <c r="G469" s="11">
+        <v>0</v>
+      </c>
+      <c r="I469" s="11">
+        <v>0</v>
+      </c>
+      <c r="K469" s="2">
+        <v>103600101</v>
+      </c>
+      <c r="L469" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L458" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L469" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">
@@ -19400,7 +19601,7 @@
   <conditionalFormatting sqref="A135:A177">
     <cfRule type="duplicateValues" dxfId="1" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A209:A461">
+  <conditionalFormatting sqref="A209:A469">
     <cfRule type="duplicateValues" dxfId="1" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B60">
@@ -19509,7 +19710,7 @@
       <formula>MOD($B455,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A462:A1048576">
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A470:A1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="437"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L4">
@@ -19522,7 +19723,7 @@
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 H179:L204 B179:G208 I205:K208 I209:I256 B259:D268 F259:L268 B269:L270 B271:B296 D271:D279 F271:L279 D280:L281 D282:D290 F282:L290 D291:L292 D293:J296 H297:L307 H310:L319 I320:L321 B322:L343 B345:L345 B297:G321 B258 K351:L383 B346:J387 B388:L421 B422:J425 B426:L440 B441:K447 I308:L309 B344:K344 B448:L454 B455:K458 B459:L1048576">
+  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45 C46:C47 F46:F47 B61:L76 D77:E84 B179:L204 B205:G208 I205:K208 I209:I256 B258 B259:D268 F259:L268 B269:L270 B271:B279 D271:D279 F271:L279 B280:B281 D280:L281 B282:B290 D282:D290 F282:L290 B291:B292 D291:L292 B293:B296 D293:J296 B297:L307 B308:G309 I308:L309 B310:L319 B320:G321 I320:L321 B322:L343 B344:K344 B345:L345 B346:J350 B351:L383 B384:J387 B388:L421 B422:J425 B426:L440 B441:K447 B448:L454 B455:K458 B459:L1048576">
     <cfRule type="expression" dxfId="0" priority="435">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="72">
   <si>
     <t>id</t>
   </si>
@@ -522,9 +522,6 @@
   </si>
   <si>
     <t>+1免费符号</t>
-  </si>
-  <si>
-    <t>触发全屏奖</t>
   </si>
   <si>
     <t>Jackpot</t>
@@ -18318,44 +18315,38 @@
     </row>
     <row r="433" customHeight="1" spans="1:12">
       <c r="A433" s="3">
-        <f t="shared" si="17"/>
-        <v>1034400108</v>
+        <f t="shared" ref="A433:A446" si="18">(B433)*10000+C433+F433*100+D433*100000</f>
+        <v>1035100301</v>
       </c>
       <c r="B433" s="2">
-        <v>103400</v>
+        <v>103500</v>
       </c>
       <c r="C433" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D433" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F433" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G433" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I433" s="11">
         <v>0</v>
-      </c>
-      <c r="K433" s="2">
-        <v>103400101</v>
-      </c>
-      <c r="L433" s="13" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="434" customHeight="1" spans="1:12">
       <c r="A434" s="3">
-        <f t="shared" ref="A434:A447" si="18">(B434)*10000+C434+F434*100+D434*100000</f>
-        <v>1035100301</v>
+        <f t="shared" si="18"/>
+        <v>1035100302</v>
       </c>
       <c r="B434" s="2">
         <v>103500</v>
       </c>
       <c r="C434" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D434" s="2">
         <v>1</v>
@@ -18364,7 +18355,7 @@
         <v>3</v>
       </c>
       <c r="G434" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I434" s="11">
         <v>0</v>
@@ -18373,13 +18364,13 @@
     <row r="435" customHeight="1" spans="1:12">
       <c r="A435" s="3">
         <f t="shared" si="18"/>
-        <v>1035100302</v>
+        <v>1035100303</v>
       </c>
       <c r="B435" s="2">
         <v>103500</v>
       </c>
       <c r="C435" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D435" s="2">
         <v>1</v>
@@ -18388,7 +18379,7 @@
         <v>3</v>
       </c>
       <c r="G435" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I435" s="11">
         <v>0</v>
@@ -18397,13 +18388,13 @@
     <row r="436" customHeight="1" spans="1:12">
       <c r="A436" s="3">
         <f t="shared" si="18"/>
-        <v>1035100303</v>
+        <v>1035100304</v>
       </c>
       <c r="B436" s="2">
         <v>103500</v>
       </c>
       <c r="C436" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D436" s="2">
         <v>1</v>
@@ -18412,7 +18403,7 @@
         <v>3</v>
       </c>
       <c r="G436" s="11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I436" s="11">
         <v>0</v>
@@ -18421,13 +18412,13 @@
     <row r="437" customHeight="1" spans="1:12">
       <c r="A437" s="3">
         <f t="shared" si="18"/>
-        <v>1035100304</v>
+        <v>1035100305</v>
       </c>
       <c r="B437" s="2">
         <v>103500</v>
       </c>
       <c r="C437" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D437" s="2">
         <v>1</v>
@@ -18436,7 +18427,7 @@
         <v>3</v>
       </c>
       <c r="G437" s="11">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I437" s="11">
         <v>0</v>
@@ -18445,13 +18436,13 @@
     <row r="438" customHeight="1" spans="1:12">
       <c r="A438" s="3">
         <f t="shared" si="18"/>
-        <v>1035100305</v>
+        <v>1035100306</v>
       </c>
       <c r="B438" s="2">
         <v>103500</v>
       </c>
       <c r="C438" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D438" s="2">
         <v>1</v>
@@ -18460,7 +18451,7 @@
         <v>3</v>
       </c>
       <c r="G438" s="11">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I438" s="11">
         <v>0</v>
@@ -18469,13 +18460,13 @@
     <row r="439" customHeight="1" spans="1:12">
       <c r="A439" s="3">
         <f t="shared" si="18"/>
-        <v>1035100306</v>
+        <v>1035100307</v>
       </c>
       <c r="B439" s="2">
         <v>103500</v>
       </c>
       <c r="C439" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D439" s="2">
         <v>1</v>
@@ -18484,7 +18475,7 @@
         <v>3</v>
       </c>
       <c r="G439" s="11">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I439" s="11">
         <v>0</v>
@@ -18493,37 +18484,43 @@
     <row r="440" customHeight="1" spans="1:12">
       <c r="A440" s="3">
         <f t="shared" si="18"/>
-        <v>1035100307</v>
+        <v>1035400109</v>
       </c>
       <c r="B440" s="2">
         <v>103500</v>
       </c>
       <c r="C440" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D440" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F440" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G440" s="11">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I440" s="11">
         <v>0</v>
+      </c>
+      <c r="K440" s="2">
+        <v>103500101</v>
+      </c>
+      <c r="L440" s="13" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="441" customHeight="1" spans="1:12">
       <c r="A441" s="3">
         <f t="shared" si="18"/>
-        <v>1035400109</v>
+        <v>1035400110</v>
       </c>
       <c r="B441" s="2">
         <v>103500</v>
       </c>
       <c r="C441" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D441" s="2">
         <v>4</v>
@@ -18538,22 +18535,22 @@
         <v>0</v>
       </c>
       <c r="K441" s="2">
-        <v>103500101</v>
+        <v>103500102</v>
       </c>
       <c r="L441" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="442" customHeight="1" spans="1:12">
       <c r="A442" s="3">
         <f t="shared" si="18"/>
-        <v>1035400110</v>
+        <v>1035400111</v>
       </c>
       <c r="B442" s="2">
         <v>103500</v>
       </c>
       <c r="C442" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D442" s="2">
         <v>4</v>
@@ -18568,22 +18565,22 @@
         <v>0</v>
       </c>
       <c r="K442" s="2">
-        <v>103500102</v>
+        <v>103500103</v>
       </c>
       <c r="L442" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="443" customHeight="1" spans="1:12">
       <c r="A443" s="3">
         <f t="shared" si="18"/>
-        <v>1035400111</v>
+        <v>1035400112</v>
       </c>
       <c r="B443" s="2">
         <v>103500</v>
       </c>
       <c r="C443" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D443" s="2">
         <v>4</v>
@@ -18598,46 +18595,43 @@
         <v>0</v>
       </c>
       <c r="K443" s="2">
-        <v>103500103</v>
+        <v>103500104</v>
       </c>
       <c r="L443" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="444" customHeight="1" spans="1:12">
       <c r="A444" s="3">
         <f t="shared" si="18"/>
-        <v>1035400112</v>
+        <v>1035400508</v>
       </c>
       <c r="B444" s="2">
         <v>103500</v>
       </c>
       <c r="C444" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D444" s="2">
         <v>4</v>
       </c>
       <c r="F444" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G444" s="11">
         <v>0</v>
       </c>
+      <c r="H444" s="11">
+        <v>30350002</v>
+      </c>
       <c r="I444" s="11">
         <v>0</v>
-      </c>
-      <c r="K444" s="2">
-        <v>103500104</v>
-      </c>
-      <c r="L444" s="13" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="445" customHeight="1" spans="1:12">
       <c r="A445" s="3">
         <f t="shared" si="18"/>
-        <v>1035400508</v>
+        <v>1035400608</v>
       </c>
       <c r="B445" s="2">
         <v>103500</v>
@@ -18649,7 +18643,7 @@
         <v>4</v>
       </c>
       <c r="F445" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G445" s="11">
         <v>0</v>
@@ -18664,25 +18658,25 @@
     <row r="446" customHeight="1" spans="1:12">
       <c r="A446" s="3">
         <f t="shared" si="18"/>
-        <v>1035400608</v>
+        <v>1035400114</v>
       </c>
       <c r="B446" s="2">
         <v>103500</v>
       </c>
       <c r="C446" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D446" s="2">
         <v>4</v>
       </c>
       <c r="F446" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G446" s="11">
         <v>0</v>
       </c>
       <c r="H446" s="11">
-        <v>30350002</v>
+        <v>30350001</v>
       </c>
       <c r="I446" s="11">
         <v>0</v>
@@ -18690,26 +18684,23 @@
     </row>
     <row r="447" customHeight="1" spans="1:12">
       <c r="A447" s="3">
-        <f t="shared" si="18"/>
-        <v>1035400114</v>
+        <f t="shared" ref="A447:A460" si="19">(B447)*10000+C447+F447*100+D447*100000</f>
+        <v>1035110301</v>
       </c>
       <c r="B447" s="2">
-        <v>103500</v>
+        <v>103501</v>
       </c>
       <c r="C447" s="2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D447" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F447" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G447" s="11">
-        <v>0</v>
-      </c>
-      <c r="H447" s="11">
-        <v>30350001</v>
+        <v>2</v>
       </c>
       <c r="I447" s="11">
         <v>0</v>
@@ -18717,14 +18708,14 @@
     </row>
     <row r="448" customHeight="1" spans="1:12">
       <c r="A448" s="3">
-        <f t="shared" ref="A448:A461" si="19">(B448)*10000+C448+F448*100+D448*100000</f>
-        <v>1035110301</v>
+        <f t="shared" si="19"/>
+        <v>1035110302</v>
       </c>
       <c r="B448" s="2">
         <v>103501</v>
       </c>
       <c r="C448" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D448" s="2">
         <v>1</v>
@@ -18733,7 +18724,7 @@
         <v>3</v>
       </c>
       <c r="G448" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I448" s="11">
         <v>0</v>
@@ -18742,13 +18733,13 @@
     <row r="449" customHeight="1" spans="1:12">
       <c r="A449" s="3">
         <f t="shared" si="19"/>
-        <v>1035110302</v>
+        <v>1035110303</v>
       </c>
       <c r="B449" s="2">
         <v>103501</v>
       </c>
       <c r="C449" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D449" s="2">
         <v>1</v>
@@ -18757,7 +18748,7 @@
         <v>3</v>
       </c>
       <c r="G449" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I449" s="11">
         <v>0</v>
@@ -18766,13 +18757,13 @@
     <row r="450" customHeight="1" spans="1:12">
       <c r="A450" s="3">
         <f t="shared" si="19"/>
-        <v>1035110303</v>
+        <v>1035110304</v>
       </c>
       <c r="B450" s="2">
         <v>103501</v>
       </c>
       <c r="C450" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D450" s="2">
         <v>1</v>
@@ -18781,7 +18772,7 @@
         <v>3</v>
       </c>
       <c r="G450" s="11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I450" s="11">
         <v>0</v>
@@ -18790,13 +18781,13 @@
     <row r="451" customHeight="1" spans="1:12">
       <c r="A451" s="3">
         <f t="shared" si="19"/>
-        <v>1035110304</v>
+        <v>1035110305</v>
       </c>
       <c r="B451" s="2">
         <v>103501</v>
       </c>
       <c r="C451" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D451" s="2">
         <v>1</v>
@@ -18805,7 +18796,7 @@
         <v>3</v>
       </c>
       <c r="G451" s="11">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I451" s="11">
         <v>0</v>
@@ -18814,13 +18805,13 @@
     <row r="452" customHeight="1" spans="1:12">
       <c r="A452" s="3">
         <f t="shared" si="19"/>
-        <v>1035110305</v>
+        <v>1035110306</v>
       </c>
       <c r="B452" s="2">
         <v>103501</v>
       </c>
       <c r="C452" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D452" s="2">
         <v>1</v>
@@ -18829,7 +18820,7 @@
         <v>3</v>
       </c>
       <c r="G452" s="11">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I452" s="11">
         <v>0</v>
@@ -18838,13 +18829,13 @@
     <row r="453" customHeight="1" spans="1:12">
       <c r="A453" s="3">
         <f t="shared" si="19"/>
-        <v>1035110306</v>
+        <v>1035110307</v>
       </c>
       <c r="B453" s="2">
         <v>103501</v>
       </c>
       <c r="C453" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D453" s="2">
         <v>1</v>
@@ -18853,7 +18844,7 @@
         <v>3</v>
       </c>
       <c r="G453" s="11">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I453" s="11">
         <v>0</v>
@@ -18862,37 +18853,43 @@
     <row r="454" customHeight="1" spans="1:12">
       <c r="A454" s="3">
         <f t="shared" si="19"/>
-        <v>1035110307</v>
+        <v>1035410109</v>
       </c>
       <c r="B454" s="2">
         <v>103501</v>
       </c>
       <c r="C454" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D454" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F454" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G454" s="11">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I454" s="11">
         <v>0</v>
+      </c>
+      <c r="K454" s="2">
+        <v>103501101</v>
+      </c>
+      <c r="L454" s="13" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="455" customHeight="1" spans="1:12">
       <c r="A455" s="3">
         <f t="shared" si="19"/>
-        <v>1035410109</v>
+        <v>1035410110</v>
       </c>
       <c r="B455" s="2">
         <v>103501</v>
       </c>
       <c r="C455" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D455" s="2">
         <v>4</v>
@@ -18907,22 +18904,22 @@
         <v>0</v>
       </c>
       <c r="K455" s="2">
-        <v>103501101</v>
+        <v>103501102</v>
       </c>
       <c r="L455" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="456" customHeight="1" spans="1:12">
       <c r="A456" s="3">
         <f t="shared" si="19"/>
-        <v>1035410110</v>
+        <v>1035410111</v>
       </c>
       <c r="B456" s="2">
         <v>103501</v>
       </c>
       <c r="C456" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D456" s="2">
         <v>4</v>
@@ -18937,22 +18934,22 @@
         <v>0</v>
       </c>
       <c r="K456" s="2">
-        <v>103501102</v>
+        <v>103501103</v>
       </c>
       <c r="L456" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="457" customHeight="1" spans="1:12">
       <c r="A457" s="3">
         <f t="shared" si="19"/>
-        <v>1035410111</v>
+        <v>1035410112</v>
       </c>
       <c r="B457" s="2">
         <v>103501</v>
       </c>
       <c r="C457" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D457" s="2">
         <v>4</v>
@@ -18967,46 +18964,43 @@
         <v>0</v>
       </c>
       <c r="K457" s="2">
-        <v>103501103</v>
+        <v>103501104</v>
       </c>
       <c r="L457" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="458" customHeight="1" spans="1:12">
       <c r="A458" s="3">
         <f t="shared" si="19"/>
-        <v>1035410112</v>
+        <v>1035410508</v>
       </c>
       <c r="B458" s="2">
         <v>103501</v>
       </c>
       <c r="C458" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D458" s="2">
         <v>4</v>
       </c>
       <c r="F458" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G458" s="11">
         <v>0</v>
       </c>
+      <c r="H458" s="11">
+        <v>30350102</v>
+      </c>
       <c r="I458" s="11">
         <v>0</v>
-      </c>
-      <c r="K458" s="2">
-        <v>103501104</v>
-      </c>
-      <c r="L458" s="13" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="459" customHeight="1" spans="1:12">
       <c r="A459" s="3">
         <f t="shared" si="19"/>
-        <v>1035410508</v>
+        <v>1035410608</v>
       </c>
       <c r="B459" s="2">
         <v>103501</v>
@@ -19018,7 +19012,7 @@
         <v>4</v>
       </c>
       <c r="F459" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G459" s="11">
         <v>0</v>
@@ -19033,25 +19027,25 @@
     <row r="460" customHeight="1" spans="1:12">
       <c r="A460" s="3">
         <f t="shared" si="19"/>
-        <v>1035410608</v>
+        <v>1035410114</v>
       </c>
       <c r="B460" s="2">
         <v>103501</v>
       </c>
       <c r="C460" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D460" s="2">
         <v>4</v>
       </c>
       <c r="F460" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G460" s="11">
         <v>0</v>
       </c>
       <c r="H460" s="11">
-        <v>30350102</v>
+        <v>30350101</v>
       </c>
       <c r="I460" s="11">
         <v>0</v>
@@ -19059,26 +19053,23 @@
     </row>
     <row r="461" customHeight="1" spans="1:12">
       <c r="A461" s="3">
-        <f t="shared" si="19"/>
-        <v>1035410114</v>
+        <f t="shared" ref="A461:A469" si="20">(B461)*10000+C461+F461*100+D461*100000</f>
+        <v>1036100301</v>
       </c>
       <c r="B461" s="2">
-        <v>103501</v>
+        <v>103600</v>
       </c>
       <c r="C461" s="2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D461" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F461" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G461" s="11">
-        <v>0</v>
-      </c>
-      <c r="H461" s="11">
-        <v>30350101</v>
+        <v>3</v>
       </c>
       <c r="I461" s="11">
         <v>0</v>
@@ -19086,14 +19077,14 @@
     </row>
     <row r="462" customHeight="1" spans="1:12">
       <c r="A462" s="3">
-        <f t="shared" ref="A462:A469" si="20">(B462)*10000+C462+F462*100+D462*100000</f>
-        <v>1036100301</v>
+        <f t="shared" si="20"/>
+        <v>1036100302</v>
       </c>
       <c r="B462" s="2">
         <v>103600</v>
       </c>
       <c r="C462" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D462" s="2">
         <v>1</v>
@@ -19102,7 +19093,7 @@
         <v>3</v>
       </c>
       <c r="G462" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I462" s="11">
         <v>0</v>
@@ -19111,13 +19102,13 @@
     <row r="463" customHeight="1" spans="1:12">
       <c r="A463" s="3">
         <f t="shared" si="20"/>
-        <v>1036100302</v>
+        <v>1036100303</v>
       </c>
       <c r="B463" s="2">
         <v>103600</v>
       </c>
       <c r="C463" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D463" s="2">
         <v>1</v>
@@ -19126,7 +19117,7 @@
         <v>3</v>
       </c>
       <c r="G463" s="11">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I463" s="11">
         <v>0</v>
@@ -19135,13 +19126,13 @@
     <row r="464" customHeight="1" spans="1:12">
       <c r="A464" s="3">
         <f t="shared" si="20"/>
-        <v>1036100303</v>
+        <v>1036100304</v>
       </c>
       <c r="B464" s="2">
         <v>103600</v>
       </c>
       <c r="C464" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D464" s="2">
         <v>1</v>
@@ -19150,7 +19141,7 @@
         <v>3</v>
       </c>
       <c r="G464" s="11">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I464" s="11">
         <v>0</v>
@@ -19159,13 +19150,13 @@
     <row r="465" customHeight="1" spans="1:12">
       <c r="A465" s="3">
         <f t="shared" si="20"/>
-        <v>1036100304</v>
+        <v>1036100305</v>
       </c>
       <c r="B465" s="2">
         <v>103600</v>
       </c>
       <c r="C465" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D465" s="2">
         <v>1</v>
@@ -19174,7 +19165,7 @@
         <v>3</v>
       </c>
       <c r="G465" s="11">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I465" s="11">
         <v>0</v>
@@ -19183,13 +19174,13 @@
     <row r="466" customHeight="1" spans="1:12">
       <c r="A466" s="3">
         <f t="shared" si="20"/>
-        <v>1036100305</v>
+        <v>1036100306</v>
       </c>
       <c r="B466" s="2">
         <v>103600</v>
       </c>
       <c r="C466" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D466" s="2">
         <v>1</v>
@@ -19198,7 +19189,7 @@
         <v>3</v>
       </c>
       <c r="G466" s="11">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I466" s="11">
         <v>0</v>
@@ -19207,13 +19198,13 @@
     <row r="467" customHeight="1" spans="1:12">
       <c r="A467" s="3">
         <f t="shared" si="20"/>
-        <v>1036100306</v>
+        <v>1036100307</v>
       </c>
       <c r="B467" s="2">
         <v>103600</v>
       </c>
       <c r="C467" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D467" s="2">
         <v>1</v>
@@ -19222,7 +19213,7 @@
         <v>3</v>
       </c>
       <c r="G467" s="11">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I467" s="11">
         <v>0</v>
@@ -19231,55 +19222,58 @@
     <row r="468" customHeight="1" spans="1:12">
       <c r="A468" s="3">
         <f t="shared" si="20"/>
-        <v>1036100307</v>
+        <v>1036400308</v>
       </c>
       <c r="B468" s="2">
         <v>103600</v>
       </c>
       <c r="C468" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D468" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F468" s="2">
         <v>3</v>
       </c>
       <c r="G468" s="11">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I468" s="11">
         <v>0</v>
+      </c>
+      <c r="K468" s="2">
+        <v>103600101</v>
+      </c>
+      <c r="L468" s="13" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="469" customHeight="1" spans="1:12">
       <c r="A469" s="3">
         <f t="shared" si="20"/>
-        <v>1036400308</v>
+        <v>1036400109</v>
       </c>
       <c r="B469" s="2">
         <v>103600</v>
       </c>
       <c r="C469" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D469" s="2">
         <v>4</v>
       </c>
       <c r="F469" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G469" s="11">
         <v>0</v>
       </c>
+      <c r="H469" s="11">
+        <v>30360001</v>
+      </c>
       <c r="I469" s="11">
         <v>0</v>
-      </c>
-      <c r="K469" s="2">
-        <v>103600101</v>
-      </c>
-      <c r="L469" s="13" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -19700,14 +19694,14 @@
       <formula>MOD($B422,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L441:L447">
+  <conditionalFormatting sqref="L440:L446">
     <cfRule type="expression" dxfId="0" priority="2">
-      <formula>MOD($B441,2)=1</formula>
+      <formula>MOD($B440,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L455:L458">
+  <conditionalFormatting sqref="L454:L457">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>MOD($B455,2)=1</formula>
+      <formula>MOD($B454,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A470:A1048576">
@@ -19723,7 +19717,7 @@
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45 C46:C47 F46:F47 B61:L76 D77:E84 B179:L204 B205:G208 I205:K208 I209:I256 B258 B259:D268 F259:L268 B269:L270 B271:B279 D271:D279 F271:L279 B280:B281 D280:L281 B282:B290 D282:D290 F282:L290 B291:B292 D291:L292 B293:B296 D293:J296 B297:L307 B308:G309 I308:L309 B310:L319 B320:G321 I320:L321 B322:L343 B344:K344 B345:L345 B346:J350 B351:L383 B384:J387 B388:L421 B422:J425 B426:L440 B441:K447 B448:L454 B455:K458 B459:L1048576">
+  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45 C46:C47 F46:F47 B61:L76 D77:E84 B179:L204 B205:G208 I205:K208 I209:I256 B258 B259:D268 F259:L268 B269:L270 B271:B279 D271:D279 F271:L279 B280:B281 D280:L281 B282:B290 D282:D290 F282:L290 B291:B292 D291:L292 B293:B296 D293:J296 B297:L307 B308:G309 I308:L309 B310:L319 B320:G321 I320:L321 B322:L343 B344:K344 B345:L345 B346:J350 B351:L383 B384:J387 B388:L421 B422:J425 B426:L439 B440:K446 B447:L453 B454:K457 B458:L1048576">
     <cfRule type="expression" dxfId="0" priority="435">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$598</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$607</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="100">
   <si>
     <t>id</t>
   </si>
@@ -559,6 +559,57 @@
   <si>
     <t>11_28_40_52_64_75_86</t>
   </si>
+  <si>
+    <t>scatter触发免费</t>
+  </si>
+  <si>
+    <t>vs1 - 普通模式</t>
+  </si>
+  <si>
+    <t>vs2 - 普通模式</t>
+  </si>
+  <si>
+    <t>vs3 - 普通模式</t>
+  </si>
+  <si>
+    <t>vs4 - 普通模式</t>
+  </si>
+  <si>
+    <t>vs1-宙斯</t>
+  </si>
+  <si>
+    <t>vs2-宙斯</t>
+  </si>
+  <si>
+    <t>vs3-宙斯</t>
+  </si>
+  <si>
+    <t>vs4-宙斯</t>
+  </si>
+  <si>
+    <t>用于触发免费游戏宙斯</t>
+  </si>
+  <si>
+    <t>用于触发免费游戏哈迪斯</t>
+  </si>
+  <si>
+    <t>vs1-哈迪斯 VS图案</t>
+  </si>
+  <si>
+    <t>vs2-哈迪斯</t>
+  </si>
+  <si>
+    <t>vs3-哈迪斯</t>
+  </si>
+  <si>
+    <t>vs4-哈迪斯</t>
+  </si>
+  <si>
+    <t>普通模式宙斯玩法</t>
+  </si>
+  <si>
+    <t>普通模式哈迪斯玩法</t>
+  </si>
 </sst>
 </file>
 
@@ -570,7 +621,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -617,6 +668,12 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -807,13 +864,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1077,7 +1134,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1112,6 +1169,45 @@
       </top>
       <bottom style="thin">
         <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1231,16 +1327,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1249,138 +1342,141 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1537,6 +1633,50 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -5857,7 +5997,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L598"/>
+  <dimension ref="A1:L611"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="11"/>
@@ -16188,7 +16328,7 @@
       <c r="I346" s="12">
         <v>0</v>
       </c>
-      <c r="L346" s="54" t="s">
+      <c r="L346" s="72" t="s">
         <v>70</v>
       </c>
     </row>
@@ -20723,7 +20863,7 @@
     </row>
     <row r="529" s="10" customFormat="1" customHeight="1" spans="1:7">
       <c r="A529" s="3">
-        <f t="shared" ref="A529:A550" si="22">(B529)*10000+C529+F529*100+D529*100000</f>
+        <f t="shared" ref="A529:A570" si="22">(B529)*10000+C529+F529*100+D529*100000</f>
         <v>1020100302</v>
       </c>
       <c r="B529" s="10">
@@ -21144,55 +21284,58 @@
     <row r="549" customHeight="1" spans="1:7">
       <c r="A549" s="3">
         <f t="shared" si="22"/>
-        <v>1020100322</v>
+        <v>1020400334</v>
       </c>
       <c r="B549" s="10">
         <v>102000</v>
       </c>
       <c r="C549" s="10">
-        <v>22</v>
-      </c>
-      <c r="D549" s="10">
-        <v>1</v>
+        <v>34</v>
+      </c>
+      <c r="D549" s="2">
+        <v>4</v>
+      </c>
+      <c r="E549" s="54" t="s">
+        <v>83</v>
       </c>
       <c r="F549" s="10">
         <v>3</v>
       </c>
       <c r="G549" s="12">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="550" customHeight="1" spans="1:7">
       <c r="A550" s="3">
         <f t="shared" si="22"/>
-        <v>1020400323</v>
+        <v>1020100401</v>
       </c>
       <c r="B550" s="10">
         <v>102000</v>
       </c>
       <c r="C550" s="10">
-        <v>23</v>
-      </c>
-      <c r="D550" s="2">
-        <v>4</v>
-      </c>
-      <c r="F550" s="10">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D550" s="10">
+        <v>1</v>
+      </c>
+      <c r="F550" s="2">
+        <v>4</v>
       </c>
       <c r="G550" s="12">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="551" customHeight="1" spans="1:7">
       <c r="A551" s="3">
-        <f t="shared" ref="A551:A598" si="23">(B551)*10000+C551+F551*100+D551*100000</f>
-        <v>1020100401</v>
+        <f t="shared" si="22"/>
+        <v>1020100402</v>
       </c>
       <c r="B551" s="10">
         <v>102000</v>
       </c>
       <c r="C551" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D551" s="10">
         <v>1</v>
@@ -21206,14 +21349,14 @@
     </row>
     <row r="552" customHeight="1" spans="1:7">
       <c r="A552" s="3">
-        <f t="shared" si="23"/>
-        <v>1020100402</v>
+        <f t="shared" si="22"/>
+        <v>1020100403</v>
       </c>
       <c r="B552" s="10">
         <v>102000</v>
       </c>
       <c r="C552" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D552" s="10">
         <v>1</v>
@@ -21227,14 +21370,14 @@
     </row>
     <row r="553" customHeight="1" spans="1:7">
       <c r="A553" s="3">
-        <f t="shared" si="23"/>
-        <v>1020100403</v>
+        <f t="shared" si="22"/>
+        <v>1020100404</v>
       </c>
       <c r="B553" s="10">
         <v>102000</v>
       </c>
       <c r="C553" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D553" s="10">
         <v>1</v>
@@ -21248,14 +21391,14 @@
     </row>
     <row r="554" customHeight="1" spans="1:7">
       <c r="A554" s="3">
-        <f t="shared" si="23"/>
-        <v>1020100404</v>
+        <f t="shared" si="22"/>
+        <v>1020100405</v>
       </c>
       <c r="B554" s="10">
         <v>102000</v>
       </c>
       <c r="C554" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D554" s="10">
         <v>1</v>
@@ -21269,14 +21412,14 @@
     </row>
     <row r="555" customHeight="1" spans="1:7">
       <c r="A555" s="3">
-        <f t="shared" si="23"/>
-        <v>1020100405</v>
+        <f t="shared" si="22"/>
+        <v>1020100406</v>
       </c>
       <c r="B555" s="10">
         <v>102000</v>
       </c>
       <c r="C555" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D555" s="10">
         <v>1</v>
@@ -21290,14 +21433,14 @@
     </row>
     <row r="556" customHeight="1" spans="1:7">
       <c r="A556" s="3">
-        <f t="shared" si="23"/>
-        <v>1020100406</v>
+        <f t="shared" si="22"/>
+        <v>1020100407</v>
       </c>
       <c r="B556" s="10">
         <v>102000</v>
       </c>
       <c r="C556" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D556" s="10">
         <v>1</v>
@@ -21311,14 +21454,14 @@
     </row>
     <row r="557" customHeight="1" spans="1:7">
       <c r="A557" s="3">
-        <f t="shared" si="23"/>
-        <v>1020100407</v>
+        <f t="shared" si="22"/>
+        <v>1020100408</v>
       </c>
       <c r="B557" s="10">
         <v>102000</v>
       </c>
       <c r="C557" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D557" s="10">
         <v>1</v>
@@ -21332,14 +21475,14 @@
     </row>
     <row r="558" customHeight="1" spans="1:7">
       <c r="A558" s="3">
-        <f t="shared" si="23"/>
-        <v>1020100408</v>
+        <f t="shared" si="22"/>
+        <v>1020100409</v>
       </c>
       <c r="B558" s="10">
         <v>102000</v>
       </c>
       <c r="C558" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D558" s="10">
         <v>1</v>
@@ -21353,14 +21496,14 @@
     </row>
     <row r="559" customHeight="1" spans="1:7">
       <c r="A559" s="3">
-        <f t="shared" si="23"/>
-        <v>1020100409</v>
+        <f t="shared" si="22"/>
+        <v>1020100410</v>
       </c>
       <c r="B559" s="10">
         <v>102000</v>
       </c>
       <c r="C559" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D559" s="10">
         <v>1</v>
@@ -21374,14 +21517,14 @@
     </row>
     <row r="560" customHeight="1" spans="1:7">
       <c r="A560" s="3">
-        <f t="shared" si="23"/>
-        <v>1020100410</v>
+        <f t="shared" si="22"/>
+        <v>1020100411</v>
       </c>
       <c r="B560" s="10">
         <v>102000</v>
       </c>
       <c r="C560" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D560" s="10">
         <v>1</v>
@@ -21390,19 +21533,19 @@
         <v>4</v>
       </c>
       <c r="G560" s="12">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="561" customHeight="1" spans="1:7">
       <c r="A561" s="3">
-        <f t="shared" si="23"/>
-        <v>1020100411</v>
+        <f t="shared" si="22"/>
+        <v>1020100412</v>
       </c>
       <c r="B561" s="10">
         <v>102000</v>
       </c>
       <c r="C561" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D561" s="10">
         <v>1</v>
@@ -21416,14 +21559,14 @@
     </row>
     <row r="562" customHeight="1" spans="1:7">
       <c r="A562" s="3">
-        <f t="shared" si="23"/>
-        <v>1020100412</v>
+        <f t="shared" si="22"/>
+        <v>1020100413</v>
       </c>
       <c r="B562" s="10">
         <v>102000</v>
       </c>
       <c r="C562" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D562" s="10">
         <v>1</v>
@@ -21437,14 +21580,14 @@
     </row>
     <row r="563" customHeight="1" spans="1:7">
       <c r="A563" s="3">
-        <f t="shared" si="23"/>
-        <v>1020100413</v>
+        <f t="shared" si="22"/>
+        <v>1020100414</v>
       </c>
       <c r="B563" s="10">
         <v>102000</v>
       </c>
       <c r="C563" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D563" s="10">
         <v>1</v>
@@ -21458,14 +21601,14 @@
     </row>
     <row r="564" customHeight="1" spans="1:7">
       <c r="A564" s="3">
-        <f t="shared" si="23"/>
-        <v>1020100414</v>
+        <f t="shared" si="22"/>
+        <v>1020100415</v>
       </c>
       <c r="B564" s="10">
         <v>102000</v>
       </c>
       <c r="C564" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D564" s="10">
         <v>1</v>
@@ -21474,19 +21617,19 @@
         <v>4</v>
       </c>
       <c r="G564" s="12">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="565" customHeight="1" spans="1:7">
       <c r="A565" s="3">
-        <f t="shared" si="23"/>
-        <v>1020100415</v>
+        <f t="shared" si="22"/>
+        <v>1020100416</v>
       </c>
       <c r="B565" s="10">
         <v>102000</v>
       </c>
       <c r="C565" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D565" s="10">
         <v>1</v>
@@ -21500,14 +21643,14 @@
     </row>
     <row r="566" customHeight="1" spans="1:7">
       <c r="A566" s="3">
-        <f t="shared" si="23"/>
-        <v>1020100416</v>
+        <f t="shared" si="22"/>
+        <v>1020100417</v>
       </c>
       <c r="B566" s="10">
         <v>102000</v>
       </c>
       <c r="C566" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D566" s="10">
         <v>1</v>
@@ -21521,14 +21664,14 @@
     </row>
     <row r="567" customHeight="1" spans="1:7">
       <c r="A567" s="3">
-        <f t="shared" si="23"/>
-        <v>1020100417</v>
+        <f t="shared" si="22"/>
+        <v>1020100418</v>
       </c>
       <c r="B567" s="10">
         <v>102000</v>
       </c>
       <c r="C567" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D567" s="10">
         <v>1</v>
@@ -21542,14 +21685,14 @@
     </row>
     <row r="568" customHeight="1" spans="1:7">
       <c r="A568" s="3">
-        <f t="shared" si="23"/>
-        <v>1020100418</v>
+        <f t="shared" si="22"/>
+        <v>1020100419</v>
       </c>
       <c r="B568" s="10">
         <v>102000</v>
       </c>
       <c r="C568" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D568" s="10">
         <v>1</v>
@@ -21558,19 +21701,19 @@
         <v>4</v>
       </c>
       <c r="G568" s="12">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="569" customHeight="1" spans="1:7">
       <c r="A569" s="3">
-        <f t="shared" si="23"/>
-        <v>1020100419</v>
+        <f t="shared" si="22"/>
+        <v>1020100420</v>
       </c>
       <c r="B569" s="10">
         <v>102000</v>
       </c>
       <c r="C569" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D569" s="10">
         <v>1</v>
@@ -21584,14 +21727,14 @@
     </row>
     <row r="570" customHeight="1" spans="1:7">
       <c r="A570" s="3">
-        <f t="shared" si="23"/>
-        <v>1020100420</v>
+        <f t="shared" si="22"/>
+        <v>1020100421</v>
       </c>
       <c r="B570" s="10">
         <v>102000</v>
       </c>
       <c r="C570" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D570" s="10">
         <v>1</v>
@@ -21605,56 +21748,56 @@
     </row>
     <row r="571" customHeight="1" spans="1:7">
       <c r="A571" s="3">
-        <f t="shared" si="23"/>
-        <v>1020100421</v>
+        <f t="shared" ref="A571:A596" si="23">(B571)*10000+C571+F571*100+D571*100000</f>
+        <v>1020100501</v>
       </c>
       <c r="B571" s="10">
         <v>102000</v>
       </c>
       <c r="C571" s="10">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D571" s="10">
         <v>1</v>
       </c>
       <c r="F571" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G571" s="12">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="572" customHeight="1" spans="1:7">
       <c r="A572" s="3">
         <f t="shared" si="23"/>
-        <v>1020100422</v>
+        <v>1020100502</v>
       </c>
       <c r="B572" s="10">
         <v>102000</v>
       </c>
       <c r="C572" s="10">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D572" s="10">
         <v>1</v>
       </c>
       <c r="F572" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G572" s="12">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="573" customHeight="1" spans="1:7">
       <c r="A573" s="3">
         <f t="shared" si="23"/>
-        <v>1020100501</v>
+        <v>1020100503</v>
       </c>
       <c r="B573" s="10">
         <v>102000</v>
       </c>
       <c r="C573" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D573" s="10">
         <v>1</v>
@@ -21669,13 +21812,13 @@
     <row r="574" customHeight="1" spans="1:7">
       <c r="A574" s="3">
         <f t="shared" si="23"/>
-        <v>1020100502</v>
+        <v>1020100504</v>
       </c>
       <c r="B574" s="10">
         <v>102000</v>
       </c>
       <c r="C574" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D574" s="10">
         <v>1</v>
@@ -21690,13 +21833,13 @@
     <row r="575" customHeight="1" spans="1:7">
       <c r="A575" s="3">
         <f t="shared" si="23"/>
-        <v>1020100503</v>
+        <v>1020100505</v>
       </c>
       <c r="B575" s="10">
         <v>102000</v>
       </c>
       <c r="C575" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D575" s="10">
         <v>1</v>
@@ -21711,13 +21854,13 @@
     <row r="576" customHeight="1" spans="1:7">
       <c r="A576" s="3">
         <f t="shared" si="23"/>
-        <v>1020100504</v>
+        <v>1020100506</v>
       </c>
       <c r="B576" s="10">
         <v>102000</v>
       </c>
       <c r="C576" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D576" s="10">
         <v>1</v>
@@ -21729,16 +21872,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="577" customHeight="1" spans="1:7">
+    <row r="577" customHeight="1" spans="1:8">
       <c r="A577" s="3">
         <f t="shared" si="23"/>
-        <v>1020100505</v>
+        <v>1020100507</v>
       </c>
       <c r="B577" s="10">
         <v>102000</v>
       </c>
       <c r="C577" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D577" s="10">
         <v>1</v>
@@ -21750,16 +21893,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="578" customHeight="1" spans="1:7">
+    <row r="578" customHeight="1" spans="1:8">
       <c r="A578" s="3">
         <f t="shared" si="23"/>
-        <v>1020100506</v>
+        <v>1020100508</v>
       </c>
       <c r="B578" s="10">
         <v>102000</v>
       </c>
       <c r="C578" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D578" s="10">
         <v>1</v>
@@ -21771,16 +21914,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="579" customHeight="1" spans="1:7">
+    <row r="579" customHeight="1" spans="1:8">
       <c r="A579" s="3">
         <f t="shared" si="23"/>
-        <v>1020100507</v>
+        <v>1020100509</v>
       </c>
       <c r="B579" s="10">
         <v>102000</v>
       </c>
       <c r="C579" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D579" s="10">
         <v>1</v>
@@ -21792,16 +21935,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="580" customHeight="1" spans="1:7">
+    <row r="580" customHeight="1" spans="1:8">
       <c r="A580" s="3">
         <f t="shared" si="23"/>
-        <v>1020100508</v>
+        <v>1020100510</v>
       </c>
       <c r="B580" s="10">
         <v>102000</v>
       </c>
       <c r="C580" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D580" s="10">
         <v>1</v>
@@ -21813,16 +21956,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="581" customHeight="1" spans="1:7">
+    <row r="581" customHeight="1" spans="1:8">
       <c r="A581" s="3">
         <f t="shared" si="23"/>
-        <v>1020100509</v>
+        <v>1020100511</v>
       </c>
       <c r="B581" s="10">
         <v>102000</v>
       </c>
       <c r="C581" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D581" s="10">
         <v>1</v>
@@ -21831,19 +21974,19 @@
         <v>5</v>
       </c>
       <c r="G581" s="12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="582" customHeight="1" spans="1:7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="582" customHeight="1" spans="1:8">
       <c r="A582" s="3">
         <f t="shared" si="23"/>
-        <v>1020100510</v>
+        <v>1020100512</v>
       </c>
       <c r="B582" s="10">
         <v>102000</v>
       </c>
       <c r="C582" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D582" s="10">
         <v>1</v>
@@ -21852,19 +21995,19 @@
         <v>5</v>
       </c>
       <c r="G582" s="12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="583" customHeight="1" spans="1:7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="583" customHeight="1" spans="1:8">
       <c r="A583" s="3">
         <f t="shared" si="23"/>
-        <v>1020100511</v>
+        <v>1020100513</v>
       </c>
       <c r="B583" s="10">
         <v>102000</v>
       </c>
       <c r="C583" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D583" s="10">
         <v>1</v>
@@ -21876,16 +22019,16 @@
         <v>50</v>
       </c>
     </row>
-    <row r="584" customHeight="1" spans="1:7">
+    <row r="584" customHeight="1" spans="1:8">
       <c r="A584" s="3">
         <f t="shared" si="23"/>
-        <v>1020100512</v>
+        <v>1020100514</v>
       </c>
       <c r="B584" s="10">
         <v>102000</v>
       </c>
       <c r="C584" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D584" s="10">
         <v>1</v>
@@ -21897,16 +22040,16 @@
         <v>50</v>
       </c>
     </row>
-    <row r="585" customHeight="1" spans="1:7">
+    <row r="585" customHeight="1" spans="1:8">
       <c r="A585" s="3">
         <f t="shared" si="23"/>
-        <v>1020100513</v>
+        <v>1020100515</v>
       </c>
       <c r="B585" s="10">
         <v>102000</v>
       </c>
       <c r="C585" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D585" s="10">
         <v>1</v>
@@ -21915,19 +22058,19 @@
         <v>5</v>
       </c>
       <c r="G585" s="12">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="586" customHeight="1" spans="1:7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="586" customHeight="1" spans="1:8">
       <c r="A586" s="3">
         <f t="shared" si="23"/>
-        <v>1020100514</v>
+        <v>1020100516</v>
       </c>
       <c r="B586" s="10">
         <v>102000</v>
       </c>
       <c r="C586" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D586" s="10">
         <v>1</v>
@@ -21936,19 +22079,19 @@
         <v>5</v>
       </c>
       <c r="G586" s="12">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="587" customHeight="1" spans="1:7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="587" customHeight="1" spans="1:8">
       <c r="A587" s="3">
         <f t="shared" si="23"/>
-        <v>1020100515</v>
+        <v>1020100517</v>
       </c>
       <c r="B587" s="10">
         <v>102000</v>
       </c>
       <c r="C587" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D587" s="10">
         <v>1</v>
@@ -21960,16 +22103,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="588" customHeight="1" spans="1:7">
+    <row r="588" customHeight="1" spans="1:8">
       <c r="A588" s="3">
         <f t="shared" si="23"/>
-        <v>1020100516</v>
+        <v>1020100518</v>
       </c>
       <c r="B588" s="10">
         <v>102000</v>
       </c>
       <c r="C588" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D588" s="10">
         <v>1</v>
@@ -21981,16 +22124,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="589" customHeight="1" spans="1:7">
+    <row r="589" customHeight="1" spans="1:8">
       <c r="A589" s="3">
         <f t="shared" si="23"/>
-        <v>1020100517</v>
+        <v>1020100519</v>
       </c>
       <c r="B589" s="10">
         <v>102000</v>
       </c>
       <c r="C589" s="10">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D589" s="10">
         <v>1</v>
@@ -21999,19 +22142,19 @@
         <v>5</v>
       </c>
       <c r="G589" s="12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="590" customHeight="1" spans="1:7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="590" customHeight="1" spans="1:8">
       <c r="A590" s="3">
         <f t="shared" si="23"/>
-        <v>1020100518</v>
+        <v>1020100520</v>
       </c>
       <c r="B590" s="10">
         <v>102000</v>
       </c>
       <c r="C590" s="10">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D590" s="10">
         <v>1</v>
@@ -22020,23 +22163,24 @@
         <v>5</v>
       </c>
       <c r="G590" s="12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="591" customHeight="1" spans="1:7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="591" customHeight="1" spans="1:8">
       <c r="A591" s="3">
         <f t="shared" si="23"/>
-        <v>1020100519</v>
+        <v>1020100521</v>
       </c>
       <c r="B591" s="10">
         <v>102000</v>
       </c>
       <c r="C591" s="10">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D591" s="10">
         <v>1</v>
       </c>
+      <c r="E591" s="55"/>
       <c r="F591" s="2">
         <v>5</v>
       </c>
@@ -22044,864 +22188,1326 @@
         <v>200</v>
       </c>
     </row>
-    <row r="592" customHeight="1" spans="1:7">
+    <row r="592" customHeight="1" spans="1:8">
       <c r="A592" s="3">
         <f t="shared" si="23"/>
-        <v>1020100520</v>
+        <v>1020400122</v>
       </c>
       <c r="B592" s="10">
         <v>102000</v>
       </c>
-      <c r="C592" s="10">
-        <v>20</v>
-      </c>
-      <c r="D592" s="10">
-        <v>1</v>
-      </c>
-      <c r="F592" s="2">
-        <v>5</v>
+      <c r="C592" s="2">
+        <v>22</v>
+      </c>
+      <c r="D592" s="56">
+        <v>4</v>
+      </c>
+      <c r="E592" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="F592" s="58">
+        <v>1</v>
       </c>
       <c r="G592" s="12">
-        <v>200</v>
+        <v>0</v>
+      </c>
+      <c r="H592" s="59">
+        <v>30200003</v>
       </c>
     </row>
     <row r="593" customHeight="1" spans="1:12">
       <c r="A593" s="3">
         <f t="shared" si="23"/>
-        <v>1020100521</v>
+        <v>1020400123</v>
       </c>
       <c r="B593" s="10">
         <v>102000</v>
       </c>
-      <c r="C593" s="10">
-        <v>21</v>
-      </c>
-      <c r="D593" s="10">
-        <v>1</v>
-      </c>
-      <c r="F593" s="2">
-        <v>5</v>
+      <c r="C593" s="2">
+        <v>23</v>
+      </c>
+      <c r="D593" s="56">
+        <v>4</v>
+      </c>
+      <c r="E593" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="F593" s="58">
+        <v>1</v>
       </c>
       <c r="G593" s="12">
-        <v>200</v>
+        <v>0</v>
+      </c>
+      <c r="H593" s="59">
+        <v>30200004</v>
       </c>
     </row>
     <row r="594" customHeight="1" spans="1:12">
       <c r="A594" s="3">
         <f t="shared" si="23"/>
-        <v>1020100522</v>
+        <v>1020400124</v>
       </c>
       <c r="B594" s="10">
         <v>102000</v>
       </c>
-      <c r="C594" s="10">
-        <v>22</v>
-      </c>
-      <c r="D594" s="10">
-        <v>1</v>
-      </c>
-      <c r="F594" s="2">
-        <v>5</v>
+      <c r="C594" s="2">
+        <v>24</v>
+      </c>
+      <c r="D594" s="56">
+        <v>4</v>
+      </c>
+      <c r="E594" s="60" t="s">
+        <v>86</v>
+      </c>
+      <c r="F594" s="58">
+        <v>1</v>
       </c>
       <c r="G594" s="12">
-        <v>200</v>
+        <v>0</v>
+      </c>
+      <c r="H594" s="59">
+        <v>30200005</v>
       </c>
     </row>
     <row r="595" customHeight="1" spans="1:12">
       <c r="A595" s="3">
         <f t="shared" si="23"/>
-        <v>1020400124</v>
+        <v>1020400125</v>
       </c>
       <c r="B595" s="10">
         <v>102000</v>
       </c>
       <c r="C595" s="2">
-        <v>24</v>
-      </c>
-      <c r="D595" s="2">
-        <v>4</v>
-      </c>
-      <c r="F595" s="2">
+        <v>25</v>
+      </c>
+      <c r="D595" s="56">
+        <v>4</v>
+      </c>
+      <c r="E595" s="60" t="s">
+        <v>87</v>
+      </c>
+      <c r="F595" s="58">
         <v>1</v>
       </c>
       <c r="G595" s="12">
         <v>0</v>
       </c>
-      <c r="K595" s="2">
+      <c r="H595" s="59">
+        <v>30200006</v>
+      </c>
+    </row>
+    <row r="596" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A596" s="50">
+        <f>(B596)*10000+C596+F596*100+D596*100000</f>
+        <v>1020400126</v>
+      </c>
+      <c r="B596" s="61">
+        <v>102000</v>
+      </c>
+      <c r="C596" s="50">
+        <v>26</v>
+      </c>
+      <c r="D596" s="62">
+        <v>4</v>
+      </c>
+      <c r="E596" s="63" t="s">
+        <v>88</v>
+      </c>
+      <c r="F596" s="64">
+        <v>1</v>
+      </c>
+      <c r="G596" s="51">
+        <v>0</v>
+      </c>
+      <c r="H596" s="65">
+        <v>30200010</v>
+      </c>
+      <c r="I596" s="51"/>
+      <c r="J596" s="52"/>
+      <c r="K596" s="50"/>
+      <c r="L596" s="52"/>
+    </row>
+    <row r="597" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A597" s="50">
+        <f>(B597)*10000+C597+F597*100+D597*100000</f>
+        <v>1020400127</v>
+      </c>
+      <c r="B597" s="61">
+        <v>102000</v>
+      </c>
+      <c r="C597" s="50">
+        <v>27</v>
+      </c>
+      <c r="D597" s="62">
+        <v>4</v>
+      </c>
+      <c r="E597" s="63" t="s">
+        <v>89</v>
+      </c>
+      <c r="F597" s="64">
+        <v>1</v>
+      </c>
+      <c r="G597" s="51">
+        <v>0</v>
+      </c>
+      <c r="H597" s="65">
+        <v>30200011</v>
+      </c>
+      <c r="I597" s="51"/>
+      <c r="J597" s="52"/>
+      <c r="K597" s="50"/>
+      <c r="L597" s="52"/>
+    </row>
+    <row r="598" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A598" s="50">
+        <f>(B598)*10000+C598+F598*100+D598*100000</f>
+        <v>1020400128</v>
+      </c>
+      <c r="B598" s="61">
+        <v>102000</v>
+      </c>
+      <c r="C598" s="50">
+        <v>28</v>
+      </c>
+      <c r="D598" s="62">
+        <v>4</v>
+      </c>
+      <c r="E598" s="63" t="s">
+        <v>90</v>
+      </c>
+      <c r="F598" s="64">
+        <v>1</v>
+      </c>
+      <c r="G598" s="51">
+        <v>0</v>
+      </c>
+      <c r="H598" s="65">
+        <v>30200012</v>
+      </c>
+      <c r="I598" s="51"/>
+      <c r="J598" s="52"/>
+      <c r="K598" s="50"/>
+      <c r="L598" s="52"/>
+    </row>
+    <row r="599" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A599" s="50">
+        <f>(B599)*10000+C599+F599*100+D599*100000</f>
+        <v>1020400129</v>
+      </c>
+      <c r="B599" s="61">
+        <v>102000</v>
+      </c>
+      <c r="C599" s="50">
+        <v>29</v>
+      </c>
+      <c r="D599" s="62">
+        <v>4</v>
+      </c>
+      <c r="E599" s="63" t="s">
+        <v>91</v>
+      </c>
+      <c r="F599" s="64">
+        <v>1</v>
+      </c>
+      <c r="G599" s="51">
+        <v>0</v>
+      </c>
+      <c r="H599" s="65">
+        <v>30200013</v>
+      </c>
+      <c r="I599" s="51"/>
+      <c r="J599" s="52"/>
+      <c r="K599" s="50"/>
+      <c r="L599" s="52"/>
+    </row>
+    <row r="600" customHeight="1" spans="1:12">
+      <c r="A600" s="3">
+        <f>(B600)*10000+C600+F600*100+D600*100000</f>
+        <v>1020400139</v>
+      </c>
+      <c r="B600" s="10">
+        <v>102000</v>
+      </c>
+      <c r="C600" s="2">
+        <v>39</v>
+      </c>
+      <c r="D600" s="56">
+        <v>4</v>
+      </c>
+      <c r="E600" s="66" t="s">
+        <v>92</v>
+      </c>
+      <c r="F600" s="58">
+        <v>1</v>
+      </c>
+      <c r="G600" s="12">
+        <v>0</v>
+      </c>
+      <c r="H600" s="67">
+        <v>30200009</v>
+      </c>
+    </row>
+    <row r="601" customHeight="1" spans="1:12">
+      <c r="A601" s="3">
+        <f>(B601)*10000+C601+F601*100+D601*100000</f>
+        <v>1020400140</v>
+      </c>
+      <c r="B601" s="10">
+        <v>102000</v>
+      </c>
+      <c r="C601" s="2">
+        <v>40</v>
+      </c>
+      <c r="D601" s="56">
+        <v>4</v>
+      </c>
+      <c r="E601" s="66" t="s">
+        <v>93</v>
+      </c>
+      <c r="F601" s="58">
+        <v>1</v>
+      </c>
+      <c r="G601" s="12">
+        <v>0</v>
+      </c>
+      <c r="H601" s="67">
+        <v>30200014</v>
+      </c>
+    </row>
+    <row r="602" customHeight="1" spans="1:12">
+      <c r="A602" s="3">
+        <f>(B602)*10000+C602+F602*100+D602*100000</f>
+        <v>1020400130</v>
+      </c>
+      <c r="B602" s="10">
+        <v>102000</v>
+      </c>
+      <c r="C602" s="2">
+        <v>30</v>
+      </c>
+      <c r="D602" s="68">
+        <v>4</v>
+      </c>
+      <c r="E602" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F602" s="58">
+        <v>1</v>
+      </c>
+      <c r="G602" s="12">
+        <v>0</v>
+      </c>
+      <c r="H602" s="69">
+        <v>30200015</v>
+      </c>
+    </row>
+    <row r="603" customHeight="1" spans="1:12">
+      <c r="A603" s="3">
+        <f>(B603)*10000+C603+F603*100+D603*100000</f>
+        <v>1020400131</v>
+      </c>
+      <c r="B603" s="10">
+        <v>102000</v>
+      </c>
+      <c r="C603" s="2">
+        <v>31</v>
+      </c>
+      <c r="D603" s="68">
+        <v>4</v>
+      </c>
+      <c r="E603" s="63" t="s">
+        <v>95</v>
+      </c>
+      <c r="F603" s="58">
+        <v>1</v>
+      </c>
+      <c r="G603" s="12">
+        <v>0</v>
+      </c>
+      <c r="H603" s="69">
+        <v>30200016</v>
+      </c>
+    </row>
+    <row r="604" customHeight="1" spans="1:12">
+      <c r="A604" s="3">
+        <f>(B604)*10000+C604+F604*100+D604*100000</f>
+        <v>1020400132</v>
+      </c>
+      <c r="B604" s="10">
+        <v>102000</v>
+      </c>
+      <c r="C604" s="2">
+        <v>32</v>
+      </c>
+      <c r="D604" s="68">
+        <v>4</v>
+      </c>
+      <c r="E604" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="F604" s="58">
+        <v>1</v>
+      </c>
+      <c r="G604" s="12">
+        <v>0</v>
+      </c>
+      <c r="H604" s="69">
+        <v>30200017</v>
+      </c>
+    </row>
+    <row r="605" customHeight="1" spans="1:12">
+      <c r="A605" s="3">
+        <f>(B605)*10000+C605+F605*100+D605*100000</f>
+        <v>1020400133</v>
+      </c>
+      <c r="B605" s="10">
+        <v>102000</v>
+      </c>
+      <c r="C605" s="2">
+        <v>33</v>
+      </c>
+      <c r="D605" s="68">
+        <v>4</v>
+      </c>
+      <c r="E605" s="70" t="s">
+        <v>97</v>
+      </c>
+      <c r="F605" s="58">
+        <v>1</v>
+      </c>
+      <c r="G605" s="12">
+        <v>0</v>
+      </c>
+      <c r="H605" s="69">
+        <v>30200018</v>
+      </c>
+    </row>
+    <row r="606" customHeight="1" spans="1:12">
+      <c r="A606" s="3">
+        <f>(B606)*10000+C606+F606*100+D606*100000</f>
+        <v>1020400141</v>
+      </c>
+      <c r="B606" s="10">
+        <v>102000</v>
+      </c>
+      <c r="C606" s="2">
+        <v>41</v>
+      </c>
+      <c r="D606" s="2">
+        <v>4</v>
+      </c>
+      <c r="E606" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="F606" s="2">
+        <v>1</v>
+      </c>
+      <c r="G606" s="12">
+        <v>0</v>
+      </c>
+      <c r="H606" s="59">
+        <v>30200007</v>
+      </c>
+    </row>
+    <row r="607" customHeight="1" spans="1:12">
+      <c r="A607" s="3">
+        <f>(B607)*10000+C607+F607*100+D607*100000</f>
+        <v>1020400142</v>
+      </c>
+      <c r="B607" s="10">
+        <v>102000</v>
+      </c>
+      <c r="C607" s="2">
+        <v>42</v>
+      </c>
+      <c r="D607" s="2">
+        <v>4</v>
+      </c>
+      <c r="E607" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="F607" s="2">
+        <v>1</v>
+      </c>
+      <c r="G607" s="12">
+        <v>0</v>
+      </c>
+      <c r="H607" s="59">
+        <v>30200008</v>
+      </c>
+    </row>
+    <row r="608" customHeight="1" spans="1:12">
+      <c r="A608" s="3">
+        <f>(B608)*10000+C608+F608*100+D608*100000</f>
+        <v>1020400135</v>
+      </c>
+      <c r="B608" s="10">
+        <v>102000</v>
+      </c>
+      <c r="C608" s="2">
+        <v>35</v>
+      </c>
+      <c r="D608" s="2">
+        <v>4</v>
+      </c>
+      <c r="E608" s="71"/>
+      <c r="F608" s="2">
+        <v>1</v>
+      </c>
+      <c r="G608" s="12">
+        <v>0</v>
+      </c>
+      <c r="H608" s="69"/>
+      <c r="K608" s="2">
         <v>102000101</v>
       </c>
-      <c r="L595" s="14" t="s">
+      <c r="L608" s="14" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="596" customHeight="1" spans="1:12">
-      <c r="A596" s="3">
-        <f t="shared" si="23"/>
-        <v>1020400125</v>
-      </c>
-      <c r="B596" s="10">
+    <row r="609" customHeight="1" spans="1:12">
+      <c r="A609" s="3">
+        <f>(B609)*10000+C609+F609*100+D609*100000</f>
+        <v>1020400136</v>
+      </c>
+      <c r="B609" s="10">
         <v>102000</v>
       </c>
-      <c r="C596" s="2">
-        <v>25</v>
-      </c>
-      <c r="D596" s="2">
-        <v>4</v>
-      </c>
-      <c r="F596" s="2">
-        <v>1</v>
-      </c>
-      <c r="G596" s="12">
-        <v>0</v>
-      </c>
-      <c r="K596" s="2">
+      <c r="C609" s="2">
+        <v>36</v>
+      </c>
+      <c r="D609" s="2">
+        <v>4</v>
+      </c>
+      <c r="F609" s="2">
+        <v>1</v>
+      </c>
+      <c r="G609" s="12">
+        <v>0</v>
+      </c>
+      <c r="K609" s="2">
         <v>102000102</v>
       </c>
-      <c r="L596" s="14" t="s">
+      <c r="L609" s="14" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="597" customHeight="1" spans="1:12">
-      <c r="A597" s="3">
-        <f t="shared" si="23"/>
-        <v>1020400126</v>
-      </c>
-      <c r="B597" s="10">
+    <row r="610" customHeight="1" spans="1:12">
+      <c r="A610" s="3">
+        <f>(B610)*10000+C610+F610*100+D610*100000</f>
+        <v>1020400137</v>
+      </c>
+      <c r="B610" s="10">
         <v>102000</v>
       </c>
-      <c r="C597" s="2">
-        <v>26</v>
-      </c>
-      <c r="D597" s="2">
-        <v>4</v>
-      </c>
-      <c r="F597" s="2">
-        <v>1</v>
-      </c>
-      <c r="G597" s="12">
-        <v>0</v>
-      </c>
-      <c r="K597" s="2">
+      <c r="C610" s="2">
+        <v>37</v>
+      </c>
+      <c r="D610" s="2">
+        <v>4</v>
+      </c>
+      <c r="F610" s="2">
+        <v>1</v>
+      </c>
+      <c r="G610" s="12">
+        <v>0</v>
+      </c>
+      <c r="K610" s="2">
         <v>102000103</v>
       </c>
-      <c r="L597" s="14" t="s">
+      <c r="L610" s="14" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="598" customHeight="1" spans="1:12">
-      <c r="A598" s="3">
-        <f t="shared" si="23"/>
-        <v>1020400127</v>
-      </c>
-      <c r="B598" s="10">
+    <row r="611" customHeight="1" spans="1:12">
+      <c r="A611" s="3">
+        <f>(B611)*10000+C611+F611*100+D611*100000</f>
+        <v>1020400138</v>
+      </c>
+      <c r="B611" s="10">
         <v>102000</v>
       </c>
-      <c r="C598" s="2">
-        <v>27</v>
-      </c>
-      <c r="D598" s="2">
-        <v>4</v>
-      </c>
-      <c r="F598" s="2">
-        <v>1</v>
-      </c>
-      <c r="G598" s="12">
-        <v>0</v>
-      </c>
-      <c r="K598" s="2">
+      <c r="C611" s="2">
+        <v>38</v>
+      </c>
+      <c r="D611" s="2">
+        <v>4</v>
+      </c>
+      <c r="F611" s="2">
+        <v>1</v>
+      </c>
+      <c r="G611" s="12">
+        <v>0</v>
+      </c>
+      <c r="K611" s="2">
         <v>102000104</v>
       </c>
-      <c r="L598" s="14" t="s">
+      <c r="L611" s="14" t="s">
         <v>68</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L598" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L607" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="0" priority="140">
+    <cfRule type="expression" dxfId="0" priority="145">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D85:E85">
-    <cfRule type="expression" dxfId="0" priority="166">
+    <cfRule type="expression" dxfId="0" priority="171">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D86:E86">
-    <cfRule type="expression" dxfId="0" priority="131">
+    <cfRule type="expression" dxfId="0" priority="136">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105">
-    <cfRule type="duplicateValues" dxfId="1" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105:E105">
-    <cfRule type="expression" dxfId="0" priority="111">
+    <cfRule type="expression" dxfId="0" priority="116">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I105">
-    <cfRule type="expression" dxfId="0" priority="113">
+    <cfRule type="expression" dxfId="0" priority="118">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A106">
-    <cfRule type="duplicateValues" dxfId="1" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D106:E106">
-    <cfRule type="expression" dxfId="0" priority="107">
+    <cfRule type="expression" dxfId="0" priority="112">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I106">
-    <cfRule type="expression" dxfId="0" priority="109">
+    <cfRule type="expression" dxfId="0" priority="114">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="1" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D107:E107">
-    <cfRule type="expression" dxfId="0" priority="103">
+    <cfRule type="expression" dxfId="0" priority="108">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I107">
-    <cfRule type="expression" dxfId="0" priority="105">
+    <cfRule type="expression" dxfId="0" priority="110">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108">
-    <cfRule type="duplicateValues" dxfId="1" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D108:E108">
-    <cfRule type="expression" dxfId="0" priority="99">
+    <cfRule type="expression" dxfId="0" priority="104">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I108">
-    <cfRule type="expression" dxfId="0" priority="101">
+    <cfRule type="expression" dxfId="0" priority="106">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" dxfId="1" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D109:E109">
-    <cfRule type="expression" dxfId="0" priority="95">
+    <cfRule type="expression" dxfId="0" priority="100">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I109">
-    <cfRule type="expression" dxfId="0" priority="97">
+    <cfRule type="expression" dxfId="0" priority="102">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110">
-    <cfRule type="duplicateValues" dxfId="1" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D110:E110">
-    <cfRule type="expression" dxfId="0" priority="91">
+    <cfRule type="expression" dxfId="0" priority="96">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I110">
-    <cfRule type="expression" dxfId="0" priority="93">
+    <cfRule type="expression" dxfId="0" priority="98">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A111">
-    <cfRule type="duplicateValues" dxfId="1" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D111:E111">
-    <cfRule type="expression" dxfId="0" priority="87">
+    <cfRule type="expression" dxfId="0" priority="92">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I111">
-    <cfRule type="expression" dxfId="0" priority="89">
+    <cfRule type="expression" dxfId="0" priority="94">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112">
-    <cfRule type="duplicateValues" dxfId="1" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D112:E112">
-    <cfRule type="expression" dxfId="0" priority="83">
+    <cfRule type="expression" dxfId="0" priority="88">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I112">
-    <cfRule type="expression" dxfId="0" priority="85">
+    <cfRule type="expression" dxfId="0" priority="90">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A113">
-    <cfRule type="duplicateValues" dxfId="1" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D113:E113">
-    <cfRule type="expression" dxfId="0" priority="79">
+    <cfRule type="expression" dxfId="0" priority="84">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I113">
-    <cfRule type="expression" dxfId="0" priority="81">
+    <cfRule type="expression" dxfId="0" priority="86">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114">
-    <cfRule type="duplicateValues" dxfId="1" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D114:E114">
-    <cfRule type="expression" dxfId="0" priority="75">
+    <cfRule type="expression" dxfId="0" priority="80">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I114">
-    <cfRule type="expression" dxfId="0" priority="77">
+    <cfRule type="expression" dxfId="0" priority="82">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A115">
-    <cfRule type="duplicateValues" dxfId="1" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D115:E115">
-    <cfRule type="expression" dxfId="0" priority="71">
+    <cfRule type="expression" dxfId="0" priority="76">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I115">
-    <cfRule type="expression" dxfId="0" priority="73">
+    <cfRule type="expression" dxfId="0" priority="78">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A116">
-    <cfRule type="duplicateValues" dxfId="1" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D116:E116">
-    <cfRule type="expression" dxfId="0" priority="67">
+    <cfRule type="expression" dxfId="0" priority="72">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I116">
-    <cfRule type="expression" dxfId="0" priority="69">
+    <cfRule type="expression" dxfId="0" priority="74">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117">
-    <cfRule type="duplicateValues" dxfId="1" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D117:E117">
-    <cfRule type="expression" dxfId="0" priority="63">
+    <cfRule type="expression" dxfId="0" priority="68">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I117">
-    <cfRule type="expression" dxfId="0" priority="65">
+    <cfRule type="expression" dxfId="0" priority="70">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A118">
-    <cfRule type="duplicateValues" dxfId="1" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D118:E118">
-    <cfRule type="expression" dxfId="0" priority="59">
+    <cfRule type="expression" dxfId="0" priority="64">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I118">
-    <cfRule type="expression" dxfId="0" priority="61">
+    <cfRule type="expression" dxfId="0" priority="66">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A119">
-    <cfRule type="duplicateValues" dxfId="1" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D119:E119">
-    <cfRule type="expression" dxfId="0" priority="55">
+    <cfRule type="expression" dxfId="0" priority="60">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I119">
-    <cfRule type="expression" dxfId="0" priority="57">
+    <cfRule type="expression" dxfId="0" priority="62">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A120">
-    <cfRule type="duplicateValues" dxfId="1" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D120:E120">
-    <cfRule type="expression" dxfId="0" priority="51">
+    <cfRule type="expression" dxfId="0" priority="56">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I120">
-    <cfRule type="expression" dxfId="0" priority="53">
+    <cfRule type="expression" dxfId="0" priority="58">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A121">
-    <cfRule type="duplicateValues" dxfId="1" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D121:E121">
-    <cfRule type="expression" dxfId="0" priority="47">
+    <cfRule type="expression" dxfId="0" priority="52">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I121">
-    <cfRule type="expression" dxfId="0" priority="49">
+    <cfRule type="expression" dxfId="0" priority="54">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A122">
-    <cfRule type="duplicateValues" dxfId="1" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D122:E122">
-    <cfRule type="expression" dxfId="0" priority="43">
+    <cfRule type="expression" dxfId="0" priority="48">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I122">
-    <cfRule type="expression" dxfId="0" priority="45">
+    <cfRule type="expression" dxfId="0" priority="50">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A123">
-    <cfRule type="duplicateValues" dxfId="1" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D123:E123">
-    <cfRule type="expression" dxfId="0" priority="39">
+    <cfRule type="expression" dxfId="0" priority="44">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I123">
-    <cfRule type="expression" dxfId="0" priority="41">
+    <cfRule type="expression" dxfId="0" priority="46">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C134:L134">
-    <cfRule type="expression" dxfId="0" priority="167">
+    <cfRule type="expression" dxfId="0" priority="172">
       <formula>MOD($B134,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="expression" dxfId="0" priority="31">
+    <cfRule type="expression" dxfId="0" priority="36">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A178">
-    <cfRule type="duplicateValues" dxfId="1" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B178">
-    <cfRule type="expression" dxfId="0" priority="27">
+    <cfRule type="expression" dxfId="0" priority="32">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D178:E178">
-    <cfRule type="expression" dxfId="0" priority="25">
+    <cfRule type="expression" dxfId="0" priority="30">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H309">
-    <cfRule type="expression" dxfId="0" priority="445">
+    <cfRule type="expression" dxfId="0" priority="450">
       <formula>MOD($B308,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H321">
-    <cfRule type="expression" dxfId="0" priority="444">
+    <cfRule type="expression" dxfId="0" priority="449">
       <formula>MOD($B320,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L346">
-    <cfRule type="expression" dxfId="0" priority="446">
+    <cfRule type="expression" dxfId="0" priority="451">
       <formula>MOD($B350,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E549">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD(#REF!,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H592">
+    <cfRule type="expression" dxfId="0" priority="455">
+      <formula>MOD(#REF!,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A48:A60">
-    <cfRule type="duplicateValues" dxfId="1" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A87:A92">
-    <cfRule type="duplicateValues" dxfId="1" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A93:A98">
-    <cfRule type="duplicateValues" dxfId="1" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99:A104">
-    <cfRule type="duplicateValues" dxfId="1" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A135:A177">
-    <cfRule type="duplicateValues" dxfId="1" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A209:A469">
-    <cfRule type="duplicateValues" dxfId="1" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A521:A598">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  <conditionalFormatting sqref="A521:A611">
+    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B60">
-    <cfRule type="expression" dxfId="0" priority="126">
+    <cfRule type="expression" dxfId="0" priority="131">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C84">
-    <cfRule type="expression" dxfId="0" priority="129">
+    <cfRule type="expression" dxfId="0" priority="134">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C271:C281">
-    <cfRule type="expression" dxfId="0" priority="18">
+    <cfRule type="expression" dxfId="0" priority="23">
       <formula>MOD($B271,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C282:C296">
-    <cfRule type="expression" dxfId="0" priority="16">
+    <cfRule type="expression" dxfId="0" priority="21">
       <formula>MOD($B282,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C602:C605">
+    <cfRule type="expression" dxfId="0" priority="460">
+      <formula>MOD($B618,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C606:C611">
+    <cfRule type="expression" dxfId="0" priority="457">
+      <formula>MOD($B623,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E93:E98">
-    <cfRule type="expression" dxfId="0" priority="118">
+    <cfRule type="expression" dxfId="0" priority="123">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E99:E104">
-    <cfRule type="expression" dxfId="0" priority="115">
+    <cfRule type="expression" dxfId="0" priority="120">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E257:E268">
-    <cfRule type="expression" dxfId="0" priority="19">
+    <cfRule type="expression" dxfId="0" priority="24">
       <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E271:E279">
-    <cfRule type="expression" dxfId="0" priority="17">
+    <cfRule type="expression" dxfId="0" priority="22">
       <formula>MOD($B271,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E282:E290">
-    <cfRule type="expression" dxfId="0" priority="15">
+    <cfRule type="expression" dxfId="0" priority="20">
       <formula>MOD($B282,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E592:E595">
+    <cfRule type="expression" dxfId="0" priority="454">
+      <formula>MOD(#REF!,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E596:E599">
+    <cfRule type="expression" dxfId="0" priority="5">
+      <formula>MOD(#REF!,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E600:E601">
+    <cfRule type="expression" dxfId="0" priority="452">
+      <formula>MOD(#REF!,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E602:E605">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>MOD(#REF!,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H593:H599">
+    <cfRule type="expression" dxfId="0" priority="456">
+      <formula>MOD(#REF!,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H600:H601">
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>MOD(#REF!,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H606:H608">
+    <cfRule type="expression" dxfId="0" priority="453">
+      <formula>MOD(#REF!,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K39:K42">
-    <cfRule type="duplicateValues" dxfId="2" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K169:K172">
-    <cfRule type="duplicateValues" dxfId="2" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K293:K296">
-    <cfRule type="expression" dxfId="0" priority="13">
+    <cfRule type="expression" dxfId="0" priority="18">
       <formula>MOD($B293,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K347:K350">
-    <cfRule type="expression" dxfId="0" priority="11">
+    <cfRule type="expression" dxfId="0" priority="16">
       <formula>MOD($B346,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K384:K387">
-    <cfRule type="expression" dxfId="0" priority="9">
+    <cfRule type="expression" dxfId="0" priority="14">
       <formula>MOD($B384,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K422:K425">
-    <cfRule type="expression" dxfId="0" priority="7">
+    <cfRule type="expression" dxfId="0" priority="12">
       <formula>MOD($B422,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K595:K598">
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>MOD($B595,2)=1</formula>
+  <conditionalFormatting sqref="K609:K611">
+    <cfRule type="expression" dxfId="0" priority="7">
+      <formula>MOD($B602,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L205:L208">
-    <cfRule type="expression" dxfId="0" priority="24">
+    <cfRule type="expression" dxfId="0" priority="29">
       <formula>MOD($B205,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L293:L296">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="0" priority="19">
       <formula>MOD($B293,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L347:L350">
-    <cfRule type="expression" dxfId="0" priority="12">
+    <cfRule type="expression" dxfId="0" priority="17">
       <formula>MOD($B346,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L384:L387">
-    <cfRule type="expression" dxfId="0" priority="10">
+    <cfRule type="expression" dxfId="0" priority="15">
       <formula>MOD($B384,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L422:L425">
-    <cfRule type="expression" dxfId="0" priority="8">
+    <cfRule type="expression" dxfId="0" priority="13">
       <formula>MOD($B422,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L440:L446">
-    <cfRule type="expression" dxfId="0" priority="6">
+    <cfRule type="expression" dxfId="0" priority="11">
       <formula>MOD($B440,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L454:L457">
-    <cfRule type="expression" dxfId="0" priority="5">
+    <cfRule type="expression" dxfId="0" priority="10">
       <formula>MOD($B454,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L517:L520">
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="0" priority="9">
       <formula>MOD($B517,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L595:L598">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>MOD($B595,2)=1</formula>
+  <conditionalFormatting sqref="L609:L611">
+    <cfRule type="expression" dxfId="0" priority="6">
+      <formula>MOD($B602,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A470:A520 A599:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="441"/>
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A470:A520 A612:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="446"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L4">
-    <cfRule type="expression" dxfId="0" priority="440">
+    <cfRule type="expression" dxfId="0" priority="445">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41:B42 B44:B47">
-    <cfRule type="expression" dxfId="0" priority="174">
+    <cfRule type="expression" dxfId="0" priority="179">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45 C46:C47 F46:F47 B61:L76 D77:E84 B179:L204 B205:G208 I205:K208 I209:I256 B258 B259:D268 F259:L268 B269:L270 B271:B279 D271:D279 F271:L279 B280:B281 D280:L281 B282:B290 D282:D290 F282:L290 B291:B292 D291:L292 B293:B296 D293:J296 B297:L307 B308:G309 I308:L309 B310:L319 B320:G321 I320:L321 B322:L343 B344:K344 B345:L345 B346:J350 B351:L383 B384:J387 B388:L421 B422:J425 B426:L439 B440:K446 B447:L453 B454:K457 B458:L516 B517:K520 B521:L594 B595:J598 B599:L1048576">
-    <cfRule type="expression" dxfId="0" priority="439">
+  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45 C46:C47 F46:F47 B61:L76 D77:E84 B179:L204 B205:G208 I205:K208 I209:I256 B258 B259:D268 F259:L268 B269:L270 B271:B279 D271:D279 F271:L279 B280:B281 D280:L281 B282:B290 D282:D290 F282:L290 B291:B292 D291:L292 B293:B296 D293:J296 B297:L307 B308:G309 I308:L309 B310:L319 B320:G321 I320:L321 B322:L343 B344:K344 B345:L345 B346:J350 B351:L383 B384:J387 B388:L421 B422:J425 B426:L439 B440:K446 B447:L453 B454:K457 B458:L516 B517:K520 B521:L548 B549:D549 F549:L549 B550:L591 B592 D592 I592:L592 B593:B594 D593:D594 I593:L594 B595 D595 I595:L595 B596:B601 D596:D601 I596:L601 B602 D602 F602:J602 B603:B604 D603:D604 F603:J604 B605 F605 H605:L605 B606:B607 F606:F607 I606:L607 B608 F608 I608:L608 B609:B610 D609:G610 I609:J610 B611 D611:J611 B612:L1048576">
+    <cfRule type="expression" dxfId="0" priority="444">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43:G43 J43:L43">
-    <cfRule type="expression" dxfId="0" priority="139">
+    <cfRule type="expression" dxfId="0" priority="144">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44:G44 J44:L47 G45:G47 C45:C47">
-    <cfRule type="expression" dxfId="0" priority="173">
+    <cfRule type="expression" dxfId="0" priority="178">
       <formula>MOD($B44,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45:E47">
-    <cfRule type="expression" dxfId="0" priority="170">
+    <cfRule type="expression" dxfId="0" priority="175">
       <formula>MOD($B45,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F60 C48:C60">
-    <cfRule type="expression" dxfId="0" priority="127">
+    <cfRule type="expression" dxfId="0" priority="132">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
-    <cfRule type="expression" dxfId="0" priority="125">
+    <cfRule type="expression" dxfId="0" priority="130">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D48:E60">
-    <cfRule type="expression" dxfId="0" priority="123">
+    <cfRule type="expression" dxfId="0" priority="128">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B77:B84 F77:L84">
-    <cfRule type="expression" dxfId="0" priority="169">
+    <cfRule type="expression" dxfId="0" priority="174">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85:C85 F85:L85">
-    <cfRule type="expression" dxfId="0" priority="165">
+    <cfRule type="expression" dxfId="0" priority="170">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B86:C86 F86:L86">
-    <cfRule type="expression" dxfId="0" priority="130">
+    <cfRule type="expression" dxfId="0" priority="135">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87:C92 F87:L92 I93:I104">
-    <cfRule type="expression" dxfId="0" priority="120">
+    <cfRule type="expression" dxfId="0" priority="125">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87:E92 D93:D104">
-    <cfRule type="expression" dxfId="0" priority="121">
+    <cfRule type="expression" dxfId="0" priority="126">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:C98 F93:H98 J93:L98">
-    <cfRule type="expression" dxfId="0" priority="117">
+    <cfRule type="expression" dxfId="0" priority="122">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99:C104 F99:H104 J99:L104">
-    <cfRule type="expression" dxfId="0" priority="114">
+    <cfRule type="expression" dxfId="0" priority="119">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:C105 F105:H105 J105:L105">
-    <cfRule type="expression" dxfId="0" priority="110">
+    <cfRule type="expression" dxfId="0" priority="115">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106:C106 F106:H106 J106:L106 H107:H111 C107:C111">
-    <cfRule type="expression" dxfId="0" priority="106">
+    <cfRule type="expression" dxfId="0" priority="111">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107 F107:G107 J107:L107">
-    <cfRule type="expression" dxfId="0" priority="102">
+    <cfRule type="expression" dxfId="0" priority="107">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B108 F108:G108 J108:L108">
-    <cfRule type="expression" dxfId="0" priority="98">
+    <cfRule type="expression" dxfId="0" priority="103">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B109 F109:G109 J109:L109">
-    <cfRule type="expression" dxfId="0" priority="94">
+    <cfRule type="expression" dxfId="0" priority="99">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B110 F110:G110 J110:L110">
-    <cfRule type="expression" dxfId="0" priority="90">
+    <cfRule type="expression" dxfId="0" priority="95">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111 F111:G111 J111:L111">
-    <cfRule type="expression" dxfId="0" priority="86">
+    <cfRule type="expression" dxfId="0" priority="91">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112:C112 F112:H112 J112:L112 H113:H117 C113:C117">
-    <cfRule type="expression" dxfId="0" priority="82">
+    <cfRule type="expression" dxfId="0" priority="87">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113 F113:G113 J113:L113">
-    <cfRule type="expression" dxfId="0" priority="78">
+    <cfRule type="expression" dxfId="0" priority="83">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114 F114:G114 J114:L114">
-    <cfRule type="expression" dxfId="0" priority="74">
+    <cfRule type="expression" dxfId="0" priority="79">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115 F115:G115 J115:L115">
-    <cfRule type="expression" dxfId="0" priority="70">
+    <cfRule type="expression" dxfId="0" priority="75">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B116 F116:G116 J116:L116">
-    <cfRule type="expression" dxfId="0" priority="66">
+    <cfRule type="expression" dxfId="0" priority="71">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117 F117:G117 J117:L117">
-    <cfRule type="expression" dxfId="0" priority="62">
+    <cfRule type="expression" dxfId="0" priority="67">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118:C118 F118:H118 J118:L118 H119:H123 C119:C123">
-    <cfRule type="expression" dxfId="0" priority="58">
+    <cfRule type="expression" dxfId="0" priority="63">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119 F119:G119 J119:L119">
-    <cfRule type="expression" dxfId="0" priority="54">
+    <cfRule type="expression" dxfId="0" priority="59">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120 F120:G120 J120:L120">
-    <cfRule type="expression" dxfId="0" priority="50">
+    <cfRule type="expression" dxfId="0" priority="55">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121 F121:G121 J121:L121">
-    <cfRule type="expression" dxfId="0" priority="46">
+    <cfRule type="expression" dxfId="0" priority="51">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122 F122:G122 J122:L122">
-    <cfRule type="expression" dxfId="0" priority="42">
+    <cfRule type="expression" dxfId="0" priority="47">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123 F123:G123 J123:L123">
-    <cfRule type="expression" dxfId="0" priority="38">
+    <cfRule type="expression" dxfId="0" priority="43">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B124:L133 B134">
-    <cfRule type="expression" dxfId="0" priority="168">
+    <cfRule type="expression" dxfId="0" priority="173">
       <formula>MOD($B124,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171:B172 B174:B177">
-    <cfRule type="expression" dxfId="0" priority="35">
+    <cfRule type="expression" dxfId="0" priority="40">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171:G172 J171:J172 L171:L172 F175:F177 C176:C177">
-    <cfRule type="expression" dxfId="0" priority="36">
+    <cfRule type="expression" dxfId="0" priority="41">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173:G173 J173:L173">
-    <cfRule type="expression" dxfId="0" priority="30">
+    <cfRule type="expression" dxfId="0" priority="35">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174:G174 J174:L177 G175:G177 C175:C177">
-    <cfRule type="expression" dxfId="0" priority="34">
+    <cfRule type="expression" dxfId="0" priority="39">
       <formula>MOD($B174,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D175:E177">
-    <cfRule type="expression" dxfId="0" priority="33">
+    <cfRule type="expression" dxfId="0" priority="38">
       <formula>MOD($B175,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F178 C178">
-    <cfRule type="expression" dxfId="0" priority="28">
+    <cfRule type="expression" dxfId="0" priority="33">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J178:L178 G178 C178">
-    <cfRule type="expression" dxfId="0" priority="26">
+    <cfRule type="expression" dxfId="0" priority="31">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B209:D209 F209:H209 J209:L250 B210:H250">
-    <cfRule type="expression" dxfId="0" priority="23">
+    <cfRule type="expression" dxfId="0" priority="28">
       <formula>MOD($B209,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B251:H256 J251:L256">
-    <cfRule type="expression" dxfId="0" priority="22">
+    <cfRule type="expression" dxfId="0" priority="27">
       <formula>MOD($B251,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B257 B259 B261 B263 B265 B267 B269 B271 B273 B275 B277 B279 B281 B283 B285 B287 B289 B291 B293 B295">
-    <cfRule type="expression" dxfId="0" priority="20">
+    <cfRule type="expression" dxfId="0" priority="25">
       <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C257:D257 F257:L257">
-    <cfRule type="expression" dxfId="0" priority="443">
+    <cfRule type="expression" dxfId="0" priority="448">
       <formula>MOD($B258,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C258:D258 I292 I290 I288 I286 I284 I282 I280 I278 I276 I274 I272 I270 I268 I266 I264 I262 I260 D268 D266 D264 D262 D260 F258:L258">
-    <cfRule type="expression" dxfId="0" priority="442">
+    <cfRule type="expression" dxfId="0" priority="447">
       <formula>MOD(#REF!,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C592 F592:G592">
+    <cfRule type="expression" dxfId="0" priority="458">
+      <formula>MOD($B605,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C593 F593:G593">
+    <cfRule type="expression" dxfId="0" priority="461">
+      <formula>MOD(#REF!,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C594:C595 F594:G595">
+    <cfRule type="expression" dxfId="0" priority="462">
+      <formula>MOD($B606,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C596 F596:G596 C597 F597:G597 C598:C599 F598:G599 C600:C601 F600:G601">
+    <cfRule type="expression" dxfId="0" priority="459">
+      <formula>MOD($B610,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$607</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$611</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="100">
   <si>
     <t>id</t>
   </si>
@@ -858,6 +858,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -866,11 +871,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1476,7 +1476,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1651,9 +1651,6 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1668,17 +1665,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -5997,7 +5987,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L611"/>
+  <dimension ref="A1:L647"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="11"/>
@@ -16328,7 +16318,7 @@
       <c r="I346" s="12">
         <v>0</v>
       </c>
-      <c r="L346" s="72" t="s">
+      <c r="L346" s="68" t="s">
         <v>70</v>
       </c>
     </row>
@@ -21748,7 +21738,7 @@
     </row>
     <row r="571" customHeight="1" spans="1:7">
       <c r="A571" s="3">
-        <f t="shared" ref="A571:A596" si="23">(B571)*10000+C571+F571*100+D571*100000</f>
+        <f t="shared" ref="A571:A611" si="23">(B571)*10000+C571+F571*100+D571*100000</f>
         <v>1020100501</v>
       </c>
       <c r="B571" s="10">
@@ -22229,7 +22219,7 @@
       <c r="D593" s="56">
         <v>4</v>
       </c>
-      <c r="E593" s="60" t="s">
+      <c r="E593" s="57" t="s">
         <v>85</v>
       </c>
       <c r="F593" s="58">
@@ -22256,7 +22246,7 @@
       <c r="D594" s="56">
         <v>4</v>
       </c>
-      <c r="E594" s="60" t="s">
+      <c r="E594" s="57" t="s">
         <v>86</v>
       </c>
       <c r="F594" s="58">
@@ -22283,7 +22273,7 @@
       <c r="D595" s="56">
         <v>4</v>
       </c>
-      <c r="E595" s="60" t="s">
+      <c r="E595" s="57" t="s">
         <v>87</v>
       </c>
       <c r="F595" s="58">
@@ -22298,28 +22288,28 @@
     </row>
     <row r="596" s="9" customFormat="1" customHeight="1" spans="1:12">
       <c r="A596" s="50">
-        <f>(B596)*10000+C596+F596*100+D596*100000</f>
+        <f t="shared" si="23"/>
         <v>1020400126</v>
       </c>
-      <c r="B596" s="61">
+      <c r="B596" s="60">
         <v>102000</v>
       </c>
       <c r="C596" s="50">
         <v>26</v>
       </c>
-      <c r="D596" s="62">
-        <v>4</v>
-      </c>
-      <c r="E596" s="63" t="s">
+      <c r="D596" s="61">
+        <v>4</v>
+      </c>
+      <c r="E596" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="F596" s="64">
+      <c r="F596" s="63">
         <v>1</v>
       </c>
       <c r="G596" s="51">
         <v>0</v>
       </c>
-      <c r="H596" s="65">
+      <c r="H596" s="64">
         <v>30200010</v>
       </c>
       <c r="I596" s="51"/>
@@ -22329,28 +22319,28 @@
     </row>
     <row r="597" s="9" customFormat="1" customHeight="1" spans="1:12">
       <c r="A597" s="50">
-        <f>(B597)*10000+C597+F597*100+D597*100000</f>
+        <f t="shared" si="23"/>
         <v>1020400127</v>
       </c>
-      <c r="B597" s="61">
+      <c r="B597" s="60">
         <v>102000</v>
       </c>
       <c r="C597" s="50">
         <v>27</v>
       </c>
-      <c r="D597" s="62">
-        <v>4</v>
-      </c>
-      <c r="E597" s="63" t="s">
+      <c r="D597" s="61">
+        <v>4</v>
+      </c>
+      <c r="E597" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="F597" s="64">
+      <c r="F597" s="63">
         <v>1</v>
       </c>
       <c r="G597" s="51">
         <v>0</v>
       </c>
-      <c r="H597" s="65">
+      <c r="H597" s="64">
         <v>30200011</v>
       </c>
       <c r="I597" s="51"/>
@@ -22360,28 +22350,28 @@
     </row>
     <row r="598" s="9" customFormat="1" customHeight="1" spans="1:12">
       <c r="A598" s="50">
-        <f>(B598)*10000+C598+F598*100+D598*100000</f>
+        <f t="shared" si="23"/>
         <v>1020400128</v>
       </c>
-      <c r="B598" s="61">
+      <c r="B598" s="60">
         <v>102000</v>
       </c>
       <c r="C598" s="50">
         <v>28</v>
       </c>
-      <c r="D598" s="62">
-        <v>4</v>
-      </c>
-      <c r="E598" s="63" t="s">
+      <c r="D598" s="61">
+        <v>4</v>
+      </c>
+      <c r="E598" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="F598" s="64">
+      <c r="F598" s="63">
         <v>1</v>
       </c>
       <c r="G598" s="51">
         <v>0</v>
       </c>
-      <c r="H598" s="65">
+      <c r="H598" s="64">
         <v>30200012</v>
       </c>
       <c r="I598" s="51"/>
@@ -22391,28 +22381,28 @@
     </row>
     <row r="599" s="9" customFormat="1" customHeight="1" spans="1:12">
       <c r="A599" s="50">
-        <f>(B599)*10000+C599+F599*100+D599*100000</f>
+        <f t="shared" si="23"/>
         <v>1020400129</v>
       </c>
-      <c r="B599" s="61">
+      <c r="B599" s="60">
         <v>102000</v>
       </c>
       <c r="C599" s="50">
         <v>29</v>
       </c>
-      <c r="D599" s="62">
-        <v>4</v>
-      </c>
-      <c r="E599" s="63" t="s">
+      <c r="D599" s="61">
+        <v>4</v>
+      </c>
+      <c r="E599" s="62" t="s">
         <v>91</v>
       </c>
-      <c r="F599" s="64">
+      <c r="F599" s="63">
         <v>1</v>
       </c>
       <c r="G599" s="51">
         <v>0</v>
       </c>
-      <c r="H599" s="65">
+      <c r="H599" s="64">
         <v>30200013</v>
       </c>
       <c r="I599" s="51"/>
@@ -22422,7 +22412,7 @@
     </row>
     <row r="600" customHeight="1" spans="1:12">
       <c r="A600" s="3">
-        <f>(B600)*10000+C600+F600*100+D600*100000</f>
+        <f t="shared" si="23"/>
         <v>1020400139</v>
       </c>
       <c r="B600" s="10">
@@ -22434,7 +22424,7 @@
       <c r="D600" s="56">
         <v>4</v>
       </c>
-      <c r="E600" s="66" t="s">
+      <c r="E600" s="65" t="s">
         <v>92</v>
       </c>
       <c r="F600" s="58">
@@ -22443,13 +22433,13 @@
       <c r="G600" s="12">
         <v>0</v>
       </c>
-      <c r="H600" s="67">
+      <c r="H600" s="5">
         <v>30200009</v>
       </c>
     </row>
     <row r="601" customHeight="1" spans="1:12">
       <c r="A601" s="3">
-        <f>(B601)*10000+C601+F601*100+D601*100000</f>
+        <f t="shared" si="23"/>
         <v>1020400140</v>
       </c>
       <c r="B601" s="10">
@@ -22461,7 +22451,7 @@
       <c r="D601" s="56">
         <v>4</v>
       </c>
-      <c r="E601" s="66" t="s">
+      <c r="E601" s="65" t="s">
         <v>93</v>
       </c>
       <c r="F601" s="58">
@@ -22470,13 +22460,13 @@
       <c r="G601" s="12">
         <v>0</v>
       </c>
-      <c r="H601" s="67">
+      <c r="H601" s="5">
         <v>30200014</v>
       </c>
     </row>
     <row r="602" customHeight="1" spans="1:12">
       <c r="A602" s="3">
-        <f>(B602)*10000+C602+F602*100+D602*100000</f>
+        <f t="shared" si="23"/>
         <v>1020400130</v>
       </c>
       <c r="B602" s="10">
@@ -22485,10 +22475,10 @@
       <c r="C602" s="2">
         <v>30</v>
       </c>
-      <c r="D602" s="68">
-        <v>4</v>
-      </c>
-      <c r="E602" s="63" t="s">
+      <c r="D602" s="66">
+        <v>4</v>
+      </c>
+      <c r="E602" s="62" t="s">
         <v>94</v>
       </c>
       <c r="F602" s="58">
@@ -22497,13 +22487,13 @@
       <c r="G602" s="12">
         <v>0</v>
       </c>
-      <c r="H602" s="69">
+      <c r="H602" s="67">
         <v>30200015</v>
       </c>
     </row>
     <row r="603" customHeight="1" spans="1:12">
       <c r="A603" s="3">
-        <f>(B603)*10000+C603+F603*100+D603*100000</f>
+        <f t="shared" si="23"/>
         <v>1020400131</v>
       </c>
       <c r="B603" s="10">
@@ -22512,10 +22502,10 @@
       <c r="C603" s="2">
         <v>31</v>
       </c>
-      <c r="D603" s="68">
-        <v>4</v>
-      </c>
-      <c r="E603" s="63" t="s">
+      <c r="D603" s="66">
+        <v>4</v>
+      </c>
+      <c r="E603" s="62" t="s">
         <v>95</v>
       </c>
       <c r="F603" s="58">
@@ -22524,13 +22514,13 @@
       <c r="G603" s="12">
         <v>0</v>
       </c>
-      <c r="H603" s="69">
+      <c r="H603" s="67">
         <v>30200016</v>
       </c>
     </row>
     <row r="604" customHeight="1" spans="1:12">
       <c r="A604" s="3">
-        <f>(B604)*10000+C604+F604*100+D604*100000</f>
+        <f t="shared" si="23"/>
         <v>1020400132</v>
       </c>
       <c r="B604" s="10">
@@ -22539,10 +22529,10 @@
       <c r="C604" s="2">
         <v>32</v>
       </c>
-      <c r="D604" s="68">
-        <v>4</v>
-      </c>
-      <c r="E604" s="63" t="s">
+      <c r="D604" s="66">
+        <v>4</v>
+      </c>
+      <c r="E604" s="62" t="s">
         <v>96</v>
       </c>
       <c r="F604" s="58">
@@ -22551,13 +22541,13 @@
       <c r="G604" s="12">
         <v>0</v>
       </c>
-      <c r="H604" s="69">
+      <c r="H604" s="67">
         <v>30200017</v>
       </c>
     </row>
     <row r="605" customHeight="1" spans="1:12">
       <c r="A605" s="3">
-        <f>(B605)*10000+C605+F605*100+D605*100000</f>
+        <f t="shared" si="23"/>
         <v>1020400133</v>
       </c>
       <c r="B605" s="10">
@@ -22566,10 +22556,10 @@
       <c r="C605" s="2">
         <v>33</v>
       </c>
-      <c r="D605" s="68">
-        <v>4</v>
-      </c>
-      <c r="E605" s="70" t="s">
+      <c r="D605" s="66">
+        <v>4</v>
+      </c>
+      <c r="E605" s="62" t="s">
         <v>97</v>
       </c>
       <c r="F605" s="58">
@@ -22578,13 +22568,13 @@
       <c r="G605" s="12">
         <v>0</v>
       </c>
-      <c r="H605" s="69">
+      <c r="H605" s="67">
         <v>30200018</v>
       </c>
     </row>
     <row r="606" customHeight="1" spans="1:12">
       <c r="A606" s="3">
-        <f>(B606)*10000+C606+F606*100+D606*100000</f>
+        <f t="shared" si="23"/>
         <v>1020400141</v>
       </c>
       <c r="B606" s="10">
@@ -22611,7 +22601,7 @@
     </row>
     <row r="607" customHeight="1" spans="1:12">
       <c r="A607" s="3">
-        <f>(B607)*10000+C607+F607*100+D607*100000</f>
+        <f t="shared" si="23"/>
         <v>1020400142</v>
       </c>
       <c r="B607" s="10">
@@ -22638,7 +22628,7 @@
     </row>
     <row r="608" customHeight="1" spans="1:12">
       <c r="A608" s="3">
-        <f>(B608)*10000+C608+F608*100+D608*100000</f>
+        <f t="shared" si="23"/>
         <v>1020400135</v>
       </c>
       <c r="B608" s="10">
@@ -22650,14 +22640,14 @@
       <c r="D608" s="2">
         <v>4</v>
       </c>
-      <c r="E608" s="71"/>
+      <c r="E608" s="3"/>
       <c r="F608" s="2">
         <v>1</v>
       </c>
       <c r="G608" s="12">
         <v>0</v>
       </c>
-      <c r="H608" s="69"/>
+      <c r="H608" s="67"/>
       <c r="K608" s="2">
         <v>102000101</v>
       </c>
@@ -22667,7 +22657,7 @@
     </row>
     <row r="609" customHeight="1" spans="1:12">
       <c r="A609" s="3">
-        <f>(B609)*10000+C609+F609*100+D609*100000</f>
+        <f t="shared" si="23"/>
         <v>1020400136</v>
       </c>
       <c r="B609" s="10">
@@ -22694,7 +22684,7 @@
     </row>
     <row r="610" customHeight="1" spans="1:12">
       <c r="A610" s="3">
-        <f>(B610)*10000+C610+F610*100+D610*100000</f>
+        <f t="shared" si="23"/>
         <v>1020400137</v>
       </c>
       <c r="B610" s="10">
@@ -22721,7 +22711,7 @@
     </row>
     <row r="611" customHeight="1" spans="1:12">
       <c r="A611" s="3">
-        <f>(B611)*10000+C611+F611*100+D611*100000</f>
+        <f t="shared" si="23"/>
         <v>1020400138</v>
       </c>
       <c r="B611" s="10">
@@ -22746,767 +22736,1557 @@
         <v>68</v>
       </c>
     </row>
+    <row r="612" customHeight="1" spans="1:12">
+      <c r="A612" s="3">
+        <f t="shared" ref="A612:A641" si="24">(B612)*10000+C612+F612*100+D612*100000</f>
+        <v>1038100301</v>
+      </c>
+      <c r="B612" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C612" s="2">
+        <v>1</v>
+      </c>
+      <c r="D612" s="2">
+        <v>1</v>
+      </c>
+      <c r="F612" s="2">
+        <v>3</v>
+      </c>
+      <c r="G612" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="613" customHeight="1" spans="1:12">
+      <c r="A613" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100302</v>
+      </c>
+      <c r="B613" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C613" s="2">
+        <v>2</v>
+      </c>
+      <c r="D613" s="2">
+        <v>1</v>
+      </c>
+      <c r="F613" s="2">
+        <v>3</v>
+      </c>
+      <c r="G613" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="614" customHeight="1" spans="1:12">
+      <c r="A614" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100303</v>
+      </c>
+      <c r="B614" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C614" s="2">
+        <v>3</v>
+      </c>
+      <c r="D614" s="2">
+        <v>1</v>
+      </c>
+      <c r="F614" s="2">
+        <v>3</v>
+      </c>
+      <c r="G614" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="615" customHeight="1" spans="1:12">
+      <c r="A615" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100304</v>
+      </c>
+      <c r="B615" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C615" s="2">
+        <v>4</v>
+      </c>
+      <c r="D615" s="2">
+        <v>1</v>
+      </c>
+      <c r="F615" s="2">
+        <v>3</v>
+      </c>
+      <c r="G615" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="616" customHeight="1" spans="1:12">
+      <c r="A616" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100305</v>
+      </c>
+      <c r="B616" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C616" s="2">
+        <v>5</v>
+      </c>
+      <c r="D616" s="2">
+        <v>1</v>
+      </c>
+      <c r="F616" s="2">
+        <v>3</v>
+      </c>
+      <c r="G616" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="617" customHeight="1" spans="1:12">
+      <c r="A617" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100306</v>
+      </c>
+      <c r="B617" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C617" s="2">
+        <v>6</v>
+      </c>
+      <c r="D617" s="2">
+        <v>1</v>
+      </c>
+      <c r="F617" s="2">
+        <v>3</v>
+      </c>
+      <c r="G617" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="618" customHeight="1" spans="1:12">
+      <c r="A618" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100307</v>
+      </c>
+      <c r="B618" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C618" s="2">
+        <v>7</v>
+      </c>
+      <c r="D618" s="2">
+        <v>1</v>
+      </c>
+      <c r="F618" s="2">
+        <v>3</v>
+      </c>
+      <c r="G618" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="619" customHeight="1" spans="1:12">
+      <c r="A619" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100308</v>
+      </c>
+      <c r="B619" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C619" s="2">
+        <v>8</v>
+      </c>
+      <c r="D619" s="2">
+        <v>1</v>
+      </c>
+      <c r="F619" s="2">
+        <v>3</v>
+      </c>
+      <c r="G619" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="620" customHeight="1" spans="1:12">
+      <c r="A620" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100309</v>
+      </c>
+      <c r="B620" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C620" s="2">
+        <v>9</v>
+      </c>
+      <c r="D620" s="2">
+        <v>1</v>
+      </c>
+      <c r="F620" s="2">
+        <v>3</v>
+      </c>
+      <c r="G620" s="12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="621" customHeight="1" spans="1:12">
+      <c r="A621" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100310</v>
+      </c>
+      <c r="B621" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C621" s="2">
+        <v>10</v>
+      </c>
+      <c r="D621" s="2">
+        <v>1</v>
+      </c>
+      <c r="F621" s="2">
+        <v>3</v>
+      </c>
+      <c r="G621" s="12">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="622" customHeight="1" spans="1:12">
+      <c r="A622" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100401</v>
+      </c>
+      <c r="B622" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C622" s="2">
+        <v>1</v>
+      </c>
+      <c r="D622" s="2">
+        <v>1</v>
+      </c>
+      <c r="F622" s="2">
+        <v>4</v>
+      </c>
+      <c r="G622" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="623" customHeight="1" spans="1:12">
+      <c r="A623" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100402</v>
+      </c>
+      <c r="B623" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C623" s="2">
+        <v>2</v>
+      </c>
+      <c r="D623" s="2">
+        <v>1</v>
+      </c>
+      <c r="F623" s="2">
+        <v>4</v>
+      </c>
+      <c r="G623" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="624" customHeight="1" spans="1:12">
+      <c r="A624" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100403</v>
+      </c>
+      <c r="B624" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C624" s="2">
+        <v>3</v>
+      </c>
+      <c r="D624" s="2">
+        <v>1</v>
+      </c>
+      <c r="F624" s="2">
+        <v>4</v>
+      </c>
+      <c r="G624" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="625" customHeight="1" spans="1:7">
+      <c r="A625" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100404</v>
+      </c>
+      <c r="B625" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C625" s="2">
+        <v>4</v>
+      </c>
+      <c r="D625" s="2">
+        <v>1</v>
+      </c>
+      <c r="F625" s="2">
+        <v>4</v>
+      </c>
+      <c r="G625" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="626" customHeight="1" spans="1:7">
+      <c r="A626" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100405</v>
+      </c>
+      <c r="B626" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C626" s="2">
+        <v>5</v>
+      </c>
+      <c r="D626" s="2">
+        <v>1</v>
+      </c>
+      <c r="F626" s="2">
+        <v>4</v>
+      </c>
+      <c r="G626" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="627" customHeight="1" spans="1:7">
+      <c r="A627" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100406</v>
+      </c>
+      <c r="B627" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C627" s="2">
+        <v>6</v>
+      </c>
+      <c r="D627" s="2">
+        <v>1</v>
+      </c>
+      <c r="F627" s="2">
+        <v>4</v>
+      </c>
+      <c r="G627" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="628" customHeight="1" spans="1:7">
+      <c r="A628" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100407</v>
+      </c>
+      <c r="B628" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C628" s="2">
+        <v>7</v>
+      </c>
+      <c r="D628" s="2">
+        <v>1</v>
+      </c>
+      <c r="F628" s="2">
+        <v>4</v>
+      </c>
+      <c r="G628" s="12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="629" customHeight="1" spans="1:7">
+      <c r="A629" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100408</v>
+      </c>
+      <c r="B629" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C629" s="2">
+        <v>8</v>
+      </c>
+      <c r="D629" s="2">
+        <v>1</v>
+      </c>
+      <c r="F629" s="2">
+        <v>4</v>
+      </c>
+      <c r="G629" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="630" customHeight="1" spans="1:7">
+      <c r="A630" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100409</v>
+      </c>
+      <c r="B630" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C630" s="2">
+        <v>9</v>
+      </c>
+      <c r="D630" s="2">
+        <v>1</v>
+      </c>
+      <c r="F630" s="2">
+        <v>4</v>
+      </c>
+      <c r="G630" s="12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="631" customHeight="1" spans="1:7">
+      <c r="A631" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100410</v>
+      </c>
+      <c r="B631" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C631" s="2">
+        <v>10</v>
+      </c>
+      <c r="D631" s="2">
+        <v>1</v>
+      </c>
+      <c r="F631" s="2">
+        <v>4</v>
+      </c>
+      <c r="G631" s="12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="632" customHeight="1" spans="1:7">
+      <c r="A632" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100501</v>
+      </c>
+      <c r="B632" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C632" s="2">
+        <v>1</v>
+      </c>
+      <c r="D632" s="2">
+        <v>1</v>
+      </c>
+      <c r="F632" s="2">
+        <v>5</v>
+      </c>
+      <c r="G632" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="633" customHeight="1" spans="1:7">
+      <c r="A633" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100502</v>
+      </c>
+      <c r="B633" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C633" s="2">
+        <v>2</v>
+      </c>
+      <c r="D633" s="2">
+        <v>1</v>
+      </c>
+      <c r="F633" s="2">
+        <v>5</v>
+      </c>
+      <c r="G633" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="634" customHeight="1" spans="1:7">
+      <c r="A634" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100503</v>
+      </c>
+      <c r="B634" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C634" s="2">
+        <v>3</v>
+      </c>
+      <c r="D634" s="2">
+        <v>1</v>
+      </c>
+      <c r="F634" s="2">
+        <v>5</v>
+      </c>
+      <c r="G634" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="635" customHeight="1" spans="1:7">
+      <c r="A635" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100504</v>
+      </c>
+      <c r="B635" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C635" s="2">
+        <v>4</v>
+      </c>
+      <c r="D635" s="2">
+        <v>1</v>
+      </c>
+      <c r="F635" s="2">
+        <v>5</v>
+      </c>
+      <c r="G635" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="636" customHeight="1" spans="1:7">
+      <c r="A636" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100505</v>
+      </c>
+      <c r="B636" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C636" s="2">
+        <v>5</v>
+      </c>
+      <c r="D636" s="2">
+        <v>1</v>
+      </c>
+      <c r="F636" s="2">
+        <v>5</v>
+      </c>
+      <c r="G636" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="637" customHeight="1" spans="1:7">
+      <c r="A637" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100506</v>
+      </c>
+      <c r="B637" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C637" s="2">
+        <v>6</v>
+      </c>
+      <c r="D637" s="2">
+        <v>1</v>
+      </c>
+      <c r="F637" s="2">
+        <v>5</v>
+      </c>
+      <c r="G637" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="638" customHeight="1" spans="1:7">
+      <c r="A638" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100507</v>
+      </c>
+      <c r="B638" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C638" s="2">
+        <v>7</v>
+      </c>
+      <c r="D638" s="2">
+        <v>1</v>
+      </c>
+      <c r="F638" s="2">
+        <v>5</v>
+      </c>
+      <c r="G638" s="12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="639" customHeight="1" spans="1:7">
+      <c r="A639" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100508</v>
+      </c>
+      <c r="B639" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C639" s="2">
+        <v>8</v>
+      </c>
+      <c r="D639" s="2">
+        <v>1</v>
+      </c>
+      <c r="F639" s="2">
+        <v>5</v>
+      </c>
+      <c r="G639" s="12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="640" customHeight="1" spans="1:7">
+      <c r="A640" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100509</v>
+      </c>
+      <c r="B640" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C640" s="2">
+        <v>9</v>
+      </c>
+      <c r="D640" s="2">
+        <v>1</v>
+      </c>
+      <c r="F640" s="2">
+        <v>5</v>
+      </c>
+      <c r="G640" s="12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="641" customHeight="1" spans="1:12">
+      <c r="A641" s="3">
+        <f t="shared" si="24"/>
+        <v>1038100510</v>
+      </c>
+      <c r="B641" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C641" s="2">
+        <v>10</v>
+      </c>
+      <c r="D641" s="2">
+        <v>1</v>
+      </c>
+      <c r="F641" s="2">
+        <v>5</v>
+      </c>
+      <c r="G641" s="12">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="642" customHeight="1" spans="1:12">
+      <c r="A642" s="3">
+        <f t="shared" ref="A642:A647" si="25">(B642)*10000+C642+F642*100+D642*100000</f>
+        <v>1038400111</v>
+      </c>
+      <c r="B642" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C642" s="2">
+        <v>11</v>
+      </c>
+      <c r="D642" s="2">
+        <v>4</v>
+      </c>
+      <c r="F642" s="2">
+        <v>1</v>
+      </c>
+      <c r="G642" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="643" customHeight="1" spans="1:12">
+      <c r="A643" s="3">
+        <f t="shared" si="25"/>
+        <v>1038400112</v>
+      </c>
+      <c r="B643" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C643" s="2">
+        <v>12</v>
+      </c>
+      <c r="D643" s="2">
+        <v>4</v>
+      </c>
+      <c r="F643" s="2">
+        <v>1</v>
+      </c>
+      <c r="G643" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="644" customHeight="1" spans="1:12">
+      <c r="A644" s="3">
+        <f t="shared" si="25"/>
+        <v>1038400113</v>
+      </c>
+      <c r="B644" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C644" s="2">
+        <v>13</v>
+      </c>
+      <c r="D644" s="2">
+        <v>4</v>
+      </c>
+      <c r="F644" s="2">
+        <v>1</v>
+      </c>
+      <c r="G644" s="12">
+        <v>0</v>
+      </c>
+      <c r="K644" s="2">
+        <v>103800101</v>
+      </c>
+      <c r="L644" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="645" customHeight="1" spans="1:12">
+      <c r="A645" s="3">
+        <f t="shared" si="25"/>
+        <v>1038400114</v>
+      </c>
+      <c r="B645" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C645" s="2">
+        <v>14</v>
+      </c>
+      <c r="D645" s="2">
+        <v>4</v>
+      </c>
+      <c r="F645" s="2">
+        <v>1</v>
+      </c>
+      <c r="G645" s="12">
+        <v>0</v>
+      </c>
+      <c r="K645" s="2">
+        <v>103800102</v>
+      </c>
+      <c r="L645" s="14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="646" customHeight="1" spans="1:12">
+      <c r="A646" s="3">
+        <f t="shared" si="25"/>
+        <v>1038400115</v>
+      </c>
+      <c r="B646" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C646" s="2">
+        <v>15</v>
+      </c>
+      <c r="D646" s="2">
+        <v>4</v>
+      </c>
+      <c r="F646" s="2">
+        <v>1</v>
+      </c>
+      <c r="G646" s="12">
+        <v>0</v>
+      </c>
+      <c r="K646" s="2">
+        <v>103800103</v>
+      </c>
+      <c r="L646" s="14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="647" customHeight="1" spans="1:12">
+      <c r="A647" s="3">
+        <f t="shared" si="25"/>
+        <v>1038400116</v>
+      </c>
+      <c r="B647" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C647" s="2">
+        <v>16</v>
+      </c>
+      <c r="D647" s="2">
+        <v>4</v>
+      </c>
+      <c r="F647" s="2">
+        <v>1</v>
+      </c>
+      <c r="G647" s="12">
+        <v>0</v>
+      </c>
+      <c r="K647" s="2">
+        <v>103800104</v>
+      </c>
+      <c r="L647" s="14" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L607" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L611" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="0" priority="145">
+    <cfRule type="expression" dxfId="0" priority="147">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D85:E85">
-    <cfRule type="expression" dxfId="0" priority="171">
+    <cfRule type="expression" dxfId="0" priority="173">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D86:E86">
-    <cfRule type="expression" dxfId="0" priority="136">
+    <cfRule type="expression" dxfId="0" priority="138">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105">
-    <cfRule type="duplicateValues" dxfId="1" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105:E105">
-    <cfRule type="expression" dxfId="0" priority="116">
+    <cfRule type="expression" dxfId="0" priority="118">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I105">
-    <cfRule type="expression" dxfId="0" priority="118">
+    <cfRule type="expression" dxfId="0" priority="120">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A106">
-    <cfRule type="duplicateValues" dxfId="1" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D106:E106">
-    <cfRule type="expression" dxfId="0" priority="112">
+    <cfRule type="expression" dxfId="0" priority="114">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I106">
-    <cfRule type="expression" dxfId="0" priority="114">
+    <cfRule type="expression" dxfId="0" priority="116">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="1" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D107:E107">
-    <cfRule type="expression" dxfId="0" priority="108">
+    <cfRule type="expression" dxfId="0" priority="110">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I107">
-    <cfRule type="expression" dxfId="0" priority="110">
+    <cfRule type="expression" dxfId="0" priority="112">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108">
-    <cfRule type="duplicateValues" dxfId="1" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D108:E108">
-    <cfRule type="expression" dxfId="0" priority="104">
+    <cfRule type="expression" dxfId="0" priority="106">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I108">
-    <cfRule type="expression" dxfId="0" priority="106">
+    <cfRule type="expression" dxfId="0" priority="108">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" dxfId="1" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D109:E109">
-    <cfRule type="expression" dxfId="0" priority="100">
+    <cfRule type="expression" dxfId="0" priority="102">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I109">
-    <cfRule type="expression" dxfId="0" priority="102">
+    <cfRule type="expression" dxfId="0" priority="104">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110">
-    <cfRule type="duplicateValues" dxfId="1" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D110:E110">
-    <cfRule type="expression" dxfId="0" priority="96">
+    <cfRule type="expression" dxfId="0" priority="98">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I110">
-    <cfRule type="expression" dxfId="0" priority="98">
+    <cfRule type="expression" dxfId="0" priority="100">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A111">
-    <cfRule type="duplicateValues" dxfId="1" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D111:E111">
-    <cfRule type="expression" dxfId="0" priority="92">
+    <cfRule type="expression" dxfId="0" priority="94">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I111">
-    <cfRule type="expression" dxfId="0" priority="94">
+    <cfRule type="expression" dxfId="0" priority="96">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112">
-    <cfRule type="duplicateValues" dxfId="1" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D112:E112">
-    <cfRule type="expression" dxfId="0" priority="88">
+    <cfRule type="expression" dxfId="0" priority="90">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I112">
-    <cfRule type="expression" dxfId="0" priority="90">
+    <cfRule type="expression" dxfId="0" priority="92">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A113">
-    <cfRule type="duplicateValues" dxfId="1" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D113:E113">
-    <cfRule type="expression" dxfId="0" priority="84">
+    <cfRule type="expression" dxfId="0" priority="86">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I113">
-    <cfRule type="expression" dxfId="0" priority="86">
+    <cfRule type="expression" dxfId="0" priority="88">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114">
-    <cfRule type="duplicateValues" dxfId="1" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D114:E114">
-    <cfRule type="expression" dxfId="0" priority="80">
+    <cfRule type="expression" dxfId="0" priority="82">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I114">
-    <cfRule type="expression" dxfId="0" priority="82">
+    <cfRule type="expression" dxfId="0" priority="84">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A115">
-    <cfRule type="duplicateValues" dxfId="1" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D115:E115">
-    <cfRule type="expression" dxfId="0" priority="76">
+    <cfRule type="expression" dxfId="0" priority="78">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I115">
-    <cfRule type="expression" dxfId="0" priority="78">
+    <cfRule type="expression" dxfId="0" priority="80">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A116">
-    <cfRule type="duplicateValues" dxfId="1" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D116:E116">
-    <cfRule type="expression" dxfId="0" priority="72">
+    <cfRule type="expression" dxfId="0" priority="74">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I116">
-    <cfRule type="expression" dxfId="0" priority="74">
+    <cfRule type="expression" dxfId="0" priority="76">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117">
-    <cfRule type="duplicateValues" dxfId="1" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D117:E117">
-    <cfRule type="expression" dxfId="0" priority="68">
+    <cfRule type="expression" dxfId="0" priority="70">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I117">
-    <cfRule type="expression" dxfId="0" priority="70">
+    <cfRule type="expression" dxfId="0" priority="72">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A118">
-    <cfRule type="duplicateValues" dxfId="1" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D118:E118">
-    <cfRule type="expression" dxfId="0" priority="64">
+    <cfRule type="expression" dxfId="0" priority="66">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I118">
-    <cfRule type="expression" dxfId="0" priority="66">
+    <cfRule type="expression" dxfId="0" priority="68">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A119">
-    <cfRule type="duplicateValues" dxfId="1" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D119:E119">
-    <cfRule type="expression" dxfId="0" priority="60">
+    <cfRule type="expression" dxfId="0" priority="62">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I119">
-    <cfRule type="expression" dxfId="0" priority="62">
+    <cfRule type="expression" dxfId="0" priority="64">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A120">
-    <cfRule type="duplicateValues" dxfId="1" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D120:E120">
-    <cfRule type="expression" dxfId="0" priority="56">
+    <cfRule type="expression" dxfId="0" priority="58">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I120">
-    <cfRule type="expression" dxfId="0" priority="58">
+    <cfRule type="expression" dxfId="0" priority="60">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A121">
-    <cfRule type="duplicateValues" dxfId="1" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D121:E121">
-    <cfRule type="expression" dxfId="0" priority="52">
+    <cfRule type="expression" dxfId="0" priority="54">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I121">
-    <cfRule type="expression" dxfId="0" priority="54">
+    <cfRule type="expression" dxfId="0" priority="56">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A122">
-    <cfRule type="duplicateValues" dxfId="1" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D122:E122">
-    <cfRule type="expression" dxfId="0" priority="48">
+    <cfRule type="expression" dxfId="0" priority="50">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I122">
-    <cfRule type="expression" dxfId="0" priority="50">
+    <cfRule type="expression" dxfId="0" priority="52">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A123">
-    <cfRule type="duplicateValues" dxfId="1" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D123:E123">
-    <cfRule type="expression" dxfId="0" priority="44">
+    <cfRule type="expression" dxfId="0" priority="46">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I123">
-    <cfRule type="expression" dxfId="0" priority="46">
+    <cfRule type="expression" dxfId="0" priority="48">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C134:L134">
-    <cfRule type="expression" dxfId="0" priority="172">
+    <cfRule type="expression" dxfId="0" priority="174">
       <formula>MOD($B134,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="expression" dxfId="0" priority="36">
+    <cfRule type="expression" dxfId="0" priority="38">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A178">
-    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B178">
+    <cfRule type="expression" dxfId="0" priority="34">
+      <formula>MOD($B178,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D178:E178">
     <cfRule type="expression" dxfId="0" priority="32">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D178:E178">
-    <cfRule type="expression" dxfId="0" priority="30">
-      <formula>MOD($B178,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H309">
-    <cfRule type="expression" dxfId="0" priority="450">
+    <cfRule type="expression" dxfId="0" priority="452">
       <formula>MOD($B308,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H321">
-    <cfRule type="expression" dxfId="0" priority="449">
+    <cfRule type="expression" dxfId="0" priority="451">
       <formula>MOD($B320,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L346">
-    <cfRule type="expression" dxfId="0" priority="451">
+    <cfRule type="expression" dxfId="0" priority="453">
       <formula>MOD($B350,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E549">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H592">
+    <cfRule type="expression" dxfId="0" priority="457">
+      <formula>MOD(#REF!,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L644">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>MOD($B644,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A48:A60">
+    <cfRule type="duplicateValues" dxfId="1" priority="135"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A87:A92">
+    <cfRule type="duplicateValues" dxfId="1" priority="129"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A93:A98">
+    <cfRule type="duplicateValues" dxfId="1" priority="126"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A99:A104">
+    <cfRule type="duplicateValues" dxfId="1" priority="123"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A135:A177">
+    <cfRule type="duplicateValues" dxfId="1" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A209:A469">
+    <cfRule type="duplicateValues" dxfId="1" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A521:A647">
+    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48:B60">
+    <cfRule type="expression" dxfId="0" priority="133">
+      <formula>MOD($B48,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C77:C84">
+    <cfRule type="expression" dxfId="0" priority="136">
+      <formula>MOD($B77,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C271:C281">
+    <cfRule type="expression" dxfId="0" priority="25">
+      <formula>MOD($B271,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C282:C296">
+    <cfRule type="expression" dxfId="0" priority="23">
+      <formula>MOD($B282,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C602:C605">
+    <cfRule type="expression" dxfId="0" priority="462">
+      <formula>MOD($B618,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C606:C611">
+    <cfRule type="expression" dxfId="0" priority="459">
+      <formula>MOD($B623,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E93:E98">
+    <cfRule type="expression" dxfId="0" priority="125">
+      <formula>MOD($B93,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E99:E104">
+    <cfRule type="expression" dxfId="0" priority="122">
+      <formula>MOD($B99,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E257:E268">
+    <cfRule type="expression" dxfId="0" priority="26">
+      <formula>MOD($B257,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E271:E279">
+    <cfRule type="expression" dxfId="0" priority="24">
+      <formula>MOD($B271,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E282:E290">
+    <cfRule type="expression" dxfId="0" priority="22">
+      <formula>MOD($B282,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E592:E595">
+    <cfRule type="expression" dxfId="0" priority="456">
+      <formula>MOD(#REF!,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E596:E599">
+    <cfRule type="expression" dxfId="0" priority="7">
+      <formula>MOD(#REF!,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E600:E601">
+    <cfRule type="expression" dxfId="0" priority="454">
+      <formula>MOD(#REF!,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E602:E605">
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>MOD(#REF!,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H593:H599">
+    <cfRule type="expression" dxfId="0" priority="458">
+      <formula>MOD(#REF!,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H600:H601">
+    <cfRule type="expression" dxfId="0" priority="5">
+      <formula>MOD(#REF!,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H606:H608">
     <cfRule type="expression" dxfId="0" priority="455">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A48:A60">
-    <cfRule type="duplicateValues" dxfId="1" priority="133"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A87:A92">
-    <cfRule type="duplicateValues" dxfId="1" priority="127"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A93:A98">
-    <cfRule type="duplicateValues" dxfId="1" priority="124"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A99:A104">
-    <cfRule type="duplicateValues" dxfId="1" priority="121"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A135:A177">
-    <cfRule type="duplicateValues" dxfId="1" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A209:A469">
-    <cfRule type="duplicateValues" dxfId="1" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A521:A611">
-    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B48:B60">
-    <cfRule type="expression" dxfId="0" priority="131">
-      <formula>MOD($B48,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C77:C84">
-    <cfRule type="expression" dxfId="0" priority="134">
-      <formula>MOD($B77,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C271:C281">
-    <cfRule type="expression" dxfId="0" priority="23">
-      <formula>MOD($B271,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C282:C296">
-    <cfRule type="expression" dxfId="0" priority="21">
-      <formula>MOD($B282,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C602:C605">
-    <cfRule type="expression" dxfId="0" priority="460">
-      <formula>MOD($B618,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C606:C611">
-    <cfRule type="expression" dxfId="0" priority="457">
-      <formula>MOD($B623,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E93:E98">
-    <cfRule type="expression" dxfId="0" priority="123">
-      <formula>MOD($B93,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E99:E104">
-    <cfRule type="expression" dxfId="0" priority="120">
-      <formula>MOD($B99,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E257:E268">
-    <cfRule type="expression" dxfId="0" priority="24">
-      <formula>MOD($B257,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E271:E279">
-    <cfRule type="expression" dxfId="0" priority="22">
-      <formula>MOD($B271,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E282:E290">
-    <cfRule type="expression" dxfId="0" priority="20">
-      <formula>MOD($B282,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E592:E595">
-    <cfRule type="expression" dxfId="0" priority="454">
-      <formula>MOD(#REF!,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E596:E599">
-    <cfRule type="expression" dxfId="0" priority="5">
-      <formula>MOD(#REF!,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E600:E601">
-    <cfRule type="expression" dxfId="0" priority="452">
-      <formula>MOD(#REF!,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E602:E605">
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>MOD(#REF!,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H593:H599">
-    <cfRule type="expression" dxfId="0" priority="456">
-      <formula>MOD(#REF!,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H600:H601">
-    <cfRule type="expression" dxfId="0" priority="3">
-      <formula>MOD(#REF!,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H606:H608">
-    <cfRule type="expression" dxfId="0" priority="453">
-      <formula>MOD(#REF!,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="K39:K42">
-    <cfRule type="duplicateValues" dxfId="2" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="149"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K169:K172">
-    <cfRule type="duplicateValues" dxfId="2" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K293:K296">
-    <cfRule type="expression" dxfId="0" priority="18">
+    <cfRule type="expression" dxfId="0" priority="20">
       <formula>MOD($B293,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K347:K350">
-    <cfRule type="expression" dxfId="0" priority="16">
+    <cfRule type="expression" dxfId="0" priority="18">
       <formula>MOD($B346,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K384:K387">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="0" priority="16">
       <formula>MOD($B384,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K422:K425">
-    <cfRule type="expression" dxfId="0" priority="12">
+    <cfRule type="expression" dxfId="0" priority="14">
       <formula>MOD($B422,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K609:K611">
-    <cfRule type="expression" dxfId="0" priority="7">
+    <cfRule type="expression" dxfId="0" priority="9">
       <formula>MOD($B602,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L205:L208">
-    <cfRule type="expression" dxfId="0" priority="29">
+    <cfRule type="expression" dxfId="0" priority="31">
       <formula>MOD($B205,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L293:L296">
-    <cfRule type="expression" dxfId="0" priority="19">
+    <cfRule type="expression" dxfId="0" priority="21">
       <formula>MOD($B293,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L347:L350">
-    <cfRule type="expression" dxfId="0" priority="17">
+    <cfRule type="expression" dxfId="0" priority="19">
       <formula>MOD($B346,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L384:L387">
-    <cfRule type="expression" dxfId="0" priority="15">
+    <cfRule type="expression" dxfId="0" priority="17">
       <formula>MOD($B384,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L422:L425">
-    <cfRule type="expression" dxfId="0" priority="13">
+    <cfRule type="expression" dxfId="0" priority="15">
       <formula>MOD($B422,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L440:L446">
-    <cfRule type="expression" dxfId="0" priority="11">
+    <cfRule type="expression" dxfId="0" priority="13">
       <formula>MOD($B440,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L454:L457">
-    <cfRule type="expression" dxfId="0" priority="10">
+    <cfRule type="expression" dxfId="0" priority="12">
       <formula>MOD($B454,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L517:L520">
-    <cfRule type="expression" dxfId="0" priority="9">
+    <cfRule type="expression" dxfId="0" priority="11">
       <formula>MOD($B517,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L609:L611">
-    <cfRule type="expression" dxfId="0" priority="6">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>MOD($B602,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A470:A520 A612:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="446"/>
+  <conditionalFormatting sqref="L645:L647">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD($B638,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A470:A520 A648:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="448"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L4">
-    <cfRule type="expression" dxfId="0" priority="445">
+    <cfRule type="expression" dxfId="0" priority="447">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41:B42 B44:B47">
-    <cfRule type="expression" dxfId="0" priority="179">
+    <cfRule type="expression" dxfId="0" priority="181">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45 C46:C47 F46:F47 B61:L76 D77:E84 B179:L204 B205:G208 I205:K208 I209:I256 B258 B259:D268 F259:L268 B269:L270 B271:B279 D271:D279 F271:L279 B280:B281 D280:L281 B282:B290 D282:D290 F282:L290 B291:B292 D291:L292 B293:B296 D293:J296 B297:L307 B308:G309 I308:L309 B310:L319 B320:G321 I320:L321 B322:L343 B344:K344 B345:L345 B346:J350 B351:L383 B384:J387 B388:L421 B422:J425 B426:L439 B440:K446 B447:L453 B454:K457 B458:L516 B517:K520 B521:L548 B549:D549 F549:L549 B550:L591 B592 D592 I592:L592 B593:B594 D593:D594 I593:L594 B595 D595 I595:L595 B596:B601 D596:D601 I596:L601 B602 D602 F602:J602 B603:B604 D603:D604 F603:J604 B605 F605 H605:L605 B606:B607 F606:F607 I606:L607 B608 F608 I608:L608 B609:B610 D609:G610 I609:J610 B611 D611:J611 B612:L1048576">
-    <cfRule type="expression" dxfId="0" priority="444">
+  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45 C46:C47 F46:F47 B61:L76 D77:E84 B179:L204 B205:G208 I205:K208 I209:I256 B258 B259:D268 F259:L268 B269:L270 B271:B279 D271:D279 F271:L279 B280:B281 D280:L281 B282:B290 D282:D290 F282:L290 B291:B292 D291:L292 B293:B296 D293:J296 B297:L307 B308:G309 I308:L309 B310:L319 B320:G321 I320:L321 B322:L343 B344:K344 B345:L345 B346:J350 B351:L383 B384:J387 B388:L421 B422:J425 B426:L439 B440:K446 B447:L453 B454:K457 B458:L516 B517:K520 B521:L548 B549:D549 F549:L549 B550:L591 B592 D592 I592:L592 B593:B594 D593:D594 I593:L594 B595 D595 I595:L595 B596:B601 D596:D601 I596:L601 B602 D602 F602:J602 B603:B604 D603:D604 F603:J604 B605 F605 H605:L605 B606:B607 F606:F607 I606:L607 B608 F608 I608:L608 B609:B610 D609:G610 I609:J610 B611 D611:J611 B612:L643 B644:K647 B648:L1048576">
+    <cfRule type="expression" dxfId="0" priority="446">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43:G43 J43:L43">
-    <cfRule type="expression" dxfId="0" priority="144">
+    <cfRule type="expression" dxfId="0" priority="146">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44:G44 J44:L47 G45:G47 C45:C47">
-    <cfRule type="expression" dxfId="0" priority="178">
+    <cfRule type="expression" dxfId="0" priority="180">
       <formula>MOD($B44,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45:E47">
-    <cfRule type="expression" dxfId="0" priority="175">
+    <cfRule type="expression" dxfId="0" priority="177">
       <formula>MOD($B45,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F60 C48:C60">
+    <cfRule type="expression" dxfId="0" priority="134">
+      <formula>MOD($B48,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
     <cfRule type="expression" dxfId="0" priority="132">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
+  <conditionalFormatting sqref="D48:E60">
     <cfRule type="expression" dxfId="0" priority="130">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D48:E60">
-    <cfRule type="expression" dxfId="0" priority="128">
-      <formula>MOD($B48,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B77:B84 F77:L84">
-    <cfRule type="expression" dxfId="0" priority="174">
+    <cfRule type="expression" dxfId="0" priority="176">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85:C85 F85:L85">
-    <cfRule type="expression" dxfId="0" priority="170">
+    <cfRule type="expression" dxfId="0" priority="172">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B86:C86 F86:L86">
-    <cfRule type="expression" dxfId="0" priority="135">
+    <cfRule type="expression" dxfId="0" priority="137">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87:C92 F87:L92 I93:I104">
-    <cfRule type="expression" dxfId="0" priority="125">
+    <cfRule type="expression" dxfId="0" priority="127">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87:E92 D93:D104">
-    <cfRule type="expression" dxfId="0" priority="126">
+    <cfRule type="expression" dxfId="0" priority="128">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:C98 F93:H98 J93:L98">
-    <cfRule type="expression" dxfId="0" priority="122">
+    <cfRule type="expression" dxfId="0" priority="124">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99:C104 F99:H104 J99:L104">
-    <cfRule type="expression" dxfId="0" priority="119">
+    <cfRule type="expression" dxfId="0" priority="121">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:C105 F105:H105 J105:L105">
-    <cfRule type="expression" dxfId="0" priority="115">
+    <cfRule type="expression" dxfId="0" priority="117">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106:C106 F106:H106 J106:L106 H107:H111 C107:C111">
-    <cfRule type="expression" dxfId="0" priority="111">
+    <cfRule type="expression" dxfId="0" priority="113">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107 F107:G107 J107:L107">
-    <cfRule type="expression" dxfId="0" priority="107">
+    <cfRule type="expression" dxfId="0" priority="109">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B108 F108:G108 J108:L108">
-    <cfRule type="expression" dxfId="0" priority="103">
+    <cfRule type="expression" dxfId="0" priority="105">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B109 F109:G109 J109:L109">
-    <cfRule type="expression" dxfId="0" priority="99">
+    <cfRule type="expression" dxfId="0" priority="101">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B110 F110:G110 J110:L110">
-    <cfRule type="expression" dxfId="0" priority="95">
+    <cfRule type="expression" dxfId="0" priority="97">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111 F111:G111 J111:L111">
-    <cfRule type="expression" dxfId="0" priority="91">
+    <cfRule type="expression" dxfId="0" priority="93">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112:C112 F112:H112 J112:L112 H113:H117 C113:C117">
-    <cfRule type="expression" dxfId="0" priority="87">
+    <cfRule type="expression" dxfId="0" priority="89">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113 F113:G113 J113:L113">
-    <cfRule type="expression" dxfId="0" priority="83">
+    <cfRule type="expression" dxfId="0" priority="85">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114 F114:G114 J114:L114">
-    <cfRule type="expression" dxfId="0" priority="79">
+    <cfRule type="expression" dxfId="0" priority="81">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115 F115:G115 J115:L115">
-    <cfRule type="expression" dxfId="0" priority="75">
+    <cfRule type="expression" dxfId="0" priority="77">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B116 F116:G116 J116:L116">
-    <cfRule type="expression" dxfId="0" priority="71">
+    <cfRule type="expression" dxfId="0" priority="73">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117 F117:G117 J117:L117">
-    <cfRule type="expression" dxfId="0" priority="67">
+    <cfRule type="expression" dxfId="0" priority="69">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118:C118 F118:H118 J118:L118 H119:H123 C119:C123">
-    <cfRule type="expression" dxfId="0" priority="63">
+    <cfRule type="expression" dxfId="0" priority="65">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119 F119:G119 J119:L119">
-    <cfRule type="expression" dxfId="0" priority="59">
+    <cfRule type="expression" dxfId="0" priority="61">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120 F120:G120 J120:L120">
-    <cfRule type="expression" dxfId="0" priority="55">
+    <cfRule type="expression" dxfId="0" priority="57">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121 F121:G121 J121:L121">
-    <cfRule type="expression" dxfId="0" priority="51">
+    <cfRule type="expression" dxfId="0" priority="53">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122 F122:G122 J122:L122">
-    <cfRule type="expression" dxfId="0" priority="47">
+    <cfRule type="expression" dxfId="0" priority="49">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123 F123:G123 J123:L123">
-    <cfRule type="expression" dxfId="0" priority="43">
+    <cfRule type="expression" dxfId="0" priority="45">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B124:L133 B134">
-    <cfRule type="expression" dxfId="0" priority="173">
+    <cfRule type="expression" dxfId="0" priority="175">
       <formula>MOD($B124,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171:B172 B174:B177">
-    <cfRule type="expression" dxfId="0" priority="40">
+    <cfRule type="expression" dxfId="0" priority="42">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171:G172 J171:J172 L171:L172 F175:F177 C176:C177">
-    <cfRule type="expression" dxfId="0" priority="41">
+    <cfRule type="expression" dxfId="0" priority="43">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173:G173 J173:L173">
-    <cfRule type="expression" dxfId="0" priority="35">
+    <cfRule type="expression" dxfId="0" priority="37">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174:G174 J174:L177 G175:G177 C175:C177">
-    <cfRule type="expression" dxfId="0" priority="39">
+    <cfRule type="expression" dxfId="0" priority="41">
       <formula>MOD($B174,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D175:E177">
-    <cfRule type="expression" dxfId="0" priority="38">
+    <cfRule type="expression" dxfId="0" priority="40">
       <formula>MOD($B175,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F178 C178">
+    <cfRule type="expression" dxfId="0" priority="35">
+      <formula>MOD($B178,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J178:L178 G178 C178">
     <cfRule type="expression" dxfId="0" priority="33">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J178:L178 G178 C178">
-    <cfRule type="expression" dxfId="0" priority="31">
-      <formula>MOD($B178,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B209:D209 F209:H209 J209:L250 B210:H250">
-    <cfRule type="expression" dxfId="0" priority="28">
+    <cfRule type="expression" dxfId="0" priority="30">
       <formula>MOD($B209,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B251:H256 J251:L256">
-    <cfRule type="expression" dxfId="0" priority="27">
+    <cfRule type="expression" dxfId="0" priority="29">
       <formula>MOD($B251,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B257 B259 B261 B263 B265 B267 B269 B271 B273 B275 B277 B279 B281 B283 B285 B287 B289 B291 B293 B295">
-    <cfRule type="expression" dxfId="0" priority="25">
+    <cfRule type="expression" dxfId="0" priority="27">
       <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C257:D257 F257:L257">
-    <cfRule type="expression" dxfId="0" priority="448">
+    <cfRule type="expression" dxfId="0" priority="450">
       <formula>MOD($B258,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C258:D258 I292 I290 I288 I286 I284 I282 I280 I278 I276 I274 I272 I270 I268 I266 I264 I262 I260 D268 D266 D264 D262 D260 F258:L258">
-    <cfRule type="expression" dxfId="0" priority="447">
+    <cfRule type="expression" dxfId="0" priority="449">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C592 F592:G592">
-    <cfRule type="expression" dxfId="0" priority="458">
+    <cfRule type="expression" dxfId="0" priority="460">
       <formula>MOD($B605,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C593 F593:G593">
-    <cfRule type="expression" dxfId="0" priority="461">
+    <cfRule type="expression" dxfId="0" priority="463">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C594:C595 F594:G595">
-    <cfRule type="expression" dxfId="0" priority="462">
+    <cfRule type="expression" dxfId="0" priority="464">
       <formula>MOD($B606,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C596 F596:G596 C597 F597:G597 C598:C599 F598:G599 C600:C601 F600:G601">
-    <cfRule type="expression" dxfId="0" priority="459">
+    <cfRule type="expression" dxfId="0" priority="461">
       <formula>MOD($B610,2)=1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$611</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$647</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="102">
   <si>
     <t>id</t>
   </si>
@@ -609,6 +609,12 @@
   </si>
   <si>
     <t>普通模式哈迪斯玩法</t>
+  </si>
+  <si>
+    <t>用于触发免费游戏</t>
+  </si>
+  <si>
+    <t>用于收集金币</t>
   </si>
 </sst>
 </file>
@@ -5987,7 +5993,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L647"/>
+  <dimension ref="A1:L649"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="11"/>
@@ -23516,8 +23522,62 @@
         <v>68</v>
       </c>
     </row>
+    <row r="648" customHeight="1" spans="1:12">
+      <c r="A648" s="3">
+        <f>(B648)*10000+C648+F648*100+D648*100000</f>
+        <v>1038400117</v>
+      </c>
+      <c r="B648" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C648" s="2">
+        <v>17</v>
+      </c>
+      <c r="D648" s="2">
+        <v>4</v>
+      </c>
+      <c r="E648" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F648" s="2">
+        <v>1</v>
+      </c>
+      <c r="G648" s="12">
+        <v>0</v>
+      </c>
+      <c r="H648" s="12">
+        <v>30380001</v>
+      </c>
+    </row>
+    <row r="649" customHeight="1" spans="1:12">
+      <c r="A649" s="3">
+        <f>(B649)*10000+C649+F649*100+D649*100000</f>
+        <v>1038400118</v>
+      </c>
+      <c r="B649" s="2">
+        <v>103800</v>
+      </c>
+      <c r="C649" s="2">
+        <v>18</v>
+      </c>
+      <c r="D649" s="2">
+        <v>4</v>
+      </c>
+      <c r="E649" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F649" s="2">
+        <v>1</v>
+      </c>
+      <c r="G649" s="12">
+        <v>0</v>
+      </c>
+      <c r="H649" s="12">
+        <v>30380002</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L611" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L647" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">
@@ -23853,7 +23913,7 @@
   <conditionalFormatting sqref="A209:A469">
     <cfRule type="duplicateValues" dxfId="1" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A521:A647">
+  <conditionalFormatting sqref="A521:A649">
     <cfRule type="duplicateValues" dxfId="1" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B60">
@@ -24027,7 +24087,7 @@
       <formula>MOD($B638,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A470:A520 A648:A1048576">
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A470:A520 A650:A1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="448"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L4">

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$647</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$680</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="106">
   <si>
     <t>id</t>
   </si>
@@ -615,6 +615,18 @@
   </si>
   <si>
     <t>用于收集金币</t>
+  </si>
+  <si>
+    <t>mini</t>
+  </si>
+  <si>
+    <t>minor</t>
+  </si>
+  <si>
+    <t>major</t>
+  </si>
+  <si>
+    <t>grand</t>
   </si>
 </sst>
 </file>
@@ -5993,7 +6005,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L649"/>
+  <dimension ref="A1:L687"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="11"/>
@@ -23374,7 +23386,7 @@
     </row>
     <row r="642" customHeight="1" spans="1:12">
       <c r="A642" s="3">
-        <f t="shared" ref="A642:A647" si="25">(B642)*10000+C642+F642*100+D642*100000</f>
+        <f t="shared" ref="A642:A649" si="25">(B642)*10000+C642+F642*100+D642*100000</f>
         <v>1038400111</v>
       </c>
       <c r="B642" s="2">
@@ -23524,7 +23536,7 @@
     </row>
     <row r="648" customHeight="1" spans="1:12">
       <c r="A648" s="3">
-        <f>(B648)*10000+C648+F648*100+D648*100000</f>
+        <f t="shared" si="25"/>
         <v>1038400117</v>
       </c>
       <c r="B648" s="2">
@@ -23551,7 +23563,7 @@
     </row>
     <row r="649" customHeight="1" spans="1:12">
       <c r="A649" s="3">
-        <f>(B649)*10000+C649+F649*100+D649*100000</f>
+        <f t="shared" si="25"/>
         <v>1038400118</v>
       </c>
       <c r="B649" s="2">
@@ -23576,8 +23588,848 @@
         <v>30380002</v>
       </c>
     </row>
+    <row r="650" customHeight="1" spans="1:12">
+      <c r="A650" s="3">
+        <f t="shared" ref="A650:A680" si="26">(B650)*10000+C650+F650*100+D650*100000</f>
+        <v>1027300301</v>
+      </c>
+      <c r="B650" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C650" s="2">
+        <v>1</v>
+      </c>
+      <c r="D650" s="2">
+        <v>3</v>
+      </c>
+      <c r="F650" s="2">
+        <v>3</v>
+      </c>
+      <c r="G650" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="651" customHeight="1" spans="1:12">
+      <c r="A651" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300302</v>
+      </c>
+      <c r="B651" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C651" s="2">
+        <v>2</v>
+      </c>
+      <c r="D651" s="2">
+        <v>3</v>
+      </c>
+      <c r="F651" s="2">
+        <v>3</v>
+      </c>
+      <c r="G651" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="652" customHeight="1" spans="1:12">
+      <c r="A652" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300303</v>
+      </c>
+      <c r="B652" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C652" s="2">
+        <v>3</v>
+      </c>
+      <c r="D652" s="2">
+        <v>3</v>
+      </c>
+      <c r="F652" s="2">
+        <v>3</v>
+      </c>
+      <c r="G652" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="653" customHeight="1" spans="1:12">
+      <c r="A653" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300304</v>
+      </c>
+      <c r="B653" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C653" s="2">
+        <v>4</v>
+      </c>
+      <c r="D653" s="2">
+        <v>3</v>
+      </c>
+      <c r="F653" s="2">
+        <v>3</v>
+      </c>
+      <c r="G653" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="654" customHeight="1" spans="1:12">
+      <c r="A654" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300305</v>
+      </c>
+      <c r="B654" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C654" s="2">
+        <v>5</v>
+      </c>
+      <c r="D654" s="2">
+        <v>3</v>
+      </c>
+      <c r="F654" s="2">
+        <v>3</v>
+      </c>
+      <c r="G654" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="655" customHeight="1" spans="1:12">
+      <c r="A655" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300306</v>
+      </c>
+      <c r="B655" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C655" s="2">
+        <v>6</v>
+      </c>
+      <c r="D655" s="2">
+        <v>3</v>
+      </c>
+      <c r="F655" s="2">
+        <v>3</v>
+      </c>
+      <c r="G655" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="656" customHeight="1" spans="1:12">
+      <c r="A656" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300307</v>
+      </c>
+      <c r="B656" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C656" s="2">
+        <v>7</v>
+      </c>
+      <c r="D656" s="2">
+        <v>3</v>
+      </c>
+      <c r="F656" s="2">
+        <v>3</v>
+      </c>
+      <c r="G656" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="657" customHeight="1" spans="1:7">
+      <c r="A657" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300308</v>
+      </c>
+      <c r="B657" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C657" s="2">
+        <v>8</v>
+      </c>
+      <c r="D657" s="2">
+        <v>3</v>
+      </c>
+      <c r="F657" s="2">
+        <v>3</v>
+      </c>
+      <c r="G657" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="658" customHeight="1" spans="1:7">
+      <c r="A658" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300401</v>
+      </c>
+      <c r="B658" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C658" s="2">
+        <v>1</v>
+      </c>
+      <c r="D658" s="2">
+        <v>3</v>
+      </c>
+      <c r="F658" s="2">
+        <v>4</v>
+      </c>
+      <c r="G658" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="659" customHeight="1" spans="1:7">
+      <c r="A659" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300402</v>
+      </c>
+      <c r="B659" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C659" s="2">
+        <v>2</v>
+      </c>
+      <c r="D659" s="2">
+        <v>3</v>
+      </c>
+      <c r="F659" s="2">
+        <v>4</v>
+      </c>
+      <c r="G659" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="660" customHeight="1" spans="1:7">
+      <c r="A660" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300403</v>
+      </c>
+      <c r="B660" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C660" s="2">
+        <v>3</v>
+      </c>
+      <c r="D660" s="2">
+        <v>3</v>
+      </c>
+      <c r="F660" s="2">
+        <v>4</v>
+      </c>
+      <c r="G660" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="661" customHeight="1" spans="1:7">
+      <c r="A661" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300404</v>
+      </c>
+      <c r="B661" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C661" s="2">
+        <v>4</v>
+      </c>
+      <c r="D661" s="2">
+        <v>3</v>
+      </c>
+      <c r="F661" s="2">
+        <v>4</v>
+      </c>
+      <c r="G661" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="662" customHeight="1" spans="1:7">
+      <c r="A662" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300405</v>
+      </c>
+      <c r="B662" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C662" s="2">
+        <v>5</v>
+      </c>
+      <c r="D662" s="2">
+        <v>3</v>
+      </c>
+      <c r="F662" s="2">
+        <v>4</v>
+      </c>
+      <c r="G662" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="663" customHeight="1" spans="1:7">
+      <c r="A663" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300406</v>
+      </c>
+      <c r="B663" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C663" s="2">
+        <v>6</v>
+      </c>
+      <c r="D663" s="2">
+        <v>3</v>
+      </c>
+      <c r="F663" s="2">
+        <v>4</v>
+      </c>
+      <c r="G663" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="664" customHeight="1" spans="1:7">
+      <c r="A664" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300407</v>
+      </c>
+      <c r="B664" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C664" s="2">
+        <v>7</v>
+      </c>
+      <c r="D664" s="2">
+        <v>3</v>
+      </c>
+      <c r="F664" s="2">
+        <v>4</v>
+      </c>
+      <c r="G664" s="12">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="665" customHeight="1" spans="1:7">
+      <c r="A665" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300408</v>
+      </c>
+      <c r="B665" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C665" s="2">
+        <v>8</v>
+      </c>
+      <c r="D665" s="2">
+        <v>3</v>
+      </c>
+      <c r="F665" s="2">
+        <v>4</v>
+      </c>
+      <c r="G665" s="12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="666" customHeight="1" spans="1:7">
+      <c r="A666" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300501</v>
+      </c>
+      <c r="B666" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C666" s="2">
+        <v>1</v>
+      </c>
+      <c r="D666" s="2">
+        <v>3</v>
+      </c>
+      <c r="F666" s="2">
+        <v>5</v>
+      </c>
+      <c r="G666" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="667" customHeight="1" spans="1:7">
+      <c r="A667" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300502</v>
+      </c>
+      <c r="B667" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C667" s="2">
+        <v>2</v>
+      </c>
+      <c r="D667" s="2">
+        <v>3</v>
+      </c>
+      <c r="F667" s="2">
+        <v>5</v>
+      </c>
+      <c r="G667" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="668" customHeight="1" spans="1:7">
+      <c r="A668" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300503</v>
+      </c>
+      <c r="B668" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C668" s="2">
+        <v>3</v>
+      </c>
+      <c r="D668" s="2">
+        <v>3</v>
+      </c>
+      <c r="F668" s="2">
+        <v>5</v>
+      </c>
+      <c r="G668" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="669" customHeight="1" spans="1:7">
+      <c r="A669" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300504</v>
+      </c>
+      <c r="B669" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C669" s="2">
+        <v>4</v>
+      </c>
+      <c r="D669" s="2">
+        <v>3</v>
+      </c>
+      <c r="F669" s="2">
+        <v>5</v>
+      </c>
+      <c r="G669" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="670" customHeight="1" spans="1:7">
+      <c r="A670" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300505</v>
+      </c>
+      <c r="B670" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C670" s="2">
+        <v>5</v>
+      </c>
+      <c r="D670" s="2">
+        <v>3</v>
+      </c>
+      <c r="F670" s="2">
+        <v>5</v>
+      </c>
+      <c r="G670" s="12">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="671" customHeight="1" spans="1:7">
+      <c r="A671" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300506</v>
+      </c>
+      <c r="B671" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C671" s="2">
+        <v>6</v>
+      </c>
+      <c r="D671" s="2">
+        <v>3</v>
+      </c>
+      <c r="F671" s="2">
+        <v>5</v>
+      </c>
+      <c r="G671" s="12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="672" customHeight="1" spans="1:7">
+      <c r="A672" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300507</v>
+      </c>
+      <c r="B672" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C672" s="2">
+        <v>7</v>
+      </c>
+      <c r="D672" s="2">
+        <v>3</v>
+      </c>
+      <c r="F672" s="2">
+        <v>5</v>
+      </c>
+      <c r="G672" s="12">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="673" customHeight="1" spans="1:12">
+      <c r="A673" s="3">
+        <f t="shared" si="26"/>
+        <v>1027300508</v>
+      </c>
+      <c r="B673" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C673" s="2">
+        <v>8</v>
+      </c>
+      <c r="D673" s="2">
+        <v>3</v>
+      </c>
+      <c r="F673" s="2">
+        <v>5</v>
+      </c>
+      <c r="G673" s="12">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="674" customHeight="1" spans="1:12">
+      <c r="A674" s="3">
+        <f t="shared" si="26"/>
+        <v>1027400310</v>
+      </c>
+      <c r="B674" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C674" s="2">
+        <v>10</v>
+      </c>
+      <c r="D674" s="2">
+        <v>4</v>
+      </c>
+      <c r="E674" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F674" s="2">
+        <v>3</v>
+      </c>
+      <c r="G674" s="12">
+        <v>0</v>
+      </c>
+      <c r="H674" s="12">
+        <v>30270001</v>
+      </c>
+    </row>
+    <row r="675" customHeight="1" spans="1:12">
+      <c r="A675" s="3">
+        <f t="shared" si="26"/>
+        <v>1027400410</v>
+      </c>
+      <c r="B675" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C675" s="2">
+        <v>10</v>
+      </c>
+      <c r="D675" s="2">
+        <v>4</v>
+      </c>
+      <c r="E675" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F675" s="2">
+        <v>4</v>
+      </c>
+      <c r="G675" s="12">
+        <v>0</v>
+      </c>
+      <c r="H675" s="12">
+        <v>30270002</v>
+      </c>
+    </row>
+    <row r="676" customHeight="1" spans="1:12">
+      <c r="A676" s="3">
+        <f t="shared" si="26"/>
+        <v>1027400510</v>
+      </c>
+      <c r="B676" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C676" s="2">
+        <v>10</v>
+      </c>
+      <c r="D676" s="2">
+        <v>4</v>
+      </c>
+      <c r="E676" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F676" s="2">
+        <v>5</v>
+      </c>
+      <c r="G676" s="12">
+        <v>0</v>
+      </c>
+      <c r="H676" s="12">
+        <v>30270003</v>
+      </c>
+    </row>
+    <row r="677" customHeight="1" spans="1:12">
+      <c r="A677" s="3">
+        <f t="shared" si="26"/>
+        <v>1027400111</v>
+      </c>
+      <c r="B677" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C677" s="2">
+        <v>11</v>
+      </c>
+      <c r="D677" s="2">
+        <v>4</v>
+      </c>
+      <c r="F677" s="2">
+        <v>1</v>
+      </c>
+      <c r="G677" s="12">
+        <v>0</v>
+      </c>
+      <c r="K677" s="2">
+        <v>102700101</v>
+      </c>
+      <c r="L677" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="678" customHeight="1" spans="1:12">
+      <c r="A678" s="3">
+        <f t="shared" si="26"/>
+        <v>1027400112</v>
+      </c>
+      <c r="B678" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C678" s="2">
+        <v>12</v>
+      </c>
+      <c r="D678" s="2">
+        <v>4</v>
+      </c>
+      <c r="F678" s="2">
+        <v>1</v>
+      </c>
+      <c r="G678" s="12">
+        <v>0</v>
+      </c>
+      <c r="K678" s="2">
+        <v>102700102</v>
+      </c>
+      <c r="L678" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="679" customHeight="1" spans="1:12">
+      <c r="A679" s="3">
+        <f t="shared" si="26"/>
+        <v>1027400113</v>
+      </c>
+      <c r="B679" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C679" s="2">
+        <v>13</v>
+      </c>
+      <c r="D679" s="2">
+        <v>4</v>
+      </c>
+      <c r="F679" s="2">
+        <v>1</v>
+      </c>
+      <c r="G679" s="12">
+        <v>0</v>
+      </c>
+      <c r="K679" s="2">
+        <v>102700103</v>
+      </c>
+      <c r="L679" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="680" customHeight="1" spans="1:12">
+      <c r="A680" s="3">
+        <f t="shared" si="26"/>
+        <v>1027400114</v>
+      </c>
+      <c r="B680" s="2">
+        <v>102700</v>
+      </c>
+      <c r="C680" s="2">
+        <v>14</v>
+      </c>
+      <c r="D680" s="2">
+        <v>4</v>
+      </c>
+      <c r="F680" s="2">
+        <v>1</v>
+      </c>
+      <c r="G680" s="12">
+        <v>0</v>
+      </c>
+      <c r="K680" s="2">
+        <v>102700104</v>
+      </c>
+      <c r="L680" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="681" customHeight="1" spans="1:12">
+      <c r="A681" s="3">
+        <f t="shared" ref="A681:A686" si="27">(B681)*10000+C681+F681*100+D681*100000</f>
+        <v>1037100301</v>
+      </c>
+      <c r="B681" s="2">
+        <v>103700</v>
+      </c>
+      <c r="C681" s="2">
+        <v>1</v>
+      </c>
+      <c r="D681" s="2">
+        <v>1</v>
+      </c>
+      <c r="F681" s="2">
+        <v>3</v>
+      </c>
+      <c r="G681" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="682" customHeight="1" spans="1:12">
+      <c r="A682" s="3">
+        <f t="shared" si="27"/>
+        <v>1037100302</v>
+      </c>
+      <c r="B682" s="2">
+        <v>103700</v>
+      </c>
+      <c r="C682" s="2">
+        <v>2</v>
+      </c>
+      <c r="D682" s="2">
+        <v>1</v>
+      </c>
+      <c r="F682" s="2">
+        <v>3</v>
+      </c>
+      <c r="G682" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="683" customHeight="1" spans="1:12">
+      <c r="A683" s="3">
+        <f t="shared" si="27"/>
+        <v>1037100303</v>
+      </c>
+      <c r="B683" s="2">
+        <v>103700</v>
+      </c>
+      <c r="C683" s="2">
+        <v>3</v>
+      </c>
+      <c r="D683" s="2">
+        <v>1</v>
+      </c>
+      <c r="F683" s="2">
+        <v>3</v>
+      </c>
+      <c r="G683" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="684" customHeight="1" spans="1:12">
+      <c r="A684" s="3">
+        <f t="shared" si="27"/>
+        <v>1037100304</v>
+      </c>
+      <c r="B684" s="2">
+        <v>103700</v>
+      </c>
+      <c r="C684" s="2">
+        <v>4</v>
+      </c>
+      <c r="D684" s="2">
+        <v>1</v>
+      </c>
+      <c r="F684" s="2">
+        <v>3</v>
+      </c>
+      <c r="G684" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="685" customHeight="1" spans="1:12">
+      <c r="A685" s="3">
+        <f t="shared" si="27"/>
+        <v>1037100305</v>
+      </c>
+      <c r="B685" s="2">
+        <v>103700</v>
+      </c>
+      <c r="C685" s="2">
+        <v>5</v>
+      </c>
+      <c r="D685" s="2">
+        <v>1</v>
+      </c>
+      <c r="F685" s="2">
+        <v>3</v>
+      </c>
+      <c r="G685" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="686" customHeight="1" spans="1:12">
+      <c r="A686" s="3">
+        <f t="shared" si="27"/>
+        <v>1037100306</v>
+      </c>
+      <c r="B686" s="2">
+        <v>103700</v>
+      </c>
+      <c r="C686" s="2">
+        <v>6</v>
+      </c>
+      <c r="D686" s="2">
+        <v>1</v>
+      </c>
+      <c r="F686" s="2">
+        <v>3</v>
+      </c>
+      <c r="G686" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="687" customHeight="1" spans="1:12">
+      <c r="A687" s="3">
+        <f>(B687)*10000+C687+F687*100+D687*100000</f>
+        <v>1037100307</v>
+      </c>
+      <c r="B687" s="2">
+        <v>103700</v>
+      </c>
+      <c r="C687" s="2">
+        <v>7</v>
+      </c>
+      <c r="D687" s="2">
+        <v>1</v>
+      </c>
+      <c r="F687" s="2">
+        <v>3</v>
+      </c>
+      <c r="G687" s="12">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L647" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L680" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">
@@ -23913,7 +24765,7 @@
   <conditionalFormatting sqref="A209:A469">
     <cfRule type="duplicateValues" dxfId="1" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A521:A649">
+  <conditionalFormatting sqref="A521:A687">
     <cfRule type="duplicateValues" dxfId="1" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B60">
@@ -24087,7 +24939,7 @@
       <formula>MOD($B638,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A470:A520 A650:A1048576">
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A470:A520 A688:A1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="448"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L4">

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$469</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$387</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="71">
   <si>
     <t>id</t>
   </si>
@@ -522,9 +522,6 @@
   </si>
   <si>
     <t>+1免费符号</t>
-  </si>
-  <si>
-    <t>Jackpot</t>
   </si>
 </sst>
 </file>
@@ -779,12 +776,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5824,7 +5821,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L469"/>
+  <dimension ref="A1:L425"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="10"/>
@@ -16155,8 +16152,11 @@
       <c r="I346" s="11">
         <v>0</v>
       </c>
-      <c r="L346" s="54" t="s">
-        <v>70</v>
+      <c r="K346" s="2">
+        <v>101800101</v>
+      </c>
+      <c r="L346" s="13" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="347" customHeight="1" spans="1:12">
@@ -16183,10 +16183,10 @@
         <v>0</v>
       </c>
       <c r="K347" s="2">
-        <v>101800101</v>
+        <v>101800102</v>
       </c>
       <c r="L347" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="348" customHeight="1" spans="1:12">
@@ -16213,10 +16213,10 @@
         <v>0</v>
       </c>
       <c r="K348" s="2">
-        <v>101800102</v>
+        <v>101800103</v>
       </c>
       <c r="L348" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="349" customHeight="1" spans="1:12">
@@ -16243,10 +16243,10 @@
         <v>0</v>
       </c>
       <c r="K349" s="2">
-        <v>101800103</v>
+        <v>101800104</v>
       </c>
       <c r="L349" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="350" customHeight="1" spans="1:12">
@@ -16272,11 +16272,8 @@
       <c r="I350" s="11">
         <v>0</v>
       </c>
-      <c r="K350" s="2">
-        <v>101800104</v>
-      </c>
-      <c r="L350" s="13" t="s">
-        <v>68</v>
+      <c r="L350" s="54" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="351" customHeight="1" spans="1:12">
@@ -17460,16 +17457,13 @@
       <c r="G398" s="11">
         <v>0</v>
       </c>
-      <c r="H398" s="11">
-        <v>30230001</v>
-      </c>
       <c r="I398" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="399" customHeight="1" spans="1:12">
       <c r="A399" s="3">
-        <f t="shared" ref="A399:A426" si="16">(B399)*10000+C399+F399*100+D399*100000</f>
+        <f t="shared" ref="A399:A420" si="16">(B399)*10000+C399+F399*100+D399*100000</f>
         <v>1023300401</v>
       </c>
       <c r="B399" s="2">
@@ -17727,9 +17721,6 @@
       <c r="G409" s="11">
         <v>0</v>
       </c>
-      <c r="H409" s="11">
-        <v>30230002</v>
-      </c>
       <c r="I409" s="11">
         <v>0</v>
       </c>
@@ -17994,16 +17985,13 @@
       <c r="G420" s="11">
         <v>0</v>
       </c>
-      <c r="H420" s="11">
-        <v>30230003</v>
-      </c>
       <c r="I420" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="421" customHeight="1" spans="1:12">
       <c r="A421" s="3">
-        <f t="shared" si="16"/>
+        <f>(B421)*10000+C421+F421*100+D421*100000</f>
         <v>1023400112</v>
       </c>
       <c r="B421" s="2">
@@ -18027,7 +18015,7 @@
     </row>
     <row r="422" customHeight="1" spans="1:12">
       <c r="A422" s="3">
-        <f t="shared" si="16"/>
+        <f>(B422)*10000+C422+F422*100+D422*100000</f>
         <v>1023400113</v>
       </c>
       <c r="B422" s="2">
@@ -18057,7 +18045,7 @@
     </row>
     <row r="423" customHeight="1" spans="1:12">
       <c r="A423" s="3">
-        <f t="shared" si="16"/>
+        <f>(B423)*10000+C423+F423*100+D423*100000</f>
         <v>1023400114</v>
       </c>
       <c r="B423" s="2">
@@ -18087,7 +18075,7 @@
     </row>
     <row r="424" customHeight="1" spans="1:12">
       <c r="A424" s="3">
-        <f t="shared" si="16"/>
+        <f>(B424)*10000+C424+F424*100+D424*100000</f>
         <v>1023400115</v>
       </c>
       <c r="B424" s="2">
@@ -18117,7 +18105,7 @@
     </row>
     <row r="425" customHeight="1" spans="1:12">
       <c r="A425" s="3">
-        <f t="shared" si="16"/>
+        <f>(B425)*10000+C425+F425*100+D425*100000</f>
         <v>1023400116</v>
       </c>
       <c r="B425" s="2">
@@ -18145,1805 +18133,659 @@
         <v>68</v>
       </c>
     </row>
-    <row r="426" customHeight="1" spans="1:12">
-      <c r="A426" s="3">
-        <f t="shared" si="16"/>
-        <v>1034100301</v>
-      </c>
-      <c r="B426" s="2">
-        <v>103400</v>
-      </c>
-      <c r="C426" s="2">
-        <v>1</v>
-      </c>
-      <c r="D426" s="2">
-        <v>1</v>
-      </c>
-      <c r="F426" s="2">
-        <v>3</v>
-      </c>
-      <c r="G426" s="11">
-        <v>3</v>
-      </c>
-      <c r="I426" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="427" customHeight="1" spans="1:12">
-      <c r="A427" s="3">
-        <f t="shared" ref="A427:A433" si="17">(B427)*10000+C427+F427*100+D427*100000</f>
-        <v>1034100302</v>
-      </c>
-      <c r="B427" s="2">
-        <v>103400</v>
-      </c>
-      <c r="C427" s="2">
-        <v>2</v>
-      </c>
-      <c r="D427" s="2">
-        <v>1</v>
-      </c>
-      <c r="F427" s="2">
-        <v>3</v>
-      </c>
-      <c r="G427" s="11">
-        <v>5</v>
-      </c>
-      <c r="I427" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="428" customHeight="1" spans="1:12">
-      <c r="A428" s="3">
-        <f t="shared" si="17"/>
-        <v>1034100303</v>
-      </c>
-      <c r="B428" s="2">
-        <v>103400</v>
-      </c>
-      <c r="C428" s="2">
-        <v>3</v>
-      </c>
-      <c r="D428" s="2">
-        <v>1</v>
-      </c>
-      <c r="F428" s="2">
-        <v>3</v>
-      </c>
-      <c r="G428" s="11">
-        <v>8</v>
-      </c>
-      <c r="I428" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="429" customHeight="1" spans="1:12">
-      <c r="A429" s="3">
-        <f t="shared" si="17"/>
-        <v>1034100304</v>
-      </c>
-      <c r="B429" s="2">
-        <v>103400</v>
-      </c>
-      <c r="C429" s="2">
-        <v>4</v>
-      </c>
-      <c r="D429" s="2">
-        <v>1</v>
-      </c>
-      <c r="F429" s="2">
-        <v>3</v>
-      </c>
-      <c r="G429" s="11">
-        <v>10</v>
-      </c>
-      <c r="I429" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="430" customHeight="1" spans="1:12">
-      <c r="A430" s="3">
-        <f t="shared" si="17"/>
-        <v>1034100305</v>
-      </c>
-      <c r="B430" s="2">
-        <v>103400</v>
-      </c>
-      <c r="C430" s="2">
-        <v>5</v>
-      </c>
-      <c r="D430" s="2">
-        <v>1</v>
-      </c>
-      <c r="F430" s="2">
-        <v>3</v>
-      </c>
-      <c r="G430" s="11">
-        <v>25</v>
-      </c>
-      <c r="I430" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="431" customHeight="1" spans="1:12">
-      <c r="A431" s="3">
-        <f t="shared" si="17"/>
-        <v>1034100306</v>
-      </c>
-      <c r="B431" s="2">
-        <v>103400</v>
-      </c>
-      <c r="C431" s="2">
-        <v>6</v>
-      </c>
-      <c r="D431" s="2">
-        <v>1</v>
-      </c>
-      <c r="F431" s="2">
-        <v>3</v>
-      </c>
-      <c r="G431" s="11">
-        <v>100</v>
-      </c>
-      <c r="I431" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="432" customHeight="1" spans="1:12">
-      <c r="A432" s="3">
-        <f t="shared" si="17"/>
-        <v>1034100307</v>
-      </c>
-      <c r="B432" s="2">
-        <v>103400</v>
-      </c>
-      <c r="C432" s="2">
-        <v>7</v>
-      </c>
-      <c r="D432" s="2">
-        <v>1</v>
-      </c>
-      <c r="F432" s="2">
-        <v>3</v>
-      </c>
-      <c r="G432" s="11">
-        <v>250</v>
-      </c>
-      <c r="I432" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="433" customHeight="1" spans="1:12">
-      <c r="A433" s="3">
-        <f t="shared" ref="A433:A446" si="18">(B433)*10000+C433+F433*100+D433*100000</f>
-        <v>1035100301</v>
-      </c>
-      <c r="B433" s="2">
-        <v>103500</v>
-      </c>
-      <c r="C433" s="2">
-        <v>1</v>
-      </c>
-      <c r="D433" s="2">
-        <v>1</v>
-      </c>
-      <c r="F433" s="2">
-        <v>3</v>
-      </c>
-      <c r="G433" s="11">
-        <v>2</v>
-      </c>
-      <c r="I433" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="434" customHeight="1" spans="1:12">
-      <c r="A434" s="3">
-        <f t="shared" si="18"/>
-        <v>1035100302</v>
-      </c>
-      <c r="B434" s="2">
-        <v>103500</v>
-      </c>
-      <c r="C434" s="2">
-        <v>2</v>
-      </c>
-      <c r="D434" s="2">
-        <v>1</v>
-      </c>
-      <c r="F434" s="2">
-        <v>3</v>
-      </c>
-      <c r="G434" s="11">
-        <v>3</v>
-      </c>
-      <c r="I434" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="435" customHeight="1" spans="1:12">
-      <c r="A435" s="3">
-        <f t="shared" si="18"/>
-        <v>1035100303</v>
-      </c>
-      <c r="B435" s="2">
-        <v>103500</v>
-      </c>
-      <c r="C435" s="2">
-        <v>3</v>
-      </c>
-      <c r="D435" s="2">
-        <v>1</v>
-      </c>
-      <c r="F435" s="2">
-        <v>3</v>
-      </c>
-      <c r="G435" s="11">
-        <v>5</v>
-      </c>
-      <c r="I435" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="436" customHeight="1" spans="1:12">
-      <c r="A436" s="3">
-        <f t="shared" si="18"/>
-        <v>1035100304</v>
-      </c>
-      <c r="B436" s="2">
-        <v>103500</v>
-      </c>
-      <c r="C436" s="2">
-        <v>4</v>
-      </c>
-      <c r="D436" s="2">
-        <v>1</v>
-      </c>
-      <c r="F436" s="2">
-        <v>3</v>
-      </c>
-      <c r="G436" s="11">
-        <v>10</v>
-      </c>
-      <c r="I436" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="437" customHeight="1" spans="1:12">
-      <c r="A437" s="3">
-        <f t="shared" si="18"/>
-        <v>1035100305</v>
-      </c>
-      <c r="B437" s="2">
-        <v>103500</v>
-      </c>
-      <c r="C437" s="2">
-        <v>5</v>
-      </c>
-      <c r="D437" s="2">
-        <v>1</v>
-      </c>
-      <c r="F437" s="2">
-        <v>3</v>
-      </c>
-      <c r="G437" s="11">
-        <v>50</v>
-      </c>
-      <c r="I437" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="438" customHeight="1" spans="1:12">
-      <c r="A438" s="3">
-        <f t="shared" si="18"/>
-        <v>1035100306</v>
-      </c>
-      <c r="B438" s="2">
-        <v>103500</v>
-      </c>
-      <c r="C438" s="2">
-        <v>6</v>
-      </c>
-      <c r="D438" s="2">
-        <v>1</v>
-      </c>
-      <c r="F438" s="2">
-        <v>3</v>
-      </c>
-      <c r="G438" s="11">
-        <v>100</v>
-      </c>
-      <c r="I438" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="439" customHeight="1" spans="1:12">
-      <c r="A439" s="3">
-        <f t="shared" si="18"/>
-        <v>1035100307</v>
-      </c>
-      <c r="B439" s="2">
-        <v>103500</v>
-      </c>
-      <c r="C439" s="2">
-        <v>7</v>
-      </c>
-      <c r="D439" s="2">
-        <v>1</v>
-      </c>
-      <c r="F439" s="2">
-        <v>3</v>
-      </c>
-      <c r="G439" s="11">
-        <v>200</v>
-      </c>
-      <c r="I439" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="440" customHeight="1" spans="1:12">
-      <c r="A440" s="3">
-        <f t="shared" si="18"/>
-        <v>1035400109</v>
-      </c>
-      <c r="B440" s="2">
-        <v>103500</v>
-      </c>
-      <c r="C440" s="2">
-        <v>9</v>
-      </c>
-      <c r="D440" s="2">
-        <v>4</v>
-      </c>
-      <c r="F440" s="2">
-        <v>1</v>
-      </c>
-      <c r="G440" s="11">
-        <v>0</v>
-      </c>
-      <c r="I440" s="11">
-        <v>0</v>
-      </c>
-      <c r="K440" s="2">
-        <v>103500101</v>
-      </c>
-      <c r="L440" s="13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="441" customHeight="1" spans="1:12">
-      <c r="A441" s="3">
-        <f t="shared" si="18"/>
-        <v>1035400110</v>
-      </c>
-      <c r="B441" s="2">
-        <v>103500</v>
-      </c>
-      <c r="C441" s="2">
-        <v>10</v>
-      </c>
-      <c r="D441" s="2">
-        <v>4</v>
-      </c>
-      <c r="F441" s="2">
-        <v>1</v>
-      </c>
-      <c r="G441" s="11">
-        <v>0</v>
-      </c>
-      <c r="I441" s="11">
-        <v>0</v>
-      </c>
-      <c r="K441" s="2">
-        <v>103500102</v>
-      </c>
-      <c r="L441" s="13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="442" customHeight="1" spans="1:12">
-      <c r="A442" s="3">
-        <f t="shared" si="18"/>
-        <v>1035400111</v>
-      </c>
-      <c r="B442" s="2">
-        <v>103500</v>
-      </c>
-      <c r="C442" s="2">
-        <v>11</v>
-      </c>
-      <c r="D442" s="2">
-        <v>4</v>
-      </c>
-      <c r="F442" s="2">
-        <v>1</v>
-      </c>
-      <c r="G442" s="11">
-        <v>0</v>
-      </c>
-      <c r="I442" s="11">
-        <v>0</v>
-      </c>
-      <c r="K442" s="2">
-        <v>103500103</v>
-      </c>
-      <c r="L442" s="13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="443" customHeight="1" spans="1:12">
-      <c r="A443" s="3">
-        <f t="shared" si="18"/>
-        <v>1035400112</v>
-      </c>
-      <c r="B443" s="2">
-        <v>103500</v>
-      </c>
-      <c r="C443" s="2">
-        <v>12</v>
-      </c>
-      <c r="D443" s="2">
-        <v>4</v>
-      </c>
-      <c r="F443" s="2">
-        <v>1</v>
-      </c>
-      <c r="G443" s="11">
-        <v>0</v>
-      </c>
-      <c r="I443" s="11">
-        <v>0</v>
-      </c>
-      <c r="K443" s="2">
-        <v>103500104</v>
-      </c>
-      <c r="L443" s="13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="444" customHeight="1" spans="1:12">
-      <c r="A444" s="3">
-        <f t="shared" si="18"/>
-        <v>1035400508</v>
-      </c>
-      <c r="B444" s="2">
-        <v>103500</v>
-      </c>
-      <c r="C444" s="2">
-        <v>8</v>
-      </c>
-      <c r="D444" s="2">
-        <v>4</v>
-      </c>
-      <c r="F444" s="2">
-        <v>5</v>
-      </c>
-      <c r="G444" s="11">
-        <v>0</v>
-      </c>
-      <c r="H444" s="11">
-        <v>30350002</v>
-      </c>
-      <c r="I444" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="445" customHeight="1" spans="1:12">
-      <c r="A445" s="3">
-        <f t="shared" si="18"/>
-        <v>1035400608</v>
-      </c>
-      <c r="B445" s="2">
-        <v>103500</v>
-      </c>
-      <c r="C445" s="2">
-        <v>8</v>
-      </c>
-      <c r="D445" s="2">
-        <v>4</v>
-      </c>
-      <c r="F445" s="2">
-        <v>6</v>
-      </c>
-      <c r="G445" s="11">
-        <v>0</v>
-      </c>
-      <c r="H445" s="11">
-        <v>30350002</v>
-      </c>
-      <c r="I445" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="446" customHeight="1" spans="1:12">
-      <c r="A446" s="3">
-        <f t="shared" si="18"/>
-        <v>1035400114</v>
-      </c>
-      <c r="B446" s="2">
-        <v>103500</v>
-      </c>
-      <c r="C446" s="2">
-        <v>14</v>
-      </c>
-      <c r="D446" s="2">
-        <v>4</v>
-      </c>
-      <c r="F446" s="2">
-        <v>1</v>
-      </c>
-      <c r="G446" s="11">
-        <v>0</v>
-      </c>
-      <c r="H446" s="11">
-        <v>30350001</v>
-      </c>
-      <c r="I446" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="447" customHeight="1" spans="1:12">
-      <c r="A447" s="3">
-        <f t="shared" ref="A447:A460" si="19">(B447)*10000+C447+F447*100+D447*100000</f>
-        <v>1035110301</v>
-      </c>
-      <c r="B447" s="2">
-        <v>103501</v>
-      </c>
-      <c r="C447" s="2">
-        <v>1</v>
-      </c>
-      <c r="D447" s="2">
-        <v>1</v>
-      </c>
-      <c r="F447" s="2">
-        <v>3</v>
-      </c>
-      <c r="G447" s="11">
-        <v>2</v>
-      </c>
-      <c r="I447" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="448" customHeight="1" spans="1:12">
-      <c r="A448" s="3">
-        <f t="shared" si="19"/>
-        <v>1035110302</v>
-      </c>
-      <c r="B448" s="2">
-        <v>103501</v>
-      </c>
-      <c r="C448" s="2">
-        <v>2</v>
-      </c>
-      <c r="D448" s="2">
-        <v>1</v>
-      </c>
-      <c r="F448" s="2">
-        <v>3</v>
-      </c>
-      <c r="G448" s="11">
-        <v>3</v>
-      </c>
-      <c r="I448" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="449" customHeight="1" spans="1:12">
-      <c r="A449" s="3">
-        <f t="shared" si="19"/>
-        <v>1035110303</v>
-      </c>
-      <c r="B449" s="2">
-        <v>103501</v>
-      </c>
-      <c r="C449" s="2">
-        <v>3</v>
-      </c>
-      <c r="D449" s="2">
-        <v>1</v>
-      </c>
-      <c r="F449" s="2">
-        <v>3</v>
-      </c>
-      <c r="G449" s="11">
-        <v>5</v>
-      </c>
-      <c r="I449" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="450" customHeight="1" spans="1:12">
-      <c r="A450" s="3">
-        <f t="shared" si="19"/>
-        <v>1035110304</v>
-      </c>
-      <c r="B450" s="2">
-        <v>103501</v>
-      </c>
-      <c r="C450" s="2">
-        <v>4</v>
-      </c>
-      <c r="D450" s="2">
-        <v>1</v>
-      </c>
-      <c r="F450" s="2">
-        <v>3</v>
-      </c>
-      <c r="G450" s="11">
-        <v>10</v>
-      </c>
-      <c r="I450" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="451" customHeight="1" spans="1:12">
-      <c r="A451" s="3">
-        <f t="shared" si="19"/>
-        <v>1035110305</v>
-      </c>
-      <c r="B451" s="2">
-        <v>103501</v>
-      </c>
-      <c r="C451" s="2">
-        <v>5</v>
-      </c>
-      <c r="D451" s="2">
-        <v>1</v>
-      </c>
-      <c r="F451" s="2">
-        <v>3</v>
-      </c>
-      <c r="G451" s="11">
-        <v>50</v>
-      </c>
-      <c r="I451" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="452" customHeight="1" spans="1:12">
-      <c r="A452" s="3">
-        <f t="shared" si="19"/>
-        <v>1035110306</v>
-      </c>
-      <c r="B452" s="2">
-        <v>103501</v>
-      </c>
-      <c r="C452" s="2">
-        <v>6</v>
-      </c>
-      <c r="D452" s="2">
-        <v>1</v>
-      </c>
-      <c r="F452" s="2">
-        <v>3</v>
-      </c>
-      <c r="G452" s="11">
-        <v>100</v>
-      </c>
-      <c r="I452" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="453" customHeight="1" spans="1:12">
-      <c r="A453" s="3">
-        <f t="shared" si="19"/>
-        <v>1035110307</v>
-      </c>
-      <c r="B453" s="2">
-        <v>103501</v>
-      </c>
-      <c r="C453" s="2">
-        <v>7</v>
-      </c>
-      <c r="D453" s="2">
-        <v>1</v>
-      </c>
-      <c r="F453" s="2">
-        <v>3</v>
-      </c>
-      <c r="G453" s="11">
-        <v>200</v>
-      </c>
-      <c r="I453" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="454" customHeight="1" spans="1:12">
-      <c r="A454" s="3">
-        <f t="shared" si="19"/>
-        <v>1035410109</v>
-      </c>
-      <c r="B454" s="2">
-        <v>103501</v>
-      </c>
-      <c r="C454" s="2">
-        <v>9</v>
-      </c>
-      <c r="D454" s="2">
-        <v>4</v>
-      </c>
-      <c r="F454" s="2">
-        <v>1</v>
-      </c>
-      <c r="G454" s="11">
-        <v>0</v>
-      </c>
-      <c r="I454" s="11">
-        <v>0</v>
-      </c>
-      <c r="K454" s="2">
-        <v>103501101</v>
-      </c>
-      <c r="L454" s="13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="455" customHeight="1" spans="1:12">
-      <c r="A455" s="3">
-        <f t="shared" si="19"/>
-        <v>1035410110</v>
-      </c>
-      <c r="B455" s="2">
-        <v>103501</v>
-      </c>
-      <c r="C455" s="2">
-        <v>10</v>
-      </c>
-      <c r="D455" s="2">
-        <v>4</v>
-      </c>
-      <c r="F455" s="2">
-        <v>1</v>
-      </c>
-      <c r="G455" s="11">
-        <v>0</v>
-      </c>
-      <c r="I455" s="11">
-        <v>0</v>
-      </c>
-      <c r="K455" s="2">
-        <v>103501102</v>
-      </c>
-      <c r="L455" s="13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="456" customHeight="1" spans="1:12">
-      <c r="A456" s="3">
-        <f t="shared" si="19"/>
-        <v>1035410111</v>
-      </c>
-      <c r="B456" s="2">
-        <v>103501</v>
-      </c>
-      <c r="C456" s="2">
-        <v>11</v>
-      </c>
-      <c r="D456" s="2">
-        <v>4</v>
-      </c>
-      <c r="F456" s="2">
-        <v>1</v>
-      </c>
-      <c r="G456" s="11">
-        <v>0</v>
-      </c>
-      <c r="I456" s="11">
-        <v>0</v>
-      </c>
-      <c r="K456" s="2">
-        <v>103501103</v>
-      </c>
-      <c r="L456" s="13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="457" customHeight="1" spans="1:12">
-      <c r="A457" s="3">
-        <f t="shared" si="19"/>
-        <v>1035410112</v>
-      </c>
-      <c r="B457" s="2">
-        <v>103501</v>
-      </c>
-      <c r="C457" s="2">
-        <v>12</v>
-      </c>
-      <c r="D457" s="2">
-        <v>4</v>
-      </c>
-      <c r="F457" s="2">
-        <v>1</v>
-      </c>
-      <c r="G457" s="11">
-        <v>0</v>
-      </c>
-      <c r="I457" s="11">
-        <v>0</v>
-      </c>
-      <c r="K457" s="2">
-        <v>103501104</v>
-      </c>
-      <c r="L457" s="13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="458" customHeight="1" spans="1:12">
-      <c r="A458" s="3">
-        <f t="shared" si="19"/>
-        <v>1035410508</v>
-      </c>
-      <c r="B458" s="2">
-        <v>103501</v>
-      </c>
-      <c r="C458" s="2">
-        <v>8</v>
-      </c>
-      <c r="D458" s="2">
-        <v>4</v>
-      </c>
-      <c r="F458" s="2">
-        <v>5</v>
-      </c>
-      <c r="G458" s="11">
-        <v>0</v>
-      </c>
-      <c r="H458" s="11">
-        <v>30350102</v>
-      </c>
-      <c r="I458" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="459" customHeight="1" spans="1:12">
-      <c r="A459" s="3">
-        <f t="shared" si="19"/>
-        <v>1035410608</v>
-      </c>
-      <c r="B459" s="2">
-        <v>103501</v>
-      </c>
-      <c r="C459" s="2">
-        <v>8</v>
-      </c>
-      <c r="D459" s="2">
-        <v>4</v>
-      </c>
-      <c r="F459" s="2">
-        <v>6</v>
-      </c>
-      <c r="G459" s="11">
-        <v>0</v>
-      </c>
-      <c r="H459" s="11">
-        <v>30350102</v>
-      </c>
-      <c r="I459" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="460" customHeight="1" spans="1:12">
-      <c r="A460" s="3">
-        <f t="shared" si="19"/>
-        <v>1035410114</v>
-      </c>
-      <c r="B460" s="2">
-        <v>103501</v>
-      </c>
-      <c r="C460" s="2">
-        <v>14</v>
-      </c>
-      <c r="D460" s="2">
-        <v>4</v>
-      </c>
-      <c r="F460" s="2">
-        <v>1</v>
-      </c>
-      <c r="G460" s="11">
-        <v>0</v>
-      </c>
-      <c r="H460" s="11">
-        <v>30350101</v>
-      </c>
-      <c r="I460" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="461" customHeight="1" spans="1:12">
-      <c r="A461" s="3">
-        <f t="shared" ref="A461:A469" si="20">(B461)*10000+C461+F461*100+D461*100000</f>
-        <v>1036100301</v>
-      </c>
-      <c r="B461" s="2">
-        <v>103600</v>
-      </c>
-      <c r="C461" s="2">
-        <v>1</v>
-      </c>
-      <c r="D461" s="2">
-        <v>1</v>
-      </c>
-      <c r="F461" s="2">
-        <v>3</v>
-      </c>
-      <c r="G461" s="11">
-        <v>3</v>
-      </c>
-      <c r="I461" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="462" customHeight="1" spans="1:12">
-      <c r="A462" s="3">
-        <f t="shared" si="20"/>
-        <v>1036100302</v>
-      </c>
-      <c r="B462" s="2">
-        <v>103600</v>
-      </c>
-      <c r="C462" s="2">
-        <v>2</v>
-      </c>
-      <c r="D462" s="2">
-        <v>1</v>
-      </c>
-      <c r="F462" s="2">
-        <v>3</v>
-      </c>
-      <c r="G462" s="11">
-        <v>5</v>
-      </c>
-      <c r="I462" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="463" customHeight="1" spans="1:12">
-      <c r="A463" s="3">
-        <f t="shared" si="20"/>
-        <v>1036100303</v>
-      </c>
-      <c r="B463" s="2">
-        <v>103600</v>
-      </c>
-      <c r="C463" s="2">
-        <v>3</v>
-      </c>
-      <c r="D463" s="2">
-        <v>1</v>
-      </c>
-      <c r="F463" s="2">
-        <v>3</v>
-      </c>
-      <c r="G463" s="11">
-        <v>15</v>
-      </c>
-      <c r="I463" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="464" customHeight="1" spans="1:12">
-      <c r="A464" s="3">
-        <f t="shared" si="20"/>
-        <v>1036100304</v>
-      </c>
-      <c r="B464" s="2">
-        <v>103600</v>
-      </c>
-      <c r="C464" s="2">
-        <v>4</v>
-      </c>
-      <c r="D464" s="2">
-        <v>1</v>
-      </c>
-      <c r="F464" s="2">
-        <v>3</v>
-      </c>
-      <c r="G464" s="11">
-        <v>30</v>
-      </c>
-      <c r="I464" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="465" customHeight="1" spans="1:12">
-      <c r="A465" s="3">
-        <f t="shared" si="20"/>
-        <v>1036100305</v>
-      </c>
-      <c r="B465" s="2">
-        <v>103600</v>
-      </c>
-      <c r="C465" s="2">
-        <v>5</v>
-      </c>
-      <c r="D465" s="2">
-        <v>1</v>
-      </c>
-      <c r="F465" s="2">
-        <v>3</v>
-      </c>
-      <c r="G465" s="11">
-        <v>50</v>
-      </c>
-      <c r="I465" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="466" customHeight="1" spans="1:12">
-      <c r="A466" s="3">
-        <f t="shared" si="20"/>
-        <v>1036100306</v>
-      </c>
-      <c r="B466" s="2">
-        <v>103600</v>
-      </c>
-      <c r="C466" s="2">
-        <v>6</v>
-      </c>
-      <c r="D466" s="2">
-        <v>1</v>
-      </c>
-      <c r="F466" s="2">
-        <v>3</v>
-      </c>
-      <c r="G466" s="11">
-        <v>100</v>
-      </c>
-      <c r="I466" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="467" customHeight="1" spans="1:12">
-      <c r="A467" s="3">
-        <f t="shared" si="20"/>
-        <v>1036100307</v>
-      </c>
-      <c r="B467" s="2">
-        <v>103600</v>
-      </c>
-      <c r="C467" s="2">
-        <v>7</v>
-      </c>
-      <c r="D467" s="2">
-        <v>1</v>
-      </c>
-      <c r="F467" s="2">
-        <v>3</v>
-      </c>
-      <c r="G467" s="11">
-        <v>300</v>
-      </c>
-      <c r="I467" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="468" customHeight="1" spans="1:12">
-      <c r="A468" s="3">
-        <f t="shared" si="20"/>
-        <v>1036400308</v>
-      </c>
-      <c r="B468" s="2">
-        <v>103600</v>
-      </c>
-      <c r="C468" s="2">
-        <v>8</v>
-      </c>
-      <c r="D468" s="2">
-        <v>4</v>
-      </c>
-      <c r="F468" s="2">
-        <v>3</v>
-      </c>
-      <c r="G468" s="11">
-        <v>0</v>
-      </c>
-      <c r="I468" s="11">
-        <v>0</v>
-      </c>
-      <c r="K468" s="2">
-        <v>103600101</v>
-      </c>
-      <c r="L468" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="469" customHeight="1" spans="1:12">
-      <c r="A469" s="3">
-        <f t="shared" si="20"/>
-        <v>1036400109</v>
-      </c>
-      <c r="B469" s="2">
-        <v>103600</v>
-      </c>
-      <c r="C469" s="2">
-        <v>9</v>
-      </c>
-      <c r="D469" s="2">
-        <v>4</v>
-      </c>
-      <c r="F469" s="2">
-        <v>1</v>
-      </c>
-      <c r="G469" s="11">
-        <v>0</v>
-      </c>
-      <c r="H469" s="11">
-        <v>30360001</v>
-      </c>
-      <c r="I469" s="11">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L469" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L387" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="0" priority="136">
+    <cfRule type="expression" dxfId="0" priority="134">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D85:E85">
-    <cfRule type="expression" dxfId="0" priority="162">
+    <cfRule type="expression" dxfId="0" priority="160">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D86:E86">
-    <cfRule type="expression" dxfId="0" priority="127">
+    <cfRule type="expression" dxfId="0" priority="125">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105">
-    <cfRule type="duplicateValues" dxfId="1" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105:E105">
+    <cfRule type="expression" dxfId="0" priority="105">
+      <formula>MOD($B105,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I105">
     <cfRule type="expression" dxfId="0" priority="107">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I105">
-    <cfRule type="expression" dxfId="0" priority="109">
-      <formula>MOD($B105,2)=1</formula>
+  <conditionalFormatting sqref="A106">
+    <cfRule type="duplicateValues" dxfId="1" priority="102"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D106:E106">
+    <cfRule type="expression" dxfId="0" priority="101">
+      <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A106">
-    <cfRule type="duplicateValues" dxfId="1" priority="104"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D106:E106">
+  <conditionalFormatting sqref="I106">
     <cfRule type="expression" dxfId="0" priority="103">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I106">
-    <cfRule type="expression" dxfId="0" priority="105">
-      <formula>MOD($B106,2)=1</formula>
+  <conditionalFormatting sqref="A107">
+    <cfRule type="duplicateValues" dxfId="1" priority="98"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D107:E107">
+    <cfRule type="expression" dxfId="0" priority="97">
+      <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="1" priority="100"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D107:E107">
+  <conditionalFormatting sqref="I107">
     <cfRule type="expression" dxfId="0" priority="99">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I107">
-    <cfRule type="expression" dxfId="0" priority="101">
-      <formula>MOD($B107,2)=1</formula>
+  <conditionalFormatting sqref="A108">
+    <cfRule type="duplicateValues" dxfId="1" priority="94"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D108:E108">
+    <cfRule type="expression" dxfId="0" priority="93">
+      <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A108">
-    <cfRule type="duplicateValues" dxfId="1" priority="96"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D108:E108">
+  <conditionalFormatting sqref="I108">
     <cfRule type="expression" dxfId="0" priority="95">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I108">
-    <cfRule type="expression" dxfId="0" priority="97">
-      <formula>MOD($B108,2)=1</formula>
+  <conditionalFormatting sqref="A109">
+    <cfRule type="duplicateValues" dxfId="1" priority="90"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D109:E109">
+    <cfRule type="expression" dxfId="0" priority="89">
+      <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" dxfId="1" priority="92"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D109:E109">
+  <conditionalFormatting sqref="I109">
     <cfRule type="expression" dxfId="0" priority="91">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I109">
-    <cfRule type="expression" dxfId="0" priority="93">
-      <formula>MOD($B109,2)=1</formula>
+  <conditionalFormatting sqref="A110">
+    <cfRule type="duplicateValues" dxfId="1" priority="86"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D110:E110">
+    <cfRule type="expression" dxfId="0" priority="85">
+      <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A110">
-    <cfRule type="duplicateValues" dxfId="1" priority="88"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D110:E110">
+  <conditionalFormatting sqref="I110">
     <cfRule type="expression" dxfId="0" priority="87">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I110">
-    <cfRule type="expression" dxfId="0" priority="89">
-      <formula>MOD($B110,2)=1</formula>
+  <conditionalFormatting sqref="A111">
+    <cfRule type="duplicateValues" dxfId="1" priority="82"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D111:E111">
+    <cfRule type="expression" dxfId="0" priority="81">
+      <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A111">
-    <cfRule type="duplicateValues" dxfId="1" priority="84"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D111:E111">
+  <conditionalFormatting sqref="I111">
     <cfRule type="expression" dxfId="0" priority="83">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I111">
-    <cfRule type="expression" dxfId="0" priority="85">
-      <formula>MOD($B111,2)=1</formula>
+  <conditionalFormatting sqref="A112">
+    <cfRule type="duplicateValues" dxfId="1" priority="78"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D112:E112">
+    <cfRule type="expression" dxfId="0" priority="77">
+      <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A112">
-    <cfRule type="duplicateValues" dxfId="1" priority="80"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D112:E112">
+  <conditionalFormatting sqref="I112">
     <cfRule type="expression" dxfId="0" priority="79">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I112">
-    <cfRule type="expression" dxfId="0" priority="81">
-      <formula>MOD($B112,2)=1</formula>
+  <conditionalFormatting sqref="A113">
+    <cfRule type="duplicateValues" dxfId="1" priority="74"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D113:E113">
+    <cfRule type="expression" dxfId="0" priority="73">
+      <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A113">
-    <cfRule type="duplicateValues" dxfId="1" priority="76"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D113:E113">
+  <conditionalFormatting sqref="I113">
     <cfRule type="expression" dxfId="0" priority="75">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I113">
-    <cfRule type="expression" dxfId="0" priority="77">
-      <formula>MOD($B113,2)=1</formula>
+  <conditionalFormatting sqref="A114">
+    <cfRule type="duplicateValues" dxfId="1" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D114:E114">
+    <cfRule type="expression" dxfId="0" priority="69">
+      <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A114">
-    <cfRule type="duplicateValues" dxfId="1" priority="72"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D114:E114">
+  <conditionalFormatting sqref="I114">
     <cfRule type="expression" dxfId="0" priority="71">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I114">
-    <cfRule type="expression" dxfId="0" priority="73">
-      <formula>MOD($B114,2)=1</formula>
+  <conditionalFormatting sqref="A115">
+    <cfRule type="duplicateValues" dxfId="1" priority="66"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D115:E115">
+    <cfRule type="expression" dxfId="0" priority="65">
+      <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A115">
-    <cfRule type="duplicateValues" dxfId="1" priority="68"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D115:E115">
+  <conditionalFormatting sqref="I115">
     <cfRule type="expression" dxfId="0" priority="67">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I115">
-    <cfRule type="expression" dxfId="0" priority="69">
-      <formula>MOD($B115,2)=1</formula>
+  <conditionalFormatting sqref="A116">
+    <cfRule type="duplicateValues" dxfId="1" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D116:E116">
+    <cfRule type="expression" dxfId="0" priority="61">
+      <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A116">
-    <cfRule type="duplicateValues" dxfId="1" priority="64"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D116:E116">
+  <conditionalFormatting sqref="I116">
     <cfRule type="expression" dxfId="0" priority="63">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I116">
-    <cfRule type="expression" dxfId="0" priority="65">
-      <formula>MOD($B116,2)=1</formula>
+  <conditionalFormatting sqref="A117">
+    <cfRule type="duplicateValues" dxfId="1" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D117:E117">
+    <cfRule type="expression" dxfId="0" priority="57">
+      <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A117">
-    <cfRule type="duplicateValues" dxfId="1" priority="60"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D117:E117">
+  <conditionalFormatting sqref="I117">
     <cfRule type="expression" dxfId="0" priority="59">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I117">
-    <cfRule type="expression" dxfId="0" priority="61">
-      <formula>MOD($B117,2)=1</formula>
+  <conditionalFormatting sqref="A118">
+    <cfRule type="duplicateValues" dxfId="1" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D118:E118">
+    <cfRule type="expression" dxfId="0" priority="53">
+      <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A118">
-    <cfRule type="duplicateValues" dxfId="1" priority="56"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D118:E118">
+  <conditionalFormatting sqref="I118">
     <cfRule type="expression" dxfId="0" priority="55">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I118">
-    <cfRule type="expression" dxfId="0" priority="57">
-      <formula>MOD($B118,2)=1</formula>
+  <conditionalFormatting sqref="A119">
+    <cfRule type="duplicateValues" dxfId="1" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D119:E119">
+    <cfRule type="expression" dxfId="0" priority="49">
+      <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A119">
-    <cfRule type="duplicateValues" dxfId="1" priority="52"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D119:E119">
+  <conditionalFormatting sqref="I119">
     <cfRule type="expression" dxfId="0" priority="51">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I119">
-    <cfRule type="expression" dxfId="0" priority="53">
-      <formula>MOD($B119,2)=1</formula>
+  <conditionalFormatting sqref="A120">
+    <cfRule type="duplicateValues" dxfId="1" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D120:E120">
+    <cfRule type="expression" dxfId="0" priority="45">
+      <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A120">
-    <cfRule type="duplicateValues" dxfId="1" priority="48"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D120:E120">
+  <conditionalFormatting sqref="I120">
     <cfRule type="expression" dxfId="0" priority="47">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I120">
-    <cfRule type="expression" dxfId="0" priority="49">
-      <formula>MOD($B120,2)=1</formula>
+  <conditionalFormatting sqref="A121">
+    <cfRule type="duplicateValues" dxfId="1" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D121:E121">
+    <cfRule type="expression" dxfId="0" priority="41">
+      <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A121">
-    <cfRule type="duplicateValues" dxfId="1" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D121:E121">
+  <conditionalFormatting sqref="I121">
     <cfRule type="expression" dxfId="0" priority="43">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I121">
-    <cfRule type="expression" dxfId="0" priority="45">
-      <formula>MOD($B121,2)=1</formula>
+  <conditionalFormatting sqref="A122">
+    <cfRule type="duplicateValues" dxfId="1" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D122:E122">
+    <cfRule type="expression" dxfId="0" priority="37">
+      <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A122">
-    <cfRule type="duplicateValues" dxfId="1" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D122:E122">
+  <conditionalFormatting sqref="I122">
     <cfRule type="expression" dxfId="0" priority="39">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I122">
-    <cfRule type="expression" dxfId="0" priority="41">
-      <formula>MOD($B122,2)=1</formula>
+  <conditionalFormatting sqref="A123">
+    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D123:E123">
+    <cfRule type="expression" dxfId="0" priority="33">
+      <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A123">
-    <cfRule type="duplicateValues" dxfId="1" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D123:E123">
+  <conditionalFormatting sqref="I123">
     <cfRule type="expression" dxfId="0" priority="35">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I123">
-    <cfRule type="expression" dxfId="0" priority="37">
-      <formula>MOD($B123,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C134:L134">
-    <cfRule type="expression" dxfId="0" priority="163">
+    <cfRule type="expression" dxfId="0" priority="161">
       <formula>MOD($B134,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="expression" dxfId="0" priority="27">
+    <cfRule type="expression" dxfId="0" priority="25">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A178">
-    <cfRule type="duplicateValues" dxfId="1" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B178">
-    <cfRule type="expression" dxfId="0" priority="23">
+    <cfRule type="expression" dxfId="0" priority="21">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D178:E178">
-    <cfRule type="expression" dxfId="0" priority="21">
+    <cfRule type="expression" dxfId="0" priority="19">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H309">
-    <cfRule type="expression" dxfId="0" priority="441">
+    <cfRule type="expression" dxfId="0" priority="439">
       <formula>MOD($B308,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H321">
-    <cfRule type="expression" dxfId="0" priority="440">
+    <cfRule type="expression" dxfId="0" priority="438">
       <formula>MOD($B320,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L346">
-    <cfRule type="expression" dxfId="0" priority="442">
-      <formula>MOD($B350,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A48:A60">
-    <cfRule type="duplicateValues" dxfId="1" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A87:A92">
-    <cfRule type="duplicateValues" dxfId="1" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A93:A98">
-    <cfRule type="duplicateValues" dxfId="1" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99:A104">
-    <cfRule type="duplicateValues" dxfId="1" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A135:A177">
-    <cfRule type="duplicateValues" dxfId="1" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A209:A469">
-    <cfRule type="duplicateValues" dxfId="1" priority="17"/>
+  <conditionalFormatting sqref="A209:A425">
+    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B60">
-    <cfRule type="expression" dxfId="0" priority="122">
+    <cfRule type="expression" dxfId="0" priority="120">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C84">
-    <cfRule type="expression" dxfId="0" priority="125">
+    <cfRule type="expression" dxfId="0" priority="123">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C271:C281">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="0" priority="12">
       <formula>MOD($B271,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C282:C296">
-    <cfRule type="expression" dxfId="0" priority="12">
+    <cfRule type="expression" dxfId="0" priority="10">
       <formula>MOD($B282,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E93:E98">
-    <cfRule type="expression" dxfId="0" priority="114">
+    <cfRule type="expression" dxfId="0" priority="112">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E99:E104">
-    <cfRule type="expression" dxfId="0" priority="111">
+    <cfRule type="expression" dxfId="0" priority="109">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E257:E268">
-    <cfRule type="expression" dxfId="0" priority="15">
+    <cfRule type="expression" dxfId="0" priority="13">
       <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E271:E279">
-    <cfRule type="expression" dxfId="0" priority="13">
+    <cfRule type="expression" dxfId="0" priority="11">
       <formula>MOD($B271,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E282:E290">
-    <cfRule type="expression" dxfId="0" priority="11">
+    <cfRule type="expression" dxfId="0" priority="9">
       <formula>MOD($B282,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39:K42">
-    <cfRule type="duplicateValues" dxfId="2" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K169:K172">
-    <cfRule type="duplicateValues" dxfId="2" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K293:K296">
-    <cfRule type="expression" dxfId="0" priority="9">
+    <cfRule type="expression" dxfId="0" priority="7">
       <formula>MOD($B293,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K347:K350">
-    <cfRule type="expression" dxfId="0" priority="7">
+  <conditionalFormatting sqref="K346:K349">
+    <cfRule type="expression" dxfId="0" priority="5">
       <formula>MOD($B346,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K384:K387">
-    <cfRule type="expression" dxfId="0" priority="5">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>MOD($B384,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K422:K425">
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD($B422,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L205:L208">
-    <cfRule type="expression" dxfId="0" priority="20">
+    <cfRule type="expression" dxfId="0" priority="18">
       <formula>MOD($B205,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L293:L296">
-    <cfRule type="expression" dxfId="0" priority="10">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>MOD($B293,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L347:L350">
-    <cfRule type="expression" dxfId="0" priority="8">
+  <conditionalFormatting sqref="L346:L349">
+    <cfRule type="expression" dxfId="0" priority="6">
       <formula>MOD($B346,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L384:L387">
-    <cfRule type="expression" dxfId="0" priority="6">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>MOD($B384,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L422:L425">
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>MOD($B422,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L440:L446">
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>MOD($B440,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L454:L457">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>MOD($B454,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A470:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="437"/>
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A426:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="435"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L4">
-    <cfRule type="expression" dxfId="0" priority="436">
+    <cfRule type="expression" dxfId="0" priority="434">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41:B42 B44:B47">
-    <cfRule type="expression" dxfId="0" priority="170">
+    <cfRule type="expression" dxfId="0" priority="168">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45 C46:C47 F46:F47 B61:L76 D77:E84 B179:L204 B205:G208 I205:K208 I209:I256 B258 B259:D268 F259:L268 B269:L270 B271:B279 D271:D279 F271:L279 B280:B281 D280:L281 B282:B290 D282:D290 F282:L290 B291:B292 D291:L292 B293:B296 D293:J296 B297:L307 B308:G309 I308:L309 B310:L319 B320:G321 I320:L321 B322:L343 B344:K344 B345:L345 B346:J350 B351:L383 B384:J387 B388:L421 B422:J425 B426:L439 B440:K446 B447:L453 B454:K457 B458:L1048576">
-    <cfRule type="expression" dxfId="0" priority="435">
+  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 H179:L204 B179:G208 I205:K208 I209:I256 B259:D268 F259:L268 B269:L270 B271:B296 D271:D279 F271:L279 D280:L281 D282:D290 F282:L290 D291:L292 D293:J296 H297:L307 H310:L319 I320:L321 B322:L345 B297:G321 B258 B346:J349 B350:L383 B384:J387 B388:L421 B422:J425 B426:L1048576 I308:L309">
+    <cfRule type="expression" dxfId="0" priority="433">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43:G43 J43:L43">
-    <cfRule type="expression" dxfId="0" priority="135">
+    <cfRule type="expression" dxfId="0" priority="133">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44:G44 J44:L47 G45:G47 C45:C47">
-    <cfRule type="expression" dxfId="0" priority="169">
+    <cfRule type="expression" dxfId="0" priority="167">
       <formula>MOD($B44,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45:E47">
-    <cfRule type="expression" dxfId="0" priority="166">
+    <cfRule type="expression" dxfId="0" priority="164">
       <formula>MOD($B45,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F60 C48:C60">
-    <cfRule type="expression" dxfId="0" priority="123">
+    <cfRule type="expression" dxfId="0" priority="121">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
-    <cfRule type="expression" dxfId="0" priority="121">
+    <cfRule type="expression" dxfId="0" priority="119">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D48:E60">
-    <cfRule type="expression" dxfId="0" priority="119">
+    <cfRule type="expression" dxfId="0" priority="117">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B77:B84 F77:L84">
-    <cfRule type="expression" dxfId="0" priority="165">
+    <cfRule type="expression" dxfId="0" priority="163">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85:C85 F85:L85">
-    <cfRule type="expression" dxfId="0" priority="161">
+    <cfRule type="expression" dxfId="0" priority="159">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B86:C86 F86:L86">
-    <cfRule type="expression" dxfId="0" priority="126">
+    <cfRule type="expression" dxfId="0" priority="124">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87:C92 F87:L92 I93:I104">
-    <cfRule type="expression" dxfId="0" priority="116">
+    <cfRule type="expression" dxfId="0" priority="114">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87:E92 D93:D104">
-    <cfRule type="expression" dxfId="0" priority="117">
+    <cfRule type="expression" dxfId="0" priority="115">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:C98 F93:H98 J93:L98">
-    <cfRule type="expression" dxfId="0" priority="113">
+    <cfRule type="expression" dxfId="0" priority="111">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99:C104 F99:H104 J99:L104">
-    <cfRule type="expression" dxfId="0" priority="110">
+    <cfRule type="expression" dxfId="0" priority="108">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:C105 F105:H105 J105:L105">
-    <cfRule type="expression" dxfId="0" priority="106">
+    <cfRule type="expression" dxfId="0" priority="104">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106:C106 F106:H106 J106:L106 H107:H111 C107:C111">
-    <cfRule type="expression" dxfId="0" priority="102">
+    <cfRule type="expression" dxfId="0" priority="100">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107 F107:G107 J107:L107">
-    <cfRule type="expression" dxfId="0" priority="98">
+    <cfRule type="expression" dxfId="0" priority="96">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B108 F108:G108 J108:L108">
-    <cfRule type="expression" dxfId="0" priority="94">
+    <cfRule type="expression" dxfId="0" priority="92">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B109 F109:G109 J109:L109">
-    <cfRule type="expression" dxfId="0" priority="90">
+    <cfRule type="expression" dxfId="0" priority="88">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B110 F110:G110 J110:L110">
-    <cfRule type="expression" dxfId="0" priority="86">
+    <cfRule type="expression" dxfId="0" priority="84">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111 F111:G111 J111:L111">
-    <cfRule type="expression" dxfId="0" priority="82">
+    <cfRule type="expression" dxfId="0" priority="80">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112:C112 F112:H112 J112:L112 H113:H117 C113:C117">
-    <cfRule type="expression" dxfId="0" priority="78">
+    <cfRule type="expression" dxfId="0" priority="76">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113 F113:G113 J113:L113">
-    <cfRule type="expression" dxfId="0" priority="74">
+    <cfRule type="expression" dxfId="0" priority="72">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114 F114:G114 J114:L114">
-    <cfRule type="expression" dxfId="0" priority="70">
+    <cfRule type="expression" dxfId="0" priority="68">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115 F115:G115 J115:L115">
-    <cfRule type="expression" dxfId="0" priority="66">
+    <cfRule type="expression" dxfId="0" priority="64">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B116 F116:G116 J116:L116">
-    <cfRule type="expression" dxfId="0" priority="62">
+    <cfRule type="expression" dxfId="0" priority="60">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117 F117:G117 J117:L117">
-    <cfRule type="expression" dxfId="0" priority="58">
+    <cfRule type="expression" dxfId="0" priority="56">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118:C118 F118:H118 J118:L118 H119:H123 C119:C123">
-    <cfRule type="expression" dxfId="0" priority="54">
+    <cfRule type="expression" dxfId="0" priority="52">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119 F119:G119 J119:L119">
-    <cfRule type="expression" dxfId="0" priority="50">
+    <cfRule type="expression" dxfId="0" priority="48">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120 F120:G120 J120:L120">
-    <cfRule type="expression" dxfId="0" priority="46">
+    <cfRule type="expression" dxfId="0" priority="44">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121 F121:G121 J121:L121">
-    <cfRule type="expression" dxfId="0" priority="42">
+    <cfRule type="expression" dxfId="0" priority="40">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122 F122:G122 J122:L122">
-    <cfRule type="expression" dxfId="0" priority="38">
+    <cfRule type="expression" dxfId="0" priority="36">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123 F123:G123 J123:L123">
-    <cfRule type="expression" dxfId="0" priority="34">
+    <cfRule type="expression" dxfId="0" priority="32">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B124:L133 B134">
-    <cfRule type="expression" dxfId="0" priority="164">
+    <cfRule type="expression" dxfId="0" priority="162">
       <formula>MOD($B124,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171:B172 B174:B177">
-    <cfRule type="expression" dxfId="0" priority="31">
+    <cfRule type="expression" dxfId="0" priority="29">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171:G172 J171:J172 L171:L172 F175:F177 C176:C177">
-    <cfRule type="expression" dxfId="0" priority="32">
+    <cfRule type="expression" dxfId="0" priority="30">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173:G173 J173:L173">
-    <cfRule type="expression" dxfId="0" priority="26">
+    <cfRule type="expression" dxfId="0" priority="24">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174:G174 J174:L177 G175:G177 C175:C177">
-    <cfRule type="expression" dxfId="0" priority="30">
+    <cfRule type="expression" dxfId="0" priority="28">
       <formula>MOD($B174,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D175:E177">
-    <cfRule type="expression" dxfId="0" priority="29">
+    <cfRule type="expression" dxfId="0" priority="27">
       <formula>MOD($B175,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F178 C178">
-    <cfRule type="expression" dxfId="0" priority="24">
+    <cfRule type="expression" dxfId="0" priority="22">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J178:L178 G178 C178">
-    <cfRule type="expression" dxfId="0" priority="22">
+    <cfRule type="expression" dxfId="0" priority="20">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B209:D209 F209:H209 J209:L250 B210:H250">
-    <cfRule type="expression" dxfId="0" priority="19">
+    <cfRule type="expression" dxfId="0" priority="17">
       <formula>MOD($B209,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B251:H256 J251:L256">
-    <cfRule type="expression" dxfId="0" priority="18">
+    <cfRule type="expression" dxfId="0" priority="16">
       <formula>MOD($B251,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B257 B259 B261 B263 B265 B267 B269 B271 B273 B275 B277 B279 B281 B283 B285 B287 B289 B291 B293 B295">
-    <cfRule type="expression" dxfId="0" priority="16">
+    <cfRule type="expression" dxfId="0" priority="14">
       <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C257:D257 F257:L257">
-    <cfRule type="expression" dxfId="0" priority="439">
+    <cfRule type="expression" dxfId="0" priority="437">
       <formula>MOD($B258,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C258:D258 I292 I290 I288 I286 I284 I282 I280 I278 I276 I274 I272 I270 I268 I266 I264 I262 I260 D268 D266 D264 D262 D260 F258:L258">
-    <cfRule type="expression" dxfId="0" priority="438">
+    <cfRule type="expression" dxfId="0" priority="436">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$680</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$731</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="107">
   <si>
     <t>id</t>
   </si>
@@ -628,6 +628,9 @@
   <si>
     <t>grand</t>
   </si>
+  <si>
+    <t>用于触发扩列</t>
+  </si>
 </sst>
 </file>
 
@@ -876,7 +879,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -887,8 +891,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -6005,7 +6008,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L687"/>
+  <dimension ref="A1:L731"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="11"/>
@@ -12507,7 +12510,7 @@
         <v>0</v>
       </c>
       <c r="K205" s="12">
-        <v>10170003</v>
+        <v>10170101</v>
       </c>
       <c r="L205" s="14" t="s">
         <v>65</v>
@@ -12536,7 +12539,7 @@
         <v>0</v>
       </c>
       <c r="K206" s="12">
-        <v>10170004</v>
+        <v>10170102</v>
       </c>
       <c r="L206" s="14" t="s">
         <v>66</v>
@@ -12565,7 +12568,7 @@
         <v>0</v>
       </c>
       <c r="K207" s="12">
-        <v>10170005</v>
+        <v>10170103</v>
       </c>
       <c r="L207" s="14" t="s">
         <v>67</v>
@@ -12594,7 +12597,7 @@
         <v>0</v>
       </c>
       <c r="K208" s="12">
-        <v>10170006</v>
+        <v>10170104</v>
       </c>
       <c r="L208" s="14" t="s">
         <v>68</v>
@@ -24283,7 +24286,7 @@
     </row>
     <row r="681" customHeight="1" spans="1:12">
       <c r="A681" s="3">
-        <f t="shared" ref="A681:A686" si="27">(B681)*10000+C681+F681*100+D681*100000</f>
+        <f t="shared" ref="A681:A687" si="27">(B681)*10000+C681+F681*100+D681*100000</f>
         <v>1037100301</v>
       </c>
       <c r="B681" s="2">
@@ -24409,7 +24412,7 @@
     </row>
     <row r="687" customHeight="1" spans="1:12">
       <c r="A687" s="3">
-        <f>(B687)*10000+C687+F687*100+D687*100000</f>
+        <f t="shared" si="27"/>
         <v>1037100307</v>
       </c>
       <c r="B687" s="2">
@@ -24428,8 +24431,980 @@
         <v>200</v>
       </c>
     </row>
+    <row r="688" customHeight="1" spans="1:12">
+      <c r="A688" s="3">
+        <f t="shared" ref="A688:A721" si="28">(B688)*10000+C688+F688*100+D688*100000</f>
+        <v>1031100207</v>
+      </c>
+      <c r="B688" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C688" s="2">
+        <v>7</v>
+      </c>
+      <c r="D688" s="2">
+        <v>1</v>
+      </c>
+      <c r="F688" s="2">
+        <v>2</v>
+      </c>
+      <c r="G688" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="689" customHeight="1" spans="1:7">
+      <c r="A689" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100208</v>
+      </c>
+      <c r="B689" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C689" s="2">
+        <v>8</v>
+      </c>
+      <c r="D689" s="2">
+        <v>1</v>
+      </c>
+      <c r="F689" s="2">
+        <v>2</v>
+      </c>
+      <c r="G689" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="690" customHeight="1" spans="1:7">
+      <c r="A690" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100209</v>
+      </c>
+      <c r="B690" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C690" s="2">
+        <v>9</v>
+      </c>
+      <c r="D690" s="2">
+        <v>1</v>
+      </c>
+      <c r="F690" s="2">
+        <v>2</v>
+      </c>
+      <c r="G690" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="691" customHeight="1" spans="1:7">
+      <c r="A691" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100210</v>
+      </c>
+      <c r="B691" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C691" s="2">
+        <v>10</v>
+      </c>
+      <c r="D691" s="2">
+        <v>1</v>
+      </c>
+      <c r="F691" s="2">
+        <v>2</v>
+      </c>
+      <c r="G691" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="692" customHeight="1" spans="1:7">
+      <c r="A692" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100301</v>
+      </c>
+      <c r="B692" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C692" s="2">
+        <v>1</v>
+      </c>
+      <c r="D692" s="2">
+        <v>1</v>
+      </c>
+      <c r="F692" s="2">
+        <v>3</v>
+      </c>
+      <c r="G692" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="693" customHeight="1" spans="1:7">
+      <c r="A693" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100302</v>
+      </c>
+      <c r="B693" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C693" s="2">
+        <v>2</v>
+      </c>
+      <c r="D693" s="2">
+        <v>1</v>
+      </c>
+      <c r="F693" s="2">
+        <v>3</v>
+      </c>
+      <c r="G693" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="694" customHeight="1" spans="1:7">
+      <c r="A694" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100303</v>
+      </c>
+      <c r="B694" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C694" s="2">
+        <v>3</v>
+      </c>
+      <c r="D694" s="2">
+        <v>1</v>
+      </c>
+      <c r="F694" s="2">
+        <v>3</v>
+      </c>
+      <c r="G694" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="695" customHeight="1" spans="1:7">
+      <c r="A695" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100304</v>
+      </c>
+      <c r="B695" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C695" s="2">
+        <v>4</v>
+      </c>
+      <c r="D695" s="2">
+        <v>1</v>
+      </c>
+      <c r="F695" s="2">
+        <v>3</v>
+      </c>
+      <c r="G695" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="696" customHeight="1" spans="1:7">
+      <c r="A696" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100305</v>
+      </c>
+      <c r="B696" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C696" s="2">
+        <v>5</v>
+      </c>
+      <c r="D696" s="2">
+        <v>1</v>
+      </c>
+      <c r="F696" s="2">
+        <v>3</v>
+      </c>
+      <c r="G696" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="697" customHeight="1" spans="1:7">
+      <c r="A697" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100306</v>
+      </c>
+      <c r="B697" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C697" s="2">
+        <v>6</v>
+      </c>
+      <c r="D697" s="2">
+        <v>1</v>
+      </c>
+      <c r="F697" s="2">
+        <v>3</v>
+      </c>
+      <c r="G697" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="698" customHeight="1" spans="1:7">
+      <c r="A698" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100307</v>
+      </c>
+      <c r="B698" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C698" s="2">
+        <v>7</v>
+      </c>
+      <c r="D698" s="2">
+        <v>1</v>
+      </c>
+      <c r="F698" s="2">
+        <v>3</v>
+      </c>
+      <c r="G698" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="699" customHeight="1" spans="1:7">
+      <c r="A699" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100308</v>
+      </c>
+      <c r="B699" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C699" s="2">
+        <v>8</v>
+      </c>
+      <c r="D699" s="2">
+        <v>1</v>
+      </c>
+      <c r="F699" s="2">
+        <v>3</v>
+      </c>
+      <c r="G699" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="700" customHeight="1" spans="1:7">
+      <c r="A700" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100309</v>
+      </c>
+      <c r="B700" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C700" s="2">
+        <v>9</v>
+      </c>
+      <c r="D700" s="2">
+        <v>1</v>
+      </c>
+      <c r="F700" s="2">
+        <v>3</v>
+      </c>
+      <c r="G700" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="701" customHeight="1" spans="1:7">
+      <c r="A701" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100310</v>
+      </c>
+      <c r="B701" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C701" s="2">
+        <v>10</v>
+      </c>
+      <c r="D701" s="2">
+        <v>1</v>
+      </c>
+      <c r="F701" s="2">
+        <v>3</v>
+      </c>
+      <c r="G701" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="702" customHeight="1" spans="1:7">
+      <c r="A702" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100401</v>
+      </c>
+      <c r="B702" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C702" s="2">
+        <v>1</v>
+      </c>
+      <c r="D702" s="2">
+        <v>1</v>
+      </c>
+      <c r="F702" s="2">
+        <v>4</v>
+      </c>
+      <c r="G702" s="12">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="703" customHeight="1" spans="1:7">
+      <c r="A703" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100402</v>
+      </c>
+      <c r="B703" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C703" s="2">
+        <v>2</v>
+      </c>
+      <c r="D703" s="2">
+        <v>1</v>
+      </c>
+      <c r="F703" s="2">
+        <v>4</v>
+      </c>
+      <c r="G703" s="12">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="704" customHeight="1" spans="1:7">
+      <c r="A704" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100403</v>
+      </c>
+      <c r="B704" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C704" s="2">
+        <v>3</v>
+      </c>
+      <c r="D704" s="2">
+        <v>1</v>
+      </c>
+      <c r="F704" s="2">
+        <v>4</v>
+      </c>
+      <c r="G704" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="705" customHeight="1" spans="1:7">
+      <c r="A705" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100404</v>
+      </c>
+      <c r="B705" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C705" s="2">
+        <v>4</v>
+      </c>
+      <c r="D705" s="2">
+        <v>1</v>
+      </c>
+      <c r="F705" s="2">
+        <v>4</v>
+      </c>
+      <c r="G705" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="706" customHeight="1" spans="1:7">
+      <c r="A706" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100405</v>
+      </c>
+      <c r="B706" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C706" s="2">
+        <v>5</v>
+      </c>
+      <c r="D706" s="2">
+        <v>1</v>
+      </c>
+      <c r="F706" s="2">
+        <v>4</v>
+      </c>
+      <c r="G706" s="12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="707" customHeight="1" spans="1:7">
+      <c r="A707" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100406</v>
+      </c>
+      <c r="B707" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C707" s="2">
+        <v>6</v>
+      </c>
+      <c r="D707" s="2">
+        <v>1</v>
+      </c>
+      <c r="F707" s="2">
+        <v>4</v>
+      </c>
+      <c r="G707" s="12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="708" customHeight="1" spans="1:7">
+      <c r="A708" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100407</v>
+      </c>
+      <c r="B708" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C708" s="2">
+        <v>7</v>
+      </c>
+      <c r="D708" s="2">
+        <v>1</v>
+      </c>
+      <c r="F708" s="2">
+        <v>4</v>
+      </c>
+      <c r="G708" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="709" customHeight="1" spans="1:7">
+      <c r="A709" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100408</v>
+      </c>
+      <c r="B709" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C709" s="2">
+        <v>8</v>
+      </c>
+      <c r="D709" s="2">
+        <v>1</v>
+      </c>
+      <c r="F709" s="2">
+        <v>4</v>
+      </c>
+      <c r="G709" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="710" customHeight="1" spans="1:7">
+      <c r="A710" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100409</v>
+      </c>
+      <c r="B710" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C710" s="2">
+        <v>9</v>
+      </c>
+      <c r="D710" s="2">
+        <v>1</v>
+      </c>
+      <c r="F710" s="2">
+        <v>4</v>
+      </c>
+      <c r="G710" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="711" customHeight="1" spans="1:7">
+      <c r="A711" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100410</v>
+      </c>
+      <c r="B711" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C711" s="2">
+        <v>10</v>
+      </c>
+      <c r="D711" s="2">
+        <v>1</v>
+      </c>
+      <c r="F711" s="2">
+        <v>4</v>
+      </c>
+      <c r="G711" s="12">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="712" customHeight="1" spans="1:7">
+      <c r="A712" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100501</v>
+      </c>
+      <c r="B712" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C712" s="2">
+        <v>1</v>
+      </c>
+      <c r="D712" s="2">
+        <v>1</v>
+      </c>
+      <c r="F712" s="2">
+        <v>5</v>
+      </c>
+      <c r="G712" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="713" customHeight="1" spans="1:7">
+      <c r="A713" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100502</v>
+      </c>
+      <c r="B713" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C713" s="2">
+        <v>2</v>
+      </c>
+      <c r="D713" s="2">
+        <v>1</v>
+      </c>
+      <c r="F713" s="2">
+        <v>5</v>
+      </c>
+      <c r="G713" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="714" customHeight="1" spans="1:7">
+      <c r="A714" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100503</v>
+      </c>
+      <c r="B714" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C714" s="2">
+        <v>3</v>
+      </c>
+      <c r="D714" s="2">
+        <v>1</v>
+      </c>
+      <c r="F714" s="2">
+        <v>5</v>
+      </c>
+      <c r="G714" s="12">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="715" customHeight="1" spans="1:7">
+      <c r="A715" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100504</v>
+      </c>
+      <c r="B715" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C715" s="2">
+        <v>4</v>
+      </c>
+      <c r="D715" s="2">
+        <v>1</v>
+      </c>
+      <c r="F715" s="2">
+        <v>5</v>
+      </c>
+      <c r="G715" s="12">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="716" customHeight="1" spans="1:7">
+      <c r="A716" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100505</v>
+      </c>
+      <c r="B716" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C716" s="2">
+        <v>5</v>
+      </c>
+      <c r="D716" s="2">
+        <v>1</v>
+      </c>
+      <c r="F716" s="2">
+        <v>5</v>
+      </c>
+      <c r="G716" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="717" customHeight="1" spans="1:7">
+      <c r="A717" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100506</v>
+      </c>
+      <c r="B717" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C717" s="2">
+        <v>6</v>
+      </c>
+      <c r="D717" s="2">
+        <v>1</v>
+      </c>
+      <c r="F717" s="2">
+        <v>5</v>
+      </c>
+      <c r="G717" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="718" customHeight="1" spans="1:7">
+      <c r="A718" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100507</v>
+      </c>
+      <c r="B718" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C718" s="2">
+        <v>7</v>
+      </c>
+      <c r="D718" s="2">
+        <v>1</v>
+      </c>
+      <c r="F718" s="2">
+        <v>5</v>
+      </c>
+      <c r="G718" s="12">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="719" customHeight="1" spans="1:7">
+      <c r="A719" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100508</v>
+      </c>
+      <c r="B719" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C719" s="2">
+        <v>8</v>
+      </c>
+      <c r="D719" s="2">
+        <v>1</v>
+      </c>
+      <c r="F719" s="2">
+        <v>5</v>
+      </c>
+      <c r="G719" s="12">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="720" customHeight="1" spans="1:7">
+      <c r="A720" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100509</v>
+      </c>
+      <c r="B720" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C720" s="2">
+        <v>9</v>
+      </c>
+      <c r="D720" s="2">
+        <v>1</v>
+      </c>
+      <c r="F720" s="2">
+        <v>5</v>
+      </c>
+      <c r="G720" s="12">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="721" customHeight="1" spans="1:12">
+      <c r="A721" s="3">
+        <f t="shared" si="28"/>
+        <v>1031100510</v>
+      </c>
+      <c r="B721" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C721" s="2">
+        <v>10</v>
+      </c>
+      <c r="D721" s="2">
+        <v>1</v>
+      </c>
+      <c r="F721" s="2">
+        <v>5</v>
+      </c>
+      <c r="G721" s="12">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="722" customHeight="1" spans="1:12">
+      <c r="A722" s="3">
+        <f t="shared" ref="A722:A731" si="29">(B722)*10000+C722+F722*100+D722*100000</f>
+        <v>1031400312</v>
+      </c>
+      <c r="B722" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C722" s="2">
+        <v>12</v>
+      </c>
+      <c r="D722" s="2">
+        <v>4</v>
+      </c>
+      <c r="F722" s="2">
+        <v>3</v>
+      </c>
+      <c r="G722" s="12">
+        <v>250</v>
+      </c>
+      <c r="H722" s="12">
+        <v>30310003</v>
+      </c>
+    </row>
+    <row r="723" customHeight="1" spans="1:12">
+      <c r="A723" s="3">
+        <f t="shared" si="29"/>
+        <v>1031400412</v>
+      </c>
+      <c r="B723" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C723" s="2">
+        <v>12</v>
+      </c>
+      <c r="D723" s="2">
+        <v>4</v>
+      </c>
+      <c r="F723" s="2">
+        <v>4</v>
+      </c>
+      <c r="G723" s="12">
+        <v>625</v>
+      </c>
+      <c r="H723" s="12">
+        <v>30310003</v>
+      </c>
+    </row>
+    <row r="724" customHeight="1" spans="1:12">
+      <c r="A724" s="3">
+        <f t="shared" si="29"/>
+        <v>1031400512</v>
+      </c>
+      <c r="B724" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C724" s="2">
+        <v>12</v>
+      </c>
+      <c r="D724" s="2">
+        <v>4</v>
+      </c>
+      <c r="F724" s="2">
+        <v>5</v>
+      </c>
+      <c r="G724" s="12">
+        <v>2500</v>
+      </c>
+      <c r="H724" s="12">
+        <v>30310003</v>
+      </c>
+    </row>
+    <row r="725" customHeight="1" spans="1:12">
+      <c r="A725" s="3">
+        <f t="shared" si="29"/>
+        <v>1031400213</v>
+      </c>
+      <c r="B725" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C725" s="2">
+        <v>13</v>
+      </c>
+      <c r="D725" s="2">
+        <v>4</v>
+      </c>
+      <c r="F725" s="2">
+        <v>2</v>
+      </c>
+      <c r="G725" s="12">
+        <v>0</v>
+      </c>
+      <c r="H725" s="12">
+        <v>30310004</v>
+      </c>
+    </row>
+    <row r="726" customHeight="1" spans="1:12">
+      <c r="A726" s="3">
+        <f t="shared" si="29"/>
+        <v>1031400114</v>
+      </c>
+      <c r="B726" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C726" s="2">
+        <v>14</v>
+      </c>
+      <c r="D726" s="2">
+        <v>4</v>
+      </c>
+      <c r="F726" s="2">
+        <v>1</v>
+      </c>
+      <c r="G726" s="12">
+        <v>0</v>
+      </c>
+      <c r="K726" s="2">
+        <v>103100101</v>
+      </c>
+      <c r="L726" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="727" customHeight="1" spans="1:12">
+      <c r="A727" s="3">
+        <f t="shared" si="29"/>
+        <v>1031400115</v>
+      </c>
+      <c r="B727" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C727" s="2">
+        <v>15</v>
+      </c>
+      <c r="D727" s="2">
+        <v>4</v>
+      </c>
+      <c r="F727" s="2">
+        <v>1</v>
+      </c>
+      <c r="G727" s="12">
+        <v>0</v>
+      </c>
+      <c r="K727" s="2">
+        <v>103100102</v>
+      </c>
+      <c r="L727" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="728" customHeight="1" spans="1:12">
+      <c r="A728" s="3">
+        <f t="shared" si="29"/>
+        <v>1031400116</v>
+      </c>
+      <c r="B728" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C728" s="2">
+        <v>16</v>
+      </c>
+      <c r="D728" s="2">
+        <v>4</v>
+      </c>
+      <c r="F728" s="2">
+        <v>1</v>
+      </c>
+      <c r="G728" s="12">
+        <v>0</v>
+      </c>
+      <c r="K728" s="2">
+        <v>103100103</v>
+      </c>
+      <c r="L728" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="729" customHeight="1" spans="1:12">
+      <c r="A729" s="3">
+        <f t="shared" si="29"/>
+        <v>1031400117</v>
+      </c>
+      <c r="B729" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C729" s="2">
+        <v>17</v>
+      </c>
+      <c r="D729" s="2">
+        <v>4</v>
+      </c>
+      <c r="F729" s="2">
+        <v>1</v>
+      </c>
+      <c r="G729" s="12">
+        <v>0</v>
+      </c>
+      <c r="K729" s="2">
+        <v>103100104</v>
+      </c>
+      <c r="L729" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="730" customHeight="1" spans="1:12">
+      <c r="A730" s="3">
+        <f t="shared" si="29"/>
+        <v>1031400118</v>
+      </c>
+      <c r="B730" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C730" s="2">
+        <v>18</v>
+      </c>
+      <c r="D730" s="2">
+        <v>4</v>
+      </c>
+      <c r="E730" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F730" s="2">
+        <v>1</v>
+      </c>
+      <c r="G730" s="12">
+        <v>0</v>
+      </c>
+      <c r="H730" s="12">
+        <v>30310001</v>
+      </c>
+    </row>
+    <row r="731" customHeight="1" spans="1:12">
+      <c r="A731" s="3">
+        <f t="shared" si="29"/>
+        <v>1031400318</v>
+      </c>
+      <c r="B731" s="2">
+        <v>103100</v>
+      </c>
+      <c r="C731" s="2">
+        <v>18</v>
+      </c>
+      <c r="D731" s="2">
+        <v>4</v>
+      </c>
+      <c r="E731" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F731" s="2">
+        <v>3</v>
+      </c>
+      <c r="G731" s="12">
+        <v>0</v>
+      </c>
+      <c r="H731" s="12">
+        <v>30310002</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L680" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L731" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">
@@ -24765,7 +25740,7 @@
   <conditionalFormatting sqref="A209:A469">
     <cfRule type="duplicateValues" dxfId="1" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A521:A687">
+  <conditionalFormatting sqref="A521:A731">
     <cfRule type="duplicateValues" dxfId="1" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B60">
@@ -24939,7 +25914,7 @@
       <formula>MOD($B638,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A470:A520 A688:A1048576">
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A470:A520 A732:A1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="448"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L4">
@@ -24952,7 +25927,7 @@
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45 C46:C47 F46:F47 B61:L76 D77:E84 B179:L204 B205:G208 I205:K208 I209:I256 B258 B259:D268 F259:L268 B269:L270 B271:B279 D271:D279 F271:L279 B280:B281 D280:L281 B282:B290 D282:D290 F282:L290 B291:B292 D291:L292 B293:B296 D293:J296 B297:L307 B308:G309 I308:L309 B310:L319 B320:G321 I320:L321 B322:L343 B344:K344 B345:L345 B346:J350 B351:L383 B384:J387 B388:L421 B422:J425 B426:L439 B440:K446 B447:L453 B454:K457 B458:L516 B517:K520 B521:L548 B549:D549 F549:L549 B550:L591 B592 D592 I592:L592 B593:B594 D593:D594 I593:L594 B595 D595 I595:L595 B596:B601 D596:D601 I596:L601 B602 D602 F602:J602 B603:B604 D603:D604 F603:J604 B605 F605 H605:L605 B606:B607 F606:F607 I606:L607 B608 F608 I608:L608 B609:B610 D609:G610 I609:J610 B611 D611:J611 B612:L643 B644:K647 B648:L1048576">
+  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45 C46:C47 F46:F47 B61:L76 D77:E84 B179:L204 B205:G205 I205:K205 B206:G208 I206:K208 I209:I256 B258 B259:D268 F259:L268 B269:L270 B271:B279 D271:D279 F271:L279 B280:B281 D280:L281 B282:B290 D282:D290 F282:L290 B291:B292 D291:L292 B293:B296 D293:J296 B297:L307 B308:G309 I308:L309 B310:L319 B320:G321 I320:L321 B322:L343 B344:K344 B345:L345 B346:J350 B351:L383 B384:J387 B388:L421 B422:J425 B426:L439 B440:K446 B447:L453 B454:K457 B458:L516 B517:K520 B521:L548 B549:D549 F549:L549 B550:L591 B592 D592 I592:L592 B593:B594 D593:D594 I593:L594 B595 D595 I595:L595 B596:B601 D596:D601 I596:L601 B602 D602 F602:J602 B603:B604 D603:D604 F603:J604 B605 F605 H605:L605 B606:B607 F606:F607 I606:L607 B608 F608 I608:L608 B609:B610 D609:G610 I609:J610 B611 D611:J611 B612:L643 B644:K647 B648:L1048576">
     <cfRule type="expression" dxfId="0" priority="446">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$387</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$469</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="72">
   <si>
     <t>id</t>
   </si>
@@ -522,6 +522,9 @@
   </si>
   <si>
     <t>+1免费符号</t>
+  </si>
+  <si>
+    <t>Jackpot</t>
   </si>
 </sst>
 </file>
@@ -776,12 +779,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5821,7 +5824,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L425"/>
+  <dimension ref="A1:L469"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="10"/>
@@ -12323,7 +12326,7 @@
         <v>0</v>
       </c>
       <c r="K205" s="11">
-        <v>10170003</v>
+        <v>10170101</v>
       </c>
       <c r="L205" s="13" t="s">
         <v>65</v>
@@ -12352,7 +12355,7 @@
         <v>0</v>
       </c>
       <c r="K206" s="11">
-        <v>10170004</v>
+        <v>10170102</v>
       </c>
       <c r="L206" s="13" t="s">
         <v>66</v>
@@ -12381,7 +12384,7 @@
         <v>0</v>
       </c>
       <c r="K207" s="11">
-        <v>10170005</v>
+        <v>10170103</v>
       </c>
       <c r="L207" s="13" t="s">
         <v>67</v>
@@ -12410,7 +12413,7 @@
         <v>0</v>
       </c>
       <c r="K208" s="11">
-        <v>10170006</v>
+        <v>10170104</v>
       </c>
       <c r="L208" s="13" t="s">
         <v>68</v>
@@ -16152,11 +16155,8 @@
       <c r="I346" s="11">
         <v>0</v>
       </c>
-      <c r="K346" s="2">
-        <v>101800101</v>
-      </c>
-      <c r="L346" s="13" t="s">
-        <v>65</v>
+      <c r="L346" s="54" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="347" customHeight="1" spans="1:12">
@@ -16183,10 +16183,10 @@
         <v>0</v>
       </c>
       <c r="K347" s="2">
-        <v>101800102</v>
+        <v>101800101</v>
       </c>
       <c r="L347" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="348" customHeight="1" spans="1:12">
@@ -16213,10 +16213,10 @@
         <v>0</v>
       </c>
       <c r="K348" s="2">
-        <v>101800103</v>
+        <v>101800102</v>
       </c>
       <c r="L348" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="349" customHeight="1" spans="1:12">
@@ -16243,10 +16243,10 @@
         <v>0</v>
       </c>
       <c r="K349" s="2">
-        <v>101800104</v>
+        <v>101800103</v>
       </c>
       <c r="L349" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="350" customHeight="1" spans="1:12">
@@ -16272,8 +16272,11 @@
       <c r="I350" s="11">
         <v>0</v>
       </c>
-      <c r="L350" s="54" t="s">
-        <v>70</v>
+      <c r="K350" s="2">
+        <v>101800104</v>
+      </c>
+      <c r="L350" s="13" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="351" customHeight="1" spans="1:12">
@@ -17457,13 +17460,16 @@
       <c r="G398" s="11">
         <v>0</v>
       </c>
+      <c r="H398" s="11">
+        <v>30230001</v>
+      </c>
       <c r="I398" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="399" customHeight="1" spans="1:12">
       <c r="A399" s="3">
-        <f t="shared" ref="A399:A420" si="16">(B399)*10000+C399+F399*100+D399*100000</f>
+        <f t="shared" ref="A399:A426" si="16">(B399)*10000+C399+F399*100+D399*100000</f>
         <v>1023300401</v>
       </c>
       <c r="B399" s="2">
@@ -17721,6 +17727,9 @@
       <c r="G409" s="11">
         <v>0</v>
       </c>
+      <c r="H409" s="11">
+        <v>30230002</v>
+      </c>
       <c r="I409" s="11">
         <v>0</v>
       </c>
@@ -17985,13 +17994,16 @@
       <c r="G420" s="11">
         <v>0</v>
       </c>
+      <c r="H420" s="11">
+        <v>30230003</v>
+      </c>
       <c r="I420" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="421" customHeight="1" spans="1:12">
       <c r="A421" s="3">
-        <f>(B421)*10000+C421+F421*100+D421*100000</f>
+        <f t="shared" si="16"/>
         <v>1023400112</v>
       </c>
       <c r="B421" s="2">
@@ -18015,7 +18027,7 @@
     </row>
     <row r="422" customHeight="1" spans="1:12">
       <c r="A422" s="3">
-        <f>(B422)*10000+C422+F422*100+D422*100000</f>
+        <f t="shared" si="16"/>
         <v>1023400113</v>
       </c>
       <c r="B422" s="2">
@@ -18045,7 +18057,7 @@
     </row>
     <row r="423" customHeight="1" spans="1:12">
       <c r="A423" s="3">
-        <f>(B423)*10000+C423+F423*100+D423*100000</f>
+        <f t="shared" si="16"/>
         <v>1023400114</v>
       </c>
       <c r="B423" s="2">
@@ -18075,7 +18087,7 @@
     </row>
     <row r="424" customHeight="1" spans="1:12">
       <c r="A424" s="3">
-        <f>(B424)*10000+C424+F424*100+D424*100000</f>
+        <f t="shared" si="16"/>
         <v>1023400115</v>
       </c>
       <c r="B424" s="2">
@@ -18105,7 +18117,7 @@
     </row>
     <row r="425" customHeight="1" spans="1:12">
       <c r="A425" s="3">
-        <f>(B425)*10000+C425+F425*100+D425*100000</f>
+        <f t="shared" si="16"/>
         <v>1023400116</v>
       </c>
       <c r="B425" s="2">
@@ -18133,659 +18145,1805 @@
         <v>68</v>
       </c>
     </row>
+    <row r="426" customHeight="1" spans="1:12">
+      <c r="A426" s="3">
+        <f t="shared" si="16"/>
+        <v>1034100301</v>
+      </c>
+      <c r="B426" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C426" s="2">
+        <v>1</v>
+      </c>
+      <c r="D426" s="2">
+        <v>1</v>
+      </c>
+      <c r="F426" s="2">
+        <v>3</v>
+      </c>
+      <c r="G426" s="11">
+        <v>3</v>
+      </c>
+      <c r="I426" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" customHeight="1" spans="1:12">
+      <c r="A427" s="3">
+        <f t="shared" ref="A427:A433" si="17">(B427)*10000+C427+F427*100+D427*100000</f>
+        <v>1034100302</v>
+      </c>
+      <c r="B427" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C427" s="2">
+        <v>2</v>
+      </c>
+      <c r="D427" s="2">
+        <v>1</v>
+      </c>
+      <c r="F427" s="2">
+        <v>3</v>
+      </c>
+      <c r="G427" s="11">
+        <v>5</v>
+      </c>
+      <c r="I427" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" customHeight="1" spans="1:12">
+      <c r="A428" s="3">
+        <f t="shared" si="17"/>
+        <v>1034100303</v>
+      </c>
+      <c r="B428" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C428" s="2">
+        <v>3</v>
+      </c>
+      <c r="D428" s="2">
+        <v>1</v>
+      </c>
+      <c r="F428" s="2">
+        <v>3</v>
+      </c>
+      <c r="G428" s="11">
+        <v>8</v>
+      </c>
+      <c r="I428" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" customHeight="1" spans="1:12">
+      <c r="A429" s="3">
+        <f t="shared" si="17"/>
+        <v>1034100304</v>
+      </c>
+      <c r="B429" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C429" s="2">
+        <v>4</v>
+      </c>
+      <c r="D429" s="2">
+        <v>1</v>
+      </c>
+      <c r="F429" s="2">
+        <v>3</v>
+      </c>
+      <c r="G429" s="11">
+        <v>10</v>
+      </c>
+      <c r="I429" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" customHeight="1" spans="1:12">
+      <c r="A430" s="3">
+        <f t="shared" si="17"/>
+        <v>1034100305</v>
+      </c>
+      <c r="B430" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C430" s="2">
+        <v>5</v>
+      </c>
+      <c r="D430" s="2">
+        <v>1</v>
+      </c>
+      <c r="F430" s="2">
+        <v>3</v>
+      </c>
+      <c r="G430" s="11">
+        <v>25</v>
+      </c>
+      <c r="I430" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" customHeight="1" spans="1:12">
+      <c r="A431" s="3">
+        <f t="shared" si="17"/>
+        <v>1034100306</v>
+      </c>
+      <c r="B431" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C431" s="2">
+        <v>6</v>
+      </c>
+      <c r="D431" s="2">
+        <v>1</v>
+      </c>
+      <c r="F431" s="2">
+        <v>3</v>
+      </c>
+      <c r="G431" s="11">
+        <v>100</v>
+      </c>
+      <c r="I431" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" customHeight="1" spans="1:12">
+      <c r="A432" s="3">
+        <f t="shared" si="17"/>
+        <v>1034100307</v>
+      </c>
+      <c r="B432" s="2">
+        <v>103400</v>
+      </c>
+      <c r="C432" s="2">
+        <v>7</v>
+      </c>
+      <c r="D432" s="2">
+        <v>1</v>
+      </c>
+      <c r="F432" s="2">
+        <v>3</v>
+      </c>
+      <c r="G432" s="11">
+        <v>250</v>
+      </c>
+      <c r="I432" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" customHeight="1" spans="1:12">
+      <c r="A433" s="3">
+        <f t="shared" ref="A433:A446" si="18">(B433)*10000+C433+F433*100+D433*100000</f>
+        <v>1035100301</v>
+      </c>
+      <c r="B433" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C433" s="2">
+        <v>1</v>
+      </c>
+      <c r="D433" s="2">
+        <v>1</v>
+      </c>
+      <c r="F433" s="2">
+        <v>3</v>
+      </c>
+      <c r="G433" s="11">
+        <v>2</v>
+      </c>
+      <c r="I433" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" customHeight="1" spans="1:12">
+      <c r="A434" s="3">
+        <f t="shared" si="18"/>
+        <v>1035100302</v>
+      </c>
+      <c r="B434" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C434" s="2">
+        <v>2</v>
+      </c>
+      <c r="D434" s="2">
+        <v>1</v>
+      </c>
+      <c r="F434" s="2">
+        <v>3</v>
+      </c>
+      <c r="G434" s="11">
+        <v>3</v>
+      </c>
+      <c r="I434" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" customHeight="1" spans="1:12">
+      <c r="A435" s="3">
+        <f t="shared" si="18"/>
+        <v>1035100303</v>
+      </c>
+      <c r="B435" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C435" s="2">
+        <v>3</v>
+      </c>
+      <c r="D435" s="2">
+        <v>1</v>
+      </c>
+      <c r="F435" s="2">
+        <v>3</v>
+      </c>
+      <c r="G435" s="11">
+        <v>5</v>
+      </c>
+      <c r="I435" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" customHeight="1" spans="1:12">
+      <c r="A436" s="3">
+        <f t="shared" si="18"/>
+        <v>1035100304</v>
+      </c>
+      <c r="B436" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C436" s="2">
+        <v>4</v>
+      </c>
+      <c r="D436" s="2">
+        <v>1</v>
+      </c>
+      <c r="F436" s="2">
+        <v>3</v>
+      </c>
+      <c r="G436" s="11">
+        <v>10</v>
+      </c>
+      <c r="I436" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" customHeight="1" spans="1:12">
+      <c r="A437" s="3">
+        <f t="shared" si="18"/>
+        <v>1035100305</v>
+      </c>
+      <c r="B437" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C437" s="2">
+        <v>5</v>
+      </c>
+      <c r="D437" s="2">
+        <v>1</v>
+      </c>
+      <c r="F437" s="2">
+        <v>3</v>
+      </c>
+      <c r="G437" s="11">
+        <v>50</v>
+      </c>
+      <c r="I437" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" customHeight="1" spans="1:12">
+      <c r="A438" s="3">
+        <f t="shared" si="18"/>
+        <v>1035100306</v>
+      </c>
+      <c r="B438" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C438" s="2">
+        <v>6</v>
+      </c>
+      <c r="D438" s="2">
+        <v>1</v>
+      </c>
+      <c r="F438" s="2">
+        <v>3</v>
+      </c>
+      <c r="G438" s="11">
+        <v>100</v>
+      </c>
+      <c r="I438" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" customHeight="1" spans="1:12">
+      <c r="A439" s="3">
+        <f t="shared" si="18"/>
+        <v>1035100307</v>
+      </c>
+      <c r="B439" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C439" s="2">
+        <v>7</v>
+      </c>
+      <c r="D439" s="2">
+        <v>1</v>
+      </c>
+      <c r="F439" s="2">
+        <v>3</v>
+      </c>
+      <c r="G439" s="11">
+        <v>200</v>
+      </c>
+      <c r="I439" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" customHeight="1" spans="1:12">
+      <c r="A440" s="3">
+        <f t="shared" si="18"/>
+        <v>1035400109</v>
+      </c>
+      <c r="B440" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C440" s="2">
+        <v>9</v>
+      </c>
+      <c r="D440" s="2">
+        <v>4</v>
+      </c>
+      <c r="F440" s="2">
+        <v>1</v>
+      </c>
+      <c r="G440" s="11">
+        <v>0</v>
+      </c>
+      <c r="I440" s="11">
+        <v>0</v>
+      </c>
+      <c r="K440" s="2">
+        <v>103500101</v>
+      </c>
+      <c r="L440" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="441" customHeight="1" spans="1:12">
+      <c r="A441" s="3">
+        <f t="shared" si="18"/>
+        <v>1035400110</v>
+      </c>
+      <c r="B441" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C441" s="2">
+        <v>10</v>
+      </c>
+      <c r="D441" s="2">
+        <v>4</v>
+      </c>
+      <c r="F441" s="2">
+        <v>1</v>
+      </c>
+      <c r="G441" s="11">
+        <v>0</v>
+      </c>
+      <c r="I441" s="11">
+        <v>0</v>
+      </c>
+      <c r="K441" s="2">
+        <v>103500102</v>
+      </c>
+      <c r="L441" s="13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="442" customHeight="1" spans="1:12">
+      <c r="A442" s="3">
+        <f t="shared" si="18"/>
+        <v>1035400111</v>
+      </c>
+      <c r="B442" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C442" s="2">
+        <v>11</v>
+      </c>
+      <c r="D442" s="2">
+        <v>4</v>
+      </c>
+      <c r="F442" s="2">
+        <v>1</v>
+      </c>
+      <c r="G442" s="11">
+        <v>0</v>
+      </c>
+      <c r="I442" s="11">
+        <v>0</v>
+      </c>
+      <c r="K442" s="2">
+        <v>103500103</v>
+      </c>
+      <c r="L442" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="443" customHeight="1" spans="1:12">
+      <c r="A443" s="3">
+        <f t="shared" si="18"/>
+        <v>1035400112</v>
+      </c>
+      <c r="B443" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C443" s="2">
+        <v>12</v>
+      </c>
+      <c r="D443" s="2">
+        <v>4</v>
+      </c>
+      <c r="F443" s="2">
+        <v>1</v>
+      </c>
+      <c r="G443" s="11">
+        <v>0</v>
+      </c>
+      <c r="I443" s="11">
+        <v>0</v>
+      </c>
+      <c r="K443" s="2">
+        <v>103500104</v>
+      </c>
+      <c r="L443" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="444" customHeight="1" spans="1:12">
+      <c r="A444" s="3">
+        <f t="shared" si="18"/>
+        <v>1035400508</v>
+      </c>
+      <c r="B444" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C444" s="2">
+        <v>8</v>
+      </c>
+      <c r="D444" s="2">
+        <v>4</v>
+      </c>
+      <c r="F444" s="2">
+        <v>5</v>
+      </c>
+      <c r="G444" s="11">
+        <v>0</v>
+      </c>
+      <c r="H444" s="11">
+        <v>30350002</v>
+      </c>
+      <c r="I444" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" customHeight="1" spans="1:12">
+      <c r="A445" s="3">
+        <f t="shared" si="18"/>
+        <v>1035400608</v>
+      </c>
+      <c r="B445" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C445" s="2">
+        <v>8</v>
+      </c>
+      <c r="D445" s="2">
+        <v>4</v>
+      </c>
+      <c r="F445" s="2">
+        <v>6</v>
+      </c>
+      <c r="G445" s="11">
+        <v>0</v>
+      </c>
+      <c r="H445" s="11">
+        <v>30350002</v>
+      </c>
+      <c r="I445" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" customHeight="1" spans="1:12">
+      <c r="A446" s="3">
+        <f t="shared" si="18"/>
+        <v>1035400114</v>
+      </c>
+      <c r="B446" s="2">
+        <v>103500</v>
+      </c>
+      <c r="C446" s="2">
+        <v>14</v>
+      </c>
+      <c r="D446" s="2">
+        <v>4</v>
+      </c>
+      <c r="F446" s="2">
+        <v>1</v>
+      </c>
+      <c r="G446" s="11">
+        <v>0</v>
+      </c>
+      <c r="H446" s="11">
+        <v>30350001</v>
+      </c>
+      <c r="I446" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" customHeight="1" spans="1:12">
+      <c r="A447" s="3">
+        <f t="shared" ref="A447:A460" si="19">(B447)*10000+C447+F447*100+D447*100000</f>
+        <v>1035110301</v>
+      </c>
+      <c r="B447" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C447" s="2">
+        <v>1</v>
+      </c>
+      <c r="D447" s="2">
+        <v>1</v>
+      </c>
+      <c r="F447" s="2">
+        <v>3</v>
+      </c>
+      <c r="G447" s="11">
+        <v>2</v>
+      </c>
+      <c r="I447" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" customHeight="1" spans="1:12">
+      <c r="A448" s="3">
+        <f t="shared" si="19"/>
+        <v>1035110302</v>
+      </c>
+      <c r="B448" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C448" s="2">
+        <v>2</v>
+      </c>
+      <c r="D448" s="2">
+        <v>1</v>
+      </c>
+      <c r="F448" s="2">
+        <v>3</v>
+      </c>
+      <c r="G448" s="11">
+        <v>3</v>
+      </c>
+      <c r="I448" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" customHeight="1" spans="1:12">
+      <c r="A449" s="3">
+        <f t="shared" si="19"/>
+        <v>1035110303</v>
+      </c>
+      <c r="B449" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C449" s="2">
+        <v>3</v>
+      </c>
+      <c r="D449" s="2">
+        <v>1</v>
+      </c>
+      <c r="F449" s="2">
+        <v>3</v>
+      </c>
+      <c r="G449" s="11">
+        <v>5</v>
+      </c>
+      <c r="I449" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" customHeight="1" spans="1:12">
+      <c r="A450" s="3">
+        <f t="shared" si="19"/>
+        <v>1035110304</v>
+      </c>
+      <c r="B450" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C450" s="2">
+        <v>4</v>
+      </c>
+      <c r="D450" s="2">
+        <v>1</v>
+      </c>
+      <c r="F450" s="2">
+        <v>3</v>
+      </c>
+      <c r="G450" s="11">
+        <v>10</v>
+      </c>
+      <c r="I450" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" customHeight="1" spans="1:12">
+      <c r="A451" s="3">
+        <f t="shared" si="19"/>
+        <v>1035110305</v>
+      </c>
+      <c r="B451" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C451" s="2">
+        <v>5</v>
+      </c>
+      <c r="D451" s="2">
+        <v>1</v>
+      </c>
+      <c r="F451" s="2">
+        <v>3</v>
+      </c>
+      <c r="G451" s="11">
+        <v>50</v>
+      </c>
+      <c r="I451" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" customHeight="1" spans="1:12">
+      <c r="A452" s="3">
+        <f t="shared" si="19"/>
+        <v>1035110306</v>
+      </c>
+      <c r="B452" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C452" s="2">
+        <v>6</v>
+      </c>
+      <c r="D452" s="2">
+        <v>1</v>
+      </c>
+      <c r="F452" s="2">
+        <v>3</v>
+      </c>
+      <c r="G452" s="11">
+        <v>100</v>
+      </c>
+      <c r="I452" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" customHeight="1" spans="1:12">
+      <c r="A453" s="3">
+        <f t="shared" si="19"/>
+        <v>1035110307</v>
+      </c>
+      <c r="B453" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C453" s="2">
+        <v>7</v>
+      </c>
+      <c r="D453" s="2">
+        <v>1</v>
+      </c>
+      <c r="F453" s="2">
+        <v>3</v>
+      </c>
+      <c r="G453" s="11">
+        <v>200</v>
+      </c>
+      <c r="I453" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" customHeight="1" spans="1:12">
+      <c r="A454" s="3">
+        <f t="shared" si="19"/>
+        <v>1035410109</v>
+      </c>
+      <c r="B454" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C454" s="2">
+        <v>9</v>
+      </c>
+      <c r="D454" s="2">
+        <v>4</v>
+      </c>
+      <c r="F454" s="2">
+        <v>1</v>
+      </c>
+      <c r="G454" s="11">
+        <v>0</v>
+      </c>
+      <c r="I454" s="11">
+        <v>0</v>
+      </c>
+      <c r="K454" s="2">
+        <v>103501101</v>
+      </c>
+      <c r="L454" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="455" customHeight="1" spans="1:12">
+      <c r="A455" s="3">
+        <f t="shared" si="19"/>
+        <v>1035410110</v>
+      </c>
+      <c r="B455" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C455" s="2">
+        <v>10</v>
+      </c>
+      <c r="D455" s="2">
+        <v>4</v>
+      </c>
+      <c r="F455" s="2">
+        <v>1</v>
+      </c>
+      <c r="G455" s="11">
+        <v>0</v>
+      </c>
+      <c r="I455" s="11">
+        <v>0</v>
+      </c>
+      <c r="K455" s="2">
+        <v>103501102</v>
+      </c>
+      <c r="L455" s="13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="456" customHeight="1" spans="1:12">
+      <c r="A456" s="3">
+        <f t="shared" si="19"/>
+        <v>1035410111</v>
+      </c>
+      <c r="B456" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C456" s="2">
+        <v>11</v>
+      </c>
+      <c r="D456" s="2">
+        <v>4</v>
+      </c>
+      <c r="F456" s="2">
+        <v>1</v>
+      </c>
+      <c r="G456" s="11">
+        <v>0</v>
+      </c>
+      <c r="I456" s="11">
+        <v>0</v>
+      </c>
+      <c r="K456" s="2">
+        <v>103501103</v>
+      </c>
+      <c r="L456" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="457" customHeight="1" spans="1:12">
+      <c r="A457" s="3">
+        <f t="shared" si="19"/>
+        <v>1035410112</v>
+      </c>
+      <c r="B457" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C457" s="2">
+        <v>12</v>
+      </c>
+      <c r="D457" s="2">
+        <v>4</v>
+      </c>
+      <c r="F457" s="2">
+        <v>1</v>
+      </c>
+      <c r="G457" s="11">
+        <v>0</v>
+      </c>
+      <c r="I457" s="11">
+        <v>0</v>
+      </c>
+      <c r="K457" s="2">
+        <v>103501104</v>
+      </c>
+      <c r="L457" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="458" customHeight="1" spans="1:12">
+      <c r="A458" s="3">
+        <f t="shared" si="19"/>
+        <v>1035410508</v>
+      </c>
+      <c r="B458" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C458" s="2">
+        <v>8</v>
+      </c>
+      <c r="D458" s="2">
+        <v>4</v>
+      </c>
+      <c r="F458" s="2">
+        <v>5</v>
+      </c>
+      <c r="G458" s="11">
+        <v>0</v>
+      </c>
+      <c r="H458" s="11">
+        <v>30350102</v>
+      </c>
+      <c r="I458" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459" customHeight="1" spans="1:12">
+      <c r="A459" s="3">
+        <f t="shared" si="19"/>
+        <v>1035410608</v>
+      </c>
+      <c r="B459" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C459" s="2">
+        <v>8</v>
+      </c>
+      <c r="D459" s="2">
+        <v>4</v>
+      </c>
+      <c r="F459" s="2">
+        <v>6</v>
+      </c>
+      <c r="G459" s="11">
+        <v>0</v>
+      </c>
+      <c r="H459" s="11">
+        <v>30350102</v>
+      </c>
+      <c r="I459" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" customHeight="1" spans="1:12">
+      <c r="A460" s="3">
+        <f t="shared" si="19"/>
+        <v>1035410114</v>
+      </c>
+      <c r="B460" s="2">
+        <v>103501</v>
+      </c>
+      <c r="C460" s="2">
+        <v>14</v>
+      </c>
+      <c r="D460" s="2">
+        <v>4</v>
+      </c>
+      <c r="F460" s="2">
+        <v>1</v>
+      </c>
+      <c r="G460" s="11">
+        <v>0</v>
+      </c>
+      <c r="H460" s="11">
+        <v>30350101</v>
+      </c>
+      <c r="I460" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461" customHeight="1" spans="1:12">
+      <c r="A461" s="3">
+        <f t="shared" ref="A461:A469" si="20">(B461)*10000+C461+F461*100+D461*100000</f>
+        <v>1036100301</v>
+      </c>
+      <c r="B461" s="2">
+        <v>103600</v>
+      </c>
+      <c r="C461" s="2">
+        <v>1</v>
+      </c>
+      <c r="D461" s="2">
+        <v>1</v>
+      </c>
+      <c r="F461" s="2">
+        <v>3</v>
+      </c>
+      <c r="G461" s="11">
+        <v>3</v>
+      </c>
+      <c r="I461" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462" customHeight="1" spans="1:12">
+      <c r="A462" s="3">
+        <f t="shared" si="20"/>
+        <v>1036100302</v>
+      </c>
+      <c r="B462" s="2">
+        <v>103600</v>
+      </c>
+      <c r="C462" s="2">
+        <v>2</v>
+      </c>
+      <c r="D462" s="2">
+        <v>1</v>
+      </c>
+      <c r="F462" s="2">
+        <v>3</v>
+      </c>
+      <c r="G462" s="11">
+        <v>5</v>
+      </c>
+      <c r="I462" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" customHeight="1" spans="1:12">
+      <c r="A463" s="3">
+        <f t="shared" si="20"/>
+        <v>1036100303</v>
+      </c>
+      <c r="B463" s="2">
+        <v>103600</v>
+      </c>
+      <c r="C463" s="2">
+        <v>3</v>
+      </c>
+      <c r="D463" s="2">
+        <v>1</v>
+      </c>
+      <c r="F463" s="2">
+        <v>3</v>
+      </c>
+      <c r="G463" s="11">
+        <v>15</v>
+      </c>
+      <c r="I463" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464" customHeight="1" spans="1:12">
+      <c r="A464" s="3">
+        <f t="shared" si="20"/>
+        <v>1036100304</v>
+      </c>
+      <c r="B464" s="2">
+        <v>103600</v>
+      </c>
+      <c r="C464" s="2">
+        <v>4</v>
+      </c>
+      <c r="D464" s="2">
+        <v>1</v>
+      </c>
+      <c r="F464" s="2">
+        <v>3</v>
+      </c>
+      <c r="G464" s="11">
+        <v>30</v>
+      </c>
+      <c r="I464" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465" customHeight="1" spans="1:12">
+      <c r="A465" s="3">
+        <f t="shared" si="20"/>
+        <v>1036100305</v>
+      </c>
+      <c r="B465" s="2">
+        <v>103600</v>
+      </c>
+      <c r="C465" s="2">
+        <v>5</v>
+      </c>
+      <c r="D465" s="2">
+        <v>1</v>
+      </c>
+      <c r="F465" s="2">
+        <v>3</v>
+      </c>
+      <c r="G465" s="11">
+        <v>50</v>
+      </c>
+      <c r="I465" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" customHeight="1" spans="1:12">
+      <c r="A466" s="3">
+        <f t="shared" si="20"/>
+        <v>1036100306</v>
+      </c>
+      <c r="B466" s="2">
+        <v>103600</v>
+      </c>
+      <c r="C466" s="2">
+        <v>6</v>
+      </c>
+      <c r="D466" s="2">
+        <v>1</v>
+      </c>
+      <c r="F466" s="2">
+        <v>3</v>
+      </c>
+      <c r="G466" s="11">
+        <v>100</v>
+      </c>
+      <c r="I466" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" customHeight="1" spans="1:12">
+      <c r="A467" s="3">
+        <f t="shared" si="20"/>
+        <v>1036100307</v>
+      </c>
+      <c r="B467" s="2">
+        <v>103600</v>
+      </c>
+      <c r="C467" s="2">
+        <v>7</v>
+      </c>
+      <c r="D467" s="2">
+        <v>1</v>
+      </c>
+      <c r="F467" s="2">
+        <v>3</v>
+      </c>
+      <c r="G467" s="11">
+        <v>300</v>
+      </c>
+      <c r="I467" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" customHeight="1" spans="1:12">
+      <c r="A468" s="3">
+        <f t="shared" si="20"/>
+        <v>1036400308</v>
+      </c>
+      <c r="B468" s="2">
+        <v>103600</v>
+      </c>
+      <c r="C468" s="2">
+        <v>8</v>
+      </c>
+      <c r="D468" s="2">
+        <v>4</v>
+      </c>
+      <c r="F468" s="2">
+        <v>3</v>
+      </c>
+      <c r="G468" s="11">
+        <v>0</v>
+      </c>
+      <c r="I468" s="11">
+        <v>0</v>
+      </c>
+      <c r="K468" s="2">
+        <v>103600101</v>
+      </c>
+      <c r="L468" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="469" customHeight="1" spans="1:12">
+      <c r="A469" s="3">
+        <f t="shared" si="20"/>
+        <v>1036400109</v>
+      </c>
+      <c r="B469" s="2">
+        <v>103600</v>
+      </c>
+      <c r="C469" s="2">
+        <v>9</v>
+      </c>
+      <c r="D469" s="2">
+        <v>4</v>
+      </c>
+      <c r="F469" s="2">
+        <v>1</v>
+      </c>
+      <c r="G469" s="11">
+        <v>0</v>
+      </c>
+      <c r="H469" s="11">
+        <v>30360001</v>
+      </c>
+      <c r="I469" s="11">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L387" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L469" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="0" priority="134">
+    <cfRule type="expression" dxfId="0" priority="136">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D85:E85">
-    <cfRule type="expression" dxfId="0" priority="160">
+    <cfRule type="expression" dxfId="0" priority="162">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D86:E86">
-    <cfRule type="expression" dxfId="0" priority="125">
+    <cfRule type="expression" dxfId="0" priority="127">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105">
-    <cfRule type="duplicateValues" dxfId="1" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105:E105">
-    <cfRule type="expression" dxfId="0" priority="105">
+    <cfRule type="expression" dxfId="0" priority="107">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I105">
-    <cfRule type="expression" dxfId="0" priority="107">
+    <cfRule type="expression" dxfId="0" priority="109">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A106">
-    <cfRule type="duplicateValues" dxfId="1" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D106:E106">
-    <cfRule type="expression" dxfId="0" priority="101">
+    <cfRule type="expression" dxfId="0" priority="103">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I106">
-    <cfRule type="expression" dxfId="0" priority="103">
+    <cfRule type="expression" dxfId="0" priority="105">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="1" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D107:E107">
-    <cfRule type="expression" dxfId="0" priority="97">
+    <cfRule type="expression" dxfId="0" priority="99">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I107">
-    <cfRule type="expression" dxfId="0" priority="99">
+    <cfRule type="expression" dxfId="0" priority="101">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108">
-    <cfRule type="duplicateValues" dxfId="1" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D108:E108">
-    <cfRule type="expression" dxfId="0" priority="93">
+    <cfRule type="expression" dxfId="0" priority="95">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I108">
-    <cfRule type="expression" dxfId="0" priority="95">
+    <cfRule type="expression" dxfId="0" priority="97">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" dxfId="1" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D109:E109">
-    <cfRule type="expression" dxfId="0" priority="89">
+    <cfRule type="expression" dxfId="0" priority="91">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I109">
-    <cfRule type="expression" dxfId="0" priority="91">
+    <cfRule type="expression" dxfId="0" priority="93">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110">
-    <cfRule type="duplicateValues" dxfId="1" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D110:E110">
-    <cfRule type="expression" dxfId="0" priority="85">
+    <cfRule type="expression" dxfId="0" priority="87">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I110">
-    <cfRule type="expression" dxfId="0" priority="87">
+    <cfRule type="expression" dxfId="0" priority="89">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A111">
-    <cfRule type="duplicateValues" dxfId="1" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D111:E111">
-    <cfRule type="expression" dxfId="0" priority="81">
+    <cfRule type="expression" dxfId="0" priority="83">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I111">
-    <cfRule type="expression" dxfId="0" priority="83">
+    <cfRule type="expression" dxfId="0" priority="85">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112">
-    <cfRule type="duplicateValues" dxfId="1" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D112:E112">
-    <cfRule type="expression" dxfId="0" priority="77">
+    <cfRule type="expression" dxfId="0" priority="79">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I112">
-    <cfRule type="expression" dxfId="0" priority="79">
+    <cfRule type="expression" dxfId="0" priority="81">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A113">
-    <cfRule type="duplicateValues" dxfId="1" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D113:E113">
-    <cfRule type="expression" dxfId="0" priority="73">
+    <cfRule type="expression" dxfId="0" priority="75">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I113">
-    <cfRule type="expression" dxfId="0" priority="75">
+    <cfRule type="expression" dxfId="0" priority="77">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114">
-    <cfRule type="duplicateValues" dxfId="1" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D114:E114">
-    <cfRule type="expression" dxfId="0" priority="69">
+    <cfRule type="expression" dxfId="0" priority="71">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I114">
-    <cfRule type="expression" dxfId="0" priority="71">
+    <cfRule type="expression" dxfId="0" priority="73">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A115">
-    <cfRule type="duplicateValues" dxfId="1" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D115:E115">
-    <cfRule type="expression" dxfId="0" priority="65">
+    <cfRule type="expression" dxfId="0" priority="67">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I115">
-    <cfRule type="expression" dxfId="0" priority="67">
+    <cfRule type="expression" dxfId="0" priority="69">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A116">
-    <cfRule type="duplicateValues" dxfId="1" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D116:E116">
-    <cfRule type="expression" dxfId="0" priority="61">
+    <cfRule type="expression" dxfId="0" priority="63">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I116">
-    <cfRule type="expression" dxfId="0" priority="63">
+    <cfRule type="expression" dxfId="0" priority="65">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117">
-    <cfRule type="duplicateValues" dxfId="1" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D117:E117">
-    <cfRule type="expression" dxfId="0" priority="57">
+    <cfRule type="expression" dxfId="0" priority="59">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I117">
-    <cfRule type="expression" dxfId="0" priority="59">
+    <cfRule type="expression" dxfId="0" priority="61">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A118">
-    <cfRule type="duplicateValues" dxfId="1" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D118:E118">
-    <cfRule type="expression" dxfId="0" priority="53">
+    <cfRule type="expression" dxfId="0" priority="55">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I118">
-    <cfRule type="expression" dxfId="0" priority="55">
+    <cfRule type="expression" dxfId="0" priority="57">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A119">
-    <cfRule type="duplicateValues" dxfId="1" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D119:E119">
-    <cfRule type="expression" dxfId="0" priority="49">
+    <cfRule type="expression" dxfId="0" priority="51">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I119">
-    <cfRule type="expression" dxfId="0" priority="51">
+    <cfRule type="expression" dxfId="0" priority="53">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A120">
-    <cfRule type="duplicateValues" dxfId="1" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D120:E120">
-    <cfRule type="expression" dxfId="0" priority="45">
+    <cfRule type="expression" dxfId="0" priority="47">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I120">
-    <cfRule type="expression" dxfId="0" priority="47">
+    <cfRule type="expression" dxfId="0" priority="49">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A121">
-    <cfRule type="duplicateValues" dxfId="1" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D121:E121">
-    <cfRule type="expression" dxfId="0" priority="41">
+    <cfRule type="expression" dxfId="0" priority="43">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I121">
-    <cfRule type="expression" dxfId="0" priority="43">
+    <cfRule type="expression" dxfId="0" priority="45">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A122">
-    <cfRule type="duplicateValues" dxfId="1" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D122:E122">
-    <cfRule type="expression" dxfId="0" priority="37">
+    <cfRule type="expression" dxfId="0" priority="39">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I122">
-    <cfRule type="expression" dxfId="0" priority="39">
+    <cfRule type="expression" dxfId="0" priority="41">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A123">
-    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D123:E123">
-    <cfRule type="expression" dxfId="0" priority="33">
+    <cfRule type="expression" dxfId="0" priority="35">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I123">
-    <cfRule type="expression" dxfId="0" priority="35">
+    <cfRule type="expression" dxfId="0" priority="37">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C134:L134">
-    <cfRule type="expression" dxfId="0" priority="161">
+    <cfRule type="expression" dxfId="0" priority="163">
       <formula>MOD($B134,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B173">
-    <cfRule type="expression" dxfId="0" priority="25">
+    <cfRule type="expression" dxfId="0" priority="27">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A178">
-    <cfRule type="duplicateValues" dxfId="1" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B178">
+    <cfRule type="expression" dxfId="0" priority="23">
+      <formula>MOD($B178,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D178:E178">
     <cfRule type="expression" dxfId="0" priority="21">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D178:E178">
-    <cfRule type="expression" dxfId="0" priority="19">
-      <formula>MOD($B178,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H309">
-    <cfRule type="expression" dxfId="0" priority="439">
+    <cfRule type="expression" dxfId="0" priority="441">
       <formula>MOD($B308,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H321">
-    <cfRule type="expression" dxfId="0" priority="438">
+    <cfRule type="expression" dxfId="0" priority="440">
       <formula>MOD($B320,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="L346">
+    <cfRule type="expression" dxfId="0" priority="442">
+      <formula>MOD($B350,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A48:A60">
-    <cfRule type="duplicateValues" dxfId="1" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A87:A92">
-    <cfRule type="duplicateValues" dxfId="1" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A93:A98">
-    <cfRule type="duplicateValues" dxfId="1" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99:A104">
-    <cfRule type="duplicateValues" dxfId="1" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A135:A177">
-    <cfRule type="duplicateValues" dxfId="1" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A209:A425">
-    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
+  <conditionalFormatting sqref="A209:A469">
+    <cfRule type="duplicateValues" dxfId="1" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B60">
-    <cfRule type="expression" dxfId="0" priority="120">
+    <cfRule type="expression" dxfId="0" priority="122">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C84">
-    <cfRule type="expression" dxfId="0" priority="123">
+    <cfRule type="expression" dxfId="0" priority="125">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C271:C281">
-    <cfRule type="expression" dxfId="0" priority="12">
+    <cfRule type="expression" dxfId="0" priority="14">
       <formula>MOD($B271,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C282:C296">
-    <cfRule type="expression" dxfId="0" priority="10">
+    <cfRule type="expression" dxfId="0" priority="12">
       <formula>MOD($B282,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E93:E98">
-    <cfRule type="expression" dxfId="0" priority="112">
+    <cfRule type="expression" dxfId="0" priority="114">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E99:E104">
-    <cfRule type="expression" dxfId="0" priority="109">
+    <cfRule type="expression" dxfId="0" priority="111">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E257:E268">
-    <cfRule type="expression" dxfId="0" priority="13">
+    <cfRule type="expression" dxfId="0" priority="15">
       <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E271:E279">
-    <cfRule type="expression" dxfId="0" priority="11">
+    <cfRule type="expression" dxfId="0" priority="13">
       <formula>MOD($B271,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E282:E290">
-    <cfRule type="expression" dxfId="0" priority="9">
+    <cfRule type="expression" dxfId="0" priority="11">
       <formula>MOD($B282,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39:K42">
-    <cfRule type="duplicateValues" dxfId="2" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K169:K172">
-    <cfRule type="duplicateValues" dxfId="2" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K293:K296">
-    <cfRule type="expression" dxfId="0" priority="7">
+    <cfRule type="expression" dxfId="0" priority="9">
       <formula>MOD($B293,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K346:K349">
-    <cfRule type="expression" dxfId="0" priority="5">
+  <conditionalFormatting sqref="K347:K350">
+    <cfRule type="expression" dxfId="0" priority="7">
       <formula>MOD($B346,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K384:K387">
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="0" priority="5">
       <formula>MOD($B384,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K422:K425">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>MOD($B422,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L205:L208">
-    <cfRule type="expression" dxfId="0" priority="18">
+    <cfRule type="expression" dxfId="0" priority="20">
       <formula>MOD($B205,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L293:L296">
-    <cfRule type="expression" dxfId="0" priority="8">
+    <cfRule type="expression" dxfId="0" priority="10">
       <formula>MOD($B293,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L346:L349">
-    <cfRule type="expression" dxfId="0" priority="6">
+  <conditionalFormatting sqref="L347:L350">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>MOD($B346,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L384:L387">
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="0" priority="6">
       <formula>MOD($B384,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L422:L425">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>MOD($B422,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A426:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="435"/>
+  <conditionalFormatting sqref="L440:L446">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>MOD($B440,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L454:L457">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD($B454,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A470:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="437"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L4">
-    <cfRule type="expression" dxfId="0" priority="434">
+    <cfRule type="expression" dxfId="0" priority="436">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41:B42 B44:B47">
-    <cfRule type="expression" dxfId="0" priority="168">
+    <cfRule type="expression" dxfId="0" priority="170">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45:F47 C46:C47 B61:L76 D77:E84 H179:L204 B179:G208 I205:K208 I209:I256 B259:D268 F259:L268 B269:L270 B271:B296 D271:D279 F271:L279 D280:L281 D282:D290 F282:L290 D291:L292 D293:J296 H297:L307 H310:L319 I320:L321 B322:L345 B297:G321 B258 B346:J349 B350:L383 B384:J387 B388:L421 B422:J425 B426:L1048576 I308:L309">
-    <cfRule type="expression" dxfId="0" priority="433">
+  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45 C46:C47 F46:F47 B61:L76 D77:E84 B179:L204 B205:G205 I205:K205 B206:G208 I206:K208 I209:I256 B258 B259:D268 F259:L268 B269:L270 B271:B279 D271:D279 F271:L279 B280:B281 D280:L281 B282:B290 D282:D290 F282:L290 B291:B292 D291:L292 B293:B296 D293:J296 B297:L307 B308:G309 I308:L309 B310:L319 B320:G321 I320:L321 B322:L343 B344:K344 B345:L345 B346:J350 B351:L383 B384:J387 B388:L421 B422:J425 B426:L439 B440:K446 B447:L453 B454:K457 B458:L1048576">
+    <cfRule type="expression" dxfId="0" priority="435">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43:G43 J43:L43">
-    <cfRule type="expression" dxfId="0" priority="133">
+    <cfRule type="expression" dxfId="0" priority="135">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44:G44 J44:L47 G45:G47 C45:C47">
-    <cfRule type="expression" dxfId="0" priority="167">
+    <cfRule type="expression" dxfId="0" priority="169">
       <formula>MOD($B44,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45:E47">
-    <cfRule type="expression" dxfId="0" priority="164">
+    <cfRule type="expression" dxfId="0" priority="166">
       <formula>MOD($B45,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F60 C48:C60">
+    <cfRule type="expression" dxfId="0" priority="123">
+      <formula>MOD($B48,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
     <cfRule type="expression" dxfId="0" priority="121">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J48:L60 G48:G60 C48:C60">
+  <conditionalFormatting sqref="D48:E60">
     <cfRule type="expression" dxfId="0" priority="119">
       <formula>MOD($B48,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D48:E60">
-    <cfRule type="expression" dxfId="0" priority="117">
-      <formula>MOD($B48,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B77:B84 F77:L84">
-    <cfRule type="expression" dxfId="0" priority="163">
+    <cfRule type="expression" dxfId="0" priority="165">
       <formula>MOD($B77,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85:C85 F85:L85">
-    <cfRule type="expression" dxfId="0" priority="159">
+    <cfRule type="expression" dxfId="0" priority="161">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B86:C86 F86:L86">
-    <cfRule type="expression" dxfId="0" priority="124">
+    <cfRule type="expression" dxfId="0" priority="126">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87:C92 F87:L92 I93:I104">
-    <cfRule type="expression" dxfId="0" priority="114">
+    <cfRule type="expression" dxfId="0" priority="116">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87:E92 D93:D104">
-    <cfRule type="expression" dxfId="0" priority="115">
+    <cfRule type="expression" dxfId="0" priority="117">
       <formula>MOD($B87,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:C98 F93:H98 J93:L98">
-    <cfRule type="expression" dxfId="0" priority="111">
+    <cfRule type="expression" dxfId="0" priority="113">
       <formula>MOD($B93,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99:C104 F99:H104 J99:L104">
-    <cfRule type="expression" dxfId="0" priority="108">
+    <cfRule type="expression" dxfId="0" priority="110">
       <formula>MOD($B99,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:C105 F105:H105 J105:L105">
-    <cfRule type="expression" dxfId="0" priority="104">
+    <cfRule type="expression" dxfId="0" priority="106">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106:C106 F106:H106 J106:L106 H107:H111 C107:C111">
-    <cfRule type="expression" dxfId="0" priority="100">
+    <cfRule type="expression" dxfId="0" priority="102">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107 F107:G107 J107:L107">
-    <cfRule type="expression" dxfId="0" priority="96">
+    <cfRule type="expression" dxfId="0" priority="98">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B108 F108:G108 J108:L108">
-    <cfRule type="expression" dxfId="0" priority="92">
+    <cfRule type="expression" dxfId="0" priority="94">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B109 F109:G109 J109:L109">
-    <cfRule type="expression" dxfId="0" priority="88">
+    <cfRule type="expression" dxfId="0" priority="90">
       <formula>MOD($B109,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B110 F110:G110 J110:L110">
-    <cfRule type="expression" dxfId="0" priority="84">
+    <cfRule type="expression" dxfId="0" priority="86">
       <formula>MOD($B110,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111 F111:G111 J111:L111">
-    <cfRule type="expression" dxfId="0" priority="80">
+    <cfRule type="expression" dxfId="0" priority="82">
       <formula>MOD($B111,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112:C112 F112:H112 J112:L112 H113:H117 C113:C117">
-    <cfRule type="expression" dxfId="0" priority="76">
+    <cfRule type="expression" dxfId="0" priority="78">
       <formula>MOD($B112,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113 F113:G113 J113:L113">
-    <cfRule type="expression" dxfId="0" priority="72">
+    <cfRule type="expression" dxfId="0" priority="74">
       <formula>MOD($B113,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114 F114:G114 J114:L114">
-    <cfRule type="expression" dxfId="0" priority="68">
+    <cfRule type="expression" dxfId="0" priority="70">
       <formula>MOD($B114,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115 F115:G115 J115:L115">
-    <cfRule type="expression" dxfId="0" priority="64">
+    <cfRule type="expression" dxfId="0" priority="66">
       <formula>MOD($B115,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B116 F116:G116 J116:L116">
-    <cfRule type="expression" dxfId="0" priority="60">
+    <cfRule type="expression" dxfId="0" priority="62">
       <formula>MOD($B116,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117 F117:G117 J117:L117">
-    <cfRule type="expression" dxfId="0" priority="56">
+    <cfRule type="expression" dxfId="0" priority="58">
       <formula>MOD($B117,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118:C118 F118:H118 J118:L118 H119:H123 C119:C123">
-    <cfRule type="expression" dxfId="0" priority="52">
+    <cfRule type="expression" dxfId="0" priority="54">
       <formula>MOD($B118,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119 F119:G119 J119:L119">
-    <cfRule type="expression" dxfId="0" priority="48">
+    <cfRule type="expression" dxfId="0" priority="50">
       <formula>MOD($B119,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120 F120:G120 J120:L120">
-    <cfRule type="expression" dxfId="0" priority="44">
+    <cfRule type="expression" dxfId="0" priority="46">
       <formula>MOD($B120,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121 F121:G121 J121:L121">
-    <cfRule type="expression" dxfId="0" priority="40">
+    <cfRule type="expression" dxfId="0" priority="42">
       <formula>MOD($B121,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122 F122:G122 J122:L122">
-    <cfRule type="expression" dxfId="0" priority="36">
+    <cfRule type="expression" dxfId="0" priority="38">
       <formula>MOD($B122,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123 F123:G123 J123:L123">
-    <cfRule type="expression" dxfId="0" priority="32">
+    <cfRule type="expression" dxfId="0" priority="34">
       <formula>MOD($B123,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B124:L133 B134">
-    <cfRule type="expression" dxfId="0" priority="162">
+    <cfRule type="expression" dxfId="0" priority="164">
       <formula>MOD($B124,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171:B172 B174:B177">
-    <cfRule type="expression" dxfId="0" priority="29">
+    <cfRule type="expression" dxfId="0" priority="31">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C171:G172 J171:J172 L171:L172 F175:F177 C176:C177">
-    <cfRule type="expression" dxfId="0" priority="30">
+    <cfRule type="expression" dxfId="0" priority="32">
       <formula>MOD($B171,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C173:G173 J173:L173">
-    <cfRule type="expression" dxfId="0" priority="24">
+    <cfRule type="expression" dxfId="0" priority="26">
       <formula>MOD($B173,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174:G174 J174:L177 G175:G177 C175:C177">
-    <cfRule type="expression" dxfId="0" priority="28">
+    <cfRule type="expression" dxfId="0" priority="30">
       <formula>MOD($B174,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D175:E177">
-    <cfRule type="expression" dxfId="0" priority="27">
+    <cfRule type="expression" dxfId="0" priority="29">
       <formula>MOD($B175,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F178 C178">
+    <cfRule type="expression" dxfId="0" priority="24">
+      <formula>MOD($B178,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J178:L178 G178 C178">
     <cfRule type="expression" dxfId="0" priority="22">
       <formula>MOD($B178,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J178:L178 G178 C178">
-    <cfRule type="expression" dxfId="0" priority="20">
-      <formula>MOD($B178,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B209:D209 F209:H209 J209:L250 B210:H250">
-    <cfRule type="expression" dxfId="0" priority="17">
+    <cfRule type="expression" dxfId="0" priority="19">
       <formula>MOD($B209,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B251:H256 J251:L256">
-    <cfRule type="expression" dxfId="0" priority="16">
+    <cfRule type="expression" dxfId="0" priority="18">
       <formula>MOD($B251,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B257 B259 B261 B263 B265 B267 B269 B271 B273 B275 B277 B279 B281 B283 B285 B287 B289 B291 B293 B295">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="0" priority="16">
       <formula>MOD($B257,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C257:D257 F257:L257">
-    <cfRule type="expression" dxfId="0" priority="437">
+    <cfRule type="expression" dxfId="0" priority="439">
       <formula>MOD($B258,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C258:D258 I292 I290 I288 I286 I284 I282 I280 I278 I276 I274 I272 I270 I268 I266 I264 I262 I260 D268 D266 D264 D262 D260 F258:L258">
-    <cfRule type="expression" dxfId="0" priority="436">
+    <cfRule type="expression" dxfId="0" priority="438">
       <formula>MOD(#REF!,2)=1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$731</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$797</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="109">
   <si>
     <t>id</t>
   </si>
@@ -631,6 +631,12 @@
   <si>
     <t>用于触发扩列</t>
   </si>
+  <si>
+    <t>免费游戏</t>
+  </si>
+  <si>
+    <t>转轴上出现符号5时在随机位置上改出1个wild</t>
+  </si>
 </sst>
 </file>
 
@@ -880,12 +886,6 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -896,6 +896,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -6008,7 +6014,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L731"/>
+  <dimension ref="A1:L798"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="11"/>
@@ -25403,8 +25409,1493 @@
         <v>30310002</v>
       </c>
     </row>
+    <row r="732" customHeight="1" spans="1:12">
+      <c r="A732" s="3">
+        <f t="shared" ref="A732:A766" si="30">(B732)*10000+C732+F732*100+D732*100000</f>
+        <v>1040100301</v>
+      </c>
+      <c r="B732" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C732" s="2">
+        <v>1</v>
+      </c>
+      <c r="D732" s="2">
+        <v>1</v>
+      </c>
+      <c r="F732" s="2">
+        <v>3</v>
+      </c>
+      <c r="G732" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="733" customHeight="1" spans="1:12">
+      <c r="A733" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100302</v>
+      </c>
+      <c r="B733" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C733" s="2">
+        <v>2</v>
+      </c>
+      <c r="D733" s="2">
+        <v>1</v>
+      </c>
+      <c r="F733" s="2">
+        <v>3</v>
+      </c>
+      <c r="G733" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="734" customHeight="1" spans="1:12">
+      <c r="A734" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100303</v>
+      </c>
+      <c r="B734" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C734" s="2">
+        <v>3</v>
+      </c>
+      <c r="D734" s="2">
+        <v>1</v>
+      </c>
+      <c r="F734" s="2">
+        <v>3</v>
+      </c>
+      <c r="G734" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="735" customHeight="1" spans="1:12">
+      <c r="A735" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100304</v>
+      </c>
+      <c r="B735" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C735" s="2">
+        <v>4</v>
+      </c>
+      <c r="D735" s="2">
+        <v>1</v>
+      </c>
+      <c r="F735" s="2">
+        <v>3</v>
+      </c>
+      <c r="G735" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="736" customHeight="1" spans="1:12">
+      <c r="A736" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100305</v>
+      </c>
+      <c r="B736" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C736" s="2">
+        <v>5</v>
+      </c>
+      <c r="D736" s="2">
+        <v>1</v>
+      </c>
+      <c r="F736" s="2">
+        <v>3</v>
+      </c>
+      <c r="G736" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="737" customHeight="1" spans="1:7">
+      <c r="A737" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100306</v>
+      </c>
+      <c r="B737" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C737" s="2">
+        <v>6</v>
+      </c>
+      <c r="D737" s="2">
+        <v>1</v>
+      </c>
+      <c r="F737" s="2">
+        <v>3</v>
+      </c>
+      <c r="G737" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="738" customHeight="1" spans="1:7">
+      <c r="A738" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100307</v>
+      </c>
+      <c r="B738" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C738" s="2">
+        <v>7</v>
+      </c>
+      <c r="D738" s="2">
+        <v>1</v>
+      </c>
+      <c r="F738" s="2">
+        <v>3</v>
+      </c>
+      <c r="G738" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="739" customHeight="1" spans="1:7">
+      <c r="A739" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100308</v>
+      </c>
+      <c r="B739" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C739" s="2">
+        <v>8</v>
+      </c>
+      <c r="D739" s="2">
+        <v>1</v>
+      </c>
+      <c r="F739" s="2">
+        <v>3</v>
+      </c>
+      <c r="G739" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="740" customHeight="1" spans="1:7">
+      <c r="A740" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100309</v>
+      </c>
+      <c r="B740" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C740" s="2">
+        <v>9</v>
+      </c>
+      <c r="D740" s="2">
+        <v>1</v>
+      </c>
+      <c r="F740" s="2">
+        <v>3</v>
+      </c>
+      <c r="G740" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="741" customHeight="1" spans="1:7">
+      <c r="A741" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100310</v>
+      </c>
+      <c r="B741" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C741" s="2">
+        <v>10</v>
+      </c>
+      <c r="D741" s="2">
+        <v>1</v>
+      </c>
+      <c r="F741" s="2">
+        <v>3</v>
+      </c>
+      <c r="G741" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="742" customHeight="1" spans="1:7">
+      <c r="A742" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100401</v>
+      </c>
+      <c r="B742" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C742" s="2">
+        <v>1</v>
+      </c>
+      <c r="D742" s="2">
+        <v>1</v>
+      </c>
+      <c r="F742" s="2">
+        <v>4</v>
+      </c>
+      <c r="G742" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="743" customHeight="1" spans="1:7">
+      <c r="A743" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100402</v>
+      </c>
+      <c r="B743" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C743" s="2">
+        <v>2</v>
+      </c>
+      <c r="D743" s="2">
+        <v>1</v>
+      </c>
+      <c r="F743" s="2">
+        <v>4</v>
+      </c>
+      <c r="G743" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="744" customHeight="1" spans="1:7">
+      <c r="A744" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100403</v>
+      </c>
+      <c r="B744" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C744" s="2">
+        <v>3</v>
+      </c>
+      <c r="D744" s="2">
+        <v>1</v>
+      </c>
+      <c r="F744" s="2">
+        <v>4</v>
+      </c>
+      <c r="G744" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="745" customHeight="1" spans="1:7">
+      <c r="A745" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100404</v>
+      </c>
+      <c r="B745" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C745" s="2">
+        <v>4</v>
+      </c>
+      <c r="D745" s="2">
+        <v>1</v>
+      </c>
+      <c r="F745" s="2">
+        <v>4</v>
+      </c>
+      <c r="G745" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="746" customHeight="1" spans="1:7">
+      <c r="A746" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100405</v>
+      </c>
+      <c r="B746" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C746" s="2">
+        <v>5</v>
+      </c>
+      <c r="D746" s="2">
+        <v>1</v>
+      </c>
+      <c r="F746" s="2">
+        <v>4</v>
+      </c>
+      <c r="G746" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="747" customHeight="1" spans="1:7">
+      <c r="A747" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100406</v>
+      </c>
+      <c r="B747" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C747" s="2">
+        <v>6</v>
+      </c>
+      <c r="D747" s="2">
+        <v>1</v>
+      </c>
+      <c r="F747" s="2">
+        <v>4</v>
+      </c>
+      <c r="G747" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="748" customHeight="1" spans="1:7">
+      <c r="A748" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100407</v>
+      </c>
+      <c r="B748" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C748" s="2">
+        <v>7</v>
+      </c>
+      <c r="D748" s="2">
+        <v>1</v>
+      </c>
+      <c r="F748" s="2">
+        <v>4</v>
+      </c>
+      <c r="G748" s="12">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="749" customHeight="1" spans="1:7">
+      <c r="A749" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100408</v>
+      </c>
+      <c r="B749" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C749" s="2">
+        <v>8</v>
+      </c>
+      <c r="D749" s="2">
+        <v>1</v>
+      </c>
+      <c r="F749" s="2">
+        <v>4</v>
+      </c>
+      <c r="G749" s="12">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="750" customHeight="1" spans="1:7">
+      <c r="A750" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100409</v>
+      </c>
+      <c r="B750" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C750" s="2">
+        <v>9</v>
+      </c>
+      <c r="D750" s="2">
+        <v>1</v>
+      </c>
+      <c r="F750" s="2">
+        <v>4</v>
+      </c>
+      <c r="G750" s="12">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="751" customHeight="1" spans="1:7">
+      <c r="A751" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100410</v>
+      </c>
+      <c r="B751" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C751" s="2">
+        <v>10</v>
+      </c>
+      <c r="D751" s="2">
+        <v>1</v>
+      </c>
+      <c r="F751" s="2">
+        <v>4</v>
+      </c>
+      <c r="G751" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="752" customHeight="1" spans="1:7">
+      <c r="A752" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100501</v>
+      </c>
+      <c r="B752" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C752" s="2">
+        <v>1</v>
+      </c>
+      <c r="D752" s="2">
+        <v>1</v>
+      </c>
+      <c r="F752" s="2">
+        <v>5</v>
+      </c>
+      <c r="G752" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="753" customHeight="1" spans="1:12">
+      <c r="A753" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100502</v>
+      </c>
+      <c r="B753" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C753" s="2">
+        <v>2</v>
+      </c>
+      <c r="D753" s="2">
+        <v>1</v>
+      </c>
+      <c r="F753" s="2">
+        <v>5</v>
+      </c>
+      <c r="G753" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="754" customHeight="1" spans="1:12">
+      <c r="A754" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100503</v>
+      </c>
+      <c r="B754" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C754" s="2">
+        <v>3</v>
+      </c>
+      <c r="D754" s="2">
+        <v>1</v>
+      </c>
+      <c r="F754" s="2">
+        <v>5</v>
+      </c>
+      <c r="G754" s="12">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="755" customHeight="1" spans="1:12">
+      <c r="A755" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100504</v>
+      </c>
+      <c r="B755" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C755" s="2">
+        <v>4</v>
+      </c>
+      <c r="D755" s="2">
+        <v>1</v>
+      </c>
+      <c r="F755" s="2">
+        <v>5</v>
+      </c>
+      <c r="G755" s="12">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="756" customHeight="1" spans="1:12">
+      <c r="A756" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100505</v>
+      </c>
+      <c r="B756" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C756" s="2">
+        <v>5</v>
+      </c>
+      <c r="D756" s="2">
+        <v>1</v>
+      </c>
+      <c r="F756" s="2">
+        <v>5</v>
+      </c>
+      <c r="G756" s="12">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="757" customHeight="1" spans="1:12">
+      <c r="A757" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100506</v>
+      </c>
+      <c r="B757" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C757" s="2">
+        <v>6</v>
+      </c>
+      <c r="D757" s="2">
+        <v>1</v>
+      </c>
+      <c r="F757" s="2">
+        <v>5</v>
+      </c>
+      <c r="G757" s="12">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="758" customHeight="1" spans="1:12">
+      <c r="A758" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100507</v>
+      </c>
+      <c r="B758" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C758" s="2">
+        <v>7</v>
+      </c>
+      <c r="D758" s="2">
+        <v>1</v>
+      </c>
+      <c r="F758" s="2">
+        <v>5</v>
+      </c>
+      <c r="G758" s="12">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="759" customHeight="1" spans="1:12">
+      <c r="A759" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100508</v>
+      </c>
+      <c r="B759" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C759" s="2">
+        <v>8</v>
+      </c>
+      <c r="D759" s="2">
+        <v>1</v>
+      </c>
+      <c r="F759" s="2">
+        <v>5</v>
+      </c>
+      <c r="G759" s="12">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="760" customHeight="1" spans="1:12">
+      <c r="A760" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100509</v>
+      </c>
+      <c r="B760" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C760" s="2">
+        <v>9</v>
+      </c>
+      <c r="D760" s="2">
+        <v>1</v>
+      </c>
+      <c r="F760" s="2">
+        <v>5</v>
+      </c>
+      <c r="G760" s="12">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="761" customHeight="1" spans="1:12">
+      <c r="A761" s="3">
+        <f t="shared" si="30"/>
+        <v>1040100510</v>
+      </c>
+      <c r="B761" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C761" s="2">
+        <v>10</v>
+      </c>
+      <c r="D761" s="2">
+        <v>1</v>
+      </c>
+      <c r="F761" s="2">
+        <v>5</v>
+      </c>
+      <c r="G761" s="12">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="762" customHeight="1" spans="1:12">
+      <c r="A762" s="3">
+        <f t="shared" si="30"/>
+        <v>1040400312</v>
+      </c>
+      <c r="B762" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C762" s="2">
+        <v>12</v>
+      </c>
+      <c r="D762" s="2">
+        <v>4</v>
+      </c>
+      <c r="E762" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F762" s="2">
+        <v>3</v>
+      </c>
+      <c r="G762" s="12">
+        <v>0</v>
+      </c>
+      <c r="H762" s="12">
+        <v>30400001</v>
+      </c>
+    </row>
+    <row r="763" customHeight="1" spans="1:12">
+      <c r="A763" s="3">
+        <f t="shared" si="30"/>
+        <v>1040400113</v>
+      </c>
+      <c r="B763" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C763" s="2">
+        <v>13</v>
+      </c>
+      <c r="D763" s="2">
+        <v>4</v>
+      </c>
+      <c r="F763" s="2">
+        <v>1</v>
+      </c>
+      <c r="G763" s="12">
+        <v>0</v>
+      </c>
+      <c r="K763" s="2">
+        <v>104000101</v>
+      </c>
+      <c r="L763" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="764" customHeight="1" spans="1:12">
+      <c r="A764" s="3">
+        <f t="shared" si="30"/>
+        <v>1040400114</v>
+      </c>
+      <c r="B764" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C764" s="2">
+        <v>14</v>
+      </c>
+      <c r="D764" s="2">
+        <v>4</v>
+      </c>
+      <c r="F764" s="2">
+        <v>1</v>
+      </c>
+      <c r="G764" s="12">
+        <v>0</v>
+      </c>
+      <c r="K764" s="2">
+        <v>104000102</v>
+      </c>
+      <c r="L764" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="765" customHeight="1" spans="1:12">
+      <c r="A765" s="3">
+        <f t="shared" si="30"/>
+        <v>1040400115</v>
+      </c>
+      <c r="B765" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C765" s="2">
+        <v>15</v>
+      </c>
+      <c r="D765" s="2">
+        <v>4</v>
+      </c>
+      <c r="F765" s="2">
+        <v>1</v>
+      </c>
+      <c r="G765" s="12">
+        <v>0</v>
+      </c>
+      <c r="K765" s="2">
+        <v>104000103</v>
+      </c>
+      <c r="L765" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="766" customHeight="1" spans="1:12">
+      <c r="A766" s="3">
+        <f t="shared" si="30"/>
+        <v>1040400116</v>
+      </c>
+      <c r="B766" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C766" s="2">
+        <v>16</v>
+      </c>
+      <c r="D766" s="2">
+        <v>4</v>
+      </c>
+      <c r="F766" s="2">
+        <v>1</v>
+      </c>
+      <c r="G766" s="12">
+        <v>0</v>
+      </c>
+      <c r="K766" s="2">
+        <v>104000104</v>
+      </c>
+      <c r="L766" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="767" customHeight="1" spans="1:12">
+      <c r="A767" s="3">
+        <f t="shared" ref="A767:A797" si="31">(B767)*10000+C767+F767*100+D767*100000</f>
+        <v>1039100301</v>
+      </c>
+      <c r="B767" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C767" s="2">
+        <v>1</v>
+      </c>
+      <c r="D767" s="2">
+        <v>1</v>
+      </c>
+      <c r="F767" s="2">
+        <v>3</v>
+      </c>
+      <c r="G767" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="768" customHeight="1" spans="1:12">
+      <c r="A768" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100302</v>
+      </c>
+      <c r="B768" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C768" s="2">
+        <v>2</v>
+      </c>
+      <c r="D768" s="2">
+        <v>1</v>
+      </c>
+      <c r="F768" s="2">
+        <v>3</v>
+      </c>
+      <c r="G768" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="769" customHeight="1" spans="1:7">
+      <c r="A769" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100303</v>
+      </c>
+      <c r="B769" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C769" s="2">
+        <v>3</v>
+      </c>
+      <c r="D769" s="2">
+        <v>1</v>
+      </c>
+      <c r="F769" s="2">
+        <v>3</v>
+      </c>
+      <c r="G769" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="770" customHeight="1" spans="1:7">
+      <c r="A770" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100304</v>
+      </c>
+      <c r="B770" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C770" s="2">
+        <v>4</v>
+      </c>
+      <c r="D770" s="2">
+        <v>1</v>
+      </c>
+      <c r="F770" s="2">
+        <v>3</v>
+      </c>
+      <c r="G770" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="771" customHeight="1" spans="1:7">
+      <c r="A771" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100305</v>
+      </c>
+      <c r="B771" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C771" s="2">
+        <v>5</v>
+      </c>
+      <c r="D771" s="2">
+        <v>1</v>
+      </c>
+      <c r="F771" s="2">
+        <v>3</v>
+      </c>
+      <c r="G771" s="12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="772" customHeight="1" spans="1:7">
+      <c r="A772" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100306</v>
+      </c>
+      <c r="B772" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C772" s="2">
+        <v>6</v>
+      </c>
+      <c r="D772" s="2">
+        <v>1</v>
+      </c>
+      <c r="F772" s="2">
+        <v>3</v>
+      </c>
+      <c r="G772" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="773" customHeight="1" spans="1:7">
+      <c r="A773" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100307</v>
+      </c>
+      <c r="B773" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C773" s="2">
+        <v>7</v>
+      </c>
+      <c r="D773" s="2">
+        <v>1</v>
+      </c>
+      <c r="F773" s="2">
+        <v>3</v>
+      </c>
+      <c r="G773" s="12">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="774" customHeight="1" spans="1:7">
+      <c r="A774" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100308</v>
+      </c>
+      <c r="B774" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C774" s="2">
+        <v>8</v>
+      </c>
+      <c r="D774" s="2">
+        <v>1</v>
+      </c>
+      <c r="F774" s="2">
+        <v>3</v>
+      </c>
+      <c r="G774" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="775" customHeight="1" spans="1:7">
+      <c r="A775" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100401</v>
+      </c>
+      <c r="B775" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C775" s="2">
+        <v>1</v>
+      </c>
+      <c r="D775" s="2">
+        <v>1</v>
+      </c>
+      <c r="F775" s="2">
+        <v>4</v>
+      </c>
+      <c r="G775" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="776" customHeight="1" spans="1:7">
+      <c r="A776" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100402</v>
+      </c>
+      <c r="B776" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C776" s="2">
+        <v>2</v>
+      </c>
+      <c r="D776" s="2">
+        <v>1</v>
+      </c>
+      <c r="F776" s="2">
+        <v>4</v>
+      </c>
+      <c r="G776" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="777" customHeight="1" spans="1:7">
+      <c r="A777" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100403</v>
+      </c>
+      <c r="B777" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C777" s="2">
+        <v>3</v>
+      </c>
+      <c r="D777" s="2">
+        <v>1</v>
+      </c>
+      <c r="F777" s="2">
+        <v>4</v>
+      </c>
+      <c r="G777" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="778" customHeight="1" spans="1:7">
+      <c r="A778" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100404</v>
+      </c>
+      <c r="B778" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C778" s="2">
+        <v>4</v>
+      </c>
+      <c r="D778" s="2">
+        <v>1</v>
+      </c>
+      <c r="F778" s="2">
+        <v>4</v>
+      </c>
+      <c r="G778" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="779" customHeight="1" spans="1:7">
+      <c r="A779" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100405</v>
+      </c>
+      <c r="B779" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C779" s="2">
+        <v>5</v>
+      </c>
+      <c r="D779" s="2">
+        <v>1</v>
+      </c>
+      <c r="F779" s="2">
+        <v>4</v>
+      </c>
+      <c r="G779" s="12">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="780" customHeight="1" spans="1:7">
+      <c r="A780" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100406</v>
+      </c>
+      <c r="B780" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C780" s="2">
+        <v>6</v>
+      </c>
+      <c r="D780" s="2">
+        <v>1</v>
+      </c>
+      <c r="F780" s="2">
+        <v>4</v>
+      </c>
+      <c r="G780" s="12">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="781" customHeight="1" spans="1:7">
+      <c r="A781" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100407</v>
+      </c>
+      <c r="B781" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C781" s="2">
+        <v>7</v>
+      </c>
+      <c r="D781" s="2">
+        <v>1</v>
+      </c>
+      <c r="F781" s="2">
+        <v>4</v>
+      </c>
+      <c r="G781" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="782" customHeight="1" spans="1:7">
+      <c r="A782" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100408</v>
+      </c>
+      <c r="B782" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C782" s="2">
+        <v>8</v>
+      </c>
+      <c r="D782" s="2">
+        <v>1</v>
+      </c>
+      <c r="F782" s="2">
+        <v>4</v>
+      </c>
+      <c r="G782" s="12">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="783" customHeight="1" spans="1:7">
+      <c r="A783" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100501</v>
+      </c>
+      <c r="B783" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C783" s="2">
+        <v>1</v>
+      </c>
+      <c r="D783" s="2">
+        <v>1</v>
+      </c>
+      <c r="F783" s="2">
+        <v>5</v>
+      </c>
+      <c r="G783" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="784" customHeight="1" spans="1:7">
+      <c r="A784" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100502</v>
+      </c>
+      <c r="B784" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C784" s="2">
+        <v>2</v>
+      </c>
+      <c r="D784" s="2">
+        <v>1</v>
+      </c>
+      <c r="F784" s="2">
+        <v>5</v>
+      </c>
+      <c r="G784" s="12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="785" customHeight="1" spans="1:12">
+      <c r="A785" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100503</v>
+      </c>
+      <c r="B785" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C785" s="2">
+        <v>3</v>
+      </c>
+      <c r="D785" s="2">
+        <v>1</v>
+      </c>
+      <c r="F785" s="2">
+        <v>5</v>
+      </c>
+      <c r="G785" s="12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="786" customHeight="1" spans="1:12">
+      <c r="A786" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100504</v>
+      </c>
+      <c r="B786" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C786" s="2">
+        <v>4</v>
+      </c>
+      <c r="D786" s="2">
+        <v>1</v>
+      </c>
+      <c r="F786" s="2">
+        <v>5</v>
+      </c>
+      <c r="G786" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="787" customHeight="1" spans="1:12">
+      <c r="A787" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100505</v>
+      </c>
+      <c r="B787" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C787" s="2">
+        <v>5</v>
+      </c>
+      <c r="D787" s="2">
+        <v>1</v>
+      </c>
+      <c r="F787" s="2">
+        <v>5</v>
+      </c>
+      <c r="G787" s="12">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="788" customHeight="1" spans="1:12">
+      <c r="A788" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100506</v>
+      </c>
+      <c r="B788" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C788" s="2">
+        <v>6</v>
+      </c>
+      <c r="D788" s="2">
+        <v>1</v>
+      </c>
+      <c r="F788" s="2">
+        <v>5</v>
+      </c>
+      <c r="G788" s="12">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="789" customHeight="1" spans="1:12">
+      <c r="A789" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100507</v>
+      </c>
+      <c r="B789" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C789" s="2">
+        <v>7</v>
+      </c>
+      <c r="D789" s="2">
+        <v>1</v>
+      </c>
+      <c r="F789" s="2">
+        <v>5</v>
+      </c>
+      <c r="G789" s="12">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="790" customHeight="1" spans="1:12">
+      <c r="A790" s="3">
+        <f t="shared" si="31"/>
+        <v>1039100508</v>
+      </c>
+      <c r="B790" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C790" s="2">
+        <v>8</v>
+      </c>
+      <c r="D790" s="2">
+        <v>1</v>
+      </c>
+      <c r="F790" s="2">
+        <v>5</v>
+      </c>
+      <c r="G790" s="12">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="791" customHeight="1" spans="1:12">
+      <c r="A791" s="3">
+        <f t="shared" si="31"/>
+        <v>1039400310</v>
+      </c>
+      <c r="B791" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C791" s="2">
+        <v>10</v>
+      </c>
+      <c r="D791" s="2">
+        <v>4</v>
+      </c>
+      <c r="E791" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F791" s="2">
+        <v>3</v>
+      </c>
+      <c r="G791" s="12">
+        <v>0</v>
+      </c>
+      <c r="H791" s="12">
+        <v>30390001</v>
+      </c>
+    </row>
+    <row r="792" customHeight="1" spans="1:12">
+      <c r="A792" s="3">
+        <f t="shared" si="31"/>
+        <v>1039400410</v>
+      </c>
+      <c r="B792" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C792" s="2">
+        <v>10</v>
+      </c>
+      <c r="D792" s="2">
+        <v>4</v>
+      </c>
+      <c r="E792" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F792" s="2">
+        <v>4</v>
+      </c>
+      <c r="G792" s="12">
+        <v>0</v>
+      </c>
+      <c r="H792" s="12">
+        <v>30390002</v>
+      </c>
+    </row>
+    <row r="793" customHeight="1" spans="1:12">
+      <c r="A793" s="3">
+        <f t="shared" si="31"/>
+        <v>1039400510</v>
+      </c>
+      <c r="B793" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C793" s="2">
+        <v>10</v>
+      </c>
+      <c r="D793" s="2">
+        <v>4</v>
+      </c>
+      <c r="E793" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F793" s="2">
+        <v>5</v>
+      </c>
+      <c r="G793" s="12">
+        <v>0</v>
+      </c>
+      <c r="H793" s="12">
+        <v>30390003</v>
+      </c>
+    </row>
+    <row r="794" customHeight="1" spans="1:12">
+      <c r="A794" s="3">
+        <f t="shared" si="31"/>
+        <v>1039400111</v>
+      </c>
+      <c r="B794" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C794" s="2">
+        <v>11</v>
+      </c>
+      <c r="D794" s="2">
+        <v>4</v>
+      </c>
+      <c r="F794" s="2">
+        <v>1</v>
+      </c>
+      <c r="G794" s="12">
+        <v>0</v>
+      </c>
+      <c r="K794" s="2">
+        <v>103900101</v>
+      </c>
+      <c r="L794" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="795" customHeight="1" spans="1:12">
+      <c r="A795" s="3">
+        <f t="shared" si="31"/>
+        <v>1039400112</v>
+      </c>
+      <c r="B795" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C795" s="2">
+        <v>12</v>
+      </c>
+      <c r="D795" s="2">
+        <v>4</v>
+      </c>
+      <c r="F795" s="2">
+        <v>1</v>
+      </c>
+      <c r="G795" s="12">
+        <v>0</v>
+      </c>
+      <c r="K795" s="2">
+        <v>103900102</v>
+      </c>
+      <c r="L795" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="796" customHeight="1" spans="1:12">
+      <c r="A796" s="3">
+        <f t="shared" si="31"/>
+        <v>1039400113</v>
+      </c>
+      <c r="B796" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C796" s="2">
+        <v>13</v>
+      </c>
+      <c r="D796" s="2">
+        <v>4</v>
+      </c>
+      <c r="F796" s="2">
+        <v>1</v>
+      </c>
+      <c r="G796" s="12">
+        <v>0</v>
+      </c>
+      <c r="K796" s="2">
+        <v>103900103</v>
+      </c>
+      <c r="L796" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="797" customHeight="1" spans="1:12">
+      <c r="A797" s="3">
+        <f t="shared" si="31"/>
+        <v>1039400114</v>
+      </c>
+      <c r="B797" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C797" s="2">
+        <v>14</v>
+      </c>
+      <c r="D797" s="2">
+        <v>4</v>
+      </c>
+      <c r="F797" s="2">
+        <v>1</v>
+      </c>
+      <c r="G797" s="12">
+        <v>0</v>
+      </c>
+      <c r="K797" s="2">
+        <v>103900104</v>
+      </c>
+      <c r="L797" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="798" customHeight="1" spans="1:12">
+      <c r="A798" s="3">
+        <f>(B798)*10000+C798+F798*100+D798*100000</f>
+        <v>1039400105</v>
+      </c>
+      <c r="B798" s="2">
+        <v>103900</v>
+      </c>
+      <c r="C798" s="2">
+        <v>5</v>
+      </c>
+      <c r="D798" s="2">
+        <v>4</v>
+      </c>
+      <c r="E798" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F798" s="2">
+        <v>1</v>
+      </c>
+      <c r="G798" s="12">
+        <v>0</v>
+      </c>
+      <c r="H798" s="12">
+        <v>30390004</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L731" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L797" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">
@@ -25740,7 +27231,7 @@
   <conditionalFormatting sqref="A209:A469">
     <cfRule type="duplicateValues" dxfId="1" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A521:A731">
+  <conditionalFormatting sqref="A521:A798">
     <cfRule type="duplicateValues" dxfId="1" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B60">
@@ -25816,6 +27307,11 @@
   <conditionalFormatting sqref="E602:E605">
     <cfRule type="expression" dxfId="0" priority="4">
       <formula>MOD(#REF!,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G754:G760">
+    <cfRule type="expression" dxfId="0" priority="465">
+      <formula>MOD($B753,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H593:H599">
@@ -25914,7 +27410,7 @@
       <formula>MOD($B638,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A470:A520 A732:A1048576">
+  <conditionalFormatting sqref="A1:A47 A61:A86 A124:A134 A179:A208 A470:A520 A799:A1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="448"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L4">
@@ -25927,7 +27423,7 @@
       <formula>MOD($B41,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45 C46:C47 F46:F47 B61:L76 D77:E84 B179:L204 B205:G205 I205:K205 B206:G208 I206:K208 I209:I256 B258 B259:D268 F259:L268 B269:L270 B271:B279 D271:D279 F271:L279 B280:B281 D280:L281 B282:B290 D282:D290 F282:L290 B291:B292 D291:L292 B293:B296 D293:J296 B297:L307 B308:G309 I308:L309 B310:L319 B320:G321 I320:L321 B322:L343 B344:K344 B345:L345 B346:J350 B351:L383 B384:J387 B388:L421 B422:J425 B426:L439 B440:K446 B447:L453 B454:K457 B458:L516 B517:K520 B521:L548 B549:D549 F549:L549 B550:L591 B592 D592 I592:L592 B593:B594 D593:D594 I593:L594 B595 D595 I595:L595 B596:B601 D596:D601 I596:L601 B602 D602 F602:J602 B603:B604 D603:D604 F603:J604 B605 F605 H605:L605 B606:B607 F606:F607 I606:L607 B608 F608 I608:L608 B609:B610 D609:G610 I609:J610 B611 D611:J611 B612:L643 B644:K647 B648:L1048576">
+  <conditionalFormatting sqref="C41:G42 J41:J42 L41:L42 F45 C46:C47 F46:F47 B61:L76 D77:E84 B179:L204 B205:G205 I205:K205 B206:G208 I206:K208 I209:I256 B258 B259:D268 F259:L268 B269:L270 B271:B279 D271:D279 F271:L279 B280:B281 D280:L281 B282:B290 D282:D290 F282:L290 B291:B292 D291:L292 B293:B296 D293:J296 B297:L307 B308:G309 I308:L309 B310:L319 B320:G321 I320:L321 B322:L343 B344:K344 B345:L345 B346:J350 B351:L383 B384:J387 B388:L421 B422:J425 B426:L439 B440:K446 B447:L453 B454:K457 B458:L516 B517:K520 B521:L548 B549:D549 F549:L549 B550:L591 B592 D592 I592:L592 B593:B594 D593:D594 I593:L594 B595 D595 I595:L595 B596:B601 D596:D601 I596:L601 B602 D602 F602:J602 B603:B604 D603:D604 F603:J604 B605 F605 H605:L605 B606:B607 F606:F607 I606:L607 B608 F608 I608:L608 B609:B610 D609:G610 I609:J610 B611 D611:J611 B612:L643 B644:K647 B648:L752 B753:F753 H753:L753 B754:F759 H754:L759 B760:F760 H760:L760 B761:L1048576">
     <cfRule type="expression" dxfId="0" priority="446">
       <formula>MOD($B41,2)=1</formula>
     </cfRule>

--- a/slots/resources/sample/BaseElementReward.xlsx
+++ b/slots/resources/sample/BaseElementReward.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BaseElementReward" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$797</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElementReward!$B$1:$L$799</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="120">
   <si>
     <t>id</t>
   </si>
@@ -637,6 +637,39 @@
   <si>
     <t>转轴上出现符号5时在随机位置上改出1个wild</t>
   </si>
+  <si>
+    <t>1_19_31_43_55_66_77_88_99_110</t>
+  </si>
+  <si>
+    <t>2_20_32_44_56_67_78_89_100_111</t>
+  </si>
+  <si>
+    <t>3_21_33_45_57_68_79_90_101_112</t>
+  </si>
+  <si>
+    <t>4_22_34_46_58_69_80_91_102_113</t>
+  </si>
+  <si>
+    <t>5_23_35_47_59_70_81_92_103_114</t>
+  </si>
+  <si>
+    <t>6_24_36_48_60_71_82_93_104_115</t>
+  </si>
+  <si>
+    <t>7_25_37_49_61_72_83_94_105_116</t>
+  </si>
+  <si>
+    <t>8_26_38_50_62_73_84_95_106_117</t>
+  </si>
+  <si>
+    <t>9_27_39_51_63_74_85_96_107_118</t>
+  </si>
+  <si>
+    <t>10_28_40_52_64_75_86_97_108_119</t>
+  </si>
+  <si>
+    <t>11_29_41_53_65_76_87_98_109_120</t>
+  </si>
 </sst>
 </file>
 
@@ -896,12 +929,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1758,11 +1791,18 @@
     <cellStyle name="超链接 3" xfId="54"/>
     <cellStyle name="好_Sheet1" xfId="55"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="8" tint="0.799340800195319"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6014,12 +6054,12 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:L798"/>
+  <dimension ref="A1:L849"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="11"/>
     <col min="2" max="2" width="11" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14.125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="26.4666666666667" style="2" customWidth="1"/>
     <col min="4" max="4" width="11.25" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.875" style="2" customWidth="1"/>
     <col min="6" max="6" width="12.2166666666667" style="2" customWidth="1"/>
@@ -26176,7 +26216,7 @@
     </row>
     <row r="767" customHeight="1" spans="1:12">
       <c r="A767" s="3">
-        <f t="shared" ref="A767:A797" si="31">(B767)*10000+C767+F767*100+D767*100000</f>
+        <f t="shared" ref="A767:A798" si="31">(B767)*10000+C767+F767*100+D767*100000</f>
         <v>1039100301</v>
       </c>
       <c r="B767" s="2">
@@ -26869,7 +26909,7 @@
     </row>
     <row r="798" customHeight="1" spans="1:12">
       <c r="A798" s="3">
-        <f>(B798)*10000+C798+F798*100+D798*100000</f>
+        <f t="shared" si="31"/>
         <v>1039400105</v>
       </c>
       <c r="B798" s="2">
@@ -26894,782 +26934,1838 @@
         <v>30390004</v>
       </c>
     </row>
+    <row r="799" customHeight="1" spans="1:12">
+      <c r="A799" s="3">
+        <v>1016300301</v>
+      </c>
+      <c r="B799" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C799" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D799" s="2">
+        <v>3</v>
+      </c>
+      <c r="F799" s="2">
+        <v>3</v>
+      </c>
+      <c r="G799" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="800" customHeight="1" spans="1:12">
+      <c r="A800" s="3">
+        <v>1016300302</v>
+      </c>
+      <c r="B800" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C800" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D800" s="2">
+        <v>3</v>
+      </c>
+      <c r="F800" s="2">
+        <v>3</v>
+      </c>
+      <c r="G800" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="801" customHeight="1" spans="1:7">
+      <c r="A801" s="3">
+        <v>1016300303</v>
+      </c>
+      <c r="B801" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C801" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D801" s="2">
+        <v>3</v>
+      </c>
+      <c r="F801" s="2">
+        <v>3</v>
+      </c>
+      <c r="G801" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="802" customHeight="1" spans="1:7">
+      <c r="A802" s="3">
+        <v>1016300304</v>
+      </c>
+      <c r="B802" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C802" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D802" s="2">
+        <v>3</v>
+      </c>
+      <c r="F802" s="2">
+        <v>3</v>
+      </c>
+      <c r="G802" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="803" customHeight="1" spans="1:7">
+      <c r="A803" s="3">
+        <v>1016300305</v>
+      </c>
+      <c r="B803" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C803" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D803" s="2">
+        <v>3</v>
+      </c>
+      <c r="F803" s="2">
+        <v>3</v>
+      </c>
+      <c r="G803" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="804" customHeight="1" spans="1:7">
+      <c r="A804" s="3">
+        <v>1016300306</v>
+      </c>
+      <c r="B804" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C804" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D804" s="2">
+        <v>3</v>
+      </c>
+      <c r="F804" s="2">
+        <v>3</v>
+      </c>
+      <c r="G804" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="805" customHeight="1" spans="1:7">
+      <c r="A805" s="3">
+        <v>1016300307</v>
+      </c>
+      <c r="B805" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C805" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D805" s="2">
+        <v>3</v>
+      </c>
+      <c r="F805" s="2">
+        <v>3</v>
+      </c>
+      <c r="G805" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="806" customHeight="1" spans="1:7">
+      <c r="A806" s="3">
+        <v>1016300308</v>
+      </c>
+      <c r="B806" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C806" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D806" s="2">
+        <v>3</v>
+      </c>
+      <c r="F806" s="2">
+        <v>3</v>
+      </c>
+      <c r="G806" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="807" customHeight="1" spans="1:7">
+      <c r="A807" s="3">
+        <v>1016300309</v>
+      </c>
+      <c r="B807" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C807" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D807" s="2">
+        <v>3</v>
+      </c>
+      <c r="F807" s="2">
+        <v>3</v>
+      </c>
+      <c r="G807" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="808" customHeight="1" spans="1:7">
+      <c r="A808" s="3">
+        <v>1016300310</v>
+      </c>
+      <c r="B808" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C808" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D808" s="2">
+        <v>3</v>
+      </c>
+      <c r="F808" s="2">
+        <v>3</v>
+      </c>
+      <c r="G808" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="809" customHeight="1" spans="1:7">
+      <c r="A809" s="3">
+        <v>1016300311</v>
+      </c>
+      <c r="B809" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C809" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D809" s="2">
+        <v>3</v>
+      </c>
+      <c r="F809" s="2">
+        <v>3</v>
+      </c>
+      <c r="G809" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="810" customHeight="1" spans="1:7">
+      <c r="A810" s="3">
+        <v>1016300401</v>
+      </c>
+      <c r="B810" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C810" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D810" s="2">
+        <v>3</v>
+      </c>
+      <c r="F810" s="2">
+        <v>4</v>
+      </c>
+      <c r="G810" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="811" customHeight="1" spans="1:7">
+      <c r="A811" s="3">
+        <v>1016300402</v>
+      </c>
+      <c r="B811" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C811" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D811" s="2">
+        <v>3</v>
+      </c>
+      <c r="F811" s="2">
+        <v>4</v>
+      </c>
+      <c r="G811" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="812" customHeight="1" spans="1:7">
+      <c r="A812" s="3">
+        <v>1016300403</v>
+      </c>
+      <c r="B812" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C812" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D812" s="2">
+        <v>3</v>
+      </c>
+      <c r="F812" s="2">
+        <v>4</v>
+      </c>
+      <c r="G812" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="813" customHeight="1" spans="1:7">
+      <c r="A813" s="3">
+        <v>1016300404</v>
+      </c>
+      <c r="B813" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C813" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D813" s="2">
+        <v>3</v>
+      </c>
+      <c r="F813" s="2">
+        <v>4</v>
+      </c>
+      <c r="G813" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="814" customHeight="1" spans="1:7">
+      <c r="A814" s="3">
+        <v>1016300405</v>
+      </c>
+      <c r="B814" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C814" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D814" s="2">
+        <v>3</v>
+      </c>
+      <c r="F814" s="2">
+        <v>4</v>
+      </c>
+      <c r="G814" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="815" customHeight="1" spans="1:7">
+      <c r="A815" s="3">
+        <v>1016300406</v>
+      </c>
+      <c r="B815" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C815" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D815" s="2">
+        <v>3</v>
+      </c>
+      <c r="F815" s="2">
+        <v>4</v>
+      </c>
+      <c r="G815" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="816" customHeight="1" spans="1:7">
+      <c r="A816" s="3">
+        <v>1016300407</v>
+      </c>
+      <c r="B816" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C816" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D816" s="2">
+        <v>3</v>
+      </c>
+      <c r="F816" s="2">
+        <v>4</v>
+      </c>
+      <c r="G816" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="817" customHeight="1" spans="1:7">
+      <c r="A817" s="3">
+        <v>1016300408</v>
+      </c>
+      <c r="B817" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C817" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D817" s="2">
+        <v>3</v>
+      </c>
+      <c r="F817" s="2">
+        <v>4</v>
+      </c>
+      <c r="G817" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="818" customHeight="1" spans="1:7">
+      <c r="A818" s="3">
+        <v>1016300409</v>
+      </c>
+      <c r="B818" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C818" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D818" s="2">
+        <v>3</v>
+      </c>
+      <c r="F818" s="2">
+        <v>4</v>
+      </c>
+      <c r="G818" s="12">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="819" customHeight="1" spans="1:7">
+      <c r="A819" s="3">
+        <v>1016300410</v>
+      </c>
+      <c r="B819" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C819" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D819" s="2">
+        <v>3</v>
+      </c>
+      <c r="F819" s="2">
+        <v>4</v>
+      </c>
+      <c r="G819" s="12">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="820" customHeight="1" spans="1:7">
+      <c r="A820" s="3">
+        <v>1016300411</v>
+      </c>
+      <c r="B820" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C820" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D820" s="2">
+        <v>3</v>
+      </c>
+      <c r="F820" s="2">
+        <v>4</v>
+      </c>
+      <c r="G820" s="12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="821" customHeight="1" spans="1:7">
+      <c r="A821" s="3">
+        <v>1016300501</v>
+      </c>
+      <c r="B821" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C821" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D821" s="2">
+        <v>3</v>
+      </c>
+      <c r="F821" s="2">
+        <v>5</v>
+      </c>
+      <c r="G821" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="822" customHeight="1" spans="1:7">
+      <c r="A822" s="3">
+        <v>1016300502</v>
+      </c>
+      <c r="B822" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C822" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D822" s="2">
+        <v>3</v>
+      </c>
+      <c r="F822" s="2">
+        <v>5</v>
+      </c>
+      <c r="G822" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="823" customHeight="1" spans="1:7">
+      <c r="A823" s="3">
+        <v>1016300503</v>
+      </c>
+      <c r="B823" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C823" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D823" s="2">
+        <v>3</v>
+      </c>
+      <c r="F823" s="2">
+        <v>5</v>
+      </c>
+      <c r="G823" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="824" customHeight="1" spans="1:7">
+      <c r="A824" s="3">
+        <v>1016300504</v>
+      </c>
+      <c r="B824" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C824" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D824" s="2">
+        <v>3</v>
+      </c>
+      <c r="F824" s="2">
+        <v>5</v>
+      </c>
+      <c r="G824" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="825" customHeight="1" spans="1:7">
+      <c r="A825" s="3">
+        <v>1016300505</v>
+      </c>
+      <c r="B825" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C825" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D825" s="2">
+        <v>3</v>
+      </c>
+      <c r="F825" s="2">
+        <v>5</v>
+      </c>
+      <c r="G825" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="826" customHeight="1" spans="1:7">
+      <c r="A826" s="3">
+        <v>1016300506</v>
+      </c>
+      <c r="B826" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C826" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D826" s="2">
+        <v>3</v>
+      </c>
+      <c r="F826" s="2">
+        <v>5</v>
+      </c>
+      <c r="G826" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="827" customHeight="1" spans="1:7">
+      <c r="A827" s="3">
+        <v>1016300507</v>
+      </c>
+      <c r="B827" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C827" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D827" s="2">
+        <v>3</v>
+      </c>
+      <c r="F827" s="2">
+        <v>5</v>
+      </c>
+      <c r="G827" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="828" customHeight="1" spans="1:7">
+      <c r="A828" s="3">
+        <v>1016300508</v>
+      </c>
+      <c r="B828" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C828" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D828" s="2">
+        <v>3</v>
+      </c>
+      <c r="F828" s="2">
+        <v>5</v>
+      </c>
+      <c r="G828" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="829" customHeight="1" spans="1:7">
+      <c r="A829" s="3">
+        <v>1016300509</v>
+      </c>
+      <c r="B829" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C829" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D829" s="2">
+        <v>3</v>
+      </c>
+      <c r="F829" s="2">
+        <v>5</v>
+      </c>
+      <c r="G829" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="830" customHeight="1" spans="1:7">
+      <c r="A830" s="3">
+        <v>1016300510</v>
+      </c>
+      <c r="B830" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C830" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D830" s="2">
+        <v>3</v>
+      </c>
+      <c r="F830" s="2">
+        <v>5</v>
+      </c>
+      <c r="G830" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="831" customHeight="1" spans="1:7">
+      <c r="A831" s="3">
+        <v>1016300511</v>
+      </c>
+      <c r="B831" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C831" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D831" s="2">
+        <v>3</v>
+      </c>
+      <c r="F831" s="2">
+        <v>5</v>
+      </c>
+      <c r="G831" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="832" customHeight="1" spans="1:7">
+      <c r="A832" s="3">
+        <v>1016300601</v>
+      </c>
+      <c r="B832" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C832" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D832" s="2">
+        <v>3</v>
+      </c>
+      <c r="F832" s="2">
+        <v>6</v>
+      </c>
+      <c r="G832" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="833" customHeight="1" spans="1:12">
+      <c r="A833" s="3">
+        <v>1016300602</v>
+      </c>
+      <c r="B833" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C833" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D833" s="2">
+        <v>3</v>
+      </c>
+      <c r="F833" s="2">
+        <v>6</v>
+      </c>
+      <c r="G833" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="834" customHeight="1" spans="1:12">
+      <c r="A834" s="3">
+        <v>1016300603</v>
+      </c>
+      <c r="B834" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C834" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D834" s="2">
+        <v>3</v>
+      </c>
+      <c r="F834" s="2">
+        <v>6</v>
+      </c>
+      <c r="G834" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="835" customHeight="1" spans="1:12">
+      <c r="A835" s="3">
+        <v>1016300604</v>
+      </c>
+      <c r="B835" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C835" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D835" s="2">
+        <v>3</v>
+      </c>
+      <c r="F835" s="2">
+        <v>6</v>
+      </c>
+      <c r="G835" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="836" customHeight="1" spans="1:12">
+      <c r="A836" s="3">
+        <v>1016300605</v>
+      </c>
+      <c r="B836" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C836" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D836" s="2">
+        <v>3</v>
+      </c>
+      <c r="F836" s="2">
+        <v>6</v>
+      </c>
+      <c r="G836" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="837" customHeight="1" spans="1:12">
+      <c r="A837" s="3">
+        <v>1016300606</v>
+      </c>
+      <c r="B837" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C837" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D837" s="2">
+        <v>3</v>
+      </c>
+      <c r="F837" s="2">
+        <v>6</v>
+      </c>
+      <c r="G837" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="838" customHeight="1" spans="1:12">
+      <c r="A838" s="3">
+        <v>1016300607</v>
+      </c>
+      <c r="B838" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C838" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D838" s="2">
+        <v>3</v>
+      </c>
+      <c r="F838" s="2">
+        <v>6</v>
+      </c>
+      <c r="G838" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="839" customHeight="1" spans="1:12">
+      <c r="A839" s="3">
+        <v>1016300608</v>
+      </c>
+      <c r="B839" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C839" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D839" s="2">
+        <v>3</v>
+      </c>
+      <c r="F839" s="2">
+        <v>6</v>
+      </c>
+      <c r="G839" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="840" customHeight="1" spans="1:12">
+      <c r="A840" s="3">
+        <v>1016300609</v>
+      </c>
+      <c r="B840" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C840" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D840" s="2">
+        <v>3</v>
+      </c>
+      <c r="F840" s="2">
+        <v>6</v>
+      </c>
+      <c r="G840" s="12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="841" customHeight="1" spans="1:12">
+      <c r="A841" s="3">
+        <v>1016300610</v>
+      </c>
+      <c r="B841" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C841" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D841" s="2">
+        <v>3</v>
+      </c>
+      <c r="F841" s="2">
+        <v>6</v>
+      </c>
+      <c r="G841" s="12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="842" customHeight="1" spans="1:12">
+      <c r="A842" s="3">
+        <v>1016300611</v>
+      </c>
+      <c r="B842" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C842" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D842" s="2">
+        <v>3</v>
+      </c>
+      <c r="F842" s="2">
+        <v>6</v>
+      </c>
+      <c r="G842" s="12">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="843" customHeight="1" spans="1:12">
+      <c r="A843" s="3">
+        <v>1016400401</v>
+      </c>
+      <c r="B843" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C843" s="2">
+        <v>13</v>
+      </c>
+      <c r="D843" s="2">
+        <v>4</v>
+      </c>
+      <c r="E843" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F843" s="2">
+        <v>4</v>
+      </c>
+      <c r="G843" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="844" customHeight="1" spans="1:12">
+      <c r="A844" s="3">
+        <v>1016400501</v>
+      </c>
+      <c r="B844" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C844" s="2">
+        <v>13</v>
+      </c>
+      <c r="D844" s="2">
+        <v>4</v>
+      </c>
+      <c r="E844" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F844" s="2">
+        <v>5</v>
+      </c>
+      <c r="G844" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="845" customHeight="1" spans="1:12">
+      <c r="A845" s="3">
+        <v>1016400601</v>
+      </c>
+      <c r="B845" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C845" s="2">
+        <v>13</v>
+      </c>
+      <c r="D845" s="2">
+        <v>4</v>
+      </c>
+      <c r="E845" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F845" s="2">
+        <v>6</v>
+      </c>
+      <c r="G845" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="846" customHeight="1" spans="1:12">
+      <c r="A846" s="3">
+        <v>1016400115</v>
+      </c>
+      <c r="B846" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C846" s="2">
+        <v>15</v>
+      </c>
+      <c r="D846" s="2">
+        <v>4</v>
+      </c>
+      <c r="F846" s="2">
+        <v>1</v>
+      </c>
+      <c r="G846" s="12">
+        <v>0</v>
+      </c>
+      <c r="K846" s="2">
+        <v>101600101</v>
+      </c>
+      <c r="L846" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="847" customHeight="1" spans="1:12">
+      <c r="A847" s="3">
+        <v>1016400116</v>
+      </c>
+      <c r="B847" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C847" s="2">
+        <v>16</v>
+      </c>
+      <c r="D847" s="2">
+        <v>4</v>
+      </c>
+      <c r="F847" s="2">
+        <v>1</v>
+      </c>
+      <c r="G847" s="12">
+        <v>0</v>
+      </c>
+      <c r="K847" s="2">
+        <v>101600102</v>
+      </c>
+      <c r="L847" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="848" customHeight="1" spans="1:12">
+      <c r="A848" s="3">
+        <v>1016400117</v>
+      </c>
+      <c r="B848" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C848" s="2">
+        <v>17</v>
+      </c>
+      <c r="D848" s="2">
+        <v>4</v>
+      </c>
+      <c r="F848" s="2">
+        <v>1</v>
+      </c>
+      <c r="G848" s="12">
+        <v>0</v>
+      </c>
+      <c r="K848" s="2">
+        <v>101600103</v>
+      </c>
+      <c r="L848" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="849" customHeight="1" spans="1:12">
+      <c r="A849" s="3">
+        <v>1016400118</v>
+      </c>
+      <c r="B849" s="2">
+        <v>101600</v>
+      </c>
+      <c r="C849" s="2">
+        <v>18</v>
+      </c>
+      <c r="D849" s="2">
+        <v>4</v>
+      </c>
+      <c r="F849" s="2">
+        <v>1</v>
+      </c>
+      <c r="G849" s="12">
+        <v>0</v>
+      </c>
+      <c r="K849" s="2">
+        <v>101600104</v>
+      </c>
+      <c r="L849" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L797" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:L799" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="0" priority="147">
+    <cfRule type="expression" dxfId="0" priority="157">
       <formula>MOD($B43,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D85:E85">
-    <cfRule type="expression" dxfId="0" priority="173">
+    <cfRule type="expression" dxfId="0" priority="183">
       <formula>MOD($B85,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D86:E86">
-    <cfRule type="expression" dxfId="0" priority="138">
+    <cfRule type="expression" dxfId="0" priority="148">
       <formula>MOD($B86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105">
-    <cfRule type="duplicateValues" dxfId="1" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="129"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105:E105">
-    <cfRule type="expression" dxfId="0" priority="118">
+    <cfRule type="expression" dxfId="0" priority="128">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I105">
-    <cfRule type="expression" dxfId="0" priority="120">
+    <cfRule type="expression" dxfId="0" priority="130">
       <formula>MOD($B105,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A106">
-    <cfRule type="duplicateValues" dxfId="1" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D106:E106">
-    <cfRule type="expression" dxfId="0" priority="114">
+    <cfRule type="expression" dxfId="0" priority="124">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I106">
-    <cfRule type="expression" dxfId="0" priority="116">
+    <cfRule type="expression" dxfId="0" priority="126">
       <formula>MOD($B106,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="1" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D107:E107">
-    <cfRule type="expression" dxfId="0" priority="110">
+    <cfRule type="expression" dxfId="0" priority="120">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I107">
-    <cfRule type="expression" dxfId="0" priority="112">
+    <cfRule type="expression" dxfId="0" priority="122">
       <formula>MOD($B107,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108">
-    <cfRule type="duplicateValues" dxfId="1" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D108:E108">
-    <cfRule type="expression" dxfId="0" priority="106">
+    <cfRule type="expression" dxfId="0" priority="116">
       <formula>MOD($B108,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I108">
-    <cfRule type="expres